--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,13 +545,13 @@
         <v>9.999095000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02690831001496714</v>
+        <v>0.0269083100149671</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03126153445695321</v>
+        <v>0.0312615344569532</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.0453599977493286</v>
       </c>
       <c r="P2" t="n">
         <v>-0.0140984632923754</v>
@@ -603,16 +603,16 @@
         <v>20.30436</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006389639349886359</v>
+        <v>0.0063896393498863</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02803853081178438</v>
+        <v>0.0280385308117843</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.0453599977493286</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.01732146693754423</v>
+        <v>-0.0173214669375442</v>
       </c>
     </row>
     <row r="4">
@@ -661,16 +661,16 @@
         <v>3.563082</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03158151444945738</v>
+        <v>0.0315815144494573</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04009189936186644</v>
+        <v>0.0400918993618664</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.0453599977493286</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.005268098387462172</v>
+        <v>-0.0052680983874621</v>
       </c>
     </row>
     <row r="5">
@@ -719,16 +719,16 @@
         <v>24.200672</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01560677157597283</v>
+        <v>0.0156067715759728</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04995133901952142</v>
+        <v>0.0499513390195214</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.0453599977493286</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004591341270192811</v>
+        <v>0.0045913412701928</v>
       </c>
     </row>
     <row r="6">
@@ -777,16 +777,16 @@
         <v>10.557256</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03578849518810149</v>
+        <v>0.0357884951881014</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03953685476815398</v>
+        <v>0.0395368547681539</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.0453599977493286</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.005823142981174631</v>
+        <v>-0.0058231429811746</v>
       </c>
     </row>
     <row r="7">
@@ -835,16 +835,16 @@
         <v>7.0025306</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04640809443507588</v>
+        <v>0.0464080944350758</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06098165261382799</v>
+        <v>0.0609816526138279</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.0453599977493286</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01562165486449938</v>
+        <v>0.0156216548644993</v>
       </c>
     </row>
     <row r="8">
@@ -893,16 +893,16 @@
         <v>9.725002999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04027167782657739</v>
+        <v>0.0402716778265773</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04643821249430004</v>
+        <v>0.0464382124943</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.0453599977493286</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001078214744971426</v>
+        <v>0.0010782147449714</v>
       </c>
     </row>
     <row r="9">
@@ -951,16 +951,16 @@
         <v>7.379899</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03772207349720126</v>
+        <v>0.0377220734972012</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0467449501095157</v>
+        <v>0.0467449501095156</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.0453599977493286</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001384952360187083</v>
+        <v>0.001384952360187</v>
       </c>
     </row>
     <row r="10">
@@ -1012,13 +1012,535 @@
         <v>0.0317893710385178</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0618344709897611</v>
+        <v>0.061834470989761</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.0453599977493286</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01647447324043248</v>
+        <v>0.0164744732404324</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>301.54</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4428825362432</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.609970000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>36.506054</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31.37783</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.810397</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.02739271738409498</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.03186963586920475</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.04552000045776367</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.01365036458855892</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>490.33</v>
+      </c>
+      <c r="F12" t="n">
+        <v>799532384256</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H12" t="n">
+        <v>13.07661</v>
+      </c>
+      <c r="I12" t="n">
+        <v>163.98996</v>
+      </c>
+      <c r="J12" t="n">
+        <v>37.496723</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L12" t="n">
+        <v>21.34705</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.006097934044419065</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.02666899842962903</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.04552000045776367</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.01885100202813465</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>245.22</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2637858340864</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9.863810000000001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>31.64129</v>
+      </c>
+      <c r="J13" t="n">
+        <v>24.860577</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.551351</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.03160427371340021</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.04022432917380312</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.04552000045776367</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.005295671283960551</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>396.6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1877769453568</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="H14" t="n">
+        <v>19.35004</v>
+      </c>
+      <c r="I14" t="n">
+        <v>65.77114</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20.496082</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L14" t="n">
+        <v>24.882654</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.01520423600605144</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.04878981341401916</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.04552000045776367</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.003269812956255488</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>361.17</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4404444921856</v>
+      </c>
+      <c r="G15" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="H15" t="n">
+        <v>14.461</v>
+      </c>
+      <c r="I15" t="n">
+        <v>27.5492</v>
+      </c>
+      <c r="J15" t="n">
+        <v>24.97545</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L15" t="n">
+        <v>10.424771</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.0362986959049755</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.04003931666528228</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.04552000045776367</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.005480683792481393</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>585.39</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1485967589376</v>
+      </c>
+      <c r="G16" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="H16" t="n">
+        <v>36.16212</v>
+      </c>
+      <c r="I16" t="n">
+        <v>21.279171</v>
+      </c>
+      <c r="J16" t="n">
+        <v>16.187933</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L16" t="n">
+        <v>6.912667</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.04699431148465126</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.06177440680571927</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.04552000045776367</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.01625440634795559</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>411.74</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3058583732224</v>
+      </c>
+      <c r="G17" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>19.34238</v>
+      </c>
+      <c r="I17" t="n">
+        <v>24.508333</v>
+      </c>
+      <c r="J17" t="n">
+        <v>21.286934</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L17" t="n">
+        <v>9.609938</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.04080244814688881</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.04697717005877495</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.04552000045776367</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.001457169601011277</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="F18" t="n">
+        <v>347980398592</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.8415</v>
+      </c>
+      <c r="I18" t="n">
+        <v>26.658066</v>
+      </c>
+      <c r="J18" t="n">
+        <v>21.51243</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7.4212084</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.03751210067763795</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.04648475314617619</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.04552000045776367</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.0009647526884125138</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>208.64</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5053469425664</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12.68225</v>
+      </c>
+      <c r="I19" t="n">
+        <v>31.950994</v>
+      </c>
+      <c r="J19" t="n">
+        <v>16.45134</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L19" t="n">
+        <v>19.935497</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.03129792944785276</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.06078532400306749</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.04552000045776367</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.01526532354530381</v>
       </c>
     </row>
   </sheetData>
@@ -1120,12 +1642,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1139,51 +1661,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>365.76</v>
+        <v>361.17</v>
       </c>
       <c r="F2" t="n">
-        <v>4460419481600</v>
+        <v>4404444921856</v>
       </c>
       <c r="G2" t="n">
-        <v>13.09</v>
+        <v>13.11</v>
       </c>
       <c r="H2" t="n">
         <v>14.461</v>
       </c>
       <c r="I2" t="n">
-        <v>27.94194</v>
+        <v>27.5492</v>
       </c>
       <c r="J2" t="n">
-        <v>25.292856</v>
+        <v>24.97545</v>
       </c>
       <c r="K2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="L2" t="n">
-        <v>10.557256</v>
+        <v>10.424771</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03578849518810149</v>
+        <v>0.0362986959049755</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03953685476815398</v>
+        <v>0.04003931666528228</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.04552000045776367</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005823142981174631</v>
+        <v>-0.005480683792481393</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1197,51 +1719,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>416.67</v>
+        <v>411.74</v>
       </c>
       <c r="F3" t="n">
-        <v>3095206035456</v>
+        <v>3058583732224</v>
       </c>
       <c r="G3" t="n">
-        <v>16.78</v>
+        <v>16.8</v>
       </c>
       <c r="H3" t="n">
-        <v>19.34941</v>
+        <v>19.34238</v>
       </c>
       <c r="I3" t="n">
-        <v>24.831347</v>
+        <v>24.508333</v>
       </c>
       <c r="J3" t="n">
-        <v>21.53399</v>
+        <v>21.286934</v>
       </c>
       <c r="K3" t="n">
         <v>1.28</v>
       </c>
       <c r="L3" t="n">
-        <v>9.725002999999999</v>
+        <v>9.609938</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04027167782657739</v>
+        <v>0.04080244814688881</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04643821249430004</v>
+        <v>0.04697717005877495</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.04552000045776367</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001078214744971426</v>
+        <v>0.001457169601011277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1255,51 +1777,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>593</v>
+        <v>585.39</v>
       </c>
       <c r="F4" t="n">
-        <v>1505284980736</v>
+        <v>1485967589376</v>
       </c>
       <c r="G4" t="n">
-        <v>27.52</v>
+        <v>27.51</v>
       </c>
       <c r="H4" t="n">
         <v>36.16212</v>
       </c>
       <c r="I4" t="n">
-        <v>21.547964</v>
+        <v>21.279171</v>
       </c>
       <c r="J4" t="n">
-        <v>16.398375</v>
+        <v>16.187933</v>
       </c>
       <c r="K4" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="L4" t="n">
-        <v>7.0025306</v>
+        <v>6.912667</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04640809443507588</v>
+        <v>0.04699431148465126</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06098165261382799</v>
+        <v>0.06177440680571927</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.04552000045776367</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01562165486449938</v>
+        <v>0.01625440634795559</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1313,51 +1835,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>246.03</v>
+        <v>245.22</v>
       </c>
       <c r="F5" t="n">
-        <v>2646571745280</v>
+        <v>2637858340864</v>
       </c>
       <c r="G5" t="n">
-        <v>7.77</v>
+        <v>7.75</v>
       </c>
       <c r="H5" t="n">
         <v>9.863810000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>31.664093</v>
+        <v>31.64129</v>
       </c>
       <c r="J5" t="n">
-        <v>24.942696</v>
+        <v>24.860577</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.563082</v>
+        <v>3.551351</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03158151444945738</v>
+        <v>0.03160427371340021</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04009189936186644</v>
+        <v>0.04022432917380312</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.04552000045776367</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.005268098387462172</v>
+        <v>-0.005295671283960551</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1371,51 +1893,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>307.34</v>
+        <v>301.54</v>
       </c>
       <c r="F6" t="n">
-        <v>4514011676672</v>
+        <v>4428825362432</v>
       </c>
       <c r="G6" t="n">
-        <v>8.27</v>
+        <v>8.26</v>
       </c>
       <c r="H6" t="n">
-        <v>9.60792</v>
+        <v>9.609970000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>37.16324</v>
+        <v>36.506054</v>
       </c>
       <c r="J6" t="n">
-        <v>31.988194</v>
+        <v>31.37783</v>
       </c>
       <c r="K6" t="n">
         <v>2.47</v>
       </c>
       <c r="L6" t="n">
-        <v>9.999095000000001</v>
+        <v>9.810397</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02690831001496714</v>
+        <v>0.02739271738409498</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03126153445695321</v>
+        <v>0.03186963586920475</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.04552000045776367</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0140984632923754</v>
+        <v>-0.01365036458855892</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1429,51 +1951,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205.1</v>
+        <v>208.64</v>
       </c>
       <c r="F7" t="n">
-        <v>4967727366144</v>
+        <v>5053469425664</v>
       </c>
       <c r="G7" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="H7" t="n">
         <v>12.68225</v>
       </c>
       <c r="I7" t="n">
-        <v>31.457056</v>
+        <v>31.950994</v>
       </c>
       <c r="J7" t="n">
-        <v>16.172209</v>
+        <v>16.45134</v>
       </c>
       <c r="K7" t="n">
         <v>0.63</v>
       </c>
       <c r="L7" t="n">
-        <v>19.597254</v>
+        <v>19.935497</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0317893710385178</v>
+        <v>0.03129792944785276</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0618344709897611</v>
+        <v>0.06078532400306749</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.04552000045776367</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01647447324043248</v>
+        <v>0.01526532354530381</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1487,51 +2009,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>466.38</v>
+        <v>490.33</v>
       </c>
       <c r="F8" t="n">
-        <v>760479481856</v>
+        <v>799532384256</v>
       </c>
       <c r="G8" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="H8" t="n">
         <v>13.07661</v>
       </c>
       <c r="I8" t="n">
-        <v>156.50336</v>
+        <v>163.98996</v>
       </c>
       <c r="J8" t="n">
-        <v>35.665207</v>
+        <v>37.496723</v>
       </c>
       <c r="K8" t="n">
         <v>1.12</v>
       </c>
       <c r="L8" t="n">
-        <v>20.30436</v>
+        <v>21.34705</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006389639349886359</v>
+        <v>0.006097934044419065</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02803853081178438</v>
+        <v>0.02666899842962903</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.04552000045776367</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01732146693754423</v>
+        <v>-0.01885100202813465</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1545,51 +2067,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>385.73</v>
+        <v>396.6</v>
       </c>
       <c r="F9" t="n">
-        <v>1826303639552</v>
+        <v>1877769453568</v>
       </c>
       <c r="G9" t="n">
-        <v>6.02</v>
+        <v>6.03</v>
       </c>
       <c r="H9" t="n">
-        <v>19.26773</v>
+        <v>19.35004</v>
       </c>
       <c r="I9" t="n">
-        <v>64.07474999999999</v>
+        <v>65.77114</v>
       </c>
       <c r="J9" t="n">
-        <v>20.019484</v>
+        <v>20.496082</v>
       </c>
       <c r="K9" t="n">
         <v>0.71</v>
       </c>
       <c r="L9" t="n">
-        <v>24.200672</v>
+        <v>24.882654</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01560677157597283</v>
+        <v>0.01520423600605144</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04995133901952142</v>
+        <v>0.04878981341401916</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.04552000045776367</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004591341270192811</v>
+        <v>0.003269812956255488</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1603,10 +2125,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>82.18000000000001</v>
+        <v>82.64</v>
       </c>
       <c r="F10" t="n">
-        <v>346043416576</v>
+        <v>347980398592</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -1615,28 +2137,28 @@
         <v>3.8415</v>
       </c>
       <c r="I10" t="n">
-        <v>26.509678</v>
+        <v>26.658066</v>
       </c>
       <c r="J10" t="n">
-        <v>21.392685</v>
+        <v>21.51243</v>
       </c>
       <c r="K10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="L10" t="n">
-        <v>7.379899</v>
+        <v>7.4212084</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03772207349720126</v>
+        <v>0.03751210067763795</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0467449501095157</v>
+        <v>0.04648475314617619</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.04552000045776367</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001384952360187083</v>
+        <v>0.0009647526884125138</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1067,16 +1067,16 @@
         <v>9.810397</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02739271738409498</v>
+        <v>0.0273927173840949</v>
       </c>
       <c r="N11" t="n">
-        <v>0.03186963586920475</v>
+        <v>0.0318696358692047</v>
       </c>
       <c r="O11" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.0455200004577636</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.01365036458855892</v>
+        <v>-0.0136503645885589</v>
       </c>
     </row>
     <row r="12">
@@ -1125,16 +1125,16 @@
         <v>21.34705</v>
       </c>
       <c r="M12" t="n">
-        <v>0.006097934044419065</v>
+        <v>0.006097934044419</v>
       </c>
       <c r="N12" t="n">
-        <v>0.02666899842962903</v>
+        <v>0.026668998429629</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.0455200004577636</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.01885100202813465</v>
+        <v>-0.0188510020281346</v>
       </c>
     </row>
     <row r="13">
@@ -1183,16 +1183,16 @@
         <v>3.551351</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03160427371340021</v>
+        <v>0.0316042737134002</v>
       </c>
       <c r="N13" t="n">
-        <v>0.04022432917380312</v>
+        <v>0.0402243291738031</v>
       </c>
       <c r="O13" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.0455200004577636</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.005295671283960551</v>
+        <v>-0.0052956712839605</v>
       </c>
     </row>
     <row r="14">
@@ -1241,16 +1241,16 @@
         <v>24.882654</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01520423600605144</v>
+        <v>0.0152042360060514</v>
       </c>
       <c r="N14" t="n">
-        <v>0.04878981341401916</v>
+        <v>0.0487898134140191</v>
       </c>
       <c r="O14" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.0455200004577636</v>
       </c>
       <c r="P14" t="n">
-        <v>0.003269812956255488</v>
+        <v>0.0032698129562554</v>
       </c>
     </row>
     <row r="15">
@@ -1299,16 +1299,16 @@
         <v>10.424771</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0362986959049755</v>
+        <v>0.0362986959049754</v>
       </c>
       <c r="N15" t="n">
-        <v>0.04003931666528228</v>
+        <v>0.0400393166652822</v>
       </c>
       <c r="O15" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.0455200004577636</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.005480683792481393</v>
+        <v>-0.0054806837924813</v>
       </c>
     </row>
     <row r="16">
@@ -1357,16 +1357,16 @@
         <v>6.912667</v>
       </c>
       <c r="M16" t="n">
-        <v>0.04699431148465126</v>
+        <v>0.0469943114846512</v>
       </c>
       <c r="N16" t="n">
-        <v>0.06177440680571927</v>
+        <v>0.0617744068057192</v>
       </c>
       <c r="O16" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.0455200004577636</v>
       </c>
       <c r="P16" t="n">
-        <v>0.01625440634795559</v>
+        <v>0.0162544063479555</v>
       </c>
     </row>
     <row r="17">
@@ -1415,16 +1415,16 @@
         <v>9.609938</v>
       </c>
       <c r="M17" t="n">
-        <v>0.04080244814688881</v>
+        <v>0.0408024481468888</v>
       </c>
       <c r="N17" t="n">
-        <v>0.04697717005877495</v>
+        <v>0.0469771700587749</v>
       </c>
       <c r="O17" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.0455200004577636</v>
       </c>
       <c r="P17" t="n">
-        <v>0.001457169601011277</v>
+        <v>0.0014571696010112</v>
       </c>
     </row>
     <row r="18">
@@ -1473,16 +1473,16 @@
         <v>7.4212084</v>
       </c>
       <c r="M18" t="n">
-        <v>0.03751210067763795</v>
+        <v>0.0375121006776379</v>
       </c>
       <c r="N18" t="n">
-        <v>0.04648475314617619</v>
+        <v>0.0464847531461761</v>
       </c>
       <c r="O18" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.0455200004577636</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0009647526884125138</v>
+        <v>0.0009647526884125</v>
       </c>
     </row>
     <row r="19">
@@ -1531,16 +1531,538 @@
         <v>19.935497</v>
       </c>
       <c r="M19" t="n">
-        <v>0.03129792944785276</v>
+        <v>0.0312979294478527</v>
       </c>
       <c r="N19" t="n">
-        <v>0.06078532400306749</v>
+        <v>0.0607853240030674</v>
       </c>
       <c r="O19" t="n">
+        <v>0.0455200004577636</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.0152653235453038</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>290.55</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4267410980864</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H20" t="n">
+        <v>9.593220000000001</v>
+      </c>
+      <c r="I20" t="n">
+        <v>35.21818</v>
+      </c>
+      <c r="J20" t="n">
+        <v>30.287014</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9.452844000000001</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.02839442436757873</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.03301744966442953</v>
+      </c>
+      <c r="O20" t="n">
         <v>0.04552000045776367</v>
       </c>
-      <c r="P19" t="n">
-        <v>0.01526532354530381</v>
+      <c r="P20" t="n">
+        <v>-0.01250255079333414</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>475.505</v>
+      </c>
+      <c r="F21" t="n">
+        <v>775358709760</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>13.07661</v>
+      </c>
+      <c r="I21" t="n">
+        <v>158.50166</v>
+      </c>
+      <c r="J21" t="n">
+        <v>36.363018</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L21" t="n">
+        <v>20.701626</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.006309081923428776</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.02750046792357599</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.04552000045776367</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.01801953253418768</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>244.19</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2626778562560</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="H22" t="n">
+        <v>9.859959999999999</v>
+      </c>
+      <c r="I22" t="n">
+        <v>31.63083</v>
+      </c>
+      <c r="J22" t="n">
+        <v>24.765821</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3.5364344</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.03161472623776567</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.0403782300667513</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.04552000045776367</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.005141770391012372</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>392.16</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1865732718592</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>19.35046</v>
+      </c>
+      <c r="I23" t="n">
+        <v>65.36</v>
+      </c>
+      <c r="J23" t="n">
+        <v>20.266186</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L23" t="n">
+        <v>24.723152</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.01529987760097919</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.04934327825377397</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.04552000045776367</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.003823277796010299</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>362.29</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4418103148544</v>
+      </c>
+      <c r="G24" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="H24" t="n">
+        <v>14.4656</v>
+      </c>
+      <c r="I24" t="n">
+        <v>27.634632</v>
+      </c>
+      <c r="J24" t="n">
+        <v>25.044935</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L24" t="n">
+        <v>10.457098</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.03618648044384332</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.03992823428744928</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.04552000045776367</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.005591766170314393</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>584.59</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1483936890880</v>
+      </c>
+      <c r="G25" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="H25" t="n">
+        <v>36.16212</v>
+      </c>
+      <c r="I25" t="n">
+        <v>21.27329</v>
+      </c>
+      <c r="J25" t="n">
+        <v>16.165812</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L25" t="n">
+        <v>6.90322</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.04700730426452727</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.06185894387519458</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.04552000045776367</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.01633894341743091</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>403.41</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2996704903168</v>
+      </c>
+      <c r="G26" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="H26" t="n">
+        <v>19.34238</v>
+      </c>
+      <c r="I26" t="n">
+        <v>24.04112</v>
+      </c>
+      <c r="J26" t="n">
+        <v>20.856276</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L26" t="n">
+        <v>9.415516999999999</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.04159539922163556</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.04794720011898564</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.04552000045776367</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.002427199661221971</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>81.41</v>
+      </c>
+      <c r="F27" t="n">
+        <v>342801121280</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.8415</v>
+      </c>
+      <c r="I27" t="n">
+        <v>26.261292</v>
+      </c>
+      <c r="J27" t="n">
+        <v>21.192244</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L27" t="n">
+        <v>7.3107524</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.03807886009089793</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.0471870777545756</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.04552000045776367</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.001667077296811932</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>208.19</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5042570002432</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="H28" t="n">
+        <v>12.68225</v>
+      </c>
+      <c r="I28" t="n">
+        <v>31.833334</v>
+      </c>
+      <c r="J28" t="n">
+        <v>16.415857</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L28" t="n">
+        <v>19.8925</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.03141361256544502</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.06091671069695951</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.04552000045776367</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.01539671023919584</v>
       </c>
     </row>
   </sheetData>
@@ -1642,12 +2164,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1661,51 +2183,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>361.17</v>
+        <v>362.29</v>
       </c>
       <c r="F2" t="n">
-        <v>4404444921856</v>
+        <v>4418103148544</v>
       </c>
       <c r="G2" t="n">
         <v>13.11</v>
       </c>
       <c r="H2" t="n">
-        <v>14.461</v>
+        <v>14.4656</v>
       </c>
       <c r="I2" t="n">
-        <v>27.5492</v>
+        <v>27.634632</v>
       </c>
       <c r="J2" t="n">
-        <v>24.97545</v>
+        <v>25.044935</v>
       </c>
       <c r="K2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="L2" t="n">
-        <v>10.424771</v>
+        <v>10.457098</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0362986959049755</v>
+        <v>0.03618648044384332</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04003931666528228</v>
+        <v>0.03992823428744928</v>
       </c>
       <c r="O2" t="n">
         <v>0.04552000045776367</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005480683792481393</v>
+        <v>-0.005591766170314393</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1719,51 +2241,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>411.74</v>
+        <v>403.41</v>
       </c>
       <c r="F3" t="n">
-        <v>3058583732224</v>
+        <v>2996704903168</v>
       </c>
       <c r="G3" t="n">
-        <v>16.8</v>
+        <v>16.78</v>
       </c>
       <c r="H3" t="n">
         <v>19.34238</v>
       </c>
       <c r="I3" t="n">
-        <v>24.508333</v>
+        <v>24.04112</v>
       </c>
       <c r="J3" t="n">
-        <v>21.286934</v>
+        <v>20.856276</v>
       </c>
       <c r="K3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="L3" t="n">
-        <v>9.609938</v>
+        <v>9.415516999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04080244814688881</v>
+        <v>0.04159539922163556</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04697717005877495</v>
+        <v>0.04794720011898564</v>
       </c>
       <c r="O3" t="n">
         <v>0.04552000045776367</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001457169601011277</v>
+        <v>0.002427199661221971</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1777,51 +2299,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>585.39</v>
+        <v>584.59</v>
       </c>
       <c r="F4" t="n">
-        <v>1485967589376</v>
+        <v>1483936890880</v>
       </c>
       <c r="G4" t="n">
-        <v>27.51</v>
+        <v>27.48</v>
       </c>
       <c r="H4" t="n">
         <v>36.16212</v>
       </c>
       <c r="I4" t="n">
-        <v>21.279171</v>
+        <v>21.27329</v>
       </c>
       <c r="J4" t="n">
-        <v>16.187933</v>
+        <v>16.165812</v>
       </c>
       <c r="K4" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="L4" t="n">
-        <v>6.912667</v>
+        <v>6.90322</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04699431148465126</v>
+        <v>0.04700730426452727</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06177440680571927</v>
+        <v>0.06185894387519458</v>
       </c>
       <c r="O4" t="n">
         <v>0.04552000045776367</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01625440634795559</v>
+        <v>0.01633894341743091</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1835,51 +2357,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>245.22</v>
+        <v>244.19</v>
       </c>
       <c r="F5" t="n">
-        <v>2637858340864</v>
+        <v>2626778562560</v>
       </c>
       <c r="G5" t="n">
-        <v>7.75</v>
+        <v>7.72</v>
       </c>
       <c r="H5" t="n">
-        <v>9.863810000000001</v>
+        <v>9.859959999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>31.64129</v>
+        <v>31.63083</v>
       </c>
       <c r="J5" t="n">
-        <v>24.860577</v>
+        <v>24.765821</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.551351</v>
+        <v>3.5364344</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03160427371340021</v>
+        <v>0.03161472623776567</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04022432917380312</v>
+        <v>0.0403782300667513</v>
       </c>
       <c r="O5" t="n">
         <v>0.04552000045776367</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.005295671283960551</v>
+        <v>-0.005141770391012372</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1893,51 +2415,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>301.54</v>
+        <v>290.55</v>
       </c>
       <c r="F6" t="n">
-        <v>4428825362432</v>
+        <v>4267410980864</v>
       </c>
       <c r="G6" t="n">
-        <v>8.26</v>
+        <v>8.25</v>
       </c>
       <c r="H6" t="n">
-        <v>9.609970000000001</v>
+        <v>9.593220000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>36.506054</v>
+        <v>35.21818</v>
       </c>
       <c r="J6" t="n">
-        <v>31.37783</v>
+        <v>30.287014</v>
       </c>
       <c r="K6" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="L6" t="n">
-        <v>9.810397</v>
+        <v>9.452844000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02739271738409498</v>
+        <v>0.02839442436757873</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03186963586920475</v>
+        <v>0.03301744966442953</v>
       </c>
       <c r="O6" t="n">
         <v>0.04552000045776367</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01365036458855892</v>
+        <v>-0.01250255079333414</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1951,51 +2473,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208.64</v>
+        <v>208.19</v>
       </c>
       <c r="F7" t="n">
-        <v>5053469425664</v>
+        <v>5042570002432</v>
       </c>
       <c r="G7" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
       <c r="H7" t="n">
         <v>12.68225</v>
       </c>
       <c r="I7" t="n">
-        <v>31.950994</v>
+        <v>31.833334</v>
       </c>
       <c r="J7" t="n">
-        <v>16.45134</v>
+        <v>16.415857</v>
       </c>
       <c r="K7" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>19.935497</v>
+        <v>19.8925</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03129792944785276</v>
+        <v>0.03141361256544502</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06078532400306749</v>
+        <v>0.06091671069695951</v>
       </c>
       <c r="O7" t="n">
         <v>0.04552000045776367</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01526532354530381</v>
+        <v>0.01539671023919584</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2009,51 +2531,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>490.33</v>
+        <v>475.505</v>
       </c>
       <c r="F8" t="n">
-        <v>799532384256</v>
+        <v>775358709760</v>
       </c>
       <c r="G8" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>13.07661</v>
       </c>
       <c r="I8" t="n">
-        <v>163.98996</v>
+        <v>158.50166</v>
       </c>
       <c r="J8" t="n">
-        <v>37.496723</v>
+        <v>36.363018</v>
       </c>
       <c r="K8" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="L8" t="n">
-        <v>21.34705</v>
+        <v>20.701626</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006097934044419065</v>
+        <v>0.006309081923428776</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02666899842962903</v>
+        <v>0.02750046792357599</v>
       </c>
       <c r="O8" t="n">
         <v>0.04552000045776367</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01885100202813465</v>
+        <v>-0.01801953253418768</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2067,51 +2589,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>396.6</v>
+        <v>392.16</v>
       </c>
       <c r="F9" t="n">
-        <v>1877769453568</v>
+        <v>1865732718592</v>
       </c>
       <c r="G9" t="n">
-        <v>6.03</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>19.35004</v>
+        <v>19.35046</v>
       </c>
       <c r="I9" t="n">
-        <v>65.77114</v>
+        <v>65.36</v>
       </c>
       <c r="J9" t="n">
-        <v>20.496082</v>
+        <v>20.266186</v>
       </c>
       <c r="K9" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="L9" t="n">
-        <v>24.882654</v>
+        <v>24.723152</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01520423600605144</v>
+        <v>0.01529987760097919</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04878981341401916</v>
+        <v>0.04934327825377397</v>
       </c>
       <c r="O9" t="n">
         <v>0.04552000045776367</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003269812956255488</v>
+        <v>0.003823277796010299</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2125,10 +2647,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>82.64</v>
+        <v>81.41</v>
       </c>
       <c r="F10" t="n">
-        <v>347980398592</v>
+        <v>342801121280</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -2137,28 +2659,28 @@
         <v>3.8415</v>
       </c>
       <c r="I10" t="n">
-        <v>26.658066</v>
+        <v>26.261292</v>
       </c>
       <c r="J10" t="n">
-        <v>21.51243</v>
+        <v>21.192244</v>
       </c>
       <c r="K10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="L10" t="n">
-        <v>7.4212084</v>
+        <v>7.3107524</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03751210067763795</v>
+        <v>0.03807886009089793</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04648475314617619</v>
+        <v>0.0471870777545756</v>
       </c>
       <c r="O10" t="n">
         <v>0.04552000045776367</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0009647526884125138</v>
+        <v>0.001667077296811932</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1589,16 +1589,16 @@
         <v>9.452844000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0.02839442436757873</v>
+        <v>0.0283944243675787</v>
       </c>
       <c r="N20" t="n">
-        <v>0.03301744966442953</v>
+        <v>0.0330174496644295</v>
       </c>
       <c r="O20" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.0455200004577636</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.01250255079333414</v>
+        <v>-0.0125025507933341</v>
       </c>
     </row>
     <row r="21">
@@ -1647,16 +1647,16 @@
         <v>20.701626</v>
       </c>
       <c r="M21" t="n">
-        <v>0.006309081923428776</v>
+        <v>0.0063090819234287</v>
       </c>
       <c r="N21" t="n">
-        <v>0.02750046792357599</v>
+        <v>0.0275004679235759</v>
       </c>
       <c r="O21" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.0455200004577636</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.01801953253418768</v>
+        <v>-0.0180195325341876</v>
       </c>
     </row>
     <row r="22">
@@ -1705,16 +1705,16 @@
         <v>3.5364344</v>
       </c>
       <c r="M22" t="n">
-        <v>0.03161472623776567</v>
+        <v>0.0316147262377656</v>
       </c>
       <c r="N22" t="n">
         <v>0.0403782300667513</v>
       </c>
       <c r="O22" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.0455200004577636</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.005141770391012372</v>
+        <v>-0.0051417703910123</v>
       </c>
     </row>
     <row r="23">
@@ -1763,16 +1763,16 @@
         <v>24.723152</v>
       </c>
       <c r="M23" t="n">
-        <v>0.01529987760097919</v>
+        <v>0.0152998776009791</v>
       </c>
       <c r="N23" t="n">
-        <v>0.04934327825377397</v>
+        <v>0.0493432782537739</v>
       </c>
       <c r="O23" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.0455200004577636</v>
       </c>
       <c r="P23" t="n">
-        <v>0.003823277796010299</v>
+        <v>0.0038232777960102</v>
       </c>
     </row>
     <row r="24">
@@ -1821,16 +1821,16 @@
         <v>10.457098</v>
       </c>
       <c r="M24" t="n">
-        <v>0.03618648044384332</v>
+        <v>0.0361864804438433</v>
       </c>
       <c r="N24" t="n">
-        <v>0.03992823428744928</v>
+        <v>0.0399282342874492</v>
       </c>
       <c r="O24" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.0455200004577636</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.005591766170314393</v>
+        <v>-0.0055917661703143</v>
       </c>
     </row>
     <row r="25">
@@ -1879,16 +1879,16 @@
         <v>6.90322</v>
       </c>
       <c r="M25" t="n">
-        <v>0.04700730426452727</v>
+        <v>0.0470073042645272</v>
       </c>
       <c r="N25" t="n">
-        <v>0.06185894387519458</v>
+        <v>0.0618589438751945</v>
       </c>
       <c r="O25" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.0455200004577636</v>
       </c>
       <c r="P25" t="n">
-        <v>0.01633894341743091</v>
+        <v>0.0163389434174309</v>
       </c>
     </row>
     <row r="26">
@@ -1937,16 +1937,16 @@
         <v>9.415516999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>0.04159539922163556</v>
+        <v>0.0415953992216355</v>
       </c>
       <c r="N26" t="n">
-        <v>0.04794720011898564</v>
+        <v>0.0479472001189856</v>
       </c>
       <c r="O26" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.0455200004577636</v>
       </c>
       <c r="P26" t="n">
-        <v>0.002427199661221971</v>
+        <v>0.0024271996612219</v>
       </c>
     </row>
     <row r="27">
@@ -1995,16 +1995,16 @@
         <v>7.3107524</v>
       </c>
       <c r="M27" t="n">
-        <v>0.03807886009089793</v>
+        <v>0.0380788600908979</v>
       </c>
       <c r="N27" t="n">
         <v>0.0471870777545756</v>
       </c>
       <c r="O27" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.0455200004577636</v>
       </c>
       <c r="P27" t="n">
-        <v>0.001667077296811932</v>
+        <v>0.0016670772968119</v>
       </c>
     </row>
     <row r="28">
@@ -2053,16 +2053,538 @@
         <v>19.8925</v>
       </c>
       <c r="M28" t="n">
-        <v>0.03141361256544502</v>
+        <v>0.031413612565445</v>
       </c>
       <c r="N28" t="n">
-        <v>0.06091671069695951</v>
+        <v>0.0609167106969595</v>
       </c>
       <c r="O28" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.0455200004577636</v>
       </c>
       <c r="P28" t="n">
-        <v>0.01539671023919584</v>
+        <v>0.0153967102391958</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>291.58</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4282539048960</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H29" t="n">
+        <v>9.595079999999999</v>
+      </c>
+      <c r="I29" t="n">
+        <v>35.34303</v>
+      </c>
+      <c r="J29" t="n">
+        <v>30.388489</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L29" t="n">
+        <v>9.486355</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.02829412168187119</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.03290719528088346</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.04546000003814697</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-0.01255280475726351</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>452.4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>737683701760</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H30" t="n">
+        <v>13.07661</v>
+      </c>
+      <c r="I30" t="n">
+        <v>151.30435</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.596123</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L30" t="n">
+        <v>19.695724</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.006609195402298851</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.02890497347480106</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.04546000003814697</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-0.01655502656334591</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>238</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2560192151552</v>
+      </c>
+      <c r="G31" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="H31" t="n">
+        <v>9.859959999999999</v>
+      </c>
+      <c r="I31" t="n">
+        <v>31.648935</v>
+      </c>
+      <c r="J31" t="n">
+        <v>24.13803</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L31" t="n">
+        <v>3.446789</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.03159663865546218</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.04142840336134453</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.04546000003814697</v>
+      </c>
+      <c r="P31" t="n">
+        <v>-0.004031596676802439</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>372.1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1770295656448</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="H32" t="n">
+        <v>19.35046</v>
+      </c>
+      <c r="I32" t="n">
+        <v>61.708126</v>
+      </c>
+      <c r="J32" t="n">
+        <v>19.229517</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L32" t="n">
+        <v>23.4585</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.01620532115022843</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.052003386186509</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.04546000003814697</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.006543386148362029</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>353.32</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4308714389504</v>
+      </c>
+      <c r="G33" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="H33" t="n">
+        <v>14.48061</v>
+      </c>
+      <c r="I33" t="n">
+        <v>26.95042</v>
+      </c>
+      <c r="J33" t="n">
+        <v>24.399525</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L33" t="n">
+        <v>10.198189</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.03710517378014264</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.04098440507188951</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.04546000003814697</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-0.004475594966257462</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>570.98</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1449388933120</v>
+      </c>
+      <c r="G34" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="H34" t="n">
+        <v>36.16212</v>
+      </c>
+      <c r="I34" t="n">
+        <v>20.747818</v>
+      </c>
+      <c r="J34" t="n">
+        <v>15.78945</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L34" t="n">
+        <v>6.7425046</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.04819783530071105</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.0633334267399909</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.04546000003814697</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.01787342670184393</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>397.36</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2951762673664</v>
+      </c>
+      <c r="G35" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="H35" t="n">
+        <v>19.39206</v>
+      </c>
+      <c r="I35" t="n">
+        <v>23.63831</v>
+      </c>
+      <c r="J35" t="n">
+        <v>20.49086</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L35" t="n">
+        <v>9.274311000000001</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.04230420777129051</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.04880224481578418</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.04546000003814697</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.003342244777637206</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>82</v>
+      </c>
+      <c r="F36" t="n">
+        <v>345285492736</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.84196</v>
+      </c>
+      <c r="I36" t="n">
+        <v>26.451614</v>
+      </c>
+      <c r="J36" t="n">
+        <v>21.343273</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L36" t="n">
+        <v>7.363735</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.03780487804878049</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.04685317073170731</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.04546000003814697</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.00139317069356034</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>200.42</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4854372630528</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H37" t="n">
+        <v>12.72715</v>
+      </c>
+      <c r="I37" t="n">
+        <v>30.692188</v>
+      </c>
+      <c r="J37" t="n">
+        <v>15.7474375</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L37" t="n">
+        <v>19.150078</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.032581578684762</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.06350239497056183</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.04546000003814697</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.01804239493241486</v>
       </c>
     </row>
   </sheetData>
@@ -2164,12 +2686,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2183,51 +2705,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>362.29</v>
+        <v>353.32</v>
       </c>
       <c r="F2" t="n">
-        <v>4418103148544</v>
+        <v>4308714389504</v>
       </c>
       <c r="G2" t="n">
         <v>13.11</v>
       </c>
       <c r="H2" t="n">
-        <v>14.4656</v>
+        <v>14.48061</v>
       </c>
       <c r="I2" t="n">
-        <v>27.634632</v>
+        <v>26.95042</v>
       </c>
       <c r="J2" t="n">
-        <v>25.044935</v>
+        <v>24.399525</v>
       </c>
       <c r="K2" t="n">
         <v>1.42</v>
       </c>
       <c r="L2" t="n">
-        <v>10.457098</v>
+        <v>10.198189</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03618648044384332</v>
+        <v>0.03710517378014264</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03992823428744928</v>
+        <v>0.04098440507188951</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.04546000003814697</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005591766170314393</v>
+        <v>-0.004475594966257462</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2241,51 +2763,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>403.41</v>
+        <v>397.36</v>
       </c>
       <c r="F3" t="n">
-        <v>2996704903168</v>
+        <v>2951762673664</v>
       </c>
       <c r="G3" t="n">
-        <v>16.78</v>
+        <v>16.81</v>
       </c>
       <c r="H3" t="n">
-        <v>19.34238</v>
+        <v>19.39206</v>
       </c>
       <c r="I3" t="n">
-        <v>24.04112</v>
+        <v>23.63831</v>
       </c>
       <c r="J3" t="n">
-        <v>20.856276</v>
+        <v>20.49086</v>
       </c>
       <c r="K3" t="n">
         <v>1.27</v>
       </c>
       <c r="L3" t="n">
-        <v>9.415516999999999</v>
+        <v>9.274311000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04159539922163556</v>
+        <v>0.04230420777129051</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04794720011898564</v>
+        <v>0.04880224481578418</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.04546000003814697</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002427199661221971</v>
+        <v>0.003342244777637206</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2299,51 +2821,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>584.59</v>
+        <v>570.98</v>
       </c>
       <c r="F4" t="n">
-        <v>1483936890880</v>
+        <v>1449388933120</v>
       </c>
       <c r="G4" t="n">
-        <v>27.48</v>
+        <v>27.52</v>
       </c>
       <c r="H4" t="n">
         <v>36.16212</v>
       </c>
       <c r="I4" t="n">
-        <v>21.27329</v>
+        <v>20.747818</v>
       </c>
       <c r="J4" t="n">
-        <v>16.165812</v>
+        <v>15.78945</v>
       </c>
       <c r="K4" t="n">
         <v>0.85</v>
       </c>
       <c r="L4" t="n">
-        <v>6.90322</v>
+        <v>6.7425046</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04700730426452727</v>
+        <v>0.04819783530071105</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06185894387519458</v>
+        <v>0.0633334267399909</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.04546000003814697</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01633894341743091</v>
+        <v>0.01787342670184393</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2357,51 +2879,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>244.19</v>
+        <v>238</v>
       </c>
       <c r="F5" t="n">
-        <v>2626778562560</v>
+        <v>2560192151552</v>
       </c>
       <c r="G5" t="n">
-        <v>7.72</v>
+        <v>7.52</v>
       </c>
       <c r="H5" t="n">
         <v>9.859959999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>31.63083</v>
+        <v>31.648935</v>
       </c>
       <c r="J5" t="n">
-        <v>24.765821</v>
+        <v>24.13803</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5364344</v>
+        <v>3.446789</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03161472623776567</v>
+        <v>0.03159663865546218</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0403782300667513</v>
+        <v>0.04142840336134453</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.04546000003814697</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.005141770391012372</v>
+        <v>-0.004031596676802439</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2415,51 +2937,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>290.55</v>
+        <v>291.58</v>
       </c>
       <c r="F6" t="n">
-        <v>4267410980864</v>
+        <v>4282539048960</v>
       </c>
       <c r="G6" t="n">
         <v>8.25</v>
       </c>
       <c r="H6" t="n">
-        <v>9.593220000000001</v>
+        <v>9.595079999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>35.21818</v>
+        <v>35.34303</v>
       </c>
       <c r="J6" t="n">
-        <v>30.287014</v>
+        <v>30.388489</v>
       </c>
       <c r="K6" t="n">
         <v>2.42</v>
       </c>
       <c r="L6" t="n">
-        <v>9.452844000000001</v>
+        <v>9.486355</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02839442436757873</v>
+        <v>0.02829412168187119</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03301744966442953</v>
+        <v>0.03290719528088346</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.04546000003814697</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01250255079333414</v>
+        <v>-0.01255280475726351</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2473,51 +2995,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208.19</v>
+        <v>200.42</v>
       </c>
       <c r="F7" t="n">
-        <v>5042570002432</v>
+        <v>4854372630528</v>
       </c>
       <c r="G7" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
       <c r="H7" t="n">
-        <v>12.68225</v>
+        <v>12.72715</v>
       </c>
       <c r="I7" t="n">
-        <v>31.833334</v>
+        <v>30.692188</v>
       </c>
       <c r="J7" t="n">
-        <v>16.415857</v>
+        <v>15.7474375</v>
       </c>
       <c r="K7" t="n">
         <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>19.8925</v>
+        <v>19.150078</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03141361256544502</v>
+        <v>0.032581578684762</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06091671069695951</v>
+        <v>0.06350239497056183</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.04546000003814697</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01539671023919584</v>
+        <v>0.01804239493241486</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2531,51 +3053,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>475.505</v>
+        <v>452.4</v>
       </c>
       <c r="F8" t="n">
-        <v>775358709760</v>
+        <v>737683701760</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="H8" t="n">
         <v>13.07661</v>
       </c>
       <c r="I8" t="n">
-        <v>158.50166</v>
+        <v>151.30435</v>
       </c>
       <c r="J8" t="n">
-        <v>36.363018</v>
+        <v>34.596123</v>
       </c>
       <c r="K8" t="n">
         <v>1.14</v>
       </c>
       <c r="L8" t="n">
-        <v>20.701626</v>
+        <v>19.695724</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006309081923428776</v>
+        <v>0.006609195402298851</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02750046792357599</v>
+        <v>0.02890497347480106</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.04546000003814697</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01801953253418768</v>
+        <v>-0.01655502656334591</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2589,51 +3111,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392.16</v>
+        <v>372.1</v>
       </c>
       <c r="F9" t="n">
-        <v>1865732718592</v>
+        <v>1770295656448</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>6.03</v>
       </c>
       <c r="H9" t="n">
         <v>19.35046</v>
       </c>
       <c r="I9" t="n">
-        <v>65.36</v>
+        <v>61.708126</v>
       </c>
       <c r="J9" t="n">
-        <v>20.266186</v>
+        <v>19.229517</v>
       </c>
       <c r="K9" t="n">
         <v>0.72</v>
       </c>
       <c r="L9" t="n">
-        <v>24.723152</v>
+        <v>23.4585</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01529987760097919</v>
+        <v>0.01620532115022843</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04934327825377397</v>
+        <v>0.052003386186509</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.04546000003814697</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003823277796010299</v>
+        <v>0.006543386148362029</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2647,40 +3169,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>81.41</v>
+        <v>82</v>
       </c>
       <c r="F10" t="n">
-        <v>342801121280</v>
+        <v>345285492736</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8415</v>
+        <v>3.84196</v>
       </c>
       <c r="I10" t="n">
-        <v>26.261292</v>
+        <v>26.451614</v>
       </c>
       <c r="J10" t="n">
-        <v>21.192244</v>
+        <v>21.343273</v>
       </c>
       <c r="K10" t="n">
         <v>1.62</v>
       </c>
       <c r="L10" t="n">
-        <v>7.3107524</v>
+        <v>7.363735</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03807886009089793</v>
+        <v>0.03780487804878049</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0471870777545756</v>
+        <v>0.04685317073170731</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.04546000003814697</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001667077296811932</v>
+        <v>0.00139317069356034</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2111,16 +2111,16 @@
         <v>9.486355</v>
       </c>
       <c r="M29" t="n">
-        <v>0.02829412168187119</v>
+        <v>0.0282941216818711</v>
       </c>
       <c r="N29" t="n">
-        <v>0.03290719528088346</v>
+        <v>0.0329071952808834</v>
       </c>
       <c r="O29" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.0454600000381469</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.01255280475726351</v>
+        <v>-0.0125528047572635</v>
       </c>
     </row>
     <row r="30">
@@ -2169,16 +2169,16 @@
         <v>19.695724</v>
       </c>
       <c r="M30" t="n">
-        <v>0.006609195402298851</v>
+        <v>0.0066091954022988</v>
       </c>
       <c r="N30" t="n">
-        <v>0.02890497347480106</v>
+        <v>0.028904973474801</v>
       </c>
       <c r="O30" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.0454600000381469</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.01655502656334591</v>
+        <v>-0.0165550265633459</v>
       </c>
     </row>
     <row r="31">
@@ -2227,16 +2227,16 @@
         <v>3.446789</v>
       </c>
       <c r="M31" t="n">
-        <v>0.03159663865546218</v>
+        <v>0.0315966386554621</v>
       </c>
       <c r="N31" t="n">
-        <v>0.04142840336134453</v>
+        <v>0.0414284033613445</v>
       </c>
       <c r="O31" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.0454600000381469</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.004031596676802439</v>
+        <v>-0.0040315966768024</v>
       </c>
     </row>
     <row r="32">
@@ -2285,16 +2285,16 @@
         <v>23.4585</v>
       </c>
       <c r="M32" t="n">
-        <v>0.01620532115022843</v>
+        <v>0.0162053211502284</v>
       </c>
       <c r="N32" t="n">
         <v>0.052003386186509</v>
       </c>
       <c r="O32" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.0454600000381469</v>
       </c>
       <c r="P32" t="n">
-        <v>0.006543386148362029</v>
+        <v>0.006543386148362</v>
       </c>
     </row>
     <row r="33">
@@ -2343,16 +2343,16 @@
         <v>10.198189</v>
       </c>
       <c r="M33" t="n">
-        <v>0.03710517378014264</v>
+        <v>0.0371051737801426</v>
       </c>
       <c r="N33" t="n">
-        <v>0.04098440507188951</v>
+        <v>0.0409844050718895</v>
       </c>
       <c r="O33" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.0454600000381469</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.004475594966257462</v>
+        <v>-0.0044755949662574</v>
       </c>
     </row>
     <row r="34">
@@ -2401,16 +2401,16 @@
         <v>6.7425046</v>
       </c>
       <c r="M34" t="n">
-        <v>0.04819783530071105</v>
+        <v>0.048197835300711</v>
       </c>
       <c r="N34" t="n">
         <v>0.0633334267399909</v>
       </c>
       <c r="O34" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.0454600000381469</v>
       </c>
       <c r="P34" t="n">
-        <v>0.01787342670184393</v>
+        <v>0.0178734267018439</v>
       </c>
     </row>
     <row r="35">
@@ -2459,16 +2459,16 @@
         <v>9.274311000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>0.04230420777129051</v>
+        <v>0.0423042077712905</v>
       </c>
       <c r="N35" t="n">
-        <v>0.04880224481578418</v>
+        <v>0.0488022448157841</v>
       </c>
       <c r="O35" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.0454600000381469</v>
       </c>
       <c r="P35" t="n">
-        <v>0.003342244777637206</v>
+        <v>0.0033422447776372</v>
       </c>
     </row>
     <row r="36">
@@ -2517,16 +2517,16 @@
         <v>7.363735</v>
       </c>
       <c r="M36" t="n">
-        <v>0.03780487804878049</v>
+        <v>0.0378048780487804</v>
       </c>
       <c r="N36" t="n">
-        <v>0.04685317073170731</v>
+        <v>0.0468531707317073</v>
       </c>
       <c r="O36" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.0454600000381469</v>
       </c>
       <c r="P36" t="n">
-        <v>0.00139317069356034</v>
+        <v>0.0013931706935603</v>
       </c>
     </row>
     <row r="37">
@@ -2578,13 +2578,535 @@
         <v>0.032581578684762</v>
       </c>
       <c r="N37" t="n">
-        <v>0.06350239497056183</v>
+        <v>0.0635023949705618</v>
       </c>
       <c r="O37" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.0454600000381469</v>
       </c>
       <c r="P37" t="n">
-        <v>0.01804239493241486</v>
+        <v>0.0180423949324148</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>295.63</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4342023192576</v>
+      </c>
+      <c r="G38" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H38" t="n">
+        <v>9.595079999999999</v>
+      </c>
+      <c r="I38" t="n">
+        <v>35.83394</v>
+      </c>
+      <c r="J38" t="n">
+        <v>30.810581</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="L38" t="n">
+        <v>9.618119</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.02790650475256232</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.03245638128742009</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.04462999820709228</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-0.0121736169196722</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>488.45</v>
+      </c>
+      <c r="F39" t="n">
+        <v>796466872320</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H39" t="n">
+        <v>13.1035</v>
+      </c>
+      <c r="I39" t="n">
+        <v>163.9094</v>
+      </c>
+      <c r="J39" t="n">
+        <v>37.2763</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L39" t="n">
+        <v>21.265202</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.006100931518067356</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.02682669669362268</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.04462999820709228</v>
+      </c>
+      <c r="P39" t="n">
+        <v>-0.0178033015134696</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>241.51</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2597949538304</v>
+      </c>
+      <c r="G40" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="H40" t="n">
+        <v>9.859959999999999</v>
+      </c>
+      <c r="I40" t="n">
+        <v>31.652685</v>
+      </c>
+      <c r="J40" t="n">
+        <v>24.494015</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3.497622</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.03159289470415304</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.04082630118835659</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.04462999820709228</v>
+      </c>
+      <c r="P40" t="n">
+        <v>-0.003803697018735695</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>385.57</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1834380296192</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H41" t="n">
+        <v>19.35046</v>
+      </c>
+      <c r="I41" t="n">
+        <v>64.15474</v>
+      </c>
+      <c r="J41" t="n">
+        <v>19.925625</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L41" t="n">
+        <v>24.307697</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.015587312290894</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.05018663277744639</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.04462999820709228</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.005556634570354102</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>356.56</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4348226043904</v>
+      </c>
+      <c r="G42" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="H42" t="n">
+        <v>14.48061</v>
+      </c>
+      <c r="I42" t="n">
+        <v>27.176828</v>
+      </c>
+      <c r="J42" t="n">
+        <v>24.623272</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L42" t="n">
+        <v>10.291708</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.03679605115548575</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.04061198676239623</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.04462999820709228</v>
+      </c>
+      <c r="P42" t="n">
+        <v>-0.004018011444696053</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>568.4299999999999</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1442915942400</v>
+      </c>
+      <c r="G43" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="H43" t="n">
+        <v>36.16212</v>
+      </c>
+      <c r="I43" t="n">
+        <v>20.662668</v>
+      </c>
+      <c r="J43" t="n">
+        <v>15.718934</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L43" t="n">
+        <v>6.7123923</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.04839646042608589</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.06361754305719262</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.04462999820709228</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.01898754485010034</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>390.34</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2899615154176</v>
+      </c>
+      <c r="G44" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="H44" t="n">
+        <v>19.3459</v>
+      </c>
+      <c r="I44" t="n">
+        <v>23.262217</v>
+      </c>
+      <c r="J44" t="n">
+        <v>20.176886</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L44" t="n">
+        <v>9.110466000000001</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.04298816416457448</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.04956166419019317</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.04462999820709228</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.004931665983100887</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>81.27</v>
+      </c>
+      <c r="F45" t="n">
+        <v>342211592192</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3.84196</v>
+      </c>
+      <c r="I45" t="n">
+        <v>26.21613</v>
+      </c>
+      <c r="J45" t="n">
+        <v>21.153265</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L45" t="n">
+        <v>7.2981796</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.03814445674910791</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.0472740248554202</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.04462999820709228</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.00264402664832792</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>204.87</v>
+      </c>
+      <c r="F46" t="n">
+        <v>4962156281856</v>
+      </c>
+      <c r="G46" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="H46" t="n">
+        <v>12.72715</v>
+      </c>
+      <c r="I46" t="n">
+        <v>31.325687</v>
+      </c>
+      <c r="J46" t="n">
+        <v>16.097084</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L46" t="n">
+        <v>19.575275</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.03192268267681945</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.0621230536437741</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.04462999820709228</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.01749305543668182</v>
       </c>
     </row>
   </sheetData>
@@ -2686,12 +3208,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2705,51 +3227,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353.32</v>
+        <v>356.56</v>
       </c>
       <c r="F2" t="n">
-        <v>4308714389504</v>
+        <v>4348226043904</v>
       </c>
       <c r="G2" t="n">
-        <v>13.11</v>
+        <v>13.12</v>
       </c>
       <c r="H2" t="n">
         <v>14.48061</v>
       </c>
       <c r="I2" t="n">
-        <v>26.95042</v>
+        <v>27.176828</v>
       </c>
       <c r="J2" t="n">
-        <v>24.399525</v>
+        <v>24.623272</v>
       </c>
       <c r="K2" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="L2" t="n">
-        <v>10.198189</v>
+        <v>10.291708</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03710517378014264</v>
+        <v>0.03679605115548575</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04098440507188951</v>
+        <v>0.04061198676239623</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.04462999820709228</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.004475594966257462</v>
+        <v>-0.004018011444696053</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2763,51 +3285,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>397.36</v>
+        <v>390.34</v>
       </c>
       <c r="F3" t="n">
-        <v>2951762673664</v>
+        <v>2899615154176</v>
       </c>
       <c r="G3" t="n">
-        <v>16.81</v>
+        <v>16.78</v>
       </c>
       <c r="H3" t="n">
-        <v>19.39206</v>
+        <v>19.3459</v>
       </c>
       <c r="I3" t="n">
-        <v>23.63831</v>
+        <v>23.262217</v>
       </c>
       <c r="J3" t="n">
-        <v>20.49086</v>
+        <v>20.176886</v>
       </c>
       <c r="K3" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="L3" t="n">
-        <v>9.274311000000001</v>
+        <v>9.110466000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04230420777129051</v>
+        <v>0.04298816416457448</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04880224481578418</v>
+        <v>0.04956166419019317</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.04462999820709228</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003342244777637206</v>
+        <v>0.004931665983100887</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2821,51 +3343,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>570.98</v>
+        <v>568.4299999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1449388933120</v>
+        <v>1442915942400</v>
       </c>
       <c r="G4" t="n">
-        <v>27.52</v>
+        <v>27.51</v>
       </c>
       <c r="H4" t="n">
         <v>36.16212</v>
       </c>
       <c r="I4" t="n">
-        <v>20.747818</v>
+        <v>20.662668</v>
       </c>
       <c r="J4" t="n">
-        <v>15.78945</v>
+        <v>15.718934</v>
       </c>
       <c r="K4" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="L4" t="n">
-        <v>6.7425046</v>
+        <v>6.7123923</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04819783530071105</v>
+        <v>0.04839646042608589</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0633334267399909</v>
+        <v>0.06361754305719262</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.04462999820709228</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01787342670184393</v>
+        <v>0.01898754485010034</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2879,51 +3401,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>238</v>
+        <v>241.51</v>
       </c>
       <c r="F5" t="n">
-        <v>2560192151552</v>
+        <v>2597949538304</v>
       </c>
       <c r="G5" t="n">
-        <v>7.52</v>
+        <v>7.63</v>
       </c>
       <c r="H5" t="n">
         <v>9.859959999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>31.648935</v>
+        <v>31.652685</v>
       </c>
       <c r="J5" t="n">
-        <v>24.13803</v>
+        <v>24.494015</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.446789</v>
+        <v>3.497622</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03159663865546218</v>
+        <v>0.03159289470415304</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04142840336134453</v>
+        <v>0.04082630118835659</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.04462999820709228</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.004031596676802439</v>
+        <v>-0.003803697018735695</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2937,10 +3459,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>291.58</v>
+        <v>295.63</v>
       </c>
       <c r="F6" t="n">
-        <v>4282539048960</v>
+        <v>4342023192576</v>
       </c>
       <c r="G6" t="n">
         <v>8.25</v>
@@ -2949,39 +3471,39 @@
         <v>9.595079999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>35.34303</v>
+        <v>35.83394</v>
       </c>
       <c r="J6" t="n">
-        <v>30.388489</v>
+        <v>30.810581</v>
       </c>
       <c r="K6" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="L6" t="n">
-        <v>9.486355</v>
+        <v>9.618119</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02829412168187119</v>
+        <v>0.02790650475256232</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03290719528088346</v>
+        <v>0.03245638128742009</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.04462999820709228</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01255280475726351</v>
+        <v>-0.0121736169196722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2995,51 +3517,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>200.42</v>
+        <v>204.87</v>
       </c>
       <c r="F7" t="n">
-        <v>4854372630528</v>
+        <v>4962156281856</v>
       </c>
       <c r="G7" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
       <c r="H7" t="n">
         <v>12.72715</v>
       </c>
       <c r="I7" t="n">
-        <v>30.692188</v>
+        <v>31.325687</v>
       </c>
       <c r="J7" t="n">
-        <v>15.7474375</v>
+        <v>16.097084</v>
       </c>
       <c r="K7" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="L7" t="n">
-        <v>19.150078</v>
+        <v>19.575275</v>
       </c>
       <c r="M7" t="n">
-        <v>0.032581578684762</v>
+        <v>0.03192268267681945</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06350239497056183</v>
+        <v>0.0621230536437741</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.04462999820709228</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01804239493241486</v>
+        <v>0.01749305543668182</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3053,51 +3575,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>452.4</v>
+        <v>488.45</v>
       </c>
       <c r="F8" t="n">
-        <v>737683701760</v>
+        <v>796466872320</v>
       </c>
       <c r="G8" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="H8" t="n">
-        <v>13.07661</v>
+        <v>13.1035</v>
       </c>
       <c r="I8" t="n">
-        <v>151.30435</v>
+        <v>163.9094</v>
       </c>
       <c r="J8" t="n">
-        <v>34.596123</v>
+        <v>37.2763</v>
       </c>
       <c r="K8" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="L8" t="n">
-        <v>19.695724</v>
+        <v>21.265202</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006609195402298851</v>
+        <v>0.006100931518067356</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02890497347480106</v>
+        <v>0.02682669669362268</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.04462999820709228</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01655502656334591</v>
+        <v>-0.0178033015134696</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3111,51 +3633,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>372.1</v>
+        <v>385.57</v>
       </c>
       <c r="F9" t="n">
-        <v>1770295656448</v>
+        <v>1834380296192</v>
       </c>
       <c r="G9" t="n">
-        <v>6.03</v>
+        <v>6.01</v>
       </c>
       <c r="H9" t="n">
         <v>19.35046</v>
       </c>
       <c r="I9" t="n">
-        <v>61.708126</v>
+        <v>64.15474</v>
       </c>
       <c r="J9" t="n">
-        <v>19.229517</v>
+        <v>19.925625</v>
       </c>
       <c r="K9" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="L9" t="n">
-        <v>23.4585</v>
+        <v>24.307697</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01620532115022843</v>
+        <v>0.015587312290894</v>
       </c>
       <c r="N9" t="n">
-        <v>0.052003386186509</v>
+        <v>0.05018663277744639</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.04462999820709228</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006543386148362029</v>
+        <v>0.005556634570354102</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3169,10 +3691,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>82</v>
+        <v>81.27</v>
       </c>
       <c r="F10" t="n">
-        <v>345285492736</v>
+        <v>342211592192</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -3181,28 +3703,28 @@
         <v>3.84196</v>
       </c>
       <c r="I10" t="n">
-        <v>26.451614</v>
+        <v>26.21613</v>
       </c>
       <c r="J10" t="n">
-        <v>21.343273</v>
+        <v>21.153265</v>
       </c>
       <c r="K10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="L10" t="n">
-        <v>7.363735</v>
+        <v>7.2981796</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03780487804878049</v>
+        <v>0.03814445674910791</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04685317073170731</v>
+        <v>0.0472740248554202</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04546000003814697</v>
+        <v>0.04462999820709228</v>
       </c>
       <c r="P10" t="n">
-        <v>0.00139317069356034</v>
+        <v>0.00264402664832792</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2633,16 +2633,16 @@
         <v>9.618119</v>
       </c>
       <c r="M38" t="n">
-        <v>0.02790650475256232</v>
+        <v>0.0279065047525623</v>
       </c>
       <c r="N38" t="n">
-        <v>0.03245638128742009</v>
+        <v>0.03245638128742</v>
       </c>
       <c r="O38" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.0446299982070922</v>
       </c>
       <c r="P38" t="n">
-        <v>-0.0121736169196722</v>
+        <v>-0.0121736169196721</v>
       </c>
     </row>
     <row r="39">
@@ -2691,13 +2691,13 @@
         <v>21.265202</v>
       </c>
       <c r="M39" t="n">
-        <v>0.006100931518067356</v>
+        <v>0.0061009315180673</v>
       </c>
       <c r="N39" t="n">
-        <v>0.02682669669362268</v>
+        <v>0.0268266966936226</v>
       </c>
       <c r="O39" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.0446299982070922</v>
       </c>
       <c r="P39" t="n">
         <v>-0.0178033015134696</v>
@@ -2749,16 +2749,16 @@
         <v>3.497622</v>
       </c>
       <c r="M40" t="n">
-        <v>0.03159289470415304</v>
+        <v>0.031592894704153</v>
       </c>
       <c r="N40" t="n">
-        <v>0.04082630118835659</v>
+        <v>0.0408263011883565</v>
       </c>
       <c r="O40" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.0446299982070922</v>
       </c>
       <c r="P40" t="n">
-        <v>-0.003803697018735695</v>
+        <v>-0.0038036970187356</v>
       </c>
     </row>
     <row r="41">
@@ -2810,13 +2810,13 @@
         <v>0.015587312290894</v>
       </c>
       <c r="N41" t="n">
-        <v>0.05018663277744639</v>
+        <v>0.0501866327774463</v>
       </c>
       <c r="O41" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.0446299982070922</v>
       </c>
       <c r="P41" t="n">
-        <v>0.005556634570354102</v>
+        <v>0.0055566345703541</v>
       </c>
     </row>
     <row r="42">
@@ -2865,16 +2865,16 @@
         <v>10.291708</v>
       </c>
       <c r="M42" t="n">
-        <v>0.03679605115548575</v>
+        <v>0.0367960511554857</v>
       </c>
       <c r="N42" t="n">
-        <v>0.04061198676239623</v>
+        <v>0.0406119867623962</v>
       </c>
       <c r="O42" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.0446299982070922</v>
       </c>
       <c r="P42" t="n">
-        <v>-0.004018011444696053</v>
+        <v>-0.004018011444696</v>
       </c>
     </row>
     <row r="43">
@@ -2923,16 +2923,16 @@
         <v>6.7123923</v>
       </c>
       <c r="M43" t="n">
-        <v>0.04839646042608589</v>
+        <v>0.0483964604260858</v>
       </c>
       <c r="N43" t="n">
-        <v>0.06361754305719262</v>
+        <v>0.0636175430571926</v>
       </c>
       <c r="O43" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.0446299982070922</v>
       </c>
       <c r="P43" t="n">
-        <v>0.01898754485010034</v>
+        <v>0.0189875448501003</v>
       </c>
     </row>
     <row r="44">
@@ -2981,16 +2981,16 @@
         <v>9.110466000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>0.04298816416457448</v>
+        <v>0.0429881641645744</v>
       </c>
       <c r="N44" t="n">
-        <v>0.04956166419019317</v>
+        <v>0.0495616641901931</v>
       </c>
       <c r="O44" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.0446299982070922</v>
       </c>
       <c r="P44" t="n">
-        <v>0.004931665983100887</v>
+        <v>0.0049316659831008</v>
       </c>
     </row>
     <row r="45">
@@ -3039,16 +3039,16 @@
         <v>7.2981796</v>
       </c>
       <c r="M45" t="n">
-        <v>0.03814445674910791</v>
+        <v>0.0381444567491079</v>
       </c>
       <c r="N45" t="n">
         <v>0.0472740248554202</v>
       </c>
       <c r="O45" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.0446299982070922</v>
       </c>
       <c r="P45" t="n">
-        <v>0.00264402664832792</v>
+        <v>0.0026440266483279</v>
       </c>
     </row>
     <row r="46">
@@ -3097,16 +3097,538 @@
         <v>19.575275</v>
       </c>
       <c r="M46" t="n">
-        <v>0.03192268267681945</v>
+        <v>0.0319226826768194</v>
       </c>
       <c r="N46" t="n">
         <v>0.0621230536437741</v>
       </c>
       <c r="O46" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.0446299982070922</v>
       </c>
       <c r="P46" t="n">
-        <v>0.01749305543668182</v>
+        <v>0.0174930554366818</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>291.13</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4275929874432</v>
+      </c>
+      <c r="G47" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="H47" t="n">
+        <v>9.594989999999999</v>
+      </c>
+      <c r="I47" t="n">
+        <v>35.203144</v>
+      </c>
+      <c r="J47" t="n">
+        <v>30.341877</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L47" t="n">
+        <v>9.471714</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.02840655377322845</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.03295775083296121</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P47" t="n">
+        <v>-0.01191224905259787</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>511.57</v>
+      </c>
+      <c r="F48" t="n">
+        <v>834166325248</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H48" t="n">
+        <v>13.1035</v>
+      </c>
+      <c r="I48" t="n">
+        <v>169.39404</v>
+      </c>
+      <c r="J48" t="n">
+        <v>39.040714</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L48" t="n">
+        <v>22.271755</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.005903395429755459</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.02561428543503333</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P48" t="n">
+        <v>-0.01925571445052576</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>238.55</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2566108479488</v>
+      </c>
+      <c r="G49" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="H49" t="n">
+        <v>9.859959999999999</v>
+      </c>
+      <c r="I49" t="n">
+        <v>31.637932</v>
+      </c>
+      <c r="J49" t="n">
+        <v>24.193811</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L49" t="n">
+        <v>3.4547544</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.03160762942779292</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.0413328861873821</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P49" t="n">
+        <v>-0.00353711369817699</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>382.07</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1817728778240</v>
+      </c>
+      <c r="G50" t="n">
+        <v>6</v>
+      </c>
+      <c r="H50" t="n">
+        <v>19.35046</v>
+      </c>
+      <c r="I50" t="n">
+        <v>63.678333</v>
+      </c>
+      <c r="J50" t="n">
+        <v>19.744751</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L50" t="n">
+        <v>24.087044</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.0157039285994713</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.05064637370115425</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.005776373815595162</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>358.16</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4367737946112</v>
+      </c>
+      <c r="G51" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="H51" t="n">
+        <v>14.48061</v>
+      </c>
+      <c r="I51" t="n">
+        <v>27.319605</v>
+      </c>
+      <c r="J51" t="n">
+        <v>24.733765</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L51" t="n">
+        <v>10.33789</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.03660375251284342</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.04043056176010721</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P51" t="n">
+        <v>-0.004439438125451875</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>566.98</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1439235178496</v>
+      </c>
+      <c r="G52" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>36.24596</v>
+      </c>
+      <c r="I52" t="n">
+        <v>20.617455</v>
+      </c>
+      <c r="J52" t="n">
+        <v>15.6425705</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L52" t="n">
+        <v>6.6952696</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.04850259268404529</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.06392811033898903</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.01905811045342994</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>390.74</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2902586556416</v>
+      </c>
+      <c r="G53" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H53" t="n">
+        <v>19.3459</v>
+      </c>
+      <c r="I53" t="n">
+        <v>23.258333</v>
+      </c>
+      <c r="J53" t="n">
+        <v>20.197561</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L53" t="n">
+        <v>9.119801499999999</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.04299534217126478</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.04951092798280186</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.004640928097242779</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>80.34</v>
+      </c>
+      <c r="F54" t="n">
+        <v>338295554048</v>
+      </c>
+      <c r="G54" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>3.84196</v>
+      </c>
+      <c r="I54" t="n">
+        <v>25.916128</v>
+      </c>
+      <c r="J54" t="n">
+        <v>20.911201</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L54" t="n">
+        <v>7.2146645</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.03858600945979587</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.04782125964650236</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.002951259760943278</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>205.19</v>
+      </c>
+      <c r="F55" t="n">
+        <v>4969906831360</v>
+      </c>
+      <c r="G55" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H55" t="n">
+        <v>12.72715</v>
+      </c>
+      <c r="I55" t="n">
+        <v>31.422665</v>
+      </c>
+      <c r="J55" t="n">
+        <v>16.122227</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L55" t="n">
+        <v>19.60585</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.03182416297090502</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.06202617086602661</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.01715617098046752</v>
       </c>
     </row>
   </sheetData>
@@ -3208,12 +3730,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3227,51 +3749,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>356.56</v>
+        <v>358.16</v>
       </c>
       <c r="F2" t="n">
-        <v>4348226043904</v>
+        <v>4367737946112</v>
       </c>
       <c r="G2" t="n">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="H2" t="n">
         <v>14.48061</v>
       </c>
       <c r="I2" t="n">
-        <v>27.176828</v>
+        <v>27.319605</v>
       </c>
       <c r="J2" t="n">
-        <v>24.623272</v>
+        <v>24.733765</v>
       </c>
       <c r="K2" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="L2" t="n">
-        <v>10.291708</v>
+        <v>10.33789</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03679605115548575</v>
+        <v>0.03660375251284342</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04061198676239623</v>
+        <v>0.04043056176010721</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.004018011444696053</v>
+        <v>-0.004439438125451875</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3285,51 +3807,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>390.34</v>
+        <v>390.74</v>
       </c>
       <c r="F3" t="n">
-        <v>2899615154176</v>
+        <v>2902586556416</v>
       </c>
       <c r="G3" t="n">
-        <v>16.78</v>
+        <v>16.8</v>
       </c>
       <c r="H3" t="n">
         <v>19.3459</v>
       </c>
       <c r="I3" t="n">
-        <v>23.262217</v>
+        <v>23.258333</v>
       </c>
       <c r="J3" t="n">
-        <v>20.176886</v>
+        <v>20.197561</v>
       </c>
       <c r="K3" t="n">
         <v>1.2</v>
       </c>
       <c r="L3" t="n">
-        <v>9.110466000000001</v>
+        <v>9.119801499999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04298816416457448</v>
+        <v>0.04299534217126478</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04956166419019317</v>
+        <v>0.04951092798280186</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004931665983100887</v>
+        <v>0.004640928097242779</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3343,51 +3865,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>568.4299999999999</v>
+        <v>566.98</v>
       </c>
       <c r="F4" t="n">
-        <v>1442915942400</v>
+        <v>1439235178496</v>
       </c>
       <c r="G4" t="n">
-        <v>27.51</v>
+        <v>27.5</v>
       </c>
       <c r="H4" t="n">
-        <v>36.16212</v>
+        <v>36.24596</v>
       </c>
       <c r="I4" t="n">
-        <v>20.662668</v>
+        <v>20.617455</v>
       </c>
       <c r="J4" t="n">
-        <v>15.718934</v>
+        <v>15.6425705</v>
       </c>
       <c r="K4" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="L4" t="n">
-        <v>6.7123923</v>
+        <v>6.6952696</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04839646042608589</v>
+        <v>0.04850259268404529</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06361754305719262</v>
+        <v>0.06392811033898903</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01898754485010034</v>
+        <v>0.01905811045342994</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3401,51 +3923,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>241.51</v>
+        <v>238.55</v>
       </c>
       <c r="F5" t="n">
-        <v>2597949538304</v>
+        <v>2566108479488</v>
       </c>
       <c r="G5" t="n">
-        <v>7.63</v>
+        <v>7.54</v>
       </c>
       <c r="H5" t="n">
         <v>9.859959999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>31.652685</v>
+        <v>31.637932</v>
       </c>
       <c r="J5" t="n">
-        <v>24.494015</v>
+        <v>24.193811</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.497622</v>
+        <v>3.4547544</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03159289470415304</v>
+        <v>0.03160762942779292</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04082630118835659</v>
+        <v>0.0413328861873821</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.003803697018735695</v>
+        <v>-0.00353711369817699</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3459,51 +3981,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>295.63</v>
+        <v>291.13</v>
       </c>
       <c r="F6" t="n">
-        <v>4342023192576</v>
+        <v>4275929874432</v>
       </c>
       <c r="G6" t="n">
-        <v>8.25</v>
+        <v>8.27</v>
       </c>
       <c r="H6" t="n">
-        <v>9.595079999999999</v>
+        <v>9.594989999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>35.83394</v>
+        <v>35.203144</v>
       </c>
       <c r="J6" t="n">
-        <v>30.810581</v>
+        <v>30.341877</v>
       </c>
       <c r="K6" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="L6" t="n">
-        <v>9.618119</v>
+        <v>9.471714</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02790650475256232</v>
+        <v>0.02840655377322845</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03245638128742009</v>
+        <v>0.03295775083296121</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0121736169196722</v>
+        <v>-0.01191224905259787</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3517,51 +4039,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>204.87</v>
+        <v>205.19</v>
       </c>
       <c r="F7" t="n">
-        <v>4962156281856</v>
+        <v>4969906831360</v>
       </c>
       <c r="G7" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
       <c r="H7" t="n">
         <v>12.72715</v>
       </c>
       <c r="I7" t="n">
-        <v>31.325687</v>
+        <v>31.422665</v>
       </c>
       <c r="J7" t="n">
-        <v>16.097084</v>
+        <v>16.122227</v>
       </c>
       <c r="K7" t="n">
         <v>0.63</v>
       </c>
       <c r="L7" t="n">
-        <v>19.575275</v>
+        <v>19.60585</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03192268267681945</v>
+        <v>0.03182416297090502</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0621230536437741</v>
+        <v>0.06202617086602661</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01749305543668182</v>
+        <v>0.01715617098046752</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3575,51 +4097,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>488.45</v>
+        <v>511.57</v>
       </c>
       <c r="F8" t="n">
-        <v>796466872320</v>
+        <v>834166325248</v>
       </c>
       <c r="G8" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="H8" t="n">
         <v>13.1035</v>
       </c>
       <c r="I8" t="n">
-        <v>163.9094</v>
+        <v>169.39404</v>
       </c>
       <c r="J8" t="n">
-        <v>37.2763</v>
+        <v>39.040714</v>
       </c>
       <c r="K8" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="L8" t="n">
-        <v>21.265202</v>
+        <v>22.271755</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006100931518067356</v>
+        <v>0.005903395429755459</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02682669669362268</v>
+        <v>0.02561428543503333</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0178033015134696</v>
+        <v>-0.01925571445052576</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3633,51 +4155,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>385.57</v>
+        <v>382.07</v>
       </c>
       <c r="F9" t="n">
-        <v>1834380296192</v>
+        <v>1817728778240</v>
       </c>
       <c r="G9" t="n">
-        <v>6.01</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>19.35046</v>
       </c>
       <c r="I9" t="n">
-        <v>64.15474</v>
+        <v>63.678333</v>
       </c>
       <c r="J9" t="n">
-        <v>19.925625</v>
+        <v>19.744751</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>24.307697</v>
+        <v>24.087044</v>
       </c>
       <c r="M9" t="n">
-        <v>0.015587312290894</v>
+        <v>0.0157039285994713</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05018663277744639</v>
+        <v>0.05064637370115425</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P9" t="n">
-        <v>0.005556634570354102</v>
+        <v>0.005776373815595162</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3691,10 +4213,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>81.27</v>
+        <v>80.34</v>
       </c>
       <c r="F10" t="n">
-        <v>342211592192</v>
+        <v>338295554048</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -3703,28 +4225,28 @@
         <v>3.84196</v>
       </c>
       <c r="I10" t="n">
-        <v>26.21613</v>
+        <v>25.916128</v>
       </c>
       <c r="J10" t="n">
-        <v>21.153265</v>
+        <v>20.911201</v>
       </c>
       <c r="K10" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="L10" t="n">
-        <v>7.2981796</v>
+        <v>7.2146645</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03814445674910791</v>
+        <v>0.03858600945979587</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0472740248554202</v>
+        <v>0.04782125964650236</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04462999820709228</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P10" t="n">
-        <v>0.00264402664832792</v>
+        <v>0.002951259760943278</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P55"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3155,16 +3155,16 @@
         <v>9.471714</v>
       </c>
       <c r="M47" t="n">
-        <v>0.02840655377322845</v>
+        <v>0.0284065537732284</v>
       </c>
       <c r="N47" t="n">
-        <v>0.03295775083296121</v>
+        <v>0.0329577508329612</v>
       </c>
       <c r="O47" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P47" t="n">
-        <v>-0.01191224905259787</v>
+        <v>-0.0119122490525978</v>
       </c>
     </row>
     <row r="48">
@@ -3213,16 +3213,16 @@
         <v>22.271755</v>
       </c>
       <c r="M48" t="n">
-        <v>0.005903395429755459</v>
+        <v>0.0059033954297554</v>
       </c>
       <c r="N48" t="n">
-        <v>0.02561428543503333</v>
+        <v>0.0256142854350333</v>
       </c>
       <c r="O48" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.01925571445052576</v>
+        <v>-0.0192557144505257</v>
       </c>
     </row>
     <row r="49">
@@ -3271,16 +3271,16 @@
         <v>3.4547544</v>
       </c>
       <c r="M49" t="n">
-        <v>0.03160762942779292</v>
+        <v>0.0316076294277929</v>
       </c>
       <c r="N49" t="n">
-        <v>0.0413328861873821</v>
+        <v>0.041332886187382</v>
       </c>
       <c r="O49" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P49" t="n">
-        <v>-0.00353711369817699</v>
+        <v>-0.0035371136981769</v>
       </c>
     </row>
     <row r="50">
@@ -3332,13 +3332,13 @@
         <v>0.0157039285994713</v>
       </c>
       <c r="N50" t="n">
-        <v>0.05064637370115425</v>
+        <v>0.0506463737011542</v>
       </c>
       <c r="O50" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P50" t="n">
-        <v>0.005776373815595162</v>
+        <v>0.0057763738155951</v>
       </c>
     </row>
     <row r="51">
@@ -3387,16 +3387,16 @@
         <v>10.33789</v>
       </c>
       <c r="M51" t="n">
-        <v>0.03660375251284342</v>
+        <v>0.0366037525128434</v>
       </c>
       <c r="N51" t="n">
-        <v>0.04043056176010721</v>
+        <v>0.0404305617601072</v>
       </c>
       <c r="O51" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.004439438125451875</v>
+        <v>-0.0044394381254518</v>
       </c>
     </row>
     <row r="52">
@@ -3445,16 +3445,16 @@
         <v>6.6952696</v>
       </c>
       <c r="M52" t="n">
-        <v>0.04850259268404529</v>
+        <v>0.0485025926840452</v>
       </c>
       <c r="N52" t="n">
-        <v>0.06392811033898903</v>
+        <v>0.063928110338989</v>
       </c>
       <c r="O52" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P52" t="n">
-        <v>0.01905811045342994</v>
+        <v>0.0190581104534299</v>
       </c>
     </row>
     <row r="53">
@@ -3503,16 +3503,16 @@
         <v>9.119801499999999</v>
       </c>
       <c r="M53" t="n">
-        <v>0.04299534217126478</v>
+        <v>0.0429953421712647</v>
       </c>
       <c r="N53" t="n">
-        <v>0.04951092798280186</v>
+        <v>0.0495109279828018</v>
       </c>
       <c r="O53" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P53" t="n">
-        <v>0.004640928097242779</v>
+        <v>0.0046409280972427</v>
       </c>
     </row>
     <row r="54">
@@ -3561,16 +3561,16 @@
         <v>7.2146645</v>
       </c>
       <c r="M54" t="n">
-        <v>0.03858600945979587</v>
+        <v>0.0385860094597958</v>
       </c>
       <c r="N54" t="n">
-        <v>0.04782125964650236</v>
+        <v>0.0478212596465023</v>
       </c>
       <c r="O54" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P54" t="n">
-        <v>0.002951259760943278</v>
+        <v>0.0029512597609432</v>
       </c>
     </row>
     <row r="55">
@@ -3619,16 +3619,538 @@
         <v>19.60585</v>
       </c>
       <c r="M55" t="n">
-        <v>0.03182416297090502</v>
+        <v>0.031824162970905</v>
       </c>
       <c r="N55" t="n">
-        <v>0.06202617086602661</v>
+        <v>0.0620261708660266</v>
       </c>
       <c r="O55" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P55" t="n">
-        <v>0.01715617098046752</v>
+        <v>0.0171561709804675</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>298.84</v>
+      </c>
+      <c r="F56" t="n">
+        <v>4389169266688</v>
+      </c>
+      <c r="G56" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="H56" t="n">
+        <v>9.594989999999999</v>
+      </c>
+      <c r="I56" t="n">
+        <v>36.135426</v>
+      </c>
+      <c r="J56" t="n">
+        <v>31.14542</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L56" t="n">
+        <v>9.722554000000001</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.02767367152991567</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.03210744880203453</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.04425999641418457</v>
+      </c>
+      <c r="P56" t="n">
+        <v>-0.01215254761215004</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>524.4299999999999</v>
+      </c>
+      <c r="F57" t="n">
+        <v>855135879168</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="H57" t="n">
+        <v>13.1035</v>
+      </c>
+      <c r="I57" t="n">
+        <v>174.22923</v>
+      </c>
+      <c r="J57" t="n">
+        <v>40.02213</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L57" t="n">
+        <v>22.83163</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.005739564860896593</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.02498617546669718</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.04425999641418457</v>
+      </c>
+      <c r="P57" t="n">
+        <v>-0.01927382094748739</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>247.55</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2662922452992</v>
+      </c>
+      <c r="G58" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="H58" t="n">
+        <v>9.859959999999999</v>
+      </c>
+      <c r="I58" t="n">
+        <v>31.859716</v>
+      </c>
+      <c r="J58" t="n">
+        <v>25.106594</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L58" t="n">
+        <v>3.585095</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.03138759846495657</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.03983017572207635</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.04425999641418457</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-0.004429820692108226</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>379.26</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1804359958528</v>
+      </c>
+      <c r="G59" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="H59" t="n">
+        <v>19.35046</v>
+      </c>
+      <c r="I59" t="n">
+        <v>62.895523</v>
+      </c>
+      <c r="J59" t="n">
+        <v>19.599535</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L59" t="n">
+        <v>23.909891</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.01589938300901756</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.05102162105152139</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.04425999641418457</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.006761624637336816</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>370.73</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4523859902464</v>
+      </c>
+      <c r="G60" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="H60" t="n">
+        <v>14.48061</v>
+      </c>
+      <c r="I60" t="n">
+        <v>28.278416</v>
+      </c>
+      <c r="J60" t="n">
+        <v>25.601824</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L60" t="n">
+        <v>10.707411</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.03536266285436841</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.03905972001186848</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.04425999641418457</v>
+      </c>
+      <c r="P60" t="n">
+        <v>-0.005200276402316094</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>594.75</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1509727272960</v>
+      </c>
+      <c r="G61" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="H61" t="n">
+        <v>36.24596</v>
+      </c>
+      <c r="I61" t="n">
+        <v>21.643013</v>
+      </c>
+      <c r="J61" t="n">
+        <v>16.408726</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L61" t="n">
+        <v>7.023196</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.04620428751576293</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.06094318621269441</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.04425999641418457</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.01668318979850984</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>392.565</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2916143595520</v>
+      </c>
+      <c r="G62" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="H62" t="n">
+        <v>19.3459</v>
+      </c>
+      <c r="I62" t="n">
+        <v>23.38088</v>
+      </c>
+      <c r="J62" t="n">
+        <v>20.291897</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L62" t="n">
+        <v>9.162397</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.04276998713588832</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.0492807560531377</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.04425999641418457</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.005020759638953126</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>78.5899</v>
+      </c>
+      <c r="F63" t="n">
+        <v>330926227456</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3.84196</v>
+      </c>
+      <c r="I63" t="n">
+        <v>25.35158</v>
+      </c>
+      <c r="J63" t="n">
+        <v>20.455679</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L63" t="n">
+        <v>7.0575023</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.03944527222963765</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.04888618003076731</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.04425999641418457</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.004626183616582735</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>209.58</v>
+      </c>
+      <c r="F64" t="n">
+        <v>5076237156352</v>
+      </c>
+      <c r="G64" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="H64" t="n">
+        <v>12.72715</v>
+      </c>
+      <c r="I64" t="n">
+        <v>32.144173</v>
+      </c>
+      <c r="J64" t="n">
+        <v>16.46716</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L64" t="n">
+        <v>20.025314</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.03110983872506918</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.06072693005057734</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.04425999641418457</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.01646693363639277</v>
       </c>
     </row>
   </sheetData>
@@ -3730,12 +4252,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3749,10 +4271,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>358.16</v>
+        <v>370.73</v>
       </c>
       <c r="F2" t="n">
-        <v>4367737946112</v>
+        <v>4523859902464</v>
       </c>
       <c r="G2" t="n">
         <v>13.11</v>
@@ -3761,39 +4283,39 @@
         <v>14.48061</v>
       </c>
       <c r="I2" t="n">
-        <v>27.319605</v>
+        <v>28.278416</v>
       </c>
       <c r="J2" t="n">
-        <v>24.733765</v>
+        <v>25.601824</v>
       </c>
       <c r="K2" t="n">
         <v>1.41</v>
       </c>
       <c r="L2" t="n">
-        <v>10.33789</v>
+        <v>10.707411</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03660375251284342</v>
+        <v>0.03536266285436841</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04043056176010721</v>
+        <v>0.03905972001186848</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04425999641418457</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.004439438125451875</v>
+        <v>-0.005200276402316094</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3807,51 +4329,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>390.74</v>
+        <v>392.565</v>
       </c>
       <c r="F3" t="n">
-        <v>2902586556416</v>
+        <v>2916143595520</v>
       </c>
       <c r="G3" t="n">
-        <v>16.8</v>
+        <v>16.79</v>
       </c>
       <c r="H3" t="n">
         <v>19.3459</v>
       </c>
       <c r="I3" t="n">
-        <v>23.258333</v>
+        <v>23.38088</v>
       </c>
       <c r="J3" t="n">
-        <v>20.197561</v>
+        <v>20.291897</v>
       </c>
       <c r="K3" t="n">
         <v>1.2</v>
       </c>
       <c r="L3" t="n">
-        <v>9.119801499999999</v>
+        <v>9.162397</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04299534217126478</v>
+        <v>0.04276998713588832</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04951092798280186</v>
+        <v>0.0492807560531377</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04425999641418457</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004640928097242779</v>
+        <v>0.005020759638953126</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3865,51 +4387,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>566.98</v>
+        <v>594.75</v>
       </c>
       <c r="F4" t="n">
-        <v>1439235178496</v>
+        <v>1509727272960</v>
       </c>
       <c r="G4" t="n">
-        <v>27.5</v>
+        <v>27.48</v>
       </c>
       <c r="H4" t="n">
         <v>36.24596</v>
       </c>
       <c r="I4" t="n">
-        <v>20.617455</v>
+        <v>21.643013</v>
       </c>
       <c r="J4" t="n">
-        <v>15.6425705</v>
+        <v>16.408726</v>
       </c>
       <c r="K4" t="n">
         <v>0.82</v>
       </c>
       <c r="L4" t="n">
-        <v>6.6952696</v>
+        <v>7.023196</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04850259268404529</v>
+        <v>0.04620428751576293</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06392811033898903</v>
+        <v>0.06094318621269441</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04425999641418457</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01905811045342994</v>
+        <v>0.01668318979850984</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3923,51 +4445,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>238.55</v>
+        <v>247.55</v>
       </c>
       <c r="F5" t="n">
-        <v>2566108479488</v>
+        <v>2662922452992</v>
       </c>
       <c r="G5" t="n">
-        <v>7.54</v>
+        <v>7.77</v>
       </c>
       <c r="H5" t="n">
         <v>9.859959999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>31.637932</v>
+        <v>31.859716</v>
       </c>
       <c r="J5" t="n">
-        <v>24.193811</v>
+        <v>25.106594</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4547544</v>
+        <v>3.585095</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03160762942779292</v>
+        <v>0.03138759846495657</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0413328861873821</v>
+        <v>0.03983017572207635</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04425999641418457</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.00353711369817699</v>
+        <v>-0.004429820692108226</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3981,10 +4503,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>291.13</v>
+        <v>298.84</v>
       </c>
       <c r="F6" t="n">
-        <v>4275929874432</v>
+        <v>4389169266688</v>
       </c>
       <c r="G6" t="n">
         <v>8.27</v>
@@ -3993,39 +4515,39 @@
         <v>9.594989999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>35.203144</v>
+        <v>36.135426</v>
       </c>
       <c r="J6" t="n">
-        <v>30.341877</v>
+        <v>31.14542</v>
       </c>
       <c r="K6" t="n">
         <v>2.35</v>
       </c>
       <c r="L6" t="n">
-        <v>9.471714</v>
+        <v>9.722554000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02840655377322845</v>
+        <v>0.02767367152991567</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03295775083296121</v>
+        <v>0.03210744880203453</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04425999641418457</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01191224905259787</v>
+        <v>-0.01215254761215004</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4039,51 +4561,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205.19</v>
+        <v>209.58</v>
       </c>
       <c r="F7" t="n">
-        <v>4969906831360</v>
+        <v>5076237156352</v>
       </c>
       <c r="G7" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
       <c r="H7" t="n">
         <v>12.72715</v>
       </c>
       <c r="I7" t="n">
-        <v>31.422665</v>
+        <v>32.144173</v>
       </c>
       <c r="J7" t="n">
-        <v>16.122227</v>
+        <v>16.46716</v>
       </c>
       <c r="K7" t="n">
         <v>0.63</v>
       </c>
       <c r="L7" t="n">
-        <v>19.60585</v>
+        <v>20.025314</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03182416297090502</v>
+        <v>0.03110983872506918</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06202617086602661</v>
+        <v>0.06072693005057734</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04425999641418457</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01715617098046752</v>
+        <v>0.01646693363639277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4097,51 +4619,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>511.57</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>834166325248</v>
+        <v>855135879168</v>
       </c>
       <c r="G8" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="H8" t="n">
         <v>13.1035</v>
       </c>
       <c r="I8" t="n">
-        <v>169.39404</v>
+        <v>174.22923</v>
       </c>
       <c r="J8" t="n">
-        <v>39.040714</v>
+        <v>40.02213</v>
       </c>
       <c r="K8" t="n">
         <v>1.23</v>
       </c>
       <c r="L8" t="n">
-        <v>22.271755</v>
+        <v>22.83163</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005903395429755459</v>
+        <v>0.005739564860896593</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02561428543503333</v>
+        <v>0.02498617546669718</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04425999641418457</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01925571445052576</v>
+        <v>-0.01927382094748739</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4155,51 +4677,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>382.07</v>
+        <v>379.26</v>
       </c>
       <c r="F9" t="n">
-        <v>1817728778240</v>
+        <v>1804359958528</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>6.03</v>
       </c>
       <c r="H9" t="n">
         <v>19.35046</v>
       </c>
       <c r="I9" t="n">
-        <v>63.678333</v>
+        <v>62.895523</v>
       </c>
       <c r="J9" t="n">
-        <v>19.744751</v>
+        <v>19.599535</v>
       </c>
       <c r="K9" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>24.087044</v>
+        <v>23.909891</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0157039285994713</v>
+        <v>0.01589938300901756</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05064637370115425</v>
+        <v>0.05102162105152139</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04425999641418457</v>
       </c>
       <c r="P9" t="n">
-        <v>0.005776373815595162</v>
+        <v>0.006761624637336816</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4213,10 +4735,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>80.34</v>
+        <v>78.5899</v>
       </c>
       <c r="F10" t="n">
-        <v>338295554048</v>
+        <v>330926227456</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -4225,28 +4747,28 @@
         <v>3.84196</v>
       </c>
       <c r="I10" t="n">
-        <v>25.916128</v>
+        <v>25.35158</v>
       </c>
       <c r="J10" t="n">
-        <v>20.911201</v>
+        <v>20.455679</v>
       </c>
       <c r="K10" t="n">
         <v>1.58</v>
       </c>
       <c r="L10" t="n">
-        <v>7.2146645</v>
+        <v>7.0575023</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03858600945979587</v>
+        <v>0.03944527222963765</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04782125964650236</v>
+        <v>0.04888618003076731</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04425999641418457</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002951259760943278</v>
+        <v>0.004626183616582735</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3677,16 +3677,16 @@
         <v>9.722554000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>0.02767367152991567</v>
+        <v>0.0276736715299156</v>
       </c>
       <c r="N56" t="n">
-        <v>0.03210744880203453</v>
+        <v>0.0321074488020345</v>
       </c>
       <c r="O56" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.0442599964141845</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.01215254761215004</v>
+        <v>-0.01215254761215</v>
       </c>
     </row>
     <row r="57">
@@ -3735,16 +3735,16 @@
         <v>22.83163</v>
       </c>
       <c r="M57" t="n">
-        <v>0.005739564860896593</v>
+        <v>0.0057395648608965</v>
       </c>
       <c r="N57" t="n">
-        <v>0.02498617546669718</v>
+        <v>0.0249861754666971</v>
       </c>
       <c r="O57" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.0442599964141845</v>
       </c>
       <c r="P57" t="n">
-        <v>-0.01927382094748739</v>
+        <v>-0.0192738209474873</v>
       </c>
     </row>
     <row r="58">
@@ -3793,16 +3793,16 @@
         <v>3.585095</v>
       </c>
       <c r="M58" t="n">
-        <v>0.03138759846495657</v>
+        <v>0.0313875984649565</v>
       </c>
       <c r="N58" t="n">
-        <v>0.03983017572207635</v>
+        <v>0.0398301757220763</v>
       </c>
       <c r="O58" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.0442599964141845</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.004429820692108226</v>
+        <v>-0.0044298206921082</v>
       </c>
     </row>
     <row r="59">
@@ -3851,16 +3851,16 @@
         <v>23.909891</v>
       </c>
       <c r="M59" t="n">
-        <v>0.01589938300901756</v>
+        <v>0.0158993830090175</v>
       </c>
       <c r="N59" t="n">
-        <v>0.05102162105152139</v>
+        <v>0.0510216210515213</v>
       </c>
       <c r="O59" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.0442599964141845</v>
       </c>
       <c r="P59" t="n">
-        <v>0.006761624637336816</v>
+        <v>0.0067616246373368</v>
       </c>
     </row>
     <row r="60">
@@ -3909,16 +3909,16 @@
         <v>10.707411</v>
       </c>
       <c r="M60" t="n">
-        <v>0.03536266285436841</v>
+        <v>0.0353626628543684</v>
       </c>
       <c r="N60" t="n">
-        <v>0.03905972001186848</v>
+        <v>0.0390597200118684</v>
       </c>
       <c r="O60" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.0442599964141845</v>
       </c>
       <c r="P60" t="n">
-        <v>-0.005200276402316094</v>
+        <v>-0.005200276402316</v>
       </c>
     </row>
     <row r="61">
@@ -3967,16 +3967,16 @@
         <v>7.023196</v>
       </c>
       <c r="M61" t="n">
-        <v>0.04620428751576293</v>
+        <v>0.0462042875157629</v>
       </c>
       <c r="N61" t="n">
-        <v>0.06094318621269441</v>
+        <v>0.0609431862126944</v>
       </c>
       <c r="O61" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.0442599964141845</v>
       </c>
       <c r="P61" t="n">
-        <v>0.01668318979850984</v>
+        <v>0.0166831897985098</v>
       </c>
     </row>
     <row r="62">
@@ -4025,16 +4025,16 @@
         <v>9.162397</v>
       </c>
       <c r="M62" t="n">
-        <v>0.04276998713588832</v>
+        <v>0.0427699871358883</v>
       </c>
       <c r="N62" t="n">
         <v>0.0492807560531377</v>
       </c>
       <c r="O62" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.0442599964141845</v>
       </c>
       <c r="P62" t="n">
-        <v>0.005020759638953126</v>
+        <v>0.0050207596389531</v>
       </c>
     </row>
     <row r="63">
@@ -4083,16 +4083,16 @@
         <v>7.0575023</v>
       </c>
       <c r="M63" t="n">
-        <v>0.03944527222963765</v>
+        <v>0.0394452722296376</v>
       </c>
       <c r="N63" t="n">
-        <v>0.04888618003076731</v>
+        <v>0.0488861800307673</v>
       </c>
       <c r="O63" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.0442599964141845</v>
       </c>
       <c r="P63" t="n">
-        <v>0.004626183616582735</v>
+        <v>0.0046261836165827</v>
       </c>
     </row>
     <row r="64">
@@ -4141,16 +4141,538 @@
         <v>20.025314</v>
       </c>
       <c r="M64" t="n">
-        <v>0.03110983872506918</v>
+        <v>0.0311098387250691</v>
       </c>
       <c r="N64" t="n">
-        <v>0.06072693005057734</v>
+        <v>0.0607269300505773</v>
       </c>
       <c r="O64" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.0442599964141845</v>
       </c>
       <c r="P64" t="n">
-        <v>0.01646693363639277</v>
+        <v>0.0164669336363927</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>299.24</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4395044175872</v>
+      </c>
+      <c r="G65" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H65" t="n">
+        <v>9.594989999999999</v>
+      </c>
+      <c r="I65" t="n">
+        <v>36.2276</v>
+      </c>
+      <c r="J65" t="n">
+        <v>31.187109</v>
+      </c>
+      <c r="K65" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L65" t="n">
+        <v>9.735567</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.02760326159604331</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.03206453014302901</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.04435999870300293</v>
+      </c>
+      <c r="P65" t="n">
+        <v>-0.01229546855997393</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>507.29</v>
+      </c>
+      <c r="F66" t="n">
+        <v>827187396608</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H66" t="n">
+        <v>13.1035</v>
+      </c>
+      <c r="I66" t="n">
+        <v>169.66222</v>
+      </c>
+      <c r="J66" t="n">
+        <v>38.714085</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L66" t="n">
+        <v>22.085423</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.005894064539021073</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.0258303928719273</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.04435999870300293</v>
+      </c>
+      <c r="P66" t="n">
+        <v>-0.01852960583107563</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>246</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2646249046016</v>
+      </c>
+      <c r="G67" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="H67" t="n">
+        <v>9.859959999999999</v>
+      </c>
+      <c r="I67" t="n">
+        <v>31.660233</v>
+      </c>
+      <c r="J67" t="n">
+        <v>24.949392</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L67" t="n">
+        <v>3.5626476</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.03158536585365854</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.04008113821138211</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.04435999870300293</v>
+      </c>
+      <c r="P67" t="n">
+        <v>-0.004278860491620823</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1792228065280</v>
+      </c>
+      <c r="G68" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="H68" t="n">
+        <v>19.35046</v>
+      </c>
+      <c r="I68" t="n">
+        <v>62.472633</v>
+      </c>
+      <c r="J68" t="n">
+        <v>19.467754</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L68" t="n">
+        <v>23.74913</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.01600700804332245</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.05136699317777602</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.04435999870300293</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.007006994474773084</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4528375070720</v>
+      </c>
+      <c r="G69" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H69" t="n">
+        <v>14.4964</v>
+      </c>
+      <c r="I69" t="n">
+        <v>28.328243</v>
+      </c>
+      <c r="J69" t="n">
+        <v>25.59946</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L69" t="n">
+        <v>10.718098</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.03530045809754783</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.03906332524925896</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.04435999870300293</v>
+      </c>
+      <c r="P69" t="n">
+        <v>-0.005296673453743975</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>600.21</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1523587088384</v>
+      </c>
+      <c r="G70" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="H70" t="n">
+        <v>36.24596</v>
+      </c>
+      <c r="I70" t="n">
+        <v>21.83376</v>
+      </c>
+      <c r="J70" t="n">
+        <v>16.559362</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L70" t="n">
+        <v>7.0876713</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.0458006364439113</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.06038879725429432</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.04435999870300293</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.01602879855129139</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>393.83</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2925540409344</v>
+      </c>
+      <c r="G71" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="H71" t="n">
+        <v>19.3459</v>
+      </c>
+      <c r="I71" t="n">
+        <v>23.470201</v>
+      </c>
+      <c r="J71" t="n">
+        <v>20.357285</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L71" t="n">
+        <v>9.191921000000001</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.04260721631160654</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.0491224640073128</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.04435999870300293</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.004762465304309869</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="F72" t="n">
+        <v>331474075648</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>3.84196</v>
+      </c>
+      <c r="I72" t="n">
+        <v>25.393549</v>
+      </c>
+      <c r="J72" t="n">
+        <v>20.489542</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L72" t="n">
+        <v>7.069186</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.03938008130081301</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.04880538617886179</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.04435999870300293</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.004445387475858854</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>207.41</v>
+      </c>
+      <c r="F73" t="n">
+        <v>5023677808640</v>
+      </c>
+      <c r="G73" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H73" t="n">
+        <v>12.72715</v>
+      </c>
+      <c r="I73" t="n">
+        <v>31.762634</v>
+      </c>
+      <c r="J73" t="n">
+        <v>16.296658</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L73" t="n">
+        <v>19.817972</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.03148353502724073</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.06136227761438696</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.04435999870300293</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.01700227891138403</v>
       </c>
     </row>
   </sheetData>
@@ -4252,12 +4774,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4271,51 +4793,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>370.73</v>
+        <v>371.1</v>
       </c>
       <c r="F2" t="n">
-        <v>4523859902464</v>
+        <v>4528375070720</v>
       </c>
       <c r="G2" t="n">
-        <v>13.11</v>
+        <v>13.1</v>
       </c>
       <c r="H2" t="n">
-        <v>14.48061</v>
+        <v>14.4964</v>
       </c>
       <c r="I2" t="n">
-        <v>28.278416</v>
+        <v>28.328243</v>
       </c>
       <c r="J2" t="n">
-        <v>25.601824</v>
+        <v>25.59946</v>
       </c>
       <c r="K2" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="L2" t="n">
-        <v>10.707411</v>
+        <v>10.718098</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03536266285436841</v>
+        <v>0.03530045809754783</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03905972001186848</v>
+        <v>0.03906332524925896</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.04435999870300293</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005200276402316094</v>
+        <v>-0.005296673453743975</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4329,51 +4851,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>392.565</v>
+        <v>393.83</v>
       </c>
       <c r="F3" t="n">
-        <v>2916143595520</v>
+        <v>2925540409344</v>
       </c>
       <c r="G3" t="n">
-        <v>16.79</v>
+        <v>16.78</v>
       </c>
       <c r="H3" t="n">
         <v>19.3459</v>
       </c>
       <c r="I3" t="n">
-        <v>23.38088</v>
+        <v>23.470201</v>
       </c>
       <c r="J3" t="n">
-        <v>20.291897</v>
+        <v>20.357285</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="L3" t="n">
-        <v>9.162397</v>
+        <v>9.191921000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04276998713588832</v>
+        <v>0.04260721631160654</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0492807560531377</v>
+        <v>0.0491224640073128</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.04435999870300293</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005020759638953126</v>
+        <v>0.004762465304309869</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4387,51 +4909,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>594.75</v>
+        <v>600.21</v>
       </c>
       <c r="F4" t="n">
-        <v>1509727272960</v>
+        <v>1523587088384</v>
       </c>
       <c r="G4" t="n">
-        <v>27.48</v>
+        <v>27.49</v>
       </c>
       <c r="H4" t="n">
         <v>36.24596</v>
       </c>
       <c r="I4" t="n">
-        <v>21.643013</v>
+        <v>21.83376</v>
       </c>
       <c r="J4" t="n">
-        <v>16.408726</v>
+        <v>16.559362</v>
       </c>
       <c r="K4" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="L4" t="n">
-        <v>7.023196</v>
+        <v>7.0876713</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04620428751576293</v>
+        <v>0.0458006364439113</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06094318621269441</v>
+        <v>0.06038879725429432</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.04435999870300293</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01668318979850984</v>
+        <v>0.01602879855129139</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4445,10 +4967,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>247.55</v>
+        <v>246</v>
       </c>
       <c r="F5" t="n">
-        <v>2662922452992</v>
+        <v>2646249046016</v>
       </c>
       <c r="G5" t="n">
         <v>7.77</v>
@@ -4457,39 +4979,39 @@
         <v>9.859959999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>31.859716</v>
+        <v>31.660233</v>
       </c>
       <c r="J5" t="n">
-        <v>25.106594</v>
+        <v>24.949392</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.585095</v>
+        <v>3.5626476</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03138759846495657</v>
+        <v>0.03158536585365854</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03983017572207635</v>
+        <v>0.04008113821138211</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.04435999870300293</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.004429820692108226</v>
+        <v>-0.004278860491620823</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4503,51 +5025,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>298.84</v>
+        <v>299.24</v>
       </c>
       <c r="F6" t="n">
-        <v>4389169266688</v>
+        <v>4395044175872</v>
       </c>
       <c r="G6" t="n">
-        <v>8.27</v>
+        <v>8.26</v>
       </c>
       <c r="H6" t="n">
         <v>9.594989999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>36.135426</v>
+        <v>36.2276</v>
       </c>
       <c r="J6" t="n">
-        <v>31.14542</v>
+        <v>31.187109</v>
       </c>
       <c r="K6" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="L6" t="n">
-        <v>9.722554000000001</v>
+        <v>9.735567</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02767367152991567</v>
+        <v>0.02760326159604331</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03210744880203453</v>
+        <v>0.03206453014302901</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.04435999870300293</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01215254761215004</v>
+        <v>-0.01229546855997393</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4561,51 +5083,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>209.58</v>
+        <v>207.41</v>
       </c>
       <c r="F7" t="n">
-        <v>5076237156352</v>
+        <v>5023677808640</v>
       </c>
       <c r="G7" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="H7" t="n">
         <v>12.72715</v>
       </c>
       <c r="I7" t="n">
-        <v>32.144173</v>
+        <v>31.762634</v>
       </c>
       <c r="J7" t="n">
-        <v>16.46716</v>
+        <v>16.296658</v>
       </c>
       <c r="K7" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>20.025314</v>
+        <v>19.817972</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03110983872506918</v>
+        <v>0.03148353502724073</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06072693005057734</v>
+        <v>0.06136227761438696</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.04435999870300293</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01646693363639277</v>
+        <v>0.01700227891138403</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4619,51 +5141,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>524.4299999999999</v>
+        <v>507.29</v>
       </c>
       <c r="F8" t="n">
-        <v>855135879168</v>
+        <v>827187396608</v>
       </c>
       <c r="G8" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="H8" t="n">
         <v>13.1035</v>
       </c>
       <c r="I8" t="n">
-        <v>174.22923</v>
+        <v>169.66222</v>
       </c>
       <c r="J8" t="n">
-        <v>40.02213</v>
+        <v>38.714085</v>
       </c>
       <c r="K8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="L8" t="n">
-        <v>22.83163</v>
+        <v>22.085423</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005739564860896593</v>
+        <v>0.005894064539021073</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02498617546669718</v>
+        <v>0.0258303928719273</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.04435999870300293</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01927382094748739</v>
+        <v>-0.01852960583107563</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4677,10 +5199,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>379.26</v>
+        <v>376.71</v>
       </c>
       <c r="F9" t="n">
-        <v>1804359958528</v>
+        <v>1792228065280</v>
       </c>
       <c r="G9" t="n">
         <v>6.03</v>
@@ -4689,39 +5211,39 @@
         <v>19.35046</v>
       </c>
       <c r="I9" t="n">
-        <v>62.895523</v>
+        <v>62.472633</v>
       </c>
       <c r="J9" t="n">
-        <v>19.599535</v>
+        <v>19.467754</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="L9" t="n">
-        <v>23.909891</v>
+        <v>23.74913</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01589938300901756</v>
+        <v>0.01600700804332245</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05102162105152139</v>
+        <v>0.05136699317777602</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.04435999870300293</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006761624637336816</v>
+        <v>0.007006994474773084</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4735,10 +5257,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>78.5899</v>
+        <v>78.72</v>
       </c>
       <c r="F10" t="n">
-        <v>330926227456</v>
+        <v>331474075648</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -4747,28 +5269,28 @@
         <v>3.84196</v>
       </c>
       <c r="I10" t="n">
-        <v>25.35158</v>
+        <v>25.393549</v>
       </c>
       <c r="J10" t="n">
-        <v>20.455679</v>
+        <v>20.489542</v>
       </c>
       <c r="K10" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="L10" t="n">
-        <v>7.0575023</v>
+        <v>7.069186</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03944527222963765</v>
+        <v>0.03938008130081301</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04888618003076731</v>
+        <v>0.04880538617886179</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.04435999870300293</v>
       </c>
       <c r="P10" t="n">
-        <v>0.004626183616582735</v>
+        <v>0.004445387475858854</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P73"/>
+  <dimension ref="A1:P82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4199,16 +4199,16 @@
         <v>9.735567</v>
       </c>
       <c r="M65" t="n">
-        <v>0.02760326159604331</v>
+        <v>0.0276032615960433</v>
       </c>
       <c r="N65" t="n">
-        <v>0.03206453014302901</v>
+        <v>0.032064530143029</v>
       </c>
       <c r="O65" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.0443599987030029</v>
       </c>
       <c r="P65" t="n">
-        <v>-0.01229546855997393</v>
+        <v>-0.0122954685599739</v>
       </c>
     </row>
     <row r="66">
@@ -4257,16 +4257,16 @@
         <v>22.085423</v>
       </c>
       <c r="M66" t="n">
-        <v>0.005894064539021073</v>
+        <v>0.005894064539021</v>
       </c>
       <c r="N66" t="n">
         <v>0.0258303928719273</v>
       </c>
       <c r="O66" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.0443599987030029</v>
       </c>
       <c r="P66" t="n">
-        <v>-0.01852960583107563</v>
+        <v>-0.0185296058310756</v>
       </c>
     </row>
     <row r="67">
@@ -4315,16 +4315,16 @@
         <v>3.5626476</v>
       </c>
       <c r="M67" t="n">
-        <v>0.03158536585365854</v>
+        <v>0.0315853658536585</v>
       </c>
       <c r="N67" t="n">
-        <v>0.04008113821138211</v>
+        <v>0.0400811382113821</v>
       </c>
       <c r="O67" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.0443599987030029</v>
       </c>
       <c r="P67" t="n">
-        <v>-0.004278860491620823</v>
+        <v>-0.0042788604916208</v>
       </c>
     </row>
     <row r="68">
@@ -4373,16 +4373,16 @@
         <v>23.74913</v>
       </c>
       <c r="M68" t="n">
-        <v>0.01600700804332245</v>
+        <v>0.0160070080433224</v>
       </c>
       <c r="N68" t="n">
-        <v>0.05136699317777602</v>
+        <v>0.051366993177776</v>
       </c>
       <c r="O68" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.0443599987030029</v>
       </c>
       <c r="P68" t="n">
-        <v>0.007006994474773084</v>
+        <v>0.007006994474773</v>
       </c>
     </row>
     <row r="69">
@@ -4431,16 +4431,16 @@
         <v>10.718098</v>
       </c>
       <c r="M69" t="n">
-        <v>0.03530045809754783</v>
+        <v>0.0353004580975478</v>
       </c>
       <c r="N69" t="n">
-        <v>0.03906332524925896</v>
+        <v>0.0390633252492589</v>
       </c>
       <c r="O69" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.0443599987030029</v>
       </c>
       <c r="P69" t="n">
-        <v>-0.005296673453743975</v>
+        <v>-0.0052966734537439</v>
       </c>
     </row>
     <row r="70">
@@ -4489,16 +4489,16 @@
         <v>7.0876713</v>
       </c>
       <c r="M70" t="n">
-        <v>0.0458006364439113</v>
+        <v>0.0458006364439112</v>
       </c>
       <c r="N70" t="n">
-        <v>0.06038879725429432</v>
+        <v>0.0603887972542943</v>
       </c>
       <c r="O70" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.0443599987030029</v>
       </c>
       <c r="P70" t="n">
-        <v>0.01602879855129139</v>
+        <v>0.0160287985512913</v>
       </c>
     </row>
     <row r="71">
@@ -4547,16 +4547,16 @@
         <v>9.191921000000001</v>
       </c>
       <c r="M71" t="n">
-        <v>0.04260721631160654</v>
+        <v>0.0426072163116065</v>
       </c>
       <c r="N71" t="n">
         <v>0.0491224640073128</v>
       </c>
       <c r="O71" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.0443599987030029</v>
       </c>
       <c r="P71" t="n">
-        <v>0.004762465304309869</v>
+        <v>0.0047624653043098</v>
       </c>
     </row>
     <row r="72">
@@ -4605,16 +4605,16 @@
         <v>7.069186</v>
       </c>
       <c r="M72" t="n">
-        <v>0.03938008130081301</v>
+        <v>0.039380081300813</v>
       </c>
       <c r="N72" t="n">
-        <v>0.04880538617886179</v>
+        <v>0.0488053861788617</v>
       </c>
       <c r="O72" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.0443599987030029</v>
       </c>
       <c r="P72" t="n">
-        <v>0.004445387475858854</v>
+        <v>0.0044453874758588</v>
       </c>
     </row>
     <row r="73">
@@ -4663,16 +4663,538 @@
         <v>19.817972</v>
       </c>
       <c r="M73" t="n">
-        <v>0.03148353502724073</v>
+        <v>0.0314835350272407</v>
       </c>
       <c r="N73" t="n">
-        <v>0.06136227761438696</v>
+        <v>0.0613622776143869</v>
       </c>
       <c r="O73" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.0443599987030029</v>
       </c>
       <c r="P73" t="n">
-        <v>0.01700227891138403</v>
+        <v>0.017002278911384</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>295.95</v>
+      </c>
+      <c r="F74" t="n">
+        <v>4346723172352</v>
+      </c>
+      <c r="G74" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H74" t="n">
+        <v>9.594989999999999</v>
+      </c>
+      <c r="I74" t="n">
+        <v>35.8293</v>
+      </c>
+      <c r="J74" t="n">
+        <v>30.844223</v>
+      </c>
+      <c r="K74" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L74" t="n">
+        <v>9.6285305</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.02791011995269471</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.03242098327420172</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P74" t="n">
+        <v>-0.01244901661135736</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>512.48</v>
+      </c>
+      <c r="F75" t="n">
+        <v>835650125824</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H75" t="n">
+        <v>13.1035</v>
+      </c>
+      <c r="I75" t="n">
+        <v>171.39798</v>
+      </c>
+      <c r="J75" t="n">
+        <v>39.110157</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L75" t="n">
+        <v>22.311373</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.00583437402435217</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.02556880268498283</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P75" t="n">
+        <v>-0.01930119720057626</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2554813480960</v>
+      </c>
+      <c r="G76" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="H76" t="n">
+        <v>9.859959999999999</v>
+      </c>
+      <c r="I76" t="n">
+        <v>30.56628</v>
+      </c>
+      <c r="J76" t="n">
+        <v>24.08732</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L76" t="n">
+        <v>3.4395478</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.03271578947368421</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.04151562105263158</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P76" t="n">
+        <v>-0.00335437883292751</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>392.9</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1869253312512</v>
+      </c>
+      <c r="G77" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="H77" t="n">
+        <v>19.35046</v>
+      </c>
+      <c r="I77" t="n">
+        <v>65.15754</v>
+      </c>
+      <c r="J77" t="n">
+        <v>20.304426</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L77" t="n">
+        <v>24.769806</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.01534741664545686</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.04925034359888013</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.004380343713321043</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>362.1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>4418551939072</v>
+      </c>
+      <c r="G78" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>14.4964</v>
+      </c>
+      <c r="I78" t="n">
+        <v>27.64122</v>
+      </c>
+      <c r="J78" t="n">
+        <v>24.978617</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L78" t="n">
+        <v>10.45816</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.03617785142225904</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.04003424468378901</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P78" t="n">
+        <v>-0.004835755201770077</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>567.58</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1440758366208</v>
+      </c>
+      <c r="G79" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="H79" t="n">
+        <v>36.24596</v>
+      </c>
+      <c r="I79" t="n">
+        <v>20.646782</v>
+      </c>
+      <c r="J79" t="n">
+        <v>15.659125</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L79" t="n">
+        <v>6.7023554</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.04843370097607385</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.06386053067408999</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.01899053078853091</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>378.91</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2814708285440</v>
+      </c>
+      <c r="G80" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="H80" t="n">
+        <v>19.3459</v>
+      </c>
+      <c r="I80" t="n">
+        <v>22.581049</v>
+      </c>
+      <c r="J80" t="n">
+        <v>19.586063</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L80" t="n">
+        <v>8.843692000000001</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.04428492254097279</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.05105671531498245</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.00618671542942336</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>76.95999999999999</v>
+      </c>
+      <c r="F81" t="n">
+        <v>324063068160</v>
+      </c>
+      <c r="G81" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3.84196</v>
+      </c>
+      <c r="I81" t="n">
+        <v>24.825808</v>
+      </c>
+      <c r="J81" t="n">
+        <v>20.031443</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L81" t="n">
+        <v>6.911135</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.04028066528066528</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.04992151767151767</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.005051517785958588</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>204.65</v>
+      </c>
+      <c r="F82" t="n">
+        <v>4956827418624</v>
+      </c>
+      <c r="G82" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H82" t="n">
+        <v>12.72715</v>
+      </c>
+      <c r="I82" t="n">
+        <v>31.339968</v>
+      </c>
+      <c r="J82" t="n">
+        <v>16.079798</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L82" t="n">
+        <v>19.554255</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.03190813584168092</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.0621898363058881</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0.01731983642032901</v>
       </c>
     </row>
   </sheetData>
@@ -4774,12 +5296,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4793,10 +5315,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>371.1</v>
+        <v>362.1</v>
       </c>
       <c r="F2" t="n">
-        <v>4528375070720</v>
+        <v>4418551939072</v>
       </c>
       <c r="G2" t="n">
         <v>13.1</v>
@@ -4805,39 +5327,39 @@
         <v>14.4964</v>
       </c>
       <c r="I2" t="n">
-        <v>28.328243</v>
+        <v>27.64122</v>
       </c>
       <c r="J2" t="n">
-        <v>25.59946</v>
+        <v>24.978617</v>
       </c>
       <c r="K2" t="n">
         <v>1.46</v>
       </c>
       <c r="L2" t="n">
-        <v>10.718098</v>
+        <v>10.45816</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03530045809754783</v>
+        <v>0.03617785142225904</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03906332524925896</v>
+        <v>0.04003424468378901</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005296673453743975</v>
+        <v>-0.004835755201770077</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4851,10 +5373,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>393.83</v>
+        <v>378.91</v>
       </c>
       <c r="F3" t="n">
-        <v>2925540409344</v>
+        <v>2814708285440</v>
       </c>
       <c r="G3" t="n">
         <v>16.78</v>
@@ -4863,39 +5385,39 @@
         <v>19.3459</v>
       </c>
       <c r="I3" t="n">
-        <v>23.470201</v>
+        <v>22.581049</v>
       </c>
       <c r="J3" t="n">
-        <v>20.357285</v>
+        <v>19.586063</v>
       </c>
       <c r="K3" t="n">
         <v>1.22</v>
       </c>
       <c r="L3" t="n">
-        <v>9.191921000000001</v>
+        <v>8.843692000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04260721631160654</v>
+        <v>0.04428492254097279</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0491224640073128</v>
+        <v>0.05105671531498245</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004762465304309869</v>
+        <v>0.00618671542942336</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4909,10 +5431,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>600.21</v>
+        <v>567.58</v>
       </c>
       <c r="F4" t="n">
-        <v>1523587088384</v>
+        <v>1440758366208</v>
       </c>
       <c r="G4" t="n">
         <v>27.49</v>
@@ -4921,39 +5443,39 @@
         <v>36.24596</v>
       </c>
       <c r="I4" t="n">
-        <v>21.83376</v>
+        <v>20.646782</v>
       </c>
       <c r="J4" t="n">
-        <v>16.559362</v>
+        <v>15.659125</v>
       </c>
       <c r="K4" t="n">
         <v>0.87</v>
       </c>
       <c r="L4" t="n">
-        <v>7.0876713</v>
+        <v>6.7023554</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0458006364439113</v>
+        <v>0.04843370097607385</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06038879725429432</v>
+        <v>0.06386053067408999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01602879855129139</v>
+        <v>0.01899053078853091</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4967,10 +5489,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>246</v>
+        <v>237.5</v>
       </c>
       <c r="F5" t="n">
-        <v>2646249046016</v>
+        <v>2554813480960</v>
       </c>
       <c r="G5" t="n">
         <v>7.77</v>
@@ -4979,39 +5501,39 @@
         <v>9.859959999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>31.660233</v>
+        <v>30.56628</v>
       </c>
       <c r="J5" t="n">
-        <v>24.949392</v>
+        <v>24.08732</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5626476</v>
+        <v>3.4395478</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03158536585365854</v>
+        <v>0.03271578947368421</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04008113821138211</v>
+        <v>0.04151562105263158</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.004278860491620823</v>
+        <v>-0.00335437883292751</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5025,10 +5547,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>299.24</v>
+        <v>295.95</v>
       </c>
       <c r="F6" t="n">
-        <v>4395044175872</v>
+        <v>4346723172352</v>
       </c>
       <c r="G6" t="n">
         <v>8.26</v>
@@ -5037,39 +5559,39 @@
         <v>9.594989999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>36.2276</v>
+        <v>35.8293</v>
       </c>
       <c r="J6" t="n">
-        <v>31.187109</v>
+        <v>30.844223</v>
       </c>
       <c r="K6" t="n">
         <v>2.42</v>
       </c>
       <c r="L6" t="n">
-        <v>9.735567</v>
+        <v>9.6285305</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02760326159604331</v>
+        <v>0.02791011995269471</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03206453014302901</v>
+        <v>0.03242098327420172</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01229546855997393</v>
+        <v>-0.01244901661135736</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5083,10 +5605,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>207.41</v>
+        <v>204.65</v>
       </c>
       <c r="F7" t="n">
-        <v>5023677808640</v>
+        <v>4956827418624</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
@@ -5095,39 +5617,39 @@
         <v>12.72715</v>
       </c>
       <c r="I7" t="n">
-        <v>31.762634</v>
+        <v>31.339968</v>
       </c>
       <c r="J7" t="n">
-        <v>16.296658</v>
+        <v>16.079798</v>
       </c>
       <c r="K7" t="n">
         <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>19.817972</v>
+        <v>19.554255</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03148353502724073</v>
+        <v>0.03190813584168092</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06136227761438696</v>
+        <v>0.0621898363058881</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01700227891138403</v>
+        <v>0.01731983642032901</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5141,10 +5663,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>507.29</v>
+        <v>512.48</v>
       </c>
       <c r="F8" t="n">
-        <v>827187396608</v>
+        <v>835650125824</v>
       </c>
       <c r="G8" t="n">
         <v>2.99</v>
@@ -5153,39 +5675,39 @@
         <v>13.1035</v>
       </c>
       <c r="I8" t="n">
-        <v>169.66222</v>
+        <v>171.39798</v>
       </c>
       <c r="J8" t="n">
-        <v>38.714085</v>
+        <v>39.110157</v>
       </c>
       <c r="K8" t="n">
         <v>1.22</v>
       </c>
       <c r="L8" t="n">
-        <v>22.085423</v>
+        <v>22.311373</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005894064539021073</v>
+        <v>0.00583437402435217</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0258303928719273</v>
+        <v>0.02556880268498283</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01852960583107563</v>
+        <v>-0.01930119720057626</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5199,10 +5721,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>376.71</v>
+        <v>392.9</v>
       </c>
       <c r="F9" t="n">
-        <v>1792228065280</v>
+        <v>1869253312512</v>
       </c>
       <c r="G9" t="n">
         <v>6.03</v>
@@ -5211,39 +5733,39 @@
         <v>19.35046</v>
       </c>
       <c r="I9" t="n">
-        <v>62.472633</v>
+        <v>65.15754</v>
       </c>
       <c r="J9" t="n">
-        <v>19.467754</v>
+        <v>20.304426</v>
       </c>
       <c r="K9" t="n">
         <v>0.68</v>
       </c>
       <c r="L9" t="n">
-        <v>23.74913</v>
+        <v>24.769806</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01600700804332245</v>
+        <v>0.01534741664545686</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05136699317777602</v>
+        <v>0.04925034359888013</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P9" t="n">
-        <v>0.007006994474773084</v>
+        <v>0.004380343713321043</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5257,10 +5779,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>78.72</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>331474075648</v>
+        <v>324063068160</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -5269,28 +5791,28 @@
         <v>3.84196</v>
       </c>
       <c r="I10" t="n">
-        <v>25.393549</v>
+        <v>24.825808</v>
       </c>
       <c r="J10" t="n">
-        <v>20.489542</v>
+        <v>20.031443</v>
       </c>
       <c r="K10" t="n">
         <v>1.55</v>
       </c>
       <c r="L10" t="n">
-        <v>7.069186</v>
+        <v>6.911135</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03938008130081301</v>
+        <v>0.04028066528066528</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04880538617886179</v>
+        <v>0.04992151767151767</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04435999870300293</v>
+        <v>0.04486999988555909</v>
       </c>
       <c r="P10" t="n">
-        <v>0.004445387475858854</v>
+        <v>0.005051517785958588</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P82"/>
+  <dimension ref="A1:P91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4721,16 +4721,16 @@
         <v>9.6285305</v>
       </c>
       <c r="M74" t="n">
-        <v>0.02791011995269471</v>
+        <v>0.0279101199526947</v>
       </c>
       <c r="N74" t="n">
-        <v>0.03242098327420172</v>
+        <v>0.0324209832742017</v>
       </c>
       <c r="O74" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P74" t="n">
-        <v>-0.01244901661135736</v>
+        <v>-0.0124490166113573</v>
       </c>
     </row>
     <row r="75">
@@ -4779,16 +4779,16 @@
         <v>22.311373</v>
       </c>
       <c r="M75" t="n">
-        <v>0.00583437402435217</v>
+        <v>0.0058343740243521</v>
       </c>
       <c r="N75" t="n">
-        <v>0.02556880268498283</v>
+        <v>0.0255688026849828</v>
       </c>
       <c r="O75" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P75" t="n">
-        <v>-0.01930119720057626</v>
+        <v>-0.0193011972005762</v>
       </c>
     </row>
     <row r="76">
@@ -4837,16 +4837,16 @@
         <v>3.4395478</v>
       </c>
       <c r="M76" t="n">
-        <v>0.03271578947368421</v>
+        <v>0.0327157894736842</v>
       </c>
       <c r="N76" t="n">
-        <v>0.04151562105263158</v>
+        <v>0.0415156210526315</v>
       </c>
       <c r="O76" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P76" t="n">
-        <v>-0.00335437883292751</v>
+        <v>-0.0033543788329275</v>
       </c>
     </row>
     <row r="77">
@@ -4895,16 +4895,16 @@
         <v>24.769806</v>
       </c>
       <c r="M77" t="n">
-        <v>0.01534741664545686</v>
+        <v>0.0153474166454568</v>
       </c>
       <c r="N77" t="n">
-        <v>0.04925034359888013</v>
+        <v>0.0492503435988801</v>
       </c>
       <c r="O77" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P77" t="n">
-        <v>0.004380343713321043</v>
+        <v>0.004380343713321</v>
       </c>
     </row>
     <row r="78">
@@ -4953,16 +4953,16 @@
         <v>10.45816</v>
       </c>
       <c r="M78" t="n">
-        <v>0.03617785142225904</v>
+        <v>0.036177851422259</v>
       </c>
       <c r="N78" t="n">
-        <v>0.04003424468378901</v>
+        <v>0.040034244683789</v>
       </c>
       <c r="O78" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.004835755201770077</v>
+        <v>-0.00483575520177</v>
       </c>
     </row>
     <row r="79">
@@ -5011,16 +5011,16 @@
         <v>6.7023554</v>
       </c>
       <c r="M79" t="n">
-        <v>0.04843370097607385</v>
+        <v>0.0484337009760738</v>
       </c>
       <c r="N79" t="n">
-        <v>0.06386053067408999</v>
+        <v>0.06386053067408989</v>
       </c>
       <c r="O79" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P79" t="n">
-        <v>0.01899053078853091</v>
+        <v>0.0189905307885309</v>
       </c>
     </row>
     <row r="80">
@@ -5069,16 +5069,16 @@
         <v>8.843692000000001</v>
       </c>
       <c r="M80" t="n">
-        <v>0.04428492254097279</v>
+        <v>0.0442849225409727</v>
       </c>
       <c r="N80" t="n">
-        <v>0.05105671531498245</v>
+        <v>0.0510567153149824</v>
       </c>
       <c r="O80" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P80" t="n">
-        <v>0.00618671542942336</v>
+        <v>0.0061867154294233</v>
       </c>
     </row>
     <row r="81">
@@ -5127,16 +5127,16 @@
         <v>6.911135</v>
       </c>
       <c r="M81" t="n">
-        <v>0.04028066528066528</v>
+        <v>0.0402806652806652</v>
       </c>
       <c r="N81" t="n">
-        <v>0.04992151767151767</v>
+        <v>0.0499215176715176</v>
       </c>
       <c r="O81" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P81" t="n">
-        <v>0.005051517785958588</v>
+        <v>0.0050515177859585</v>
       </c>
     </row>
     <row r="82">
@@ -5185,16 +5185,538 @@
         <v>19.554255</v>
       </c>
       <c r="M82" t="n">
-        <v>0.03190813584168092</v>
+        <v>0.0319081358416809</v>
       </c>
       <c r="N82" t="n">
         <v>0.0621898363058881</v>
       </c>
       <c r="O82" t="n">
+        <v>0.044869999885559</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0.017319836420329</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>298.01</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4376979046400</v>
+      </c>
+      <c r="G83" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H83" t="n">
+        <v>9.594989999999999</v>
+      </c>
+      <c r="I83" t="n">
+        <v>36.078693</v>
+      </c>
+      <c r="J83" t="n">
+        <v>31.058918</v>
+      </c>
+      <c r="K83" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="L83" t="n">
+        <v>9.695551</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.02771719069829872</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0.03219687258816818</v>
+      </c>
+      <c r="O83" t="n">
         <v>0.04486999988555909</v>
       </c>
-      <c r="P82" t="n">
-        <v>0.01731983642032901</v>
+      <c r="P83" t="n">
+        <v>-0.0126731272973909</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>537.37</v>
+      </c>
+      <c r="F84" t="n">
+        <v>876235849728</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H84" t="n">
+        <v>13.1035</v>
+      </c>
+      <c r="I84" t="n">
+        <v>179.72241</v>
+      </c>
+      <c r="J84" t="n">
+        <v>41.00965</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L84" t="n">
+        <v>23.394987</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.005564136442302325</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.02438450229823027</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P84" t="n">
+        <v>-0.02048549758732882</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>244.39</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2628929978368</v>
+      </c>
+      <c r="G85" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="H85" t="n">
+        <v>9.859959999999999</v>
+      </c>
+      <c r="I85" t="n">
+        <v>31.453024</v>
+      </c>
+      <c r="J85" t="n">
+        <v>24.786106</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L85" t="n">
+        <v>3.539331</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.03179344490363763</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.04034518597323949</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P85" t="n">
+        <v>-0.00452481391231959</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>411.35</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1957030658048</v>
+      </c>
+      <c r="G86" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="H86" t="n">
+        <v>19.35046</v>
+      </c>
+      <c r="I86" t="n">
+        <v>68.21725000000001</v>
+      </c>
+      <c r="J86" t="n">
+        <v>21.257893</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L86" t="n">
+        <v>25.932959</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.01465904947125319</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.04704135164701592</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.002171351761456837</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>367.46</v>
+      </c>
+      <c r="F87" t="n">
+        <v>4483957391360</v>
+      </c>
+      <c r="G87" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>14.4964</v>
+      </c>
+      <c r="I87" t="n">
+        <v>28.05038</v>
+      </c>
+      <c r="J87" t="n">
+        <v>25.348362</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L87" t="n">
+        <v>10.612967</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.03565013879061667</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.03945028030261797</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P87" t="n">
+        <v>-0.005419719582941115</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>577.22</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1465228591104</v>
+      </c>
+      <c r="G88" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="H88" t="n">
+        <v>36.24596</v>
+      </c>
+      <c r="I88" t="n">
+        <v>20.997452</v>
+      </c>
+      <c r="J88" t="n">
+        <v>15.925084</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L88" t="n">
+        <v>6.81619</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.0476248224247254</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0.06279401268147326</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0.01792401279591418</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>379.4</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2818348154880</v>
+      </c>
+      <c r="G89" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="H89" t="n">
+        <v>19.3459</v>
+      </c>
+      <c r="I89" t="n">
+        <v>22.610249</v>
+      </c>
+      <c r="J89" t="n">
+        <v>19.611391</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L89" t="n">
+        <v>8.855128000000001</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.04422772799156564</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.05099077490774908</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0.006120775022189995</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>77.38</v>
+      </c>
+      <c r="F90" t="n">
+        <v>325831589888</v>
+      </c>
+      <c r="G90" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>3.84196</v>
+      </c>
+      <c r="I90" t="n">
+        <v>24.96129</v>
+      </c>
+      <c r="J90" t="n">
+        <v>20.14076</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L90" t="n">
+        <v>6.9488516</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.04006203153269579</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0.04965055569914707</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0.004780555813587981</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>210.69</v>
+      </c>
+      <c r="F91" t="n">
+        <v>5103122644992</v>
+      </c>
+      <c r="G91" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H91" t="n">
+        <v>12.72715</v>
+      </c>
+      <c r="I91" t="n">
+        <v>32.26493</v>
+      </c>
+      <c r="J91" t="n">
+        <v>16.554375</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L91" t="n">
+        <v>20.131376</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.0309934026294556</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.06040699606056291</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.01553699617500383</v>
       </c>
     </row>
   </sheetData>
@@ -5296,12 +5818,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5315,10 +5837,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>362.1</v>
+        <v>367.46</v>
       </c>
       <c r="F2" t="n">
-        <v>4418551939072</v>
+        <v>4483957391360</v>
       </c>
       <c r="G2" t="n">
         <v>13.1</v>
@@ -5327,39 +5849,39 @@
         <v>14.4964</v>
       </c>
       <c r="I2" t="n">
-        <v>27.64122</v>
+        <v>28.05038</v>
       </c>
       <c r="J2" t="n">
-        <v>24.978617</v>
+        <v>25.348362</v>
       </c>
       <c r="K2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="L2" t="n">
-        <v>10.45816</v>
+        <v>10.612967</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03617785142225904</v>
+        <v>0.03565013879061667</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04003424468378901</v>
+        <v>0.03945028030261797</v>
       </c>
       <c r="O2" t="n">
         <v>0.04486999988555909</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.004835755201770077</v>
+        <v>-0.005419719582941115</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5373,10 +5895,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>378.91</v>
+        <v>379.4</v>
       </c>
       <c r="F3" t="n">
-        <v>2814708285440</v>
+        <v>2818348154880</v>
       </c>
       <c r="G3" t="n">
         <v>16.78</v>
@@ -5385,39 +5907,39 @@
         <v>19.3459</v>
       </c>
       <c r="I3" t="n">
-        <v>22.581049</v>
+        <v>22.610249</v>
       </c>
       <c r="J3" t="n">
-        <v>19.586063</v>
+        <v>19.611391</v>
       </c>
       <c r="K3" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="L3" t="n">
-        <v>8.843692000000001</v>
+        <v>8.855128000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04428492254097279</v>
+        <v>0.04422772799156564</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05105671531498245</v>
+        <v>0.05099077490774908</v>
       </c>
       <c r="O3" t="n">
         <v>0.04486999988555909</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00618671542942336</v>
+        <v>0.006120775022189995</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5431,10 +5953,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>567.58</v>
+        <v>577.22</v>
       </c>
       <c r="F4" t="n">
-        <v>1440758366208</v>
+        <v>1465228591104</v>
       </c>
       <c r="G4" t="n">
         <v>27.49</v>
@@ -5443,39 +5965,39 @@
         <v>36.24596</v>
       </c>
       <c r="I4" t="n">
-        <v>20.646782</v>
+        <v>20.997452</v>
       </c>
       <c r="J4" t="n">
-        <v>15.659125</v>
+        <v>15.925084</v>
       </c>
       <c r="K4" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="L4" t="n">
-        <v>6.7023554</v>
+        <v>6.81619</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04843370097607385</v>
+        <v>0.0476248224247254</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06386053067408999</v>
+        <v>0.06279401268147326</v>
       </c>
       <c r="O4" t="n">
         <v>0.04486999988555909</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01899053078853091</v>
+        <v>0.01792401279591418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5489,10 +6011,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>237.5</v>
+        <v>244.39</v>
       </c>
       <c r="F5" t="n">
-        <v>2554813480960</v>
+        <v>2628929978368</v>
       </c>
       <c r="G5" t="n">
         <v>7.77</v>
@@ -5501,39 +6023,39 @@
         <v>9.859959999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>30.56628</v>
+        <v>31.453024</v>
       </c>
       <c r="J5" t="n">
-        <v>24.08732</v>
+        <v>24.786106</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4395478</v>
+        <v>3.539331</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03271578947368421</v>
+        <v>0.03179344490363763</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04151562105263158</v>
+        <v>0.04034518597323949</v>
       </c>
       <c r="O5" t="n">
         <v>0.04486999988555909</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.00335437883292751</v>
+        <v>-0.00452481391231959</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5547,10 +6069,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>295.95</v>
+        <v>298.01</v>
       </c>
       <c r="F6" t="n">
-        <v>4346723172352</v>
+        <v>4376979046400</v>
       </c>
       <c r="G6" t="n">
         <v>8.26</v>
@@ -5559,39 +6081,39 @@
         <v>9.594989999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>35.8293</v>
+        <v>36.078693</v>
       </c>
       <c r="J6" t="n">
-        <v>30.844223</v>
+        <v>31.058918</v>
       </c>
       <c r="K6" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="L6" t="n">
-        <v>9.6285305</v>
+        <v>9.695551</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02791011995269471</v>
+        <v>0.02771719069829872</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03242098327420172</v>
+        <v>0.03219687258816818</v>
       </c>
       <c r="O6" t="n">
         <v>0.04486999988555909</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01244901661135736</v>
+        <v>-0.0126731272973909</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5605,10 +6127,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>204.65</v>
+        <v>210.69</v>
       </c>
       <c r="F7" t="n">
-        <v>4956827418624</v>
+        <v>5103122644992</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
@@ -5617,39 +6139,39 @@
         <v>12.72715</v>
       </c>
       <c r="I7" t="n">
-        <v>31.339968</v>
+        <v>32.26493</v>
       </c>
       <c r="J7" t="n">
-        <v>16.079798</v>
+        <v>16.554375</v>
       </c>
       <c r="K7" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="L7" t="n">
-        <v>19.554255</v>
+        <v>20.131376</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03190813584168092</v>
+        <v>0.0309934026294556</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0621898363058881</v>
+        <v>0.06040699606056291</v>
       </c>
       <c r="O7" t="n">
         <v>0.04486999988555909</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01731983642032901</v>
+        <v>0.01553699617500383</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5663,10 +6185,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>512.48</v>
+        <v>537.37</v>
       </c>
       <c r="F8" t="n">
-        <v>835650125824</v>
+        <v>876235849728</v>
       </c>
       <c r="G8" t="n">
         <v>2.99</v>
@@ -5675,39 +6197,39 @@
         <v>13.1035</v>
       </c>
       <c r="I8" t="n">
-        <v>171.39798</v>
+        <v>179.72241</v>
       </c>
       <c r="J8" t="n">
-        <v>39.110157</v>
+        <v>41.00965</v>
       </c>
       <c r="K8" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="L8" t="n">
-        <v>22.311373</v>
+        <v>23.394987</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00583437402435217</v>
+        <v>0.005564136442302325</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02556880268498283</v>
+        <v>0.02438450229823027</v>
       </c>
       <c r="O8" t="n">
         <v>0.04486999988555909</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01930119720057626</v>
+        <v>-0.02048549758732882</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5721,10 +6243,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392.9</v>
+        <v>411.35</v>
       </c>
       <c r="F9" t="n">
-        <v>1869253312512</v>
+        <v>1957030658048</v>
       </c>
       <c r="G9" t="n">
         <v>6.03</v>
@@ -5733,39 +6255,39 @@
         <v>19.35046</v>
       </c>
       <c r="I9" t="n">
-        <v>65.15754</v>
+        <v>68.21725000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>20.304426</v>
+        <v>21.257893</v>
       </c>
       <c r="K9" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="L9" t="n">
-        <v>24.769806</v>
+        <v>25.932959</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01534741664545686</v>
+        <v>0.01465904947125319</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04925034359888013</v>
+        <v>0.04704135164701592</v>
       </c>
       <c r="O9" t="n">
         <v>0.04486999988555909</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004380343713321043</v>
+        <v>0.002171351761456837</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5779,10 +6301,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>76.95999999999999</v>
+        <v>77.38</v>
       </c>
       <c r="F10" t="n">
-        <v>324063068160</v>
+        <v>325831589888</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -5791,28 +6313,28 @@
         <v>3.84196</v>
       </c>
       <c r="I10" t="n">
-        <v>24.825808</v>
+        <v>24.96129</v>
       </c>
       <c r="J10" t="n">
-        <v>20.031443</v>
+        <v>20.14076</v>
       </c>
       <c r="K10" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="L10" t="n">
-        <v>6.911135</v>
+        <v>6.9488516</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04028066528066528</v>
+        <v>0.04006203153269579</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04992151767151767</v>
+        <v>0.04965055569914707</v>
       </c>
       <c r="O10" t="n">
         <v>0.04486999988555909</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005051517785958588</v>
+        <v>0.004780555813587981</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P91"/>
+  <dimension ref="A1:P100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5243,13 +5243,13 @@
         <v>9.695551</v>
       </c>
       <c r="M83" t="n">
-        <v>0.02771719069829872</v>
+        <v>0.0277171906982987</v>
       </c>
       <c r="N83" t="n">
-        <v>0.03219687258816818</v>
+        <v>0.0321968725881681</v>
       </c>
       <c r="O83" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P83" t="n">
         <v>-0.0126731272973909</v>
@@ -5301,16 +5301,16 @@
         <v>23.394987</v>
       </c>
       <c r="M84" t="n">
-        <v>0.005564136442302325</v>
+        <v>0.0055641364423023</v>
       </c>
       <c r="N84" t="n">
-        <v>0.02438450229823027</v>
+        <v>0.0243845022982302</v>
       </c>
       <c r="O84" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P84" t="n">
-        <v>-0.02048549758732882</v>
+        <v>-0.0204854975873288</v>
       </c>
     </row>
     <row r="85">
@@ -5359,16 +5359,16 @@
         <v>3.539331</v>
       </c>
       <c r="M85" t="n">
-        <v>0.03179344490363763</v>
+        <v>0.0317934449036376</v>
       </c>
       <c r="N85" t="n">
-        <v>0.04034518597323949</v>
+        <v>0.0403451859732394</v>
       </c>
       <c r="O85" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P85" t="n">
-        <v>-0.00452481391231959</v>
+        <v>-0.0045248139123195</v>
       </c>
     </row>
     <row r="86">
@@ -5417,16 +5417,16 @@
         <v>25.932959</v>
       </c>
       <c r="M86" t="n">
-        <v>0.01465904947125319</v>
+        <v>0.0146590494712531</v>
       </c>
       <c r="N86" t="n">
-        <v>0.04704135164701592</v>
+        <v>0.0470413516470159</v>
       </c>
       <c r="O86" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P86" t="n">
-        <v>0.002171351761456837</v>
+        <v>0.0021713517614568</v>
       </c>
     </row>
     <row r="87">
@@ -5475,16 +5475,16 @@
         <v>10.612967</v>
       </c>
       <c r="M87" t="n">
-        <v>0.03565013879061667</v>
+        <v>0.0356501387906166</v>
       </c>
       <c r="N87" t="n">
-        <v>0.03945028030261797</v>
+        <v>0.0394502803026179</v>
       </c>
       <c r="O87" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P87" t="n">
-        <v>-0.005419719582941115</v>
+        <v>-0.0054197195829411</v>
       </c>
     </row>
     <row r="88">
@@ -5536,13 +5536,13 @@
         <v>0.0476248224247254</v>
       </c>
       <c r="N88" t="n">
-        <v>0.06279401268147326</v>
+        <v>0.06279401268147319</v>
       </c>
       <c r="O88" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P88" t="n">
-        <v>0.01792401279591418</v>
+        <v>0.0179240127959141</v>
       </c>
     </row>
     <row r="89">
@@ -5591,16 +5591,16 @@
         <v>8.855128000000001</v>
       </c>
       <c r="M89" t="n">
-        <v>0.04422772799156564</v>
+        <v>0.0442277279915656</v>
       </c>
       <c r="N89" t="n">
-        <v>0.05099077490774908</v>
+        <v>0.050990774907749</v>
       </c>
       <c r="O89" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P89" t="n">
-        <v>0.006120775022189995</v>
+        <v>0.0061207750221899</v>
       </c>
     </row>
     <row r="90">
@@ -5649,16 +5649,16 @@
         <v>6.9488516</v>
       </c>
       <c r="M90" t="n">
-        <v>0.04006203153269579</v>
+        <v>0.0400620315326957</v>
       </c>
       <c r="N90" t="n">
-        <v>0.04965055569914707</v>
+        <v>0.049650555699147</v>
       </c>
       <c r="O90" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P90" t="n">
-        <v>0.004780555813587981</v>
+        <v>0.0047805558135879</v>
       </c>
     </row>
     <row r="91">
@@ -5710,12 +5710,534 @@
         <v>0.0309934026294556</v>
       </c>
       <c r="N91" t="n">
+        <v>0.0604069960605629</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.044869999885559</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.0155369961750038</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>298.01</v>
+      </c>
+      <c r="F92" t="n">
+        <v>4376979046400</v>
+      </c>
+      <c r="G92" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H92" t="n">
+        <v>9.594989999999999</v>
+      </c>
+      <c r="I92" t="n">
+        <v>36.122425</v>
+      </c>
+      <c r="J92" t="n">
+        <v>31.058918</v>
+      </c>
+      <c r="K92" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="L92" t="n">
+        <v>9.695551</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.02768363477735647</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.03219687258816818</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P92" t="n">
+        <v>-0.0126731272973909</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>537.37</v>
+      </c>
+      <c r="F93" t="n">
+        <v>876235849728</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H93" t="n">
+        <v>13.1035</v>
+      </c>
+      <c r="I93" t="n">
+        <v>179.72241</v>
+      </c>
+      <c r="J93" t="n">
+        <v>41.00965</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L93" t="n">
+        <v>23.394987</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.005564136442302325</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0.02438450229823027</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P93" t="n">
+        <v>-0.02048549758732882</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>244.39</v>
+      </c>
+      <c r="F94" t="n">
+        <v>2628929978368</v>
+      </c>
+      <c r="G94" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="H94" t="n">
+        <v>9.859959999999999</v>
+      </c>
+      <c r="I94" t="n">
+        <v>31.453024</v>
+      </c>
+      <c r="J94" t="n">
+        <v>24.786106</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L94" t="n">
+        <v>3.539331</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.03179344490363763</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.04034518597323949</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P94" t="n">
+        <v>-0.00452481391231959</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>411.35</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1957030658048</v>
+      </c>
+      <c r="G95" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="H95" t="n">
+        <v>19.35046</v>
+      </c>
+      <c r="I95" t="n">
+        <v>68.21725000000001</v>
+      </c>
+      <c r="J95" t="n">
+        <v>21.257893</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L95" t="n">
+        <v>25.932959</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.01465904947125319</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0.04704135164701592</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0.002171351761456837</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>367.46</v>
+      </c>
+      <c r="F96" t="n">
+        <v>4483957391360</v>
+      </c>
+      <c r="G96" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="H96" t="n">
+        <v>14.4964</v>
+      </c>
+      <c r="I96" t="n">
+        <v>28.007622</v>
+      </c>
+      <c r="J96" t="n">
+        <v>25.348362</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L96" t="n">
+        <v>10.612967</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.03570456648342676</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0.03945028030261797</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P96" t="n">
+        <v>-0.005419719582941115</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>577.22</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1465228591104</v>
+      </c>
+      <c r="G97" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="H97" t="n">
+        <v>36.24596</v>
+      </c>
+      <c r="I97" t="n">
+        <v>20.997452</v>
+      </c>
+      <c r="J97" t="n">
+        <v>15.925084</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L97" t="n">
+        <v>6.81619</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.0476248224247254</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0.06279401268147326</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.01792401279591418</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>379.4</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2818348154880</v>
+      </c>
+      <c r="G98" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="H98" t="n">
+        <v>19.3459</v>
+      </c>
+      <c r="I98" t="n">
+        <v>22.610249</v>
+      </c>
+      <c r="J98" t="n">
+        <v>19.611391</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L98" t="n">
+        <v>8.855128000000001</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.04422772799156564</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0.05099077490774908</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0.006120775022189995</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>77.38</v>
+      </c>
+      <c r="F99" t="n">
+        <v>325831589888</v>
+      </c>
+      <c r="G99" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H99" t="n">
+        <v>3.84196</v>
+      </c>
+      <c r="I99" t="n">
+        <v>24.96129</v>
+      </c>
+      <c r="J99" t="n">
+        <v>20.14076</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L99" t="n">
+        <v>6.9488516</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.04006203153269579</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.04965055569914707</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.04486999988555909</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0.004780555813587981</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>210.69</v>
+      </c>
+      <c r="F100" t="n">
+        <v>5103122644992</v>
+      </c>
+      <c r="G100" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H100" t="n">
+        <v>12.72715</v>
+      </c>
+      <c r="I100" t="n">
+        <v>32.26493</v>
+      </c>
+      <c r="J100" t="n">
+        <v>16.554375</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L100" t="n">
+        <v>20.131376</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.0309934026294556</v>
+      </c>
+      <c r="N100" t="n">
         <v>0.06040699606056291</v>
       </c>
-      <c r="O91" t="n">
+      <c r="O100" t="n">
         <v>0.04486999988555909</v>
       </c>
-      <c r="P91" t="n">
+      <c r="P100" t="n">
         <v>0.01553699617500383</v>
       </c>
     </row>
@@ -5818,12 +6340,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5843,13 +6365,13 @@
         <v>4483957391360</v>
       </c>
       <c r="G2" t="n">
-        <v>13.1</v>
+        <v>13.12</v>
       </c>
       <c r="H2" t="n">
         <v>14.4964</v>
       </c>
       <c r="I2" t="n">
-        <v>28.05038</v>
+        <v>28.007622</v>
       </c>
       <c r="J2" t="n">
         <v>25.348362</v>
@@ -5861,7 +6383,7 @@
         <v>10.612967</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03565013879061667</v>
+        <v>0.03570456648342676</v>
       </c>
       <c r="N2" t="n">
         <v>0.03945028030261797</v>
@@ -5876,12 +6398,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5934,12 +6456,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5992,12 +6514,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6050,12 +6572,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6075,13 +6597,13 @@
         <v>4376979046400</v>
       </c>
       <c r="G6" t="n">
-        <v>8.26</v>
+        <v>8.25</v>
       </c>
       <c r="H6" t="n">
         <v>9.594989999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>36.078693</v>
+        <v>36.122425</v>
       </c>
       <c r="J6" t="n">
         <v>31.058918</v>
@@ -6093,7 +6615,7 @@
         <v>9.695551</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02771719069829872</v>
+        <v>0.02768363477735647</v>
       </c>
       <c r="N6" t="n">
         <v>0.03219687258816818</v>
@@ -6108,12 +6630,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6166,12 +6688,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6224,12 +6746,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6282,12 +6804,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P100"/>
+  <dimension ref="A1:P109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5765,13 +5765,13 @@
         <v>9.695551</v>
       </c>
       <c r="M92" t="n">
-        <v>0.02768363477735647</v>
+        <v>0.0276836347773564</v>
       </c>
       <c r="N92" t="n">
-        <v>0.03219687258816818</v>
+        <v>0.0321968725881681</v>
       </c>
       <c r="O92" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P92" t="n">
         <v>-0.0126731272973909</v>
@@ -5823,16 +5823,16 @@
         <v>23.394987</v>
       </c>
       <c r="M93" t="n">
-        <v>0.005564136442302325</v>
+        <v>0.0055641364423023</v>
       </c>
       <c r="N93" t="n">
-        <v>0.02438450229823027</v>
+        <v>0.0243845022982302</v>
       </c>
       <c r="O93" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P93" t="n">
-        <v>-0.02048549758732882</v>
+        <v>-0.0204854975873288</v>
       </c>
     </row>
     <row r="94">
@@ -5881,16 +5881,16 @@
         <v>3.539331</v>
       </c>
       <c r="M94" t="n">
-        <v>0.03179344490363763</v>
+        <v>0.0317934449036376</v>
       </c>
       <c r="N94" t="n">
-        <v>0.04034518597323949</v>
+        <v>0.0403451859732394</v>
       </c>
       <c r="O94" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P94" t="n">
-        <v>-0.00452481391231959</v>
+        <v>-0.0045248139123195</v>
       </c>
     </row>
     <row r="95">
@@ -5939,16 +5939,16 @@
         <v>25.932959</v>
       </c>
       <c r="M95" t="n">
-        <v>0.01465904947125319</v>
+        <v>0.0146590494712531</v>
       </c>
       <c r="N95" t="n">
-        <v>0.04704135164701592</v>
+        <v>0.0470413516470159</v>
       </c>
       <c r="O95" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P95" t="n">
-        <v>0.002171351761456837</v>
+        <v>0.0021713517614568</v>
       </c>
     </row>
     <row r="96">
@@ -5997,16 +5997,16 @@
         <v>10.612967</v>
       </c>
       <c r="M96" t="n">
-        <v>0.03570456648342676</v>
+        <v>0.0357045664834267</v>
       </c>
       <c r="N96" t="n">
-        <v>0.03945028030261797</v>
+        <v>0.0394502803026179</v>
       </c>
       <c r="O96" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P96" t="n">
-        <v>-0.005419719582941115</v>
+        <v>-0.0054197195829411</v>
       </c>
     </row>
     <row r="97">
@@ -6058,13 +6058,13 @@
         <v>0.0476248224247254</v>
       </c>
       <c r="N97" t="n">
-        <v>0.06279401268147326</v>
+        <v>0.06279401268147319</v>
       </c>
       <c r="O97" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P97" t="n">
-        <v>0.01792401279591418</v>
+        <v>0.0179240127959141</v>
       </c>
     </row>
     <row r="98">
@@ -6113,16 +6113,16 @@
         <v>8.855128000000001</v>
       </c>
       <c r="M98" t="n">
-        <v>0.04422772799156564</v>
+        <v>0.0442277279915656</v>
       </c>
       <c r="N98" t="n">
-        <v>0.05099077490774908</v>
+        <v>0.050990774907749</v>
       </c>
       <c r="O98" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P98" t="n">
-        <v>0.006120775022189995</v>
+        <v>0.0061207750221899</v>
       </c>
     </row>
     <row r="99">
@@ -6171,16 +6171,16 @@
         <v>6.9488516</v>
       </c>
       <c r="M99" t="n">
-        <v>0.04006203153269579</v>
+        <v>0.0400620315326957</v>
       </c>
       <c r="N99" t="n">
-        <v>0.04965055569914707</v>
+        <v>0.049650555699147</v>
       </c>
       <c r="O99" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P99" t="n">
-        <v>0.004780555813587981</v>
+        <v>0.0047805558135879</v>
       </c>
     </row>
     <row r="100">
@@ -6232,13 +6232,535 @@
         <v>0.0309934026294556</v>
       </c>
       <c r="N100" t="n">
-        <v>0.06040699606056291</v>
+        <v>0.0604069960605629</v>
       </c>
       <c r="O100" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.044869999885559</v>
       </c>
       <c r="P100" t="n">
-        <v>0.01553699617500383</v>
+        <v>0.0155369961750038</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>297.01</v>
+      </c>
+      <c r="F101" t="n">
+        <v>4362291642368</v>
+      </c>
+      <c r="G101" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H101" t="n">
+        <v>9.60059</v>
+      </c>
+      <c r="I101" t="n">
+        <v>35.957626</v>
+      </c>
+      <c r="J101" t="n">
+        <v>30.936642</v>
+      </c>
+      <c r="K101" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="L101" t="n">
+        <v>9.663016000000001</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.02781051143059156</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.03232413050065654</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P101" t="n">
+        <v>-0.01218587163557393</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>551.63</v>
+      </c>
+      <c r="F102" t="n">
+        <v>899488219136</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H102" t="n">
+        <v>13.10372</v>
+      </c>
+      <c r="I102" t="n">
+        <v>185.11073</v>
+      </c>
+      <c r="J102" t="n">
+        <v>42.097206</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L102" t="n">
+        <v>24.015812</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.005402171745554085</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0.0237545456193463</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P102" t="n">
+        <v>-0.02075545651688417</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>232.79</v>
+      </c>
+      <c r="F103" t="n">
+        <v>2504147599360</v>
+      </c>
+      <c r="G103" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="H103" t="n">
+        <v>9.88035</v>
+      </c>
+      <c r="I103" t="n">
+        <v>31.629074</v>
+      </c>
+      <c r="J103" t="n">
+        <v>23.560905</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L103" t="n">
+        <v>3.3713362</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.03161647837106405</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0.042443189140427</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P103" t="n">
+        <v>-0.002066812995803476</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>392.13</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1865589981184</v>
+      </c>
+      <c r="G104" t="n">
+        <v>6</v>
+      </c>
+      <c r="H104" t="n">
+        <v>19.38501</v>
+      </c>
+      <c r="I104" t="n">
+        <v>65.355</v>
+      </c>
+      <c r="J104" t="n">
+        <v>20.228518</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L104" t="n">
+        <v>24.721262</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.01530104812179634</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0.04943516180858389</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0.004925159672353421</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>348.78</v>
+      </c>
+      <c r="F105" t="n">
+        <v>4256013221888</v>
+      </c>
+      <c r="G105" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="H105" t="n">
+        <v>14.4964</v>
+      </c>
+      <c r="I105" t="n">
+        <v>26.60412</v>
+      </c>
+      <c r="J105" t="n">
+        <v>24.059767</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L105" t="n">
+        <v>10.073452</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.03758816445897127</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0.04156316302540283</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P105" t="n">
+        <v>-0.002946839110827638</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>563.85</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1431289856000</v>
+      </c>
+      <c r="G106" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="H106" t="n">
+        <v>36.24596</v>
+      </c>
+      <c r="I106" t="n">
+        <v>20.488733</v>
+      </c>
+      <c r="J106" t="n">
+        <v>15.556215</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L106" t="n">
+        <v>6.658308</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.04880730690786556</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0.06428298306287132</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0.01977298092664085</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>367.34</v>
+      </c>
+      <c r="F107" t="n">
+        <v>2728761229312</v>
+      </c>
+      <c r="G107" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="H107" t="n">
+        <v>19.3459</v>
+      </c>
+      <c r="I107" t="n">
+        <v>21.878498</v>
+      </c>
+      <c r="J107" t="n">
+        <v>18.988003</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L107" t="n">
+        <v>8.573650000000001</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.04570697446507323</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0.05266483366908042</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0.008154831532849946</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>72.88</v>
+      </c>
+      <c r="F108" t="n">
+        <v>306883002368</v>
+      </c>
+      <c r="G108" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H108" t="n">
+        <v>3.84196</v>
+      </c>
+      <c r="I108" t="n">
+        <v>23.509678</v>
+      </c>
+      <c r="J108" t="n">
+        <v>18.969484</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L108" t="n">
+        <v>6.544744</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.04253567508232712</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0.05271624588364435</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0.008206243747413876</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>208.65</v>
+      </c>
+      <c r="F109" t="n">
+        <v>5053711646720</v>
+      </c>
+      <c r="G109" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H109" t="n">
+        <v>12.72901</v>
+      </c>
+      <c r="I109" t="n">
+        <v>31.952524</v>
+      </c>
+      <c r="J109" t="n">
+        <v>16.391691</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L109" t="n">
+        <v>19.936453</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.03129642942727055</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.0610065180924994</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0.01649651595626893</v>
       </c>
     </row>
   </sheetData>
@@ -6340,12 +6862,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6359,51 +6881,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>367.46</v>
+        <v>348.78</v>
       </c>
       <c r="F2" t="n">
-        <v>4483957391360</v>
+        <v>4256013221888</v>
       </c>
       <c r="G2" t="n">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="H2" t="n">
         <v>14.4964</v>
       </c>
       <c r="I2" t="n">
-        <v>28.007622</v>
+        <v>26.60412</v>
       </c>
       <c r="J2" t="n">
-        <v>25.348362</v>
+        <v>24.059767</v>
       </c>
       <c r="K2" t="n">
         <v>1.45</v>
       </c>
       <c r="L2" t="n">
-        <v>10.612967</v>
+        <v>10.073452</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03570456648342676</v>
+        <v>0.03758816445897127</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03945028030261797</v>
+        <v>0.04156316302540283</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04451000213623047</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005419719582941115</v>
+        <v>-0.002946839110827638</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6417,51 +6939,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>379.4</v>
+        <v>367.34</v>
       </c>
       <c r="F3" t="n">
-        <v>2818348154880</v>
+        <v>2728761229312</v>
       </c>
       <c r="G3" t="n">
-        <v>16.78</v>
+        <v>16.79</v>
       </c>
       <c r="H3" t="n">
         <v>19.3459</v>
       </c>
       <c r="I3" t="n">
-        <v>22.610249</v>
+        <v>21.878498</v>
       </c>
       <c r="J3" t="n">
-        <v>19.611391</v>
+        <v>18.988003</v>
       </c>
       <c r="K3" t="n">
         <v>1.17</v>
       </c>
       <c r="L3" t="n">
-        <v>8.855128000000001</v>
+        <v>8.573650000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04422772799156564</v>
+        <v>0.04570697446507323</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05099077490774908</v>
+        <v>0.05266483366908042</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04451000213623047</v>
       </c>
       <c r="P3" t="n">
-        <v>0.006120775022189995</v>
+        <v>0.008154831532849946</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6475,51 +6997,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>577.22</v>
+        <v>563.85</v>
       </c>
       <c r="F4" t="n">
-        <v>1465228591104</v>
+        <v>1431289856000</v>
       </c>
       <c r="G4" t="n">
-        <v>27.49</v>
+        <v>27.52</v>
       </c>
       <c r="H4" t="n">
         <v>36.24596</v>
       </c>
       <c r="I4" t="n">
-        <v>20.997452</v>
+        <v>20.488733</v>
       </c>
       <c r="J4" t="n">
-        <v>15.925084</v>
+        <v>15.556215</v>
       </c>
       <c r="K4" t="n">
         <v>0.83</v>
       </c>
       <c r="L4" t="n">
-        <v>6.81619</v>
+        <v>6.658308</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0476248224247254</v>
+        <v>0.04880730690786556</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06279401268147326</v>
+        <v>0.06428298306287132</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04451000213623047</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01792401279591418</v>
+        <v>0.01977298092664085</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6533,51 +7055,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>244.39</v>
+        <v>232.79</v>
       </c>
       <c r="F5" t="n">
-        <v>2628929978368</v>
+        <v>2504147599360</v>
       </c>
       <c r="G5" t="n">
-        <v>7.77</v>
+        <v>7.36</v>
       </c>
       <c r="H5" t="n">
-        <v>9.859959999999999</v>
+        <v>9.88035</v>
       </c>
       <c r="I5" t="n">
-        <v>31.453024</v>
+        <v>31.629074</v>
       </c>
       <c r="J5" t="n">
-        <v>24.786106</v>
+        <v>23.560905</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.539331</v>
+        <v>3.3713362</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03179344490363763</v>
+        <v>0.03161647837106405</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04034518597323949</v>
+        <v>0.042443189140427</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04451000213623047</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.00452481391231959</v>
+        <v>-0.002066812995803476</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6591,51 +7113,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>298.01</v>
+        <v>297.01</v>
       </c>
       <c r="F6" t="n">
-        <v>4376979046400</v>
+        <v>4362291642368</v>
       </c>
       <c r="G6" t="n">
-        <v>8.25</v>
+        <v>8.26</v>
       </c>
       <c r="H6" t="n">
-        <v>9.594989999999999</v>
+        <v>9.60059</v>
       </c>
       <c r="I6" t="n">
-        <v>36.122425</v>
+        <v>35.957626</v>
       </c>
       <c r="J6" t="n">
-        <v>31.058918</v>
+        <v>30.936642</v>
       </c>
       <c r="K6" t="n">
         <v>2.41</v>
       </c>
       <c r="L6" t="n">
-        <v>9.695551</v>
+        <v>9.663016000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02768363477735647</v>
+        <v>0.02781051143059156</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03219687258816818</v>
+        <v>0.03232413050065654</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04451000213623047</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0126731272973909</v>
+        <v>-0.01218587163557393</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6649,51 +7171,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210.69</v>
+        <v>208.65</v>
       </c>
       <c r="F7" t="n">
-        <v>5103122644992</v>
+        <v>5053711646720</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
       </c>
       <c r="H7" t="n">
-        <v>12.72715</v>
+        <v>12.72901</v>
       </c>
       <c r="I7" t="n">
-        <v>32.26493</v>
+        <v>31.952524</v>
       </c>
       <c r="J7" t="n">
-        <v>16.554375</v>
+        <v>16.391691</v>
       </c>
       <c r="K7" t="n">
         <v>0.65</v>
       </c>
       <c r="L7" t="n">
-        <v>20.131376</v>
+        <v>19.936453</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0309934026294556</v>
+        <v>0.03129642942727055</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06040699606056291</v>
+        <v>0.0610065180924994</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04451000213623047</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01553699617500383</v>
+        <v>0.01649651595626893</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6707,51 +7229,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>537.37</v>
+        <v>551.63</v>
       </c>
       <c r="F8" t="n">
-        <v>876235849728</v>
+        <v>899488219136</v>
       </c>
       <c r="G8" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="H8" t="n">
-        <v>13.1035</v>
+        <v>13.10372</v>
       </c>
       <c r="I8" t="n">
-        <v>179.72241</v>
+        <v>185.11073</v>
       </c>
       <c r="J8" t="n">
-        <v>41.00965</v>
+        <v>42.097206</v>
       </c>
       <c r="K8" t="n">
         <v>1.29</v>
       </c>
       <c r="L8" t="n">
-        <v>23.394987</v>
+        <v>24.015812</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005564136442302325</v>
+        <v>0.005402171745554085</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02438450229823027</v>
+        <v>0.0237545456193463</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04451000213623047</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02048549758732882</v>
+        <v>-0.02075545651688417</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6765,51 +7287,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>411.35</v>
+        <v>392.13</v>
       </c>
       <c r="F9" t="n">
-        <v>1957030658048</v>
+        <v>1865589981184</v>
       </c>
       <c r="G9" t="n">
-        <v>6.03</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>19.35046</v>
+        <v>19.38501</v>
       </c>
       <c r="I9" t="n">
-        <v>68.21725000000001</v>
+        <v>65.355</v>
       </c>
       <c r="J9" t="n">
-        <v>21.257893</v>
+        <v>20.228518</v>
       </c>
       <c r="K9" t="n">
         <v>0.75</v>
       </c>
       <c r="L9" t="n">
-        <v>25.932959</v>
+        <v>24.721262</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01465904947125319</v>
+        <v>0.01530104812179634</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04704135164701592</v>
+        <v>0.04943516180858389</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04451000213623047</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002171351761456837</v>
+        <v>0.004925159672353421</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6823,10 +7345,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>77.38</v>
+        <v>72.88</v>
       </c>
       <c r="F10" t="n">
-        <v>325831589888</v>
+        <v>306883002368</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -6835,28 +7357,28 @@
         <v>3.84196</v>
       </c>
       <c r="I10" t="n">
-        <v>24.96129</v>
+        <v>23.509678</v>
       </c>
       <c r="J10" t="n">
-        <v>20.14076</v>
+        <v>18.969484</v>
       </c>
       <c r="K10" t="n">
         <v>1.52</v>
       </c>
       <c r="L10" t="n">
-        <v>6.9488516</v>
+        <v>6.544744</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04006203153269579</v>
+        <v>0.04253567508232712</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04965055569914707</v>
+        <v>0.05271624588364435</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04451000213623047</v>
       </c>
       <c r="P10" t="n">
-        <v>0.004780555813587981</v>
+        <v>0.008206243747413876</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P109"/>
+  <dimension ref="A1:P118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6287,16 +6287,16 @@
         <v>9.663016000000001</v>
       </c>
       <c r="M101" t="n">
-        <v>0.02781051143059156</v>
+        <v>0.0278105114305915</v>
       </c>
       <c r="N101" t="n">
-        <v>0.03232413050065654</v>
+        <v>0.0323241305006565</v>
       </c>
       <c r="O101" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P101" t="n">
-        <v>-0.01218587163557393</v>
+        <v>-0.0121858716355739</v>
       </c>
     </row>
     <row r="102">
@@ -6345,16 +6345,16 @@
         <v>24.015812</v>
       </c>
       <c r="M102" t="n">
-        <v>0.005402171745554085</v>
+        <v>0.005402171745554</v>
       </c>
       <c r="N102" t="n">
         <v>0.0237545456193463</v>
       </c>
       <c r="O102" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P102" t="n">
-        <v>-0.02075545651688417</v>
+        <v>-0.0207554565168841</v>
       </c>
     </row>
     <row r="103">
@@ -6403,16 +6403,16 @@
         <v>3.3713362</v>
       </c>
       <c r="M103" t="n">
-        <v>0.03161647837106405</v>
+        <v>0.031616478371064</v>
       </c>
       <c r="N103" t="n">
-        <v>0.042443189140427</v>
+        <v>0.0424431891404269</v>
       </c>
       <c r="O103" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P103" t="n">
-        <v>-0.002066812995803476</v>
+        <v>-0.0020668129958034</v>
       </c>
     </row>
     <row r="104">
@@ -6461,16 +6461,16 @@
         <v>24.721262</v>
       </c>
       <c r="M104" t="n">
-        <v>0.01530104812179634</v>
+        <v>0.0153010481217963</v>
       </c>
       <c r="N104" t="n">
-        <v>0.04943516180858389</v>
+        <v>0.0494351618085838</v>
       </c>
       <c r="O104" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P104" t="n">
-        <v>0.004925159672353421</v>
+        <v>0.0049251596723534</v>
       </c>
     </row>
     <row r="105">
@@ -6519,16 +6519,16 @@
         <v>10.073452</v>
       </c>
       <c r="M105" t="n">
-        <v>0.03758816445897127</v>
+        <v>0.0375881644589712</v>
       </c>
       <c r="N105" t="n">
-        <v>0.04156316302540283</v>
+        <v>0.0415631630254028</v>
       </c>
       <c r="O105" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P105" t="n">
-        <v>-0.002946839110827638</v>
+        <v>-0.0029468391108276</v>
       </c>
     </row>
     <row r="106">
@@ -6577,16 +6577,16 @@
         <v>6.658308</v>
       </c>
       <c r="M106" t="n">
-        <v>0.04880730690786556</v>
+        <v>0.0488073069078655</v>
       </c>
       <c r="N106" t="n">
-        <v>0.06428298306287132</v>
+        <v>0.06428298306287129</v>
       </c>
       <c r="O106" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P106" t="n">
-        <v>0.01977298092664085</v>
+        <v>0.0197729809266408</v>
       </c>
     </row>
     <row r="107">
@@ -6635,16 +6635,16 @@
         <v>8.573650000000001</v>
       </c>
       <c r="M107" t="n">
-        <v>0.04570697446507323</v>
+        <v>0.0457069744650732</v>
       </c>
       <c r="N107" t="n">
-        <v>0.05266483366908042</v>
+        <v>0.0526648336690804</v>
       </c>
       <c r="O107" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P107" t="n">
-        <v>0.008154831532849946</v>
+        <v>0.008154831532849899</v>
       </c>
     </row>
     <row r="108">
@@ -6693,16 +6693,16 @@
         <v>6.544744</v>
       </c>
       <c r="M108" t="n">
-        <v>0.04253567508232712</v>
+        <v>0.0425356750823271</v>
       </c>
       <c r="N108" t="n">
-        <v>0.05271624588364435</v>
+        <v>0.0527162458836443</v>
       </c>
       <c r="O108" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P108" t="n">
-        <v>0.008206243747413876</v>
+        <v>0.008206243747413799</v>
       </c>
     </row>
     <row r="109">
@@ -6751,16 +6751,538 @@
         <v>19.936453</v>
       </c>
       <c r="M109" t="n">
-        <v>0.03129642942727055</v>
+        <v>0.0312964294272705</v>
       </c>
       <c r="N109" t="n">
         <v>0.0610065180924994</v>
       </c>
       <c r="O109" t="n">
+        <v>0.0445100021362304</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0.0164965159562689</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>294.3</v>
+      </c>
+      <c r="F110" t="n">
+        <v>4322488745984</v>
+      </c>
+      <c r="G110" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="H110" t="n">
+        <v>9.60059</v>
+      </c>
+      <c r="I110" t="n">
+        <v>35.586452</v>
+      </c>
+      <c r="J110" t="n">
+        <v>30.654366</v>
+      </c>
+      <c r="K110" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L110" t="n">
+        <v>9.574847999999999</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.02810057764186204</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0.03262178049609242</v>
+      </c>
+      <c r="O110" t="n">
         <v>0.04451000213623047</v>
       </c>
-      <c r="P109" t="n">
-        <v>0.01649651595626893</v>
+      <c r="P110" t="n">
+        <v>-0.01188822164013805</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>519.85</v>
+      </c>
+      <c r="F111" t="n">
+        <v>847667658752</v>
+      </c>
+      <c r="G111" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H111" t="n">
+        <v>13.10372</v>
+      </c>
+      <c r="I111" t="n">
+        <v>172.13576</v>
+      </c>
+      <c r="J111" t="n">
+        <v>39.67194</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L111" t="n">
+        <v>22.632233</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.005809368086948158</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.02520673271135904</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P111" t="n">
+        <v>-0.01930326942487143</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>234.11</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2518346891264</v>
+      </c>
+      <c r="G112" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H112" t="n">
+        <v>9.88054</v>
+      </c>
+      <c r="I112" t="n">
+        <v>31.636486</v>
+      </c>
+      <c r="J112" t="n">
+        <v>23.69405</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L112" t="n">
+        <v>3.3904529</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.03160907265815215</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0.04220469010294306</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P112" t="n">
+        <v>-0.002305312033287411</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>380.15</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1808594108416</v>
+      </c>
+      <c r="G113" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H113" t="n">
+        <v>19.38501</v>
+      </c>
+      <c r="I113" t="n">
+        <v>63.252907</v>
+      </c>
+      <c r="J113" t="n">
+        <v>19.610514</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L113" t="n">
+        <v>23.966</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.0158095488622912</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0.05099305537287913</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0.006483053236648662</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>346.08</v>
+      </c>
+      <c r="F114" t="n">
+        <v>4223066177536</v>
+      </c>
+      <c r="G114" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="H114" t="n">
+        <v>14.55347</v>
+      </c>
+      <c r="I114" t="n">
+        <v>26.378048</v>
+      </c>
+      <c r="J114" t="n">
+        <v>23.779896</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L114" t="n">
+        <v>9.995469999999999</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.03791030975496995</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0.04205232894128526</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P114" t="n">
+        <v>-0.002457673194945213</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>562.2</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1427101581312</v>
+      </c>
+      <c r="G115" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="H115" t="n">
+        <v>36.24596</v>
+      </c>
+      <c r="I115" t="n">
+        <v>20.451075</v>
+      </c>
+      <c r="J115" t="n">
+        <v>15.5106945</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L115" t="n">
+        <v>6.6388245</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.04889718961223763</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0.06447164710067591</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0.01996164496444543</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>373.94</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2777788973056</v>
+      </c>
+      <c r="G116" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="H116" t="n">
+        <v>19.3459</v>
+      </c>
+      <c r="I116" t="n">
+        <v>22.27159</v>
+      </c>
+      <c r="J116" t="n">
+        <v>19.32916</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L116" t="n">
+        <v>8.727693</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.04490025137722629</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0.0517353051291651</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0.007225302992934633</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>72.81999999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>306630361088</v>
+      </c>
+      <c r="G117" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>3.84196</v>
+      </c>
+      <c r="I117" t="n">
+        <v>23.490324</v>
+      </c>
+      <c r="J117" t="n">
+        <v>18.953867</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L117" t="n">
+        <v>6.539356</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.04257072232903049</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.05275968140620709</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.00824967926997662</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>200.04</v>
+      </c>
+      <c r="F118" t="n">
+        <v>4845168754688</v>
+      </c>
+      <c r="G118" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="H118" t="n">
+        <v>12.72901</v>
+      </c>
+      <c r="I118" t="n">
+        <v>30.68098</v>
+      </c>
+      <c r="J118" t="n">
+        <v>15.715283</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L118" t="n">
+        <v>19.11377</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.03259348130373925</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.06363232353529295</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.01912232139906248</v>
       </c>
     </row>
   </sheetData>
@@ -6862,12 +7384,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6881,51 +7403,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>348.78</v>
+        <v>346.08</v>
       </c>
       <c r="F2" t="n">
-        <v>4256013221888</v>
+        <v>4223066177536</v>
       </c>
       <c r="G2" t="n">
-        <v>13.11</v>
+        <v>13.12</v>
       </c>
       <c r="H2" t="n">
-        <v>14.4964</v>
+        <v>14.55347</v>
       </c>
       <c r="I2" t="n">
-        <v>26.60412</v>
+        <v>26.378048</v>
       </c>
       <c r="J2" t="n">
-        <v>24.059767</v>
+        <v>23.779896</v>
       </c>
       <c r="K2" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="L2" t="n">
-        <v>10.073452</v>
+        <v>9.995469999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03758816445897127</v>
+        <v>0.03791030975496995</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04156316302540283</v>
+        <v>0.04205232894128526</v>
       </c>
       <c r="O2" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.002946839110827638</v>
+        <v>-0.002457673194945213</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6939,10 +7461,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>367.34</v>
+        <v>373.94</v>
       </c>
       <c r="F3" t="n">
-        <v>2728761229312</v>
+        <v>2777788973056</v>
       </c>
       <c r="G3" t="n">
         <v>16.79</v>
@@ -6951,39 +7473,39 @@
         <v>19.3459</v>
       </c>
       <c r="I3" t="n">
-        <v>21.878498</v>
+        <v>22.27159</v>
       </c>
       <c r="J3" t="n">
-        <v>18.988003</v>
+        <v>19.32916</v>
       </c>
       <c r="K3" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="L3" t="n">
-        <v>8.573650000000001</v>
+        <v>8.727693</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04570697446507323</v>
+        <v>0.04490025137722629</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05266483366908042</v>
+        <v>0.0517353051291651</v>
       </c>
       <c r="O3" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008154831532849946</v>
+        <v>0.007225302992934633</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6997,51 +7519,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>563.85</v>
+        <v>562.2</v>
       </c>
       <c r="F4" t="n">
-        <v>1431289856000</v>
+        <v>1427101581312</v>
       </c>
       <c r="G4" t="n">
-        <v>27.52</v>
+        <v>27.49</v>
       </c>
       <c r="H4" t="n">
         <v>36.24596</v>
       </c>
       <c r="I4" t="n">
-        <v>20.488733</v>
+        <v>20.451075</v>
       </c>
       <c r="J4" t="n">
-        <v>15.556215</v>
+        <v>15.5106945</v>
       </c>
       <c r="K4" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>6.658308</v>
+        <v>6.6388245</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04880730690786556</v>
+        <v>0.04889718961223763</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06428298306287132</v>
+        <v>0.06447164710067591</v>
       </c>
       <c r="O4" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01977298092664085</v>
+        <v>0.01996164496444543</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7055,51 +7577,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>232.79</v>
+        <v>234.11</v>
       </c>
       <c r="F5" t="n">
-        <v>2504147599360</v>
+        <v>2518346891264</v>
       </c>
       <c r="G5" t="n">
-        <v>7.36</v>
+        <v>7.4</v>
       </c>
       <c r="H5" t="n">
-        <v>9.88035</v>
+        <v>9.88054</v>
       </c>
       <c r="I5" t="n">
-        <v>31.629074</v>
+        <v>31.636486</v>
       </c>
       <c r="J5" t="n">
-        <v>23.560905</v>
+        <v>23.69405</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.3713362</v>
+        <v>3.3904529</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03161647837106405</v>
+        <v>0.03160907265815215</v>
       </c>
       <c r="N5" t="n">
-        <v>0.042443189140427</v>
+        <v>0.04220469010294306</v>
       </c>
       <c r="O5" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.002066812995803476</v>
+        <v>-0.002305312033287411</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7113,51 +7635,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>297.01</v>
+        <v>294.3</v>
       </c>
       <c r="F6" t="n">
-        <v>4362291642368</v>
+        <v>4322488745984</v>
       </c>
       <c r="G6" t="n">
-        <v>8.26</v>
+        <v>8.27</v>
       </c>
       <c r="H6" t="n">
         <v>9.60059</v>
       </c>
       <c r="I6" t="n">
-        <v>35.957626</v>
+        <v>35.586452</v>
       </c>
       <c r="J6" t="n">
-        <v>30.936642</v>
+        <v>30.654366</v>
       </c>
       <c r="K6" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="L6" t="n">
-        <v>9.663016000000001</v>
+        <v>9.574847999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02781051143059156</v>
+        <v>0.02810057764186204</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03232413050065654</v>
+        <v>0.03262178049609242</v>
       </c>
       <c r="O6" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01218587163557393</v>
+        <v>-0.01188822164013805</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7171,51 +7693,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208.65</v>
+        <v>200.04</v>
       </c>
       <c r="F7" t="n">
-        <v>5053711646720</v>
+        <v>4845168754688</v>
       </c>
       <c r="G7" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
       <c r="H7" t="n">
         <v>12.72901</v>
       </c>
       <c r="I7" t="n">
-        <v>31.952524</v>
+        <v>30.68098</v>
       </c>
       <c r="J7" t="n">
-        <v>16.391691</v>
+        <v>15.715283</v>
       </c>
       <c r="K7" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>19.936453</v>
+        <v>19.11377</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03129642942727055</v>
+        <v>0.03259348130373925</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0610065180924994</v>
+        <v>0.06363232353529295</v>
       </c>
       <c r="O7" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01649651595626893</v>
+        <v>0.01912232139906248</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7229,51 +7751,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>551.63</v>
+        <v>519.85</v>
       </c>
       <c r="F8" t="n">
-        <v>899488219136</v>
+        <v>847667658752</v>
       </c>
       <c r="G8" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="H8" t="n">
         <v>13.10372</v>
       </c>
       <c r="I8" t="n">
-        <v>185.11073</v>
+        <v>172.13576</v>
       </c>
       <c r="J8" t="n">
-        <v>42.097206</v>
+        <v>39.67194</v>
       </c>
       <c r="K8" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="L8" t="n">
-        <v>24.015812</v>
+        <v>22.632233</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005402171745554085</v>
+        <v>0.005809368086948158</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0237545456193463</v>
+        <v>0.02520673271135904</v>
       </c>
       <c r="O8" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02075545651688417</v>
+        <v>-0.01930326942487143</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7287,51 +7809,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392.13</v>
+        <v>380.15</v>
       </c>
       <c r="F9" t="n">
-        <v>1865589981184</v>
+        <v>1808594108416</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>6.01</v>
       </c>
       <c r="H9" t="n">
         <v>19.38501</v>
       </c>
       <c r="I9" t="n">
-        <v>65.355</v>
+        <v>63.252907</v>
       </c>
       <c r="J9" t="n">
-        <v>20.228518</v>
+        <v>19.610514</v>
       </c>
       <c r="K9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="L9" t="n">
-        <v>24.721262</v>
+        <v>23.966</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01530104812179634</v>
+        <v>0.0158095488622912</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04943516180858389</v>
+        <v>0.05099305537287913</v>
       </c>
       <c r="O9" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004925159672353421</v>
+        <v>0.006483053236648662</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7345,10 +7867,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>72.88</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>306883002368</v>
+        <v>306630361088</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -7357,28 +7879,28 @@
         <v>3.84196</v>
       </c>
       <c r="I10" t="n">
-        <v>23.509678</v>
+        <v>23.490324</v>
       </c>
       <c r="J10" t="n">
-        <v>18.969484</v>
+        <v>18.953867</v>
       </c>
       <c r="K10" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="L10" t="n">
-        <v>6.544744</v>
+        <v>6.539356</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04253567508232712</v>
+        <v>0.04257072232903049</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05271624588364435</v>
+        <v>0.05275968140620709</v>
       </c>
       <c r="O10" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P10" t="n">
-        <v>0.008206243747413876</v>
+        <v>0.00824967926997662</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P118"/>
+  <dimension ref="A1:P127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6809,16 +6809,16 @@
         <v>9.574847999999999</v>
       </c>
       <c r="M110" t="n">
-        <v>0.02810057764186204</v>
+        <v>0.028100577641862</v>
       </c>
       <c r="N110" t="n">
-        <v>0.03262178049609242</v>
+        <v>0.0326217804960924</v>
       </c>
       <c r="O110" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P110" t="n">
-        <v>-0.01188822164013805</v>
+        <v>-0.011888221640138</v>
       </c>
     </row>
     <row r="111">
@@ -6867,16 +6867,16 @@
         <v>22.632233</v>
       </c>
       <c r="M111" t="n">
-        <v>0.005809368086948158</v>
+        <v>0.0058093680869481</v>
       </c>
       <c r="N111" t="n">
-        <v>0.02520673271135904</v>
+        <v>0.025206732711359</v>
       </c>
       <c r="O111" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P111" t="n">
-        <v>-0.01930326942487143</v>
+        <v>-0.0193032694248714</v>
       </c>
     </row>
     <row r="112">
@@ -6925,16 +6925,16 @@
         <v>3.3904529</v>
       </c>
       <c r="M112" t="n">
-        <v>0.03160907265815215</v>
+        <v>0.0316090726581521</v>
       </c>
       <c r="N112" t="n">
-        <v>0.04220469010294306</v>
+        <v>0.042204690102943</v>
       </c>
       <c r="O112" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P112" t="n">
-        <v>-0.002305312033287411</v>
+        <v>-0.0023053120332874</v>
       </c>
     </row>
     <row r="113">
@@ -6986,13 +6986,13 @@
         <v>0.0158095488622912</v>
       </c>
       <c r="N113" t="n">
-        <v>0.05099305537287913</v>
+        <v>0.0509930553728791</v>
       </c>
       <c r="O113" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P113" t="n">
-        <v>0.006483053236648662</v>
+        <v>0.0064830532366486</v>
       </c>
     </row>
     <row r="114">
@@ -7041,16 +7041,16 @@
         <v>9.995469999999999</v>
       </c>
       <c r="M114" t="n">
-        <v>0.03791030975496995</v>
+        <v>0.0379103097549699</v>
       </c>
       <c r="N114" t="n">
-        <v>0.04205232894128526</v>
+        <v>0.0420523289412852</v>
       </c>
       <c r="O114" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P114" t="n">
-        <v>-0.002457673194945213</v>
+        <v>-0.0024576731949452</v>
       </c>
     </row>
     <row r="115">
@@ -7099,16 +7099,16 @@
         <v>6.6388245</v>
       </c>
       <c r="M115" t="n">
-        <v>0.04889718961223763</v>
+        <v>0.0488971896122376</v>
       </c>
       <c r="N115" t="n">
         <v>0.06447164710067591</v>
       </c>
       <c r="O115" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P115" t="n">
-        <v>0.01996164496444543</v>
+        <v>0.0199616449644454</v>
       </c>
     </row>
     <row r="116">
@@ -7157,16 +7157,16 @@
         <v>8.727693</v>
       </c>
       <c r="M116" t="n">
-        <v>0.04490025137722629</v>
+        <v>0.0449002513772262</v>
       </c>
       <c r="N116" t="n">
         <v>0.0517353051291651</v>
       </c>
       <c r="O116" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P116" t="n">
-        <v>0.007225302992934633</v>
+        <v>0.0072253029929346</v>
       </c>
     </row>
     <row r="117">
@@ -7215,16 +7215,16 @@
         <v>6.539356</v>
       </c>
       <c r="M117" t="n">
-        <v>0.04257072232903049</v>
+        <v>0.0425707223290304</v>
       </c>
       <c r="N117" t="n">
-        <v>0.05275968140620709</v>
+        <v>0.052759681406207</v>
       </c>
       <c r="O117" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P117" t="n">
-        <v>0.00824967926997662</v>
+        <v>0.008249679269976599</v>
       </c>
     </row>
     <row r="118">
@@ -7273,16 +7273,538 @@
         <v>19.11377</v>
       </c>
       <c r="M118" t="n">
-        <v>0.03259348130373925</v>
+        <v>0.0325934813037392</v>
       </c>
       <c r="N118" t="n">
-        <v>0.06363232353529295</v>
+        <v>0.0636323235352929</v>
       </c>
       <c r="O118" t="n">
+        <v>0.0445100021362304</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.0191223213990624</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>293.08</v>
+      </c>
+      <c r="F119" t="n">
+        <v>4304570155008</v>
+      </c>
+      <c r="G119" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H119" t="n">
+        <v>9.610110000000001</v>
+      </c>
+      <c r="I119" t="n">
+        <v>35.48184</v>
+      </c>
+      <c r="J119" t="n">
+        <v>30.497047</v>
+      </c>
+      <c r="K119" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L119" t="n">
+        <v>9.535156000000001</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.02818343114507984</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.03279005732223284</v>
+      </c>
+      <c r="O119" t="n">
         <v>0.04451000213623047</v>
       </c>
-      <c r="P118" t="n">
-        <v>0.01912232139906248</v>
+      <c r="P119" t="n">
+        <v>-0.01171994481399763</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>519.74</v>
+      </c>
+      <c r="F120" t="n">
+        <v>847488352256</v>
+      </c>
+      <c r="G120" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="H120" t="n">
+        <v>13.16815</v>
+      </c>
+      <c r="I120" t="n">
+        <v>172.6711</v>
+      </c>
+      <c r="J120" t="n">
+        <v>39.46948</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L120" t="n">
+        <v>22.627445</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.005791357217070073</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.02533603340131604</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P120" t="n">
+        <v>-0.01917396873491443</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>234.27</v>
+      </c>
+      <c r="F121" t="n">
+        <v>2520068128768</v>
+      </c>
+      <c r="G121" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H121" t="n">
+        <v>9.88054</v>
+      </c>
+      <c r="I121" t="n">
+        <v>31.658108</v>
+      </c>
+      <c r="J121" t="n">
+        <v>23.710243</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L121" t="n">
+        <v>3.39277</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.03158748452640116</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.04217586545439023</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P121" t="n">
+        <v>-0.002334136681840238</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>382.07</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1817728778240</v>
+      </c>
+      <c r="G122" t="n">
+        <v>6</v>
+      </c>
+      <c r="H122" t="n">
+        <v>19.39578</v>
+      </c>
+      <c r="I122" t="n">
+        <v>63.678333</v>
+      </c>
+      <c r="J122" t="n">
+        <v>19.698614</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L122" t="n">
+        <v>24.087044</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.0157039285994713</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.05076499070850891</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.006254988572278436</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>345.04</v>
+      </c>
+      <c r="F123" t="n">
+        <v>4210375786496</v>
+      </c>
+      <c r="G123" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="H123" t="n">
+        <v>14.55347</v>
+      </c>
+      <c r="I123" t="n">
+        <v>26.318842</v>
+      </c>
+      <c r="J123" t="n">
+        <v>23.708437</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L123" t="n">
+        <v>9.965433000000001</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.03799559471365638</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.04217908068629724</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P123" t="n">
+        <v>-0.002330921449933229</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>557.67</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1415602503680</v>
+      </c>
+      <c r="G124" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="H124" t="n">
+        <v>36.24596</v>
+      </c>
+      <c r="I124" t="n">
+        <v>20.286285</v>
+      </c>
+      <c r="J124" t="n">
+        <v>15.385715</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L124" t="n">
+        <v>6.585331</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.04929438556852619</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.06499535567629601</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.02048535354006554</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>365.46</v>
+      </c>
+      <c r="F125" t="n">
+        <v>2714795769856</v>
+      </c>
+      <c r="G125" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="H125" t="n">
+        <v>19.3459</v>
+      </c>
+      <c r="I125" t="n">
+        <v>21.792486</v>
+      </c>
+      <c r="J125" t="n">
+        <v>18.890825</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L125" t="n">
+        <v>8.529771</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.04588737481530127</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.05293575220270345</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.008425750066472976</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>71.84</v>
+      </c>
+      <c r="F126" t="n">
+        <v>302503755776</v>
+      </c>
+      <c r="G126" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H126" t="n">
+        <v>3.84196</v>
+      </c>
+      <c r="I126" t="n">
+        <v>23.174192</v>
+      </c>
+      <c r="J126" t="n">
+        <v>18.698788</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L126" t="n">
+        <v>6.45135</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.04315144766146993</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.0534793986636971</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.00896939652746663</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>199</v>
+      </c>
+      <c r="F127" t="n">
+        <v>4819978813440</v>
+      </c>
+      <c r="G127" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H127" t="n">
+        <v>12.72901</v>
+      </c>
+      <c r="I127" t="n">
+        <v>30.474731</v>
+      </c>
+      <c r="J127" t="n">
+        <v>15.633581</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L127" t="n">
+        <v>19.014399</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.0328140703517588</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.0639648743718593</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.01945487223562883</v>
       </c>
     </row>
   </sheetData>
@@ -7384,12 +7906,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -7403,51 +7925,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>346.08</v>
+        <v>345.04</v>
       </c>
       <c r="F2" t="n">
-        <v>4223066177536</v>
+        <v>4210375786496</v>
       </c>
       <c r="G2" t="n">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="H2" t="n">
         <v>14.55347</v>
       </c>
       <c r="I2" t="n">
-        <v>26.378048</v>
+        <v>26.318842</v>
       </c>
       <c r="J2" t="n">
-        <v>23.779896</v>
+        <v>23.708437</v>
       </c>
       <c r="K2" t="n">
         <v>1.37</v>
       </c>
       <c r="L2" t="n">
-        <v>9.995469999999999</v>
+        <v>9.965433000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03791030975496995</v>
+        <v>0.03799559471365638</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04205232894128526</v>
+        <v>0.04217908068629724</v>
       </c>
       <c r="O2" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.002457673194945213</v>
+        <v>-0.002330921449933229</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7461,51 +7983,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>373.94</v>
+        <v>365.46</v>
       </c>
       <c r="F3" t="n">
-        <v>2777788973056</v>
+        <v>2714795769856</v>
       </c>
       <c r="G3" t="n">
-        <v>16.79</v>
+        <v>16.77</v>
       </c>
       <c r="H3" t="n">
         <v>19.3459</v>
       </c>
       <c r="I3" t="n">
-        <v>22.27159</v>
+        <v>21.792486</v>
       </c>
       <c r="J3" t="n">
-        <v>19.32916</v>
+        <v>18.890825</v>
       </c>
       <c r="K3" t="n">
         <v>1.13</v>
       </c>
       <c r="L3" t="n">
-        <v>8.727693</v>
+        <v>8.529771</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04490025137722629</v>
+        <v>0.04588737481530127</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0517353051291651</v>
+        <v>0.05293575220270345</v>
       </c>
       <c r="O3" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007225302992934633</v>
+        <v>0.008425750066472976</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7519,10 +8041,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>562.2</v>
+        <v>557.67</v>
       </c>
       <c r="F4" t="n">
-        <v>1427101581312</v>
+        <v>1415602503680</v>
       </c>
       <c r="G4" t="n">
         <v>27.49</v>
@@ -7531,39 +8053,39 @@
         <v>36.24596</v>
       </c>
       <c r="I4" t="n">
-        <v>20.451075</v>
+        <v>20.286285</v>
       </c>
       <c r="J4" t="n">
-        <v>15.5106945</v>
+        <v>15.385715</v>
       </c>
       <c r="K4" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>6.6388245</v>
+        <v>6.585331</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04889718961223763</v>
+        <v>0.04929438556852619</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06447164710067591</v>
+        <v>0.06499535567629601</v>
       </c>
       <c r="O4" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01996164496444543</v>
+        <v>0.02048535354006554</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7577,10 +8099,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>234.11</v>
+        <v>234.27</v>
       </c>
       <c r="F5" t="n">
-        <v>2518346891264</v>
+        <v>2520068128768</v>
       </c>
       <c r="G5" t="n">
         <v>7.4</v>
@@ -7589,39 +8111,39 @@
         <v>9.88054</v>
       </c>
       <c r="I5" t="n">
-        <v>31.636486</v>
+        <v>31.658108</v>
       </c>
       <c r="J5" t="n">
-        <v>23.69405</v>
+        <v>23.710243</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.3904529</v>
+        <v>3.39277</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03160907265815215</v>
+        <v>0.03158748452640116</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04220469010294306</v>
+        <v>0.04217586545439023</v>
       </c>
       <c r="O5" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.002305312033287411</v>
+        <v>-0.002334136681840238</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7635,51 +8157,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>294.3</v>
+        <v>293.08</v>
       </c>
       <c r="F6" t="n">
-        <v>4322488745984</v>
+        <v>4304570155008</v>
       </c>
       <c r="G6" t="n">
-        <v>8.27</v>
+        <v>8.26</v>
       </c>
       <c r="H6" t="n">
-        <v>9.60059</v>
+        <v>9.610110000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>35.586452</v>
+        <v>35.48184</v>
       </c>
       <c r="J6" t="n">
-        <v>30.654366</v>
+        <v>30.497047</v>
       </c>
       <c r="K6" t="n">
         <v>2.4</v>
       </c>
       <c r="L6" t="n">
-        <v>9.574847999999999</v>
+        <v>9.535156000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02810057764186204</v>
+        <v>0.02818343114507984</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03262178049609242</v>
+        <v>0.03279005732223284</v>
       </c>
       <c r="O6" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01188822164013805</v>
+        <v>-0.01171994481399763</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7693,51 +8215,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>200.04</v>
+        <v>199</v>
       </c>
       <c r="F7" t="n">
-        <v>4845168754688</v>
+        <v>4819978813440</v>
       </c>
       <c r="G7" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="H7" t="n">
         <v>12.72901</v>
       </c>
       <c r="I7" t="n">
-        <v>30.68098</v>
+        <v>30.474731</v>
       </c>
       <c r="J7" t="n">
-        <v>15.715283</v>
+        <v>15.633581</v>
       </c>
       <c r="K7" t="n">
         <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>19.11377</v>
+        <v>19.014399</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03259348130373925</v>
+        <v>0.0328140703517588</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06363232353529295</v>
+        <v>0.0639648743718593</v>
       </c>
       <c r="O7" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01912232139906248</v>
+        <v>0.01945487223562883</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7751,51 +8273,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>519.85</v>
+        <v>519.74</v>
       </c>
       <c r="F8" t="n">
-        <v>847667658752</v>
+        <v>847488352256</v>
       </c>
       <c r="G8" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="H8" t="n">
-        <v>13.10372</v>
+        <v>13.16815</v>
       </c>
       <c r="I8" t="n">
-        <v>172.13576</v>
+        <v>172.6711</v>
       </c>
       <c r="J8" t="n">
-        <v>39.67194</v>
+        <v>39.46948</v>
       </c>
       <c r="K8" t="n">
         <v>1.33</v>
       </c>
       <c r="L8" t="n">
-        <v>22.632233</v>
+        <v>22.627445</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005809368086948158</v>
+        <v>0.005791357217070073</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02520673271135904</v>
+        <v>0.02533603340131604</v>
       </c>
       <c r="O8" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01930326942487143</v>
+        <v>-0.01917396873491443</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7809,51 +8331,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>380.15</v>
+        <v>382.07</v>
       </c>
       <c r="F9" t="n">
-        <v>1808594108416</v>
+        <v>1817728778240</v>
       </c>
       <c r="G9" t="n">
-        <v>6.01</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>19.38501</v>
+        <v>19.39578</v>
       </c>
       <c r="I9" t="n">
-        <v>63.252907</v>
+        <v>63.678333</v>
       </c>
       <c r="J9" t="n">
-        <v>19.610514</v>
+        <v>19.698614</v>
       </c>
       <c r="K9" t="n">
         <v>0.71</v>
       </c>
       <c r="L9" t="n">
-        <v>23.966</v>
+        <v>24.087044</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0158095488622912</v>
+        <v>0.0157039285994713</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05099305537287913</v>
+        <v>0.05076499070850891</v>
       </c>
       <c r="O9" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006483053236648662</v>
+        <v>0.006254988572278436</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7867,10 +8389,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>72.81999999999999</v>
+        <v>71.84</v>
       </c>
       <c r="F10" t="n">
-        <v>306630361088</v>
+        <v>302503755776</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -7879,28 +8401,28 @@
         <v>3.84196</v>
       </c>
       <c r="I10" t="n">
-        <v>23.490324</v>
+        <v>23.174192</v>
       </c>
       <c r="J10" t="n">
-        <v>18.953867</v>
+        <v>18.698788</v>
       </c>
       <c r="K10" t="n">
         <v>1.43</v>
       </c>
       <c r="L10" t="n">
-        <v>6.539356</v>
+        <v>6.45135</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04257072232903049</v>
+        <v>0.04315144766146993</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05275968140620709</v>
+        <v>0.0534793986636971</v>
       </c>
       <c r="O10" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P10" t="n">
-        <v>0.00824967926997662</v>
+        <v>0.00896939652746663</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P127"/>
+  <dimension ref="A1:P136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7331,16 +7331,16 @@
         <v>9.535156000000001</v>
       </c>
       <c r="M119" t="n">
-        <v>0.02818343114507984</v>
+        <v>0.0281834311450798</v>
       </c>
       <c r="N119" t="n">
-        <v>0.03279005732223284</v>
+        <v>0.0327900573222328</v>
       </c>
       <c r="O119" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P119" t="n">
-        <v>-0.01171994481399763</v>
+        <v>-0.0117199448139976</v>
       </c>
     </row>
     <row r="120">
@@ -7389,16 +7389,16 @@
         <v>22.627445</v>
       </c>
       <c r="M120" t="n">
-        <v>0.005791357217070073</v>
+        <v>0.00579135721707</v>
       </c>
       <c r="N120" t="n">
-        <v>0.02533603340131604</v>
+        <v>0.025336033401316</v>
       </c>
       <c r="O120" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P120" t="n">
-        <v>-0.01917396873491443</v>
+        <v>-0.0191739687349144</v>
       </c>
     </row>
     <row r="121">
@@ -7447,16 +7447,16 @@
         <v>3.39277</v>
       </c>
       <c r="M121" t="n">
-        <v>0.03158748452640116</v>
+        <v>0.0315874845264011</v>
       </c>
       <c r="N121" t="n">
-        <v>0.04217586545439023</v>
+        <v>0.0421758654543902</v>
       </c>
       <c r="O121" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P121" t="n">
-        <v>-0.002334136681840238</v>
+        <v>-0.0023341366818402</v>
       </c>
     </row>
     <row r="122">
@@ -7508,13 +7508,13 @@
         <v>0.0157039285994713</v>
       </c>
       <c r="N122" t="n">
-        <v>0.05076499070850891</v>
+        <v>0.0507649907085089</v>
       </c>
       <c r="O122" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P122" t="n">
-        <v>0.006254988572278436</v>
+        <v>0.0062549885722784</v>
       </c>
     </row>
     <row r="123">
@@ -7563,16 +7563,16 @@
         <v>9.965433000000001</v>
       </c>
       <c r="M123" t="n">
-        <v>0.03799559471365638</v>
+        <v>0.0379955947136563</v>
       </c>
       <c r="N123" t="n">
-        <v>0.04217908068629724</v>
+        <v>0.0421790806862972</v>
       </c>
       <c r="O123" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P123" t="n">
-        <v>-0.002330921449933229</v>
+        <v>-0.0023309214499332</v>
       </c>
     </row>
     <row r="124">
@@ -7621,16 +7621,16 @@
         <v>6.585331</v>
       </c>
       <c r="M124" t="n">
-        <v>0.04929438556852619</v>
+        <v>0.0492943855685261</v>
       </c>
       <c r="N124" t="n">
-        <v>0.06499535567629601</v>
+        <v>0.064995355676296</v>
       </c>
       <c r="O124" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P124" t="n">
-        <v>0.02048535354006554</v>
+        <v>0.0204853535400655</v>
       </c>
     </row>
     <row r="125">
@@ -7679,16 +7679,16 @@
         <v>8.529771</v>
       </c>
       <c r="M125" t="n">
-        <v>0.04588737481530127</v>
+        <v>0.0458873748153012</v>
       </c>
       <c r="N125" t="n">
-        <v>0.05293575220270345</v>
+        <v>0.0529357522027034</v>
       </c>
       <c r="O125" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P125" t="n">
-        <v>0.008425750066472976</v>
+        <v>0.008425750066472899</v>
       </c>
     </row>
     <row r="126">
@@ -7737,16 +7737,16 @@
         <v>6.45135</v>
       </c>
       <c r="M126" t="n">
-        <v>0.04315144766146993</v>
+        <v>0.0431514476614699</v>
       </c>
       <c r="N126" t="n">
         <v>0.0534793986636971</v>
       </c>
       <c r="O126" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P126" t="n">
-        <v>0.00896939652746663</v>
+        <v>0.008969396527466599</v>
       </c>
     </row>
     <row r="127">
@@ -7795,16 +7795,538 @@
         <v>19.014399</v>
       </c>
       <c r="M127" t="n">
-        <v>0.0328140703517588</v>
+        <v>0.0328140703517587</v>
       </c>
       <c r="N127" t="n">
         <v>0.0639648743718593</v>
       </c>
       <c r="O127" t="n">
+        <v>0.0445100021362304</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.0194548722356288</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>275.15</v>
+      </c>
+      <c r="F128" t="n">
+        <v>4041225797632</v>
+      </c>
+      <c r="G128" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H128" t="n">
+        <v>9.608919999999999</v>
+      </c>
+      <c r="I128" t="n">
+        <v>33.351513</v>
+      </c>
+      <c r="J128" t="n">
+        <v>28.634851</v>
+      </c>
+      <c r="K128" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="L128" t="n">
+        <v>8.951816000000001</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.02998364528439033</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.03492247864801018</v>
+      </c>
+      <c r="O128" t="n">
         <v>0.04451000213623047</v>
       </c>
-      <c r="P127" t="n">
-        <v>0.01945487223562883</v>
+      <c r="P128" t="n">
+        <v>-0.009587523488220291</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>532.5700000000001</v>
+      </c>
+      <c r="F129" t="n">
+        <v>868408950784</v>
+      </c>
+      <c r="G129" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H129" t="n">
+        <v>13.16815</v>
+      </c>
+      <c r="I129" t="n">
+        <v>178.71477</v>
+      </c>
+      <c r="J129" t="n">
+        <v>40.443798</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L129" t="n">
+        <v>23.186014</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.005595508571643164</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.02472566986499427</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P129" t="n">
+        <v>-0.0197843322712362</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>227.01</v>
+      </c>
+      <c r="F130" t="n">
+        <v>2441971499008</v>
+      </c>
+      <c r="G130" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="H130" t="n">
+        <v>9.88054</v>
+      </c>
+      <c r="I130" t="n">
+        <v>31.661087</v>
+      </c>
+      <c r="J130" t="n">
+        <v>22.975464</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L130" t="n">
+        <v>3.2876284</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.03158451169552002</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.04352469054226686</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P130" t="n">
+        <v>-0.0009853115939636101</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>378.91</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1802694819840</v>
+      </c>
+      <c r="G131" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H131" t="n">
+        <v>19.39578</v>
+      </c>
+      <c r="I131" t="n">
+        <v>62.94186</v>
+      </c>
+      <c r="J131" t="n">
+        <v>19.535692</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L131" t="n">
+        <v>23.887827</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.01588767781267319</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.05118835607400173</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.006678353937771261</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>342.19</v>
+      </c>
+      <c r="F132" t="n">
+        <v>4175598452736</v>
+      </c>
+      <c r="G132" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="H132" t="n">
+        <v>14.55347</v>
+      </c>
+      <c r="I132" t="n">
+        <v>26.10145</v>
+      </c>
+      <c r="J132" t="n">
+        <v>23.512606</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L132" t="n">
+        <v>9.88312</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.03831204886174348</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.04253037786025308</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P132" t="n">
+        <v>-0.001979624275977393</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>542.87</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1378033860608</v>
+      </c>
+      <c r="G133" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="H133" t="n">
+        <v>36.24596</v>
+      </c>
+      <c r="I133" t="n">
+        <v>19.72638</v>
+      </c>
+      <c r="J133" t="n">
+        <v>14.977393</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L133" t="n">
+        <v>6.410563</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.05069353620572144</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.06676729235360214</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.02225729021737167</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>352.83</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2620974694400</v>
+      </c>
+      <c r="G134" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="H134" t="n">
+        <v>19.36884</v>
+      </c>
+      <c r="I134" t="n">
+        <v>21.014292</v>
+      </c>
+      <c r="J134" t="n">
+        <v>18.216372</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L134" t="n">
+        <v>8.234989000000001</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.04758665646345266</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.05489567213672307</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.0103856700004926</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="F135" t="n">
+        <v>298545610752</v>
+      </c>
+      <c r="G135" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H135" t="n">
+        <v>3.84196</v>
+      </c>
+      <c r="I135" t="n">
+        <v>22.87097</v>
+      </c>
+      <c r="J135" t="n">
+        <v>18.454123</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L135" t="n">
+        <v>6.3669367</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.04372355430183356</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.05418843441466854</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.009678432278438072</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>195.74</v>
+      </c>
+      <c r="F136" t="n">
+        <v>4741018419200</v>
+      </c>
+      <c r="G136" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="H136" t="n">
+        <v>12.72901</v>
+      </c>
+      <c r="I136" t="n">
+        <v>29.929665</v>
+      </c>
+      <c r="J136" t="n">
+        <v>15.377473</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L136" t="n">
+        <v>18.702906</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.03341166853989987</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.06503019311331358</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.02052019097708311</v>
       </c>
     </row>
   </sheetData>
@@ -7906,12 +8428,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -7925,10 +8447,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>345.04</v>
+        <v>342.19</v>
       </c>
       <c r="F2" t="n">
-        <v>4210375786496</v>
+        <v>4175598452736</v>
       </c>
       <c r="G2" t="n">
         <v>13.11</v>
@@ -7937,39 +8459,39 @@
         <v>14.55347</v>
       </c>
       <c r="I2" t="n">
-        <v>26.318842</v>
+        <v>26.10145</v>
       </c>
       <c r="J2" t="n">
-        <v>23.708437</v>
+        <v>23.512606</v>
       </c>
       <c r="K2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="L2" t="n">
-        <v>9.965433000000001</v>
+        <v>9.88312</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03799559471365638</v>
+        <v>0.03831204886174348</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04217908068629724</v>
+        <v>0.04253037786025308</v>
       </c>
       <c r="O2" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.002330921449933229</v>
+        <v>-0.001979624275977393</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7983,51 +8505,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>365.46</v>
+        <v>352.83</v>
       </c>
       <c r="F3" t="n">
-        <v>2714795769856</v>
+        <v>2620974694400</v>
       </c>
       <c r="G3" t="n">
-        <v>16.77</v>
+        <v>16.79</v>
       </c>
       <c r="H3" t="n">
-        <v>19.3459</v>
+        <v>19.36884</v>
       </c>
       <c r="I3" t="n">
-        <v>21.792486</v>
+        <v>21.014292</v>
       </c>
       <c r="J3" t="n">
-        <v>18.890825</v>
+        <v>18.216372</v>
       </c>
       <c r="K3" t="n">
         <v>1.13</v>
       </c>
       <c r="L3" t="n">
-        <v>8.529771</v>
+        <v>8.234989000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04588737481530127</v>
+        <v>0.04758665646345266</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05293575220270345</v>
+        <v>0.05489567213672307</v>
       </c>
       <c r="O3" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008425750066472976</v>
+        <v>0.0103856700004926</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8041,51 +8563,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>557.67</v>
+        <v>542.87</v>
       </c>
       <c r="F4" t="n">
-        <v>1415602503680</v>
+        <v>1378033860608</v>
       </c>
       <c r="G4" t="n">
-        <v>27.49</v>
+        <v>27.52</v>
       </c>
       <c r="H4" t="n">
         <v>36.24596</v>
       </c>
       <c r="I4" t="n">
-        <v>20.286285</v>
+        <v>19.72638</v>
       </c>
       <c r="J4" t="n">
-        <v>15.385715</v>
+        <v>14.977393</v>
       </c>
       <c r="K4" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>6.585331</v>
+        <v>6.410563</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04929438556852619</v>
+        <v>0.05069353620572144</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06499535567629601</v>
+        <v>0.06676729235360214</v>
       </c>
       <c r="O4" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02048535354006554</v>
+        <v>0.02225729021737167</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8099,51 +8621,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>234.27</v>
+        <v>227.01</v>
       </c>
       <c r="F5" t="n">
-        <v>2520068128768</v>
+        <v>2441971499008</v>
       </c>
       <c r="G5" t="n">
-        <v>7.4</v>
+        <v>7.17</v>
       </c>
       <c r="H5" t="n">
         <v>9.88054</v>
       </c>
       <c r="I5" t="n">
-        <v>31.658108</v>
+        <v>31.661087</v>
       </c>
       <c r="J5" t="n">
-        <v>23.710243</v>
+        <v>22.975464</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.39277</v>
+        <v>3.2876284</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03158748452640116</v>
+        <v>0.03158451169552002</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04217586545439023</v>
+        <v>0.04352469054226686</v>
       </c>
       <c r="O5" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.002334136681840238</v>
+        <v>-0.0009853115939636101</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8157,51 +8679,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>293.08</v>
+        <v>275.15</v>
       </c>
       <c r="F6" t="n">
-        <v>4304570155008</v>
+        <v>4041225797632</v>
       </c>
       <c r="G6" t="n">
-        <v>8.26</v>
+        <v>8.25</v>
       </c>
       <c r="H6" t="n">
-        <v>9.610110000000001</v>
+        <v>9.608919999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>35.48184</v>
+        <v>33.351513</v>
       </c>
       <c r="J6" t="n">
-        <v>30.497047</v>
+        <v>28.634851</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="L6" t="n">
-        <v>9.535156000000001</v>
+        <v>8.951816000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02818343114507984</v>
+        <v>0.02998364528439033</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03279005732223284</v>
+        <v>0.03492247864801018</v>
       </c>
       <c r="O6" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01171994481399763</v>
+        <v>-0.009587523488220291</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8215,51 +8737,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>199</v>
+        <v>195.74</v>
       </c>
       <c r="F7" t="n">
-        <v>4819978813440</v>
+        <v>4741018419200</v>
       </c>
       <c r="G7" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
       <c r="H7" t="n">
         <v>12.72901</v>
       </c>
       <c r="I7" t="n">
-        <v>30.474731</v>
+        <v>29.929665</v>
       </c>
       <c r="J7" t="n">
-        <v>15.633581</v>
+        <v>15.377473</v>
       </c>
       <c r="K7" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="L7" t="n">
-        <v>19.014399</v>
+        <v>18.702906</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0328140703517588</v>
+        <v>0.03341166853989987</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0639648743718593</v>
+        <v>0.06503019311331358</v>
       </c>
       <c r="O7" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01945487223562883</v>
+        <v>0.02052019097708311</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8273,51 +8795,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>519.74</v>
+        <v>532.5700000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>847488352256</v>
+        <v>868408950784</v>
       </c>
       <c r="G8" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="H8" t="n">
         <v>13.16815</v>
       </c>
       <c r="I8" t="n">
-        <v>172.6711</v>
+        <v>178.71477</v>
       </c>
       <c r="J8" t="n">
-        <v>39.46948</v>
+        <v>40.443798</v>
       </c>
       <c r="K8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="L8" t="n">
-        <v>22.627445</v>
+        <v>23.186014</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005791357217070073</v>
+        <v>0.005595508571643164</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02533603340131604</v>
+        <v>0.02472566986499427</v>
       </c>
       <c r="O8" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01917396873491443</v>
+        <v>-0.0197843322712362</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8331,51 +8853,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>382.07</v>
+        <v>378.91</v>
       </c>
       <c r="F9" t="n">
-        <v>1817728778240</v>
+        <v>1802694819840</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>6.02</v>
       </c>
       <c r="H9" t="n">
         <v>19.39578</v>
       </c>
       <c r="I9" t="n">
-        <v>63.678333</v>
+        <v>62.94186</v>
       </c>
       <c r="J9" t="n">
-        <v>19.698614</v>
+        <v>19.535692</v>
       </c>
       <c r="K9" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>24.087044</v>
+        <v>23.887827</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0157039285994713</v>
+        <v>0.01588767781267319</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05076499070850891</v>
+        <v>0.05118835607400173</v>
       </c>
       <c r="O9" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006254988572278436</v>
+        <v>0.006678353937771261</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -8389,10 +8911,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71.84</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>302503755776</v>
+        <v>298545610752</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -8401,28 +8923,28 @@
         <v>3.84196</v>
       </c>
       <c r="I10" t="n">
-        <v>23.174192</v>
+        <v>22.87097</v>
       </c>
       <c r="J10" t="n">
-        <v>18.698788</v>
+        <v>18.454123</v>
       </c>
       <c r="K10" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="L10" t="n">
-        <v>6.45135</v>
+        <v>6.3669367</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04315144766146993</v>
+        <v>0.04372355430183356</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0534793986636971</v>
+        <v>0.05418843441466854</v>
       </c>
       <c r="O10" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P10" t="n">
-        <v>0.00896939652746663</v>
+        <v>0.009678432278438072</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P136"/>
+  <dimension ref="A1:P145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7853,16 +7853,16 @@
         <v>8.951816000000001</v>
       </c>
       <c r="M128" t="n">
-        <v>0.02998364528439033</v>
+        <v>0.0299836452843903</v>
       </c>
       <c r="N128" t="n">
-        <v>0.03492247864801018</v>
+        <v>0.0349224786480101</v>
       </c>
       <c r="O128" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P128" t="n">
-        <v>-0.009587523488220291</v>
+        <v>-0.009587523488220199</v>
       </c>
     </row>
     <row r="129">
@@ -7911,13 +7911,13 @@
         <v>23.186014</v>
       </c>
       <c r="M129" t="n">
-        <v>0.005595508571643164</v>
+        <v>0.0055955085716431</v>
       </c>
       <c r="N129" t="n">
-        <v>0.02472566986499427</v>
+        <v>0.0247256698649942</v>
       </c>
       <c r="O129" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P129" t="n">
         <v>-0.0197843322712362</v>
@@ -7969,16 +7969,16 @@
         <v>3.2876284</v>
       </c>
       <c r="M130" t="n">
-        <v>0.03158451169552002</v>
+        <v>0.03158451169552</v>
       </c>
       <c r="N130" t="n">
-        <v>0.04352469054226686</v>
+        <v>0.0435246905422668</v>
       </c>
       <c r="O130" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P130" t="n">
-        <v>-0.0009853115939636101</v>
+        <v>-0.0009853115939636001</v>
       </c>
     </row>
     <row r="131">
@@ -8027,16 +8027,16 @@
         <v>23.887827</v>
       </c>
       <c r="M131" t="n">
-        <v>0.01588767781267319</v>
+        <v>0.0158876778126731</v>
       </c>
       <c r="N131" t="n">
-        <v>0.05118835607400173</v>
+        <v>0.0511883560740017</v>
       </c>
       <c r="O131" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P131" t="n">
-        <v>0.006678353937771261</v>
+        <v>0.0066783539377712</v>
       </c>
     </row>
     <row r="132">
@@ -8085,16 +8085,16 @@
         <v>9.88312</v>
       </c>
       <c r="M132" t="n">
-        <v>0.03831204886174348</v>
+        <v>0.0383120488617434</v>
       </c>
       <c r="N132" t="n">
-        <v>0.04253037786025308</v>
+        <v>0.042530377860253</v>
       </c>
       <c r="O132" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P132" t="n">
-        <v>-0.001979624275977393</v>
+        <v>-0.0019796242759773</v>
       </c>
     </row>
     <row r="133">
@@ -8143,16 +8143,16 @@
         <v>6.410563</v>
       </c>
       <c r="M133" t="n">
-        <v>0.05069353620572144</v>
+        <v>0.0506935362057214</v>
       </c>
       <c r="N133" t="n">
-        <v>0.06676729235360214</v>
+        <v>0.0667672923536021</v>
       </c>
       <c r="O133" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P133" t="n">
-        <v>0.02225729021737167</v>
+        <v>0.0222572902173716</v>
       </c>
     </row>
     <row r="134">
@@ -8201,16 +8201,16 @@
         <v>8.234989000000001</v>
       </c>
       <c r="M134" t="n">
-        <v>0.04758665646345266</v>
+        <v>0.0475866564634526</v>
       </c>
       <c r="N134" t="n">
-        <v>0.05489567213672307</v>
+        <v>0.054895672136723</v>
       </c>
       <c r="O134" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P134" t="n">
-        <v>0.0103856700004926</v>
+        <v>0.0103856700004925</v>
       </c>
     </row>
     <row r="135">
@@ -8259,16 +8259,16 @@
         <v>6.3669367</v>
       </c>
       <c r="M135" t="n">
-        <v>0.04372355430183356</v>
+        <v>0.0437235543018335</v>
       </c>
       <c r="N135" t="n">
-        <v>0.05418843441466854</v>
+        <v>0.0541884344146685</v>
       </c>
       <c r="O135" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P135" t="n">
-        <v>0.009678432278438072</v>
+        <v>0.009678432278438001</v>
       </c>
     </row>
     <row r="136">
@@ -8317,16 +8317,538 @@
         <v>18.702906</v>
       </c>
       <c r="M136" t="n">
-        <v>0.03341166853989987</v>
+        <v>0.0334116685398998</v>
       </c>
       <c r="N136" t="n">
-        <v>0.06503019311331358</v>
+        <v>0.0650301931133135</v>
       </c>
       <c r="O136" t="n">
+        <v>0.0445100021362304</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.0205201909770831</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>283.78</v>
+      </c>
+      <c r="F137" t="n">
+        <v>4167977926656</v>
+      </c>
+      <c r="G137" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H137" t="n">
+        <v>9.608919999999999</v>
+      </c>
+      <c r="I137" t="n">
+        <v>34.35593</v>
+      </c>
+      <c r="J137" t="n">
+        <v>29.532974</v>
+      </c>
+      <c r="K137" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="L137" t="n">
+        <v>9.232588</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.02910705476073015</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.03386045528226091</v>
+      </c>
+      <c r="O137" t="n">
         <v>0.04451000213623047</v>
       </c>
-      <c r="P136" t="n">
-        <v>0.02052019097708311</v>
+      <c r="P137" t="n">
+        <v>-0.01064954685396956</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>521.58</v>
+      </c>
+      <c r="F138" t="n">
+        <v>850488655872</v>
+      </c>
+      <c r="G138" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="H138" t="n">
+        <v>13.16815</v>
+      </c>
+      <c r="I138" t="n">
+        <v>172.13863</v>
+      </c>
+      <c r="J138" t="n">
+        <v>39.60921</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L138" t="n">
+        <v>22.707552</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.005809271827907511</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.02524665439625752</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P138" t="n">
+        <v>-0.01926334773997295</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>232.69</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2503072022528</v>
+      </c>
+      <c r="G139" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="H139" t="n">
+        <v>9.88054</v>
+      </c>
+      <c r="I139" t="n">
+        <v>31.658504</v>
+      </c>
+      <c r="J139" t="n">
+        <v>23.550333</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L139" t="n">
+        <v>3.3698883</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.03158709011990202</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.04246224590657097</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P139" t="n">
+        <v>-0.002047756229659498</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>365.02</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1736611856384</v>
+      </c>
+      <c r="G140" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H140" t="n">
+        <v>19.39578</v>
+      </c>
+      <c r="I140" t="n">
+        <v>60.63455</v>
+      </c>
+      <c r="J140" t="n">
+        <v>18.819557</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L140" t="n">
+        <v>23.01215</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.01649224700016437</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.0531362117144266</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.008626209578196133</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>334.69</v>
+      </c>
+      <c r="F141" t="n">
+        <v>4084079001600</v>
+      </c>
+      <c r="G141" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="H141" t="n">
+        <v>14.55347</v>
+      </c>
+      <c r="I141" t="n">
+        <v>25.509909</v>
+      </c>
+      <c r="J141" t="n">
+        <v>22.997265</v>
+      </c>
+      <c r="K141" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L141" t="n">
+        <v>9.666505000000001</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.03920045415160298</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.04348343243000986</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P141" t="n">
+        <v>-0.001026569706220608</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>550.25</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1396767457280</v>
+      </c>
+      <c r="G142" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="H142" t="n">
+        <v>36.24596</v>
+      </c>
+      <c r="I142" t="n">
+        <v>20.001818</v>
+      </c>
+      <c r="J142" t="n">
+        <v>15.181003</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L142" t="n">
+        <v>6.497711</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.04999545661063153</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.06587180372557927</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.0213618015893488</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="F143" t="n">
+        <v>2770583420928</v>
+      </c>
+      <c r="G143" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="H143" t="n">
+        <v>19.36884</v>
+      </c>
+      <c r="I143" t="n">
+        <v>22.227055</v>
+      </c>
+      <c r="J143" t="n">
+        <v>19.256187</v>
+      </c>
+      <c r="K143" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L143" t="n">
+        <v>8.705052999999999</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.04499021369010912</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.05193136177172426</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.007421359635493792</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>73.81</v>
+      </c>
+      <c r="F144" t="n">
+        <v>310799040512</v>
+      </c>
+      <c r="G144" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H144" t="n">
+        <v>3.84196</v>
+      </c>
+      <c r="I144" t="n">
+        <v>23.809677</v>
+      </c>
+      <c r="J144" t="n">
+        <v>19.211548</v>
+      </c>
+      <c r="K144" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L144" t="n">
+        <v>6.6282597</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0.04199972903400623</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0.05205202547080341</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0.007542023334572941</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>192.53</v>
+      </c>
+      <c r="F145" t="n">
+        <v>4663269130240</v>
+      </c>
+      <c r="G145" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H145" t="n">
+        <v>12.72901</v>
+      </c>
+      <c r="I145" t="n">
+        <v>29.48392</v>
+      </c>
+      <c r="J145" t="n">
+        <v>15.125293</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L145" t="n">
+        <v>18.396193</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0.0339167921882304</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0.06611442372617254</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0.04451000213623047</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0.02160442158994207</v>
       </c>
     </row>
   </sheetData>
@@ -8428,12 +8950,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8447,51 +8969,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>342.19</v>
+        <v>334.69</v>
       </c>
       <c r="F2" t="n">
-        <v>4175598452736</v>
+        <v>4084079001600</v>
       </c>
       <c r="G2" t="n">
-        <v>13.11</v>
+        <v>13.12</v>
       </c>
       <c r="H2" t="n">
         <v>14.55347</v>
       </c>
       <c r="I2" t="n">
-        <v>26.10145</v>
+        <v>25.509909</v>
       </c>
       <c r="J2" t="n">
-        <v>23.512606</v>
+        <v>22.997265</v>
       </c>
       <c r="K2" t="n">
         <v>1.36</v>
       </c>
       <c r="L2" t="n">
-        <v>9.88312</v>
+        <v>9.666505000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03831204886174348</v>
+        <v>0.03920045415160298</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04253037786025308</v>
+        <v>0.04348343243000986</v>
       </c>
       <c r="O2" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.001979624275977393</v>
+        <v>-0.001026569706220608</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -8505,51 +9027,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>352.83</v>
+        <v>372.97</v>
       </c>
       <c r="F3" t="n">
-        <v>2620974694400</v>
+        <v>2770583420928</v>
       </c>
       <c r="G3" t="n">
-        <v>16.79</v>
+        <v>16.78</v>
       </c>
       <c r="H3" t="n">
         <v>19.36884</v>
       </c>
       <c r="I3" t="n">
-        <v>21.014292</v>
+        <v>22.227055</v>
       </c>
       <c r="J3" t="n">
-        <v>18.216372</v>
+        <v>19.256187</v>
       </c>
       <c r="K3" t="n">
         <v>1.13</v>
       </c>
       <c r="L3" t="n">
-        <v>8.234989000000001</v>
+        <v>8.705052999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04758665646345266</v>
+        <v>0.04499021369010912</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05489567213672307</v>
+        <v>0.05193136177172426</v>
       </c>
       <c r="O3" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0103856700004926</v>
+        <v>0.007421359635493792</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8563,51 +9085,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>542.87</v>
+        <v>550.25</v>
       </c>
       <c r="F4" t="n">
-        <v>1378033860608</v>
+        <v>1396767457280</v>
       </c>
       <c r="G4" t="n">
-        <v>27.52</v>
+        <v>27.51</v>
       </c>
       <c r="H4" t="n">
         <v>36.24596</v>
       </c>
       <c r="I4" t="n">
-        <v>19.72638</v>
+        <v>20.001818</v>
       </c>
       <c r="J4" t="n">
-        <v>14.977393</v>
+        <v>15.181003</v>
       </c>
       <c r="K4" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>6.410563</v>
+        <v>6.497711</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05069353620572144</v>
+        <v>0.04999545661063153</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06676729235360214</v>
+        <v>0.06587180372557927</v>
       </c>
       <c r="O4" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02225729021737167</v>
+        <v>0.0213618015893488</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8621,51 +9143,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>227.01</v>
+        <v>232.69</v>
       </c>
       <c r="F5" t="n">
-        <v>2441971499008</v>
+        <v>2503072022528</v>
       </c>
       <c r="G5" t="n">
-        <v>7.17</v>
+        <v>7.35</v>
       </c>
       <c r="H5" t="n">
         <v>9.88054</v>
       </c>
       <c r="I5" t="n">
-        <v>31.661087</v>
+        <v>31.658504</v>
       </c>
       <c r="J5" t="n">
-        <v>22.975464</v>
+        <v>23.550333</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.2876284</v>
+        <v>3.3698883</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03158451169552002</v>
+        <v>0.03158709011990202</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04352469054226686</v>
+        <v>0.04246224590657097</v>
       </c>
       <c r="O5" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0009853115939636101</v>
+        <v>-0.002047756229659498</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8679,51 +9201,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>275.15</v>
+        <v>283.78</v>
       </c>
       <c r="F6" t="n">
-        <v>4041225797632</v>
+        <v>4167977926656</v>
       </c>
       <c r="G6" t="n">
-        <v>8.25</v>
+        <v>8.26</v>
       </c>
       <c r="H6" t="n">
         <v>9.608919999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>33.351513</v>
+        <v>34.35593</v>
       </c>
       <c r="J6" t="n">
-        <v>28.634851</v>
+        <v>29.532974</v>
       </c>
       <c r="K6" t="n">
         <v>2.37</v>
       </c>
       <c r="L6" t="n">
-        <v>8.951816000000001</v>
+        <v>9.232588</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02998364528439033</v>
+        <v>0.02910705476073015</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03492247864801018</v>
+        <v>0.03386045528226091</v>
       </c>
       <c r="O6" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.009587523488220291</v>
+        <v>-0.01064954685396956</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8737,51 +9259,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>195.74</v>
+        <v>192.53</v>
       </c>
       <c r="F7" t="n">
-        <v>4741018419200</v>
+        <v>4663269130240</v>
       </c>
       <c r="G7" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
       <c r="H7" t="n">
         <v>12.72901</v>
       </c>
       <c r="I7" t="n">
-        <v>29.929665</v>
+        <v>29.48392</v>
       </c>
       <c r="J7" t="n">
-        <v>15.377473</v>
+        <v>15.125293</v>
       </c>
       <c r="K7" t="n">
         <v>0.61</v>
       </c>
       <c r="L7" t="n">
-        <v>18.702906</v>
+        <v>18.396193</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03341166853989987</v>
+        <v>0.0339167921882304</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06503019311331358</v>
+        <v>0.06611442372617254</v>
       </c>
       <c r="O7" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02052019097708311</v>
+        <v>0.02160442158994207</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8795,51 +9317,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>532.5700000000001</v>
+        <v>521.58</v>
       </c>
       <c r="F8" t="n">
-        <v>868408950784</v>
+        <v>850488655872</v>
       </c>
       <c r="G8" t="n">
-        <v>2.98</v>
+        <v>3.03</v>
       </c>
       <c r="H8" t="n">
         <v>13.16815</v>
       </c>
       <c r="I8" t="n">
-        <v>178.71477</v>
+        <v>172.13863</v>
       </c>
       <c r="J8" t="n">
-        <v>40.443798</v>
+        <v>39.60921</v>
       </c>
       <c r="K8" t="n">
         <v>1.25</v>
       </c>
       <c r="L8" t="n">
-        <v>23.186014</v>
+        <v>22.707552</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005595508571643164</v>
+        <v>0.005809271827907511</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02472566986499427</v>
+        <v>0.02524665439625752</v>
       </c>
       <c r="O8" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0197843322712362</v>
+        <v>-0.01926334773997295</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8853,10 +9375,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>378.91</v>
+        <v>365.02</v>
       </c>
       <c r="F9" t="n">
-        <v>1802694819840</v>
+        <v>1736611856384</v>
       </c>
       <c r="G9" t="n">
         <v>6.02</v>
@@ -8865,39 +9387,39 @@
         <v>19.39578</v>
       </c>
       <c r="I9" t="n">
-        <v>62.94186</v>
+        <v>60.63455</v>
       </c>
       <c r="J9" t="n">
-        <v>19.535692</v>
+        <v>18.819557</v>
       </c>
       <c r="K9" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>23.887827</v>
+        <v>23.01215</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01588767781267319</v>
+        <v>0.01649224700016437</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05118835607400173</v>
+        <v>0.0531362117144266</v>
       </c>
       <c r="O9" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006678353937771261</v>
+        <v>0.008626209578196133</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -8911,10 +9433,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>70.90000000000001</v>
+        <v>73.81</v>
       </c>
       <c r="F10" t="n">
-        <v>298545610752</v>
+        <v>310799040512</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -8923,28 +9445,28 @@
         <v>3.84196</v>
       </c>
       <c r="I10" t="n">
-        <v>22.87097</v>
+        <v>23.809677</v>
       </c>
       <c r="J10" t="n">
-        <v>18.454123</v>
+        <v>19.211548</v>
       </c>
       <c r="K10" t="n">
         <v>1.41</v>
       </c>
       <c r="L10" t="n">
-        <v>6.3669367</v>
+        <v>6.6282597</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04372355430183356</v>
+        <v>0.04199972903400623</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05418843441466854</v>
+        <v>0.05205202547080341</v>
       </c>
       <c r="O10" t="n">
         <v>0.04451000213623047</v>
       </c>
       <c r="P10" t="n">
-        <v>0.009678432278438072</v>
+        <v>0.007542023334572941</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P145"/>
+  <dimension ref="A1:P154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8375,16 +8375,16 @@
         <v>9.232588</v>
       </c>
       <c r="M137" t="n">
-        <v>0.02910705476073015</v>
+        <v>0.0291070547607301</v>
       </c>
       <c r="N137" t="n">
-        <v>0.03386045528226091</v>
+        <v>0.0338604552822609</v>
       </c>
       <c r="O137" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P137" t="n">
-        <v>-0.01064954685396956</v>
+        <v>-0.0106495468539695</v>
       </c>
     </row>
     <row r="138">
@@ -8433,16 +8433,16 @@
         <v>22.707552</v>
       </c>
       <c r="M138" t="n">
-        <v>0.005809271827907511</v>
+        <v>0.0058092718279075</v>
       </c>
       <c r="N138" t="n">
-        <v>0.02524665439625752</v>
+        <v>0.0252466543962575</v>
       </c>
       <c r="O138" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P138" t="n">
-        <v>-0.01926334773997295</v>
+        <v>-0.0192633477399729</v>
       </c>
     </row>
     <row r="139">
@@ -8491,16 +8491,16 @@
         <v>3.3698883</v>
       </c>
       <c r="M139" t="n">
-        <v>0.03158709011990202</v>
+        <v>0.031587090119902</v>
       </c>
       <c r="N139" t="n">
-        <v>0.04246224590657097</v>
+        <v>0.0424622459065709</v>
       </c>
       <c r="O139" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P139" t="n">
-        <v>-0.002047756229659498</v>
+        <v>-0.0020477562296594</v>
       </c>
     </row>
     <row r="140">
@@ -8549,16 +8549,16 @@
         <v>23.01215</v>
       </c>
       <c r="M140" t="n">
-        <v>0.01649224700016437</v>
+        <v>0.0164922470001643</v>
       </c>
       <c r="N140" t="n">
         <v>0.0531362117144266</v>
       </c>
       <c r="O140" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P140" t="n">
-        <v>0.008626209578196133</v>
+        <v>0.0086262095781961</v>
       </c>
     </row>
     <row r="141">
@@ -8607,16 +8607,16 @@
         <v>9.666505000000001</v>
       </c>
       <c r="M141" t="n">
-        <v>0.03920045415160298</v>
+        <v>0.0392004541516029</v>
       </c>
       <c r="N141" t="n">
-        <v>0.04348343243000986</v>
+        <v>0.0434834324300098</v>
       </c>
       <c r="O141" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P141" t="n">
-        <v>-0.001026569706220608</v>
+        <v>-0.0010265697062206</v>
       </c>
     </row>
     <row r="142">
@@ -8665,13 +8665,13 @@
         <v>6.497711</v>
       </c>
       <c r="M142" t="n">
-        <v>0.04999545661063153</v>
+        <v>0.0499954566106315</v>
       </c>
       <c r="N142" t="n">
-        <v>0.06587180372557927</v>
+        <v>0.0658718037255792</v>
       </c>
       <c r="O142" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P142" t="n">
         <v>0.0213618015893488</v>
@@ -8723,16 +8723,16 @@
         <v>8.705052999999999</v>
       </c>
       <c r="M143" t="n">
-        <v>0.04499021369010912</v>
+        <v>0.0449902136901091</v>
       </c>
       <c r="N143" t="n">
-        <v>0.05193136177172426</v>
+        <v>0.0519313617717242</v>
       </c>
       <c r="O143" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P143" t="n">
-        <v>0.007421359635493792</v>
+        <v>0.0074213596354937</v>
       </c>
     </row>
     <row r="144">
@@ -8781,16 +8781,16 @@
         <v>6.6282597</v>
       </c>
       <c r="M144" t="n">
-        <v>0.04199972903400623</v>
+        <v>0.0419997290340062</v>
       </c>
       <c r="N144" t="n">
-        <v>0.05205202547080341</v>
+        <v>0.0520520254708034</v>
       </c>
       <c r="O144" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P144" t="n">
-        <v>0.007542023334572941</v>
+        <v>0.0075420233345729</v>
       </c>
     </row>
     <row r="145">
@@ -8842,13 +8842,535 @@
         <v>0.0339167921882304</v>
       </c>
       <c r="N145" t="n">
-        <v>0.06611442372617254</v>
+        <v>0.0661144237261725</v>
       </c>
       <c r="O145" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.0445100021362304</v>
       </c>
       <c r="P145" t="n">
-        <v>0.02160442158994207</v>
+        <v>0.021604421589942</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>281.74</v>
+      </c>
+      <c r="F146" t="n">
+        <v>4138015391744</v>
+      </c>
+      <c r="G146" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H146" t="n">
+        <v>9.608919999999999</v>
+      </c>
+      <c r="I146" t="n">
+        <v>34.150303</v>
+      </c>
+      <c r="J146" t="n">
+        <v>29.320671</v>
+      </c>
+      <c r="K146" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="L146" t="n">
+        <v>9.166217</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0.02928231702988571</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0.03410562930361326</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P146" t="n">
+        <v>-0.009614372870764186</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>539.49</v>
+      </c>
+      <c r="F147" t="n">
+        <v>879692677120</v>
+      </c>
+      <c r="G147" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H147" t="n">
+        <v>13.16815</v>
+      </c>
+      <c r="I147" t="n">
+        <v>178.63907</v>
+      </c>
+      <c r="J147" t="n">
+        <v>40.969307</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L147" t="n">
+        <v>23.487282</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0.005597879478766984</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0.02440851544977664</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P147" t="n">
+        <v>-0.0193114867246008</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>240.14</v>
+      </c>
+      <c r="F148" t="n">
+        <v>2583212326912</v>
+      </c>
+      <c r="G148" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="H148" t="n">
+        <v>9.88054</v>
+      </c>
+      <c r="I148" t="n">
+        <v>31.638998</v>
+      </c>
+      <c r="J148" t="n">
+        <v>24.30434</v>
+      </c>
+      <c r="K148" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L148" t="n">
+        <v>3.4777813</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0.0316065628383443</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0.04114491546597818</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P148" t="n">
+        <v>-0.00257508670839926</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>372.45</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1771960795136</v>
+      </c>
+      <c r="G149" t="n">
+        <v>6</v>
+      </c>
+      <c r="H149" t="n">
+        <v>19.39578</v>
+      </c>
+      <c r="I149" t="n">
+        <v>62.075</v>
+      </c>
+      <c r="J149" t="n">
+        <v>19.202631</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L149" t="n">
+        <v>23.480564</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0.01610954490535643</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0.05207619814740233</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P149" t="n">
+        <v>0.008356195973024887</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>351.28</v>
+      </c>
+      <c r="F150" t="n">
+        <v>4286519705600</v>
+      </c>
+      <c r="G150" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H150" t="n">
+        <v>14.55347</v>
+      </c>
+      <c r="I150" t="n">
+        <v>26.815266</v>
+      </c>
+      <c r="J150" t="n">
+        <v>24.1372</v>
+      </c>
+      <c r="K150" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L150" t="n">
+        <v>10.145657</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0.03729218856752448</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0.04142982805739012</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P150" t="n">
+        <v>-0.002290174116987322</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>562.6</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1428116865024</v>
+      </c>
+      <c r="G151" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="H151" t="n">
+        <v>36.24596</v>
+      </c>
+      <c r="I151" t="n">
+        <v>20.450745</v>
+      </c>
+      <c r="J151" t="n">
+        <v>15.521729</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L151" t="n">
+        <v>6.6435475</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0.04889797369356559</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0.06442580874511197</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0.02070580657073453</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>368.57</v>
+      </c>
+      <c r="F152" t="n">
+        <v>2737898258432</v>
+      </c>
+      <c r="G152" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="H152" t="n">
+        <v>19.36884</v>
+      </c>
+      <c r="I152" t="n">
+        <v>21.92564</v>
+      </c>
+      <c r="J152" t="n">
+        <v>19.029018</v>
+      </c>
+      <c r="K152" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L152" t="n">
+        <v>8.602358000000001</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0.04560870390970508</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0.05255131996635646</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0.008831317791979015</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="F153" t="n">
+        <v>310672719872</v>
+      </c>
+      <c r="G153" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H153" t="n">
+        <v>3.84241</v>
+      </c>
+      <c r="I153" t="n">
+        <v>23.800001</v>
+      </c>
+      <c r="J153" t="n">
+        <v>19.20149</v>
+      </c>
+      <c r="K153" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L153" t="n">
+        <v>6.6255655</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0.04201680672268908</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0.0520792897804283</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0.008359287606050855</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>194.97</v>
+      </c>
+      <c r="F154" t="n">
+        <v>4722368446464</v>
+      </c>
+      <c r="G154" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H154" t="n">
+        <v>12.76443</v>
+      </c>
+      <c r="I154" t="n">
+        <v>29.85758</v>
+      </c>
+      <c r="J154" t="n">
+        <v>15.274478</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L154" t="n">
+        <v>18.629333</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0.03349233215366467</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0.06546868749038313</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0.02174868531600569</v>
       </c>
     </row>
   </sheetData>
@@ -8950,12 +9472,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8969,51 +9491,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>334.69</v>
+        <v>351.28</v>
       </c>
       <c r="F2" t="n">
-        <v>4084079001600</v>
+        <v>4286519705600</v>
       </c>
       <c r="G2" t="n">
-        <v>13.12</v>
+        <v>13.1</v>
       </c>
       <c r="H2" t="n">
         <v>14.55347</v>
       </c>
       <c r="I2" t="n">
-        <v>25.509909</v>
+        <v>26.815266</v>
       </c>
       <c r="J2" t="n">
-        <v>22.997265</v>
+        <v>24.1372</v>
       </c>
       <c r="K2" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="L2" t="n">
-        <v>9.666505000000001</v>
+        <v>10.145657</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03920045415160298</v>
+        <v>0.03729218856752448</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04348343243000986</v>
+        <v>0.04142982805739012</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.04372000217437744</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.001026569706220608</v>
+        <v>-0.002290174116987322</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -9027,51 +9549,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>372.97</v>
+        <v>368.57</v>
       </c>
       <c r="F3" t="n">
-        <v>2770583420928</v>
+        <v>2737898258432</v>
       </c>
       <c r="G3" t="n">
-        <v>16.78</v>
+        <v>16.81</v>
       </c>
       <c r="H3" t="n">
         <v>19.36884</v>
       </c>
       <c r="I3" t="n">
-        <v>22.227055</v>
+        <v>21.92564</v>
       </c>
       <c r="J3" t="n">
-        <v>19.256187</v>
+        <v>19.029018</v>
       </c>
       <c r="K3" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="L3" t="n">
-        <v>8.705052999999999</v>
+        <v>8.602358000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04499021369010912</v>
+        <v>0.04560870390970508</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05193136177172426</v>
+        <v>0.05255131996635646</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.04372000217437744</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007421359635493792</v>
+        <v>0.008831317791979015</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9085,10 +9607,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>550.25</v>
+        <v>562.6</v>
       </c>
       <c r="F4" t="n">
-        <v>1396767457280</v>
+        <v>1428116865024</v>
       </c>
       <c r="G4" t="n">
         <v>27.51</v>
@@ -9097,39 +9619,39 @@
         <v>36.24596</v>
       </c>
       <c r="I4" t="n">
-        <v>20.001818</v>
+        <v>20.450745</v>
       </c>
       <c r="J4" t="n">
-        <v>15.181003</v>
+        <v>15.521729</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="L4" t="n">
-        <v>6.497711</v>
+        <v>6.6435475</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04999545661063153</v>
+        <v>0.04889797369356559</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06587180372557927</v>
+        <v>0.06442580874511197</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.04372000217437744</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0213618015893488</v>
+        <v>0.02070580657073453</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9143,51 +9665,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>232.69</v>
+        <v>240.14</v>
       </c>
       <c r="F5" t="n">
-        <v>2503072022528</v>
+        <v>2583212326912</v>
       </c>
       <c r="G5" t="n">
-        <v>7.35</v>
+        <v>7.59</v>
       </c>
       <c r="H5" t="n">
         <v>9.88054</v>
       </c>
       <c r="I5" t="n">
-        <v>31.658504</v>
+        <v>31.638998</v>
       </c>
       <c r="J5" t="n">
-        <v>23.550333</v>
+        <v>24.30434</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.3698883</v>
+        <v>3.4777813</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03158709011990202</v>
+        <v>0.0316065628383443</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04246224590657097</v>
+        <v>0.04114491546597818</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.04372000217437744</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.002047756229659498</v>
+        <v>-0.00257508670839926</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9201,51 +9723,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>283.78</v>
+        <v>281.74</v>
       </c>
       <c r="F6" t="n">
-        <v>4167977926656</v>
+        <v>4138015391744</v>
       </c>
       <c r="G6" t="n">
-        <v>8.26</v>
+        <v>8.25</v>
       </c>
       <c r="H6" t="n">
         <v>9.608919999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>34.35593</v>
+        <v>34.150303</v>
       </c>
       <c r="J6" t="n">
-        <v>29.532974</v>
+        <v>29.320671</v>
       </c>
       <c r="K6" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="L6" t="n">
-        <v>9.232588</v>
+        <v>9.166217</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02910705476073015</v>
+        <v>0.02928231702988571</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03386045528226091</v>
+        <v>0.03410562930361326</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.04372000217437744</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01064954685396956</v>
+        <v>-0.009614372870764186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9259,51 +9781,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>192.53</v>
+        <v>194.97</v>
       </c>
       <c r="F7" t="n">
-        <v>4663269130240</v>
+        <v>4722368446464</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
       </c>
       <c r="H7" t="n">
-        <v>12.72901</v>
+        <v>12.76443</v>
       </c>
       <c r="I7" t="n">
-        <v>29.48392</v>
+        <v>29.85758</v>
       </c>
       <c r="J7" t="n">
-        <v>15.125293</v>
+        <v>15.274478</v>
       </c>
       <c r="K7" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="L7" t="n">
-        <v>18.396193</v>
+        <v>18.629333</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0339167921882304</v>
+        <v>0.03349233215366467</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06611442372617254</v>
+        <v>0.06546868749038313</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.04372000217437744</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02160442158994207</v>
+        <v>0.02174868531600569</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -9317,51 +9839,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>521.58</v>
+        <v>539.49</v>
       </c>
       <c r="F8" t="n">
-        <v>850488655872</v>
+        <v>879692677120</v>
       </c>
       <c r="G8" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="H8" t="n">
         <v>13.16815</v>
       </c>
       <c r="I8" t="n">
-        <v>172.13863</v>
+        <v>178.63907</v>
       </c>
       <c r="J8" t="n">
-        <v>39.60921</v>
+        <v>40.969307</v>
       </c>
       <c r="K8" t="n">
         <v>1.25</v>
       </c>
       <c r="L8" t="n">
-        <v>22.707552</v>
+        <v>23.487282</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005809271827907511</v>
+        <v>0.005597879478766984</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02524665439625752</v>
+        <v>0.02440851544977664</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.04372000217437744</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01926334773997295</v>
+        <v>-0.0193114867246008</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -9375,51 +9897,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>365.02</v>
+        <v>372.45</v>
       </c>
       <c r="F9" t="n">
-        <v>1736611856384</v>
+        <v>1771960795136</v>
       </c>
       <c r="G9" t="n">
-        <v>6.02</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>19.39578</v>
       </c>
       <c r="I9" t="n">
-        <v>60.63455</v>
+        <v>62.075</v>
       </c>
       <c r="J9" t="n">
-        <v>18.819557</v>
+        <v>19.202631</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="L9" t="n">
-        <v>23.01215</v>
+        <v>23.480564</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01649224700016437</v>
+        <v>0.01610954490535643</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0531362117144266</v>
+        <v>0.05207619814740233</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.04372000217437744</v>
       </c>
       <c r="P9" t="n">
-        <v>0.008626209578196133</v>
+        <v>0.008356195973024887</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -9433,40 +9955,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73.81</v>
+        <v>73.78</v>
       </c>
       <c r="F10" t="n">
-        <v>310799040512</v>
+        <v>310672719872</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.84196</v>
+        <v>3.84241</v>
       </c>
       <c r="I10" t="n">
-        <v>23.809677</v>
+        <v>23.800001</v>
       </c>
       <c r="J10" t="n">
-        <v>19.211548</v>
+        <v>19.20149</v>
       </c>
       <c r="K10" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="L10" t="n">
-        <v>6.6282597</v>
+        <v>6.6255655</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04199972903400623</v>
+        <v>0.04201680672268908</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05205202547080341</v>
+        <v>0.0520792897804283</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04451000213623047</v>
+        <v>0.04372000217437744</v>
       </c>
       <c r="P10" t="n">
-        <v>0.007542023334572941</v>
+        <v>0.008359287606050855</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P154"/>
+  <dimension ref="A1:P163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8897,16 +8897,16 @@
         <v>9.166217</v>
       </c>
       <c r="M146" t="n">
-        <v>0.02928231702988571</v>
+        <v>0.0292823170298857</v>
       </c>
       <c r="N146" t="n">
-        <v>0.03410562930361326</v>
+        <v>0.0341056293036132</v>
       </c>
       <c r="O146" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P146" t="n">
-        <v>-0.009614372870764186</v>
+        <v>-0.009614372870764099</v>
       </c>
     </row>
     <row r="147">
@@ -8955,13 +8955,13 @@
         <v>23.487282</v>
       </c>
       <c r="M147" t="n">
-        <v>0.005597879478766984</v>
+        <v>0.0055978794787669</v>
       </c>
       <c r="N147" t="n">
-        <v>0.02440851544977664</v>
+        <v>0.0244085154497766</v>
       </c>
       <c r="O147" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P147" t="n">
         <v>-0.0193114867246008</v>
@@ -9016,13 +9016,13 @@
         <v>0.0316065628383443</v>
       </c>
       <c r="N148" t="n">
-        <v>0.04114491546597818</v>
+        <v>0.0411449154659781</v>
       </c>
       <c r="O148" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P148" t="n">
-        <v>-0.00257508670839926</v>
+        <v>-0.0025750867083992</v>
       </c>
     </row>
     <row r="149">
@@ -9071,16 +9071,16 @@
         <v>23.480564</v>
       </c>
       <c r="M149" t="n">
-        <v>0.01610954490535643</v>
+        <v>0.0161095449053564</v>
       </c>
       <c r="N149" t="n">
-        <v>0.05207619814740233</v>
+        <v>0.0520761981474023</v>
       </c>
       <c r="O149" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P149" t="n">
-        <v>0.008356195973024887</v>
+        <v>0.0083561959730248</v>
       </c>
     </row>
     <row r="150">
@@ -9129,16 +9129,16 @@
         <v>10.145657</v>
       </c>
       <c r="M150" t="n">
-        <v>0.03729218856752448</v>
+        <v>0.0372921885675244</v>
       </c>
       <c r="N150" t="n">
-        <v>0.04142982805739012</v>
+        <v>0.0414298280573901</v>
       </c>
       <c r="O150" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P150" t="n">
-        <v>-0.002290174116987322</v>
+        <v>-0.0022901741169873</v>
       </c>
     </row>
     <row r="151">
@@ -9187,16 +9187,16 @@
         <v>6.6435475</v>
       </c>
       <c r="M151" t="n">
-        <v>0.04889797369356559</v>
+        <v>0.0488979736935655</v>
       </c>
       <c r="N151" t="n">
-        <v>0.06442580874511197</v>
+        <v>0.0644258087451119</v>
       </c>
       <c r="O151" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P151" t="n">
-        <v>0.02070580657073453</v>
+        <v>0.0207058065707345</v>
       </c>
     </row>
     <row r="152">
@@ -9245,16 +9245,16 @@
         <v>8.602358000000001</v>
       </c>
       <c r="M152" t="n">
-        <v>0.04560870390970508</v>
+        <v>0.045608703909705</v>
       </c>
       <c r="N152" t="n">
-        <v>0.05255131996635646</v>
+        <v>0.0525513199663564</v>
       </c>
       <c r="O152" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P152" t="n">
-        <v>0.008831317791979015</v>
+        <v>0.008831317791979</v>
       </c>
     </row>
     <row r="153">
@@ -9303,16 +9303,16 @@
         <v>6.6255655</v>
       </c>
       <c r="M153" t="n">
-        <v>0.04201680672268908</v>
+        <v>0.042016806722689</v>
       </c>
       <c r="N153" t="n">
         <v>0.0520792897804283</v>
       </c>
       <c r="O153" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P153" t="n">
-        <v>0.008359287606050855</v>
+        <v>0.0083592876060508</v>
       </c>
     </row>
     <row r="154">
@@ -9361,16 +9361,538 @@
         <v>18.629333</v>
       </c>
       <c r="M154" t="n">
-        <v>0.03349233215366467</v>
+        <v>0.0334923321536646</v>
       </c>
       <c r="N154" t="n">
-        <v>0.06546868749038313</v>
+        <v>0.06546868749038311</v>
       </c>
       <c r="O154" t="n">
+        <v>0.0437200021743774</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0.0217486853160056</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>289.36</v>
+      </c>
+      <c r="F155" t="n">
+        <v>4249933053952</v>
+      </c>
+      <c r="G155" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H155" t="n">
+        <v>9.608919999999999</v>
+      </c>
+      <c r="I155" t="n">
+        <v>35.073936</v>
+      </c>
+      <c r="J155" t="n">
+        <v>30.113684</v>
+      </c>
+      <c r="K155" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="L155" t="n">
+        <v>9.414128</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0.02851119712468897</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0.03320749239701409</v>
+      </c>
+      <c r="O155" t="n">
         <v>0.04372000217437744</v>
       </c>
-      <c r="P154" t="n">
-        <v>0.02174868531600569</v>
+      <c r="P155" t="n">
+        <v>-0.01051250977736335</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>580.91</v>
+      </c>
+      <c r="F156" t="n">
+        <v>947232112640</v>
+      </c>
+      <c r="G156" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H156" t="n">
+        <v>13.17704</v>
+      </c>
+      <c r="I156" t="n">
+        <v>192.3543</v>
+      </c>
+      <c r="J156" t="n">
+        <v>44.08501</v>
+      </c>
+      <c r="K156" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L156" t="n">
+        <v>25.290546</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0.005198739908075262</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0.02268344493983578</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P156" t="n">
+        <v>-0.02103655723454167</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>238.34</v>
+      </c>
+      <c r="F157" t="n">
+        <v>2563849584640</v>
+      </c>
+      <c r="G157" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="H157" t="n">
+        <v>9.88054</v>
+      </c>
+      <c r="I157" t="n">
+        <v>31.652058</v>
+      </c>
+      <c r="J157" t="n">
+        <v>24.122164</v>
+      </c>
+      <c r="K157" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L157" t="n">
+        <v>3.451713</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0.03159352185952841</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0.04145565159016531</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P157" t="n">
+        <v>-0.002264350584212135</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>377.75</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1797175902208</v>
+      </c>
+      <c r="G158" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H158" t="n">
+        <v>19.39578</v>
+      </c>
+      <c r="I158" t="n">
+        <v>62.853577</v>
+      </c>
+      <c r="J158" t="n">
+        <v>19.475885</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L158" t="n">
+        <v>23.814695</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0.01590999338186631</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0.05134554599602911</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0.007625543821651669</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>353.33</v>
+      </c>
+      <c r="F159" t="n">
+        <v>4311534796800</v>
+      </c>
+      <c r="G159" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="H159" t="n">
+        <v>14.55347</v>
+      </c>
+      <c r="I159" t="n">
+        <v>26.951181</v>
+      </c>
+      <c r="J159" t="n">
+        <v>24.278059</v>
+      </c>
+      <c r="K159" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L159" t="n">
+        <v>10.2048645</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0.03710412362380777</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0.04118945461749639</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P159" t="n">
+        <v>-0.002530547556881049</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>563.29</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1429868380160</v>
+      </c>
+      <c r="G160" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="H160" t="n">
+        <v>36.24596</v>
+      </c>
+      <c r="I160" t="n">
+        <v>20.490723</v>
+      </c>
+      <c r="J160" t="n">
+        <v>15.540766</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L160" t="n">
+        <v>6.6516953</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0.04880257061194056</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0.06434689058921692</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0.02062688841483947</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>373.02</v>
+      </c>
+      <c r="F161" t="n">
+        <v>2770954616832</v>
+      </c>
+      <c r="G161" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="H161" t="n">
+        <v>19.36884</v>
+      </c>
+      <c r="I161" t="n">
+        <v>22.216793</v>
+      </c>
+      <c r="J161" t="n">
+        <v>19.258768</v>
+      </c>
+      <c r="K161" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L161" t="n">
+        <v>8.70622</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0.04501099136775508</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0.05192440083641628</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0.008204398662038835</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="F162" t="n">
+        <v>300651020288</v>
+      </c>
+      <c r="G162" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H162" t="n">
+        <v>3.84241</v>
+      </c>
+      <c r="I162" t="n">
+        <v>23.032259</v>
+      </c>
+      <c r="J162" t="n">
+        <v>18.582088</v>
+      </c>
+      <c r="K162" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L162" t="n">
+        <v>6.4118376</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0.04341736694677871</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0.05381526610644258</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0.01009526393206513</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>200.09</v>
+      </c>
+      <c r="F163" t="n">
+        <v>4846379859968</v>
+      </c>
+      <c r="G163" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="H163" t="n">
+        <v>12.76443</v>
+      </c>
+      <c r="I163" t="n">
+        <v>30.68865</v>
+      </c>
+      <c r="J163" t="n">
+        <v>15.675591</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L163" t="n">
+        <v>19.118547</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0.03258533659853066</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0.0637934429506722</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0.02007344077629476</v>
       </c>
     </row>
   </sheetData>
@@ -9472,12 +9994,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9491,51 +10013,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>351.28</v>
+        <v>353.33</v>
       </c>
       <c r="F2" t="n">
-        <v>4286519705600</v>
+        <v>4311534796800</v>
       </c>
       <c r="G2" t="n">
-        <v>13.1</v>
+        <v>13.11</v>
       </c>
       <c r="H2" t="n">
         <v>14.55347</v>
       </c>
       <c r="I2" t="n">
-        <v>26.815266</v>
+        <v>26.951181</v>
       </c>
       <c r="J2" t="n">
-        <v>24.1372</v>
+        <v>24.278059</v>
       </c>
       <c r="K2" t="n">
         <v>1.32</v>
       </c>
       <c r="L2" t="n">
-        <v>10.145657</v>
+        <v>10.2048645</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03729218856752448</v>
+        <v>0.03710412362380777</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04142982805739012</v>
+        <v>0.04118945461749639</v>
       </c>
       <c r="O2" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.002290174116987322</v>
+        <v>-0.002530547556881049</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -9549,51 +10071,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>368.57</v>
+        <v>373.02</v>
       </c>
       <c r="F3" t="n">
-        <v>2737898258432</v>
+        <v>2770954616832</v>
       </c>
       <c r="G3" t="n">
-        <v>16.81</v>
+        <v>16.79</v>
       </c>
       <c r="H3" t="n">
         <v>19.36884</v>
       </c>
       <c r="I3" t="n">
-        <v>21.92564</v>
+        <v>22.216793</v>
       </c>
       <c r="J3" t="n">
-        <v>19.029018</v>
+        <v>19.258768</v>
       </c>
       <c r="K3" t="n">
         <v>1.15</v>
       </c>
       <c r="L3" t="n">
-        <v>8.602358000000001</v>
+        <v>8.70622</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04560870390970508</v>
+        <v>0.04501099136775508</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05255131996635646</v>
+        <v>0.05192440083641628</v>
       </c>
       <c r="O3" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008831317791979015</v>
+        <v>0.008204398662038835</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9607,51 +10129,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>562.6</v>
+        <v>563.29</v>
       </c>
       <c r="F4" t="n">
-        <v>1428116865024</v>
+        <v>1429868380160</v>
       </c>
       <c r="G4" t="n">
-        <v>27.51</v>
+        <v>27.49</v>
       </c>
       <c r="H4" t="n">
         <v>36.24596</v>
       </c>
       <c r="I4" t="n">
-        <v>20.450745</v>
+        <v>20.490723</v>
       </c>
       <c r="J4" t="n">
-        <v>15.521729</v>
+        <v>15.540766</v>
       </c>
       <c r="K4" t="n">
         <v>0.8</v>
       </c>
       <c r="L4" t="n">
-        <v>6.6435475</v>
+        <v>6.6516953</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04889797369356559</v>
+        <v>0.04880257061194056</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06442580874511197</v>
+        <v>0.06434689058921692</v>
       </c>
       <c r="O4" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02070580657073453</v>
+        <v>0.02062688841483947</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9665,51 +10187,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>240.14</v>
+        <v>238.34</v>
       </c>
       <c r="F5" t="n">
-        <v>2583212326912</v>
+        <v>2563849584640</v>
       </c>
       <c r="G5" t="n">
-        <v>7.59</v>
+        <v>7.53</v>
       </c>
       <c r="H5" t="n">
         <v>9.88054</v>
       </c>
       <c r="I5" t="n">
-        <v>31.638998</v>
+        <v>31.652058</v>
       </c>
       <c r="J5" t="n">
-        <v>24.30434</v>
+        <v>24.122164</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4777813</v>
+        <v>3.451713</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0316065628383443</v>
+        <v>0.03159352185952841</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04114491546597818</v>
+        <v>0.04145565159016531</v>
       </c>
       <c r="O5" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.00257508670839926</v>
+        <v>-0.002264350584212135</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9723,10 +10245,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>281.74</v>
+        <v>289.36</v>
       </c>
       <c r="F6" t="n">
-        <v>4138015391744</v>
+        <v>4249933053952</v>
       </c>
       <c r="G6" t="n">
         <v>8.25</v>
@@ -9735,39 +10257,39 @@
         <v>9.608919999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>34.150303</v>
+        <v>35.073936</v>
       </c>
       <c r="J6" t="n">
-        <v>29.320671</v>
+        <v>30.113684</v>
       </c>
       <c r="K6" t="n">
         <v>2.29</v>
       </c>
       <c r="L6" t="n">
-        <v>9.166217</v>
+        <v>9.414128</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02928231702988571</v>
+        <v>0.02851119712468897</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03410562930361326</v>
+        <v>0.03320749239701409</v>
       </c>
       <c r="O6" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.009614372870764186</v>
+        <v>-0.01051250977736335</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9781,51 +10303,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>194.97</v>
+        <v>200.09</v>
       </c>
       <c r="F7" t="n">
-        <v>4722368446464</v>
+        <v>4846379859968</v>
       </c>
       <c r="G7" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
       <c r="H7" t="n">
         <v>12.76443</v>
       </c>
       <c r="I7" t="n">
-        <v>29.85758</v>
+        <v>30.68865</v>
       </c>
       <c r="J7" t="n">
-        <v>15.274478</v>
+        <v>15.675591</v>
       </c>
       <c r="K7" t="n">
         <v>0.59</v>
       </c>
       <c r="L7" t="n">
-        <v>18.629333</v>
+        <v>19.118547</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03349233215366467</v>
+        <v>0.03258533659853066</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06546868749038313</v>
+        <v>0.0637934429506722</v>
       </c>
       <c r="O7" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02174868531600569</v>
+        <v>0.02007344077629476</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -9839,51 +10361,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>539.49</v>
+        <v>580.91</v>
       </c>
       <c r="F8" t="n">
-        <v>879692677120</v>
+        <v>947232112640</v>
       </c>
       <c r="G8" t="n">
         <v>3.02</v>
       </c>
       <c r="H8" t="n">
-        <v>13.16815</v>
+        <v>13.17704</v>
       </c>
       <c r="I8" t="n">
-        <v>178.63907</v>
+        <v>192.3543</v>
       </c>
       <c r="J8" t="n">
-        <v>40.969307</v>
+        <v>44.08501</v>
       </c>
       <c r="K8" t="n">
         <v>1.25</v>
       </c>
       <c r="L8" t="n">
-        <v>23.487282</v>
+        <v>25.290546</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005597879478766984</v>
+        <v>0.005198739908075262</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02440851544977664</v>
+        <v>0.02268344493983578</v>
       </c>
       <c r="O8" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0193114867246008</v>
+        <v>-0.02103655723454167</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -9897,51 +10419,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>372.45</v>
+        <v>377.75</v>
       </c>
       <c r="F9" t="n">
-        <v>1771960795136</v>
+        <v>1797175902208</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>6.01</v>
       </c>
       <c r="H9" t="n">
         <v>19.39578</v>
       </c>
       <c r="I9" t="n">
-        <v>62.075</v>
+        <v>62.853577</v>
       </c>
       <c r="J9" t="n">
-        <v>19.202631</v>
+        <v>19.475885</v>
       </c>
       <c r="K9" t="n">
         <v>0.66</v>
       </c>
       <c r="L9" t="n">
-        <v>23.480564</v>
+        <v>23.814695</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01610954490535643</v>
+        <v>0.01590999338186631</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05207619814740233</v>
+        <v>0.05134554599602911</v>
       </c>
       <c r="O9" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P9" t="n">
-        <v>0.008356195973024887</v>
+        <v>0.007625543821651669</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -9955,10 +10477,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73.78</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>310672719872</v>
+        <v>300651020288</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -9967,28 +10489,28 @@
         <v>3.84241</v>
       </c>
       <c r="I10" t="n">
-        <v>23.800001</v>
+        <v>23.032259</v>
       </c>
       <c r="J10" t="n">
-        <v>19.20149</v>
+        <v>18.582088</v>
       </c>
       <c r="K10" t="n">
         <v>1.45</v>
       </c>
       <c r="L10" t="n">
-        <v>6.6255655</v>
+        <v>6.4118376</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04201680672268908</v>
+        <v>0.04341736694677871</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0520792897804283</v>
+        <v>0.05381526610644258</v>
       </c>
       <c r="O10" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P10" t="n">
-        <v>0.008359287606050855</v>
+        <v>0.01009526393206513</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P163"/>
+  <dimension ref="A1:P172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9419,16 +9419,16 @@
         <v>9.414128</v>
       </c>
       <c r="M155" t="n">
-        <v>0.02851119712468897</v>
+        <v>0.0285111971246889</v>
       </c>
       <c r="N155" t="n">
-        <v>0.03320749239701409</v>
+        <v>0.033207492397014</v>
       </c>
       <c r="O155" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P155" t="n">
-        <v>-0.01051250977736335</v>
+        <v>-0.0105125097773633</v>
       </c>
     </row>
     <row r="156">
@@ -9477,16 +9477,16 @@
         <v>25.290546</v>
       </c>
       <c r="M156" t="n">
-        <v>0.005198739908075262</v>
+        <v>0.0051987399080752</v>
       </c>
       <c r="N156" t="n">
-        <v>0.02268344493983578</v>
+        <v>0.0226834449398357</v>
       </c>
       <c r="O156" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P156" t="n">
-        <v>-0.02103655723454167</v>
+        <v>-0.0210365572345416</v>
       </c>
     </row>
     <row r="157">
@@ -9535,16 +9535,16 @@
         <v>3.451713</v>
       </c>
       <c r="M157" t="n">
-        <v>0.03159352185952841</v>
+        <v>0.0315935218595284</v>
       </c>
       <c r="N157" t="n">
-        <v>0.04145565159016531</v>
+        <v>0.0414556515901653</v>
       </c>
       <c r="O157" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P157" t="n">
-        <v>-0.002264350584212135</v>
+        <v>-0.0022643505842121</v>
       </c>
     </row>
     <row r="158">
@@ -9593,16 +9593,16 @@
         <v>23.814695</v>
       </c>
       <c r="M158" t="n">
-        <v>0.01590999338186631</v>
+        <v>0.0159099933818663</v>
       </c>
       <c r="N158" t="n">
-        <v>0.05134554599602911</v>
+        <v>0.0513455459960291</v>
       </c>
       <c r="O158" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P158" t="n">
-        <v>0.007625543821651669</v>
+        <v>0.0076255438216516</v>
       </c>
     </row>
     <row r="159">
@@ -9651,16 +9651,16 @@
         <v>10.2048645</v>
       </c>
       <c r="M159" t="n">
-        <v>0.03710412362380777</v>
+        <v>0.0371041236238077</v>
       </c>
       <c r="N159" t="n">
-        <v>0.04118945461749639</v>
+        <v>0.0411894546174963</v>
       </c>
       <c r="O159" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P159" t="n">
-        <v>-0.002530547556881049</v>
+        <v>-0.002530547556881</v>
       </c>
     </row>
     <row r="160">
@@ -9709,16 +9709,16 @@
         <v>6.6516953</v>
       </c>
       <c r="M160" t="n">
-        <v>0.04880257061194056</v>
+        <v>0.0488025706119405</v>
       </c>
       <c r="N160" t="n">
-        <v>0.06434689058921692</v>
+        <v>0.0643468905892169</v>
       </c>
       <c r="O160" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P160" t="n">
-        <v>0.02062688841483947</v>
+        <v>0.0206268884148394</v>
       </c>
     </row>
     <row r="161">
@@ -9767,16 +9767,16 @@
         <v>8.70622</v>
       </c>
       <c r="M161" t="n">
-        <v>0.04501099136775508</v>
+        <v>0.045010991367755</v>
       </c>
       <c r="N161" t="n">
-        <v>0.05192440083641628</v>
+        <v>0.0519244008364162</v>
       </c>
       <c r="O161" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P161" t="n">
-        <v>0.008204398662038835</v>
+        <v>0.0082043986620388</v>
       </c>
     </row>
     <row r="162">
@@ -9825,16 +9825,16 @@
         <v>6.4118376</v>
       </c>
       <c r="M162" t="n">
-        <v>0.04341736694677871</v>
+        <v>0.0434173669467787</v>
       </c>
       <c r="N162" t="n">
-        <v>0.05381526610644258</v>
+        <v>0.0538152661064425</v>
       </c>
       <c r="O162" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P162" t="n">
-        <v>0.01009526393206513</v>
+        <v>0.0100952639320651</v>
       </c>
     </row>
     <row r="163">
@@ -9883,16 +9883,538 @@
         <v>19.118547</v>
       </c>
       <c r="M163" t="n">
-        <v>0.03258533659853066</v>
+        <v>0.0325853365985306</v>
       </c>
       <c r="N163" t="n">
         <v>0.0637934429506722</v>
       </c>
       <c r="O163" t="n">
+        <v>0.0437200021743774</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0.0200734407762947</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>294.38</v>
+      </c>
+      <c r="F164" t="n">
+        <v>4323663937536</v>
+      </c>
+      <c r="G164" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="H164" t="n">
+        <v>9.608919999999999</v>
+      </c>
+      <c r="I164" t="n">
+        <v>35.59613</v>
+      </c>
+      <c r="J164" t="n">
+        <v>30.636118</v>
+      </c>
+      <c r="K164" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="L164" t="n">
+        <v>9.577451999999999</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0.02809294109654189</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0.03264121203886133</v>
+      </c>
+      <c r="O164" t="n">
         <v>0.04372000217437744</v>
       </c>
-      <c r="P163" t="n">
-        <v>0.02007344077629476</v>
+      <c r="P164" t="n">
+        <v>-0.01107879013551611</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>540.88</v>
+      </c>
+      <c r="F165" t="n">
+        <v>881959239680</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="H165" t="n">
+        <v>13.17704</v>
+      </c>
+      <c r="I165" t="n">
+        <v>182.11447</v>
+      </c>
+      <c r="J165" t="n">
+        <v>41.047153</v>
+      </c>
+      <c r="K165" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L165" t="n">
+        <v>23.547798</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0.005491051619582903</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0.02436222452299956</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P165" t="n">
+        <v>-0.01935777765137789</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>241.7</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2599993475072</v>
+      </c>
+      <c r="G166" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="H166" t="n">
+        <v>9.88054</v>
+      </c>
+      <c r="I166" t="n">
+        <v>31.636126</v>
+      </c>
+      <c r="J166" t="n">
+        <v>24.462225</v>
+      </c>
+      <c r="K166" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L166" t="n">
+        <v>3.5003736</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0.03160943318163012</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0.0408793545717832</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P166" t="n">
+        <v>-0.00284064760259424</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>369.34</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1757164732416</v>
+      </c>
+      <c r="G167" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H167" t="n">
+        <v>19.39578</v>
+      </c>
+      <c r="I167" t="n">
+        <v>61.352158</v>
+      </c>
+      <c r="J167" t="n">
+        <v>19.042286</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L167" t="n">
+        <v>23.2845</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0.01629934477717009</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0.05251470190068772</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0.008794699726310272</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>357.89</v>
+      </c>
+      <c r="F168" t="n">
+        <v>4367179055104</v>
+      </c>
+      <c r="G168" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H168" t="n">
+        <v>14.57146</v>
+      </c>
+      <c r="I168" t="n">
+        <v>27.319847</v>
+      </c>
+      <c r="J168" t="n">
+        <v>24.561028</v>
+      </c>
+      <c r="K168" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L168" t="n">
+        <v>10.336567</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0.03660342563357456</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0.0407149124032524</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P168" t="n">
+        <v>-0.003005089771125048</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>612.91</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1555824902144</v>
+      </c>
+      <c r="G169" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="H169" t="n">
+        <v>36.24596</v>
+      </c>
+      <c r="I169" t="n">
+        <v>22.271437</v>
+      </c>
+      <c r="J169" t="n">
+        <v>16.909746</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L169" t="n">
+        <v>7.2376404</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0.04490055636227179</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0.05913749163825031</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0.01541748946387287</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>384.28</v>
+      </c>
+      <c r="F170" t="n">
+        <v>2854599000064</v>
+      </c>
+      <c r="G170" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="H170" t="n">
+        <v>19.36884</v>
+      </c>
+      <c r="I170" t="n">
+        <v>22.887432</v>
+      </c>
+      <c r="J170" t="n">
+        <v>19.840115</v>
+      </c>
+      <c r="K170" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L170" t="n">
+        <v>8.969027000000001</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0.04369209951077339</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0.0504029353596336</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0.00668293318525616</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>74.19</v>
+      </c>
+      <c r="F171" t="n">
+        <v>312399167488</v>
+      </c>
+      <c r="G171" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H171" t="n">
+        <v>3.84241</v>
+      </c>
+      <c r="I171" t="n">
+        <v>23.93226</v>
+      </c>
+      <c r="J171" t="n">
+        <v>19.308195</v>
+      </c>
+      <c r="K171" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L171" t="n">
+        <v>6.6623845</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0.0417846070899043</v>
+      </c>
+      <c r="N171" t="n">
+        <v>0.05179148133171587</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0.008071479157338426</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>197.58</v>
+      </c>
+      <c r="F172" t="n">
+        <v>4785584996352</v>
+      </c>
+      <c r="G172" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="H172" t="n">
+        <v>12.76443</v>
+      </c>
+      <c r="I172" t="n">
+        <v>30.30368</v>
+      </c>
+      <c r="J172" t="n">
+        <v>15.478952</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L172" t="n">
+        <v>18.878717</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0.03299929142625772</v>
+      </c>
+      <c r="N172" t="n">
+        <v>0.06460385666565442</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P172" t="n">
+        <v>0.02088385449127698</v>
       </c>
     </row>
   </sheetData>
@@ -9994,12 +10516,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -10013,51 +10535,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353.33</v>
+        <v>357.89</v>
       </c>
       <c r="F2" t="n">
-        <v>4311534796800</v>
+        <v>4367179055104</v>
       </c>
       <c r="G2" t="n">
-        <v>13.11</v>
+        <v>13.1</v>
       </c>
       <c r="H2" t="n">
-        <v>14.55347</v>
+        <v>14.57146</v>
       </c>
       <c r="I2" t="n">
-        <v>26.951181</v>
+        <v>27.319847</v>
       </c>
       <c r="J2" t="n">
-        <v>24.278059</v>
+        <v>24.561028</v>
       </c>
       <c r="K2" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="L2" t="n">
-        <v>10.2048645</v>
+        <v>10.336567</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03710412362380777</v>
+        <v>0.03660342563357456</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04118945461749639</v>
+        <v>0.0407149124032524</v>
       </c>
       <c r="O2" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.002530547556881049</v>
+        <v>-0.003005089771125048</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -10071,10 +10593,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>373.02</v>
+        <v>384.28</v>
       </c>
       <c r="F3" t="n">
-        <v>2770954616832</v>
+        <v>2854599000064</v>
       </c>
       <c r="G3" t="n">
         <v>16.79</v>
@@ -10083,39 +10605,39 @@
         <v>19.36884</v>
       </c>
       <c r="I3" t="n">
-        <v>22.216793</v>
+        <v>22.887432</v>
       </c>
       <c r="J3" t="n">
-        <v>19.258768</v>
+        <v>19.840115</v>
       </c>
       <c r="K3" t="n">
         <v>1.15</v>
       </c>
       <c r="L3" t="n">
-        <v>8.70622</v>
+        <v>8.969027000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04501099136775508</v>
+        <v>0.04369209951077339</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05192440083641628</v>
+        <v>0.0504029353596336</v>
       </c>
       <c r="O3" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008204398662038835</v>
+        <v>0.00668293318525616</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -10129,51 +10651,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>563.29</v>
+        <v>612.91</v>
       </c>
       <c r="F4" t="n">
-        <v>1429868380160</v>
+        <v>1555824902144</v>
       </c>
       <c r="G4" t="n">
-        <v>27.49</v>
+        <v>27.52</v>
       </c>
       <c r="H4" t="n">
         <v>36.24596</v>
       </c>
       <c r="I4" t="n">
-        <v>20.490723</v>
+        <v>22.271437</v>
       </c>
       <c r="J4" t="n">
-        <v>15.540766</v>
+        <v>16.909746</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>6.6516953</v>
+        <v>7.2376404</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04880257061194056</v>
+        <v>0.04490055636227179</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06434689058921692</v>
+        <v>0.05913749163825031</v>
       </c>
       <c r="O4" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02062688841483947</v>
+        <v>0.01541748946387287</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -10187,51 +10709,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>238.34</v>
+        <v>241.7</v>
       </c>
       <c r="F5" t="n">
-        <v>2563849584640</v>
+        <v>2599993475072</v>
       </c>
       <c r="G5" t="n">
-        <v>7.53</v>
+        <v>7.64</v>
       </c>
       <c r="H5" t="n">
         <v>9.88054</v>
       </c>
       <c r="I5" t="n">
-        <v>31.652058</v>
+        <v>31.636126</v>
       </c>
       <c r="J5" t="n">
-        <v>24.122164</v>
+        <v>24.462225</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.451713</v>
+        <v>3.5003736</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03159352185952841</v>
+        <v>0.03160943318163012</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04145565159016531</v>
+        <v>0.0408793545717832</v>
       </c>
       <c r="O5" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.002264350584212135</v>
+        <v>-0.00284064760259424</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -10245,51 +10767,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>289.36</v>
+        <v>294.38</v>
       </c>
       <c r="F6" t="n">
-        <v>4249933053952</v>
+        <v>4323663937536</v>
       </c>
       <c r="G6" t="n">
-        <v>8.25</v>
+        <v>8.27</v>
       </c>
       <c r="H6" t="n">
         <v>9.608919999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>35.073936</v>
+        <v>35.59613</v>
       </c>
       <c r="J6" t="n">
-        <v>30.113684</v>
+        <v>30.636118</v>
       </c>
       <c r="K6" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="L6" t="n">
-        <v>9.414128</v>
+        <v>9.577451999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02851119712468897</v>
+        <v>0.02809294109654189</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03320749239701409</v>
+        <v>0.03264121203886133</v>
       </c>
       <c r="O6" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01051250977736335</v>
+        <v>-0.01107879013551611</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -10303,10 +10825,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>200.09</v>
+        <v>197.58</v>
       </c>
       <c r="F7" t="n">
-        <v>4846379859968</v>
+        <v>4785584996352</v>
       </c>
       <c r="G7" t="n">
         <v>6.52</v>
@@ -10315,39 +10837,39 @@
         <v>12.76443</v>
       </c>
       <c r="I7" t="n">
-        <v>30.68865</v>
+        <v>30.30368</v>
       </c>
       <c r="J7" t="n">
-        <v>15.675591</v>
+        <v>15.478952</v>
       </c>
       <c r="K7" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="L7" t="n">
-        <v>19.118547</v>
+        <v>18.878717</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03258533659853066</v>
+        <v>0.03299929142625772</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0637934429506722</v>
+        <v>0.06460385666565442</v>
       </c>
       <c r="O7" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02007344077629476</v>
+        <v>0.02088385449127698</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10361,51 +10883,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>580.91</v>
+        <v>540.88</v>
       </c>
       <c r="F8" t="n">
-        <v>947232112640</v>
+        <v>881959239680</v>
       </c>
       <c r="G8" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="H8" t="n">
         <v>13.17704</v>
       </c>
       <c r="I8" t="n">
-        <v>192.3543</v>
+        <v>182.11447</v>
       </c>
       <c r="J8" t="n">
-        <v>44.08501</v>
+        <v>41.047153</v>
       </c>
       <c r="K8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="L8" t="n">
-        <v>25.290546</v>
+        <v>23.547798</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005198739908075262</v>
+        <v>0.005491051619582903</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02268344493983578</v>
+        <v>0.02436222452299956</v>
       </c>
       <c r="O8" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02103655723454167</v>
+        <v>-0.01935777765137789</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10419,51 +10941,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>377.75</v>
+        <v>369.34</v>
       </c>
       <c r="F9" t="n">
-        <v>1797175902208</v>
+        <v>1757164732416</v>
       </c>
       <c r="G9" t="n">
-        <v>6.01</v>
+        <v>6.02</v>
       </c>
       <c r="H9" t="n">
         <v>19.39578</v>
       </c>
       <c r="I9" t="n">
-        <v>62.853577</v>
+        <v>61.352158</v>
       </c>
       <c r="J9" t="n">
-        <v>19.475885</v>
+        <v>19.042286</v>
       </c>
       <c r="K9" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>23.814695</v>
+        <v>23.2845</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01590999338186631</v>
+        <v>0.01629934477717009</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05134554599602911</v>
+        <v>0.05251470190068772</v>
       </c>
       <c r="O9" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P9" t="n">
-        <v>0.007625543821651669</v>
+        <v>0.008794699726310272</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -10477,10 +10999,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71.40000000000001</v>
+        <v>74.19</v>
       </c>
       <c r="F10" t="n">
-        <v>300651020288</v>
+        <v>312399167488</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -10489,28 +11011,28 @@
         <v>3.84241</v>
       </c>
       <c r="I10" t="n">
-        <v>23.032259</v>
+        <v>23.93226</v>
       </c>
       <c r="J10" t="n">
-        <v>18.582088</v>
+        <v>19.308195</v>
       </c>
       <c r="K10" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="L10" t="n">
-        <v>6.4118376</v>
+        <v>6.6623845</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04341736694677871</v>
+        <v>0.0417846070899043</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05381526610644258</v>
+        <v>0.05179148133171587</v>
       </c>
       <c r="O10" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01009526393206513</v>
+        <v>0.008071479157338426</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P172"/>
+  <dimension ref="A1:P181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9941,16 +9941,16 @@
         <v>9.577451999999999</v>
       </c>
       <c r="M164" t="n">
-        <v>0.02809294109654189</v>
+        <v>0.0280929410965418</v>
       </c>
       <c r="N164" t="n">
-        <v>0.03264121203886133</v>
+        <v>0.0326412120388613</v>
       </c>
       <c r="O164" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P164" t="n">
-        <v>-0.01107879013551611</v>
+        <v>-0.0110787901355161</v>
       </c>
     </row>
     <row r="165">
@@ -9999,16 +9999,16 @@
         <v>23.547798</v>
       </c>
       <c r="M165" t="n">
-        <v>0.005491051619582903</v>
+        <v>0.0054910516195829</v>
       </c>
       <c r="N165" t="n">
-        <v>0.02436222452299956</v>
+        <v>0.0243622245229995</v>
       </c>
       <c r="O165" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P165" t="n">
-        <v>-0.01935777765137789</v>
+        <v>-0.0193577776513778</v>
       </c>
     </row>
     <row r="166">
@@ -10057,16 +10057,16 @@
         <v>3.5003736</v>
       </c>
       <c r="M166" t="n">
-        <v>0.03160943318163012</v>
+        <v>0.0316094331816301</v>
       </c>
       <c r="N166" t="n">
         <v>0.0408793545717832</v>
       </c>
       <c r="O166" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P166" t="n">
-        <v>-0.00284064760259424</v>
+        <v>-0.0028406476025942</v>
       </c>
     </row>
     <row r="167">
@@ -10115,16 +10115,16 @@
         <v>23.2845</v>
       </c>
       <c r="M167" t="n">
-        <v>0.01629934477717009</v>
+        <v>0.01629934477717</v>
       </c>
       <c r="N167" t="n">
-        <v>0.05251470190068772</v>
+        <v>0.0525147019006877</v>
       </c>
       <c r="O167" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P167" t="n">
-        <v>0.008794699726310272</v>
+        <v>0.008794699726310201</v>
       </c>
     </row>
     <row r="168">
@@ -10173,16 +10173,16 @@
         <v>10.336567</v>
       </c>
       <c r="M168" t="n">
-        <v>0.03660342563357456</v>
+        <v>0.0366034256335745</v>
       </c>
       <c r="N168" t="n">
-        <v>0.0407149124032524</v>
+        <v>0.0407149124032523</v>
       </c>
       <c r="O168" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P168" t="n">
-        <v>-0.003005089771125048</v>
+        <v>-0.003005089771125</v>
       </c>
     </row>
     <row r="169">
@@ -10231,16 +10231,16 @@
         <v>7.2376404</v>
       </c>
       <c r="M169" t="n">
-        <v>0.04490055636227179</v>
+        <v>0.0449005563622717</v>
       </c>
       <c r="N169" t="n">
-        <v>0.05913749163825031</v>
+        <v>0.0591374916382503</v>
       </c>
       <c r="O169" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P169" t="n">
-        <v>0.01541748946387287</v>
+        <v>0.0154174894638728</v>
       </c>
     </row>
     <row r="170">
@@ -10289,16 +10289,16 @@
         <v>8.969027000000001</v>
       </c>
       <c r="M170" t="n">
-        <v>0.04369209951077339</v>
+        <v>0.0436920995107733</v>
       </c>
       <c r="N170" t="n">
         <v>0.0504029353596336</v>
       </c>
       <c r="O170" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P170" t="n">
-        <v>0.00668293318525616</v>
+        <v>0.0066829331852561</v>
       </c>
     </row>
     <row r="171">
@@ -10350,13 +10350,13 @@
         <v>0.0417846070899043</v>
       </c>
       <c r="N171" t="n">
-        <v>0.05179148133171587</v>
+        <v>0.0517914813317158</v>
       </c>
       <c r="O171" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P171" t="n">
-        <v>0.008071479157338426</v>
+        <v>0.0080714791573384</v>
       </c>
     </row>
     <row r="172">
@@ -10405,16 +10405,538 @@
         <v>18.878717</v>
       </c>
       <c r="M172" t="n">
-        <v>0.03299929142625772</v>
+        <v>0.0329992914262577</v>
       </c>
       <c r="N172" t="n">
-        <v>0.06460385666565442</v>
+        <v>0.06460385666565439</v>
       </c>
       <c r="O172" t="n">
+        <v>0.0437200021743774</v>
+      </c>
+      <c r="P172" t="n">
+        <v>0.0208838544912769</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>308.63</v>
+      </c>
+      <c r="F173" t="n">
+        <v>4532958920704</v>
+      </c>
+      <c r="G173" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="H173" t="n">
+        <v>9.608919999999999</v>
+      </c>
+      <c r="I173" t="n">
+        <v>37.319225</v>
+      </c>
+      <c r="J173" t="n">
+        <v>32.119114</v>
+      </c>
+      <c r="K173" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="L173" t="n">
+        <v>10.041065</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0.02679583967857953</v>
+      </c>
+      <c r="N173" t="n">
+        <v>0.03113410880342157</v>
+      </c>
+      <c r="O173" t="n">
         <v>0.04372000217437744</v>
       </c>
-      <c r="P172" t="n">
-        <v>0.02088385449127698</v>
+      <c r="P173" t="n">
+        <v>-0.01258589337095587</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>517.8200000000001</v>
+      </c>
+      <c r="F174" t="n">
+        <v>844357632000</v>
+      </c>
+      <c r="G174" t="n">
+        <v>3</v>
+      </c>
+      <c r="H174" t="n">
+        <v>13.17704</v>
+      </c>
+      <c r="I174" t="n">
+        <v>172.60667</v>
+      </c>
+      <c r="J174" t="n">
+        <v>39.297142</v>
+      </c>
+      <c r="K174" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L174" t="n">
+        <v>22.543858</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0.005793518983430535</v>
+      </c>
+      <c r="N174" t="n">
+        <v>0.02544714379514117</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P174" t="n">
+        <v>-0.01827285837923628</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>242.67</v>
+      </c>
+      <c r="F175" t="n">
+        <v>2610427854848</v>
+      </c>
+      <c r="G175" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="H175" t="n">
+        <v>9.902509999999999</v>
+      </c>
+      <c r="I175" t="n">
+        <v>31.638851</v>
+      </c>
+      <c r="J175" t="n">
+        <v>24.505909</v>
+      </c>
+      <c r="K175" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L175" t="n">
+        <v>3.5144215</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0.03160670869905633</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0.04080648617464046</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P175" t="n">
+        <v>-0.002913515999736986</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>360.45</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1714869895168</v>
+      </c>
+      <c r="G176" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H176" t="n">
+        <v>19.39578</v>
+      </c>
+      <c r="I176" t="n">
+        <v>59.875416</v>
+      </c>
+      <c r="J176" t="n">
+        <v>18.583939</v>
+      </c>
+      <c r="K176" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L176" t="n">
+        <v>22.724043</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0.01670134554029685</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0.05380990428630878</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P176" t="n">
+        <v>0.01008990211193134</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="F177" t="n">
+        <v>4346312392704</v>
+      </c>
+      <c r="G177" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="H177" t="n">
+        <v>14.55771</v>
+      </c>
+      <c r="I177" t="n">
+        <v>27.168573</v>
+      </c>
+      <c r="J177" t="n">
+        <v>24.46676</v>
+      </c>
+      <c r="K177" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L177" t="n">
+        <v>10.287178</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0.03680723229827615</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0.04087177831433545</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P177" t="n">
+        <v>-0.002848223860041993</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>582.9</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1479647035392</v>
+      </c>
+      <c r="G178" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="H178" t="n">
+        <v>36.82768</v>
+      </c>
+      <c r="I178" t="n">
+        <v>21.18866</v>
+      </c>
+      <c r="J178" t="n">
+        <v>15.82777</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L178" t="n">
+        <v>6.883264</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0.0471950591868245</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0.06318009950248757</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0.01946009732811012</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>390.49</v>
+      </c>
+      <c r="F179" t="n">
+        <v>2900729528320</v>
+      </c>
+      <c r="G179" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="H179" t="n">
+        <v>19.36884</v>
+      </c>
+      <c r="I179" t="n">
+        <v>23.257294</v>
+      </c>
+      <c r="J179" t="n">
+        <v>20.160732</v>
+      </c>
+      <c r="K179" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L179" t="n">
+        <v>9.113967000000001</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0.0429972598530052</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0.04960137263438244</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0.005881370460004996</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="F180" t="n">
+        <v>326968508416</v>
+      </c>
+      <c r="G180" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H180" t="n">
+        <v>3.84155</v>
+      </c>
+      <c r="I180" t="n">
+        <v>25.048388</v>
+      </c>
+      <c r="J180" t="n">
+        <v>20.213196</v>
+      </c>
+      <c r="K180" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L180" t="n">
+        <v>6.973098</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0.03992273019961365</v>
+      </c>
+      <c r="N180" t="n">
+        <v>0.04947263361236316</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P180" t="n">
+        <v>0.005752631437985718</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>194.83</v>
+      </c>
+      <c r="F181" t="n">
+        <v>4718977351680</v>
+      </c>
+      <c r="G181" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H181" t="n">
+        <v>12.76443</v>
+      </c>
+      <c r="I181" t="n">
+        <v>29.83614</v>
+      </c>
+      <c r="J181" t="n">
+        <v>15.26351</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L181" t="n">
+        <v>18.615955</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0.03351639891187189</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0.06551573166350151</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0.02179572948912407</v>
       </c>
     </row>
   </sheetData>
@@ -10516,12 +11038,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -10535,51 +11057,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>357.89</v>
+        <v>356.18</v>
       </c>
       <c r="F2" t="n">
-        <v>4367179055104</v>
+        <v>4346312392704</v>
       </c>
       <c r="G2" t="n">
-        <v>13.1</v>
+        <v>13.11</v>
       </c>
       <c r="H2" t="n">
-        <v>14.57146</v>
+        <v>14.55771</v>
       </c>
       <c r="I2" t="n">
-        <v>27.319847</v>
+        <v>27.168573</v>
       </c>
       <c r="J2" t="n">
-        <v>24.561028</v>
+        <v>24.46676</v>
       </c>
       <c r="K2" t="n">
         <v>1.39</v>
       </c>
       <c r="L2" t="n">
-        <v>10.336567</v>
+        <v>10.287178</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03660342563357456</v>
+        <v>0.03680723229827615</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0407149124032524</v>
+        <v>0.04087177831433545</v>
       </c>
       <c r="O2" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003005089771125048</v>
+        <v>-0.002848223860041993</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -10593,10 +11115,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>384.28</v>
+        <v>390.49</v>
       </c>
       <c r="F3" t="n">
-        <v>2854599000064</v>
+        <v>2900729528320</v>
       </c>
       <c r="G3" t="n">
         <v>16.79</v>
@@ -10605,39 +11127,39 @@
         <v>19.36884</v>
       </c>
       <c r="I3" t="n">
-        <v>22.887432</v>
+        <v>23.257294</v>
       </c>
       <c r="J3" t="n">
-        <v>19.840115</v>
+        <v>20.160732</v>
       </c>
       <c r="K3" t="n">
         <v>1.15</v>
       </c>
       <c r="L3" t="n">
-        <v>8.969027000000001</v>
+        <v>9.113967000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04369209951077339</v>
+        <v>0.0429972598530052</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0504029353596336</v>
+        <v>0.04960137263438244</v>
       </c>
       <c r="O3" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00668293318525616</v>
+        <v>0.005881370460004996</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -10651,51 +11173,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>612.91</v>
+        <v>582.9</v>
       </c>
       <c r="F4" t="n">
-        <v>1555824902144</v>
+        <v>1479647035392</v>
       </c>
       <c r="G4" t="n">
-        <v>27.52</v>
+        <v>27.51</v>
       </c>
       <c r="H4" t="n">
-        <v>36.24596</v>
+        <v>36.82768</v>
       </c>
       <c r="I4" t="n">
-        <v>22.271437</v>
+        <v>21.18866</v>
       </c>
       <c r="J4" t="n">
-        <v>16.909746</v>
+        <v>15.82777</v>
       </c>
       <c r="K4" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>7.2376404</v>
+        <v>6.883264</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04490055636227179</v>
+        <v>0.0471950591868245</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05913749163825031</v>
+        <v>0.06318009950248757</v>
       </c>
       <c r="O4" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01541748946387287</v>
+        <v>0.01946009732811012</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -10709,51 +11231,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>241.7</v>
+        <v>242.67</v>
       </c>
       <c r="F5" t="n">
-        <v>2599993475072</v>
+        <v>2610427854848</v>
       </c>
       <c r="G5" t="n">
-        <v>7.64</v>
+        <v>7.67</v>
       </c>
       <c r="H5" t="n">
-        <v>9.88054</v>
+        <v>9.902509999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>31.636126</v>
+        <v>31.638851</v>
       </c>
       <c r="J5" t="n">
-        <v>24.462225</v>
+        <v>24.505909</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5003736</v>
+        <v>3.5144215</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03160943318163012</v>
+        <v>0.03160670869905633</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0408793545717832</v>
+        <v>0.04080648617464046</v>
       </c>
       <c r="O5" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.00284064760259424</v>
+        <v>-0.002913515999736986</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -10767,10 +11289,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>294.38</v>
+        <v>308.63</v>
       </c>
       <c r="F6" t="n">
-        <v>4323663937536</v>
+        <v>4532958920704</v>
       </c>
       <c r="G6" t="n">
         <v>8.27</v>
@@ -10779,39 +11301,39 @@
         <v>9.608919999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>35.59613</v>
+        <v>37.319225</v>
       </c>
       <c r="J6" t="n">
-        <v>30.636118</v>
+        <v>32.119114</v>
       </c>
       <c r="K6" t="n">
         <v>2.34</v>
       </c>
       <c r="L6" t="n">
-        <v>9.577451999999999</v>
+        <v>10.041065</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02809294109654189</v>
+        <v>0.02679583967857953</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03264121203886133</v>
+        <v>0.03113410880342157</v>
       </c>
       <c r="O6" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01107879013551611</v>
+        <v>-0.01258589337095587</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -10825,51 +11347,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>197.58</v>
+        <v>194.83</v>
       </c>
       <c r="F7" t="n">
-        <v>4785584996352</v>
+        <v>4718977351680</v>
       </c>
       <c r="G7" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="H7" t="n">
         <v>12.76443</v>
       </c>
       <c r="I7" t="n">
-        <v>30.30368</v>
+        <v>29.83614</v>
       </c>
       <c r="J7" t="n">
-        <v>15.478952</v>
+        <v>15.26351</v>
       </c>
       <c r="K7" t="n">
         <v>0.61</v>
       </c>
       <c r="L7" t="n">
-        <v>18.878717</v>
+        <v>18.615955</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03299929142625772</v>
+        <v>0.03351639891187189</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06460385666565442</v>
+        <v>0.06551573166350151</v>
       </c>
       <c r="O7" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02088385449127698</v>
+        <v>0.02179572948912407</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10883,51 +11405,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>540.88</v>
+        <v>517.8200000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>881959239680</v>
+        <v>844357632000</v>
       </c>
       <c r="G8" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>13.17704</v>
       </c>
       <c r="I8" t="n">
-        <v>182.11447</v>
+        <v>172.60667</v>
       </c>
       <c r="J8" t="n">
-        <v>41.047153</v>
+        <v>39.297142</v>
       </c>
       <c r="K8" t="n">
         <v>1.3</v>
       </c>
       <c r="L8" t="n">
-        <v>23.547798</v>
+        <v>22.543858</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005491051619582903</v>
+        <v>0.005793518983430535</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02436222452299956</v>
+        <v>0.02544714379514117</v>
       </c>
       <c r="O8" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01935777765137789</v>
+        <v>-0.01827285837923628</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10941,10 +11463,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>369.34</v>
+        <v>360.45</v>
       </c>
       <c r="F9" t="n">
-        <v>1757164732416</v>
+        <v>1714869895168</v>
       </c>
       <c r="G9" t="n">
         <v>6.02</v>
@@ -10953,39 +11475,39 @@
         <v>19.39578</v>
       </c>
       <c r="I9" t="n">
-        <v>61.352158</v>
+        <v>59.875416</v>
       </c>
       <c r="J9" t="n">
-        <v>19.042286</v>
+        <v>18.583939</v>
       </c>
       <c r="K9" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>23.2845</v>
+        <v>22.724043</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01629934477717009</v>
+        <v>0.01670134554029685</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05251470190068772</v>
+        <v>0.05380990428630878</v>
       </c>
       <c r="O9" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P9" t="n">
-        <v>0.008794699726310272</v>
+        <v>0.01008990211193134</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -10999,40 +11521,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>74.19</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>312399167488</v>
+        <v>326968508416</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.84241</v>
+        <v>3.84155</v>
       </c>
       <c r="I10" t="n">
-        <v>23.93226</v>
+        <v>25.048388</v>
       </c>
       <c r="J10" t="n">
-        <v>19.308195</v>
+        <v>20.213196</v>
       </c>
       <c r="K10" t="n">
         <v>1.4</v>
       </c>
       <c r="L10" t="n">
-        <v>6.6623845</v>
+        <v>6.973098</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0417846070899043</v>
+        <v>0.03992273019961365</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05179148133171587</v>
+        <v>0.04947263361236316</v>
       </c>
       <c r="O10" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P10" t="n">
-        <v>0.008071479157338426</v>
+        <v>0.005752631437985718</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P181"/>
+  <dimension ref="A1:P190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10463,16 +10463,16 @@
         <v>10.041065</v>
       </c>
       <c r="M173" t="n">
-        <v>0.02679583967857953</v>
+        <v>0.0267958396785795</v>
       </c>
       <c r="N173" t="n">
-        <v>0.03113410880342157</v>
+        <v>0.0311341088034215</v>
       </c>
       <c r="O173" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P173" t="n">
-        <v>-0.01258589337095587</v>
+        <v>-0.0125858933709558</v>
       </c>
     </row>
     <row r="174">
@@ -10521,16 +10521,16 @@
         <v>22.543858</v>
       </c>
       <c r="M174" t="n">
-        <v>0.005793518983430535</v>
+        <v>0.0057935189834305</v>
       </c>
       <c r="N174" t="n">
-        <v>0.02544714379514117</v>
+        <v>0.0254471437951411</v>
       </c>
       <c r="O174" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P174" t="n">
-        <v>-0.01827285837923628</v>
+        <v>-0.0182728583792362</v>
       </c>
     </row>
     <row r="175">
@@ -10579,16 +10579,16 @@
         <v>3.5144215</v>
       </c>
       <c r="M175" t="n">
-        <v>0.03160670869905633</v>
+        <v>0.0316067086990563</v>
       </c>
       <c r="N175" t="n">
-        <v>0.04080648617464046</v>
+        <v>0.0408064861746404</v>
       </c>
       <c r="O175" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P175" t="n">
-        <v>-0.002913515999736986</v>
+        <v>-0.0029135159997369</v>
       </c>
     </row>
     <row r="176">
@@ -10637,16 +10637,16 @@
         <v>22.724043</v>
       </c>
       <c r="M176" t="n">
-        <v>0.01670134554029685</v>
+        <v>0.0167013455402968</v>
       </c>
       <c r="N176" t="n">
-        <v>0.05380990428630878</v>
+        <v>0.0538099042863087</v>
       </c>
       <c r="O176" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P176" t="n">
-        <v>0.01008990211193134</v>
+        <v>0.0100899021119313</v>
       </c>
     </row>
     <row r="177">
@@ -10695,16 +10695,16 @@
         <v>10.287178</v>
       </c>
       <c r="M177" t="n">
-        <v>0.03680723229827615</v>
+        <v>0.0368072322982761</v>
       </c>
       <c r="N177" t="n">
-        <v>0.04087177831433545</v>
+        <v>0.0408717783143354</v>
       </c>
       <c r="O177" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P177" t="n">
-        <v>-0.002848223860041993</v>
+        <v>-0.0028482238600419</v>
       </c>
     </row>
     <row r="178">
@@ -10756,13 +10756,13 @@
         <v>0.0471950591868245</v>
       </c>
       <c r="N178" t="n">
-        <v>0.06318009950248757</v>
+        <v>0.0631800995024875</v>
       </c>
       <c r="O178" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P178" t="n">
-        <v>0.01946009732811012</v>
+        <v>0.0194600973281101</v>
       </c>
     </row>
     <row r="179">
@@ -10814,13 +10814,13 @@
         <v>0.0429972598530052</v>
       </c>
       <c r="N179" t="n">
-        <v>0.04960137263438244</v>
+        <v>0.0496013726343824</v>
       </c>
       <c r="O179" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P179" t="n">
-        <v>0.005881370460004996</v>
+        <v>0.0058813704600049</v>
       </c>
     </row>
     <row r="180">
@@ -10869,16 +10869,16 @@
         <v>6.973098</v>
       </c>
       <c r="M180" t="n">
-        <v>0.03992273019961365</v>
+        <v>0.0399227301996136</v>
       </c>
       <c r="N180" t="n">
-        <v>0.04947263361236316</v>
+        <v>0.0494726336123631</v>
       </c>
       <c r="O180" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P180" t="n">
-        <v>0.005752631437985718</v>
+        <v>0.0057526314379857</v>
       </c>
     </row>
     <row r="181">
@@ -10927,15 +10927,537 @@
         <v>18.615955</v>
       </c>
       <c r="M181" t="n">
+        <v>0.0335163989118718</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0.0655157316635015</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0.0437200021743774</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0.021795729489124</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>308.63</v>
+      </c>
+      <c r="F182" t="n">
+        <v>4532958920704</v>
+      </c>
+      <c r="G182" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="H182" t="n">
+        <v>9.608919999999999</v>
+      </c>
+      <c r="I182" t="n">
+        <v>37.319225</v>
+      </c>
+      <c r="J182" t="n">
+        <v>32.119114</v>
+      </c>
+      <c r="K182" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L182" t="n">
+        <v>10.041065</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0.02679583967857953</v>
+      </c>
+      <c r="N182" t="n">
+        <v>0.03113410880342157</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P182" t="n">
+        <v>-0.01258589337095587</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>517.8200000000001</v>
+      </c>
+      <c r="F183" t="n">
+        <v>844357632000</v>
+      </c>
+      <c r="G183" t="n">
+        <v>3</v>
+      </c>
+      <c r="H183" t="n">
+        <v>13.17704</v>
+      </c>
+      <c r="I183" t="n">
+        <v>172.60667</v>
+      </c>
+      <c r="J183" t="n">
+        <v>39.297142</v>
+      </c>
+      <c r="K183" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L183" t="n">
+        <v>22.543858</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0.005793518983430535</v>
+      </c>
+      <c r="N183" t="n">
+        <v>0.02544714379514117</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P183" t="n">
+        <v>-0.01827285837923628</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>242.67</v>
+      </c>
+      <c r="F184" t="n">
+        <v>2610427854848</v>
+      </c>
+      <c r="G184" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="H184" t="n">
+        <v>9.902509999999999</v>
+      </c>
+      <c r="I184" t="n">
+        <v>31.638851</v>
+      </c>
+      <c r="J184" t="n">
+        <v>24.505909</v>
+      </c>
+      <c r="K184" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L184" t="n">
+        <v>3.5144215</v>
+      </c>
+      <c r="M184" t="n">
+        <v>0.03160670869905633</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0.04080648617464046</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P184" t="n">
+        <v>-0.002913515999736986</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>360.45</v>
+      </c>
+      <c r="F185" t="n">
+        <v>1714869895168</v>
+      </c>
+      <c r="G185" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H185" t="n">
+        <v>19.39578</v>
+      </c>
+      <c r="I185" t="n">
+        <v>59.875416</v>
+      </c>
+      <c r="J185" t="n">
+        <v>18.583939</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L185" t="n">
+        <v>22.724043</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0.01670134554029685</v>
+      </c>
+      <c r="N185" t="n">
+        <v>0.05380990428630878</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P185" t="n">
+        <v>0.01008990211193134</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="F186" t="n">
+        <v>4346312392704</v>
+      </c>
+      <c r="G186" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="H186" t="n">
+        <v>14.55771</v>
+      </c>
+      <c r="I186" t="n">
+        <v>27.168573</v>
+      </c>
+      <c r="J186" t="n">
+        <v>24.46676</v>
+      </c>
+      <c r="K186" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L186" t="n">
+        <v>10.287178</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0.03680723229827615</v>
+      </c>
+      <c r="N186" t="n">
+        <v>0.04087177831433545</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P186" t="n">
+        <v>-0.002848223860041993</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>582.9</v>
+      </c>
+      <c r="F187" t="n">
+        <v>1479647035392</v>
+      </c>
+      <c r="G187" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="H187" t="n">
+        <v>36.82768</v>
+      </c>
+      <c r="I187" t="n">
+        <v>21.18866</v>
+      </c>
+      <c r="J187" t="n">
+        <v>15.82777</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L187" t="n">
+        <v>6.883264</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0.0471950591868245</v>
+      </c>
+      <c r="N187" t="n">
+        <v>0.06318009950248757</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P187" t="n">
+        <v>0.01946009732811012</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>390.49</v>
+      </c>
+      <c r="F188" t="n">
+        <v>2900729528320</v>
+      </c>
+      <c r="G188" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="H188" t="n">
+        <v>19.36884</v>
+      </c>
+      <c r="I188" t="n">
+        <v>23.257294</v>
+      </c>
+      <c r="J188" t="n">
+        <v>20.160732</v>
+      </c>
+      <c r="K188" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L188" t="n">
+        <v>9.113967000000001</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0.0429972598530052</v>
+      </c>
+      <c r="N188" t="n">
+        <v>0.04960137263438244</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P188" t="n">
+        <v>0.005881370460004996</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="F189" t="n">
+        <v>326968508416</v>
+      </c>
+      <c r="G189" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H189" t="n">
+        <v>3.84473</v>
+      </c>
+      <c r="I189" t="n">
+        <v>25.048388</v>
+      </c>
+      <c r="J189" t="n">
+        <v>20.196478</v>
+      </c>
+      <c r="K189" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L189" t="n">
+        <v>6.973098</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0.03992273019961365</v>
+      </c>
+      <c r="N189" t="n">
+        <v>0.04951358660656793</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0.04372000217437744</v>
+      </c>
+      <c r="P189" t="n">
+        <v>0.005793584432190489</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>194.83</v>
+      </c>
+      <c r="F190" t="n">
+        <v>4718977351680</v>
+      </c>
+      <c r="G190" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H190" t="n">
+        <v>12.76443</v>
+      </c>
+      <c r="I190" t="n">
+        <v>29.83614</v>
+      </c>
+      <c r="J190" t="n">
+        <v>15.26351</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L190" t="n">
+        <v>18.615955</v>
+      </c>
+      <c r="M190" t="n">
         <v>0.03351639891187189</v>
       </c>
-      <c r="N181" t="n">
+      <c r="N190" t="n">
         <v>0.06551573166350151</v>
       </c>
-      <c r="O181" t="n">
+      <c r="O190" t="n">
         <v>0.04372000217437744</v>
       </c>
-      <c r="P181" t="n">
+      <c r="P190" t="n">
         <v>0.02179572948912407</v>
       </c>
     </row>
@@ -11038,12 +11560,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -11075,7 +11597,7 @@
         <v>24.46676</v>
       </c>
       <c r="K2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="L2" t="n">
         <v>10.287178</v>
@@ -11096,12 +11618,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -11133,7 +11655,7 @@
         <v>20.160732</v>
       </c>
       <c r="K3" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="L3" t="n">
         <v>9.113967000000001</v>
@@ -11154,12 +11676,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -11191,7 +11713,7 @@
         <v>15.82777</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="L4" t="n">
         <v>6.883264</v>
@@ -11212,12 +11734,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -11270,12 +11792,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -11307,7 +11829,7 @@
         <v>32.119114</v>
       </c>
       <c r="K6" t="n">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="L6" t="n">
         <v>10.041065</v>
@@ -11328,12 +11850,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -11365,7 +11887,7 @@
         <v>15.26351</v>
       </c>
       <c r="K7" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="L7" t="n">
         <v>18.615955</v>
@@ -11386,12 +11908,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -11423,7 +11945,7 @@
         <v>39.297142</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="L8" t="n">
         <v>22.543858</v>
@@ -11444,12 +11966,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -11481,7 +12003,7 @@
         <v>18.583939</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="L9" t="n">
         <v>22.724043</v>
@@ -11502,12 +12024,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -11530,16 +12052,16 @@
         <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.84155</v>
+        <v>3.84473</v>
       </c>
       <c r="I10" t="n">
         <v>25.048388</v>
       </c>
       <c r="J10" t="n">
-        <v>20.213196</v>
+        <v>20.196478</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="L10" t="n">
         <v>6.973098</v>
@@ -11548,13 +12070,13 @@
         <v>0.03992273019961365</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04947263361236316</v>
+        <v>0.04951358660656793</v>
       </c>
       <c r="O10" t="n">
         <v>0.04372000217437744</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005752631437985718</v>
+        <v>0.005793584432190489</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P190"/>
+  <dimension ref="A1:P199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10985,16 +10985,16 @@
         <v>10.041065</v>
       </c>
       <c r="M182" t="n">
-        <v>0.02679583967857953</v>
+        <v>0.0267958396785795</v>
       </c>
       <c r="N182" t="n">
-        <v>0.03113410880342157</v>
+        <v>0.0311341088034215</v>
       </c>
       <c r="O182" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P182" t="n">
-        <v>-0.01258589337095587</v>
+        <v>-0.0125858933709558</v>
       </c>
     </row>
     <row r="183">
@@ -11043,16 +11043,16 @@
         <v>22.543858</v>
       </c>
       <c r="M183" t="n">
-        <v>0.005793518983430535</v>
+        <v>0.0057935189834305</v>
       </c>
       <c r="N183" t="n">
-        <v>0.02544714379514117</v>
+        <v>0.0254471437951411</v>
       </c>
       <c r="O183" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P183" t="n">
-        <v>-0.01827285837923628</v>
+        <v>-0.0182728583792362</v>
       </c>
     </row>
     <row r="184">
@@ -11101,16 +11101,16 @@
         <v>3.5144215</v>
       </c>
       <c r="M184" t="n">
-        <v>0.03160670869905633</v>
+        <v>0.0316067086990563</v>
       </c>
       <c r="N184" t="n">
-        <v>0.04080648617464046</v>
+        <v>0.0408064861746404</v>
       </c>
       <c r="O184" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P184" t="n">
-        <v>-0.002913515999736986</v>
+        <v>-0.0029135159997369</v>
       </c>
     </row>
     <row r="185">
@@ -11159,16 +11159,16 @@
         <v>22.724043</v>
       </c>
       <c r="M185" t="n">
-        <v>0.01670134554029685</v>
+        <v>0.0167013455402968</v>
       </c>
       <c r="N185" t="n">
-        <v>0.05380990428630878</v>
+        <v>0.0538099042863087</v>
       </c>
       <c r="O185" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P185" t="n">
-        <v>0.01008990211193134</v>
+        <v>0.0100899021119313</v>
       </c>
     </row>
     <row r="186">
@@ -11217,16 +11217,16 @@
         <v>10.287178</v>
       </c>
       <c r="M186" t="n">
-        <v>0.03680723229827615</v>
+        <v>0.0368072322982761</v>
       </c>
       <c r="N186" t="n">
-        <v>0.04087177831433545</v>
+        <v>0.0408717783143354</v>
       </c>
       <c r="O186" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P186" t="n">
-        <v>-0.002848223860041993</v>
+        <v>-0.0028482238600419</v>
       </c>
     </row>
     <row r="187">
@@ -11278,13 +11278,13 @@
         <v>0.0471950591868245</v>
       </c>
       <c r="N187" t="n">
-        <v>0.06318009950248757</v>
+        <v>0.0631800995024875</v>
       </c>
       <c r="O187" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P187" t="n">
-        <v>0.01946009732811012</v>
+        <v>0.0194600973281101</v>
       </c>
     </row>
     <row r="188">
@@ -11336,13 +11336,13 @@
         <v>0.0429972598530052</v>
       </c>
       <c r="N188" t="n">
-        <v>0.04960137263438244</v>
+        <v>0.0496013726343824</v>
       </c>
       <c r="O188" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P188" t="n">
-        <v>0.005881370460004996</v>
+        <v>0.0058813704600049</v>
       </c>
     </row>
     <row r="189">
@@ -11391,16 +11391,16 @@
         <v>6.973098</v>
       </c>
       <c r="M189" t="n">
-        <v>0.03992273019961365</v>
+        <v>0.0399227301996136</v>
       </c>
       <c r="N189" t="n">
-        <v>0.04951358660656793</v>
+        <v>0.0495135866065679</v>
       </c>
       <c r="O189" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P189" t="n">
-        <v>0.005793584432190489</v>
+        <v>0.0057935844321904</v>
       </c>
     </row>
     <row r="190">
@@ -11449,16 +11449,538 @@
         <v>18.615955</v>
       </c>
       <c r="M190" t="n">
-        <v>0.03351639891187189</v>
+        <v>0.0335163989118718</v>
       </c>
       <c r="N190" t="n">
-        <v>0.06551573166350151</v>
+        <v>0.0655157316635015</v>
       </c>
       <c r="O190" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.0437200021743774</v>
       </c>
       <c r="P190" t="n">
-        <v>0.02179572948912407</v>
+        <v>0.021795729489124</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>312.66</v>
+      </c>
+      <c r="F191" t="n">
+        <v>4592148938752</v>
+      </c>
+      <c r="G191" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="H191" t="n">
+        <v>9.608919999999999</v>
+      </c>
+      <c r="I191" t="n">
+        <v>37.806526</v>
+      </c>
+      <c r="J191" t="n">
+        <v>32.538517</v>
+      </c>
+      <c r="K191" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L191" t="n">
+        <v>10.172179</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0.02645045736582869</v>
+      </c>
+      <c r="N191" t="n">
+        <v>0.03073280880189343</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0.04479000091552734</v>
+      </c>
+      <c r="P191" t="n">
+        <v>-0.01405719211363392</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>552.05</v>
+      </c>
+      <c r="F192" t="n">
+        <v>900173004800</v>
+      </c>
+      <c r="G192" t="n">
+        <v>3</v>
+      </c>
+      <c r="H192" t="n">
+        <v>13.19926</v>
+      </c>
+      <c r="I192" t="n">
+        <v>184.01666</v>
+      </c>
+      <c r="J192" t="n">
+        <v>41.824314</v>
+      </c>
+      <c r="K192" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L192" t="n">
+        <v>24.034096</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0.005434290372248891</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0.0239095371796033</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0.04479000091552734</v>
+      </c>
+      <c r="P192" t="n">
+        <v>-0.02088046373592405</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>244.16</v>
+      </c>
+      <c r="F193" t="n">
+        <v>2626455863296</v>
+      </c>
+      <c r="G193" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="H193" t="n">
+        <v>9.902509999999999</v>
+      </c>
+      <c r="I193" t="n">
+        <v>31.833117</v>
+      </c>
+      <c r="J193" t="n">
+        <v>24.656376</v>
+      </c>
+      <c r="K193" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L193" t="n">
+        <v>3.536</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0.03141382699868939</v>
+      </c>
+      <c r="N193" t="n">
+        <v>0.0405574623197903</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0.04479000091552734</v>
+      </c>
+      <c r="P193" t="n">
+        <v>-0.004232538595737044</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1778859245568</v>
+      </c>
+      <c r="G194" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H194" t="n">
+        <v>19.39578</v>
+      </c>
+      <c r="I194" t="n">
+        <v>62.109634</v>
+      </c>
+      <c r="J194" t="n">
+        <v>19.277388</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L194" t="n">
+        <v>23.571978</v>
+      </c>
+      <c r="M194" t="n">
+        <v>0.01610056164749933</v>
+      </c>
+      <c r="N194" t="n">
+        <v>0.0518742444503878</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0.04479000091552734</v>
+      </c>
+      <c r="P194" t="n">
+        <v>0.007084243534860458</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>364.9</v>
+      </c>
+      <c r="F195" t="n">
+        <v>4452718739456</v>
+      </c>
+      <c r="G195" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="H195" t="n">
+        <v>14.55771</v>
+      </c>
+      <c r="I195" t="n">
+        <v>27.833715</v>
+      </c>
+      <c r="J195" t="n">
+        <v>25.065756</v>
+      </c>
+      <c r="K195" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L195" t="n">
+        <v>10.539029</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0.03592765141134557</v>
+      </c>
+      <c r="N195" t="n">
+        <v>0.03989506714168266</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0.04479000091552734</v>
+      </c>
+      <c r="P195" t="n">
+        <v>-0.004894933773844687</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>600.29</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1523790118912</v>
+      </c>
+      <c r="G196" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="H196" t="n">
+        <v>36.82768</v>
+      </c>
+      <c r="I196" t="n">
+        <v>21.820791</v>
+      </c>
+      <c r="J196" t="n">
+        <v>16.299969</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L196" t="n">
+        <v>7.088616</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0.0458278498725616</v>
+      </c>
+      <c r="N196" t="n">
+        <v>0.06134981425644272</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0.04479000091552734</v>
+      </c>
+      <c r="P196" t="n">
+        <v>0.01655981334091538</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>386.74</v>
+      </c>
+      <c r="F197" t="n">
+        <v>2872872796160</v>
+      </c>
+      <c r="G197" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="H197" t="n">
+        <v>19.36162</v>
+      </c>
+      <c r="I197" t="n">
+        <v>23.033947</v>
+      </c>
+      <c r="J197" t="n">
+        <v>19.974567</v>
+      </c>
+      <c r="K197" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L197" t="n">
+        <v>9.026443</v>
+      </c>
+      <c r="M197" t="n">
+        <v>0.0434141800692972</v>
+      </c>
+      <c r="N197" t="n">
+        <v>0.05006366034028029</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0.04479000091552734</v>
+      </c>
+      <c r="P197" t="n">
+        <v>0.005273659424752941</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>76.02</v>
+      </c>
+      <c r="F198" t="n">
+        <v>320104890368</v>
+      </c>
+      <c r="G198" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H198" t="n">
+        <v>3.84473</v>
+      </c>
+      <c r="I198" t="n">
+        <v>24.522581</v>
+      </c>
+      <c r="J198" t="n">
+        <v>19.77252</v>
+      </c>
+      <c r="K198" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L198" t="n">
+        <v>6.8267207</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0.04077874243620101</v>
+      </c>
+      <c r="N198" t="n">
+        <v>0.05057524335701132</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0.04479000091552734</v>
+      </c>
+      <c r="P198" t="n">
+        <v>0.00578524244148397</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>195.55</v>
+      </c>
+      <c r="F199" t="n">
+        <v>4736416743424</v>
+      </c>
+      <c r="G199" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H199" t="n">
+        <v>12.76443</v>
+      </c>
+      <c r="I199" t="n">
+        <v>29.946402</v>
+      </c>
+      <c r="J199" t="n">
+        <v>15.319917</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L199" t="n">
+        <v>18.684753</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0.03339299411915111</v>
+      </c>
+      <c r="N199" t="n">
+        <v>0.065274507798517</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0.04479000091552734</v>
+      </c>
+      <c r="P199" t="n">
+        <v>0.02048450688298965</v>
       </c>
     </row>
   </sheetData>
@@ -11560,12 +12082,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -11579,10 +12101,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>356.18</v>
+        <v>364.9</v>
       </c>
       <c r="F2" t="n">
-        <v>4346312392704</v>
+        <v>4452718739456</v>
       </c>
       <c r="G2" t="n">
         <v>13.11</v>
@@ -11591,39 +12113,39 @@
         <v>14.55771</v>
       </c>
       <c r="I2" t="n">
-        <v>27.168573</v>
+        <v>27.833715</v>
       </c>
       <c r="J2" t="n">
-        <v>24.46676</v>
+        <v>25.065756</v>
       </c>
       <c r="K2" t="n">
         <v>1.4</v>
       </c>
       <c r="L2" t="n">
-        <v>10.287178</v>
+        <v>10.539029</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03680723229827615</v>
+        <v>0.03592765141134557</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04087177831433545</v>
+        <v>0.03989506714168266</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04479000091552734</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.002848223860041993</v>
+        <v>-0.004894933773844687</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -11637,51 +12159,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>390.49</v>
+        <v>386.74</v>
       </c>
       <c r="F3" t="n">
-        <v>2900729528320</v>
+        <v>2872872796160</v>
       </c>
       <c r="G3" t="n">
         <v>16.79</v>
       </c>
       <c r="H3" t="n">
-        <v>19.36884</v>
+        <v>19.36162</v>
       </c>
       <c r="I3" t="n">
-        <v>23.257294</v>
+        <v>23.033947</v>
       </c>
       <c r="J3" t="n">
-        <v>20.160732</v>
+        <v>19.974567</v>
       </c>
       <c r="K3" t="n">
         <v>1.2</v>
       </c>
       <c r="L3" t="n">
-        <v>9.113967000000001</v>
+        <v>9.026443</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0429972598530052</v>
+        <v>0.0434141800692972</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04960137263438244</v>
+        <v>0.05006366034028029</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04479000091552734</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005881370460004996</v>
+        <v>0.005273659424752941</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -11695,10 +12217,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>582.9</v>
+        <v>600.29</v>
       </c>
       <c r="F4" t="n">
-        <v>1479647035392</v>
+        <v>1523790118912</v>
       </c>
       <c r="G4" t="n">
         <v>27.51</v>
@@ -11707,39 +12229,39 @@
         <v>36.82768</v>
       </c>
       <c r="I4" t="n">
-        <v>21.18866</v>
+        <v>21.820791</v>
       </c>
       <c r="J4" t="n">
-        <v>15.82777</v>
+        <v>16.299969</v>
       </c>
       <c r="K4" t="n">
         <v>0.84</v>
       </c>
       <c r="L4" t="n">
-        <v>6.883264</v>
+        <v>7.088616</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0471950591868245</v>
+        <v>0.0458278498725616</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06318009950248757</v>
+        <v>0.06134981425644272</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04479000091552734</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01946009732811012</v>
+        <v>0.01655981334091538</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -11753,10 +12275,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>242.67</v>
+        <v>244.16</v>
       </c>
       <c r="F5" t="n">
-        <v>2610427854848</v>
+        <v>2626455863296</v>
       </c>
       <c r="G5" t="n">
         <v>7.67</v>
@@ -11765,39 +12287,39 @@
         <v>9.902509999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>31.638851</v>
+        <v>31.833117</v>
       </c>
       <c r="J5" t="n">
-        <v>24.505909</v>
+        <v>24.656376</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5144215</v>
+        <v>3.536</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03160670869905633</v>
+        <v>0.03141382699868939</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04080648617464046</v>
+        <v>0.0405574623197903</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04479000091552734</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.002913515999736986</v>
+        <v>-0.004232538595737044</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -11811,10 +12333,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308.63</v>
+        <v>312.66</v>
       </c>
       <c r="F6" t="n">
-        <v>4532958920704</v>
+        <v>4592148938752</v>
       </c>
       <c r="G6" t="n">
         <v>8.27</v>
@@ -11823,39 +12345,39 @@
         <v>9.608919999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>37.319225</v>
+        <v>37.806526</v>
       </c>
       <c r="J6" t="n">
-        <v>32.119114</v>
+        <v>32.538517</v>
       </c>
       <c r="K6" t="n">
         <v>2.49</v>
       </c>
       <c r="L6" t="n">
-        <v>10.041065</v>
+        <v>10.172179</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02679583967857953</v>
+        <v>0.02645045736582869</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03113410880342157</v>
+        <v>0.03073280880189343</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04479000091552734</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01258589337095587</v>
+        <v>-0.01405719211363392</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -11869,10 +12391,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>194.83</v>
+        <v>195.55</v>
       </c>
       <c r="F7" t="n">
-        <v>4718977351680</v>
+        <v>4736416743424</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
@@ -11881,39 +12403,39 @@
         <v>12.76443</v>
       </c>
       <c r="I7" t="n">
-        <v>29.83614</v>
+        <v>29.946402</v>
       </c>
       <c r="J7" t="n">
-        <v>15.26351</v>
+        <v>15.319917</v>
       </c>
       <c r="K7" t="n">
         <v>0.6</v>
       </c>
       <c r="L7" t="n">
-        <v>18.615955</v>
+        <v>18.684753</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03351639891187189</v>
+        <v>0.03339299411915111</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06551573166350151</v>
+        <v>0.065274507798517</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04479000091552734</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02179572948912407</v>
+        <v>0.02048450688298965</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -11927,51 +12449,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>517.8200000000001</v>
+        <v>552.05</v>
       </c>
       <c r="F8" t="n">
-        <v>844357632000</v>
+        <v>900173004800</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>13.17704</v>
+        <v>13.19926</v>
       </c>
       <c r="I8" t="n">
-        <v>172.60667</v>
+        <v>184.01666</v>
       </c>
       <c r="J8" t="n">
-        <v>39.297142</v>
+        <v>41.824314</v>
       </c>
       <c r="K8" t="n">
         <v>1.24</v>
       </c>
       <c r="L8" t="n">
-        <v>22.543858</v>
+        <v>24.034096</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005793518983430535</v>
+        <v>0.005434290372248891</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02544714379514117</v>
+        <v>0.0239095371796033</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04479000091552734</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01827285837923628</v>
+        <v>-0.02088046373592405</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -11985,10 +12507,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>360.45</v>
+        <v>373.9</v>
       </c>
       <c r="F9" t="n">
-        <v>1714869895168</v>
+        <v>1778859245568</v>
       </c>
       <c r="G9" t="n">
         <v>6.02</v>
@@ -11997,39 +12519,39 @@
         <v>19.39578</v>
       </c>
       <c r="I9" t="n">
-        <v>59.875416</v>
+        <v>62.109634</v>
       </c>
       <c r="J9" t="n">
-        <v>18.583939</v>
+        <v>19.277388</v>
       </c>
       <c r="K9" t="n">
         <v>0.41</v>
       </c>
       <c r="L9" t="n">
-        <v>22.724043</v>
+        <v>23.571978</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01670134554029685</v>
+        <v>0.01610056164749933</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05380990428630878</v>
+        <v>0.0518742444503878</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04479000091552734</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01008990211193134</v>
+        <v>0.007084243534860458</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -12043,10 +12565,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>77.65000000000001</v>
+        <v>76.02</v>
       </c>
       <c r="F10" t="n">
-        <v>326968508416</v>
+        <v>320104890368</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -12055,28 +12577,28 @@
         <v>3.84473</v>
       </c>
       <c r="I10" t="n">
-        <v>25.048388</v>
+        <v>24.522581</v>
       </c>
       <c r="J10" t="n">
-        <v>20.196478</v>
+        <v>19.77252</v>
       </c>
       <c r="K10" t="n">
         <v>1.53</v>
       </c>
       <c r="L10" t="n">
-        <v>6.973098</v>
+        <v>6.8267207</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03992273019961365</v>
+        <v>0.04077874243620101</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04951358660656793</v>
+        <v>0.05057524335701132</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04479000091552734</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005793584432190489</v>
+        <v>0.00578524244148397</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P199"/>
+  <dimension ref="A1:P208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11507,16 +11507,16 @@
         <v>10.172179</v>
       </c>
       <c r="M191" t="n">
-        <v>0.02645045736582869</v>
+        <v>0.0264504573658286</v>
       </c>
       <c r="N191" t="n">
-        <v>0.03073280880189343</v>
+        <v>0.0307328088018934</v>
       </c>
       <c r="O191" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.0447900009155273</v>
       </c>
       <c r="P191" t="n">
-        <v>-0.01405719211363392</v>
+        <v>-0.0140571921136339</v>
       </c>
     </row>
     <row r="192">
@@ -11565,16 +11565,16 @@
         <v>24.034096</v>
       </c>
       <c r="M192" t="n">
-        <v>0.005434290372248891</v>
+        <v>0.0054342903722488</v>
       </c>
       <c r="N192" t="n">
         <v>0.0239095371796033</v>
       </c>
       <c r="O192" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.0447900009155273</v>
       </c>
       <c r="P192" t="n">
-        <v>-0.02088046373592405</v>
+        <v>-0.020880463735924</v>
       </c>
     </row>
     <row r="193">
@@ -11623,16 +11623,16 @@
         <v>3.536</v>
       </c>
       <c r="M193" t="n">
-        <v>0.03141382699868939</v>
+        <v>0.0314138269986893</v>
       </c>
       <c r="N193" t="n">
         <v>0.0405574623197903</v>
       </c>
       <c r="O193" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.0447900009155273</v>
       </c>
       <c r="P193" t="n">
-        <v>-0.004232538595737044</v>
+        <v>-0.004232538595737</v>
       </c>
     </row>
     <row r="194">
@@ -11681,16 +11681,16 @@
         <v>23.571978</v>
       </c>
       <c r="M194" t="n">
-        <v>0.01610056164749933</v>
+        <v>0.0161005616474993</v>
       </c>
       <c r="N194" t="n">
         <v>0.0518742444503878</v>
       </c>
       <c r="O194" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.0447900009155273</v>
       </c>
       <c r="P194" t="n">
-        <v>0.007084243534860458</v>
+        <v>0.0070842435348604</v>
       </c>
     </row>
     <row r="195">
@@ -11739,16 +11739,16 @@
         <v>10.539029</v>
       </c>
       <c r="M195" t="n">
-        <v>0.03592765141134557</v>
+        <v>0.0359276514113455</v>
       </c>
       <c r="N195" t="n">
-        <v>0.03989506714168266</v>
+        <v>0.0398950671416826</v>
       </c>
       <c r="O195" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.0447900009155273</v>
       </c>
       <c r="P195" t="n">
-        <v>-0.004894933773844687</v>
+        <v>-0.0048949337738446</v>
       </c>
     </row>
     <row r="196">
@@ -11800,13 +11800,13 @@
         <v>0.0458278498725616</v>
       </c>
       <c r="N196" t="n">
-        <v>0.06134981425644272</v>
+        <v>0.0613498142564427</v>
       </c>
       <c r="O196" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.0447900009155273</v>
       </c>
       <c r="P196" t="n">
-        <v>0.01655981334091538</v>
+        <v>0.0165598133409153</v>
       </c>
     </row>
     <row r="197">
@@ -11858,13 +11858,13 @@
         <v>0.0434141800692972</v>
       </c>
       <c r="N197" t="n">
-        <v>0.05006366034028029</v>
+        <v>0.0500636603402802</v>
       </c>
       <c r="O197" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.0447900009155273</v>
       </c>
       <c r="P197" t="n">
-        <v>0.005273659424752941</v>
+        <v>0.0052736594247529</v>
       </c>
     </row>
     <row r="198">
@@ -11913,16 +11913,16 @@
         <v>6.8267207</v>
       </c>
       <c r="M198" t="n">
-        <v>0.04077874243620101</v>
+        <v>0.040778742436201</v>
       </c>
       <c r="N198" t="n">
-        <v>0.05057524335701132</v>
+        <v>0.0505752433570113</v>
       </c>
       <c r="O198" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.0447900009155273</v>
       </c>
       <c r="P198" t="n">
-        <v>0.00578524244148397</v>
+        <v>0.0057852424414839</v>
       </c>
     </row>
     <row r="199">
@@ -11971,16 +11971,538 @@
         <v>18.684753</v>
       </c>
       <c r="M199" t="n">
-        <v>0.03339299411915111</v>
+        <v>0.0333929941191511</v>
       </c>
       <c r="N199" t="n">
         <v>0.065274507798517</v>
       </c>
       <c r="O199" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.0447900009155273</v>
       </c>
       <c r="P199" t="n">
-        <v>0.02048450688298965</v>
+        <v>0.0204845068829896</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>310.66</v>
+      </c>
+      <c r="F200" t="n">
+        <v>4562774130688</v>
+      </c>
+      <c r="G200" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H200" t="n">
+        <v>9.60895</v>
+      </c>
+      <c r="I200" t="n">
+        <v>37.655758</v>
+      </c>
+      <c r="J200" t="n">
+        <v>32.330276</v>
+      </c>
+      <c r="K200" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L200" t="n">
+        <v>10.10711</v>
+      </c>
+      <c r="M200" t="n">
+        <v>0.02655636387046932</v>
+      </c>
+      <c r="N200" t="n">
+        <v>0.03093076031674499</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0.04529000282287598</v>
+      </c>
+      <c r="P200" t="n">
+        <v>-0.01435924250613099</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>516.11</v>
+      </c>
+      <c r="F201" t="n">
+        <v>841569271808</v>
+      </c>
+      <c r="G201" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H201" t="n">
+        <v>13.19926</v>
+      </c>
+      <c r="I201" t="n">
+        <v>173.19127</v>
+      </c>
+      <c r="J201" t="n">
+        <v>39.101433</v>
+      </c>
+      <c r="K201" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L201" t="n">
+        <v>22.46941</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0.005773962914882486</v>
+      </c>
+      <c r="N201" t="n">
+        <v>0.02557450931003081</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0.04529000282287598</v>
+      </c>
+      <c r="P201" t="n">
+        <v>-0.01971549351284517</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>245.98</v>
+      </c>
+      <c r="F202" t="n">
+        <v>2646033825792</v>
+      </c>
+      <c r="G202" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="H202" t="n">
+        <v>9.902509999999999</v>
+      </c>
+      <c r="I202" t="n">
+        <v>31.862694</v>
+      </c>
+      <c r="J202" t="n">
+        <v>24.840168</v>
+      </c>
+      <c r="K202" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L202" t="n">
+        <v>3.562358</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0.03138466541995284</v>
+      </c>
+      <c r="N202" t="n">
+        <v>0.04025737864867062</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0.04529000282287598</v>
+      </c>
+      <c r="P202" t="n">
+        <v>-0.005032624174205358</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>370.78</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1764015603712</v>
+      </c>
+      <c r="G203" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H203" t="n">
+        <v>19.39578</v>
+      </c>
+      <c r="I203" t="n">
+        <v>61.591362</v>
+      </c>
+      <c r="J203" t="n">
+        <v>19.11653</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L203" t="n">
+        <v>23.375282</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0.01623604293651222</v>
+      </c>
+      <c r="N203" t="n">
+        <v>0.05231075031015697</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0.04529000282287598</v>
+      </c>
+      <c r="P203" t="n">
+        <v>0.007020747487280987</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>363.62</v>
+      </c>
+      <c r="F204" t="n">
+        <v>4437099675648</v>
+      </c>
+      <c r="G204" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H204" t="n">
+        <v>14.55771</v>
+      </c>
+      <c r="I204" t="n">
+        <v>27.75725</v>
+      </c>
+      <c r="J204" t="n">
+        <v>24.977829</v>
+      </c>
+      <c r="K204" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L204" t="n">
+        <v>10.502061</v>
+      </c>
+      <c r="M204" t="n">
+        <v>0.0360266211979539</v>
+      </c>
+      <c r="N204" t="n">
+        <v>0.04003550409768439</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0.04529000282287598</v>
+      </c>
+      <c r="P204" t="n">
+        <v>-0.005254498725191584</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>615.58</v>
+      </c>
+      <c r="F205" t="n">
+        <v>1562602635264</v>
+      </c>
+      <c r="G205" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="H205" t="n">
+        <v>36.82768</v>
+      </c>
+      <c r="I205" t="n">
+        <v>22.392872</v>
+      </c>
+      <c r="J205" t="n">
+        <v>16.715145</v>
+      </c>
+      <c r="K205" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L205" t="n">
+        <v>7.2691703</v>
+      </c>
+      <c r="M205" t="n">
+        <v>0.0446570713798369</v>
+      </c>
+      <c r="N205" t="n">
+        <v>0.05982598524968322</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0.04529000282287598</v>
+      </c>
+      <c r="P205" t="n">
+        <v>0.01453598242680725</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>388.84</v>
+      </c>
+      <c r="F206" t="n">
+        <v>2888472723456</v>
+      </c>
+      <c r="G206" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="H206" t="n">
+        <v>19.36162</v>
+      </c>
+      <c r="I206" t="n">
+        <v>23.172823</v>
+      </c>
+      <c r="J206" t="n">
+        <v>20.08303</v>
+      </c>
+      <c r="K206" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L206" t="n">
+        <v>9.075457</v>
+      </c>
+      <c r="M206" t="n">
+        <v>0.04315399650241745</v>
+      </c>
+      <c r="N206" t="n">
+        <v>0.04979328258409629</v>
+      </c>
+      <c r="O206" t="n">
+        <v>0.04529000282287598</v>
+      </c>
+      <c r="P206" t="n">
+        <v>0.004503279761220308</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>76.18000000000001</v>
+      </c>
+      <c r="F207" t="n">
+        <v>320778633216</v>
+      </c>
+      <c r="G207" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H207" t="n">
+        <v>3.84473</v>
+      </c>
+      <c r="I207" t="n">
+        <v>24.574194</v>
+      </c>
+      <c r="J207" t="n">
+        <v>19.814137</v>
+      </c>
+      <c r="K207" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L207" t="n">
+        <v>6.8410897</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0.04069309530060383</v>
+      </c>
+      <c r="N207" t="n">
+        <v>0.0504690207403518</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0.04529000282287598</v>
+      </c>
+      <c r="P207" t="n">
+        <v>0.005179017917475819</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>196.93</v>
+      </c>
+      <c r="F208" t="n">
+        <v>4769841152000</v>
+      </c>
+      <c r="G208" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H208" t="n">
+        <v>12.76443</v>
+      </c>
+      <c r="I208" t="n">
+        <v>30.157732</v>
+      </c>
+      <c r="J208" t="n">
+        <v>15.428029</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L208" t="n">
+        <v>18.816608</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0.03315899050424009</v>
+      </c>
+      <c r="N208" t="n">
+        <v>0.06481709236784644</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0.04529000282287598</v>
+      </c>
+      <c r="P208" t="n">
+        <v>0.01952708954497046</v>
       </c>
     </row>
   </sheetData>
@@ -12082,12 +12604,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -12101,51 +12623,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>364.9</v>
+        <v>363.62</v>
       </c>
       <c r="F2" t="n">
-        <v>4452718739456</v>
+        <v>4437099675648</v>
       </c>
       <c r="G2" t="n">
-        <v>13.11</v>
+        <v>13.1</v>
       </c>
       <c r="H2" t="n">
         <v>14.55771</v>
       </c>
       <c r="I2" t="n">
-        <v>27.833715</v>
+        <v>27.75725</v>
       </c>
       <c r="J2" t="n">
-        <v>25.065756</v>
+        <v>24.977829</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="L2" t="n">
-        <v>10.539029</v>
+        <v>10.502061</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03592765141134557</v>
+        <v>0.0360266211979539</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03989506714168266</v>
+        <v>0.04003550409768439</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.04529000282287598</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.004894933773844687</v>
+        <v>-0.005254498725191584</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -12159,51 +12681,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>386.74</v>
+        <v>388.84</v>
       </c>
       <c r="F3" t="n">
-        <v>2872872796160</v>
+        <v>2888472723456</v>
       </c>
       <c r="G3" t="n">
-        <v>16.79</v>
+        <v>16.78</v>
       </c>
       <c r="H3" t="n">
         <v>19.36162</v>
       </c>
       <c r="I3" t="n">
-        <v>23.033947</v>
+        <v>23.172823</v>
       </c>
       <c r="J3" t="n">
-        <v>19.974567</v>
+        <v>20.08303</v>
       </c>
       <c r="K3" t="n">
         <v>1.2</v>
       </c>
       <c r="L3" t="n">
-        <v>9.026443</v>
+        <v>9.075457</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0434141800692972</v>
+        <v>0.04315399650241745</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05006366034028029</v>
+        <v>0.04979328258409629</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.04529000282287598</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005273659424752941</v>
+        <v>0.004503279761220308</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -12217,51 +12739,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>600.29</v>
+        <v>615.58</v>
       </c>
       <c r="F4" t="n">
-        <v>1523790118912</v>
+        <v>1562602635264</v>
       </c>
       <c r="G4" t="n">
-        <v>27.51</v>
+        <v>27.49</v>
       </c>
       <c r="H4" t="n">
         <v>36.82768</v>
       </c>
       <c r="I4" t="n">
-        <v>21.820791</v>
+        <v>22.392872</v>
       </c>
       <c r="J4" t="n">
-        <v>16.299969</v>
+        <v>16.715145</v>
       </c>
       <c r="K4" t="n">
         <v>0.84</v>
       </c>
       <c r="L4" t="n">
-        <v>7.088616</v>
+        <v>7.2691703</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0458278498725616</v>
+        <v>0.0446570713798369</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06134981425644272</v>
+        <v>0.05982598524968322</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.04529000282287598</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01655981334091538</v>
+        <v>0.01453598242680725</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -12275,51 +12797,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>244.16</v>
+        <v>245.98</v>
       </c>
       <c r="F5" t="n">
-        <v>2626455863296</v>
+        <v>2646033825792</v>
       </c>
       <c r="G5" t="n">
-        <v>7.67</v>
+        <v>7.72</v>
       </c>
       <c r="H5" t="n">
         <v>9.902509999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>31.833117</v>
+        <v>31.862694</v>
       </c>
       <c r="J5" t="n">
-        <v>24.656376</v>
+        <v>24.840168</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.536</v>
+        <v>3.562358</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03141382699868939</v>
+        <v>0.03138466541995284</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0405574623197903</v>
+        <v>0.04025737864867062</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.04529000282287598</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.004232538595737044</v>
+        <v>-0.005032624174205358</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -12333,51 +12855,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>312.66</v>
+        <v>310.66</v>
       </c>
       <c r="F6" t="n">
-        <v>4592148938752</v>
+        <v>4562774130688</v>
       </c>
       <c r="G6" t="n">
-        <v>8.27</v>
+        <v>8.25</v>
       </c>
       <c r="H6" t="n">
-        <v>9.608919999999999</v>
+        <v>9.60895</v>
       </c>
       <c r="I6" t="n">
-        <v>37.806526</v>
+        <v>37.655758</v>
       </c>
       <c r="J6" t="n">
-        <v>32.538517</v>
+        <v>32.330276</v>
       </c>
       <c r="K6" t="n">
         <v>2.49</v>
       </c>
       <c r="L6" t="n">
-        <v>10.172179</v>
+        <v>10.10711</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02645045736582869</v>
+        <v>0.02655636387046932</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03073280880189343</v>
+        <v>0.03093076031674499</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.04529000282287598</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01405719211363392</v>
+        <v>-0.01435924250613099</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -12391,10 +12913,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>195.55</v>
+        <v>196.93</v>
       </c>
       <c r="F7" t="n">
-        <v>4736416743424</v>
+        <v>4769841152000</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
@@ -12403,39 +12925,39 @@
         <v>12.76443</v>
       </c>
       <c r="I7" t="n">
-        <v>29.946402</v>
+        <v>30.157732</v>
       </c>
       <c r="J7" t="n">
-        <v>15.319917</v>
+        <v>15.428029</v>
       </c>
       <c r="K7" t="n">
         <v>0.6</v>
       </c>
       <c r="L7" t="n">
-        <v>18.684753</v>
+        <v>18.816608</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03339299411915111</v>
+        <v>0.03315899050424009</v>
       </c>
       <c r="N7" t="n">
-        <v>0.065274507798517</v>
+        <v>0.06481709236784644</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.04529000282287598</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02048450688298965</v>
+        <v>0.01952708954497046</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -12449,51 +12971,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>552.05</v>
+        <v>516.11</v>
       </c>
       <c r="F8" t="n">
-        <v>900173004800</v>
+        <v>841569271808</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H8" t="n">
         <v>13.19926</v>
       </c>
       <c r="I8" t="n">
-        <v>184.01666</v>
+        <v>173.19127</v>
       </c>
       <c r="J8" t="n">
-        <v>41.824314</v>
+        <v>39.101433</v>
       </c>
       <c r="K8" t="n">
         <v>1.24</v>
       </c>
       <c r="L8" t="n">
-        <v>24.034096</v>
+        <v>22.46941</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005434290372248891</v>
+        <v>0.005773962914882486</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0239095371796033</v>
+        <v>0.02557450931003081</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.04529000282287598</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02088046373592405</v>
+        <v>-0.01971549351284517</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -12507,10 +13029,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>373.9</v>
+        <v>370.78</v>
       </c>
       <c r="F9" t="n">
-        <v>1778859245568</v>
+        <v>1764015603712</v>
       </c>
       <c r="G9" t="n">
         <v>6.02</v>
@@ -12519,39 +13041,39 @@
         <v>19.39578</v>
       </c>
       <c r="I9" t="n">
-        <v>62.109634</v>
+        <v>61.591362</v>
       </c>
       <c r="J9" t="n">
-        <v>19.277388</v>
+        <v>19.11653</v>
       </c>
       <c r="K9" t="n">
         <v>0.41</v>
       </c>
       <c r="L9" t="n">
-        <v>23.571978</v>
+        <v>23.375282</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01610056164749933</v>
+        <v>0.01623604293651222</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0518742444503878</v>
+        <v>0.05231075031015697</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.04529000282287598</v>
       </c>
       <c r="P9" t="n">
-        <v>0.007084243534860458</v>
+        <v>0.007020747487280987</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -12565,10 +13087,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>76.02</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>320104890368</v>
+        <v>320778633216</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -12577,28 +13099,28 @@
         <v>3.84473</v>
       </c>
       <c r="I10" t="n">
-        <v>24.522581</v>
+        <v>24.574194</v>
       </c>
       <c r="J10" t="n">
-        <v>19.77252</v>
+        <v>19.814137</v>
       </c>
       <c r="K10" t="n">
         <v>1.53</v>
       </c>
       <c r="L10" t="n">
-        <v>6.8267207</v>
+        <v>6.8410897</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04077874243620101</v>
+        <v>0.04069309530060383</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05057524335701132</v>
+        <v>0.0504690207403518</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.04529000282287598</v>
       </c>
       <c r="P10" t="n">
-        <v>0.00578524244148397</v>
+        <v>0.005179017917475819</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P208"/>
+  <dimension ref="A1:P217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12029,16 +12029,16 @@
         <v>10.10711</v>
       </c>
       <c r="M200" t="n">
-        <v>0.02655636387046932</v>
+        <v>0.0265563638704693</v>
       </c>
       <c r="N200" t="n">
-        <v>0.03093076031674499</v>
+        <v>0.0309307603167449</v>
       </c>
       <c r="O200" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.0452900028228759</v>
       </c>
       <c r="P200" t="n">
-        <v>-0.01435924250613099</v>
+        <v>-0.0143592425061309</v>
       </c>
     </row>
     <row r="201">
@@ -12087,16 +12087,16 @@
         <v>22.46941</v>
       </c>
       <c r="M201" t="n">
-        <v>0.005773962914882486</v>
+        <v>0.0057739629148824</v>
       </c>
       <c r="N201" t="n">
-        <v>0.02557450931003081</v>
+        <v>0.0255745093100308</v>
       </c>
       <c r="O201" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.0452900028228759</v>
       </c>
       <c r="P201" t="n">
-        <v>-0.01971549351284517</v>
+        <v>-0.0197154935128451</v>
       </c>
     </row>
     <row r="202">
@@ -12145,16 +12145,16 @@
         <v>3.562358</v>
       </c>
       <c r="M202" t="n">
-        <v>0.03138466541995284</v>
+        <v>0.0313846654199528</v>
       </c>
       <c r="N202" t="n">
-        <v>0.04025737864867062</v>
+        <v>0.0402573786486706</v>
       </c>
       <c r="O202" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.0452900028228759</v>
       </c>
       <c r="P202" t="n">
-        <v>-0.005032624174205358</v>
+        <v>-0.0050326241742053</v>
       </c>
     </row>
     <row r="203">
@@ -12203,16 +12203,16 @@
         <v>23.375282</v>
       </c>
       <c r="M203" t="n">
-        <v>0.01623604293651222</v>
+        <v>0.0162360429365122</v>
       </c>
       <c r="N203" t="n">
-        <v>0.05231075031015697</v>
+        <v>0.0523107503101569</v>
       </c>
       <c r="O203" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.0452900028228759</v>
       </c>
       <c r="P203" t="n">
-        <v>0.007020747487280987</v>
+        <v>0.0070207474872809</v>
       </c>
     </row>
     <row r="204">
@@ -12264,13 +12264,13 @@
         <v>0.0360266211979539</v>
       </c>
       <c r="N204" t="n">
-        <v>0.04003550409768439</v>
+        <v>0.0400355040976843</v>
       </c>
       <c r="O204" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.0452900028228759</v>
       </c>
       <c r="P204" t="n">
-        <v>-0.005254498725191584</v>
+        <v>-0.0052544987251915</v>
       </c>
     </row>
     <row r="205">
@@ -12322,13 +12322,13 @@
         <v>0.0446570713798369</v>
       </c>
       <c r="N205" t="n">
-        <v>0.05982598524968322</v>
+        <v>0.0598259852496832</v>
       </c>
       <c r="O205" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.0452900028228759</v>
       </c>
       <c r="P205" t="n">
-        <v>0.01453598242680725</v>
+        <v>0.0145359824268072</v>
       </c>
     </row>
     <row r="206">
@@ -12377,16 +12377,16 @@
         <v>9.075457</v>
       </c>
       <c r="M206" t="n">
-        <v>0.04315399650241745</v>
+        <v>0.0431539965024174</v>
       </c>
       <c r="N206" t="n">
-        <v>0.04979328258409629</v>
+        <v>0.0497932825840962</v>
       </c>
       <c r="O206" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.0452900028228759</v>
       </c>
       <c r="P206" t="n">
-        <v>0.004503279761220308</v>
+        <v>0.0045032797612203</v>
       </c>
     </row>
     <row r="207">
@@ -12435,16 +12435,16 @@
         <v>6.8410897</v>
       </c>
       <c r="M207" t="n">
-        <v>0.04069309530060383</v>
+        <v>0.0406930953006038</v>
       </c>
       <c r="N207" t="n">
         <v>0.0504690207403518</v>
       </c>
       <c r="O207" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.0452900028228759</v>
       </c>
       <c r="P207" t="n">
-        <v>0.005179017917475819</v>
+        <v>0.0051790179174758</v>
       </c>
     </row>
     <row r="208">
@@ -12493,16 +12493,538 @@
         <v>18.816608</v>
       </c>
       <c r="M208" t="n">
-        <v>0.03315899050424009</v>
+        <v>0.03315899050424</v>
       </c>
       <c r="N208" t="n">
-        <v>0.06481709236784644</v>
+        <v>0.0648170923678464</v>
       </c>
       <c r="O208" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.0452900028228759</v>
       </c>
       <c r="P208" t="n">
-        <v>0.01952708954497046</v>
+        <v>0.0195270895449704</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>313.39</v>
+      </c>
+      <c r="F209" t="n">
+        <v>4602870628352</v>
+      </c>
+      <c r="G209" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H209" t="n">
+        <v>9.60895</v>
+      </c>
+      <c r="I209" t="n">
+        <v>37.940678</v>
+      </c>
+      <c r="J209" t="n">
+        <v>32.614388</v>
+      </c>
+      <c r="K209" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="L209" t="n">
+        <v>10.195929</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0.02635693544784454</v>
+      </c>
+      <c r="N209" t="n">
+        <v>0.03066131657040748</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P209" t="n">
+        <v>-0.01502868110262718</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>517.405</v>
+      </c>
+      <c r="F210" t="n">
+        <v>843680907264</v>
+      </c>
+      <c r="G210" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H210" t="n">
+        <v>13.19926</v>
+      </c>
+      <c r="I210" t="n">
+        <v>173.04517</v>
+      </c>
+      <c r="J210" t="n">
+        <v>39.19955</v>
+      </c>
+      <c r="K210" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L210" t="n">
+        <v>22.52579</v>
+      </c>
+      <c r="M210" t="n">
+        <v>0.005778838627380873</v>
+      </c>
+      <c r="N210" t="n">
+        <v>0.02551049951198771</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P210" t="n">
+        <v>-0.02017949816104695</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>243.62</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2620647014400</v>
+      </c>
+      <c r="G211" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="H211" t="n">
+        <v>9.891920000000001</v>
+      </c>
+      <c r="I211" t="n">
+        <v>31.353926</v>
+      </c>
+      <c r="J211" t="n">
+        <v>24.628181</v>
+      </c>
+      <c r="K211" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L211" t="n">
+        <v>3.5281796</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0.0318939331746162</v>
+      </c>
+      <c r="N211" t="n">
+        <v>0.0406038913061325</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P211" t="n">
+        <v>-0.005086106366902161</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>388.69</v>
+      </c>
+      <c r="F212" t="n">
+        <v>1849223938048</v>
+      </c>
+      <c r="G212" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H212" t="n">
+        <v>19.39578</v>
+      </c>
+      <c r="I212" t="n">
+        <v>64.673874</v>
+      </c>
+      <c r="J212" t="n">
+        <v>20.039927</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L212" t="n">
+        <v>24.504393</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0.01546219352182973</v>
+      </c>
+      <c r="N212" t="n">
+        <v>0.04990038333890761</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P212" t="n">
+        <v>0.004210385665872944</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>358.71</v>
+      </c>
+      <c r="F213" t="n">
+        <v>4377184829440</v>
+      </c>
+      <c r="G213" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="H213" t="n">
+        <v>14.55771</v>
+      </c>
+      <c r="I213" t="n">
+        <v>27.319878</v>
+      </c>
+      <c r="J213" t="n">
+        <v>24.64055</v>
+      </c>
+      <c r="K213" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L213" t="n">
+        <v>10.3602495</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0.03660338434947451</v>
+      </c>
+      <c r="N213" t="n">
+        <v>0.04058350756878816</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P213" t="n">
+        <v>-0.005106490104246506</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>603.12</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1530973782016</v>
+      </c>
+      <c r="G214" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="H214" t="n">
+        <v>36.83411</v>
+      </c>
+      <c r="I214" t="n">
+        <v>21.915697</v>
+      </c>
+      <c r="J214" t="n">
+        <v>16.373953</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L214" t="n">
+        <v>7.122034</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0.04562939381880886</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0.06107260578326038</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0.01538260811022572</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>383.34</v>
+      </c>
+      <c r="F215" t="n">
+        <v>2847616270336</v>
+      </c>
+      <c r="G215" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H215" t="n">
+        <v>19.3605</v>
+      </c>
+      <c r="I215" t="n">
+        <v>22.817858</v>
+      </c>
+      <c r="J215" t="n">
+        <v>19.800108</v>
+      </c>
+      <c r="K215" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L215" t="n">
+        <v>8.947087</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0.0438253247769604</v>
+      </c>
+      <c r="N215" t="n">
+        <v>0.05050477383002035</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0.004814776156985681</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>75.59</v>
+      </c>
+      <c r="F216" t="n">
+        <v>318294261760</v>
+      </c>
+      <c r="G216" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H216" t="n">
+        <v>3.8436</v>
+      </c>
+      <c r="I216" t="n">
+        <v>24.383871</v>
+      </c>
+      <c r="J216" t="n">
+        <v>19.666458</v>
+      </c>
+      <c r="K216" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L216" t="n">
+        <v>6.7881064</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0.04101071570313534</v>
+      </c>
+      <c r="N216" t="n">
+        <v>0.0508479957666358</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0.005157998093601131</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>204.12</v>
+      </c>
+      <c r="F217" t="n">
+        <v>4943990226944</v>
+      </c>
+      <c r="G217" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="H217" t="n">
+        <v>12.76443</v>
+      </c>
+      <c r="I217" t="n">
+        <v>31.211008</v>
+      </c>
+      <c r="J217" t="n">
+        <v>15.991313</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L217" t="n">
+        <v>19.503613</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0.03203997648442093</v>
+      </c>
+      <c r="N217" t="n">
+        <v>0.06253395061728395</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P217" t="n">
+        <v>0.01684395294424929</v>
       </c>
     </row>
   </sheetData>
@@ -12604,12 +13126,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -12623,51 +13145,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>363.62</v>
+        <v>358.71</v>
       </c>
       <c r="F2" t="n">
-        <v>4437099675648</v>
+        <v>4377184829440</v>
       </c>
       <c r="G2" t="n">
-        <v>13.1</v>
+        <v>13.13</v>
       </c>
       <c r="H2" t="n">
         <v>14.55771</v>
       </c>
       <c r="I2" t="n">
-        <v>27.75725</v>
+        <v>27.319878</v>
       </c>
       <c r="J2" t="n">
-        <v>24.977829</v>
+        <v>24.64055</v>
       </c>
       <c r="K2" t="n">
         <v>1.44</v>
       </c>
       <c r="L2" t="n">
-        <v>10.502061</v>
+        <v>10.3602495</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0360266211979539</v>
+        <v>0.03660338434947451</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04003550409768439</v>
+        <v>0.04058350756878816</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005254498725191584</v>
+        <v>-0.005106490104246506</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -12681,51 +13203,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>388.84</v>
+        <v>383.34</v>
       </c>
       <c r="F3" t="n">
-        <v>2888472723456</v>
+        <v>2847616270336</v>
       </c>
       <c r="G3" t="n">
-        <v>16.78</v>
+        <v>16.8</v>
       </c>
       <c r="H3" t="n">
-        <v>19.36162</v>
+        <v>19.3605</v>
       </c>
       <c r="I3" t="n">
-        <v>23.172823</v>
+        <v>22.817858</v>
       </c>
       <c r="J3" t="n">
-        <v>20.08303</v>
+        <v>19.800108</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="L3" t="n">
-        <v>9.075457</v>
+        <v>8.947087</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04315399650241745</v>
+        <v>0.0438253247769604</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04979328258409629</v>
+        <v>0.05050477383002035</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004503279761220308</v>
+        <v>0.004814776156985681</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -12739,51 +13261,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>615.58</v>
+        <v>603.12</v>
       </c>
       <c r="F4" t="n">
-        <v>1562602635264</v>
+        <v>1530973782016</v>
       </c>
       <c r="G4" t="n">
-        <v>27.49</v>
+        <v>27.52</v>
       </c>
       <c r="H4" t="n">
-        <v>36.82768</v>
+        <v>36.83411</v>
       </c>
       <c r="I4" t="n">
-        <v>22.392872</v>
+        <v>21.915697</v>
       </c>
       <c r="J4" t="n">
-        <v>16.715145</v>
+        <v>16.373953</v>
       </c>
       <c r="K4" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="L4" t="n">
-        <v>7.2691703</v>
+        <v>7.122034</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0446570713798369</v>
+        <v>0.04562939381880886</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05982598524968322</v>
+        <v>0.06107260578326038</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01453598242680725</v>
+        <v>0.01538260811022572</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -12797,51 +13319,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>245.98</v>
+        <v>243.62</v>
       </c>
       <c r="F5" t="n">
-        <v>2646033825792</v>
+        <v>2620647014400</v>
       </c>
       <c r="G5" t="n">
-        <v>7.72</v>
+        <v>7.77</v>
       </c>
       <c r="H5" t="n">
-        <v>9.902509999999999</v>
+        <v>9.891920000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>31.862694</v>
+        <v>31.353926</v>
       </c>
       <c r="J5" t="n">
-        <v>24.840168</v>
+        <v>24.628181</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.562358</v>
+        <v>3.5281796</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03138466541995284</v>
+        <v>0.0318939331746162</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04025737864867062</v>
+        <v>0.0406038913061325</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.005032624174205358</v>
+        <v>-0.005086106366902161</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -12855,51 +13377,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>310.66</v>
+        <v>313.39</v>
       </c>
       <c r="F6" t="n">
-        <v>4562774130688</v>
+        <v>4602870628352</v>
       </c>
       <c r="G6" t="n">
-        <v>8.25</v>
+        <v>8.26</v>
       </c>
       <c r="H6" t="n">
         <v>9.60895</v>
       </c>
       <c r="I6" t="n">
-        <v>37.655758</v>
+        <v>37.940678</v>
       </c>
       <c r="J6" t="n">
-        <v>32.330276</v>
+        <v>32.614388</v>
       </c>
       <c r="K6" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="L6" t="n">
-        <v>10.10711</v>
+        <v>10.195929</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02655636387046932</v>
+        <v>0.02635693544784454</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03093076031674499</v>
+        <v>0.03066131657040748</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01435924250613099</v>
+        <v>-0.01502868110262718</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -12913,51 +13435,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>196.93</v>
+        <v>204.12</v>
       </c>
       <c r="F7" t="n">
-        <v>4769841152000</v>
+        <v>4943990226944</v>
       </c>
       <c r="G7" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
       <c r="H7" t="n">
         <v>12.76443</v>
       </c>
       <c r="I7" t="n">
-        <v>30.157732</v>
+        <v>31.211008</v>
       </c>
       <c r="J7" t="n">
-        <v>15.428029</v>
+        <v>15.991313</v>
       </c>
       <c r="K7" t="n">
         <v>0.6</v>
       </c>
       <c r="L7" t="n">
-        <v>18.816608</v>
+        <v>19.503613</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03315899050424009</v>
+        <v>0.03203997648442093</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06481709236784644</v>
+        <v>0.06253395061728395</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01952708954497046</v>
+        <v>0.01684395294424929</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -12971,51 +13493,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>516.11</v>
+        <v>517.405</v>
       </c>
       <c r="F8" t="n">
-        <v>841569271808</v>
+        <v>843680907264</v>
       </c>
       <c r="G8" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="H8" t="n">
         <v>13.19926</v>
       </c>
       <c r="I8" t="n">
-        <v>173.19127</v>
+        <v>173.04517</v>
       </c>
       <c r="J8" t="n">
-        <v>39.101433</v>
+        <v>39.19955</v>
       </c>
       <c r="K8" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="L8" t="n">
-        <v>22.46941</v>
+        <v>22.52579</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005773962914882486</v>
+        <v>0.005778838627380873</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02557450931003081</v>
+        <v>0.02551049951198771</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01971549351284517</v>
+        <v>-0.02017949816104695</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -13029,51 +13551,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>370.78</v>
+        <v>388.69</v>
       </c>
       <c r="F9" t="n">
-        <v>1764015603712</v>
+        <v>1849223938048</v>
       </c>
       <c r="G9" t="n">
-        <v>6.02</v>
+        <v>6.01</v>
       </c>
       <c r="H9" t="n">
         <v>19.39578</v>
       </c>
       <c r="I9" t="n">
-        <v>61.591362</v>
+        <v>64.673874</v>
       </c>
       <c r="J9" t="n">
-        <v>19.11653</v>
+        <v>20.039927</v>
       </c>
       <c r="K9" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="L9" t="n">
-        <v>23.375282</v>
+        <v>24.504393</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01623604293651222</v>
+        <v>0.01546219352182973</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05231075031015697</v>
+        <v>0.04990038333890761</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P9" t="n">
-        <v>0.007020747487280987</v>
+        <v>0.004210385665872944</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -13087,40 +13609,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>76.18000000000001</v>
+        <v>75.59</v>
       </c>
       <c r="F10" t="n">
-        <v>320778633216</v>
+        <v>318294261760</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.84473</v>
+        <v>3.8436</v>
       </c>
       <c r="I10" t="n">
-        <v>24.574194</v>
+        <v>24.383871</v>
       </c>
       <c r="J10" t="n">
-        <v>19.814137</v>
+        <v>19.666458</v>
       </c>
       <c r="K10" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="L10" t="n">
-        <v>6.8410897</v>
+        <v>6.7881064</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04069309530060383</v>
+        <v>0.04101071570313534</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0504690207403518</v>
+        <v>0.0508479957666358</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04529000282287598</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005179017917475819</v>
+        <v>0.005157998093601131</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P217"/>
+  <dimension ref="A1:P226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12551,16 +12551,16 @@
         <v>10.195929</v>
       </c>
       <c r="M209" t="n">
-        <v>0.02635693544784454</v>
+        <v>0.0263569354478445</v>
       </c>
       <c r="N209" t="n">
-        <v>0.03066131657040748</v>
+        <v>0.0306613165704074</v>
       </c>
       <c r="O209" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P209" t="n">
-        <v>-0.01502868110262718</v>
+        <v>-0.0150286811026271</v>
       </c>
     </row>
     <row r="210">
@@ -12609,16 +12609,16 @@
         <v>22.52579</v>
       </c>
       <c r="M210" t="n">
-        <v>0.005778838627380873</v>
+        <v>0.0057788386273808</v>
       </c>
       <c r="N210" t="n">
-        <v>0.02551049951198771</v>
+        <v>0.0255104995119877</v>
       </c>
       <c r="O210" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P210" t="n">
-        <v>-0.02017949816104695</v>
+        <v>-0.0201794981610469</v>
       </c>
     </row>
     <row r="211">
@@ -12673,10 +12673,10 @@
         <v>0.0406038913061325</v>
       </c>
       <c r="O211" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P211" t="n">
-        <v>-0.005086106366902161</v>
+        <v>-0.0050861063669021</v>
       </c>
     </row>
     <row r="212">
@@ -12725,16 +12725,16 @@
         <v>24.504393</v>
       </c>
       <c r="M212" t="n">
-        <v>0.01546219352182973</v>
+        <v>0.0154621935218297</v>
       </c>
       <c r="N212" t="n">
-        <v>0.04990038333890761</v>
+        <v>0.0499003833389076</v>
       </c>
       <c r="O212" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P212" t="n">
-        <v>0.004210385665872944</v>
+        <v>0.0042103856658729</v>
       </c>
     </row>
     <row r="213">
@@ -12783,16 +12783,16 @@
         <v>10.3602495</v>
       </c>
       <c r="M213" t="n">
-        <v>0.03660338434947451</v>
+        <v>0.0366033843494745</v>
       </c>
       <c r="N213" t="n">
-        <v>0.04058350756878816</v>
+        <v>0.0405835075687881</v>
       </c>
       <c r="O213" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P213" t="n">
-        <v>-0.005106490104246506</v>
+        <v>-0.0051064901042465</v>
       </c>
     </row>
     <row r="214">
@@ -12841,16 +12841,16 @@
         <v>7.122034</v>
       </c>
       <c r="M214" t="n">
-        <v>0.04562939381880886</v>
+        <v>0.0456293938188088</v>
       </c>
       <c r="N214" t="n">
-        <v>0.06107260578326038</v>
+        <v>0.0610726057832603</v>
       </c>
       <c r="O214" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P214" t="n">
-        <v>0.01538260811022572</v>
+        <v>0.0153826081102257</v>
       </c>
     </row>
     <row r="215">
@@ -12902,13 +12902,13 @@
         <v>0.0438253247769604</v>
       </c>
       <c r="N215" t="n">
-        <v>0.05050477383002035</v>
+        <v>0.0505047738300203</v>
       </c>
       <c r="O215" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P215" t="n">
-        <v>0.004814776156985681</v>
+        <v>0.0048147761569856</v>
       </c>
     </row>
     <row r="216">
@@ -12957,16 +12957,16 @@
         <v>6.7881064</v>
       </c>
       <c r="M216" t="n">
-        <v>0.04101071570313534</v>
+        <v>0.0410107157031353</v>
       </c>
       <c r="N216" t="n">
-        <v>0.0508479957666358</v>
+        <v>0.0508479957666357</v>
       </c>
       <c r="O216" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P216" t="n">
-        <v>0.005157998093601131</v>
+        <v>0.0051579980936011</v>
       </c>
     </row>
     <row r="217">
@@ -13015,16 +13015,538 @@
         <v>19.503613</v>
       </c>
       <c r="M217" t="n">
-        <v>0.03203997648442093</v>
+        <v>0.0320399764844209</v>
       </c>
       <c r="N217" t="n">
-        <v>0.06253395061728395</v>
+        <v>0.0625339506172839</v>
       </c>
       <c r="O217" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P217" t="n">
-        <v>0.01684395294424929</v>
+        <v>0.0168439529442492</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>316.22</v>
+      </c>
+      <c r="F218" t="n">
+        <v>4644435656704</v>
+      </c>
+      <c r="G218" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="H218" t="n">
+        <v>9.60895</v>
+      </c>
+      <c r="I218" t="n">
+        <v>38.237</v>
+      </c>
+      <c r="J218" t="n">
+        <v>32.908905</v>
+      </c>
+      <c r="K218" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="L218" t="n">
+        <v>10.288</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0.02615267851495794</v>
+      </c>
+      <c r="N218" t="n">
+        <v>0.03038691417367655</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0.04539000034332275</v>
+      </c>
+      <c r="P218" t="n">
+        <v>-0.0150030861696462</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>546.72</v>
+      </c>
+      <c r="F219" t="n">
+        <v>891481882624</v>
+      </c>
+      <c r="G219" t="n">
+        <v>3</v>
+      </c>
+      <c r="H219" t="n">
+        <v>13.25123</v>
+      </c>
+      <c r="I219" t="n">
+        <v>182.23999</v>
+      </c>
+      <c r="J219" t="n">
+        <v>41.258053</v>
+      </c>
+      <c r="K219" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L219" t="n">
+        <v>23.802048</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0.005487269534679543</v>
+      </c>
+      <c r="N219" t="n">
+        <v>0.02423769022534387</v>
+      </c>
+      <c r="O219" t="n">
+        <v>0.04539000034332275</v>
+      </c>
+      <c r="P219" t="n">
+        <v>-0.02115231011797888</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>247.04</v>
+      </c>
+      <c r="F220" t="n">
+        <v>2657436303360</v>
+      </c>
+      <c r="G220" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H220" t="n">
+        <v>9.891920000000001</v>
+      </c>
+      <c r="I220" t="n">
+        <v>32.08312</v>
+      </c>
+      <c r="J220" t="n">
+        <v>24.973917</v>
+      </c>
+      <c r="K220" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L220" t="n">
+        <v>3.577709</v>
+      </c>
+      <c r="M220" t="n">
+        <v>0.03116904145077721</v>
+      </c>
+      <c r="N220" t="n">
+        <v>0.04004177461139897</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0.04539000034332275</v>
+      </c>
+      <c r="P220" t="n">
+        <v>-0.005348225731923784</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>401.11</v>
+      </c>
+      <c r="F221" t="n">
+        <v>1908312899584</v>
+      </c>
+      <c r="G221" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H221" t="n">
+        <v>19.39578</v>
+      </c>
+      <c r="I221" t="n">
+        <v>66.62956</v>
+      </c>
+      <c r="J221" t="n">
+        <v>20.680271</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L221" t="n">
+        <v>25.28739</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0.01500835182368926</v>
+      </c>
+      <c r="N221" t="n">
+        <v>0.04835526414200593</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0.04539000034332275</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0.002965263798683178</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>356.24</v>
+      </c>
+      <c r="F222" t="n">
+        <v>4347044298752</v>
+      </c>
+      <c r="G222" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="H222" t="n">
+        <v>14.55792</v>
+      </c>
+      <c r="I222" t="n">
+        <v>27.214666</v>
+      </c>
+      <c r="J222" t="n">
+        <v>24.470528</v>
+      </c>
+      <c r="K222" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L222" t="n">
+        <v>10.288911</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0.03674489108466202</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0.04086548394340894</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0.04539000034332275</v>
+      </c>
+      <c r="P222" t="n">
+        <v>-0.004524516399913817</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>631.48</v>
+      </c>
+      <c r="F223" t="n">
+        <v>1602963505152</v>
+      </c>
+      <c r="G223" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H223" t="n">
+        <v>36.83411</v>
+      </c>
+      <c r="I223" t="n">
+        <v>22.962908</v>
+      </c>
+      <c r="J223" t="n">
+        <v>17.14389</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L223" t="n">
+        <v>7.456928</v>
+      </c>
+      <c r="M223" t="n">
+        <v>0.04354848926331792</v>
+      </c>
+      <c r="N223" t="n">
+        <v>0.05832981250395895</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0.04539000034332275</v>
+      </c>
+      <c r="P223" t="n">
+        <v>0.0129398121606362</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>384.36</v>
+      </c>
+      <c r="F224" t="n">
+        <v>2855193018368</v>
+      </c>
+      <c r="G224" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="H224" t="n">
+        <v>19.35634</v>
+      </c>
+      <c r="I224" t="n">
+        <v>22.892195</v>
+      </c>
+      <c r="J224" t="n">
+        <v>19.85706</v>
+      </c>
+      <c r="K224" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L224" t="n">
+        <v>8.970893</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0.0436830055156624</v>
+      </c>
+      <c r="N224" t="n">
+        <v>0.0503599229888646</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0.04539000034332275</v>
+      </c>
+      <c r="P224" t="n">
+        <v>0.004969922645541851</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>75.47</v>
+      </c>
+      <c r="F225" t="n">
+        <v>317788979200</v>
+      </c>
+      <c r="G225" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H225" t="n">
+        <v>3.8421</v>
+      </c>
+      <c r="I225" t="n">
+        <v>24.345163</v>
+      </c>
+      <c r="J225" t="n">
+        <v>19.642904</v>
+      </c>
+      <c r="K225" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L225" t="n">
+        <v>6.7773304</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0.04107592420829469</v>
+      </c>
+      <c r="N225" t="n">
+        <v>0.05090897045183516</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0.04539000034332275</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0.005518970108512412</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>202.78</v>
+      </c>
+      <c r="F226" t="n">
+        <v>4911534178304</v>
+      </c>
+      <c r="G226" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H226" t="n">
+        <v>12.76383</v>
+      </c>
+      <c r="I226" t="n">
+        <v>31.053598</v>
+      </c>
+      <c r="J226" t="n">
+        <v>15.88708</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L226" t="n">
+        <v>19.375576</v>
+      </c>
+      <c r="M226" t="n">
+        <v>0.0322023868231581</v>
+      </c>
+      <c r="N226" t="n">
+        <v>0.06294422526876418</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0.04539000034332275</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0.01755422492544143</v>
       </c>
     </row>
   </sheetData>
@@ -13126,12 +13648,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -13145,51 +13667,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>358.71</v>
+        <v>356.24</v>
       </c>
       <c r="F2" t="n">
-        <v>4377184829440</v>
+        <v>4347044298752</v>
       </c>
       <c r="G2" t="n">
-        <v>13.13</v>
+        <v>13.09</v>
       </c>
       <c r="H2" t="n">
-        <v>14.55771</v>
+        <v>14.55792</v>
       </c>
       <c r="I2" t="n">
-        <v>27.319878</v>
+        <v>27.214666</v>
       </c>
       <c r="J2" t="n">
-        <v>24.64055</v>
+        <v>24.470528</v>
       </c>
       <c r="K2" t="n">
         <v>1.44</v>
       </c>
       <c r="L2" t="n">
-        <v>10.3602495</v>
+        <v>10.288911</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03660338434947451</v>
+        <v>0.03674489108466202</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04058350756878816</v>
+        <v>0.04086548394340894</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04539000034332275</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005106490104246506</v>
+        <v>-0.004524516399913817</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -13203,51 +13725,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>383.34</v>
+        <v>384.36</v>
       </c>
       <c r="F3" t="n">
-        <v>2847616270336</v>
+        <v>2855193018368</v>
       </c>
       <c r="G3" t="n">
-        <v>16.8</v>
+        <v>16.79</v>
       </c>
       <c r="H3" t="n">
-        <v>19.3605</v>
+        <v>19.35634</v>
       </c>
       <c r="I3" t="n">
-        <v>22.817858</v>
+        <v>22.892195</v>
       </c>
       <c r="J3" t="n">
-        <v>19.800108</v>
+        <v>19.85706</v>
       </c>
       <c r="K3" t="n">
         <v>1.19</v>
       </c>
       <c r="L3" t="n">
-        <v>8.947087</v>
+        <v>8.970893</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0438253247769604</v>
+        <v>0.0436830055156624</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05050477383002035</v>
+        <v>0.0503599229888646</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04539000034332275</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004814776156985681</v>
+        <v>0.004969922645541851</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -13261,51 +13783,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>603.12</v>
+        <v>631.48</v>
       </c>
       <c r="F4" t="n">
-        <v>1530973782016</v>
+        <v>1602963505152</v>
       </c>
       <c r="G4" t="n">
-        <v>27.52</v>
+        <v>27.5</v>
       </c>
       <c r="H4" t="n">
         <v>36.83411</v>
       </c>
       <c r="I4" t="n">
-        <v>21.915697</v>
+        <v>22.962908</v>
       </c>
       <c r="J4" t="n">
-        <v>16.373953</v>
+        <v>17.14389</v>
       </c>
       <c r="K4" t="n">
         <v>0.87</v>
       </c>
       <c r="L4" t="n">
-        <v>7.122034</v>
+        <v>7.456928</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04562939381880886</v>
+        <v>0.04354848926331792</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06107260578326038</v>
+        <v>0.05832981250395895</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04539000034332275</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01538260811022572</v>
+        <v>0.0129398121606362</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -13319,51 +13841,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>243.62</v>
+        <v>247.04</v>
       </c>
       <c r="F5" t="n">
-        <v>2620647014400</v>
+        <v>2657436303360</v>
       </c>
       <c r="G5" t="n">
-        <v>7.77</v>
+        <v>7.7</v>
       </c>
       <c r="H5" t="n">
         <v>9.891920000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>31.353926</v>
+        <v>32.08312</v>
       </c>
       <c r="J5" t="n">
-        <v>24.628181</v>
+        <v>24.973917</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5281796</v>
+        <v>3.577709</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0318939331746162</v>
+        <v>0.03116904145077721</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0406038913061325</v>
+        <v>0.04004177461139897</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04539000034332275</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.005086106366902161</v>
+        <v>-0.005348225731923784</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -13377,51 +13899,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>313.39</v>
+        <v>316.22</v>
       </c>
       <c r="F6" t="n">
-        <v>4602870628352</v>
+        <v>4644435656704</v>
       </c>
       <c r="G6" t="n">
-        <v>8.26</v>
+        <v>8.27</v>
       </c>
       <c r="H6" t="n">
         <v>9.60895</v>
       </c>
       <c r="I6" t="n">
-        <v>37.940678</v>
+        <v>38.237</v>
       </c>
       <c r="J6" t="n">
-        <v>32.614388</v>
+        <v>32.908905</v>
       </c>
       <c r="K6" t="n">
         <v>2.53</v>
       </c>
       <c r="L6" t="n">
-        <v>10.195929</v>
+        <v>10.288</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02635693544784454</v>
+        <v>0.02615267851495794</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03066131657040748</v>
+        <v>0.03038691417367655</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04539000034332275</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01502868110262718</v>
+        <v>-0.0150030861696462</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -13435,51 +13957,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>204.12</v>
+        <v>202.78</v>
       </c>
       <c r="F7" t="n">
-        <v>4943990226944</v>
+        <v>4911534178304</v>
       </c>
       <c r="G7" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
       <c r="H7" t="n">
-        <v>12.76443</v>
+        <v>12.76383</v>
       </c>
       <c r="I7" t="n">
-        <v>31.211008</v>
+        <v>31.053598</v>
       </c>
       <c r="J7" t="n">
-        <v>15.991313</v>
+        <v>15.88708</v>
       </c>
       <c r="K7" t="n">
         <v>0.6</v>
       </c>
       <c r="L7" t="n">
-        <v>19.503613</v>
+        <v>19.375576</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03203997648442093</v>
+        <v>0.0322023868231581</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06253395061728395</v>
+        <v>0.06294422526876418</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04539000034332275</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01684395294424929</v>
+        <v>0.01755422492544143</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -13493,51 +14015,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>517.405</v>
+        <v>546.72</v>
       </c>
       <c r="F8" t="n">
-        <v>843680907264</v>
+        <v>891481882624</v>
       </c>
       <c r="G8" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>13.19926</v>
+        <v>13.25123</v>
       </c>
       <c r="I8" t="n">
-        <v>173.04517</v>
+        <v>182.23999</v>
       </c>
       <c r="J8" t="n">
-        <v>39.19955</v>
+        <v>41.258053</v>
       </c>
       <c r="K8" t="n">
         <v>1.32</v>
       </c>
       <c r="L8" t="n">
-        <v>22.52579</v>
+        <v>23.802048</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005778838627380873</v>
+        <v>0.005487269534679543</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02551049951198771</v>
+        <v>0.02423769022534387</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04539000034332275</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02017949816104695</v>
+        <v>-0.02115231011797888</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -13551,51 +14073,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>388.69</v>
+        <v>401.11</v>
       </c>
       <c r="F9" t="n">
-        <v>1849223938048</v>
+        <v>1908312899584</v>
       </c>
       <c r="G9" t="n">
-        <v>6.01</v>
+        <v>6.02</v>
       </c>
       <c r="H9" t="n">
         <v>19.39578</v>
       </c>
       <c r="I9" t="n">
-        <v>64.673874</v>
+        <v>66.62956</v>
       </c>
       <c r="J9" t="n">
-        <v>20.039927</v>
+        <v>20.680271</v>
       </c>
       <c r="K9" t="n">
         <v>0.42</v>
       </c>
       <c r="L9" t="n">
-        <v>24.504393</v>
+        <v>25.28739</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01546219352182973</v>
+        <v>0.01500835182368926</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04990038333890761</v>
+        <v>0.04835526414200593</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04539000034332275</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004210385665872944</v>
+        <v>0.002965263798683178</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -13609,40 +14131,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>75.59</v>
+        <v>75.47</v>
       </c>
       <c r="F10" t="n">
-        <v>318294261760</v>
+        <v>317788979200</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8436</v>
+        <v>3.8421</v>
       </c>
       <c r="I10" t="n">
-        <v>24.383871</v>
+        <v>24.345163</v>
       </c>
       <c r="J10" t="n">
-        <v>19.666458</v>
+        <v>19.642904</v>
       </c>
       <c r="K10" t="n">
         <v>1.49</v>
       </c>
       <c r="L10" t="n">
-        <v>6.7881064</v>
+        <v>6.7773304</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04101071570313534</v>
+        <v>0.04107592420829469</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0508479957666358</v>
+        <v>0.05090897045183516</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04539000034332275</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005157998093601131</v>
+        <v>0.005518970108512412</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P226"/>
+  <dimension ref="A1:P235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13073,16 +13073,16 @@
         <v>10.288</v>
       </c>
       <c r="M218" t="n">
-        <v>0.02615267851495794</v>
+        <v>0.0261526785149579</v>
       </c>
       <c r="N218" t="n">
-        <v>0.03038691417367655</v>
+        <v>0.0303869141736765</v>
       </c>
       <c r="O218" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.0453900003433227</v>
       </c>
       <c r="P218" t="n">
-        <v>-0.0150030861696462</v>
+        <v>-0.0150030861696461</v>
       </c>
     </row>
     <row r="219">
@@ -13131,16 +13131,16 @@
         <v>23.802048</v>
       </c>
       <c r="M219" t="n">
-        <v>0.005487269534679543</v>
+        <v>0.0054872695346795</v>
       </c>
       <c r="N219" t="n">
-        <v>0.02423769022534387</v>
+        <v>0.0242376902253438</v>
       </c>
       <c r="O219" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.0453900003433227</v>
       </c>
       <c r="P219" t="n">
-        <v>-0.02115231011797888</v>
+        <v>-0.0211523101179788</v>
       </c>
     </row>
     <row r="220">
@@ -13189,16 +13189,16 @@
         <v>3.577709</v>
       </c>
       <c r="M220" t="n">
-        <v>0.03116904145077721</v>
+        <v>0.0311690414507772</v>
       </c>
       <c r="N220" t="n">
-        <v>0.04004177461139897</v>
+        <v>0.0400417746113989</v>
       </c>
       <c r="O220" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.0453900003433227</v>
       </c>
       <c r="P220" t="n">
-        <v>-0.005348225731923784</v>
+        <v>-0.0053482257319237</v>
       </c>
     </row>
     <row r="221">
@@ -13247,16 +13247,16 @@
         <v>25.28739</v>
       </c>
       <c r="M221" t="n">
-        <v>0.01500835182368926</v>
+        <v>0.0150083518236892</v>
       </c>
       <c r="N221" t="n">
-        <v>0.04835526414200593</v>
+        <v>0.0483552641420059</v>
       </c>
       <c r="O221" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.0453900003433227</v>
       </c>
       <c r="P221" t="n">
-        <v>0.002965263798683178</v>
+        <v>0.0029652637986831</v>
       </c>
     </row>
     <row r="222">
@@ -13305,16 +13305,16 @@
         <v>10.288911</v>
       </c>
       <c r="M222" t="n">
-        <v>0.03674489108466202</v>
+        <v>0.036744891084662</v>
       </c>
       <c r="N222" t="n">
-        <v>0.04086548394340894</v>
+        <v>0.0408654839434089</v>
       </c>
       <c r="O222" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.0453900003433227</v>
       </c>
       <c r="P222" t="n">
-        <v>-0.004524516399913817</v>
+        <v>-0.0045245163999138</v>
       </c>
     </row>
     <row r="223">
@@ -13363,13 +13363,13 @@
         <v>7.456928</v>
       </c>
       <c r="M223" t="n">
-        <v>0.04354848926331792</v>
+        <v>0.0435484892633179</v>
       </c>
       <c r="N223" t="n">
-        <v>0.05832981250395895</v>
+        <v>0.0583298125039589</v>
       </c>
       <c r="O223" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.0453900003433227</v>
       </c>
       <c r="P223" t="n">
         <v>0.0129398121606362</v>
@@ -13427,10 +13427,10 @@
         <v>0.0503599229888646</v>
       </c>
       <c r="O224" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.0453900003433227</v>
       </c>
       <c r="P224" t="n">
-        <v>0.004969922645541851</v>
+        <v>0.0049699226455418</v>
       </c>
     </row>
     <row r="225">
@@ -13479,16 +13479,16 @@
         <v>6.7773304</v>
       </c>
       <c r="M225" t="n">
-        <v>0.04107592420829469</v>
+        <v>0.0410759242082946</v>
       </c>
       <c r="N225" t="n">
-        <v>0.05090897045183516</v>
+        <v>0.0509089704518351</v>
       </c>
       <c r="O225" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.0453900003433227</v>
       </c>
       <c r="P225" t="n">
-        <v>0.005518970108512412</v>
+        <v>0.0055189701085124</v>
       </c>
     </row>
     <row r="226">
@@ -13540,13 +13540,535 @@
         <v>0.0322023868231581</v>
       </c>
       <c r="N226" t="n">
-        <v>0.06294422526876418</v>
+        <v>0.0629442252687641</v>
       </c>
       <c r="O226" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.0453900003433227</v>
       </c>
       <c r="P226" t="n">
-        <v>0.01755422492544143</v>
+        <v>0.0175542249254414</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>315.32</v>
+      </c>
+      <c r="F227" t="n">
+        <v>4631217307648</v>
+      </c>
+      <c r="G227" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H227" t="n">
+        <v>9.60895</v>
+      </c>
+      <c r="I227" t="n">
+        <v>38.220608</v>
+      </c>
+      <c r="J227" t="n">
+        <v>32.815243</v>
+      </c>
+      <c r="K227" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="L227" t="n">
+        <v>10.25872</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0.02616389699353038</v>
+      </c>
+      <c r="N227" t="n">
+        <v>0.03047364582011924</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P227" t="n">
+        <v>-0.01521635185291542</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>557.89</v>
+      </c>
+      <c r="F228" t="n">
+        <v>909695778816</v>
+      </c>
+      <c r="G228" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="H228" t="n">
+        <v>13.28145</v>
+      </c>
+      <c r="I228" t="n">
+        <v>185.34552</v>
+      </c>
+      <c r="J228" t="n">
+        <v>42.005203</v>
+      </c>
+      <c r="K228" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L228" t="n">
+        <v>24.288347</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0.005395328828263636</v>
+      </c>
+      <c r="N228" t="n">
+        <v>0.02380657477280467</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P228" t="n">
+        <v>-0.02188342290022999</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>245.34</v>
+      </c>
+      <c r="F229" t="n">
+        <v>2639149400064</v>
+      </c>
+      <c r="G229" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="H229" t="n">
+        <v>9.891920000000001</v>
+      </c>
+      <c r="I229" t="n">
+        <v>31.413572</v>
+      </c>
+      <c r="J229" t="n">
+        <v>24.80206</v>
+      </c>
+      <c r="K229" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L229" t="n">
+        <v>3.5530894</v>
+      </c>
+      <c r="M229" t="n">
+        <v>0.03183337409309529</v>
+      </c>
+      <c r="N229" t="n">
+        <v>0.04031923045569414</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P229" t="n">
+        <v>-0.005370767217340526</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>399.97</v>
+      </c>
+      <c r="F230" t="n">
+        <v>1902889402368</v>
+      </c>
+      <c r="G230" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H230" t="n">
+        <v>19.39578</v>
+      </c>
+      <c r="I230" t="n">
+        <v>66.4402</v>
+      </c>
+      <c r="J230" t="n">
+        <v>20.621496</v>
+      </c>
+      <c r="K230" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L230" t="n">
+        <v>25.215523</v>
+      </c>
+      <c r="M230" t="n">
+        <v>0.0150511288346626</v>
+      </c>
+      <c r="N230" t="n">
+        <v>0.04849308698152361</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P230" t="n">
+        <v>0.002803089308488944</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>355.03</v>
+      </c>
+      <c r="F231" t="n">
+        <v>4332279300096</v>
+      </c>
+      <c r="G231" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="H231" t="n">
+        <v>14.5725</v>
+      </c>
+      <c r="I231" t="n">
+        <v>27.080854</v>
+      </c>
+      <c r="J231" t="n">
+        <v>24.363012</v>
+      </c>
+      <c r="K231" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L231" t="n">
+        <v>10.253963</v>
+      </c>
+      <c r="M231" t="n">
+        <v>0.0369264569191336</v>
+      </c>
+      <c r="N231" t="n">
+        <v>0.0410458271132017</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P231" t="n">
+        <v>-0.004644170559832961</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>669.21</v>
+      </c>
+      <c r="F232" t="n">
+        <v>1698738339840</v>
+      </c>
+      <c r="G232" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="H232" t="n">
+        <v>36.32896</v>
+      </c>
+      <c r="I232" t="n">
+        <v>24.361486</v>
+      </c>
+      <c r="J232" t="n">
+        <v>18.420841</v>
+      </c>
+      <c r="K232" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L232" t="n">
+        <v>7.9024687</v>
+      </c>
+      <c r="M232" t="n">
+        <v>0.04104840035265462</v>
+      </c>
+      <c r="N232" t="n">
+        <v>0.05428633762197218</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P232" t="n">
+        <v>0.008596339948937513</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="F233" t="n">
+        <v>2860690440192</v>
+      </c>
+      <c r="G233" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H233" t="n">
+        <v>19.35995</v>
+      </c>
+      <c r="I233" t="n">
+        <v>22.92262</v>
+      </c>
+      <c r="J233" t="n">
+        <v>19.89158</v>
+      </c>
+      <c r="K233" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L233" t="n">
+        <v>8.988166</v>
+      </c>
+      <c r="M233" t="n">
+        <v>0.04362503245910153</v>
+      </c>
+      <c r="N233" t="n">
+        <v>0.05027252661646325</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P233" t="n">
+        <v>0.004582528943428588</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>73.37</v>
+      </c>
+      <c r="F234" t="n">
+        <v>308946305024</v>
+      </c>
+      <c r="G234" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H234" t="n">
+        <v>3.8421</v>
+      </c>
+      <c r="I234" t="n">
+        <v>23.667744</v>
+      </c>
+      <c r="J234" t="n">
+        <v>19.096329</v>
+      </c>
+      <c r="K234" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L234" t="n">
+        <v>6.588747</v>
+      </c>
+      <c r="M234" t="n">
+        <v>0.04225160147199128</v>
+      </c>
+      <c r="N234" t="n">
+        <v>0.0523660896824315</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P234" t="n">
+        <v>0.006676092009396839</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>210.96</v>
+      </c>
+      <c r="F235" t="n">
+        <v>5109662089216</v>
+      </c>
+      <c r="G235" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H235" t="n">
+        <v>12.79003</v>
+      </c>
+      <c r="I235" t="n">
+        <v>32.30628</v>
+      </c>
+      <c r="J235" t="n">
+        <v>16.494099</v>
+      </c>
+      <c r="K235" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L235" t="n">
+        <v>20.157173</v>
+      </c>
+      <c r="M235" t="n">
+        <v>0.03095373530527114</v>
+      </c>
+      <c r="N235" t="n">
+        <v>0.06062774933636708</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P235" t="n">
+        <v>0.01493775166333242</v>
       </c>
     </row>
   </sheetData>
@@ -13648,12 +14170,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -13667,51 +14189,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>356.24</v>
+        <v>355.03</v>
       </c>
       <c r="F2" t="n">
-        <v>4347044298752</v>
+        <v>4332279300096</v>
       </c>
       <c r="G2" t="n">
-        <v>13.09</v>
+        <v>13.11</v>
       </c>
       <c r="H2" t="n">
-        <v>14.55792</v>
+        <v>14.5725</v>
       </c>
       <c r="I2" t="n">
-        <v>27.214666</v>
+        <v>27.080854</v>
       </c>
       <c r="J2" t="n">
-        <v>24.470528</v>
+        <v>24.363012</v>
       </c>
       <c r="K2" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="L2" t="n">
-        <v>10.288911</v>
+        <v>10.253963</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03674489108466202</v>
+        <v>0.0369264569191336</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04086548394340894</v>
+        <v>0.0410458271132017</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.004524516399913817</v>
+        <v>-0.004644170559832961</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -13725,51 +14247,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>384.36</v>
+        <v>385.1</v>
       </c>
       <c r="F3" t="n">
-        <v>2855193018368</v>
+        <v>2860690440192</v>
       </c>
       <c r="G3" t="n">
-        <v>16.79</v>
+        <v>16.8</v>
       </c>
       <c r="H3" t="n">
-        <v>19.35634</v>
+        <v>19.35995</v>
       </c>
       <c r="I3" t="n">
-        <v>22.892195</v>
+        <v>22.92262</v>
       </c>
       <c r="J3" t="n">
-        <v>19.85706</v>
+        <v>19.89158</v>
       </c>
       <c r="K3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="L3" t="n">
-        <v>8.970893</v>
+        <v>8.988166</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0436830055156624</v>
+        <v>0.04362503245910153</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0503599229888646</v>
+        <v>0.05027252661646325</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004969922645541851</v>
+        <v>0.004582528943428588</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -13783,51 +14305,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>631.48</v>
+        <v>669.21</v>
       </c>
       <c r="F4" t="n">
-        <v>1602963505152</v>
+        <v>1698738339840</v>
       </c>
       <c r="G4" t="n">
-        <v>27.5</v>
+        <v>27.47</v>
       </c>
       <c r="H4" t="n">
-        <v>36.83411</v>
+        <v>36.32896</v>
       </c>
       <c r="I4" t="n">
-        <v>22.962908</v>
+        <v>24.361486</v>
       </c>
       <c r="J4" t="n">
-        <v>17.14389</v>
+        <v>18.420841</v>
       </c>
       <c r="K4" t="n">
         <v>0.87</v>
       </c>
       <c r="L4" t="n">
-        <v>7.456928</v>
+        <v>7.9024687</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04354848926331792</v>
+        <v>0.04104840035265462</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05832981250395895</v>
+        <v>0.05428633762197218</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0129398121606362</v>
+        <v>0.008596339948937513</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -13841,51 +14363,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>247.04</v>
+        <v>245.34</v>
       </c>
       <c r="F5" t="n">
-        <v>2657436303360</v>
+        <v>2639149400064</v>
       </c>
       <c r="G5" t="n">
-        <v>7.7</v>
+        <v>7.81</v>
       </c>
       <c r="H5" t="n">
         <v>9.891920000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>32.08312</v>
+        <v>31.413572</v>
       </c>
       <c r="J5" t="n">
-        <v>24.973917</v>
+        <v>24.80206</v>
       </c>
       <c r="K5" t="n">
         <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>3.577709</v>
+        <v>3.5530894</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03116904145077721</v>
+        <v>0.03183337409309529</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04004177461139897</v>
+        <v>0.04031923045569414</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.005348225731923784</v>
+        <v>-0.005370767217340526</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -13899,51 +14421,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>316.22</v>
+        <v>315.32</v>
       </c>
       <c r="F6" t="n">
-        <v>4644435656704</v>
+        <v>4631217307648</v>
       </c>
       <c r="G6" t="n">
-        <v>8.27</v>
+        <v>8.25</v>
       </c>
       <c r="H6" t="n">
         <v>9.60895</v>
       </c>
       <c r="I6" t="n">
-        <v>38.237</v>
+        <v>38.220608</v>
       </c>
       <c r="J6" t="n">
-        <v>32.908905</v>
+        <v>32.815243</v>
       </c>
       <c r="K6" t="n">
         <v>2.53</v>
       </c>
       <c r="L6" t="n">
-        <v>10.288</v>
+        <v>10.25872</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02615267851495794</v>
+        <v>0.02616389699353038</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03038691417367655</v>
+        <v>0.03047364582011924</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0150030861696462</v>
+        <v>-0.01521635185291542</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -13957,51 +14479,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>202.78</v>
+        <v>210.96</v>
       </c>
       <c r="F7" t="n">
-        <v>4911534178304</v>
+        <v>5109662089216</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
       </c>
       <c r="H7" t="n">
-        <v>12.76383</v>
+        <v>12.79003</v>
       </c>
       <c r="I7" t="n">
-        <v>31.053598</v>
+        <v>32.30628</v>
       </c>
       <c r="J7" t="n">
-        <v>15.88708</v>
+        <v>16.494099</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="L7" t="n">
-        <v>19.375576</v>
+        <v>20.157173</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0322023868231581</v>
+        <v>0.03095373530527114</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06294422526876418</v>
+        <v>0.06062774933636708</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01755422492544143</v>
+        <v>0.01493775166333242</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -14015,51 +14537,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>546.72</v>
+        <v>557.89</v>
       </c>
       <c r="F8" t="n">
-        <v>891481882624</v>
+        <v>909695778816</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="H8" t="n">
-        <v>13.25123</v>
+        <v>13.28145</v>
       </c>
       <c r="I8" t="n">
-        <v>182.23999</v>
+        <v>185.34552</v>
       </c>
       <c r="J8" t="n">
-        <v>41.258053</v>
+        <v>42.005203</v>
       </c>
       <c r="K8" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="L8" t="n">
-        <v>23.802048</v>
+        <v>24.288347</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005487269534679543</v>
+        <v>0.005395328828263636</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02423769022534387</v>
+        <v>0.02380657477280467</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02115231011797888</v>
+        <v>-0.02188342290022999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14073,10 +14595,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>401.11</v>
+        <v>399.97</v>
       </c>
       <c r="F9" t="n">
-        <v>1908312899584</v>
+        <v>1902889402368</v>
       </c>
       <c r="G9" t="n">
         <v>6.02</v>
@@ -14085,39 +14607,39 @@
         <v>19.39578</v>
       </c>
       <c r="I9" t="n">
-        <v>66.62956</v>
+        <v>66.4402</v>
       </c>
       <c r="J9" t="n">
-        <v>20.680271</v>
+        <v>20.621496</v>
       </c>
       <c r="K9" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="L9" t="n">
-        <v>25.28739</v>
+        <v>25.215523</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01500835182368926</v>
+        <v>0.0150511288346626</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04835526414200593</v>
+        <v>0.04849308698152361</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002965263798683178</v>
+        <v>0.002803089308488944</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -14131,10 +14653,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>75.47</v>
+        <v>73.37</v>
       </c>
       <c r="F10" t="n">
-        <v>317788979200</v>
+        <v>308946305024</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -14143,28 +14665,28 @@
         <v>3.8421</v>
       </c>
       <c r="I10" t="n">
-        <v>24.345163</v>
+        <v>23.667744</v>
       </c>
       <c r="J10" t="n">
-        <v>19.642904</v>
+        <v>19.096329</v>
       </c>
       <c r="K10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="L10" t="n">
-        <v>6.7773304</v>
+        <v>6.588747</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04107592420829469</v>
+        <v>0.04225160147199128</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05090897045183516</v>
+        <v>0.0523660896824315</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04539000034332275</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005518970108512412</v>
+        <v>0.006676092009396839</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P235"/>
+  <dimension ref="A1:P244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13595,16 +13595,16 @@
         <v>10.25872</v>
       </c>
       <c r="M227" t="n">
-        <v>0.02616389699353038</v>
+        <v>0.0261638969935303</v>
       </c>
       <c r="N227" t="n">
-        <v>0.03047364582011924</v>
+        <v>0.0304736458201192</v>
       </c>
       <c r="O227" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P227" t="n">
-        <v>-0.01521635185291542</v>
+        <v>-0.0152163518529154</v>
       </c>
     </row>
     <row r="228">
@@ -13653,16 +13653,16 @@
         <v>24.288347</v>
       </c>
       <c r="M228" t="n">
-        <v>0.005395328828263636</v>
+        <v>0.0053953288282636</v>
       </c>
       <c r="N228" t="n">
-        <v>0.02380657477280467</v>
+        <v>0.0238065747728046</v>
       </c>
       <c r="O228" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P228" t="n">
-        <v>-0.02188342290022999</v>
+        <v>-0.0218834229002299</v>
       </c>
     </row>
     <row r="229">
@@ -13711,16 +13711,16 @@
         <v>3.5530894</v>
       </c>
       <c r="M229" t="n">
-        <v>0.03183337409309529</v>
+        <v>0.0318333740930952</v>
       </c>
       <c r="N229" t="n">
-        <v>0.04031923045569414</v>
+        <v>0.0403192304556941</v>
       </c>
       <c r="O229" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P229" t="n">
-        <v>-0.005370767217340526</v>
+        <v>-0.0053707672173405</v>
       </c>
     </row>
     <row r="230">
@@ -13769,16 +13769,16 @@
         <v>25.215523</v>
       </c>
       <c r="M230" t="n">
-        <v>0.0150511288346626</v>
+        <v>0.0150511288346625</v>
       </c>
       <c r="N230" t="n">
-        <v>0.04849308698152361</v>
+        <v>0.0484930869815236</v>
       </c>
       <c r="O230" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P230" t="n">
-        <v>0.002803089308488944</v>
+        <v>0.0028030893084889</v>
       </c>
     </row>
     <row r="231">
@@ -13833,10 +13833,10 @@
         <v>0.0410458271132017</v>
       </c>
       <c r="O231" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P231" t="n">
-        <v>-0.004644170559832961</v>
+        <v>-0.0046441705598329</v>
       </c>
     </row>
     <row r="232">
@@ -13885,16 +13885,16 @@
         <v>7.9024687</v>
       </c>
       <c r="M232" t="n">
-        <v>0.04104840035265462</v>
+        <v>0.0410484003526546</v>
       </c>
       <c r="N232" t="n">
-        <v>0.05428633762197218</v>
+        <v>0.0542863376219721</v>
       </c>
       <c r="O232" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P232" t="n">
-        <v>0.008596339948937513</v>
+        <v>0.008596339948937499</v>
       </c>
     </row>
     <row r="233">
@@ -13943,16 +13943,16 @@
         <v>8.988166</v>
       </c>
       <c r="M233" t="n">
-        <v>0.04362503245910153</v>
+        <v>0.0436250324591015</v>
       </c>
       <c r="N233" t="n">
-        <v>0.05027252661646325</v>
+        <v>0.0502725266164632</v>
       </c>
       <c r="O233" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P233" t="n">
-        <v>0.004582528943428588</v>
+        <v>0.0045825289434285</v>
       </c>
     </row>
     <row r="234">
@@ -14001,16 +14001,16 @@
         <v>6.588747</v>
       </c>
       <c r="M234" t="n">
-        <v>0.04225160147199128</v>
+        <v>0.0422516014719912</v>
       </c>
       <c r="N234" t="n">
         <v>0.0523660896824315</v>
       </c>
       <c r="O234" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P234" t="n">
-        <v>0.006676092009396839</v>
+        <v>0.0066760920093968</v>
       </c>
     </row>
     <row r="235">
@@ -14059,16 +14059,538 @@
         <v>20.157173</v>
       </c>
       <c r="M235" t="n">
-        <v>0.03095373530527114</v>
+        <v>0.0309537353052711</v>
       </c>
       <c r="N235" t="n">
-        <v>0.06062774933636708</v>
+        <v>0.060627749336367</v>
       </c>
       <c r="O235" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P235" t="n">
-        <v>0.01493775166333242</v>
+        <v>0.0149377516633324</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>317.31</v>
+      </c>
+      <c r="F236" t="n">
+        <v>4660444790784</v>
+      </c>
+      <c r="G236" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H236" t="n">
+        <v>9.612740000000001</v>
+      </c>
+      <c r="I236" t="n">
+        <v>38.415253</v>
+      </c>
+      <c r="J236" t="n">
+        <v>33.00932</v>
+      </c>
+      <c r="K236" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L236" t="n">
+        <v>10.3234625</v>
+      </c>
+      <c r="M236" t="n">
+        <v>0.02603132583278182</v>
+      </c>
+      <c r="N236" t="n">
+        <v>0.03029447543411806</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0.04609000205993653</v>
+      </c>
+      <c r="P236" t="n">
+        <v>-0.01579552662581847</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>534.39</v>
+      </c>
+      <c r="F237" t="n">
+        <v>871376683008</v>
+      </c>
+      <c r="G237" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="H237" t="n">
+        <v>13.28145</v>
+      </c>
+      <c r="I237" t="n">
+        <v>177.53821</v>
+      </c>
+      <c r="J237" t="n">
+        <v>40.235817</v>
+      </c>
+      <c r="K237" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L237" t="n">
+        <v>23.26525</v>
+      </c>
+      <c r="M237" t="n">
+        <v>0.005632590430210146</v>
+      </c>
+      <c r="N237" t="n">
+        <v>0.02485347779711447</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0.04609000205993653</v>
+      </c>
+      <c r="P237" t="n">
+        <v>-0.02123652426282206</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>247.31</v>
+      </c>
+      <c r="F238" t="n">
+        <v>2660340858880</v>
+      </c>
+      <c r="G238" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="H238" t="n">
+        <v>9.88631</v>
+      </c>
+      <c r="I238" t="n">
+        <v>29.547192</v>
+      </c>
+      <c r="J238" t="n">
+        <v>25.0154</v>
+      </c>
+      <c r="K238" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L238" t="n">
+        <v>3.5816195</v>
+      </c>
+      <c r="M238" t="n">
+        <v>0.03384416319598884</v>
+      </c>
+      <c r="N238" t="n">
+        <v>0.0399753750353807</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0.04609000205993653</v>
+      </c>
+      <c r="P238" t="n">
+        <v>-0.006114627024555827</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>384.05</v>
+      </c>
+      <c r="F239" t="n">
+        <v>1827148660736</v>
+      </c>
+      <c r="G239" t="n">
+        <v>6</v>
+      </c>
+      <c r="H239" t="n">
+        <v>19.39578</v>
+      </c>
+      <c r="I239" t="n">
+        <v>64.00833</v>
+      </c>
+      <c r="J239" t="n">
+        <v>19.800697</v>
+      </c>
+      <c r="K239" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L239" t="n">
+        <v>24.211868</v>
+      </c>
+      <c r="M239" t="n">
+        <v>0.01562296575966671</v>
+      </c>
+      <c r="N239" t="n">
+        <v>0.05050326780367139</v>
+      </c>
+      <c r="O239" t="n">
+        <v>0.04609000205993653</v>
+      </c>
+      <c r="P239" t="n">
+        <v>0.004413265743734865</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>350.67</v>
+      </c>
+      <c r="F240" t="n">
+        <v>4279076388864</v>
+      </c>
+      <c r="G240" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H240" t="n">
+        <v>14.63415</v>
+      </c>
+      <c r="I240" t="n">
+        <v>26.768703</v>
+      </c>
+      <c r="J240" t="n">
+        <v>23.962446</v>
+      </c>
+      <c r="K240" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L240" t="n">
+        <v>10.128039</v>
+      </c>
+      <c r="M240" t="n">
+        <v>0.03735705934354236</v>
+      </c>
+      <c r="N240" t="n">
+        <v>0.04173197022841988</v>
+      </c>
+      <c r="O240" t="n">
+        <v>0.04609000205993653</v>
+      </c>
+      <c r="P240" t="n">
+        <v>-0.004358031831516646</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>656.73</v>
+      </c>
+      <c r="F241" t="n">
+        <v>1667058630656</v>
+      </c>
+      <c r="G241" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H241" t="n">
+        <v>36.32896</v>
+      </c>
+      <c r="I241" t="n">
+        <v>23.88109</v>
+      </c>
+      <c r="J241" t="n">
+        <v>18.077312</v>
+      </c>
+      <c r="K241" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L241" t="n">
+        <v>7.755096</v>
+      </c>
+      <c r="M241" t="n">
+        <v>0.04187413396677478</v>
+      </c>
+      <c r="N241" t="n">
+        <v>0.05531795410594918</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0.04609000205993653</v>
+      </c>
+      <c r="P241" t="n">
+        <v>0.00922795204601265</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>390.99</v>
+      </c>
+      <c r="F242" t="n">
+        <v>2904443584512</v>
+      </c>
+      <c r="G242" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="H242" t="n">
+        <v>19.35995</v>
+      </c>
+      <c r="I242" t="n">
+        <v>23.287073</v>
+      </c>
+      <c r="J242" t="n">
+        <v>20.195818</v>
+      </c>
+      <c r="K242" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L242" t="n">
+        <v>9.125636</v>
+      </c>
+      <c r="M242" t="n">
+        <v>0.04294227473848436</v>
+      </c>
+      <c r="N242" t="n">
+        <v>0.04951520499245505</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0.04609000205993653</v>
+      </c>
+      <c r="P242" t="n">
+        <v>0.003425202932518523</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>73.83</v>
+      </c>
+      <c r="F243" t="n">
+        <v>310883254272</v>
+      </c>
+      <c r="G243" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H243" t="n">
+        <v>3.838</v>
+      </c>
+      <c r="I243" t="n">
+        <v>23.81613</v>
+      </c>
+      <c r="J243" t="n">
+        <v>19.236582</v>
+      </c>
+      <c r="K243" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L243" t="n">
+        <v>6.6300554</v>
+      </c>
+      <c r="M243" t="n">
+        <v>0.04198835161858323</v>
+      </c>
+      <c r="N243" t="n">
+        <v>0.05198428822971692</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0.04609000205993653</v>
+      </c>
+      <c r="P243" t="n">
+        <v>0.005894286169780397</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>203.53</v>
+      </c>
+      <c r="F244" t="n">
+        <v>4929700233216</v>
+      </c>
+      <c r="G244" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="H244" t="n">
+        <v>12.79063</v>
+      </c>
+      <c r="I244" t="n">
+        <v>31.120794</v>
+      </c>
+      <c r="J244" t="n">
+        <v>15.912429</v>
+      </c>
+      <c r="K244" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L244" t="n">
+        <v>19.447239</v>
+      </c>
+      <c r="M244" t="n">
+        <v>0.03213285510735518</v>
+      </c>
+      <c r="N244" t="n">
+        <v>0.06284395420822483</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0.04609000205993653</v>
+      </c>
+      <c r="P244" t="n">
+        <v>0.01675395214828831</v>
       </c>
     </row>
   </sheetData>
@@ -14170,12 +14692,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -14189,51 +14711,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>355.03</v>
+        <v>350.67</v>
       </c>
       <c r="F2" t="n">
-        <v>4332279300096</v>
+        <v>4279076388864</v>
       </c>
       <c r="G2" t="n">
-        <v>13.11</v>
+        <v>13.1</v>
       </c>
       <c r="H2" t="n">
-        <v>14.5725</v>
+        <v>14.63415</v>
       </c>
       <c r="I2" t="n">
-        <v>27.080854</v>
+        <v>26.768703</v>
       </c>
       <c r="J2" t="n">
-        <v>24.363012</v>
+        <v>23.962446</v>
       </c>
       <c r="K2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="L2" t="n">
-        <v>10.253963</v>
+        <v>10.128039</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0369264569191336</v>
+        <v>0.03735705934354236</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0410458271132017</v>
+        <v>0.04173197022841988</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04609000205993653</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.004644170559832961</v>
+        <v>-0.004358031831516646</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -14247,51 +14769,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>385.1</v>
+        <v>390.99</v>
       </c>
       <c r="F3" t="n">
-        <v>2860690440192</v>
+        <v>2904443584512</v>
       </c>
       <c r="G3" t="n">
-        <v>16.8</v>
+        <v>16.79</v>
       </c>
       <c r="H3" t="n">
         <v>19.35995</v>
       </c>
       <c r="I3" t="n">
-        <v>22.92262</v>
+        <v>23.287073</v>
       </c>
       <c r="J3" t="n">
-        <v>19.89158</v>
+        <v>20.195818</v>
       </c>
       <c r="K3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="L3" t="n">
-        <v>8.988166</v>
+        <v>9.125636</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04362503245910153</v>
+        <v>0.04294227473848436</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05027252661646325</v>
+        <v>0.04951520499245505</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04609000205993653</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004582528943428588</v>
+        <v>0.003425202932518523</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -14305,51 +14827,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>669.21</v>
+        <v>656.73</v>
       </c>
       <c r="F4" t="n">
-        <v>1698738339840</v>
+        <v>1667058630656</v>
       </c>
       <c r="G4" t="n">
-        <v>27.47</v>
+        <v>27.5</v>
       </c>
       <c r="H4" t="n">
         <v>36.32896</v>
       </c>
       <c r="I4" t="n">
-        <v>24.361486</v>
+        <v>23.88109</v>
       </c>
       <c r="J4" t="n">
-        <v>18.420841</v>
+        <v>18.077312</v>
       </c>
       <c r="K4" t="n">
-        <v>0.87</v>
+        <v>0.97</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9024687</v>
+        <v>7.755096</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04104840035265462</v>
+        <v>0.04187413396677478</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05428633762197218</v>
+        <v>0.05531795410594918</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04609000205993653</v>
       </c>
       <c r="P4" t="n">
-        <v>0.008596339948937513</v>
+        <v>0.00922795204601265</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -14363,51 +14885,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>245.34</v>
+        <v>247.31</v>
       </c>
       <c r="F5" t="n">
-        <v>2639149400064</v>
+        <v>2660340858880</v>
       </c>
       <c r="G5" t="n">
-        <v>7.81</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>9.891920000000001</v>
+        <v>9.88631</v>
       </c>
       <c r="I5" t="n">
-        <v>31.413572</v>
+        <v>29.547192</v>
       </c>
       <c r="J5" t="n">
-        <v>24.80206</v>
+        <v>25.0154</v>
       </c>
       <c r="K5" t="n">
-        <v>1.83</v>
+        <v>1.41</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5530894</v>
+        <v>3.5816195</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03183337409309529</v>
+        <v>0.03384416319598884</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04031923045569414</v>
+        <v>0.0399753750353807</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04609000205993653</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.005370767217340526</v>
+        <v>-0.006114627024555827</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -14421,51 +14943,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>315.32</v>
+        <v>317.31</v>
       </c>
       <c r="F6" t="n">
-        <v>4631217307648</v>
+        <v>4660444790784</v>
       </c>
       <c r="G6" t="n">
-        <v>8.25</v>
+        <v>8.26</v>
       </c>
       <c r="H6" t="n">
-        <v>9.60895</v>
+        <v>9.612740000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>38.220608</v>
+        <v>38.415253</v>
       </c>
       <c r="J6" t="n">
-        <v>32.815243</v>
+        <v>33.00932</v>
       </c>
       <c r="K6" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="L6" t="n">
-        <v>10.25872</v>
+        <v>10.3234625</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02616389699353038</v>
+        <v>0.02603132583278182</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03047364582011924</v>
+        <v>0.03029447543411806</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04609000205993653</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01521635185291542</v>
+        <v>-0.01579552662581847</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -14479,51 +15001,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210.96</v>
+        <v>203.53</v>
       </c>
       <c r="F7" t="n">
-        <v>5109662089216</v>
+        <v>4929700233216</v>
       </c>
       <c r="G7" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
       <c r="H7" t="n">
-        <v>12.79003</v>
+        <v>12.79063</v>
       </c>
       <c r="I7" t="n">
-        <v>32.30628</v>
+        <v>31.120794</v>
       </c>
       <c r="J7" t="n">
-        <v>16.494099</v>
+        <v>15.912429</v>
       </c>
       <c r="K7" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="L7" t="n">
-        <v>20.157173</v>
+        <v>19.447239</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03095373530527114</v>
+        <v>0.03213285510735518</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06062774933636708</v>
+        <v>0.06284395420822483</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04609000205993653</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01493775166333242</v>
+        <v>0.01675395214828831</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -14537,10 +15059,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>557.89</v>
+        <v>534.39</v>
       </c>
       <c r="F8" t="n">
-        <v>909695778816</v>
+        <v>871376683008</v>
       </c>
       <c r="G8" t="n">
         <v>3.01</v>
@@ -14549,39 +15071,39 @@
         <v>13.28145</v>
       </c>
       <c r="I8" t="n">
-        <v>185.34552</v>
+        <v>177.53821</v>
       </c>
       <c r="J8" t="n">
-        <v>42.005203</v>
+        <v>40.235817</v>
       </c>
       <c r="K8" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="L8" t="n">
-        <v>24.288347</v>
+        <v>23.26525</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005395328828263636</v>
+        <v>0.005632590430210146</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02380657477280467</v>
+        <v>0.02485347779711447</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04609000205993653</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02188342290022999</v>
+        <v>-0.02123652426282206</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14595,51 +15117,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>399.97</v>
+        <v>384.05</v>
       </c>
       <c r="F9" t="n">
-        <v>1902889402368</v>
+        <v>1827148660736</v>
       </c>
       <c r="G9" t="n">
-        <v>6.02</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>19.39578</v>
       </c>
       <c r="I9" t="n">
-        <v>66.4402</v>
+        <v>64.00833</v>
       </c>
       <c r="J9" t="n">
-        <v>20.621496</v>
+        <v>19.800697</v>
       </c>
       <c r="K9" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="L9" t="n">
-        <v>25.215523</v>
+        <v>24.211868</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0150511288346626</v>
+        <v>0.01562296575966671</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04849308698152361</v>
+        <v>0.05050326780367139</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04609000205993653</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002803089308488944</v>
+        <v>0.004413265743734865</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -14653,40 +15175,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73.37</v>
+        <v>73.83</v>
       </c>
       <c r="F10" t="n">
-        <v>308946305024</v>
+        <v>310883254272</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8421</v>
+        <v>3.838</v>
       </c>
       <c r="I10" t="n">
-        <v>23.667744</v>
+        <v>23.81613</v>
       </c>
       <c r="J10" t="n">
-        <v>19.096329</v>
+        <v>19.236582</v>
       </c>
       <c r="K10" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="L10" t="n">
-        <v>6.588747</v>
+        <v>6.6300554</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04225160147199128</v>
+        <v>0.04198835161858323</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0523660896824315</v>
+        <v>0.05198428822971692</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04609000205993653</v>
       </c>
       <c r="P10" t="n">
-        <v>0.006676092009396839</v>
+        <v>0.005894286169780397</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P244"/>
+  <dimension ref="A1:P253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14117,16 +14117,16 @@
         <v>10.3234625</v>
       </c>
       <c r="M236" t="n">
-        <v>0.02603132583278182</v>
+        <v>0.0260313258327818</v>
       </c>
       <c r="N236" t="n">
-        <v>0.03029447543411806</v>
+        <v>0.030294475434118</v>
       </c>
       <c r="O236" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.0460900020599365</v>
       </c>
       <c r="P236" t="n">
-        <v>-0.01579552662581847</v>
+        <v>-0.0157955266258184</v>
       </c>
     </row>
     <row r="237">
@@ -14175,16 +14175,16 @@
         <v>23.26525</v>
       </c>
       <c r="M237" t="n">
-        <v>0.005632590430210146</v>
+        <v>0.0056325904302101</v>
       </c>
       <c r="N237" t="n">
-        <v>0.02485347779711447</v>
+        <v>0.0248534777971144</v>
       </c>
       <c r="O237" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.0460900020599365</v>
       </c>
       <c r="P237" t="n">
-        <v>-0.02123652426282206</v>
+        <v>-0.021236524262822</v>
       </c>
     </row>
     <row r="238">
@@ -14233,16 +14233,16 @@
         <v>3.5816195</v>
       </c>
       <c r="M238" t="n">
-        <v>0.03384416319598884</v>
+        <v>0.0338441631959888</v>
       </c>
       <c r="N238" t="n">
         <v>0.0399753750353807</v>
       </c>
       <c r="O238" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.0460900020599365</v>
       </c>
       <c r="P238" t="n">
-        <v>-0.006114627024555827</v>
+        <v>-0.0061146270245558</v>
       </c>
     </row>
     <row r="239">
@@ -14291,16 +14291,16 @@
         <v>24.211868</v>
       </c>
       <c r="M239" t="n">
-        <v>0.01562296575966671</v>
+        <v>0.0156229657596667</v>
       </c>
       <c r="N239" t="n">
-        <v>0.05050326780367139</v>
+        <v>0.0505032678036713</v>
       </c>
       <c r="O239" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.0460900020599365</v>
       </c>
       <c r="P239" t="n">
-        <v>0.004413265743734865</v>
+        <v>0.0044132657437348</v>
       </c>
     </row>
     <row r="240">
@@ -14349,16 +14349,16 @@
         <v>10.128039</v>
       </c>
       <c r="M240" t="n">
-        <v>0.03735705934354236</v>
+        <v>0.0373570593435423</v>
       </c>
       <c r="N240" t="n">
-        <v>0.04173197022841988</v>
+        <v>0.0417319702284198</v>
       </c>
       <c r="O240" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.0460900020599365</v>
       </c>
       <c r="P240" t="n">
-        <v>-0.004358031831516646</v>
+        <v>-0.0043580318315166</v>
       </c>
     </row>
     <row r="241">
@@ -14407,16 +14407,16 @@
         <v>7.755096</v>
       </c>
       <c r="M241" t="n">
-        <v>0.04187413396677478</v>
+        <v>0.0418741339667747</v>
       </c>
       <c r="N241" t="n">
-        <v>0.05531795410594918</v>
+        <v>0.0553179541059491</v>
       </c>
       <c r="O241" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.0460900020599365</v>
       </c>
       <c r="P241" t="n">
-        <v>0.00922795204601265</v>
+        <v>0.009227952046012599</v>
       </c>
     </row>
     <row r="242">
@@ -14465,16 +14465,16 @@
         <v>9.125636</v>
       </c>
       <c r="M242" t="n">
-        <v>0.04294227473848436</v>
+        <v>0.0429422747384843</v>
       </c>
       <c r="N242" t="n">
-        <v>0.04951520499245505</v>
+        <v>0.049515204992455</v>
       </c>
       <c r="O242" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.0460900020599365</v>
       </c>
       <c r="P242" t="n">
-        <v>0.003425202932518523</v>
+        <v>0.0034252029325185</v>
       </c>
     </row>
     <row r="243">
@@ -14523,16 +14523,16 @@
         <v>6.6300554</v>
       </c>
       <c r="M243" t="n">
-        <v>0.04198835161858323</v>
+        <v>0.0419883516185832</v>
       </c>
       <c r="N243" t="n">
-        <v>0.05198428822971692</v>
+        <v>0.0519842882297169</v>
       </c>
       <c r="O243" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.0460900020599365</v>
       </c>
       <c r="P243" t="n">
-        <v>0.005894286169780397</v>
+        <v>0.0058942861697803</v>
       </c>
     </row>
     <row r="244">
@@ -14581,16 +14581,538 @@
         <v>19.447239</v>
       </c>
       <c r="M244" t="n">
-        <v>0.03213285510735518</v>
+        <v>0.0321328551073551</v>
       </c>
       <c r="N244" t="n">
-        <v>0.06284395420822483</v>
+        <v>0.06284395420822481</v>
       </c>
       <c r="O244" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.0460900020599365</v>
       </c>
       <c r="P244" t="n">
-        <v>0.01675395214828831</v>
+        <v>0.0167539521482883</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>314.86</v>
+      </c>
+      <c r="F245" t="n">
+        <v>4624460808192</v>
+      </c>
+      <c r="G245" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H245" t="n">
+        <v>9.62082</v>
+      </c>
+      <c r="I245" t="n">
+        <v>38.16485</v>
+      </c>
+      <c r="J245" t="n">
+        <v>32.72694</v>
+      </c>
+      <c r="K245" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L245" t="n">
+        <v>10.243753</v>
+      </c>
+      <c r="M245" t="n">
+        <v>0.02620212157784412</v>
+      </c>
+      <c r="N245" t="n">
+        <v>0.0305558660992187</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0.04585000038146973</v>
+      </c>
+      <c r="P245" t="n">
+        <v>-0.01529413428225103</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>548.13</v>
+      </c>
+      <c r="F246" t="n">
+        <v>893781082112</v>
+      </c>
+      <c r="G246" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H246" t="n">
+        <v>13.33059</v>
+      </c>
+      <c r="I246" t="n">
+        <v>183.32108</v>
+      </c>
+      <c r="J246" t="n">
+        <v>41.11821</v>
+      </c>
+      <c r="K246" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L246" t="n">
+        <v>23.863434</v>
+      </c>
+      <c r="M246" t="n">
+        <v>0.005454910331490705</v>
+      </c>
+      <c r="N246" t="n">
+        <v>0.02432012478791528</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0.04585000038146973</v>
+      </c>
+      <c r="P246" t="n">
+        <v>-0.02152987559355445</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>247.49</v>
+      </c>
+      <c r="F247" t="n">
+        <v>2662277054464</v>
+      </c>
+      <c r="G247" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="H247" t="n">
+        <v>9.88631</v>
+      </c>
+      <c r="I247" t="n">
+        <v>29.604069</v>
+      </c>
+      <c r="J247" t="n">
+        <v>25.03361</v>
+      </c>
+      <c r="K247" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L247" t="n">
+        <v>3.5842261</v>
+      </c>
+      <c r="M247" t="n">
+        <v>0.03377914259161986</v>
+      </c>
+      <c r="N247" t="n">
+        <v>0.03994630086064083</v>
+      </c>
+      <c r="O247" t="n">
+        <v>0.04585000038146973</v>
+      </c>
+      <c r="P247" t="n">
+        <v>-0.005903699520828892</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>389.11</v>
+      </c>
+      <c r="F248" t="n">
+        <v>1851221999616</v>
+      </c>
+      <c r="G248" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="H248" t="n">
+        <v>19.39578</v>
+      </c>
+      <c r="I248" t="n">
+        <v>64.95993</v>
+      </c>
+      <c r="J248" t="n">
+        <v>20.061579</v>
+      </c>
+      <c r="K248" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L248" t="n">
+        <v>24.530869</v>
+      </c>
+      <c r="M248" t="n">
+        <v>0.01539410449487292</v>
+      </c>
+      <c r="N248" t="n">
+        <v>0.04984652154917632</v>
+      </c>
+      <c r="O248" t="n">
+        <v>0.04585000038146973</v>
+      </c>
+      <c r="P248" t="n">
+        <v>0.003996521167706595</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>357.33</v>
+      </c>
+      <c r="F249" t="n">
+        <v>4360345223168</v>
+      </c>
+      <c r="G249" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="H249" t="n">
+        <v>14.59104</v>
+      </c>
+      <c r="I249" t="n">
+        <v>27.235518</v>
+      </c>
+      <c r="J249" t="n">
+        <v>24.489687</v>
+      </c>
+      <c r="K249" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L249" t="n">
+        <v>10.320393</v>
+      </c>
+      <c r="M249" t="n">
+        <v>0.03671676041754121</v>
+      </c>
+      <c r="N249" t="n">
+        <v>0.04083351523801528</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0.04585000038146973</v>
+      </c>
+      <c r="P249" t="n">
+        <v>-0.005016485143454444</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>661.04</v>
+      </c>
+      <c r="F250" t="n">
+        <v>1677999341568</v>
+      </c>
+      <c r="G250" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="H250" t="n">
+        <v>36.32896</v>
+      </c>
+      <c r="I250" t="n">
+        <v>24.020348</v>
+      </c>
+      <c r="J250" t="n">
+        <v>18.195951</v>
+      </c>
+      <c r="K250" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L250" t="n">
+        <v>7.8059916</v>
+      </c>
+      <c r="M250" t="n">
+        <v>0.04163136875226915</v>
+      </c>
+      <c r="N250" t="n">
+        <v>0.05495727943846061</v>
+      </c>
+      <c r="O250" t="n">
+        <v>0.04585000038146973</v>
+      </c>
+      <c r="P250" t="n">
+        <v>0.009107279056990887</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>384.93</v>
+      </c>
+      <c r="F251" t="n">
+        <v>2859427430400</v>
+      </c>
+      <c r="G251" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="H251" t="n">
+        <v>19.35995</v>
+      </c>
+      <c r="I251" t="n">
+        <v>22.953487</v>
+      </c>
+      <c r="J251" t="n">
+        <v>19.8828</v>
+      </c>
+      <c r="K251" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L251" t="n">
+        <v>8.984197999999999</v>
+      </c>
+      <c r="M251" t="n">
+        <v>0.04356636271529889</v>
+      </c>
+      <c r="N251" t="n">
+        <v>0.05029472891175019</v>
+      </c>
+      <c r="O251" t="n">
+        <v>0.04585000038146973</v>
+      </c>
+      <c r="P251" t="n">
+        <v>0.004444728530280467</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>73.53</v>
+      </c>
+      <c r="F252" t="n">
+        <v>309620015104</v>
+      </c>
+      <c r="G252" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H252" t="n">
+        <v>3.83407</v>
+      </c>
+      <c r="I252" t="n">
+        <v>23.719355</v>
+      </c>
+      <c r="J252" t="n">
+        <v>19.178053</v>
+      </c>
+      <c r="K252" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L252" t="n">
+        <v>6.603115</v>
+      </c>
+      <c r="M252" t="n">
+        <v>0.04215966272269822</v>
+      </c>
+      <c r="N252" t="n">
+        <v>0.05214293485652115</v>
+      </c>
+      <c r="O252" t="n">
+        <v>0.04585000038146973</v>
+      </c>
+      <c r="P252" t="n">
+        <v>0.006292934475051422</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>211.8</v>
+      </c>
+      <c r="F253" t="n">
+        <v>5130007609344</v>
+      </c>
+      <c r="G253" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H253" t="n">
+        <v>12.80493</v>
+      </c>
+      <c r="I253" t="n">
+        <v>32.434914</v>
+      </c>
+      <c r="J253" t="n">
+        <v>16.558996</v>
+      </c>
+      <c r="K253" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L253" t="n">
+        <v>20.237434</v>
+      </c>
+      <c r="M253" t="n">
+        <v>0.03083097261567517</v>
+      </c>
+      <c r="N253" t="n">
+        <v>0.06045764872521246</v>
+      </c>
+      <c r="O253" t="n">
+        <v>0.04585000038146973</v>
+      </c>
+      <c r="P253" t="n">
+        <v>0.01460764834374274</v>
       </c>
     </row>
   </sheetData>
@@ -14692,12 +15214,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -14711,51 +15233,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>350.67</v>
+        <v>357.33</v>
       </c>
       <c r="F2" t="n">
-        <v>4279076388864</v>
+        <v>4360345223168</v>
       </c>
       <c r="G2" t="n">
-        <v>13.1</v>
+        <v>13.12</v>
       </c>
       <c r="H2" t="n">
-        <v>14.63415</v>
+        <v>14.59104</v>
       </c>
       <c r="I2" t="n">
-        <v>26.768703</v>
+        <v>27.235518</v>
       </c>
       <c r="J2" t="n">
-        <v>23.962446</v>
+        <v>24.489687</v>
       </c>
       <c r="K2" t="n">
         <v>1.4</v>
       </c>
       <c r="L2" t="n">
-        <v>10.128039</v>
+        <v>10.320393</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03735705934354236</v>
+        <v>0.03671676041754121</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04173197022841988</v>
+        <v>0.04083351523801528</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.04585000038146973</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.004358031831516646</v>
+        <v>-0.005016485143454444</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -14769,51 +15291,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>390.99</v>
+        <v>384.93</v>
       </c>
       <c r="F3" t="n">
-        <v>2904443584512</v>
+        <v>2859427430400</v>
       </c>
       <c r="G3" t="n">
-        <v>16.79</v>
+        <v>16.77</v>
       </c>
       <c r="H3" t="n">
         <v>19.35995</v>
       </c>
       <c r="I3" t="n">
-        <v>23.287073</v>
+        <v>22.953487</v>
       </c>
       <c r="J3" t="n">
-        <v>20.195818</v>
+        <v>19.8828</v>
       </c>
       <c r="K3" t="n">
         <v>1.19</v>
       </c>
       <c r="L3" t="n">
-        <v>9.125636</v>
+        <v>8.984197999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04294227473848436</v>
+        <v>0.04356636271529889</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04951520499245505</v>
+        <v>0.05029472891175019</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.04585000038146973</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003425202932518523</v>
+        <v>0.004444728530280467</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -14827,51 +15349,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>656.73</v>
+        <v>661.04</v>
       </c>
       <c r="F4" t="n">
-        <v>1667058630656</v>
+        <v>1677999341568</v>
       </c>
       <c r="G4" t="n">
-        <v>27.5</v>
+        <v>27.52</v>
       </c>
       <c r="H4" t="n">
         <v>36.32896</v>
       </c>
       <c r="I4" t="n">
-        <v>23.88109</v>
+        <v>24.020348</v>
       </c>
       <c r="J4" t="n">
-        <v>18.077312</v>
+        <v>18.195951</v>
       </c>
       <c r="K4" t="n">
         <v>0.97</v>
       </c>
       <c r="L4" t="n">
-        <v>7.755096</v>
+        <v>7.8059916</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04187413396677478</v>
+        <v>0.04163136875226915</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05531795410594918</v>
+        <v>0.05495727943846061</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.04585000038146973</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00922795204601265</v>
+        <v>0.009107279056990887</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -14885,51 +15407,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>247.31</v>
+        <v>247.49</v>
       </c>
       <c r="F5" t="n">
-        <v>2660340858880</v>
+        <v>2662277054464</v>
       </c>
       <c r="G5" t="n">
-        <v>8.369999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="H5" t="n">
         <v>9.88631</v>
       </c>
       <c r="I5" t="n">
-        <v>29.547192</v>
+        <v>29.604069</v>
       </c>
       <c r="J5" t="n">
-        <v>25.0154</v>
+        <v>25.03361</v>
       </c>
       <c r="K5" t="n">
         <v>1.41</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5816195</v>
+        <v>3.5842261</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03384416319598884</v>
+        <v>0.03377914259161986</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0399753750353807</v>
+        <v>0.03994630086064083</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.04585000038146973</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.006114627024555827</v>
+        <v>-0.005903699520828892</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -14943,51 +15465,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>317.31</v>
+        <v>314.86</v>
       </c>
       <c r="F6" t="n">
-        <v>4660444790784</v>
+        <v>4624460808192</v>
       </c>
       <c r="G6" t="n">
-        <v>8.26</v>
+        <v>8.25</v>
       </c>
       <c r="H6" t="n">
-        <v>9.612740000000001</v>
+        <v>9.62082</v>
       </c>
       <c r="I6" t="n">
-        <v>38.415253</v>
+        <v>38.16485</v>
       </c>
       <c r="J6" t="n">
-        <v>33.00932</v>
+        <v>32.72694</v>
       </c>
       <c r="K6" t="n">
         <v>2.55</v>
       </c>
       <c r="L6" t="n">
-        <v>10.3234625</v>
+        <v>10.243753</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02603132583278182</v>
+        <v>0.02620212157784412</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03029447543411806</v>
+        <v>0.0305558660992187</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.04585000038146973</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01579552662581847</v>
+        <v>-0.01529413428225103</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -15001,51 +15523,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>203.53</v>
+        <v>211.8</v>
       </c>
       <c r="F7" t="n">
-        <v>4929700233216</v>
+        <v>5130007609344</v>
       </c>
       <c r="G7" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
       <c r="H7" t="n">
-        <v>12.79063</v>
+        <v>12.80493</v>
       </c>
       <c r="I7" t="n">
-        <v>31.120794</v>
+        <v>32.434914</v>
       </c>
       <c r="J7" t="n">
-        <v>15.912429</v>
+        <v>16.558996</v>
       </c>
       <c r="K7" t="n">
         <v>0.65</v>
       </c>
       <c r="L7" t="n">
-        <v>19.447239</v>
+        <v>20.237434</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03213285510735518</v>
+        <v>0.03083097261567517</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06284395420822483</v>
+        <v>0.06045764872521246</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.04585000038146973</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01675395214828831</v>
+        <v>0.01460764834374274</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -15059,51 +15581,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>534.39</v>
+        <v>548.13</v>
       </c>
       <c r="F8" t="n">
-        <v>871376683008</v>
+        <v>893781082112</v>
       </c>
       <c r="G8" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="H8" t="n">
-        <v>13.28145</v>
+        <v>13.33059</v>
       </c>
       <c r="I8" t="n">
-        <v>177.53821</v>
+        <v>183.32108</v>
       </c>
       <c r="J8" t="n">
-        <v>40.235817</v>
+        <v>41.11821</v>
       </c>
       <c r="K8" t="n">
         <v>1.34</v>
       </c>
       <c r="L8" t="n">
-        <v>23.26525</v>
+        <v>23.863434</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005632590430210146</v>
+        <v>0.005454910331490705</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02485347779711447</v>
+        <v>0.02432012478791528</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.04585000038146973</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02123652426282206</v>
+        <v>-0.02152987559355445</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -15117,51 +15639,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>384.05</v>
+        <v>389.11</v>
       </c>
       <c r="F9" t="n">
-        <v>1827148660736</v>
+        <v>1851221999616</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>5.99</v>
       </c>
       <c r="H9" t="n">
         <v>19.39578</v>
       </c>
       <c r="I9" t="n">
-        <v>64.00833</v>
+        <v>64.95993</v>
       </c>
       <c r="J9" t="n">
-        <v>19.800697</v>
+        <v>20.061579</v>
       </c>
       <c r="K9" t="n">
         <v>0.45</v>
       </c>
       <c r="L9" t="n">
-        <v>24.211868</v>
+        <v>24.530869</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01562296575966671</v>
+        <v>0.01539410449487292</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05050326780367139</v>
+        <v>0.04984652154917632</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.04585000038146973</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004413265743734865</v>
+        <v>0.003996521167706595</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -15175,40 +15697,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73.83</v>
+        <v>73.53</v>
       </c>
       <c r="F10" t="n">
-        <v>310883254272</v>
+        <v>309620015104</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.838</v>
+        <v>3.83407</v>
       </c>
       <c r="I10" t="n">
-        <v>23.81613</v>
+        <v>23.719355</v>
       </c>
       <c r="J10" t="n">
-        <v>19.236582</v>
+        <v>19.178053</v>
       </c>
       <c r="K10" t="n">
         <v>1.44</v>
       </c>
       <c r="L10" t="n">
-        <v>6.6300554</v>
+        <v>6.603115</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04198835161858323</v>
+        <v>0.04215966272269822</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05198428822971692</v>
+        <v>0.05214293485652115</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.04585000038146973</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005894286169780397</v>
+        <v>0.006292934475051422</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P253"/>
+  <dimension ref="A1:P262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14639,16 +14639,16 @@
         <v>10.243753</v>
       </c>
       <c r="M245" t="n">
-        <v>0.02620212157784412</v>
+        <v>0.0262021215778441</v>
       </c>
       <c r="N245" t="n">
         <v>0.0305558660992187</v>
       </c>
       <c r="O245" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.0458500003814697</v>
       </c>
       <c r="P245" t="n">
-        <v>-0.01529413428225103</v>
+        <v>-0.015294134282251</v>
       </c>
     </row>
     <row r="246">
@@ -14697,16 +14697,16 @@
         <v>23.863434</v>
       </c>
       <c r="M246" t="n">
-        <v>0.005454910331490705</v>
+        <v>0.0054549103314907</v>
       </c>
       <c r="N246" t="n">
-        <v>0.02432012478791528</v>
+        <v>0.0243201247879152</v>
       </c>
       <c r="O246" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.0458500003814697</v>
       </c>
       <c r="P246" t="n">
-        <v>-0.02152987559355445</v>
+        <v>-0.0215298755935544</v>
       </c>
     </row>
     <row r="247">
@@ -14755,16 +14755,16 @@
         <v>3.5842261</v>
       </c>
       <c r="M247" t="n">
-        <v>0.03377914259161986</v>
+        <v>0.0337791425916198</v>
       </c>
       <c r="N247" t="n">
-        <v>0.03994630086064083</v>
+        <v>0.0399463008606408</v>
       </c>
       <c r="O247" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.0458500003814697</v>
       </c>
       <c r="P247" t="n">
-        <v>-0.005903699520828892</v>
+        <v>-0.0059036995208288</v>
       </c>
     </row>
     <row r="248">
@@ -14813,16 +14813,16 @@
         <v>24.530869</v>
       </c>
       <c r="M248" t="n">
-        <v>0.01539410449487292</v>
+        <v>0.0153941044948729</v>
       </c>
       <c r="N248" t="n">
-        <v>0.04984652154917632</v>
+        <v>0.0498465215491763</v>
       </c>
       <c r="O248" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.0458500003814697</v>
       </c>
       <c r="P248" t="n">
-        <v>0.003996521167706595</v>
+        <v>0.0039965211677065</v>
       </c>
     </row>
     <row r="249">
@@ -14871,16 +14871,16 @@
         <v>10.320393</v>
       </c>
       <c r="M249" t="n">
-        <v>0.03671676041754121</v>
+        <v>0.0367167604175412</v>
       </c>
       <c r="N249" t="n">
-        <v>0.04083351523801528</v>
+        <v>0.0408335152380152</v>
       </c>
       <c r="O249" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.0458500003814697</v>
       </c>
       <c r="P249" t="n">
-        <v>-0.005016485143454444</v>
+        <v>-0.0050164851434544</v>
       </c>
     </row>
     <row r="250">
@@ -14929,16 +14929,16 @@
         <v>7.8059916</v>
       </c>
       <c r="M250" t="n">
-        <v>0.04163136875226915</v>
+        <v>0.0416313687522691</v>
       </c>
       <c r="N250" t="n">
-        <v>0.05495727943846061</v>
+        <v>0.0549572794384606</v>
       </c>
       <c r="O250" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.0458500003814697</v>
       </c>
       <c r="P250" t="n">
-        <v>0.009107279056990887</v>
+        <v>0.0091072790569908</v>
       </c>
     </row>
     <row r="251">
@@ -14987,16 +14987,16 @@
         <v>8.984197999999999</v>
       </c>
       <c r="M251" t="n">
-        <v>0.04356636271529889</v>
+        <v>0.0435663627152988</v>
       </c>
       <c r="N251" t="n">
-        <v>0.05029472891175019</v>
+        <v>0.0502947289117501</v>
       </c>
       <c r="O251" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.0458500003814697</v>
       </c>
       <c r="P251" t="n">
-        <v>0.004444728530280467</v>
+        <v>0.0044447285302804</v>
       </c>
     </row>
     <row r="252">
@@ -15045,16 +15045,16 @@
         <v>6.603115</v>
       </c>
       <c r="M252" t="n">
-        <v>0.04215966272269822</v>
+        <v>0.0421596627226982</v>
       </c>
       <c r="N252" t="n">
-        <v>0.05214293485652115</v>
+        <v>0.0521429348565211</v>
       </c>
       <c r="O252" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.0458500003814697</v>
       </c>
       <c r="P252" t="n">
-        <v>0.006292934475051422</v>
+        <v>0.0062929344750514</v>
       </c>
     </row>
     <row r="253">
@@ -15103,16 +15103,538 @@
         <v>20.237434</v>
       </c>
       <c r="M253" t="n">
-        <v>0.03083097261567517</v>
+        <v>0.0308309726156751</v>
       </c>
       <c r="N253" t="n">
-        <v>0.06045764872521246</v>
+        <v>0.0604576487252124</v>
       </c>
       <c r="O253" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.0458500003814697</v>
       </c>
       <c r="P253" t="n">
-        <v>0.01460764834374274</v>
+        <v>0.0146076483437427</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="F254" t="n">
+        <v>4810109091840</v>
+      </c>
+      <c r="G254" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H254" t="n">
+        <v>9.62082</v>
+      </c>
+      <c r="I254" t="n">
+        <v>39.696968</v>
+      </c>
+      <c r="J254" t="n">
+        <v>34.040756</v>
+      </c>
+      <c r="K254" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L254" t="n">
+        <v>10.654987</v>
+      </c>
+      <c r="M254" t="n">
+        <v>0.02519083969465649</v>
+      </c>
+      <c r="N254" t="n">
+        <v>0.02937654961832061</v>
+      </c>
+      <c r="O254" t="n">
+        <v>0.04545000076293945</v>
+      </c>
+      <c r="P254" t="n">
+        <v>-0.01607345114461884</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>529.14</v>
+      </c>
+      <c r="F255" t="n">
+        <v>862816043008</v>
+      </c>
+      <c r="G255" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="H255" t="n">
+        <v>13.33059</v>
+      </c>
+      <c r="I255" t="n">
+        <v>175.79402</v>
+      </c>
+      <c r="J255" t="n">
+        <v>39.69367</v>
+      </c>
+      <c r="K255" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L255" t="n">
+        <v>23.036686</v>
+      </c>
+      <c r="M255" t="n">
+        <v>0.005688475639717277</v>
+      </c>
+      <c r="N255" t="n">
+        <v>0.02519293570699626</v>
+      </c>
+      <c r="O255" t="n">
+        <v>0.04545000076293945</v>
+      </c>
+      <c r="P255" t="n">
+        <v>-0.02025706505594319</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>254.96</v>
+      </c>
+      <c r="F256" t="n">
+        <v>2742632841216</v>
+      </c>
+      <c r="G256" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="H256" t="n">
+        <v>9.88631</v>
+      </c>
+      <c r="I256" t="n">
+        <v>30.461172</v>
+      </c>
+      <c r="J256" t="n">
+        <v>25.7892</v>
+      </c>
+      <c r="K256" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L256" t="n">
+        <v>3.6924093</v>
+      </c>
+      <c r="M256" t="n">
+        <v>0.03282867900847191</v>
+      </c>
+      <c r="N256" t="n">
+        <v>0.03877592563539379</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0.04545000076293945</v>
+      </c>
+      <c r="P256" t="n">
+        <v>-0.006674075127545663</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>394.28</v>
+      </c>
+      <c r="F257" t="n">
+        <v>1875818708992</v>
+      </c>
+      <c r="G257" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="H257" t="n">
+        <v>19.4169</v>
+      </c>
+      <c r="I257" t="n">
+        <v>65.823044</v>
+      </c>
+      <c r="J257" t="n">
+        <v>20.30602</v>
+      </c>
+      <c r="K257" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L257" t="n">
+        <v>24.856804</v>
+      </c>
+      <c r="M257" t="n">
+        <v>0.01519224916303135</v>
+      </c>
+      <c r="N257" t="n">
+        <v>0.04924647458658821</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0.04545000076293945</v>
+      </c>
+      <c r="P257" t="n">
+        <v>0.003796473823648762</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>370.21</v>
+      </c>
+      <c r="F258" t="n">
+        <v>4517514444800</v>
+      </c>
+      <c r="G258" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="H258" t="n">
+        <v>14.59104</v>
+      </c>
+      <c r="I258" t="n">
+        <v>28.238749</v>
+      </c>
+      <c r="J258" t="n">
+        <v>25.372421</v>
+      </c>
+      <c r="K258" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L258" t="n">
+        <v>10.692392</v>
+      </c>
+      <c r="M258" t="n">
+        <v>0.035412333540423</v>
+      </c>
+      <c r="N258" t="n">
+        <v>0.03941287377434429</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0.04545000076293945</v>
+      </c>
+      <c r="P258" t="n">
+        <v>-0.006037126988595161</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>681.3099999999999</v>
+      </c>
+      <c r="F259" t="n">
+        <v>1729453228032</v>
+      </c>
+      <c r="G259" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H259" t="n">
+        <v>36.32896</v>
+      </c>
+      <c r="I259" t="n">
+        <v>24.774908</v>
+      </c>
+      <c r="J259" t="n">
+        <v>18.753908</v>
+      </c>
+      <c r="K259" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L259" t="n">
+        <v>8.045353</v>
+      </c>
+      <c r="M259" t="n">
+        <v>0.04036341753386858</v>
+      </c>
+      <c r="N259" t="n">
+        <v>0.05332221749277129</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0.04545000076293945</v>
+      </c>
+      <c r="P259" t="n">
+        <v>0.007872216729831835</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>395.63</v>
+      </c>
+      <c r="F260" t="n">
+        <v>2938911850496</v>
+      </c>
+      <c r="G260" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="H260" t="n">
+        <v>19.36852</v>
+      </c>
+      <c r="I260" t="n">
+        <v>23.577473</v>
+      </c>
+      <c r="J260" t="n">
+        <v>20.426443</v>
+      </c>
+      <c r="K260" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L260" t="n">
+        <v>9.233934</v>
+      </c>
+      <c r="M260" t="n">
+        <v>0.04241336602381013</v>
+      </c>
+      <c r="N260" t="n">
+        <v>0.04895614589389076</v>
+      </c>
+      <c r="O260" t="n">
+        <v>0.04545000076293945</v>
+      </c>
+      <c r="P260" t="n">
+        <v>0.003506145130951308</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>73.68000000000001</v>
+      </c>
+      <c r="F261" t="n">
+        <v>310251651072</v>
+      </c>
+      <c r="G261" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H261" t="n">
+        <v>3.83294</v>
+      </c>
+      <c r="I261" t="n">
+        <v>23.767742</v>
+      </c>
+      <c r="J261" t="n">
+        <v>19.222841</v>
+      </c>
+      <c r="K261" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L261" t="n">
+        <v>6.6165857</v>
+      </c>
+      <c r="M261" t="n">
+        <v>0.04207383279044517</v>
+      </c>
+      <c r="N261" t="n">
+        <v>0.05202144408251899</v>
+      </c>
+      <c r="O261" t="n">
+        <v>0.04545000076293945</v>
+      </c>
+      <c r="P261" t="n">
+        <v>0.00657144331957954</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="F262" t="n">
+        <v>5146962558976</v>
+      </c>
+      <c r="G262" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="H262" t="n">
+        <v>12.80493</v>
+      </c>
+      <c r="I262" t="n">
+        <v>32.592026</v>
+      </c>
+      <c r="J262" t="n">
+        <v>16.595171</v>
+      </c>
+      <c r="K262" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L262" t="n">
+        <v>20.304321</v>
+      </c>
+      <c r="M262" t="n">
+        <v>0.03068235294117647</v>
+      </c>
+      <c r="N262" t="n">
+        <v>0.06025849411764706</v>
+      </c>
+      <c r="O262" t="n">
+        <v>0.04545000076293945</v>
+      </c>
+      <c r="P262" t="n">
+        <v>0.01480849335470761</v>
       </c>
     </row>
   </sheetData>
@@ -15214,12 +15736,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -15233,51 +15755,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>357.33</v>
+        <v>370.21</v>
       </c>
       <c r="F2" t="n">
-        <v>4360345223168</v>
+        <v>4517514444800</v>
       </c>
       <c r="G2" t="n">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="H2" t="n">
         <v>14.59104</v>
       </c>
       <c r="I2" t="n">
-        <v>27.235518</v>
+        <v>28.238749</v>
       </c>
       <c r="J2" t="n">
-        <v>24.489687</v>
+        <v>25.372421</v>
       </c>
       <c r="K2" t="n">
         <v>1.4</v>
       </c>
       <c r="L2" t="n">
-        <v>10.320393</v>
+        <v>10.692392</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03671676041754121</v>
+        <v>0.035412333540423</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04083351523801528</v>
+        <v>0.03941287377434429</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.04545000076293945</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005016485143454444</v>
+        <v>-0.006037126988595161</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -15291,51 +15813,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>384.93</v>
+        <v>395.63</v>
       </c>
       <c r="F3" t="n">
-        <v>2859427430400</v>
+        <v>2938911850496</v>
       </c>
       <c r="G3" t="n">
-        <v>16.77</v>
+        <v>16.78</v>
       </c>
       <c r="H3" t="n">
-        <v>19.35995</v>
+        <v>19.36852</v>
       </c>
       <c r="I3" t="n">
-        <v>22.953487</v>
+        <v>23.577473</v>
       </c>
       <c r="J3" t="n">
-        <v>19.8828</v>
+        <v>20.426443</v>
       </c>
       <c r="K3" t="n">
         <v>1.19</v>
       </c>
       <c r="L3" t="n">
-        <v>8.984197999999999</v>
+        <v>9.233934</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04356636271529889</v>
+        <v>0.04241336602381013</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05029472891175019</v>
+        <v>0.04895614589389076</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.04545000076293945</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004444728530280467</v>
+        <v>0.003506145130951308</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -15349,51 +15871,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>661.04</v>
+        <v>681.3099999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1677999341568</v>
+        <v>1729453228032</v>
       </c>
       <c r="G4" t="n">
-        <v>27.52</v>
+        <v>27.5</v>
       </c>
       <c r="H4" t="n">
         <v>36.32896</v>
       </c>
       <c r="I4" t="n">
-        <v>24.020348</v>
+        <v>24.774908</v>
       </c>
       <c r="J4" t="n">
-        <v>18.195951</v>
+        <v>18.753908</v>
       </c>
       <c r="K4" t="n">
         <v>0.97</v>
       </c>
       <c r="L4" t="n">
-        <v>7.8059916</v>
+        <v>8.045353</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04163136875226915</v>
+        <v>0.04036341753386858</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05495727943846061</v>
+        <v>0.05332221749277129</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.04545000076293945</v>
       </c>
       <c r="P4" t="n">
-        <v>0.009107279056990887</v>
+        <v>0.007872216729831835</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -15407,51 +15929,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>247.49</v>
+        <v>254.96</v>
       </c>
       <c r="F5" t="n">
-        <v>2662277054464</v>
+        <v>2742632841216</v>
       </c>
       <c r="G5" t="n">
-        <v>8.359999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H5" t="n">
         <v>9.88631</v>
       </c>
       <c r="I5" t="n">
-        <v>29.604069</v>
+        <v>30.461172</v>
       </c>
       <c r="J5" t="n">
-        <v>25.03361</v>
+        <v>25.7892</v>
       </c>
       <c r="K5" t="n">
         <v>1.41</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5842261</v>
+        <v>3.6924093</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03377914259161986</v>
+        <v>0.03282867900847191</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03994630086064083</v>
+        <v>0.03877592563539379</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.04545000076293945</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.005903699520828892</v>
+        <v>-0.006674075127545663</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -15465,10 +15987,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>314.86</v>
+        <v>327.5</v>
       </c>
       <c r="F6" t="n">
-        <v>4624460808192</v>
+        <v>4810109091840</v>
       </c>
       <c r="G6" t="n">
         <v>8.25</v>
@@ -15477,39 +15999,39 @@
         <v>9.62082</v>
       </c>
       <c r="I6" t="n">
-        <v>38.16485</v>
+        <v>39.696968</v>
       </c>
       <c r="J6" t="n">
-        <v>32.72694</v>
+        <v>34.040756</v>
       </c>
       <c r="K6" t="n">
         <v>2.55</v>
       </c>
       <c r="L6" t="n">
-        <v>10.243753</v>
+        <v>10.654987</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02620212157784412</v>
+        <v>0.02519083969465649</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0305558660992187</v>
+        <v>0.02937654961832061</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.04545000076293945</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01529413428225103</v>
+        <v>-0.01607345114461884</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -15523,51 +16045,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>211.8</v>
+        <v>212.5</v>
       </c>
       <c r="F7" t="n">
-        <v>5130007609344</v>
+        <v>5146962558976</v>
       </c>
       <c r="G7" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
       <c r="H7" t="n">
         <v>12.80493</v>
       </c>
       <c r="I7" t="n">
-        <v>32.434914</v>
+        <v>32.592026</v>
       </c>
       <c r="J7" t="n">
-        <v>16.558996</v>
+        <v>16.595171</v>
       </c>
       <c r="K7" t="n">
         <v>0.65</v>
       </c>
       <c r="L7" t="n">
-        <v>20.237434</v>
+        <v>20.304321</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03083097261567517</v>
+        <v>0.03068235294117647</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06045764872521246</v>
+        <v>0.06025849411764706</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.04545000076293945</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01460764834374274</v>
+        <v>0.01480849335470761</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -15581,51 +16103,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>548.13</v>
+        <v>529.14</v>
       </c>
       <c r="F8" t="n">
-        <v>893781082112</v>
+        <v>862816043008</v>
       </c>
       <c r="G8" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="H8" t="n">
         <v>13.33059</v>
       </c>
       <c r="I8" t="n">
-        <v>183.32108</v>
+        <v>175.79402</v>
       </c>
       <c r="J8" t="n">
-        <v>41.11821</v>
+        <v>39.69367</v>
       </c>
       <c r="K8" t="n">
         <v>1.34</v>
       </c>
       <c r="L8" t="n">
-        <v>23.863434</v>
+        <v>23.036686</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005454910331490705</v>
+        <v>0.005688475639717277</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02432012478791528</v>
+        <v>0.02519293570699626</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.04545000076293945</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02152987559355445</v>
+        <v>-0.02025706505594319</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -15639,51 +16161,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>389.11</v>
+        <v>394.28</v>
       </c>
       <c r="F9" t="n">
-        <v>1851221999616</v>
+        <v>1875818708992</v>
       </c>
       <c r="G9" t="n">
         <v>5.99</v>
       </c>
       <c r="H9" t="n">
-        <v>19.39578</v>
+        <v>19.4169</v>
       </c>
       <c r="I9" t="n">
-        <v>64.95993</v>
+        <v>65.823044</v>
       </c>
       <c r="J9" t="n">
-        <v>20.061579</v>
+        <v>20.30602</v>
       </c>
       <c r="K9" t="n">
         <v>0.45</v>
       </c>
       <c r="L9" t="n">
-        <v>24.530869</v>
+        <v>24.856804</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01539410449487292</v>
+        <v>0.01519224916303135</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04984652154917632</v>
+        <v>0.04924647458658821</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.04545000076293945</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003996521167706595</v>
+        <v>0.003796473823648762</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -15697,40 +16219,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73.53</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>309620015104</v>
+        <v>310251651072</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.83407</v>
+        <v>3.83294</v>
       </c>
       <c r="I10" t="n">
-        <v>23.719355</v>
+        <v>23.767742</v>
       </c>
       <c r="J10" t="n">
-        <v>19.178053</v>
+        <v>19.222841</v>
       </c>
       <c r="K10" t="n">
         <v>1.44</v>
       </c>
       <c r="L10" t="n">
-        <v>6.603115</v>
+        <v>6.6165857</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04215966272269822</v>
+        <v>0.04207383279044517</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05214293485652115</v>
+        <v>0.05202144408251899</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04585000038146973</v>
+        <v>0.04545000076293945</v>
       </c>
       <c r="P10" t="n">
-        <v>0.006292934475051422</v>
+        <v>0.00657144331957954</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P262"/>
+  <dimension ref="A1:P271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15161,16 +15161,16 @@
         <v>10.654987</v>
       </c>
       <c r="M254" t="n">
-        <v>0.02519083969465649</v>
+        <v>0.0251908396946564</v>
       </c>
       <c r="N254" t="n">
-        <v>0.02937654961832061</v>
+        <v>0.0293765496183206</v>
       </c>
       <c r="O254" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.0454500007629394</v>
       </c>
       <c r="P254" t="n">
-        <v>-0.01607345114461884</v>
+        <v>-0.0160734511446188</v>
       </c>
     </row>
     <row r="255">
@@ -15219,16 +15219,16 @@
         <v>23.036686</v>
       </c>
       <c r="M255" t="n">
-        <v>0.005688475639717277</v>
+        <v>0.0056884756397172</v>
       </c>
       <c r="N255" t="n">
-        <v>0.02519293570699626</v>
+        <v>0.0251929357069962</v>
       </c>
       <c r="O255" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.0454500007629394</v>
       </c>
       <c r="P255" t="n">
-        <v>-0.02025706505594319</v>
+        <v>-0.0202570650559431</v>
       </c>
     </row>
     <row r="256">
@@ -15277,16 +15277,16 @@
         <v>3.6924093</v>
       </c>
       <c r="M256" t="n">
-        <v>0.03282867900847191</v>
+        <v>0.0328286790084719</v>
       </c>
       <c r="N256" t="n">
-        <v>0.03877592563539379</v>
+        <v>0.0387759256353937</v>
       </c>
       <c r="O256" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.0454500007629394</v>
       </c>
       <c r="P256" t="n">
-        <v>-0.006674075127545663</v>
+        <v>-0.0066740751275456</v>
       </c>
     </row>
     <row r="257">
@@ -15335,16 +15335,16 @@
         <v>24.856804</v>
       </c>
       <c r="M257" t="n">
-        <v>0.01519224916303135</v>
+        <v>0.0151922491630313</v>
       </c>
       <c r="N257" t="n">
-        <v>0.04924647458658821</v>
+        <v>0.0492464745865882</v>
       </c>
       <c r="O257" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.0454500007629394</v>
       </c>
       <c r="P257" t="n">
-        <v>0.003796473823648762</v>
+        <v>0.0037964738236487</v>
       </c>
     </row>
     <row r="258">
@@ -15396,13 +15396,13 @@
         <v>0.035412333540423</v>
       </c>
       <c r="N258" t="n">
-        <v>0.03941287377434429</v>
+        <v>0.0394128737743442</v>
       </c>
       <c r="O258" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.0454500007629394</v>
       </c>
       <c r="P258" t="n">
-        <v>-0.006037126988595161</v>
+        <v>-0.0060371269885951</v>
       </c>
     </row>
     <row r="259">
@@ -15451,16 +15451,16 @@
         <v>8.045353</v>
       </c>
       <c r="M259" t="n">
-        <v>0.04036341753386858</v>
+        <v>0.0403634175338685</v>
       </c>
       <c r="N259" t="n">
-        <v>0.05332221749277129</v>
+        <v>0.0533222174927712</v>
       </c>
       <c r="O259" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.0454500007629394</v>
       </c>
       <c r="P259" t="n">
-        <v>0.007872216729831835</v>
+        <v>0.0078722167298318</v>
       </c>
     </row>
     <row r="260">
@@ -15509,16 +15509,16 @@
         <v>9.233934</v>
       </c>
       <c r="M260" t="n">
-        <v>0.04241336602381013</v>
+        <v>0.0424133660238101</v>
       </c>
       <c r="N260" t="n">
-        <v>0.04895614589389076</v>
+        <v>0.0489561458938907</v>
       </c>
       <c r="O260" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.0454500007629394</v>
       </c>
       <c r="P260" t="n">
-        <v>0.003506145130951308</v>
+        <v>0.0035061451309513</v>
       </c>
     </row>
     <row r="261">
@@ -15567,16 +15567,16 @@
         <v>6.6165857</v>
       </c>
       <c r="M261" t="n">
-        <v>0.04207383279044517</v>
+        <v>0.0420738327904451</v>
       </c>
       <c r="N261" t="n">
-        <v>0.05202144408251899</v>
+        <v>0.0520214440825189</v>
       </c>
       <c r="O261" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.0454500007629394</v>
       </c>
       <c r="P261" t="n">
-        <v>0.00657144331957954</v>
+        <v>0.0065714433195795</v>
       </c>
     </row>
     <row r="262">
@@ -15625,16 +15625,538 @@
         <v>20.304321</v>
       </c>
       <c r="M262" t="n">
-        <v>0.03068235294117647</v>
+        <v>0.0306823529411764</v>
       </c>
       <c r="N262" t="n">
-        <v>0.06025849411764706</v>
+        <v>0.060258494117647</v>
       </c>
       <c r="O262" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.0454500007629394</v>
       </c>
       <c r="P262" t="n">
-        <v>0.01480849335470761</v>
+        <v>0.0148084933547076</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>333.26</v>
+      </c>
+      <c r="F263" t="n">
+        <v>4894708203520</v>
+      </c>
+      <c r="G263" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H263" t="n">
+        <v>9.62091</v>
+      </c>
+      <c r="I263" t="n">
+        <v>40.395153</v>
+      </c>
+      <c r="J263" t="n">
+        <v>34.639137</v>
+      </c>
+      <c r="K263" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="L263" t="n">
+        <v>10.842385</v>
+      </c>
+      <c r="M263" t="n">
+        <v>0.0247554461981636</v>
+      </c>
+      <c r="N263" t="n">
+        <v>0.02886908119786353</v>
+      </c>
+      <c r="O263" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P263" t="n">
+        <v>-0.01682091647517113</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>500.94</v>
+      </c>
+      <c r="F264" t="n">
+        <v>816833036288</v>
+      </c>
+      <c r="G264" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H264" t="n">
+        <v>13.46474</v>
+      </c>
+      <c r="I264" t="n">
+        <v>165.87418</v>
+      </c>
+      <c r="J264" t="n">
+        <v>37.20384</v>
+      </c>
+      <c r="K264" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L264" t="n">
+        <v>21.808966</v>
+      </c>
+      <c r="M264" t="n">
+        <v>0.006028666107717491</v>
+      </c>
+      <c r="N264" t="n">
+        <v>0.02687894757855232</v>
+      </c>
+      <c r="O264" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P264" t="n">
+        <v>-0.01881105009448234</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>249.89</v>
+      </c>
+      <c r="F265" t="n">
+        <v>2688094044160</v>
+      </c>
+      <c r="G265" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="H265" t="n">
+        <v>9.90619</v>
+      </c>
+      <c r="I265" t="n">
+        <v>29.89115</v>
+      </c>
+      <c r="J265" t="n">
+        <v>25.225641</v>
+      </c>
+      <c r="K265" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L265" t="n">
+        <v>3.6189835</v>
+      </c>
+      <c r="M265" t="n">
+        <v>0.0334547200768338</v>
+      </c>
+      <c r="N265" t="n">
+        <v>0.03964220256913042</v>
+      </c>
+      <c r="O265" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P265" t="n">
+        <v>-0.006047795103904241</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>374.45</v>
+      </c>
+      <c r="F266" t="n">
+        <v>1781475966976</v>
+      </c>
+      <c r="G266" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="H266" t="n">
+        <v>19.4169</v>
+      </c>
+      <c r="I266" t="n">
+        <v>62.512524</v>
+      </c>
+      <c r="J266" t="n">
+        <v>19.284746</v>
+      </c>
+      <c r="K266" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L266" t="n">
+        <v>23.606651</v>
+      </c>
+      <c r="M266" t="n">
+        <v>0.015996795299773</v>
+      </c>
+      <c r="N266" t="n">
+        <v>0.05185445319802377</v>
+      </c>
+      <c r="O266" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P266" t="n">
+        <v>0.0061644555249891</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>353.81</v>
+      </c>
+      <c r="F267" t="n">
+        <v>4317392142336</v>
+      </c>
+      <c r="G267" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="H267" t="n">
+        <v>14.62456</v>
+      </c>
+      <c r="I267" t="n">
+        <v>26.987797</v>
+      </c>
+      <c r="J267" t="n">
+        <v>24.192863</v>
+      </c>
+      <c r="K267" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L267" t="n">
+        <v>10.218728</v>
+      </c>
+      <c r="M267" t="n">
+        <v>0.03705378593030157</v>
+      </c>
+      <c r="N267" t="n">
+        <v>0.04133450156863853</v>
+      </c>
+      <c r="O267" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P267" t="n">
+        <v>-0.004355496104396131</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>664.54</v>
+      </c>
+      <c r="F268" t="n">
+        <v>1686883794944</v>
+      </c>
+      <c r="G268" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="H268" t="n">
+        <v>36.32896</v>
+      </c>
+      <c r="I268" t="n">
+        <v>24.147528</v>
+      </c>
+      <c r="J268" t="n">
+        <v>18.292294</v>
+      </c>
+      <c r="K268" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L268" t="n">
+        <v>7.847322</v>
+      </c>
+      <c r="M268" t="n">
+        <v>0.04141210461371776</v>
+      </c>
+      <c r="N268" t="n">
+        <v>0.05466783037890872</v>
+      </c>
+      <c r="O268" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P268" t="n">
+        <v>0.008977832705874059</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>401.1</v>
+      </c>
+      <c r="F269" t="n">
+        <v>2979545219072</v>
+      </c>
+      <c r="G269" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="H269" t="n">
+        <v>19.37791</v>
+      </c>
+      <c r="I269" t="n">
+        <v>23.91771</v>
+      </c>
+      <c r="J269" t="n">
+        <v>20.698826</v>
+      </c>
+      <c r="K269" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L269" t="n">
+        <v>9.361603000000001</v>
+      </c>
+      <c r="M269" t="n">
+        <v>0.04181002243829469</v>
+      </c>
+      <c r="N269" t="n">
+        <v>0.04831191722762403</v>
+      </c>
+      <c r="O269" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P269" t="n">
+        <v>0.002621919554589368</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="F270" t="n">
+        <v>313072877568</v>
+      </c>
+      <c r="G270" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H270" t="n">
+        <v>3.83294</v>
+      </c>
+      <c r="I270" t="n">
+        <v>23.983871</v>
+      </c>
+      <c r="J270" t="n">
+        <v>19.397642</v>
+      </c>
+      <c r="K270" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L270" t="n">
+        <v>6.6767526</v>
+      </c>
+      <c r="M270" t="n">
+        <v>0.04169468728984533</v>
+      </c>
+      <c r="N270" t="n">
+        <v>0.05155265635507734</v>
+      </c>
+      <c r="O270" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P270" t="n">
+        <v>0.005862658682042672</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>207.4</v>
+      </c>
+      <c r="F271" t="n">
+        <v>5023435063296</v>
+      </c>
+      <c r="G271" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="H271" t="n">
+        <v>12.80493</v>
+      </c>
+      <c r="I271" t="n">
+        <v>31.809814</v>
+      </c>
+      <c r="J271" t="n">
+        <v>16.196886</v>
+      </c>
+      <c r="K271" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L271" t="n">
+        <v>19.817015</v>
+      </c>
+      <c r="M271" t="n">
+        <v>0.03143683702989392</v>
+      </c>
+      <c r="N271" t="n">
+        <v>0.06174026036644166</v>
+      </c>
+      <c r="O271" t="n">
+        <v>0.04568999767303467</v>
+      </c>
+      <c r="P271" t="n">
+        <v>0.01605026269340699</v>
       </c>
     </row>
   </sheetData>
@@ -15736,12 +16258,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -15755,51 +16277,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>370.21</v>
+        <v>353.81</v>
       </c>
       <c r="F2" t="n">
-        <v>4517514444800</v>
+        <v>4317392142336</v>
       </c>
       <c r="G2" t="n">
         <v>13.11</v>
       </c>
       <c r="H2" t="n">
-        <v>14.59104</v>
+        <v>14.62456</v>
       </c>
       <c r="I2" t="n">
-        <v>28.238749</v>
+        <v>26.987797</v>
       </c>
       <c r="J2" t="n">
-        <v>25.372421</v>
+        <v>24.192863</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="L2" t="n">
-        <v>10.692392</v>
+        <v>10.218728</v>
       </c>
       <c r="M2" t="n">
-        <v>0.035412333540423</v>
+        <v>0.03705378593030157</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03941287377434429</v>
+        <v>0.04133450156863853</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.006037126988595161</v>
+        <v>-0.004355496104396131</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -15813,51 +16335,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>395.63</v>
+        <v>401.1</v>
       </c>
       <c r="F3" t="n">
-        <v>2938911850496</v>
+        <v>2979545219072</v>
       </c>
       <c r="G3" t="n">
-        <v>16.78</v>
+        <v>16.77</v>
       </c>
       <c r="H3" t="n">
-        <v>19.36852</v>
+        <v>19.37791</v>
       </c>
       <c r="I3" t="n">
-        <v>23.577473</v>
+        <v>23.91771</v>
       </c>
       <c r="J3" t="n">
-        <v>20.426443</v>
+        <v>20.698826</v>
       </c>
       <c r="K3" t="n">
         <v>1.19</v>
       </c>
       <c r="L3" t="n">
-        <v>9.233934</v>
+        <v>9.361603000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04241336602381013</v>
+        <v>0.04181002243829469</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04895614589389076</v>
+        <v>0.04831191722762403</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003506145130951308</v>
+        <v>0.002621919554589368</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -15871,51 +16393,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>681.3099999999999</v>
+        <v>664.54</v>
       </c>
       <c r="F4" t="n">
-        <v>1729453228032</v>
+        <v>1686883794944</v>
       </c>
       <c r="G4" t="n">
-        <v>27.5</v>
+        <v>27.52</v>
       </c>
       <c r="H4" t="n">
         <v>36.32896</v>
       </c>
       <c r="I4" t="n">
-        <v>24.774908</v>
+        <v>24.147528</v>
       </c>
       <c r="J4" t="n">
-        <v>18.753908</v>
+        <v>18.292294</v>
       </c>
       <c r="K4" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="L4" t="n">
-        <v>8.045353</v>
+        <v>7.847322</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04036341753386858</v>
+        <v>0.04141210461371776</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05332221749277129</v>
+        <v>0.05466783037890872</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P4" t="n">
-        <v>0.007872216729831835</v>
+        <v>0.008977832705874059</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -15929,51 +16451,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>254.96</v>
+        <v>249.89</v>
       </c>
       <c r="F5" t="n">
-        <v>2742632841216</v>
+        <v>2688094044160</v>
       </c>
       <c r="G5" t="n">
-        <v>8.369999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>9.88631</v>
+        <v>9.90619</v>
       </c>
       <c r="I5" t="n">
-        <v>30.461172</v>
+        <v>29.89115</v>
       </c>
       <c r="J5" t="n">
-        <v>25.7892</v>
+        <v>25.225641</v>
       </c>
       <c r="K5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6924093</v>
+        <v>3.6189835</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03282867900847191</v>
+        <v>0.0334547200768338</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03877592563539379</v>
+        <v>0.03964220256913042</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.006674075127545663</v>
+        <v>-0.006047795103904241</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -15987,51 +16509,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>327.5</v>
+        <v>333.26</v>
       </c>
       <c r="F6" t="n">
-        <v>4810109091840</v>
+        <v>4894708203520</v>
       </c>
       <c r="G6" t="n">
         <v>8.25</v>
       </c>
       <c r="H6" t="n">
-        <v>9.62082</v>
+        <v>9.62091</v>
       </c>
       <c r="I6" t="n">
-        <v>39.696968</v>
+        <v>40.395153</v>
       </c>
       <c r="J6" t="n">
-        <v>34.040756</v>
+        <v>34.639137</v>
       </c>
       <c r="K6" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="L6" t="n">
-        <v>10.654987</v>
+        <v>10.842385</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02519083969465649</v>
+        <v>0.0247554461981636</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02937654961832061</v>
+        <v>0.02886908119786353</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01607345114461884</v>
+        <v>-0.01682091647517113</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -16045,10 +16567,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>212.5</v>
+        <v>207.4</v>
       </c>
       <c r="F7" t="n">
-        <v>5146962558976</v>
+        <v>5023435063296</v>
       </c>
       <c r="G7" t="n">
         <v>6.52</v>
@@ -16057,39 +16579,39 @@
         <v>12.80493</v>
       </c>
       <c r="I7" t="n">
-        <v>32.592026</v>
+        <v>31.809814</v>
       </c>
       <c r="J7" t="n">
-        <v>16.595171</v>
+        <v>16.196886</v>
       </c>
       <c r="K7" t="n">
         <v>0.65</v>
       </c>
       <c r="L7" t="n">
-        <v>20.304321</v>
+        <v>19.817015</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03068235294117647</v>
+        <v>0.03143683702989392</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06025849411764706</v>
+        <v>0.06174026036644166</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01480849335470761</v>
+        <v>0.01605026269340699</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -16103,51 +16625,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>529.14</v>
+        <v>500.94</v>
       </c>
       <c r="F8" t="n">
-        <v>862816043008</v>
+        <v>816833036288</v>
       </c>
       <c r="G8" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="H8" t="n">
-        <v>13.33059</v>
+        <v>13.46474</v>
       </c>
       <c r="I8" t="n">
-        <v>175.79402</v>
+        <v>165.87418</v>
       </c>
       <c r="J8" t="n">
-        <v>39.69367</v>
+        <v>37.20384</v>
       </c>
       <c r="K8" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="L8" t="n">
-        <v>23.036686</v>
+        <v>21.808966</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005688475639717277</v>
+        <v>0.006028666107717491</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02519293570699626</v>
+        <v>0.02687894757855232</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02025706505594319</v>
+        <v>-0.01881105009448234</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -16161,10 +16683,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>394.28</v>
+        <v>374.45</v>
       </c>
       <c r="F9" t="n">
-        <v>1875818708992</v>
+        <v>1781475966976</v>
       </c>
       <c r="G9" t="n">
         <v>5.99</v>
@@ -16173,39 +16695,39 @@
         <v>19.4169</v>
       </c>
       <c r="I9" t="n">
-        <v>65.823044</v>
+        <v>62.512524</v>
       </c>
       <c r="J9" t="n">
-        <v>20.30602</v>
+        <v>19.284746</v>
       </c>
       <c r="K9" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="L9" t="n">
-        <v>24.856804</v>
+        <v>23.606651</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01519224916303135</v>
+        <v>0.015996795299773</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04924647458658821</v>
+        <v>0.05185445319802377</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003796473823648762</v>
+        <v>0.0061644555249891</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -16219,10 +16741,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73.68000000000001</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>310251651072</v>
+        <v>313072877568</v>
       </c>
       <c r="G10" t="n">
         <v>3.1</v>
@@ -16231,28 +16753,28 @@
         <v>3.83294</v>
       </c>
       <c r="I10" t="n">
-        <v>23.767742</v>
+        <v>23.983871</v>
       </c>
       <c r="J10" t="n">
-        <v>19.222841</v>
+        <v>19.397642</v>
       </c>
       <c r="K10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="L10" t="n">
-        <v>6.6165857</v>
+        <v>6.6767526</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04207383279044517</v>
+        <v>0.04169468728984533</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05202144408251899</v>
+        <v>0.05155265635507734</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04545000076293945</v>
+        <v>0.04568999767303467</v>
       </c>
       <c r="P10" t="n">
-        <v>0.00657144331957954</v>
+        <v>0.005862658682042672</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P271"/>
+  <dimension ref="A1:P280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15683,16 +15683,16 @@
         <v>10.842385</v>
       </c>
       <c r="M263" t="n">
-        <v>0.0247554461981636</v>
+        <v>0.0247554461981635</v>
       </c>
       <c r="N263" t="n">
-        <v>0.02886908119786353</v>
+        <v>0.0288690811978635</v>
       </c>
       <c r="O263" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P263" t="n">
-        <v>-0.01682091647517113</v>
+        <v>-0.0168209164751711</v>
       </c>
     </row>
     <row r="264">
@@ -15741,16 +15741,16 @@
         <v>21.808966</v>
       </c>
       <c r="M264" t="n">
-        <v>0.006028666107717491</v>
+        <v>0.0060286661077174</v>
       </c>
       <c r="N264" t="n">
-        <v>0.02687894757855232</v>
+        <v>0.0268789475785523</v>
       </c>
       <c r="O264" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P264" t="n">
-        <v>-0.01881105009448234</v>
+        <v>-0.0188110500944823</v>
       </c>
     </row>
     <row r="265">
@@ -15802,13 +15802,13 @@
         <v>0.0334547200768338</v>
       </c>
       <c r="N265" t="n">
-        <v>0.03964220256913042</v>
+        <v>0.0396422025691304</v>
       </c>
       <c r="O265" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P265" t="n">
-        <v>-0.006047795103904241</v>
+        <v>-0.0060477951039042</v>
       </c>
     </row>
     <row r="266">
@@ -15860,10 +15860,10 @@
         <v>0.015996795299773</v>
       </c>
       <c r="N266" t="n">
-        <v>0.05185445319802377</v>
+        <v>0.0518544531980237</v>
       </c>
       <c r="O266" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P266" t="n">
         <v>0.0061644555249891</v>
@@ -15915,16 +15915,16 @@
         <v>10.218728</v>
       </c>
       <c r="M267" t="n">
-        <v>0.03705378593030157</v>
+        <v>0.0370537859303015</v>
       </c>
       <c r="N267" t="n">
-        <v>0.04133450156863853</v>
+        <v>0.0413345015686385</v>
       </c>
       <c r="O267" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P267" t="n">
-        <v>-0.004355496104396131</v>
+        <v>-0.0043554961043961</v>
       </c>
     </row>
     <row r="268">
@@ -15973,16 +15973,16 @@
         <v>7.847322</v>
       </c>
       <c r="M268" t="n">
-        <v>0.04141210461371776</v>
+        <v>0.0414121046137177</v>
       </c>
       <c r="N268" t="n">
-        <v>0.05466783037890872</v>
+        <v>0.0546678303789087</v>
       </c>
       <c r="O268" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P268" t="n">
-        <v>0.008977832705874059</v>
+        <v>0.008977832705874</v>
       </c>
     </row>
     <row r="269">
@@ -16031,16 +16031,16 @@
         <v>9.361603000000001</v>
       </c>
       <c r="M269" t="n">
-        <v>0.04181002243829469</v>
+        <v>0.0418100224382946</v>
       </c>
       <c r="N269" t="n">
-        <v>0.04831191722762403</v>
+        <v>0.048311917227624</v>
       </c>
       <c r="O269" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P269" t="n">
-        <v>0.002621919554589368</v>
+        <v>0.0026219195545893</v>
       </c>
     </row>
     <row r="270">
@@ -16089,16 +16089,16 @@
         <v>6.6767526</v>
       </c>
       <c r="M270" t="n">
-        <v>0.04169468728984533</v>
+        <v>0.0416946872898453</v>
       </c>
       <c r="N270" t="n">
-        <v>0.05155265635507734</v>
+        <v>0.0515526563550773</v>
       </c>
       <c r="O270" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P270" t="n">
-        <v>0.005862658682042672</v>
+        <v>0.0058626586820426</v>
       </c>
     </row>
     <row r="271">
@@ -16147,16 +16147,538 @@
         <v>19.817015</v>
       </c>
       <c r="M271" t="n">
-        <v>0.03143683702989392</v>
+        <v>0.0314368370298939</v>
       </c>
       <c r="N271" t="n">
-        <v>0.06174026036644166</v>
+        <v>0.0617402603664416</v>
       </c>
       <c r="O271" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.0456899976730346</v>
       </c>
       <c r="P271" t="n">
-        <v>0.01605026269340699</v>
+        <v>0.0160502626934069</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="F272" t="n">
+        <v>4901757779968</v>
+      </c>
+      <c r="G272" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H272" t="n">
+        <v>9.63869</v>
+      </c>
+      <c r="I272" t="n">
+        <v>40.404358</v>
+      </c>
+      <c r="J272" t="n">
+        <v>34.625034</v>
+      </c>
+      <c r="K272" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="L272" t="n">
+        <v>10.858001</v>
+      </c>
+      <c r="M272" t="n">
+        <v>0.02474980523761012</v>
+      </c>
+      <c r="N272" t="n">
+        <v>0.02888083538083538</v>
+      </c>
+      <c r="O272" t="n">
+        <v>0.04540999889373779</v>
+      </c>
+      <c r="P272" t="n">
+        <v>-0.01652916351290241</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>495.76</v>
+      </c>
+      <c r="F273" t="n">
+        <v>808386560000</v>
+      </c>
+      <c r="G273" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="H273" t="n">
+        <v>13.46474</v>
+      </c>
+      <c r="I273" t="n">
+        <v>164.70432</v>
+      </c>
+      <c r="J273" t="n">
+        <v>36.81913</v>
+      </c>
+      <c r="K273" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L273" t="n">
+        <v>21.58345</v>
+      </c>
+      <c r="M273" t="n">
+        <v>0.006071486203001452</v>
+      </c>
+      <c r="N273" t="n">
+        <v>0.02715979506212684</v>
+      </c>
+      <c r="O273" t="n">
+        <v>0.04540999889373779</v>
+      </c>
+      <c r="P273" t="n">
+        <v>-0.01825020383161095</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>247.23</v>
+      </c>
+      <c r="F274" t="n">
+        <v>2659480240128</v>
+      </c>
+      <c r="G274" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="H274" t="n">
+        <v>9.910030000000001</v>
+      </c>
+      <c r="I274" t="n">
+        <v>29.537634</v>
+      </c>
+      <c r="J274" t="n">
+        <v>24.94745</v>
+      </c>
+      <c r="K274" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L274" t="n">
+        <v>3.5804608</v>
+      </c>
+      <c r="M274" t="n">
+        <v>0.03385511467054969</v>
+      </c>
+      <c r="N274" t="n">
+        <v>0.04008425352910246</v>
+      </c>
+      <c r="O274" t="n">
+        <v>0.04540999889373779</v>
+      </c>
+      <c r="P274" t="n">
+        <v>-0.005325745364635329</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>370.825</v>
+      </c>
+      <c r="F275" t="n">
+        <v>1764229775360</v>
+      </c>
+      <c r="G275" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="H275" t="n">
+        <v>19.4169</v>
+      </c>
+      <c r="I275" t="n">
+        <v>61.496685</v>
+      </c>
+      <c r="J275" t="n">
+        <v>19.098053</v>
+      </c>
+      <c r="K275" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L275" t="n">
+        <v>23.37812</v>
+      </c>
+      <c r="M275" t="n">
+        <v>0.01626103957392301</v>
+      </c>
+      <c r="N275" t="n">
+        <v>0.05236135643497607</v>
+      </c>
+      <c r="O275" t="n">
+        <v>0.04540999889373779</v>
+      </c>
+      <c r="P275" t="n">
+        <v>0.006951357541238275</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>346.12</v>
+      </c>
+      <c r="F276" t="n">
+        <v>4223554551808</v>
+      </c>
+      <c r="G276" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="H276" t="n">
+        <v>14.63706</v>
+      </c>
+      <c r="I276" t="n">
+        <v>26.361004</v>
+      </c>
+      <c r="J276" t="n">
+        <v>23.646824</v>
+      </c>
+      <c r="K276" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L276" t="n">
+        <v>9.996625999999999</v>
+      </c>
+      <c r="M276" t="n">
+        <v>0.03793482029353981</v>
+      </c>
+      <c r="N276" t="n">
+        <v>0.04228897492199237</v>
+      </c>
+      <c r="O276" t="n">
+        <v>0.04540999889373779</v>
+      </c>
+      <c r="P276" t="n">
+        <v>-0.003121023971745421</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>646.01</v>
+      </c>
+      <c r="F277" t="n">
+        <v>1639846903808</v>
+      </c>
+      <c r="G277" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="H277" t="n">
+        <v>36.32896</v>
+      </c>
+      <c r="I277" t="n">
+        <v>23.482733</v>
+      </c>
+      <c r="J277" t="n">
+        <v>17.782232</v>
+      </c>
+      <c r="K277" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L277" t="n">
+        <v>7.628508</v>
+      </c>
+      <c r="M277" t="n">
+        <v>0.04258448011640687</v>
+      </c>
+      <c r="N277" t="n">
+        <v>0.05623590966084117</v>
+      </c>
+      <c r="O277" t="n">
+        <v>0.04540999889373779</v>
+      </c>
+      <c r="P277" t="n">
+        <v>0.01082591076710337</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="F278" t="n">
+        <v>2925466222592</v>
+      </c>
+      <c r="G278" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="H278" t="n">
+        <v>19.37648</v>
+      </c>
+      <c r="I278" t="n">
+        <v>23.427723</v>
+      </c>
+      <c r="J278" t="n">
+        <v>20.324642</v>
+      </c>
+      <c r="K278" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L278" t="n">
+        <v>9.191689</v>
+      </c>
+      <c r="M278" t="n">
+        <v>0.04268447514092732</v>
+      </c>
+      <c r="N278" t="n">
+        <v>0.04920136102788076</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0.04540999889373779</v>
+      </c>
+      <c r="P278" t="n">
+        <v>0.003791362134142967</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="F279" t="n">
+        <v>290334539776</v>
+      </c>
+      <c r="G279" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H279" t="n">
+        <v>3.8196</v>
+      </c>
+      <c r="I279" t="n">
+        <v>21.682388</v>
+      </c>
+      <c r="J279" t="n">
+        <v>18.051626</v>
+      </c>
+      <c r="K279" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L279" t="n">
+        <v>6.002273</v>
+      </c>
+      <c r="M279" t="n">
+        <v>0.04612037708484409</v>
+      </c>
+      <c r="N279" t="n">
+        <v>0.05539666424945612</v>
+      </c>
+      <c r="O279" t="n">
+        <v>0.04540999889373779</v>
+      </c>
+      <c r="P279" t="n">
+        <v>0.009986665355718329</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="F280" t="n">
+        <v>4912260841472</v>
+      </c>
+      <c r="G280" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H280" t="n">
+        <v>12.83126</v>
+      </c>
+      <c r="I280" t="n">
+        <v>31.058191</v>
+      </c>
+      <c r="J280" t="n">
+        <v>15.80593</v>
+      </c>
+      <c r="K280" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L280" t="n">
+        <v>19.378443</v>
+      </c>
+      <c r="M280" t="n">
+        <v>0.03219762339135152</v>
+      </c>
+      <c r="N280" t="n">
+        <v>0.06326739312657167</v>
+      </c>
+      <c r="O280" t="n">
+        <v>0.04540999889373779</v>
+      </c>
+      <c r="P280" t="n">
+        <v>0.01785739423283388</v>
       </c>
     </row>
   </sheetData>
@@ -16258,12 +16780,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-16 16:22:58</t>
+          <t>2026-07-17 16:13:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -16277,51 +16799,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353.81</v>
+        <v>346.12</v>
       </c>
       <c r="F2" t="n">
-        <v>4317392142336</v>
+        <v>4223554551808</v>
       </c>
       <c r="G2" t="n">
-        <v>13.11</v>
+        <v>13.13</v>
       </c>
       <c r="H2" t="n">
-        <v>14.62456</v>
+        <v>14.63706</v>
       </c>
       <c r="I2" t="n">
-        <v>26.987797</v>
+        <v>26.361004</v>
       </c>
       <c r="J2" t="n">
-        <v>24.192863</v>
+        <v>23.646824</v>
       </c>
       <c r="K2" t="n">
         <v>1.41</v>
       </c>
       <c r="L2" t="n">
-        <v>10.218728</v>
+        <v>9.996625999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03705378593030157</v>
+        <v>0.03793482029353981</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04133450156863853</v>
+        <v>0.04228897492199237</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04540999889373779</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.004355496104396131</v>
+        <v>-0.003121023971745421</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-16 16:22:58</t>
+          <t>2026-07-17 16:13:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -16335,51 +16857,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>401.1</v>
+        <v>393.82</v>
       </c>
       <c r="F3" t="n">
-        <v>2979545219072</v>
+        <v>2925466222592</v>
       </c>
       <c r="G3" t="n">
-        <v>16.77</v>
+        <v>16.81</v>
       </c>
       <c r="H3" t="n">
-        <v>19.37791</v>
+        <v>19.37648</v>
       </c>
       <c r="I3" t="n">
-        <v>23.91771</v>
+        <v>23.427723</v>
       </c>
       <c r="J3" t="n">
-        <v>20.698826</v>
+        <v>20.324642</v>
       </c>
       <c r="K3" t="n">
         <v>1.19</v>
       </c>
       <c r="L3" t="n">
-        <v>9.361603000000001</v>
+        <v>9.191689</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04181002243829469</v>
+        <v>0.04268447514092732</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04831191722762403</v>
+        <v>0.04920136102788076</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04540999889373779</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002621919554589368</v>
+        <v>0.003791362134142967</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-16 16:22:58</t>
+          <t>2026-07-17 16:13:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -16393,51 +16915,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>664.54</v>
+        <v>646.01</v>
       </c>
       <c r="F4" t="n">
-        <v>1686883794944</v>
+        <v>1639846903808</v>
       </c>
       <c r="G4" t="n">
-        <v>27.52</v>
+        <v>27.51</v>
       </c>
       <c r="H4" t="n">
         <v>36.32896</v>
       </c>
       <c r="I4" t="n">
-        <v>24.147528</v>
+        <v>23.482733</v>
       </c>
       <c r="J4" t="n">
-        <v>18.292294</v>
+        <v>17.782232</v>
       </c>
       <c r="K4" t="n">
         <v>0.96</v>
       </c>
       <c r="L4" t="n">
-        <v>7.847322</v>
+        <v>7.628508</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04141210461371776</v>
+        <v>0.04258448011640687</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05466783037890872</v>
+        <v>0.05623590966084117</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04540999889373779</v>
       </c>
       <c r="P4" t="n">
-        <v>0.008977832705874059</v>
+        <v>0.01082591076710337</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-16 16:22:58</t>
+          <t>2026-07-17 16:13:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -16451,51 +16973,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>249.89</v>
+        <v>247.23</v>
       </c>
       <c r="F5" t="n">
-        <v>2688094044160</v>
+        <v>2659480240128</v>
       </c>
       <c r="G5" t="n">
-        <v>8.359999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>9.90619</v>
+        <v>9.910030000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>29.89115</v>
+        <v>29.537634</v>
       </c>
       <c r="J5" t="n">
-        <v>25.225641</v>
+        <v>24.94745</v>
       </c>
       <c r="K5" t="n">
         <v>1.43</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6189835</v>
+        <v>3.5804608</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0334547200768338</v>
+        <v>0.03385511467054969</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03964220256913042</v>
+        <v>0.04008425352910246</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04540999889373779</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.006047795103904241</v>
+        <v>-0.005325745364635329</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-16 16:22:58</t>
+          <t>2026-07-17 16:13:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -16509,51 +17031,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>333.26</v>
+        <v>333.74</v>
       </c>
       <c r="F6" t="n">
-        <v>4894708203520</v>
+        <v>4901757779968</v>
       </c>
       <c r="G6" t="n">
-        <v>8.25</v>
+        <v>8.26</v>
       </c>
       <c r="H6" t="n">
-        <v>9.62091</v>
+        <v>9.63869</v>
       </c>
       <c r="I6" t="n">
-        <v>40.395153</v>
+        <v>40.404358</v>
       </c>
       <c r="J6" t="n">
-        <v>34.639137</v>
+        <v>34.625034</v>
       </c>
       <c r="K6" t="n">
         <v>2.54</v>
       </c>
       <c r="L6" t="n">
-        <v>10.842385</v>
+        <v>10.858001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0247554461981636</v>
+        <v>0.02474980523761012</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02886908119786353</v>
+        <v>0.02888083538083538</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04540999889373779</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01682091647517113</v>
+        <v>-0.01652916351290241</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-16 16:22:58</t>
+          <t>2026-07-17 16:13:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -16567,51 +17089,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>207.4</v>
+        <v>202.81</v>
       </c>
       <c r="F7" t="n">
-        <v>5023435063296</v>
+        <v>4912260841472</v>
       </c>
       <c r="G7" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="H7" t="n">
-        <v>12.80493</v>
+        <v>12.83126</v>
       </c>
       <c r="I7" t="n">
-        <v>31.809814</v>
+        <v>31.058191</v>
       </c>
       <c r="J7" t="n">
-        <v>16.196886</v>
+        <v>15.80593</v>
       </c>
       <c r="K7" t="n">
         <v>0.65</v>
       </c>
       <c r="L7" t="n">
-        <v>19.817015</v>
+        <v>19.378443</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03143683702989392</v>
+        <v>0.03219762339135152</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06174026036644166</v>
+        <v>0.06326739312657167</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04540999889373779</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01605026269340699</v>
+        <v>0.01785739423283388</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-16 16:22:58</t>
+          <t>2026-07-17 16:13:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -16625,51 +17147,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>500.94</v>
+        <v>495.76</v>
       </c>
       <c r="F8" t="n">
-        <v>816833036288</v>
+        <v>808386560000</v>
       </c>
       <c r="G8" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="H8" t="n">
         <v>13.46474</v>
       </c>
       <c r="I8" t="n">
-        <v>165.87418</v>
+        <v>164.70432</v>
       </c>
       <c r="J8" t="n">
-        <v>37.20384</v>
+        <v>36.81913</v>
       </c>
       <c r="K8" t="n">
         <v>1.27</v>
       </c>
       <c r="L8" t="n">
-        <v>21.808966</v>
+        <v>21.58345</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006028666107717491</v>
+        <v>0.006071486203001452</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02687894757855232</v>
+        <v>0.02715979506212684</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04540999889373779</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01881105009448234</v>
+        <v>-0.01825020383161095</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-16 16:22:58</t>
+          <t>2026-07-17 16:13:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -16683,51 +17205,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>374.45</v>
+        <v>370.825</v>
       </c>
       <c r="F9" t="n">
-        <v>1781475966976</v>
+        <v>1764229775360</v>
       </c>
       <c r="G9" t="n">
-        <v>5.99</v>
+        <v>6.03</v>
       </c>
       <c r="H9" t="n">
         <v>19.4169</v>
       </c>
       <c r="I9" t="n">
-        <v>62.512524</v>
+        <v>61.496685</v>
       </c>
       <c r="J9" t="n">
-        <v>19.284746</v>
+        <v>19.098053</v>
       </c>
       <c r="K9" t="n">
         <v>0.44</v>
       </c>
       <c r="L9" t="n">
-        <v>23.606651</v>
+        <v>23.37812</v>
       </c>
       <c r="M9" t="n">
-        <v>0.015996795299773</v>
+        <v>0.01626103957392301</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05185445319802377</v>
+        <v>0.05236135643497607</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04540999889373779</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0061644555249891</v>
+        <v>0.006951357541238275</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-16 16:22:58</t>
+          <t>2026-07-17 16:13:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -16741,40 +17263,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>74.34999999999999</v>
+        <v>68.95</v>
       </c>
       <c r="F10" t="n">
-        <v>313072877568</v>
+        <v>290334539776</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.83294</v>
+        <v>3.8196</v>
       </c>
       <c r="I10" t="n">
-        <v>23.983871</v>
+        <v>21.682388</v>
       </c>
       <c r="J10" t="n">
-        <v>19.397642</v>
+        <v>18.051626</v>
       </c>
       <c r="K10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="L10" t="n">
-        <v>6.6767526</v>
+        <v>6.002273</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04169468728984533</v>
+        <v>0.04612037708484409</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05155265635507734</v>
+        <v>0.05539666424945612</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04540999889373779</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005862658682042672</v>
+        <v>0.009986665355718329</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P280"/>
+  <dimension ref="A1:P289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16205,16 +16205,16 @@
         <v>10.858001</v>
       </c>
       <c r="M272" t="n">
-        <v>0.02474980523761012</v>
+        <v>0.0247498052376101</v>
       </c>
       <c r="N272" t="n">
-        <v>0.02888083538083538</v>
+        <v>0.0288808353808353</v>
       </c>
       <c r="O272" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.0454099988937377</v>
       </c>
       <c r="P272" t="n">
-        <v>-0.01652916351290241</v>
+        <v>-0.0165291635129024</v>
       </c>
     </row>
     <row r="273">
@@ -16263,16 +16263,16 @@
         <v>21.58345</v>
       </c>
       <c r="M273" t="n">
-        <v>0.006071486203001452</v>
+        <v>0.0060714862030014</v>
       </c>
       <c r="N273" t="n">
-        <v>0.02715979506212684</v>
+        <v>0.0271597950621268</v>
       </c>
       <c r="O273" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.0454099988937377</v>
       </c>
       <c r="P273" t="n">
-        <v>-0.01825020383161095</v>
+        <v>-0.0182502038316109</v>
       </c>
     </row>
     <row r="274">
@@ -16321,16 +16321,16 @@
         <v>3.5804608</v>
       </c>
       <c r="M274" t="n">
-        <v>0.03385511467054969</v>
+        <v>0.0338551146705496</v>
       </c>
       <c r="N274" t="n">
-        <v>0.04008425352910246</v>
+        <v>0.0400842535291024</v>
       </c>
       <c r="O274" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.0454099988937377</v>
       </c>
       <c r="P274" t="n">
-        <v>-0.005325745364635329</v>
+        <v>-0.0053257453646353</v>
       </c>
     </row>
     <row r="275">
@@ -16379,16 +16379,16 @@
         <v>23.37812</v>
       </c>
       <c r="M275" t="n">
-        <v>0.01626103957392301</v>
+        <v>0.016261039573923</v>
       </c>
       <c r="N275" t="n">
-        <v>0.05236135643497607</v>
+        <v>0.052361356434976</v>
       </c>
       <c r="O275" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.0454099988937377</v>
       </c>
       <c r="P275" t="n">
-        <v>0.006951357541238275</v>
+        <v>0.0069513575412382</v>
       </c>
     </row>
     <row r="276">
@@ -16437,16 +16437,16 @@
         <v>9.996625999999999</v>
       </c>
       <c r="M276" t="n">
-        <v>0.03793482029353981</v>
+        <v>0.0379348202935398</v>
       </c>
       <c r="N276" t="n">
-        <v>0.04228897492199237</v>
+        <v>0.0422889749219923</v>
       </c>
       <c r="O276" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.0454099988937377</v>
       </c>
       <c r="P276" t="n">
-        <v>-0.003121023971745421</v>
+        <v>-0.0031210239717454</v>
       </c>
     </row>
     <row r="277">
@@ -16495,16 +16495,16 @@
         <v>7.628508</v>
       </c>
       <c r="M277" t="n">
-        <v>0.04258448011640687</v>
+        <v>0.0425844801164068</v>
       </c>
       <c r="N277" t="n">
-        <v>0.05623590966084117</v>
+        <v>0.0562359096608411</v>
       </c>
       <c r="O277" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.0454099988937377</v>
       </c>
       <c r="P277" t="n">
-        <v>0.01082591076710337</v>
+        <v>0.0108259107671033</v>
       </c>
     </row>
     <row r="278">
@@ -16553,16 +16553,16 @@
         <v>9.191689</v>
       </c>
       <c r="M278" t="n">
-        <v>0.04268447514092732</v>
+        <v>0.0426844751409273</v>
       </c>
       <c r="N278" t="n">
-        <v>0.04920136102788076</v>
+        <v>0.0492013610278807</v>
       </c>
       <c r="O278" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.0454099988937377</v>
       </c>
       <c r="P278" t="n">
-        <v>0.003791362134142967</v>
+        <v>0.0037913621341429</v>
       </c>
     </row>
     <row r="279">
@@ -16611,16 +16611,16 @@
         <v>6.002273</v>
       </c>
       <c r="M279" t="n">
-        <v>0.04612037708484409</v>
+        <v>0.046120377084844</v>
       </c>
       <c r="N279" t="n">
-        <v>0.05539666424945612</v>
+        <v>0.0553966642494561</v>
       </c>
       <c r="O279" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.0454099988937377</v>
       </c>
       <c r="P279" t="n">
-        <v>0.009986665355718329</v>
+        <v>0.009986665355718301</v>
       </c>
     </row>
     <row r="280">
@@ -16669,16 +16669,538 @@
         <v>19.378443</v>
       </c>
       <c r="M280" t="n">
-        <v>0.03219762339135152</v>
+        <v>0.0321976233913515</v>
       </c>
       <c r="N280" t="n">
-        <v>0.06326739312657167</v>
+        <v>0.06326739312657161</v>
       </c>
       <c r="O280" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.0454099988937377</v>
       </c>
       <c r="P280" t="n">
-        <v>0.01785739423283388</v>
+        <v>0.0178573942328338</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:28:10</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>326.59</v>
+      </c>
+      <c r="F281" t="n">
+        <v>4796743417856</v>
+      </c>
+      <c r="G281" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="H281" t="n">
+        <v>9.639150000000001</v>
+      </c>
+      <c r="I281" t="n">
+        <v>39.63471</v>
+      </c>
+      <c r="J281" t="n">
+        <v>33.88162</v>
+      </c>
+      <c r="K281" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="L281" t="n">
+        <v>10.6253805</v>
+      </c>
+      <c r="M281" t="n">
+        <v>0.02523041121895955</v>
+      </c>
+      <c r="N281" t="n">
+        <v>0.02951452892005267</v>
+      </c>
+      <c r="O281" t="n">
+        <v>0.04598000049591065</v>
+      </c>
+      <c r="P281" t="n">
+        <v>-0.01646547157585797</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:28:10</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>503.57</v>
+      </c>
+      <c r="F282" t="n">
+        <v>821121515520</v>
+      </c>
+      <c r="G282" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H282" t="n">
+        <v>13.46474</v>
+      </c>
+      <c r="I282" t="n">
+        <v>166.74504</v>
+      </c>
+      <c r="J282" t="n">
+        <v>37.399162</v>
+      </c>
+      <c r="K282" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L282" t="n">
+        <v>21.923466</v>
+      </c>
+      <c r="M282" t="n">
+        <v>0.005997180133844352</v>
+      </c>
+      <c r="N282" t="n">
+        <v>0.02673856663423159</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0.04598000049591065</v>
+      </c>
+      <c r="P282" t="n">
+        <v>-0.01924143386167906</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:28:10</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>249.99</v>
+      </c>
+      <c r="F283" t="n">
+        <v>2689169883136</v>
+      </c>
+      <c r="G283" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="H283" t="n">
+        <v>9.93547</v>
+      </c>
+      <c r="I283" t="n">
+        <v>29.903112</v>
+      </c>
+      <c r="J283" t="n">
+        <v>25.161367</v>
+      </c>
+      <c r="K283" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L283" t="n">
+        <v>3.620432</v>
+      </c>
+      <c r="M283" t="n">
+        <v>0.03344133765350614</v>
+      </c>
+      <c r="N283" t="n">
+        <v>0.03974346973878955</v>
+      </c>
+      <c r="O283" t="n">
+        <v>0.04598000049591065</v>
+      </c>
+      <c r="P283" t="n">
+        <v>-0.006236530757121092</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:28:10</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>378.16</v>
+      </c>
+      <c r="F284" t="n">
+        <v>1799126515712</v>
+      </c>
+      <c r="G284" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H284" t="n">
+        <v>19.4169</v>
+      </c>
+      <c r="I284" t="n">
+        <v>62.921795</v>
+      </c>
+      <c r="J284" t="n">
+        <v>19.475817</v>
+      </c>
+      <c r="K284" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L284" t="n">
+        <v>23.840542</v>
+      </c>
+      <c r="M284" t="n">
+        <v>0.01589274381214301</v>
+      </c>
+      <c r="N284" t="n">
+        <v>0.05134572667653902</v>
+      </c>
+      <c r="O284" t="n">
+        <v>0.04598000049591065</v>
+      </c>
+      <c r="P284" t="n">
+        <v>0.005365726180628375</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:28:10</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>351.37</v>
+      </c>
+      <c r="F285" t="n">
+        <v>4287617826816</v>
+      </c>
+      <c r="G285" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="H285" t="n">
+        <v>14.64943</v>
+      </c>
+      <c r="I285" t="n">
+        <v>26.78125</v>
+      </c>
+      <c r="J285" t="n">
+        <v>23.985233</v>
+      </c>
+      <c r="K285" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L285" t="n">
+        <v>10.148255</v>
+      </c>
+      <c r="M285" t="n">
+        <v>0.03733955659276546</v>
+      </c>
+      <c r="N285" t="n">
+        <v>0.04169231863847227</v>
+      </c>
+      <c r="O285" t="n">
+        <v>0.04598000049591065</v>
+      </c>
+      <c r="P285" t="n">
+        <v>-0.004287681857438379</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:28:10</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>645.85</v>
+      </c>
+      <c r="F286" t="n">
+        <v>1639440580608</v>
+      </c>
+      <c r="G286" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="H286" t="n">
+        <v>36.32896</v>
+      </c>
+      <c r="I286" t="n">
+        <v>23.468386</v>
+      </c>
+      <c r="J286" t="n">
+        <v>17.777826</v>
+      </c>
+      <c r="K286" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L286" t="n">
+        <v>7.626618</v>
+      </c>
+      <c r="M286" t="n">
+        <v>0.04261051327707672</v>
+      </c>
+      <c r="N286" t="n">
+        <v>0.05624984129441821</v>
+      </c>
+      <c r="O286" t="n">
+        <v>0.04598000049591065</v>
+      </c>
+      <c r="P286" t="n">
+        <v>0.01026984079850756</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:28:10</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>402.29</v>
+      </c>
+      <c r="F287" t="n">
+        <v>2988385239040</v>
+      </c>
+      <c r="G287" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="H287" t="n">
+        <v>19.38105</v>
+      </c>
+      <c r="I287" t="n">
+        <v>23.974373</v>
+      </c>
+      <c r="J287" t="n">
+        <v>20.756874</v>
+      </c>
+      <c r="K287" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L287" t="n">
+        <v>9.389378000000001</v>
+      </c>
+      <c r="M287" t="n">
+        <v>0.04171120336075965</v>
+      </c>
+      <c r="N287" t="n">
+        <v>0.04817681274702328</v>
+      </c>
+      <c r="O287" t="n">
+        <v>0.04598000049591065</v>
+      </c>
+      <c r="P287" t="n">
+        <v>0.002196812251112637</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:28:10</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="F288" t="n">
+        <v>284649979904</v>
+      </c>
+      <c r="G288" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H288" t="n">
+        <v>3.81704</v>
+      </c>
+      <c r="I288" t="n">
+        <v>21.25786</v>
+      </c>
+      <c r="J288" t="n">
+        <v>17.710058</v>
+      </c>
+      <c r="K288" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L288" t="n">
+        <v>5.8847523</v>
+      </c>
+      <c r="M288" t="n">
+        <v>0.0470414201183432</v>
+      </c>
+      <c r="N288" t="n">
+        <v>0.05646508875739645</v>
+      </c>
+      <c r="O288" t="n">
+        <v>0.04598000049591065</v>
+      </c>
+      <c r="P288" t="n">
+        <v>0.01048508826148581</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:28:10</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>203.28</v>
+      </c>
+      <c r="F289" t="n">
+        <v>4923644706816</v>
+      </c>
+      <c r="G289" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H289" t="n">
+        <v>12.84363</v>
+      </c>
+      <c r="I289" t="n">
+        <v>31.130167</v>
+      </c>
+      <c r="J289" t="n">
+        <v>15.827301</v>
+      </c>
+      <c r="K289" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L289" t="n">
+        <v>19.423351</v>
+      </c>
+      <c r="M289" t="n">
+        <v>0.03212317985045258</v>
+      </c>
+      <c r="N289" t="n">
+        <v>0.06318196576151121</v>
+      </c>
+      <c r="O289" t="n">
+        <v>0.04598000049591065</v>
+      </c>
+      <c r="P289" t="n">
+        <v>0.01720196526560056</v>
       </c>
     </row>
   </sheetData>
@@ -16780,12 +17302,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-17 16:13:03</t>
+          <t>2026-07-20 16:28:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -16799,51 +17321,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>346.12</v>
+        <v>351.37</v>
       </c>
       <c r="F2" t="n">
-        <v>4223554551808</v>
+        <v>4287617826816</v>
       </c>
       <c r="G2" t="n">
-        <v>13.13</v>
+        <v>13.12</v>
       </c>
       <c r="H2" t="n">
-        <v>14.63706</v>
+        <v>14.64943</v>
       </c>
       <c r="I2" t="n">
-        <v>26.361004</v>
+        <v>26.78125</v>
       </c>
       <c r="J2" t="n">
-        <v>23.646824</v>
+        <v>23.985233</v>
       </c>
       <c r="K2" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="L2" t="n">
-        <v>9.996625999999999</v>
+        <v>10.148255</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03793482029353981</v>
+        <v>0.03733955659276546</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04228897492199237</v>
+        <v>0.04169231863847227</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.04598000049591065</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003121023971745421</v>
+        <v>-0.004287681857438379</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-17 16:13:03</t>
+          <t>2026-07-20 16:28:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -16857,51 +17379,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>393.82</v>
+        <v>402.29</v>
       </c>
       <c r="F3" t="n">
-        <v>2925466222592</v>
+        <v>2988385239040</v>
       </c>
       <c r="G3" t="n">
-        <v>16.81</v>
+        <v>16.78</v>
       </c>
       <c r="H3" t="n">
-        <v>19.37648</v>
+        <v>19.38105</v>
       </c>
       <c r="I3" t="n">
-        <v>23.427723</v>
+        <v>23.974373</v>
       </c>
       <c r="J3" t="n">
-        <v>20.324642</v>
+        <v>20.756874</v>
       </c>
       <c r="K3" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="L3" t="n">
-        <v>9.191689</v>
+        <v>9.389378000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04268447514092732</v>
+        <v>0.04171120336075965</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04920136102788076</v>
+        <v>0.04817681274702328</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.04598000049591065</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003791362134142967</v>
+        <v>0.002196812251112637</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-17 16:13:03</t>
+          <t>2026-07-20 16:28:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -16915,51 +17437,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>646.01</v>
+        <v>645.85</v>
       </c>
       <c r="F4" t="n">
-        <v>1639846903808</v>
+        <v>1639440580608</v>
       </c>
       <c r="G4" t="n">
-        <v>27.51</v>
+        <v>27.52</v>
       </c>
       <c r="H4" t="n">
         <v>36.32896</v>
       </c>
       <c r="I4" t="n">
-        <v>23.482733</v>
+        <v>23.468386</v>
       </c>
       <c r="J4" t="n">
-        <v>17.782232</v>
+        <v>17.777826</v>
       </c>
       <c r="K4" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>7.628508</v>
+        <v>7.626618</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04258448011640687</v>
+        <v>0.04261051327707672</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05623590966084117</v>
+        <v>0.05624984129441821</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.04598000049591065</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01082591076710337</v>
+        <v>0.01026984079850756</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-17 16:13:03</t>
+          <t>2026-07-20 16:28:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -16973,51 +17495,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>247.23</v>
+        <v>249.99</v>
       </c>
       <c r="F5" t="n">
-        <v>2659480240128</v>
+        <v>2689169883136</v>
       </c>
       <c r="G5" t="n">
-        <v>8.369999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>9.910030000000001</v>
+        <v>9.93547</v>
       </c>
       <c r="I5" t="n">
-        <v>29.537634</v>
+        <v>29.903112</v>
       </c>
       <c r="J5" t="n">
-        <v>24.94745</v>
+        <v>25.161367</v>
       </c>
       <c r="K5" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5804608</v>
+        <v>3.620432</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03385511467054969</v>
+        <v>0.03344133765350614</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04008425352910246</v>
+        <v>0.03974346973878955</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.04598000049591065</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.005325745364635329</v>
+        <v>-0.006236530757121092</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-17 16:13:03</t>
+          <t>2026-07-20 16:28:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -17031,51 +17553,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>333.74</v>
+        <v>326.59</v>
       </c>
       <c r="F6" t="n">
-        <v>4901757779968</v>
+        <v>4796743417856</v>
       </c>
       <c r="G6" t="n">
-        <v>8.26</v>
+        <v>8.24</v>
       </c>
       <c r="H6" t="n">
-        <v>9.63869</v>
+        <v>9.639150000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>40.404358</v>
+        <v>39.63471</v>
       </c>
       <c r="J6" t="n">
-        <v>34.625034</v>
+        <v>33.88162</v>
       </c>
       <c r="K6" t="n">
-        <v>2.54</v>
+        <v>2.69</v>
       </c>
       <c r="L6" t="n">
-        <v>10.858001</v>
+        <v>10.6253805</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02474980523761012</v>
+        <v>0.02523041121895955</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02888083538083538</v>
+        <v>0.02951452892005267</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.04598000049591065</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01652916351290241</v>
+        <v>-0.01646547157585797</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-17 16:13:03</t>
+          <t>2026-07-20 16:28:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -17089,51 +17611,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>202.81</v>
+        <v>203.28</v>
       </c>
       <c r="F7" t="n">
-        <v>4912260841472</v>
+        <v>4923644706816</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
       </c>
       <c r="H7" t="n">
-        <v>12.83126</v>
+        <v>12.84363</v>
       </c>
       <c r="I7" t="n">
-        <v>31.058191</v>
+        <v>31.130167</v>
       </c>
       <c r="J7" t="n">
-        <v>15.80593</v>
+        <v>15.827301</v>
       </c>
       <c r="K7" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>19.378443</v>
+        <v>19.423351</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03219762339135152</v>
+        <v>0.03212317985045258</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06326739312657167</v>
+        <v>0.06318196576151121</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.04598000049591065</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01785739423283388</v>
+        <v>0.01720196526560056</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-17 16:13:03</t>
+          <t>2026-07-20 16:28:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -17147,51 +17669,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>495.76</v>
+        <v>503.57</v>
       </c>
       <c r="F8" t="n">
-        <v>808386560000</v>
+        <v>821121515520</v>
       </c>
       <c r="G8" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="H8" t="n">
         <v>13.46474</v>
       </c>
       <c r="I8" t="n">
-        <v>164.70432</v>
+        <v>166.74504</v>
       </c>
       <c r="J8" t="n">
-        <v>36.81913</v>
+        <v>37.399162</v>
       </c>
       <c r="K8" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="L8" t="n">
-        <v>21.58345</v>
+        <v>21.923466</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006071486203001452</v>
+        <v>0.005997180133844352</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02715979506212684</v>
+        <v>0.02673856663423159</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.04598000049591065</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01825020383161095</v>
+        <v>-0.01924143386167906</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-17 16:13:03</t>
+          <t>2026-07-20 16:28:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -17205,51 +17727,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>370.825</v>
+        <v>378.16</v>
       </c>
       <c r="F9" t="n">
-        <v>1764229775360</v>
+        <v>1799126515712</v>
       </c>
       <c r="G9" t="n">
-        <v>6.03</v>
+        <v>6.01</v>
       </c>
       <c r="H9" t="n">
         <v>19.4169</v>
       </c>
       <c r="I9" t="n">
-        <v>61.496685</v>
+        <v>62.921795</v>
       </c>
       <c r="J9" t="n">
-        <v>19.098053</v>
+        <v>19.475817</v>
       </c>
       <c r="K9" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="L9" t="n">
-        <v>23.37812</v>
+        <v>23.840542</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01626103957392301</v>
+        <v>0.01589274381214301</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05236135643497607</v>
+        <v>0.05134572667653902</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.04598000049591065</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006951357541238275</v>
+        <v>0.005365726180628375</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-17 16:13:03</t>
+          <t>2026-07-20 16:28:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -17263,40 +17785,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>68.95</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>290334539776</v>
+        <v>284649979904</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8196</v>
+        <v>3.81704</v>
       </c>
       <c r="I10" t="n">
-        <v>21.682388</v>
+        <v>21.25786</v>
       </c>
       <c r="J10" t="n">
-        <v>18.051626</v>
+        <v>17.710058</v>
       </c>
       <c r="K10" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="L10" t="n">
-        <v>6.002273</v>
+        <v>5.8847523</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04612037708484409</v>
+        <v>0.0470414201183432</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05539666424945612</v>
+        <v>0.05646508875739645</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.04598000049591065</v>
       </c>
       <c r="P10" t="n">
-        <v>0.009986665355718329</v>
+        <v>0.01048508826148581</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P289"/>
+  <dimension ref="A1:P298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16727,16 +16727,16 @@
         <v>10.6253805</v>
       </c>
       <c r="M281" t="n">
-        <v>0.02523041121895955</v>
+        <v>0.0252304112189595</v>
       </c>
       <c r="N281" t="n">
-        <v>0.02951452892005267</v>
+        <v>0.0295145289200526</v>
       </c>
       <c r="O281" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.0459800004959106</v>
       </c>
       <c r="P281" t="n">
-        <v>-0.01646547157585797</v>
+        <v>-0.0164654715758579</v>
       </c>
     </row>
     <row r="282">
@@ -16785,16 +16785,16 @@
         <v>21.923466</v>
       </c>
       <c r="M282" t="n">
-        <v>0.005997180133844352</v>
+        <v>0.0059971801338443</v>
       </c>
       <c r="N282" t="n">
-        <v>0.02673856663423159</v>
+        <v>0.0267385666342315</v>
       </c>
       <c r="O282" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.0459800004959106</v>
       </c>
       <c r="P282" t="n">
-        <v>-0.01924143386167906</v>
+        <v>-0.019241433861679</v>
       </c>
     </row>
     <row r="283">
@@ -16843,16 +16843,16 @@
         <v>3.620432</v>
       </c>
       <c r="M283" t="n">
-        <v>0.03344133765350614</v>
+        <v>0.0334413376535061</v>
       </c>
       <c r="N283" t="n">
-        <v>0.03974346973878955</v>
+        <v>0.0397434697387895</v>
       </c>
       <c r="O283" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.0459800004959106</v>
       </c>
       <c r="P283" t="n">
-        <v>-0.006236530757121092</v>
+        <v>-0.006236530757121</v>
       </c>
     </row>
     <row r="284">
@@ -16901,16 +16901,16 @@
         <v>23.840542</v>
       </c>
       <c r="M284" t="n">
-        <v>0.01589274381214301</v>
+        <v>0.015892743812143</v>
       </c>
       <c r="N284" t="n">
-        <v>0.05134572667653902</v>
+        <v>0.051345726676539</v>
       </c>
       <c r="O284" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.0459800004959106</v>
       </c>
       <c r="P284" t="n">
-        <v>0.005365726180628375</v>
+        <v>0.0053657261806283</v>
       </c>
     </row>
     <row r="285">
@@ -16959,16 +16959,16 @@
         <v>10.148255</v>
       </c>
       <c r="M285" t="n">
-        <v>0.03733955659276546</v>
+        <v>0.0373395565927654</v>
       </c>
       <c r="N285" t="n">
-        <v>0.04169231863847227</v>
+        <v>0.0416923186384722</v>
       </c>
       <c r="O285" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.0459800004959106</v>
       </c>
       <c r="P285" t="n">
-        <v>-0.004287681857438379</v>
+        <v>-0.0042876818574383</v>
       </c>
     </row>
     <row r="286">
@@ -17017,16 +17017,16 @@
         <v>7.626618</v>
       </c>
       <c r="M286" t="n">
-        <v>0.04261051327707672</v>
+        <v>0.0426105132770767</v>
       </c>
       <c r="N286" t="n">
-        <v>0.05624984129441821</v>
+        <v>0.0562498412944182</v>
       </c>
       <c r="O286" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.0459800004959106</v>
       </c>
       <c r="P286" t="n">
-        <v>0.01026984079850756</v>
+        <v>0.0102698407985075</v>
       </c>
     </row>
     <row r="287">
@@ -17075,16 +17075,16 @@
         <v>9.389378000000001</v>
       </c>
       <c r="M287" t="n">
-        <v>0.04171120336075965</v>
+        <v>0.0417112033607596</v>
       </c>
       <c r="N287" t="n">
-        <v>0.04817681274702328</v>
+        <v>0.0481768127470232</v>
       </c>
       <c r="O287" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.0459800004959106</v>
       </c>
       <c r="P287" t="n">
-        <v>0.002196812251112637</v>
+        <v>0.0021968122511126</v>
       </c>
     </row>
     <row r="288">
@@ -17136,13 +17136,13 @@
         <v>0.0470414201183432</v>
       </c>
       <c r="N288" t="n">
-        <v>0.05646508875739645</v>
+        <v>0.0564650887573964</v>
       </c>
       <c r="O288" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.0459800004959106</v>
       </c>
       <c r="P288" t="n">
-        <v>0.01048508826148581</v>
+        <v>0.0104850882614858</v>
       </c>
     </row>
     <row r="289">
@@ -17191,16 +17191,538 @@
         <v>19.423351</v>
       </c>
       <c r="M289" t="n">
-        <v>0.03212317985045258</v>
+        <v>0.0321231798504525</v>
       </c>
       <c r="N289" t="n">
-        <v>0.06318196576151121</v>
+        <v>0.06318196576151119</v>
       </c>
       <c r="O289" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.0459800004959106</v>
       </c>
       <c r="P289" t="n">
-        <v>0.01720196526560056</v>
+        <v>0.0172019652656005</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:25:49</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>327.74</v>
+      </c>
+      <c r="F290" t="n">
+        <v>4813633880064</v>
+      </c>
+      <c r="G290" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H290" t="n">
+        <v>9.639150000000001</v>
+      </c>
+      <c r="I290" t="n">
+        <v>39.677963</v>
+      </c>
+      <c r="J290" t="n">
+        <v>34.000923</v>
+      </c>
+      <c r="K290" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="L290" t="n">
+        <v>10.662795</v>
+      </c>
+      <c r="M290" t="n">
+        <v>0.02520290474156343</v>
+      </c>
+      <c r="N290" t="n">
+        <v>0.02941096600964179</v>
+      </c>
+      <c r="O290" t="n">
+        <v>0.04627999782562256</v>
+      </c>
+      <c r="P290" t="n">
+        <v>-0.01686903181598077</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:25:49</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>544.4299999999999</v>
+      </c>
+      <c r="F291" t="n">
+        <v>887747837952</v>
+      </c>
+      <c r="G291" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H291" t="n">
+        <v>13.46474</v>
+      </c>
+      <c r="I291" t="n">
+        <v>180.27483</v>
+      </c>
+      <c r="J291" t="n">
+        <v>40.433754</v>
+      </c>
+      <c r="K291" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L291" t="n">
+        <v>23.70235</v>
+      </c>
+      <c r="M291" t="n">
+        <v>0.00554708594309645</v>
+      </c>
+      <c r="N291" t="n">
+        <v>0.02473181125213526</v>
+      </c>
+      <c r="O291" t="n">
+        <v>0.04627999782562256</v>
+      </c>
+      <c r="P291" t="n">
+        <v>-0.0215481865734873</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:25:49</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>247.55</v>
+      </c>
+      <c r="F292" t="n">
+        <v>2662922452992</v>
+      </c>
+      <c r="G292" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="H292" t="n">
+        <v>9.918060000000001</v>
+      </c>
+      <c r="I292" t="n">
+        <v>29.646706</v>
+      </c>
+      <c r="J292" t="n">
+        <v>24.959518</v>
+      </c>
+      <c r="K292" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L292" t="n">
+        <v>3.585095</v>
+      </c>
+      <c r="M292" t="n">
+        <v>0.03373055948293274</v>
+      </c>
+      <c r="N292" t="n">
+        <v>0.04006487578267016</v>
+      </c>
+      <c r="O292" t="n">
+        <v>0.04627999782562256</v>
+      </c>
+      <c r="P292" t="n">
+        <v>-0.006215122042952395</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:25:49</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>386.5</v>
+      </c>
+      <c r="F293" t="n">
+        <v>1838804762624</v>
+      </c>
+      <c r="G293" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H293" t="n">
+        <v>19.46067</v>
+      </c>
+      <c r="I293" t="n">
+        <v>64.30947999999999</v>
+      </c>
+      <c r="J293" t="n">
+        <v>19.860569</v>
+      </c>
+      <c r="K293" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L293" t="n">
+        <v>24.366325</v>
+      </c>
+      <c r="M293" t="n">
+        <v>0.01554980595084088</v>
+      </c>
+      <c r="N293" t="n">
+        <v>0.05035102199223804</v>
+      </c>
+      <c r="O293" t="n">
+        <v>0.04627999782562256</v>
+      </c>
+      <c r="P293" t="n">
+        <v>0.004071024166615478</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:25:49</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>346.19</v>
+      </c>
+      <c r="F294" t="n">
+        <v>4224408616960</v>
+      </c>
+      <c r="G294" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="H294" t="n">
+        <v>14.67151</v>
+      </c>
+      <c r="I294" t="n">
+        <v>26.40656</v>
+      </c>
+      <c r="J294" t="n">
+        <v>23.596071</v>
+      </c>
+      <c r="K294" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L294" t="n">
+        <v>9.998647999999999</v>
+      </c>
+      <c r="M294" t="n">
+        <v>0.03786937808717756</v>
+      </c>
+      <c r="N294" t="n">
+        <v>0.04237993587336434</v>
+      </c>
+      <c r="O294" t="n">
+        <v>0.04627999782562256</v>
+      </c>
+      <c r="P294" t="n">
+        <v>-0.00390006195225822</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:25:49</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>643.8099999999999</v>
+      </c>
+      <c r="F295" t="n">
+        <v>1634262319104</v>
+      </c>
+      <c r="G295" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="H295" t="n">
+        <v>36.32896</v>
+      </c>
+      <c r="I295" t="n">
+        <v>23.402761</v>
+      </c>
+      <c r="J295" t="n">
+        <v>17.721674</v>
+      </c>
+      <c r="K295" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L295" t="n">
+        <v>7.6025286</v>
+      </c>
+      <c r="M295" t="n">
+        <v>0.04272999798077073</v>
+      </c>
+      <c r="N295" t="n">
+        <v>0.05642807660645222</v>
+      </c>
+      <c r="O295" t="n">
+        <v>0.04627999782562256</v>
+      </c>
+      <c r="P295" t="n">
+        <v>0.01014807878082966</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:25:49</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>397.75</v>
+      </c>
+      <c r="F296" t="n">
+        <v>2954659889152</v>
+      </c>
+      <c r="G296" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="H296" t="n">
+        <v>19.37881</v>
+      </c>
+      <c r="I296" t="n">
+        <v>23.703814</v>
+      </c>
+      <c r="J296" t="n">
+        <v>20.524996</v>
+      </c>
+      <c r="K296" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L296" t="n">
+        <v>9.283414</v>
+      </c>
+      <c r="M296" t="n">
+        <v>0.04218730358265242</v>
+      </c>
+      <c r="N296" t="n">
+        <v>0.04872108108108109</v>
+      </c>
+      <c r="O296" t="n">
+        <v>0.04627999782562256</v>
+      </c>
+      <c r="P296" t="n">
+        <v>0.002441083255458526</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:25:49</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>68.67</v>
+      </c>
+      <c r="F297" t="n">
+        <v>285937729536</v>
+      </c>
+      <c r="G297" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H297" t="n">
+        <v>3.8136</v>
+      </c>
+      <c r="I297" t="n">
+        <v>21.59434</v>
+      </c>
+      <c r="J297" t="n">
+        <v>18.006607</v>
+      </c>
+      <c r="K297" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L297" t="n">
+        <v>5.911375</v>
+      </c>
+      <c r="M297" t="n">
+        <v>0.04630843162953255</v>
+      </c>
+      <c r="N297" t="n">
+        <v>0.05553516819571865</v>
+      </c>
+      <c r="O297" t="n">
+        <v>0.04627999782562256</v>
+      </c>
+      <c r="P297" t="n">
+        <v>0.009255170370096093</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:25:49</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>207.29</v>
+      </c>
+      <c r="F298" t="n">
+        <v>5020770631680</v>
+      </c>
+      <c r="G298" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H298" t="n">
+        <v>12.84363</v>
+      </c>
+      <c r="I298" t="n">
+        <v>31.744255</v>
+      </c>
+      <c r="J298" t="n">
+        <v>16.139519</v>
+      </c>
+      <c r="K298" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L298" t="n">
+        <v>19.806503</v>
+      </c>
+      <c r="M298" t="n">
+        <v>0.03150176081817743</v>
+      </c>
+      <c r="N298" t="n">
+        <v>0.06195971826909161</v>
+      </c>
+      <c r="O298" t="n">
+        <v>0.04627999782562256</v>
+      </c>
+      <c r="P298" t="n">
+        <v>0.01567972044346905</v>
       </c>
     </row>
   </sheetData>
@@ -17302,12 +17824,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-20 16:28:10</t>
+          <t>2026-07-21 16:25:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -17321,51 +17843,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>351.37</v>
+        <v>346.19</v>
       </c>
       <c r="F2" t="n">
-        <v>4287617826816</v>
+        <v>4224408616960</v>
       </c>
       <c r="G2" t="n">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="H2" t="n">
-        <v>14.64943</v>
+        <v>14.67151</v>
       </c>
       <c r="I2" t="n">
-        <v>26.78125</v>
+        <v>26.40656</v>
       </c>
       <c r="J2" t="n">
-        <v>23.985233</v>
+        <v>23.596071</v>
       </c>
       <c r="K2" t="n">
         <v>1.36</v>
       </c>
       <c r="L2" t="n">
-        <v>10.148255</v>
+        <v>9.998647999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03733955659276546</v>
+        <v>0.03786937808717756</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04169231863847227</v>
+        <v>0.04237993587336434</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.04627999782562256</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.004287681857438379</v>
+        <v>-0.00390006195225822</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-20 16:28:10</t>
+          <t>2026-07-21 16:25:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -17379,51 +17901,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>402.29</v>
+        <v>397.75</v>
       </c>
       <c r="F3" t="n">
-        <v>2988385239040</v>
+        <v>2954659889152</v>
       </c>
       <c r="G3" t="n">
         <v>16.78</v>
       </c>
       <c r="H3" t="n">
-        <v>19.38105</v>
+        <v>19.37881</v>
       </c>
       <c r="I3" t="n">
-        <v>23.974373</v>
+        <v>23.703814</v>
       </c>
       <c r="J3" t="n">
-        <v>20.756874</v>
+        <v>20.524996</v>
       </c>
       <c r="K3" t="n">
         <v>1.21</v>
       </c>
       <c r="L3" t="n">
-        <v>9.389378000000001</v>
+        <v>9.283414</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04171120336075965</v>
+        <v>0.04218730358265242</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04817681274702328</v>
+        <v>0.04872108108108109</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.04627999782562256</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002196812251112637</v>
+        <v>0.002441083255458526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-20 16:28:10</t>
+          <t>2026-07-21 16:25:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -17437,51 +17959,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>645.85</v>
+        <v>643.8099999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1639440580608</v>
+        <v>1634262319104</v>
       </c>
       <c r="G4" t="n">
-        <v>27.52</v>
+        <v>27.51</v>
       </c>
       <c r="H4" t="n">
         <v>36.32896</v>
       </c>
       <c r="I4" t="n">
-        <v>23.468386</v>
+        <v>23.402761</v>
       </c>
       <c r="J4" t="n">
-        <v>17.777826</v>
+        <v>17.721674</v>
       </c>
       <c r="K4" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>7.626618</v>
+        <v>7.6025286</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04261051327707672</v>
+        <v>0.04272999798077073</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05624984129441821</v>
+        <v>0.05642807660645222</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.04627999782562256</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01026984079850756</v>
+        <v>0.01014807878082966</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-20 16:28:10</t>
+          <t>2026-07-21 16:25:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -17495,51 +18017,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>249.99</v>
+        <v>247.55</v>
       </c>
       <c r="F5" t="n">
-        <v>2689169883136</v>
+        <v>2662922452992</v>
       </c>
       <c r="G5" t="n">
-        <v>8.359999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="H5" t="n">
-        <v>9.93547</v>
+        <v>9.918060000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>29.903112</v>
+        <v>29.646706</v>
       </c>
       <c r="J5" t="n">
-        <v>25.161367</v>
+        <v>24.959518</v>
       </c>
       <c r="K5" t="n">
         <v>1.3</v>
       </c>
       <c r="L5" t="n">
-        <v>3.620432</v>
+        <v>3.585095</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03344133765350614</v>
+        <v>0.03373055948293274</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03974346973878955</v>
+        <v>0.04006487578267016</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.04627999782562256</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.006236530757121092</v>
+        <v>-0.006215122042952395</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-20 16:28:10</t>
+          <t>2026-07-21 16:25:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -17553,51 +18075,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>326.59</v>
+        <v>327.74</v>
       </c>
       <c r="F6" t="n">
-        <v>4796743417856</v>
+        <v>4813633880064</v>
       </c>
       <c r="G6" t="n">
-        <v>8.24</v>
+        <v>8.26</v>
       </c>
       <c r="H6" t="n">
         <v>9.639150000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>39.63471</v>
+        <v>39.677963</v>
       </c>
       <c r="J6" t="n">
-        <v>33.88162</v>
+        <v>34.000923</v>
       </c>
       <c r="K6" t="n">
         <v>2.69</v>
       </c>
       <c r="L6" t="n">
-        <v>10.6253805</v>
+        <v>10.662795</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02523041121895955</v>
+        <v>0.02520290474156343</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02951452892005267</v>
+        <v>0.02941096600964179</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.04627999782562256</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01646547157585797</v>
+        <v>-0.01686903181598077</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-20 16:28:10</t>
+          <t>2026-07-21 16:25:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -17611,10 +18133,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>203.28</v>
+        <v>207.29</v>
       </c>
       <c r="F7" t="n">
-        <v>4923644706816</v>
+        <v>5020770631680</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
@@ -17623,39 +18145,39 @@
         <v>12.84363</v>
       </c>
       <c r="I7" t="n">
-        <v>31.130167</v>
+        <v>31.744255</v>
       </c>
       <c r="J7" t="n">
-        <v>15.827301</v>
+        <v>16.139519</v>
       </c>
       <c r="K7" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>19.423351</v>
+        <v>19.806503</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03212317985045258</v>
+        <v>0.03150176081817743</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06318196576151121</v>
+        <v>0.06195971826909161</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.04627999782562256</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01720196526560056</v>
+        <v>0.01567972044346905</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-20 16:28:10</t>
+          <t>2026-07-21 16:25:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -17669,10 +18191,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>503.57</v>
+        <v>544.4299999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>821121515520</v>
+        <v>887747837952</v>
       </c>
       <c r="G8" t="n">
         <v>3.02</v>
@@ -17681,39 +18203,39 @@
         <v>13.46474</v>
       </c>
       <c r="I8" t="n">
-        <v>166.74504</v>
+        <v>180.27483</v>
       </c>
       <c r="J8" t="n">
-        <v>37.399162</v>
+        <v>40.433754</v>
       </c>
       <c r="K8" t="n">
         <v>1.16</v>
       </c>
       <c r="L8" t="n">
-        <v>21.923466</v>
+        <v>23.70235</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005997180133844352</v>
+        <v>0.00554708594309645</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02673856663423159</v>
+        <v>0.02473181125213526</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.04627999782562256</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01924143386167906</v>
+        <v>-0.0215481865734873</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-20 16:28:10</t>
+          <t>2026-07-21 16:25:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -17727,51 +18249,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>378.16</v>
+        <v>386.5</v>
       </c>
       <c r="F9" t="n">
-        <v>1799126515712</v>
+        <v>1838804762624</v>
       </c>
       <c r="G9" t="n">
         <v>6.01</v>
       </c>
       <c r="H9" t="n">
-        <v>19.4169</v>
+        <v>19.46067</v>
       </c>
       <c r="I9" t="n">
-        <v>62.921795</v>
+        <v>64.30947999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>19.475817</v>
+        <v>19.860569</v>
       </c>
       <c r="K9" t="n">
         <v>0.42</v>
       </c>
       <c r="L9" t="n">
-        <v>23.840542</v>
+        <v>24.366325</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01589274381214301</v>
+        <v>0.01554980595084088</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05134572667653902</v>
+        <v>0.05035102199223804</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.04627999782562256</v>
       </c>
       <c r="P9" t="n">
-        <v>0.005365726180628375</v>
+        <v>0.004071024166615478</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-20 16:28:10</t>
+          <t>2026-07-21 16:25:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -17785,40 +18307,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67.59999999999999</v>
+        <v>68.67</v>
       </c>
       <c r="F10" t="n">
-        <v>284649979904</v>
+        <v>285937729536</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.81704</v>
+        <v>3.8136</v>
       </c>
       <c r="I10" t="n">
-        <v>21.25786</v>
+        <v>21.59434</v>
       </c>
       <c r="J10" t="n">
-        <v>17.710058</v>
+        <v>18.006607</v>
       </c>
       <c r="K10" t="n">
         <v>1.35</v>
       </c>
       <c r="L10" t="n">
-        <v>5.8847523</v>
+        <v>5.911375</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0470414201183432</v>
+        <v>0.04630843162953255</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05646508875739645</v>
+        <v>0.05553516819571865</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04598000049591065</v>
+        <v>0.04627999782562256</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01048508826148581</v>
+        <v>0.009255170370096093</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P298"/>
+  <dimension ref="A1:P307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17249,16 +17249,16 @@
         <v>10.662795</v>
       </c>
       <c r="M290" t="n">
-        <v>0.02520290474156343</v>
+        <v>0.0252029047415634</v>
       </c>
       <c r="N290" t="n">
-        <v>0.02941096600964179</v>
+        <v>0.0294109660096417</v>
       </c>
       <c r="O290" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.0462799978256225</v>
       </c>
       <c r="P290" t="n">
-        <v>-0.01686903181598077</v>
+        <v>-0.0168690318159807</v>
       </c>
     </row>
     <row r="291">
@@ -17307,16 +17307,16 @@
         <v>23.70235</v>
       </c>
       <c r="M291" t="n">
-        <v>0.00554708594309645</v>
+        <v>0.0055470859430964</v>
       </c>
       <c r="N291" t="n">
-        <v>0.02473181125213526</v>
+        <v>0.0247318112521352</v>
       </c>
       <c r="O291" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.0462799978256225</v>
       </c>
       <c r="P291" t="n">
-        <v>-0.0215481865734873</v>
+        <v>-0.0215481865734872</v>
       </c>
     </row>
     <row r="292">
@@ -17365,16 +17365,16 @@
         <v>3.585095</v>
       </c>
       <c r="M292" t="n">
-        <v>0.03373055948293274</v>
+        <v>0.0337305594829327</v>
       </c>
       <c r="N292" t="n">
-        <v>0.04006487578267016</v>
+        <v>0.0400648757826701</v>
       </c>
       <c r="O292" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.0462799978256225</v>
       </c>
       <c r="P292" t="n">
-        <v>-0.006215122042952395</v>
+        <v>-0.0062151220429523</v>
       </c>
     </row>
     <row r="293">
@@ -17423,16 +17423,16 @@
         <v>24.366325</v>
       </c>
       <c r="M293" t="n">
-        <v>0.01554980595084088</v>
+        <v>0.0155498059508408</v>
       </c>
       <c r="N293" t="n">
-        <v>0.05035102199223804</v>
+        <v>0.050351021992238</v>
       </c>
       <c r="O293" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.0462799978256225</v>
       </c>
       <c r="P293" t="n">
-        <v>0.004071024166615478</v>
+        <v>0.0040710241666154</v>
       </c>
     </row>
     <row r="294">
@@ -17481,16 +17481,16 @@
         <v>9.998647999999999</v>
       </c>
       <c r="M294" t="n">
-        <v>0.03786937808717756</v>
+        <v>0.0378693780871775</v>
       </c>
       <c r="N294" t="n">
-        <v>0.04237993587336434</v>
+        <v>0.0423799358733643</v>
       </c>
       <c r="O294" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.0462799978256225</v>
       </c>
       <c r="P294" t="n">
-        <v>-0.00390006195225822</v>
+        <v>-0.0039000619522582</v>
       </c>
     </row>
     <row r="295">
@@ -17539,16 +17539,16 @@
         <v>7.6025286</v>
       </c>
       <c r="M295" t="n">
-        <v>0.04272999798077073</v>
+        <v>0.0427299979807707</v>
       </c>
       <c r="N295" t="n">
-        <v>0.05642807660645222</v>
+        <v>0.0564280766064522</v>
       </c>
       <c r="O295" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.0462799978256225</v>
       </c>
       <c r="P295" t="n">
-        <v>0.01014807878082966</v>
+        <v>0.0101480787808296</v>
       </c>
     </row>
     <row r="296">
@@ -17597,16 +17597,16 @@
         <v>9.283414</v>
       </c>
       <c r="M296" t="n">
-        <v>0.04218730358265242</v>
+        <v>0.0421873035826524</v>
       </c>
       <c r="N296" t="n">
-        <v>0.04872108108108109</v>
+        <v>0.048721081081081</v>
       </c>
       <c r="O296" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.0462799978256225</v>
       </c>
       <c r="P296" t="n">
-        <v>0.002441083255458526</v>
+        <v>0.0024410832554585</v>
       </c>
     </row>
     <row r="297">
@@ -17655,16 +17655,16 @@
         <v>5.911375</v>
       </c>
       <c r="M297" t="n">
-        <v>0.04630843162953255</v>
+        <v>0.0463084316295325</v>
       </c>
       <c r="N297" t="n">
-        <v>0.05553516819571865</v>
+        <v>0.0555351681957186</v>
       </c>
       <c r="O297" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.0462799978256225</v>
       </c>
       <c r="P297" t="n">
-        <v>0.009255170370096093</v>
+        <v>0.009255170370096001</v>
       </c>
     </row>
     <row r="298">
@@ -17713,16 +17713,538 @@
         <v>19.806503</v>
       </c>
       <c r="M298" t="n">
-        <v>0.03150176081817743</v>
+        <v>0.0315017608181774</v>
       </c>
       <c r="N298" t="n">
-        <v>0.06195971826909161</v>
+        <v>0.0619597182690916</v>
       </c>
       <c r="O298" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.0462799978256225</v>
       </c>
       <c r="P298" t="n">
-        <v>0.01567972044346905</v>
+        <v>0.015679720443469</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-07-22 16:27:56</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>325.89</v>
+      </c>
+      <c r="F299" t="n">
+        <v>4786462654464</v>
+      </c>
+      <c r="G299" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H299" t="n">
+        <v>9.639150000000001</v>
+      </c>
+      <c r="I299" t="n">
+        <v>39.453995</v>
+      </c>
+      <c r="J299" t="n">
+        <v>33.809002</v>
+      </c>
+      <c r="K299" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="L299" t="n">
+        <v>10.602608</v>
+      </c>
+      <c r="M299" t="n">
+        <v>0.02534597563595078</v>
+      </c>
+      <c r="N299" t="n">
+        <v>0.02957792506674032</v>
+      </c>
+      <c r="O299" t="n">
+        <v>0.04657000064849853</v>
+      </c>
+      <c r="P299" t="n">
+        <v>-0.01699207558175822</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-07-22 16:27:56</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>552.33</v>
+      </c>
+      <c r="F300" t="n">
+        <v>900629659648</v>
+      </c>
+      <c r="G300" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H300" t="n">
+        <v>13.49207</v>
+      </c>
+      <c r="I300" t="n">
+        <v>184.72575</v>
+      </c>
+      <c r="J300" t="n">
+        <v>40.93738</v>
+      </c>
+      <c r="K300" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L300" t="n">
+        <v>24.046288</v>
+      </c>
+      <c r="M300" t="n">
+        <v>0.005413430376767512</v>
+      </c>
+      <c r="N300" t="n">
+        <v>0.02442755236905473</v>
+      </c>
+      <c r="O300" t="n">
+        <v>0.04657000064849853</v>
+      </c>
+      <c r="P300" t="n">
+        <v>-0.0221424482794438</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-07-22 16:27:56</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>244.85</v>
+      </c>
+      <c r="F301" t="n">
+        <v>2633878470656</v>
+      </c>
+      <c r="G301" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="H301" t="n">
+        <v>9.91676</v>
+      </c>
+      <c r="I301" t="n">
+        <v>29.253286</v>
+      </c>
+      <c r="J301" t="n">
+        <v>24.690523</v>
+      </c>
+      <c r="K301" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L301" t="n">
+        <v>3.545993</v>
+      </c>
+      <c r="M301" t="n">
+        <v>0.03418419440473759</v>
+      </c>
+      <c r="N301" t="n">
+        <v>0.04050136818460282</v>
+      </c>
+      <c r="O301" t="n">
+        <v>0.04657000064849853</v>
+      </c>
+      <c r="P301" t="n">
+        <v>-0.006068632463895711</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-07-22 16:27:56</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>396.81</v>
+      </c>
+      <c r="F302" t="n">
+        <v>1887855443968</v>
+      </c>
+      <c r="G302" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="H302" t="n">
+        <v>19.46067</v>
+      </c>
+      <c r="I302" t="n">
+        <v>66.24541499999999</v>
+      </c>
+      <c r="J302" t="n">
+        <v>20.390356</v>
+      </c>
+      <c r="K302" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L302" t="n">
+        <v>25.016306</v>
+      </c>
+      <c r="M302" t="n">
+        <v>0.0150953857009652</v>
+      </c>
+      <c r="N302" t="n">
+        <v>0.0490427912603009</v>
+      </c>
+      <c r="O302" t="n">
+        <v>0.04657000064849853</v>
+      </c>
+      <c r="P302" t="n">
+        <v>0.002472790611802368</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-07-22 16:27:56</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>341.91</v>
+      </c>
+      <c r="F303" t="n">
+        <v>4172181667840</v>
+      </c>
+      <c r="G303" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="H303" t="n">
+        <v>14.67422</v>
+      </c>
+      <c r="I303" t="n">
+        <v>26.060213</v>
+      </c>
+      <c r="J303" t="n">
+        <v>23.300047</v>
+      </c>
+      <c r="K303" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L303" t="n">
+        <v>9.875031999999999</v>
+      </c>
+      <c r="M303" t="n">
+        <v>0.03837267117077593</v>
+      </c>
+      <c r="N303" t="n">
+        <v>0.04291837033137375</v>
+      </c>
+      <c r="O303" t="n">
+        <v>0.04657000064849853</v>
+      </c>
+      <c r="P303" t="n">
+        <v>-0.003651630317124781</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-07-22 16:27:56</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>627.17</v>
+      </c>
+      <c r="F304" t="n">
+        <v>1592022925312</v>
+      </c>
+      <c r="G304" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="H304" t="n">
+        <v>37.01198</v>
+      </c>
+      <c r="I304" t="n">
+        <v>22.814478</v>
+      </c>
+      <c r="J304" t="n">
+        <v>16.945055</v>
+      </c>
+      <c r="K304" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L304" t="n">
+        <v>7.4060326</v>
+      </c>
+      <c r="M304" t="n">
+        <v>0.04383181593507342</v>
+      </c>
+      <c r="N304" t="n">
+        <v>0.05901427045298723</v>
+      </c>
+      <c r="O304" t="n">
+        <v>0.04657000064849853</v>
+      </c>
+      <c r="P304" t="n">
+        <v>0.0124442698044887</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-07-22 16:27:56</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>390.34</v>
+      </c>
+      <c r="F305" t="n">
+        <v>2899615154176</v>
+      </c>
+      <c r="G305" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="H305" t="n">
+        <v>19.37881</v>
+      </c>
+      <c r="I305" t="n">
+        <v>23.248362</v>
+      </c>
+      <c r="J305" t="n">
+        <v>20.142618</v>
+      </c>
+      <c r="K305" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L305" t="n">
+        <v>9.110466000000001</v>
+      </c>
+      <c r="M305" t="n">
+        <v>0.04301378285597172</v>
+      </c>
+      <c r="N305" t="n">
+        <v>0.0496459753035815</v>
+      </c>
+      <c r="O305" t="n">
+        <v>0.04657000064849853</v>
+      </c>
+      <c r="P305" t="n">
+        <v>0.003075974655082969</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026-07-22 16:27:56</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>68.53</v>
+      </c>
+      <c r="F306" t="n">
+        <v>285354786816</v>
+      </c>
+      <c r="G306" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H306" t="n">
+        <v>3.81314</v>
+      </c>
+      <c r="I306" t="n">
+        <v>21.550314</v>
+      </c>
+      <c r="J306" t="n">
+        <v>17.972065</v>
+      </c>
+      <c r="K306" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L306" t="n">
+        <v>5.8993235</v>
+      </c>
+      <c r="M306" t="n">
+        <v>0.04640303516708012</v>
+      </c>
+      <c r="N306" t="n">
+        <v>0.05564190865314461</v>
+      </c>
+      <c r="O306" t="n">
+        <v>0.04657000064849853</v>
+      </c>
+      <c r="P306" t="n">
+        <v>0.009071908004646079</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-07-22 16:27:56</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>212.06</v>
+      </c>
+      <c r="F307" t="n">
+        <v>5136305356800</v>
+      </c>
+      <c r="G307" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H307" t="n">
+        <v>12.86903</v>
+      </c>
+      <c r="I307" t="n">
+        <v>32.47473</v>
+      </c>
+      <c r="J307" t="n">
+        <v>16.478321</v>
+      </c>
+      <c r="K307" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L307" t="n">
+        <v>20.26228</v>
+      </c>
+      <c r="M307" t="n">
+        <v>0.03079317174384608</v>
+      </c>
+      <c r="N307" t="n">
+        <v>0.06068579647269641</v>
+      </c>
+      <c r="O307" t="n">
+        <v>0.04657000064849853</v>
+      </c>
+      <c r="P307" t="n">
+        <v>0.01411579582419788</v>
       </c>
     </row>
   </sheetData>
@@ -17824,12 +18346,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-21 16:25:49</t>
+          <t>2026-07-22 16:27:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -17843,51 +18365,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>346.19</v>
+        <v>341.91</v>
       </c>
       <c r="F2" t="n">
-        <v>4224408616960</v>
+        <v>4172181667840</v>
       </c>
       <c r="G2" t="n">
-        <v>13.11</v>
+        <v>13.12</v>
       </c>
       <c r="H2" t="n">
-        <v>14.67151</v>
+        <v>14.67422</v>
       </c>
       <c r="I2" t="n">
-        <v>26.40656</v>
+        <v>26.060213</v>
       </c>
       <c r="J2" t="n">
-        <v>23.596071</v>
+        <v>23.300047</v>
       </c>
       <c r="K2" t="n">
         <v>1.36</v>
       </c>
       <c r="L2" t="n">
-        <v>9.998647999999999</v>
+        <v>9.875031999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03786937808717756</v>
+        <v>0.03837267117077593</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04237993587336434</v>
+        <v>0.04291837033137375</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.04657000064849853</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.00390006195225822</v>
+        <v>-0.003651630317124781</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-21 16:25:49</t>
+          <t>2026-07-22 16:27:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -17901,51 +18423,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>397.75</v>
+        <v>390.34</v>
       </c>
       <c r="F3" t="n">
-        <v>2954659889152</v>
+        <v>2899615154176</v>
       </c>
       <c r="G3" t="n">
-        <v>16.78</v>
+        <v>16.79</v>
       </c>
       <c r="H3" t="n">
         <v>19.37881</v>
       </c>
       <c r="I3" t="n">
-        <v>23.703814</v>
+        <v>23.248362</v>
       </c>
       <c r="J3" t="n">
-        <v>20.524996</v>
+        <v>20.142618</v>
       </c>
       <c r="K3" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="L3" t="n">
-        <v>9.283414</v>
+        <v>9.110466000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04218730358265242</v>
+        <v>0.04301378285597172</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04872108108108109</v>
+        <v>0.0496459753035815</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.04657000064849853</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002441083255458526</v>
+        <v>0.003075974655082969</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-21 16:25:49</t>
+          <t>2026-07-22 16:27:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -17959,51 +18481,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>643.8099999999999</v>
+        <v>627.17</v>
       </c>
       <c r="F4" t="n">
-        <v>1634262319104</v>
+        <v>1592022925312</v>
       </c>
       <c r="G4" t="n">
-        <v>27.51</v>
+        <v>27.49</v>
       </c>
       <c r="H4" t="n">
-        <v>36.32896</v>
+        <v>37.01198</v>
       </c>
       <c r="I4" t="n">
-        <v>23.402761</v>
+        <v>22.814478</v>
       </c>
       <c r="J4" t="n">
-        <v>17.721674</v>
+        <v>16.945055</v>
       </c>
       <c r="K4" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>7.6025286</v>
+        <v>7.4060326</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04272999798077073</v>
+        <v>0.04383181593507342</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05642807660645222</v>
+        <v>0.05901427045298723</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.04657000064849853</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01014807878082966</v>
+        <v>0.0124442698044887</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-21 16:25:49</t>
+          <t>2026-07-22 16:27:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -18017,51 +18539,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>247.55</v>
+        <v>244.85</v>
       </c>
       <c r="F5" t="n">
-        <v>2662922452992</v>
+        <v>2633878470656</v>
       </c>
       <c r="G5" t="n">
-        <v>8.35</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>9.918060000000001</v>
+        <v>9.91676</v>
       </c>
       <c r="I5" t="n">
-        <v>29.646706</v>
+        <v>29.253286</v>
       </c>
       <c r="J5" t="n">
-        <v>24.959518</v>
+        <v>24.690523</v>
       </c>
       <c r="K5" t="n">
         <v>1.3</v>
       </c>
       <c r="L5" t="n">
-        <v>3.585095</v>
+        <v>3.545993</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03373055948293274</v>
+        <v>0.03418419440473759</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04006487578267016</v>
+        <v>0.04050136818460282</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.04657000064849853</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.006215122042952395</v>
+        <v>-0.006068632463895711</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-21 16:25:49</t>
+          <t>2026-07-22 16:27:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -18075,10 +18597,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>327.74</v>
+        <v>325.89</v>
       </c>
       <c r="F6" t="n">
-        <v>4813633880064</v>
+        <v>4786462654464</v>
       </c>
       <c r="G6" t="n">
         <v>8.26</v>
@@ -18087,39 +18609,39 @@
         <v>9.639150000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>39.677963</v>
+        <v>39.453995</v>
       </c>
       <c r="J6" t="n">
-        <v>34.000923</v>
+        <v>33.809002</v>
       </c>
       <c r="K6" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="L6" t="n">
-        <v>10.662795</v>
+        <v>10.602608</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02520290474156343</v>
+        <v>0.02534597563595078</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02941096600964179</v>
+        <v>0.02957792506674032</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.04657000064849853</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01686903181598077</v>
+        <v>-0.01699207558175822</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-21 16:25:49</t>
+          <t>2026-07-22 16:27:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -18133,51 +18655,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>207.29</v>
+        <v>212.06</v>
       </c>
       <c r="F7" t="n">
-        <v>5020770631680</v>
+        <v>5136305356800</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
       </c>
       <c r="H7" t="n">
-        <v>12.84363</v>
+        <v>12.86903</v>
       </c>
       <c r="I7" t="n">
-        <v>31.744255</v>
+        <v>32.47473</v>
       </c>
       <c r="J7" t="n">
-        <v>16.139519</v>
+        <v>16.478321</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="L7" t="n">
-        <v>19.806503</v>
+        <v>20.26228</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03150176081817743</v>
+        <v>0.03079317174384608</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06195971826909161</v>
+        <v>0.06068579647269641</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.04657000064849853</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01567972044346905</v>
+        <v>0.01411579582419788</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-21 16:25:49</t>
+          <t>2026-07-22 16:27:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -18191,51 +18713,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>544.4299999999999</v>
+        <v>552.33</v>
       </c>
       <c r="F8" t="n">
-        <v>887747837952</v>
+        <v>900629659648</v>
       </c>
       <c r="G8" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="H8" t="n">
-        <v>13.46474</v>
+        <v>13.49207</v>
       </c>
       <c r="I8" t="n">
-        <v>180.27483</v>
+        <v>184.72575</v>
       </c>
       <c r="J8" t="n">
-        <v>40.433754</v>
+        <v>40.93738</v>
       </c>
       <c r="K8" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="L8" t="n">
-        <v>23.70235</v>
+        <v>24.046288</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00554708594309645</v>
+        <v>0.005413430376767512</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02473181125213526</v>
+        <v>0.02442755236905473</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.04657000064849853</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0215481865734873</v>
+        <v>-0.0221424482794438</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-21 16:25:49</t>
+          <t>2026-07-22 16:27:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -18249,51 +18771,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>386.5</v>
+        <v>396.81</v>
       </c>
       <c r="F9" t="n">
-        <v>1838804762624</v>
+        <v>1887855443968</v>
       </c>
       <c r="G9" t="n">
-        <v>6.01</v>
+        <v>5.99</v>
       </c>
       <c r="H9" t="n">
         <v>19.46067</v>
       </c>
       <c r="I9" t="n">
-        <v>64.30947999999999</v>
+        <v>66.24541499999999</v>
       </c>
       <c r="J9" t="n">
-        <v>19.860569</v>
+        <v>20.390356</v>
       </c>
       <c r="K9" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="L9" t="n">
-        <v>24.366325</v>
+        <v>25.016306</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01554980595084088</v>
+        <v>0.0150953857009652</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05035102199223804</v>
+        <v>0.0490427912603009</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.04657000064849853</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004071024166615478</v>
+        <v>0.002472790611802368</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-21 16:25:49</t>
+          <t>2026-07-22 16:27:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -18307,40 +18829,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>68.67</v>
+        <v>68.53</v>
       </c>
       <c r="F10" t="n">
-        <v>285937729536</v>
+        <v>285354786816</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8136</v>
+        <v>3.81314</v>
       </c>
       <c r="I10" t="n">
-        <v>21.59434</v>
+        <v>21.550314</v>
       </c>
       <c r="J10" t="n">
-        <v>18.006607</v>
+        <v>17.972065</v>
       </c>
       <c r="K10" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="L10" t="n">
-        <v>5.911375</v>
+        <v>5.8993235</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04630843162953255</v>
+        <v>0.04640303516708012</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05553516819571865</v>
+        <v>0.05564190865314461</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04627999782562256</v>
+        <v>0.04657000064849853</v>
       </c>
       <c r="P10" t="n">
-        <v>0.009255170370096093</v>
+        <v>0.009071908004646079</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P307"/>
+  <dimension ref="A1:P316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17771,16 +17771,16 @@
         <v>10.602608</v>
       </c>
       <c r="M299" t="n">
-        <v>0.02534597563595078</v>
+        <v>0.0253459756359507</v>
       </c>
       <c r="N299" t="n">
-        <v>0.02957792506674032</v>
+        <v>0.0295779250667403</v>
       </c>
       <c r="O299" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.0465700006484985</v>
       </c>
       <c r="P299" t="n">
-        <v>-0.01699207558175822</v>
+        <v>-0.0169920755817582</v>
       </c>
     </row>
     <row r="300">
@@ -17829,13 +17829,13 @@
         <v>24.046288</v>
       </c>
       <c r="M300" t="n">
-        <v>0.005413430376767512</v>
+        <v>0.0054134303767675</v>
       </c>
       <c r="N300" t="n">
-        <v>0.02442755236905473</v>
+        <v>0.0244275523690547</v>
       </c>
       <c r="O300" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.0465700006484985</v>
       </c>
       <c r="P300" t="n">
         <v>-0.0221424482794438</v>
@@ -17887,16 +17887,16 @@
         <v>3.545993</v>
       </c>
       <c r="M301" t="n">
-        <v>0.03418419440473759</v>
+        <v>0.0341841944047375</v>
       </c>
       <c r="N301" t="n">
-        <v>0.04050136818460282</v>
+        <v>0.0405013681846028</v>
       </c>
       <c r="O301" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.0465700006484985</v>
       </c>
       <c r="P301" t="n">
-        <v>-0.006068632463895711</v>
+        <v>-0.0060686324638957</v>
       </c>
     </row>
     <row r="302">
@@ -17945,16 +17945,16 @@
         <v>25.016306</v>
       </c>
       <c r="M302" t="n">
-        <v>0.0150953857009652</v>
+        <v>0.0150953857009651</v>
       </c>
       <c r="N302" t="n">
         <v>0.0490427912603009</v>
       </c>
       <c r="O302" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.0465700006484985</v>
       </c>
       <c r="P302" t="n">
-        <v>0.002472790611802368</v>
+        <v>0.0024727906118023</v>
       </c>
     </row>
     <row r="303">
@@ -18003,16 +18003,16 @@
         <v>9.875031999999999</v>
       </c>
       <c r="M303" t="n">
-        <v>0.03837267117077593</v>
+        <v>0.0383726711707759</v>
       </c>
       <c r="N303" t="n">
-        <v>0.04291837033137375</v>
+        <v>0.0429183703313737</v>
       </c>
       <c r="O303" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.0465700006484985</v>
       </c>
       <c r="P303" t="n">
-        <v>-0.003651630317124781</v>
+        <v>-0.0036516303171247</v>
       </c>
     </row>
     <row r="304">
@@ -18061,16 +18061,16 @@
         <v>7.4060326</v>
       </c>
       <c r="M304" t="n">
-        <v>0.04383181593507342</v>
+        <v>0.0438318159350734</v>
       </c>
       <c r="N304" t="n">
-        <v>0.05901427045298723</v>
+        <v>0.0590142704529872</v>
       </c>
       <c r="O304" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.0465700006484985</v>
       </c>
       <c r="P304" t="n">
-        <v>0.0124442698044887</v>
+        <v>0.0124442698044886</v>
       </c>
     </row>
     <row r="305">
@@ -18119,16 +18119,16 @@
         <v>9.110466000000001</v>
       </c>
       <c r="M305" t="n">
-        <v>0.04301378285597172</v>
+        <v>0.0430137828559717</v>
       </c>
       <c r="N305" t="n">
         <v>0.0496459753035815</v>
       </c>
       <c r="O305" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.0465700006484985</v>
       </c>
       <c r="P305" t="n">
-        <v>0.003075974655082969</v>
+        <v>0.0030759746550829</v>
       </c>
     </row>
     <row r="306">
@@ -18177,16 +18177,16 @@
         <v>5.8993235</v>
       </c>
       <c r="M306" t="n">
-        <v>0.04640303516708012</v>
+        <v>0.0464030351670801</v>
       </c>
       <c r="N306" t="n">
-        <v>0.05564190865314461</v>
+        <v>0.0556419086531446</v>
       </c>
       <c r="O306" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.0465700006484985</v>
       </c>
       <c r="P306" t="n">
-        <v>0.009071908004646079</v>
+        <v>0.009071908004646001</v>
       </c>
     </row>
     <row r="307">
@@ -18235,16 +18235,536 @@
         <v>20.26228</v>
       </c>
       <c r="M307" t="n">
-        <v>0.03079317174384608</v>
+        <v>0.030793171743846</v>
       </c>
       <c r="N307" t="n">
-        <v>0.06068579647269641</v>
+        <v>0.0606857964726964</v>
       </c>
       <c r="O307" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.0465700006484985</v>
       </c>
       <c r="P307" t="n">
-        <v>0.01411579582419788</v>
+        <v>0.0141157958241978</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:25:40</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>321.66</v>
+      </c>
+      <c r="F308" t="n">
+        <v>4724335050752</v>
+      </c>
+      <c r="G308" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H308" t="n">
+        <v>9.641249999999999</v>
+      </c>
+      <c r="I308" t="n">
+        <v>38.98909</v>
+      </c>
+      <c r="J308" t="n">
+        <v>33.362896</v>
+      </c>
+      <c r="K308" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="L308" t="n">
+        <v>10.464988</v>
+      </c>
+      <c r="M308" t="n">
+        <v>0.02564819996269353</v>
+      </c>
+      <c r="N308" t="n">
+        <v>0.02997341913822048</v>
+      </c>
+      <c r="O308" t="n">
+        <v>0.04703000068664551</v>
+      </c>
+      <c r="P308" t="n">
+        <v>-0.01705658154842503</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:25:40</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>539.6900000000001</v>
+      </c>
+      <c r="F309" t="n">
+        <v>880018849792</v>
+      </c>
+      <c r="G309" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H309" t="n">
+        <v>13.49207</v>
+      </c>
+      <c r="I309" t="n">
+        <v>181.10402</v>
+      </c>
+      <c r="J309" t="n">
+        <v>40.000534</v>
+      </c>
+      <c r="K309" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L309" t="inlineStr"/>
+      <c r="M309" t="n">
+        <v>0.005521688376660675</v>
+      </c>
+      <c r="N309" t="n">
+        <v>0.02499966647519872</v>
+      </c>
+      <c r="O309" t="n">
+        <v>0.04703000068664551</v>
+      </c>
+      <c r="P309" t="n">
+        <v>-0.02203033421144678</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:25:40</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>233.66</v>
+      </c>
+      <c r="F310" t="n">
+        <v>2513506402304</v>
+      </c>
+      <c r="G310" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="H310" t="n">
+        <v>9.91676</v>
+      </c>
+      <c r="I310" t="n">
+        <v>27.983232</v>
+      </c>
+      <c r="J310" t="n">
+        <v>23.56213</v>
+      </c>
+      <c r="K310" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L310" t="n">
+        <v>3.383936</v>
+      </c>
+      <c r="M310" t="n">
+        <v>0.03573568432765557</v>
+      </c>
+      <c r="N310" t="n">
+        <v>0.04244098262432595</v>
+      </c>
+      <c r="O310" t="n">
+        <v>0.04703000068664551</v>
+      </c>
+      <c r="P310" t="n">
+        <v>-0.004589018062319559</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:25:40</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>392.47</v>
+      </c>
+      <c r="F311" t="n">
+        <v>1867207540736</v>
+      </c>
+      <c r="G311" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="H311" t="n">
+        <v>19.46067</v>
+      </c>
+      <c r="I311" t="n">
+        <v>65.52087400000001</v>
+      </c>
+      <c r="J311" t="n">
+        <v>20.167343</v>
+      </c>
+      <c r="K311" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L311" t="n">
+        <v>24.742697</v>
+      </c>
+      <c r="M311" t="n">
+        <v>0.01526231304303514</v>
+      </c>
+      <c r="N311" t="n">
+        <v>0.0495851147858435</v>
+      </c>
+      <c r="O311" t="n">
+        <v>0.04703000068664551</v>
+      </c>
+      <c r="P311" t="n">
+        <v>0.002555114099197994</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:25:40</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>318.34</v>
+      </c>
+      <c r="F312" t="n">
+        <v>3884566970368</v>
+      </c>
+      <c r="G312" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H312" t="n">
+        <v>14.75247</v>
+      </c>
+      <c r="I312" t="n">
+        <v>15.972905</v>
+      </c>
+      <c r="J312" t="n">
+        <v>21.578758</v>
+      </c>
+      <c r="K312" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L312" t="n">
+        <v>8.712408999999999</v>
+      </c>
+      <c r="M312" t="n">
+        <v>0.062606018722121</v>
+      </c>
+      <c r="N312" t="n">
+        <v>0.04634186718602752</v>
+      </c>
+      <c r="O312" t="n">
+        <v>0.04703000068664551</v>
+      </c>
+      <c r="P312" t="n">
+        <v>-0.0006881335006179851</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:25:40</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>606.1</v>
+      </c>
+      <c r="F313" t="n">
+        <v>1538538340352</v>
+      </c>
+      <c r="G313" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="H313" t="n">
+        <v>37.01198</v>
+      </c>
+      <c r="I313" t="n">
+        <v>22.06407</v>
+      </c>
+      <c r="J313" t="n">
+        <v>16.375778</v>
+      </c>
+      <c r="K313" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L313" t="n">
+        <v>7.157224</v>
+      </c>
+      <c r="M313" t="n">
+        <v>0.04532255403398779</v>
+      </c>
+      <c r="N313" t="n">
+        <v>0.061065797723148</v>
+      </c>
+      <c r="O313" t="n">
+        <v>0.04703000068664551</v>
+      </c>
+      <c r="P313" t="n">
+        <v>0.01403579703650249</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:25:40</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>381.58</v>
+      </c>
+      <c r="F314" t="n">
+        <v>2834542100480</v>
+      </c>
+      <c r="G314" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="H314" t="n">
+        <v>19.37881</v>
+      </c>
+      <c r="I314" t="n">
+        <v>22.740166</v>
+      </c>
+      <c r="J314" t="n">
+        <v>19.690578</v>
+      </c>
+      <c r="K314" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L314" t="n">
+        <v>8.906008999999999</v>
+      </c>
+      <c r="M314" t="n">
+        <v>0.04397505110330731</v>
+      </c>
+      <c r="N314" t="n">
+        <v>0.05078570679805022</v>
+      </c>
+      <c r="O314" t="n">
+        <v>0.04703000068664551</v>
+      </c>
+      <c r="P314" t="n">
+        <v>0.003755706111404709</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:25:40</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>68.89</v>
+      </c>
+      <c r="F315" t="n">
+        <v>286853791744</v>
+      </c>
+      <c r="G315" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H315" t="n">
+        <v>3.81314</v>
+      </c>
+      <c r="I315" t="n">
+        <v>21.66352</v>
+      </c>
+      <c r="J315" t="n">
+        <v>18.066475</v>
+      </c>
+      <c r="K315" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L315" t="n">
+        <v>5.930313</v>
+      </c>
+      <c r="M315" t="n">
+        <v>0.04616054579764842</v>
+      </c>
+      <c r="N315" t="n">
+        <v>0.05535113949775004</v>
+      </c>
+      <c r="O315" t="n">
+        <v>0.04703000068664551</v>
+      </c>
+      <c r="P315" t="n">
+        <v>0.00832113881110453</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:25:40</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>208.76</v>
+      </c>
+      <c r="F316" t="n">
+        <v>5056375554048</v>
+      </c>
+      <c r="G316" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H316" t="n">
+        <v>12.86903</v>
+      </c>
+      <c r="I316" t="n">
+        <v>31.96937</v>
+      </c>
+      <c r="J316" t="n">
+        <v>16.22189</v>
+      </c>
+      <c r="K316" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L316" t="n">
+        <v>19.946962</v>
+      </c>
+      <c r="M316" t="n">
+        <v>0.03127993868557195</v>
+      </c>
+      <c r="N316" t="n">
+        <v>0.06164509484575589</v>
+      </c>
+      <c r="O316" t="n">
+        <v>0.04703000068664551</v>
+      </c>
+      <c r="P316" t="n">
+        <v>0.01461509415911039</v>
       </c>
     </row>
   </sheetData>
@@ -18346,12 +18866,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-22 16:27:56</t>
+          <t>2026-07-23 16:25:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -18365,51 +18885,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>341.91</v>
+        <v>318.34</v>
       </c>
       <c r="F2" t="n">
-        <v>4172181667840</v>
+        <v>3884566970368</v>
       </c>
       <c r="G2" t="n">
-        <v>13.12</v>
+        <v>19.93</v>
       </c>
       <c r="H2" t="n">
-        <v>14.67422</v>
+        <v>14.75247</v>
       </c>
       <c r="I2" t="n">
-        <v>26.060213</v>
+        <v>15.972905</v>
       </c>
       <c r="J2" t="n">
-        <v>23.300047</v>
+        <v>21.578758</v>
       </c>
       <c r="K2" t="n">
         <v>1.36</v>
       </c>
       <c r="L2" t="n">
-        <v>9.875031999999999</v>
+        <v>8.712408999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03837267117077593</v>
+        <v>0.062606018722121</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04291837033137375</v>
+        <v>0.04634186718602752</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.04703000068664551</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003651630317124781</v>
+        <v>-0.0006881335006179851</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-22 16:27:56</t>
+          <t>2026-07-23 16:25:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -18423,51 +18943,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>390.34</v>
+        <v>381.58</v>
       </c>
       <c r="F3" t="n">
-        <v>2899615154176</v>
+        <v>2834542100480</v>
       </c>
       <c r="G3" t="n">
-        <v>16.79</v>
+        <v>16.78</v>
       </c>
       <c r="H3" t="n">
         <v>19.37881</v>
       </c>
       <c r="I3" t="n">
-        <v>23.248362</v>
+        <v>22.740166</v>
       </c>
       <c r="J3" t="n">
-        <v>20.142618</v>
+        <v>19.690578</v>
       </c>
       <c r="K3" t="n">
         <v>1.23</v>
       </c>
       <c r="L3" t="n">
-        <v>9.110466000000001</v>
+        <v>8.906008999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04301378285597172</v>
+        <v>0.04397505110330731</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0496459753035815</v>
+        <v>0.05078570679805022</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.04703000068664551</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003075974655082969</v>
+        <v>0.003755706111404709</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-22 16:27:56</t>
+          <t>2026-07-23 16:25:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -18481,51 +19001,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>627.17</v>
+        <v>606.1</v>
       </c>
       <c r="F4" t="n">
-        <v>1592022925312</v>
+        <v>1538538340352</v>
       </c>
       <c r="G4" t="n">
-        <v>27.49</v>
+        <v>27.47</v>
       </c>
       <c r="H4" t="n">
         <v>37.01198</v>
       </c>
       <c r="I4" t="n">
-        <v>22.814478</v>
+        <v>22.06407</v>
       </c>
       <c r="J4" t="n">
-        <v>16.945055</v>
+        <v>16.375778</v>
       </c>
       <c r="K4" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>7.4060326</v>
+        <v>7.157224</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04383181593507342</v>
+        <v>0.04532255403398779</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05901427045298723</v>
+        <v>0.061065797723148</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.04703000068664551</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0124442698044887</v>
+        <v>0.01403579703650249</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-22 16:27:56</t>
+          <t>2026-07-23 16:25:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -18539,51 +19059,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>244.85</v>
+        <v>233.66</v>
       </c>
       <c r="F5" t="n">
-        <v>2633878470656</v>
+        <v>2513506402304</v>
       </c>
       <c r="G5" t="n">
-        <v>8.369999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="H5" t="n">
         <v>9.91676</v>
       </c>
       <c r="I5" t="n">
-        <v>29.253286</v>
+        <v>27.983232</v>
       </c>
       <c r="J5" t="n">
-        <v>24.690523</v>
+        <v>23.56213</v>
       </c>
       <c r="K5" t="n">
         <v>1.3</v>
       </c>
       <c r="L5" t="n">
-        <v>3.545993</v>
+        <v>3.383936</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03418419440473759</v>
+        <v>0.03573568432765557</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04050136818460282</v>
+        <v>0.04244098262432595</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.04703000068664551</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.006068632463895711</v>
+        <v>-0.004589018062319559</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-22 16:27:56</t>
+          <t>2026-07-23 16:25:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -18597,51 +19117,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>325.89</v>
+        <v>321.66</v>
       </c>
       <c r="F6" t="n">
-        <v>4786462654464</v>
+        <v>4724335050752</v>
       </c>
       <c r="G6" t="n">
-        <v>8.26</v>
+        <v>8.25</v>
       </c>
       <c r="H6" t="n">
-        <v>9.639150000000001</v>
+        <v>9.641249999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>39.453995</v>
+        <v>38.98909</v>
       </c>
       <c r="J6" t="n">
-        <v>33.809002</v>
+        <v>33.362896</v>
       </c>
       <c r="K6" t="n">
         <v>2.64</v>
       </c>
       <c r="L6" t="n">
-        <v>10.602608</v>
+        <v>10.464988</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02534597563595078</v>
+        <v>0.02564819996269353</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02957792506674032</v>
+        <v>0.02997341913822048</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.04703000068664551</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01699207558175822</v>
+        <v>-0.01705658154842503</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-22 16:27:56</t>
+          <t>2026-07-23 16:25:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -18655,10 +19175,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>212.06</v>
+        <v>208.76</v>
       </c>
       <c r="F7" t="n">
-        <v>5136305356800</v>
+        <v>5056375554048</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
@@ -18667,39 +19187,39 @@
         <v>12.86903</v>
       </c>
       <c r="I7" t="n">
-        <v>32.47473</v>
+        <v>31.96937</v>
       </c>
       <c r="J7" t="n">
-        <v>16.478321</v>
+        <v>16.22189</v>
       </c>
       <c r="K7" t="n">
         <v>0.57</v>
       </c>
       <c r="L7" t="n">
-        <v>20.26228</v>
+        <v>19.946962</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03079317174384608</v>
+        <v>0.03127993868557195</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06068579647269641</v>
+        <v>0.06164509484575589</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.04703000068664551</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01411579582419788</v>
+        <v>0.01461509415911039</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-22 16:27:56</t>
+          <t>2026-07-23 16:25:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -18713,51 +19233,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>552.33</v>
+        <v>539.6900000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>900629659648</v>
+        <v>880018849792</v>
       </c>
       <c r="G8" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="H8" t="n">
         <v>13.49207</v>
       </c>
       <c r="I8" t="n">
-        <v>184.72575</v>
+        <v>181.10402</v>
       </c>
       <c r="J8" t="n">
-        <v>40.93738</v>
+        <v>40.000534</v>
       </c>
       <c r="K8" t="n">
         <v>1.28</v>
       </c>
-      <c r="L8" t="n">
-        <v>24.046288</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0.005413430376767512</v>
+        <v>0.005521688376660675</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02442755236905473</v>
+        <v>0.02499966647519872</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.04703000068664551</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0221424482794438</v>
+        <v>-0.02203033421144678</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-22 16:27:56</t>
+          <t>2026-07-23 16:25:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -18771,10 +19289,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>396.81</v>
+        <v>392.47</v>
       </c>
       <c r="F9" t="n">
-        <v>1887855443968</v>
+        <v>1867207540736</v>
       </c>
       <c r="G9" t="n">
         <v>5.99</v>
@@ -18783,39 +19301,39 @@
         <v>19.46067</v>
       </c>
       <c r="I9" t="n">
-        <v>66.24541499999999</v>
+        <v>65.52087400000001</v>
       </c>
       <c r="J9" t="n">
-        <v>20.390356</v>
+        <v>20.167343</v>
       </c>
       <c r="K9" t="n">
         <v>0.43</v>
       </c>
       <c r="L9" t="n">
-        <v>25.016306</v>
+        <v>24.742697</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0150953857009652</v>
+        <v>0.01526231304303514</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0490427912603009</v>
+        <v>0.0495851147858435</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.04703000068664551</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002472790611802368</v>
+        <v>0.002555114099197994</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-22 16:27:56</t>
+          <t>2026-07-23 16:25:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -18829,10 +19347,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>68.53</v>
+        <v>68.89</v>
       </c>
       <c r="F10" t="n">
-        <v>285354786816</v>
+        <v>286853791744</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -18841,28 +19359,28 @@
         <v>3.81314</v>
       </c>
       <c r="I10" t="n">
-        <v>21.550314</v>
+        <v>21.66352</v>
       </c>
       <c r="J10" t="n">
-        <v>17.972065</v>
+        <v>18.066475</v>
       </c>
       <c r="K10" t="n">
         <v>1.54</v>
       </c>
       <c r="L10" t="n">
-        <v>5.8993235</v>
+        <v>5.930313</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04640303516708012</v>
+        <v>0.04616054579764842</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05564190865314461</v>
+        <v>0.05535113949775004</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04657000064849853</v>
+        <v>0.04703000068664551</v>
       </c>
       <c r="P10" t="n">
-        <v>0.009071908004646079</v>
+        <v>0.00832113881110453</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P316"/>
+  <dimension ref="A1:P325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18293,16 +18293,16 @@
         <v>10.464988</v>
       </c>
       <c r="M308" t="n">
-        <v>0.02564819996269353</v>
+        <v>0.0256481999626935</v>
       </c>
       <c r="N308" t="n">
-        <v>0.02997341913822048</v>
+        <v>0.0299734191382204</v>
       </c>
       <c r="O308" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.0470300006866455</v>
       </c>
       <c r="P308" t="n">
-        <v>-0.01705658154842503</v>
+        <v>-0.017056581548425</v>
       </c>
     </row>
     <row r="309">
@@ -18349,16 +18349,16 @@
       </c>
       <c r="L309" t="inlineStr"/>
       <c r="M309" t="n">
-        <v>0.005521688376660675</v>
+        <v>0.0055216883766606</v>
       </c>
       <c r="N309" t="n">
-        <v>0.02499966647519872</v>
+        <v>0.0249996664751987</v>
       </c>
       <c r="O309" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.0470300006866455</v>
       </c>
       <c r="P309" t="n">
-        <v>-0.02203033421144678</v>
+        <v>-0.0220303342114467</v>
       </c>
     </row>
     <row r="310">
@@ -18407,16 +18407,16 @@
         <v>3.383936</v>
       </c>
       <c r="M310" t="n">
-        <v>0.03573568432765557</v>
+        <v>0.0357356843276555</v>
       </c>
       <c r="N310" t="n">
-        <v>0.04244098262432595</v>
+        <v>0.0424409826243259</v>
       </c>
       <c r="O310" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.0470300006866455</v>
       </c>
       <c r="P310" t="n">
-        <v>-0.004589018062319559</v>
+        <v>-0.0045890180623195</v>
       </c>
     </row>
     <row r="311">
@@ -18465,16 +18465,16 @@
         <v>24.742697</v>
       </c>
       <c r="M311" t="n">
-        <v>0.01526231304303514</v>
+        <v>0.0152623130430351</v>
       </c>
       <c r="N311" t="n">
         <v>0.0495851147858435</v>
       </c>
       <c r="O311" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.0470300006866455</v>
       </c>
       <c r="P311" t="n">
-        <v>0.002555114099197994</v>
+        <v>0.0025551140991979</v>
       </c>
     </row>
     <row r="312">
@@ -18526,13 +18526,13 @@
         <v>0.062606018722121</v>
       </c>
       <c r="N312" t="n">
-        <v>0.04634186718602752</v>
+        <v>0.0463418671860275</v>
       </c>
       <c r="O312" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.0470300006866455</v>
       </c>
       <c r="P312" t="n">
-        <v>-0.0006881335006179851</v>
+        <v>-0.0006881335006179</v>
       </c>
     </row>
     <row r="313">
@@ -18581,16 +18581,16 @@
         <v>7.157224</v>
       </c>
       <c r="M313" t="n">
-        <v>0.04532255403398779</v>
+        <v>0.0453225540339877</v>
       </c>
       <c r="N313" t="n">
         <v>0.061065797723148</v>
       </c>
       <c r="O313" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.0470300006866455</v>
       </c>
       <c r="P313" t="n">
-        <v>0.01403579703650249</v>
+        <v>0.0140357970365024</v>
       </c>
     </row>
     <row r="314">
@@ -18639,16 +18639,16 @@
         <v>8.906008999999999</v>
       </c>
       <c r="M314" t="n">
-        <v>0.04397505110330731</v>
+        <v>0.0439750511033073</v>
       </c>
       <c r="N314" t="n">
-        <v>0.05078570679805022</v>
+        <v>0.0507857067980502</v>
       </c>
       <c r="O314" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.0470300006866455</v>
       </c>
       <c r="P314" t="n">
-        <v>0.003755706111404709</v>
+        <v>0.0037557061114047</v>
       </c>
     </row>
     <row r="315">
@@ -18697,16 +18697,16 @@
         <v>5.930313</v>
       </c>
       <c r="M315" t="n">
-        <v>0.04616054579764842</v>
+        <v>0.0461605457976484</v>
       </c>
       <c r="N315" t="n">
-        <v>0.05535113949775004</v>
+        <v>0.05535113949775</v>
       </c>
       <c r="O315" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.0470300006866455</v>
       </c>
       <c r="P315" t="n">
-        <v>0.00832113881110453</v>
+        <v>0.0083211388111045</v>
       </c>
     </row>
     <row r="316">
@@ -18755,16 +18755,538 @@
         <v>19.946962</v>
       </c>
       <c r="M316" t="n">
-        <v>0.03127993868557195</v>
+        <v>0.0312799386855719</v>
       </c>
       <c r="N316" t="n">
-        <v>0.06164509484575589</v>
+        <v>0.0616450948457558</v>
       </c>
       <c r="O316" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.0470300006866455</v>
       </c>
       <c r="P316" t="n">
-        <v>0.01461509415911039</v>
+        <v>0.0146150941591103</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:30:12</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>333.02</v>
+      </c>
+      <c r="F317" t="n">
+        <v>4891182891008</v>
+      </c>
+      <c r="G317" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="H317" t="n">
+        <v>9.641249999999999</v>
+      </c>
+      <c r="I317" t="n">
+        <v>40.268436</v>
+      </c>
+      <c r="J317" t="n">
+        <v>34.541164</v>
+      </c>
+      <c r="K317" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="L317" t="n">
+        <v>10.834576</v>
+      </c>
+      <c r="M317" t="n">
+        <v>0.02483334334274218</v>
+      </c>
+      <c r="N317" t="n">
+        <v>0.02895096390607171</v>
+      </c>
+      <c r="O317" t="n">
+        <v>0.04678999900817871</v>
+      </c>
+      <c r="P317" t="n">
+        <v>-0.01783903510210701</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:30:12</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>521.95</v>
+      </c>
+      <c r="F318" t="n">
+        <v>851091980288</v>
+      </c>
+      <c r="G318" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H318" t="n">
+        <v>13.51362</v>
+      </c>
+      <c r="I318" t="n">
+        <v>172.83113</v>
+      </c>
+      <c r="J318" t="n">
+        <v>38.623997</v>
+      </c>
+      <c r="K318" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L318" t="n">
+        <v>22.72366</v>
+      </c>
+      <c r="M318" t="n">
+        <v>0.005785994827090717</v>
+      </c>
+      <c r="N318" t="n">
+        <v>0.02589064086598333</v>
+      </c>
+      <c r="O318" t="n">
+        <v>0.04678999900817871</v>
+      </c>
+      <c r="P318" t="n">
+        <v>-0.02089935814219538</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:30:12</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>232.11</v>
+      </c>
+      <c r="F319" t="n">
+        <v>2496832733184</v>
+      </c>
+      <c r="G319" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="H319" t="n">
+        <v>9.907080000000001</v>
+      </c>
+      <c r="I319" t="n">
+        <v>27.731184</v>
+      </c>
+      <c r="J319" t="n">
+        <v>23.4287</v>
+      </c>
+      <c r="K319" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L319" t="n">
+        <v>3.3614883</v>
+      </c>
+      <c r="M319" t="n">
+        <v>0.03606048856145792</v>
+      </c>
+      <c r="N319" t="n">
+        <v>0.04268269355047176</v>
+      </c>
+      <c r="O319" t="n">
+        <v>0.04678999900817871</v>
+      </c>
+      <c r="P319" t="n">
+        <v>-0.004107305457706954</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:30:12</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>381.92</v>
+      </c>
+      <c r="F320" t="n">
+        <v>1817015091200</v>
+      </c>
+      <c r="G320" t="n">
+        <v>6</v>
+      </c>
+      <c r="H320" t="n">
+        <v>19.46067</v>
+      </c>
+      <c r="I320" t="n">
+        <v>63.653336</v>
+      </c>
+      <c r="J320" t="n">
+        <v>19.625223</v>
+      </c>
+      <c r="K320" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L320" t="n">
+        <v>24.077587</v>
+      </c>
+      <c r="M320" t="n">
+        <v>0.01571009635525765</v>
+      </c>
+      <c r="N320" t="n">
+        <v>0.05095483347297863</v>
+      </c>
+      <c r="O320" t="n">
+        <v>0.04678999900817871</v>
+      </c>
+      <c r="P320" t="n">
+        <v>0.00416483446479992</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:30:12</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>319.09</v>
+      </c>
+      <c r="F321" t="n">
+        <v>3902449909760</v>
+      </c>
+      <c r="G321" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H321" t="n">
+        <v>14.77894</v>
+      </c>
+      <c r="I321" t="n">
+        <v>16.010536</v>
+      </c>
+      <c r="J321" t="n">
+        <v>21.590858</v>
+      </c>
+      <c r="K321" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L321" t="n">
+        <v>8.752518</v>
+      </c>
+      <c r="M321" t="n">
+        <v>0.06245886740418064</v>
+      </c>
+      <c r="N321" t="n">
+        <v>0.0463158983358927</v>
+      </c>
+      <c r="O321" t="n">
+        <v>0.04678999900817871</v>
+      </c>
+      <c r="P321" t="n">
+        <v>-0.0004741006722860167</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:30:12</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>595.1900000000001</v>
+      </c>
+      <c r="F322" t="n">
+        <v>1510844137472</v>
+      </c>
+      <c r="G322" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="H322" t="n">
+        <v>37.01198</v>
+      </c>
+      <c r="I322" t="n">
+        <v>21.627542</v>
+      </c>
+      <c r="J322" t="n">
+        <v>16.08101</v>
+      </c>
+      <c r="K322" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L322" t="n">
+        <v>7.028392</v>
+      </c>
+      <c r="M322" t="n">
+        <v>0.04623733597674692</v>
+      </c>
+      <c r="N322" t="n">
+        <v>0.06218515096019758</v>
+      </c>
+      <c r="O322" t="n">
+        <v>0.04678999900817871</v>
+      </c>
+      <c r="P322" t="n">
+        <v>0.01539515195201887</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:30:12</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>381.7</v>
+      </c>
+      <c r="F323" t="n">
+        <v>2835433652224</v>
+      </c>
+      <c r="G323" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="H323" t="n">
+        <v>19.37881</v>
+      </c>
+      <c r="I323" t="n">
+        <v>22.73377</v>
+      </c>
+      <c r="J323" t="n">
+        <v>19.696772</v>
+      </c>
+      <c r="K323" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L323" t="n">
+        <v>8.908810000000001</v>
+      </c>
+      <c r="M323" t="n">
+        <v>0.04398742467906733</v>
+      </c>
+      <c r="N323" t="n">
+        <v>0.05076974063400577</v>
+      </c>
+      <c r="O323" t="n">
+        <v>0.04678999900817871</v>
+      </c>
+      <c r="P323" t="n">
+        <v>0.003979741625827059</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:30:12</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>70.09</v>
+      </c>
+      <c r="F324" t="n">
+        <v>291850518528</v>
+      </c>
+      <c r="G324" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H324" t="n">
+        <v>3.81756</v>
+      </c>
+      <c r="I324" t="n">
+        <v>22.040878</v>
+      </c>
+      <c r="J324" t="n">
+        <v>18.359894</v>
+      </c>
+      <c r="K324" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L324" t="n">
+        <v>6.0336137</v>
+      </c>
+      <c r="M324" t="n">
+        <v>0.04537023826508774</v>
+      </c>
+      <c r="N324" t="n">
+        <v>0.05446654301612212</v>
+      </c>
+      <c r="O324" t="n">
+        <v>0.04678999900817871</v>
+      </c>
+      <c r="P324" t="n">
+        <v>0.00767654400794341</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-07-24 16:30:12</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>206.84</v>
+      </c>
+      <c r="F325" t="n">
+        <v>5009871732736</v>
+      </c>
+      <c r="G325" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H325" t="n">
+        <v>12.86903</v>
+      </c>
+      <c r="I325" t="n">
+        <v>31.675343</v>
+      </c>
+      <c r="J325" t="n">
+        <v>16.072695</v>
+      </c>
+      <c r="K325" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L325" t="n">
+        <v>19.76351</v>
+      </c>
+      <c r="M325" t="n">
+        <v>0.03157029588087411</v>
+      </c>
+      <c r="N325" t="n">
+        <v>0.06221731773351383</v>
+      </c>
+      <c r="O325" t="n">
+        <v>0.04678999900817871</v>
+      </c>
+      <c r="P325" t="n">
+        <v>0.01542731872533511</v>
       </c>
     </row>
   </sheetData>
@@ -18866,12 +19388,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:25:40</t>
+          <t>2026-07-24 16:30:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -18885,51 +19407,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>318.34</v>
+        <v>319.09</v>
       </c>
       <c r="F2" t="n">
-        <v>3884566970368</v>
+        <v>3902449909760</v>
       </c>
       <c r="G2" t="n">
         <v>19.93</v>
       </c>
       <c r="H2" t="n">
-        <v>14.75247</v>
+        <v>14.77894</v>
       </c>
       <c r="I2" t="n">
-        <v>15.972905</v>
+        <v>16.010536</v>
       </c>
       <c r="J2" t="n">
-        <v>21.578758</v>
+        <v>21.590858</v>
       </c>
       <c r="K2" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="L2" t="n">
-        <v>8.712408999999999</v>
+        <v>8.752518</v>
       </c>
       <c r="M2" t="n">
-        <v>0.062606018722121</v>
+        <v>0.06245886740418064</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04634186718602752</v>
+        <v>0.0463158983358927</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.04678999900817871</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0006881335006179851</v>
+        <v>-0.0004741006722860167</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-23 16:25:40</t>
+          <t>2026-07-24 16:30:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -18943,51 +19465,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>381.58</v>
+        <v>381.7</v>
       </c>
       <c r="F3" t="n">
-        <v>2834542100480</v>
+        <v>2835433652224</v>
       </c>
       <c r="G3" t="n">
-        <v>16.78</v>
+        <v>16.79</v>
       </c>
       <c r="H3" t="n">
         <v>19.37881</v>
       </c>
       <c r="I3" t="n">
-        <v>22.740166</v>
+        <v>22.73377</v>
       </c>
       <c r="J3" t="n">
-        <v>19.690578</v>
+        <v>19.696772</v>
       </c>
       <c r="K3" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="L3" t="n">
-        <v>8.906008999999999</v>
+        <v>8.908810000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04397505110330731</v>
+        <v>0.04398742467906733</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05078570679805022</v>
+        <v>0.05076974063400577</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.04678999900817871</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003755706111404709</v>
+        <v>0.003979741625827059</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-23 16:25:40</t>
+          <t>2026-07-24 16:30:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -19001,51 +19523,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>606.1</v>
+        <v>595.1900000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1538538340352</v>
+        <v>1510844137472</v>
       </c>
       <c r="G4" t="n">
-        <v>27.47</v>
+        <v>27.52</v>
       </c>
       <c r="H4" t="n">
         <v>37.01198</v>
       </c>
       <c r="I4" t="n">
-        <v>22.06407</v>
+        <v>21.627542</v>
       </c>
       <c r="J4" t="n">
-        <v>16.375778</v>
+        <v>16.08101</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="L4" t="n">
-        <v>7.157224</v>
+        <v>7.028392</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04532255403398779</v>
+        <v>0.04623733597674692</v>
       </c>
       <c r="N4" t="n">
-        <v>0.061065797723148</v>
+        <v>0.06218515096019758</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.04678999900817871</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01403579703650249</v>
+        <v>0.01539515195201887</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-23 16:25:40</t>
+          <t>2026-07-24 16:30:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -19059,51 +19581,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>233.66</v>
+        <v>232.11</v>
       </c>
       <c r="F5" t="n">
-        <v>2513506402304</v>
+        <v>2496832733184</v>
       </c>
       <c r="G5" t="n">
-        <v>8.35</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>9.91676</v>
+        <v>9.907080000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>27.983232</v>
+        <v>27.731184</v>
       </c>
       <c r="J5" t="n">
-        <v>23.56213</v>
+        <v>23.4287</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="L5" t="n">
-        <v>3.383936</v>
+        <v>3.3614883</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03573568432765557</v>
+        <v>0.03606048856145792</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04244098262432595</v>
+        <v>0.04268269355047176</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.04678999900817871</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.004589018062319559</v>
+        <v>-0.004107305457706954</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-23 16:25:40</t>
+          <t>2026-07-24 16:30:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -19117,51 +19639,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>321.66</v>
+        <v>333.02</v>
       </c>
       <c r="F6" t="n">
-        <v>4724335050752</v>
+        <v>4891182891008</v>
       </c>
       <c r="G6" t="n">
-        <v>8.25</v>
+        <v>8.27</v>
       </c>
       <c r="H6" t="n">
         <v>9.641249999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>38.98909</v>
+        <v>40.268436</v>
       </c>
       <c r="J6" t="n">
-        <v>33.362896</v>
+        <v>34.541164</v>
       </c>
       <c r="K6" t="n">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="L6" t="n">
-        <v>10.464988</v>
+        <v>10.834576</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02564819996269353</v>
+        <v>0.02483334334274218</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02997341913822048</v>
+        <v>0.02895096390607171</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.04678999900817871</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01705658154842503</v>
+        <v>-0.01783903510210701</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-23 16:25:40</t>
+          <t>2026-07-24 16:30:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -19175,10 +19697,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208.76</v>
+        <v>206.84</v>
       </c>
       <c r="F7" t="n">
-        <v>5056375554048</v>
+        <v>5009871732736</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
@@ -19187,39 +19709,39 @@
         <v>12.86903</v>
       </c>
       <c r="I7" t="n">
-        <v>31.96937</v>
+        <v>31.675343</v>
       </c>
       <c r="J7" t="n">
-        <v>16.22189</v>
+        <v>16.072695</v>
       </c>
       <c r="K7" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="L7" t="n">
-        <v>19.946962</v>
+        <v>19.76351</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03127993868557195</v>
+        <v>0.03157029588087411</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06164509484575589</v>
+        <v>0.06221731773351383</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.04678999900817871</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01461509415911039</v>
+        <v>0.01542731872533511</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-23 16:25:40</t>
+          <t>2026-07-24 16:30:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -19233,49 +19755,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>539.6900000000001</v>
+        <v>521.95</v>
       </c>
       <c r="F8" t="n">
-        <v>880018849792</v>
+        <v>851091980288</v>
       </c>
       <c r="G8" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="H8" t="n">
-        <v>13.49207</v>
+        <v>13.51362</v>
       </c>
       <c r="I8" t="n">
-        <v>181.10402</v>
+        <v>172.83113</v>
       </c>
       <c r="J8" t="n">
-        <v>40.000534</v>
+        <v>38.623997</v>
       </c>
       <c r="K8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>1.26</v>
+      </c>
+      <c r="L8" t="n">
+        <v>22.72366</v>
+      </c>
       <c r="M8" t="n">
-        <v>0.005521688376660675</v>
+        <v>0.005785994827090717</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02499966647519872</v>
+        <v>0.02589064086598333</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.04678999900817871</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02203033421144678</v>
+        <v>-0.02089935814219538</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-23 16:25:40</t>
+          <t>2026-07-24 16:30:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -19289,51 +19813,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392.47</v>
+        <v>381.92</v>
       </c>
       <c r="F9" t="n">
-        <v>1867207540736</v>
+        <v>1817015091200</v>
       </c>
       <c r="G9" t="n">
-        <v>5.99</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>19.46067</v>
       </c>
       <c r="I9" t="n">
-        <v>65.52087400000001</v>
+        <v>63.653336</v>
       </c>
       <c r="J9" t="n">
-        <v>20.167343</v>
+        <v>19.625223</v>
       </c>
       <c r="K9" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="L9" t="n">
-        <v>24.742697</v>
+        <v>24.077587</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01526231304303514</v>
+        <v>0.01571009635525765</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0495851147858435</v>
+        <v>0.05095483347297863</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.04678999900817871</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002555114099197994</v>
+        <v>0.00416483446479992</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-23 16:25:40</t>
+          <t>2026-07-24 16:30:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -19347,40 +19871,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>68.89</v>
+        <v>70.09</v>
       </c>
       <c r="F10" t="n">
-        <v>286853791744</v>
+        <v>291850518528</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.81314</v>
+        <v>3.81756</v>
       </c>
       <c r="I10" t="n">
-        <v>21.66352</v>
+        <v>22.040878</v>
       </c>
       <c r="J10" t="n">
-        <v>18.066475</v>
+        <v>18.359894</v>
       </c>
       <c r="K10" t="n">
         <v>1.54</v>
       </c>
       <c r="L10" t="n">
-        <v>5.930313</v>
+        <v>6.0336137</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04616054579764842</v>
+        <v>0.04537023826508774</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05535113949775004</v>
+        <v>0.05446654301612212</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04703000068664551</v>
+        <v>0.04678999900817871</v>
       </c>
       <c r="P10" t="n">
-        <v>0.00832113881110453</v>
+        <v>0.00767654400794341</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P325"/>
+  <dimension ref="A1:P334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18813,16 +18813,16 @@
         <v>10.834576</v>
       </c>
       <c r="M317" t="n">
-        <v>0.02483334334274218</v>
+        <v>0.0248333433427421</v>
       </c>
       <c r="N317" t="n">
-        <v>0.02895096390607171</v>
+        <v>0.0289509639060717</v>
       </c>
       <c r="O317" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.0467899990081787</v>
       </c>
       <c r="P317" t="n">
-        <v>-0.01783903510210701</v>
+        <v>-0.017839035102107</v>
       </c>
     </row>
     <row r="318">
@@ -18871,16 +18871,16 @@
         <v>22.72366</v>
       </c>
       <c r="M318" t="n">
-        <v>0.005785994827090717</v>
+        <v>0.0057859948270907</v>
       </c>
       <c r="N318" t="n">
-        <v>0.02589064086598333</v>
+        <v>0.0258906408659833</v>
       </c>
       <c r="O318" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.0467899990081787</v>
       </c>
       <c r="P318" t="n">
-        <v>-0.02089935814219538</v>
+        <v>-0.0208993581421953</v>
       </c>
     </row>
     <row r="319">
@@ -18929,16 +18929,16 @@
         <v>3.3614883</v>
       </c>
       <c r="M319" t="n">
-        <v>0.03606048856145792</v>
+        <v>0.0360604885614579</v>
       </c>
       <c r="N319" t="n">
-        <v>0.04268269355047176</v>
+        <v>0.0426826935504717</v>
       </c>
       <c r="O319" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.0467899990081787</v>
       </c>
       <c r="P319" t="n">
-        <v>-0.004107305457706954</v>
+        <v>-0.0041073054577069</v>
       </c>
     </row>
     <row r="320">
@@ -18987,16 +18987,16 @@
         <v>24.077587</v>
       </c>
       <c r="M320" t="n">
-        <v>0.01571009635525765</v>
+        <v>0.0157100963552576</v>
       </c>
       <c r="N320" t="n">
-        <v>0.05095483347297863</v>
+        <v>0.0509548334729786</v>
       </c>
       <c r="O320" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.0467899990081787</v>
       </c>
       <c r="P320" t="n">
-        <v>0.00416483446479992</v>
+        <v>0.0041648344647999</v>
       </c>
     </row>
     <row r="321">
@@ -19045,16 +19045,16 @@
         <v>8.752518</v>
       </c>
       <c r="M321" t="n">
-        <v>0.06245886740418064</v>
+        <v>0.0624588674041806</v>
       </c>
       <c r="N321" t="n">
         <v>0.0463158983358927</v>
       </c>
       <c r="O321" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.0467899990081787</v>
       </c>
       <c r="P321" t="n">
-        <v>-0.0004741006722860167</v>
+        <v>-0.000474100672286</v>
       </c>
     </row>
     <row r="322">
@@ -19103,16 +19103,16 @@
         <v>7.028392</v>
       </c>
       <c r="M322" t="n">
-        <v>0.04623733597674692</v>
+        <v>0.0462373359767469</v>
       </c>
       <c r="N322" t="n">
-        <v>0.06218515096019758</v>
+        <v>0.0621851509601975</v>
       </c>
       <c r="O322" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.0467899990081787</v>
       </c>
       <c r="P322" t="n">
-        <v>0.01539515195201887</v>
+        <v>0.0153951519520188</v>
       </c>
     </row>
     <row r="323">
@@ -19161,16 +19161,16 @@
         <v>8.908810000000001</v>
       </c>
       <c r="M323" t="n">
-        <v>0.04398742467906733</v>
+        <v>0.0439874246790673</v>
       </c>
       <c r="N323" t="n">
-        <v>0.05076974063400577</v>
+        <v>0.0507697406340057</v>
       </c>
       <c r="O323" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.0467899990081787</v>
       </c>
       <c r="P323" t="n">
-        <v>0.003979741625827059</v>
+        <v>0.003979741625827</v>
       </c>
     </row>
     <row r="324">
@@ -19219,16 +19219,16 @@
         <v>6.0336137</v>
       </c>
       <c r="M324" t="n">
-        <v>0.04537023826508774</v>
+        <v>0.0453702382650877</v>
       </c>
       <c r="N324" t="n">
-        <v>0.05446654301612212</v>
+        <v>0.0544665430161221</v>
       </c>
       <c r="O324" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.0467899990081787</v>
       </c>
       <c r="P324" t="n">
-        <v>0.00767654400794341</v>
+        <v>0.0076765440079434</v>
       </c>
     </row>
     <row r="325">
@@ -19277,16 +19277,536 @@
         <v>19.76351</v>
       </c>
       <c r="M325" t="n">
-        <v>0.03157029588087411</v>
+        <v>0.0315702958808741</v>
       </c>
       <c r="N325" t="n">
-        <v>0.06221731773351383</v>
+        <v>0.0622173177335138</v>
       </c>
       <c r="O325" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.0467899990081787</v>
       </c>
       <c r="P325" t="n">
-        <v>0.01542731872533511</v>
+        <v>0.0154273187253351</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-07-27 16:31:23</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>336.91</v>
+      </c>
+      <c r="F326" t="n">
+        <v>4948317175808</v>
+      </c>
+      <c r="G326" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H326" t="n">
+        <v>9.646129999999999</v>
+      </c>
+      <c r="I326" t="n">
+        <v>40.788136</v>
+      </c>
+      <c r="J326" t="n">
+        <v>34.926964</v>
+      </c>
+      <c r="K326" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="L326" t="n">
+        <v>10.961136</v>
+      </c>
+      <c r="M326" t="n">
+        <v>0.02451693330563058</v>
+      </c>
+      <c r="N326" t="n">
+        <v>0.02863117746579205</v>
+      </c>
+      <c r="O326" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P326" t="n">
+        <v>-0.01777882047427143</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2026-07-27 16:31:23</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>494.95</v>
+      </c>
+      <c r="F327" t="n">
+        <v>807065747456</v>
+      </c>
+      <c r="G327" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H327" t="n">
+        <v>13.72374</v>
+      </c>
+      <c r="I327" t="n">
+        <v>166.0906</v>
+      </c>
+      <c r="J327" t="n">
+        <v>36.065243</v>
+      </c>
+      <c r="K327" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L327" t="inlineStr"/>
+      <c r="M327" t="n">
+        <v>0.006020810182846752</v>
+      </c>
+      <c r="N327" t="n">
+        <v>0.02772752803313466</v>
+      </c>
+      <c r="O327" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P327" t="n">
+        <v>-0.01868246990692882</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2026-07-27 16:31:23</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>231.39</v>
+      </c>
+      <c r="F328" t="n">
+        <v>2489087688704</v>
+      </c>
+      <c r="G328" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="H328" t="n">
+        <v>9.91639</v>
+      </c>
+      <c r="I328" t="n">
+        <v>27.67823</v>
+      </c>
+      <c r="J328" t="n">
+        <v>23.334095</v>
+      </c>
+      <c r="K328" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L328" t="n">
+        <v>3.351061</v>
+      </c>
+      <c r="M328" t="n">
+        <v>0.03612947836985177</v>
+      </c>
+      <c r="N328" t="n">
+        <v>0.04285574138899693</v>
+      </c>
+      <c r="O328" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P328" t="n">
+        <v>-0.003554256551066545</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2026-07-27 16:31:23</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>383.22</v>
+      </c>
+      <c r="F329" t="n">
+        <v>1823199985664</v>
+      </c>
+      <c r="G329" t="n">
+        <v>6</v>
+      </c>
+      <c r="H329" t="n">
+        <v>19.51378</v>
+      </c>
+      <c r="I329" t="n">
+        <v>63.87</v>
+      </c>
+      <c r="J329" t="n">
+        <v>19.63843</v>
+      </c>
+      <c r="K329" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L329" t="n">
+        <v>24.159544</v>
+      </c>
+      <c r="M329" t="n">
+        <v>0.01565680288085173</v>
+      </c>
+      <c r="N329" t="n">
+        <v>0.05092056782005114</v>
+      </c>
+      <c r="O329" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P329" t="n">
+        <v>0.004510569879987665</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2026-07-27 16:31:23</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>326.57</v>
+      </c>
+      <c r="F330" t="n">
+        <v>3993930039296</v>
+      </c>
+      <c r="G330" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="H330" t="n">
+        <v>14.70592</v>
+      </c>
+      <c r="I330" t="n">
+        <v>16.377632</v>
+      </c>
+      <c r="J330" t="n">
+        <v>22.206703</v>
+      </c>
+      <c r="K330" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L330" t="n">
+        <v>8.957692</v>
+      </c>
+      <c r="M330" t="n">
+        <v>0.06105888477202438</v>
+      </c>
+      <c r="N330" t="n">
+        <v>0.04503144808157516</v>
+      </c>
+      <c r="O330" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P330" t="n">
+        <v>-0.001378549858488315</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2026-07-27 16:31:23</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>593.87</v>
+      </c>
+      <c r="F331" t="n">
+        <v>1507493412864</v>
+      </c>
+      <c r="G331" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H331" t="n">
+        <v>37.01198</v>
+      </c>
+      <c r="I331" t="n">
+        <v>21.595272</v>
+      </c>
+      <c r="J331" t="n">
+        <v>16.045345</v>
+      </c>
+      <c r="K331" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L331" t="n">
+        <v>7.0128045</v>
+      </c>
+      <c r="M331" t="n">
+        <v>0.04630643070032162</v>
+      </c>
+      <c r="N331" t="n">
+        <v>0.0623233704346069</v>
+      </c>
+      <c r="O331" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P331" t="n">
+        <v>0.01591337249454342</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>2026-07-27 16:31:23</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>389.1</v>
+      </c>
+      <c r="F332" t="n">
+        <v>2890404200448</v>
+      </c>
+      <c r="G332" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="H332" t="n">
+        <v>19.36655</v>
+      </c>
+      <c r="I332" t="n">
+        <v>23.174507</v>
+      </c>
+      <c r="J332" t="n">
+        <v>20.091343</v>
+      </c>
+      <c r="K332" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L332" t="n">
+        <v>9.081524999999999</v>
+      </c>
+      <c r="M332" t="n">
+        <v>0.04315086096119249</v>
+      </c>
+      <c r="N332" t="n">
+        <v>0.04977268054484708</v>
+      </c>
+      <c r="O332" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P332" t="n">
+        <v>0.003362682604783604</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2026-07-27 16:31:23</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="F333" t="n">
+        <v>293141348352</v>
+      </c>
+      <c r="G333" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H333" t="n">
+        <v>3.81756</v>
+      </c>
+      <c r="I333" t="n">
+        <v>22.138365</v>
+      </c>
+      <c r="J333" t="n">
+        <v>18.4411</v>
+      </c>
+      <c r="K333" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L333" t="n">
+        <v>6.0603</v>
+      </c>
+      <c r="M333" t="n">
+        <v>0.04517045454545454</v>
+      </c>
+      <c r="N333" t="n">
+        <v>0.05422670454545454</v>
+      </c>
+      <c r="O333" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P333" t="n">
+        <v>0.007816706605391056</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2026-07-27 16:31:23</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>196.51</v>
+      </c>
+      <c r="F334" t="n">
+        <v>4759668391936</v>
+      </c>
+      <c r="G334" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="H334" t="n">
+        <v>12.86903</v>
+      </c>
+      <c r="I334" t="n">
+        <v>30.0474</v>
+      </c>
+      <c r="J334" t="n">
+        <v>15.269993</v>
+      </c>
+      <c r="K334" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L334" t="n">
+        <v>18.776478</v>
+      </c>
+      <c r="M334" t="n">
+        <v>0.03328074907129408</v>
+      </c>
+      <c r="N334" t="n">
+        <v>0.06548791410106357</v>
+      </c>
+      <c r="O334" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P334" t="n">
+        <v>0.01907791616100009</v>
       </c>
     </row>
   </sheetData>
@@ -19388,12 +19908,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-24 16:30:12</t>
+          <t>2026-07-27 16:31:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -19407,51 +19927,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>319.09</v>
+        <v>326.57</v>
       </c>
       <c r="F2" t="n">
-        <v>3902449909760</v>
+        <v>3993930039296</v>
       </c>
       <c r="G2" t="n">
-        <v>19.93</v>
+        <v>19.94</v>
       </c>
       <c r="H2" t="n">
-        <v>14.77894</v>
+        <v>14.70592</v>
       </c>
       <c r="I2" t="n">
-        <v>16.010536</v>
+        <v>16.377632</v>
       </c>
       <c r="J2" t="n">
-        <v>21.590858</v>
+        <v>22.206703</v>
       </c>
       <c r="K2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="L2" t="n">
-        <v>8.752518</v>
+        <v>8.957692</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06245886740418064</v>
+        <v>0.06105888477202438</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0463158983358927</v>
+        <v>0.04503144808157516</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0004741006722860167</v>
+        <v>-0.001378549858488315</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-24 16:30:12</t>
+          <t>2026-07-27 16:31:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -19465,51 +19985,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>381.7</v>
+        <v>389.1</v>
       </c>
       <c r="F3" t="n">
-        <v>2835433652224</v>
+        <v>2890404200448</v>
       </c>
       <c r="G3" t="n">
         <v>16.79</v>
       </c>
       <c r="H3" t="n">
-        <v>19.37881</v>
+        <v>19.36655</v>
       </c>
       <c r="I3" t="n">
-        <v>22.73377</v>
+        <v>23.174507</v>
       </c>
       <c r="J3" t="n">
-        <v>19.696772</v>
+        <v>20.091343</v>
       </c>
       <c r="K3" t="n">
         <v>1.18</v>
       </c>
       <c r="L3" t="n">
-        <v>8.908810000000001</v>
+        <v>9.081524999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04398742467906733</v>
+        <v>0.04315086096119249</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05076974063400577</v>
+        <v>0.04977268054484708</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003979741625827059</v>
+        <v>0.003362682604783604</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-24 16:30:12</t>
+          <t>2026-07-27 16:31:23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -19523,51 +20043,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>595.1900000000001</v>
+        <v>593.87</v>
       </c>
       <c r="F4" t="n">
-        <v>1510844137472</v>
+        <v>1507493412864</v>
       </c>
       <c r="G4" t="n">
-        <v>27.52</v>
+        <v>27.5</v>
       </c>
       <c r="H4" t="n">
         <v>37.01198</v>
       </c>
       <c r="I4" t="n">
-        <v>21.627542</v>
+        <v>21.595272</v>
       </c>
       <c r="J4" t="n">
-        <v>16.08101</v>
+        <v>16.045345</v>
       </c>
       <c r="K4" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="L4" t="n">
-        <v>7.028392</v>
+        <v>7.0128045</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04623733597674692</v>
+        <v>0.04630643070032162</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06218515096019758</v>
+        <v>0.0623233704346069</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01539515195201887</v>
+        <v>0.01591337249454342</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-24 16:30:12</t>
+          <t>2026-07-27 16:31:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -19581,51 +20101,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>232.11</v>
+        <v>231.39</v>
       </c>
       <c r="F5" t="n">
-        <v>2496832733184</v>
+        <v>2489087688704</v>
       </c>
       <c r="G5" t="n">
-        <v>8.369999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>9.907080000000001</v>
+        <v>9.91639</v>
       </c>
       <c r="I5" t="n">
-        <v>27.731184</v>
+        <v>27.67823</v>
       </c>
       <c r="J5" t="n">
-        <v>23.4287</v>
+        <v>23.334095</v>
       </c>
       <c r="K5" t="n">
         <v>1.25</v>
       </c>
       <c r="L5" t="n">
-        <v>3.3614883</v>
+        <v>3.351061</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03606048856145792</v>
+        <v>0.03612947836985177</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04268269355047176</v>
+        <v>0.04285574138899693</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.004107305457706954</v>
+        <v>-0.003554256551066545</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-24 16:30:12</t>
+          <t>2026-07-27 16:31:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -19639,51 +20159,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>333.02</v>
+        <v>336.91</v>
       </c>
       <c r="F6" t="n">
-        <v>4891182891008</v>
+        <v>4948317175808</v>
       </c>
       <c r="G6" t="n">
-        <v>8.27</v>
+        <v>8.26</v>
       </c>
       <c r="H6" t="n">
-        <v>9.641249999999999</v>
+        <v>9.646129999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>40.268436</v>
+        <v>40.788136</v>
       </c>
       <c r="J6" t="n">
-        <v>34.541164</v>
+        <v>34.926964</v>
       </c>
       <c r="K6" t="n">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="L6" t="n">
-        <v>10.834576</v>
+        <v>10.961136</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02483334334274218</v>
+        <v>0.02451693330563058</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02895096390607171</v>
+        <v>0.02863117746579205</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01783903510210701</v>
+        <v>-0.01777882047427143</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-24 16:30:12</t>
+          <t>2026-07-27 16:31:23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -19697,51 +20217,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206.84</v>
+        <v>196.51</v>
       </c>
       <c r="F7" t="n">
-        <v>5009871732736</v>
+        <v>4759668391936</v>
       </c>
       <c r="G7" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
       <c r="H7" t="n">
         <v>12.86903</v>
       </c>
       <c r="I7" t="n">
-        <v>31.675343</v>
+        <v>30.0474</v>
       </c>
       <c r="J7" t="n">
-        <v>16.072695</v>
+        <v>15.269993</v>
       </c>
       <c r="K7" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="L7" t="n">
-        <v>19.76351</v>
+        <v>18.776478</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03157029588087411</v>
+        <v>0.03328074907129408</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06221731773351383</v>
+        <v>0.06548791410106357</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01542731872533511</v>
+        <v>0.01907791616100009</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-24 16:30:12</t>
+          <t>2026-07-27 16:31:23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -19755,51 +20275,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>521.95</v>
+        <v>494.95</v>
       </c>
       <c r="F8" t="n">
-        <v>851091980288</v>
+        <v>807065747456</v>
       </c>
       <c r="G8" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="H8" t="n">
-        <v>13.51362</v>
+        <v>13.72374</v>
       </c>
       <c r="I8" t="n">
-        <v>172.83113</v>
+        <v>166.0906</v>
       </c>
       <c r="J8" t="n">
-        <v>38.623997</v>
+        <v>36.065243</v>
       </c>
       <c r="K8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="L8" t="n">
-        <v>22.72366</v>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0.005785994827090717</v>
+        <v>0.006020810182846752</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02589064086598333</v>
+        <v>0.02772752803313466</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.02089935814219538</v>
+        <v>-0.01868246990692882</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-24 16:30:12</t>
+          <t>2026-07-27 16:31:23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -19813,51 +20331,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>381.92</v>
+        <v>383.22</v>
       </c>
       <c r="F9" t="n">
-        <v>1817015091200</v>
+        <v>1823199985664</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>19.46067</v>
+        <v>19.51378</v>
       </c>
       <c r="I9" t="n">
-        <v>63.653336</v>
+        <v>63.87</v>
       </c>
       <c r="J9" t="n">
-        <v>19.625223</v>
+        <v>19.63843</v>
       </c>
       <c r="K9" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="L9" t="n">
-        <v>24.077587</v>
+        <v>24.159544</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01571009635525765</v>
+        <v>0.01565680288085173</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05095483347297863</v>
+        <v>0.05092056782005114</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P9" t="n">
-        <v>0.00416483446479992</v>
+        <v>0.004510569879987665</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-24 16:30:12</t>
+          <t>2026-07-27 16:31:23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -19871,10 +20389,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>70.09</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>291850518528</v>
+        <v>293141348352</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -19883,28 +20401,28 @@
         <v>3.81756</v>
       </c>
       <c r="I10" t="n">
-        <v>22.040878</v>
+        <v>22.138365</v>
       </c>
       <c r="J10" t="n">
-        <v>18.359894</v>
+        <v>18.4411</v>
       </c>
       <c r="K10" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="L10" t="n">
-        <v>6.0336137</v>
+        <v>6.0603</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04537023826508774</v>
+        <v>0.04517045454545454</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05446654301612212</v>
+        <v>0.05422670454545454</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P10" t="n">
-        <v>0.00767654400794341</v>
+        <v>0.007816706605391056</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P334"/>
+  <dimension ref="A1:P343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19335,16 +19335,16 @@
         <v>10.961136</v>
       </c>
       <c r="M326" t="n">
-        <v>0.02451693330563058</v>
+        <v>0.0245169333056305</v>
       </c>
       <c r="N326" t="n">
-        <v>0.02863117746579205</v>
+        <v>0.028631177465792</v>
       </c>
       <c r="O326" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P326" t="n">
-        <v>-0.01777882047427143</v>
+        <v>-0.0177788204742714</v>
       </c>
     </row>
     <row r="327">
@@ -19391,16 +19391,16 @@
       </c>
       <c r="L327" t="inlineStr"/>
       <c r="M327" t="n">
-        <v>0.006020810182846752</v>
+        <v>0.0060208101828467</v>
       </c>
       <c r="N327" t="n">
-        <v>0.02772752803313466</v>
+        <v>0.0277275280331346</v>
       </c>
       <c r="O327" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P327" t="n">
-        <v>-0.01868246990692882</v>
+        <v>-0.0186824699069288</v>
       </c>
     </row>
     <row r="328">
@@ -19449,16 +19449,16 @@
         <v>3.351061</v>
       </c>
       <c r="M328" t="n">
-        <v>0.03612947836985177</v>
+        <v>0.0361294783698517</v>
       </c>
       <c r="N328" t="n">
-        <v>0.04285574138899693</v>
+        <v>0.0428557413889969</v>
       </c>
       <c r="O328" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P328" t="n">
-        <v>-0.003554256551066545</v>
+        <v>-0.0035542565510665</v>
       </c>
     </row>
     <row r="329">
@@ -19507,16 +19507,16 @@
         <v>24.159544</v>
       </c>
       <c r="M329" t="n">
-        <v>0.01565680288085173</v>
+        <v>0.0156568028808517</v>
       </c>
       <c r="N329" t="n">
-        <v>0.05092056782005114</v>
+        <v>0.0509205678200511</v>
       </c>
       <c r="O329" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P329" t="n">
-        <v>0.004510569879987665</v>
+        <v>0.0045105698799876</v>
       </c>
     </row>
     <row r="330">
@@ -19565,16 +19565,16 @@
         <v>8.957692</v>
       </c>
       <c r="M330" t="n">
-        <v>0.06105888477202438</v>
+        <v>0.0610588847720243</v>
       </c>
       <c r="N330" t="n">
-        <v>0.04503144808157516</v>
+        <v>0.0450314480815751</v>
       </c>
       <c r="O330" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P330" t="n">
-        <v>-0.001378549858488315</v>
+        <v>-0.0013785498584883</v>
       </c>
     </row>
     <row r="331">
@@ -19623,16 +19623,16 @@
         <v>7.0128045</v>
       </c>
       <c r="M331" t="n">
-        <v>0.04630643070032162</v>
+        <v>0.0463064307003216</v>
       </c>
       <c r="N331" t="n">
         <v>0.0623233704346069</v>
       </c>
       <c r="O331" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P331" t="n">
-        <v>0.01591337249454342</v>
+        <v>0.0159133724945434</v>
       </c>
     </row>
     <row r="332">
@@ -19681,16 +19681,16 @@
         <v>9.081524999999999</v>
       </c>
       <c r="M332" t="n">
-        <v>0.04315086096119249</v>
+        <v>0.0431508609611924</v>
       </c>
       <c r="N332" t="n">
-        <v>0.04977268054484708</v>
+        <v>0.049772680544847</v>
       </c>
       <c r="O332" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P332" t="n">
-        <v>0.003362682604783604</v>
+        <v>0.0033626826047836</v>
       </c>
     </row>
     <row r="333">
@@ -19739,16 +19739,16 @@
         <v>6.0603</v>
       </c>
       <c r="M333" t="n">
-        <v>0.04517045454545454</v>
+        <v>0.0451704545454545</v>
       </c>
       <c r="N333" t="n">
-        <v>0.05422670454545454</v>
+        <v>0.0542267045454545</v>
       </c>
       <c r="O333" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P333" t="n">
-        <v>0.007816706605391056</v>
+        <v>0.007816706605390999</v>
       </c>
     </row>
     <row r="334">
@@ -19797,16 +19797,536 @@
         <v>18.776478</v>
       </c>
       <c r="M334" t="n">
-        <v>0.03328074907129408</v>
+        <v>0.033280749071294</v>
       </c>
       <c r="N334" t="n">
-        <v>0.06548791410106357</v>
+        <v>0.0654879141010635</v>
       </c>
       <c r="O334" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P334" t="n">
-        <v>0.01907791616100009</v>
+        <v>0.019077916161</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:27:38</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>340.08</v>
+      </c>
+      <c r="F335" t="n">
+        <v>4994876047360</v>
+      </c>
+      <c r="G335" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H335" t="n">
+        <v>9.646129999999999</v>
+      </c>
+      <c r="I335" t="n">
+        <v>41.221817</v>
+      </c>
+      <c r="J335" t="n">
+        <v>35.25559</v>
+      </c>
+      <c r="K335" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L335" t="n">
+        <v>11.064269</v>
+      </c>
+      <c r="M335" t="n">
+        <v>0.0242589978828511</v>
+      </c>
+      <c r="N335" t="n">
+        <v>0.02836429663608563</v>
+      </c>
+      <c r="O335" t="n">
+        <v>0.04604000091552735</v>
+      </c>
+      <c r="P335" t="n">
+        <v>-0.01767570427944172</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:27:38</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>454.62</v>
+      </c>
+      <c r="F336" t="n">
+        <v>741303648256</v>
+      </c>
+      <c r="G336" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="H336" t="n">
+        <v>13.77774</v>
+      </c>
+      <c r="I336" t="n">
+        <v>150.53642</v>
+      </c>
+      <c r="J336" t="n">
+        <v>32.996704</v>
+      </c>
+      <c r="K336" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L336" t="inlineStr"/>
+      <c r="M336" t="n">
+        <v>0.006642910562667722</v>
+      </c>
+      <c r="N336" t="n">
+        <v>0.03030605780651973</v>
+      </c>
+      <c r="O336" t="n">
+        <v>0.04604000091552735</v>
+      </c>
+      <c r="P336" t="n">
+        <v>-0.01573394310900762</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:27:38</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>230.86</v>
+      </c>
+      <c r="F337" t="n">
+        <v>2483386318848</v>
+      </c>
+      <c r="G337" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="H337" t="n">
+        <v>9.920820000000001</v>
+      </c>
+      <c r="I337" t="n">
+        <v>27.647903</v>
+      </c>
+      <c r="J337" t="n">
+        <v>23.270254</v>
+      </c>
+      <c r="K337" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L337" t="n">
+        <v>3.3433852</v>
+      </c>
+      <c r="M337" t="n">
+        <v>0.03616910681798492</v>
+      </c>
+      <c r="N337" t="n">
+        <v>0.04297331716191631</v>
+      </c>
+      <c r="O337" t="n">
+        <v>0.04604000091552735</v>
+      </c>
+      <c r="P337" t="n">
+        <v>-0.003066683753611035</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:27:38</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>380.91</v>
+      </c>
+      <c r="F338" t="n">
+        <v>1812209860608</v>
+      </c>
+      <c r="G338" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H338" t="n">
+        <v>19.51378</v>
+      </c>
+      <c r="I338" t="n">
+        <v>63.274086</v>
+      </c>
+      <c r="J338" t="n">
+        <v>19.520052</v>
+      </c>
+      <c r="K338" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L338" t="n">
+        <v>24.013912</v>
+      </c>
+      <c r="M338" t="n">
+        <v>0.01580425822372739</v>
+      </c>
+      <c r="N338" t="n">
+        <v>0.05122937176760915</v>
+      </c>
+      <c r="O338" t="n">
+        <v>0.04604000091552735</v>
+      </c>
+      <c r="P338" t="n">
+        <v>0.0051893708520818</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:27:38</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>332.6</v>
+      </c>
+      <c r="F339" t="n">
+        <v>4067676389376</v>
+      </c>
+      <c r="G339" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H339" t="n">
+        <v>14.71912</v>
+      </c>
+      <c r="I339" t="n">
+        <v>16.696787</v>
+      </c>
+      <c r="J339" t="n">
+        <v>22.59646</v>
+      </c>
+      <c r="K339" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L339" t="n">
+        <v>9.123092</v>
+      </c>
+      <c r="M339" t="n">
+        <v>0.05989176187612748</v>
+      </c>
+      <c r="N339" t="n">
+        <v>0.04425472038484666</v>
+      </c>
+      <c r="O339" t="n">
+        <v>0.04604000091552735</v>
+      </c>
+      <c r="P339" t="n">
+        <v>-0.001785280530680687</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:27:38</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>593.41</v>
+      </c>
+      <c r="F340" t="n">
+        <v>1506325692416</v>
+      </c>
+      <c r="G340" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H340" t="n">
+        <v>37.01198</v>
+      </c>
+      <c r="I340" t="n">
+        <v>21.578545</v>
+      </c>
+      <c r="J340" t="n">
+        <v>16.032917</v>
+      </c>
+      <c r="K340" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L340" t="n">
+        <v>7.007372</v>
+      </c>
+      <c r="M340" t="n">
+        <v>0.04634232655331053</v>
+      </c>
+      <c r="N340" t="n">
+        <v>0.06237168231071267</v>
+      </c>
+      <c r="O340" t="n">
+        <v>0.04604000091552735</v>
+      </c>
+      <c r="P340" t="n">
+        <v>0.01633168139518532</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:27:38</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>393.35</v>
+      </c>
+      <c r="F341" t="n">
+        <v>2921974988800</v>
+      </c>
+      <c r="G341" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="H341" t="n">
+        <v>19.37878</v>
+      </c>
+      <c r="I341" t="n">
+        <v>23.399763</v>
+      </c>
+      <c r="J341" t="n">
+        <v>20.297976</v>
+      </c>
+      <c r="K341" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L341" t="n">
+        <v>9.180719</v>
+      </c>
+      <c r="M341" t="n">
+        <v>0.04273547731028346</v>
+      </c>
+      <c r="N341" t="n">
+        <v>0.04926599720350832</v>
+      </c>
+      <c r="O341" t="n">
+        <v>0.04604000091552735</v>
+      </c>
+      <c r="P341" t="n">
+        <v>0.003225996287980974</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:27:38</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>72.39</v>
+      </c>
+      <c r="F342" t="n">
+        <v>301427589120</v>
+      </c>
+      <c r="G342" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H342" t="n">
+        <v>3.81756</v>
+      </c>
+      <c r="I342" t="n">
+        <v>22.76415</v>
+      </c>
+      <c r="J342" t="n">
+        <v>18.962374</v>
+      </c>
+      <c r="K342" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L342" t="n">
+        <v>6.2316065</v>
+      </c>
+      <c r="M342" t="n">
+        <v>0.04392871943638624</v>
+      </c>
+      <c r="N342" t="n">
+        <v>0.0527360132615002</v>
+      </c>
+      <c r="O342" t="n">
+        <v>0.04604000091552735</v>
+      </c>
+      <c r="P342" t="n">
+        <v>0.006696012345972856</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:27:38</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>197.01</v>
+      </c>
+      <c r="F343" t="n">
+        <v>4771778920448</v>
+      </c>
+      <c r="G343" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="H343" t="n">
+        <v>12.86903</v>
+      </c>
+      <c r="I343" t="n">
+        <v>30.216257</v>
+      </c>
+      <c r="J343" t="n">
+        <v>15.3088455</v>
+      </c>
+      <c r="K343" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L343" t="n">
+        <v>18.824253</v>
+      </c>
+      <c r="M343" t="n">
+        <v>0.03309476676310847</v>
+      </c>
+      <c r="N343" t="n">
+        <v>0.06532170955789046</v>
+      </c>
+      <c r="O343" t="n">
+        <v>0.04604000091552735</v>
+      </c>
+      <c r="P343" t="n">
+        <v>0.01928170864236312</v>
       </c>
     </row>
   </sheetData>
@@ -19908,12 +20428,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-27 16:31:23</t>
+          <t>2026-07-28 16:27:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -19927,51 +20447,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>326.57</v>
+        <v>332.6</v>
       </c>
       <c r="F2" t="n">
-        <v>3993930039296</v>
+        <v>4067676389376</v>
       </c>
       <c r="G2" t="n">
-        <v>19.94</v>
+        <v>19.92</v>
       </c>
       <c r="H2" t="n">
-        <v>14.70592</v>
+        <v>14.71912</v>
       </c>
       <c r="I2" t="n">
-        <v>16.377632</v>
+        <v>16.696787</v>
       </c>
       <c r="J2" t="n">
-        <v>22.206703</v>
+        <v>22.59646</v>
       </c>
       <c r="K2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="L2" t="n">
-        <v>8.957692</v>
+        <v>9.123092</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06105888477202438</v>
+        <v>0.05989176187612748</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04503144808157516</v>
+        <v>0.04425472038484666</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04604000091552735</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.001378549858488315</v>
+        <v>-0.001785280530680687</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-27 16:31:23</t>
+          <t>2026-07-28 16:27:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -19985,51 +20505,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>389.1</v>
+        <v>393.35</v>
       </c>
       <c r="F3" t="n">
-        <v>2890404200448</v>
+        <v>2921974988800</v>
       </c>
       <c r="G3" t="n">
-        <v>16.79</v>
+        <v>16.81</v>
       </c>
       <c r="H3" t="n">
-        <v>19.36655</v>
+        <v>19.37878</v>
       </c>
       <c r="I3" t="n">
-        <v>23.174507</v>
+        <v>23.399763</v>
       </c>
       <c r="J3" t="n">
-        <v>20.091343</v>
+        <v>20.297976</v>
       </c>
       <c r="K3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="L3" t="n">
-        <v>9.081524999999999</v>
+        <v>9.180719</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04315086096119249</v>
+        <v>0.04273547731028346</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04977268054484708</v>
+        <v>0.04926599720350832</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04604000091552735</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003362682604783604</v>
+        <v>0.003225996287980974</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-27 16:31:23</t>
+          <t>2026-07-28 16:27:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -20043,10 +20563,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>593.87</v>
+        <v>593.41</v>
       </c>
       <c r="F4" t="n">
-        <v>1507493412864</v>
+        <v>1506325692416</v>
       </c>
       <c r="G4" t="n">
         <v>27.5</v>
@@ -20055,39 +20575,39 @@
         <v>37.01198</v>
       </c>
       <c r="I4" t="n">
-        <v>21.595272</v>
+        <v>21.578545</v>
       </c>
       <c r="J4" t="n">
-        <v>16.045345</v>
+        <v>16.032917</v>
       </c>
       <c r="K4" t="n">
         <v>0.87</v>
       </c>
       <c r="L4" t="n">
-        <v>7.0128045</v>
+        <v>7.007372</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04630643070032162</v>
+        <v>0.04634232655331053</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0623233704346069</v>
+        <v>0.06237168231071267</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04604000091552735</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01591337249454342</v>
+        <v>0.01633168139518532</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-27 16:31:23</t>
+          <t>2026-07-28 16:27:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -20101,51 +20621,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>231.39</v>
+        <v>230.86</v>
       </c>
       <c r="F5" t="n">
-        <v>2489087688704</v>
+        <v>2483386318848</v>
       </c>
       <c r="G5" t="n">
-        <v>8.359999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="H5" t="n">
-        <v>9.91639</v>
+        <v>9.920820000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>27.67823</v>
+        <v>27.647903</v>
       </c>
       <c r="J5" t="n">
-        <v>23.334095</v>
+        <v>23.270254</v>
       </c>
       <c r="K5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="L5" t="n">
-        <v>3.351061</v>
+        <v>3.3433852</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03612947836985177</v>
+        <v>0.03616910681798492</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04285574138899693</v>
+        <v>0.04297331716191631</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04604000091552735</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.003554256551066545</v>
+        <v>-0.003066683753611035</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-27 16:31:23</t>
+          <t>2026-07-28 16:27:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -20159,51 +20679,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>336.91</v>
+        <v>340.08</v>
       </c>
       <c r="F6" t="n">
-        <v>4948317175808</v>
+        <v>4994876047360</v>
       </c>
       <c r="G6" t="n">
-        <v>8.26</v>
+        <v>8.25</v>
       </c>
       <c r="H6" t="n">
         <v>9.646129999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>40.788136</v>
+        <v>41.221817</v>
       </c>
       <c r="J6" t="n">
-        <v>34.926964</v>
+        <v>35.25559</v>
       </c>
       <c r="K6" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="L6" t="n">
-        <v>10.961136</v>
+        <v>11.064269</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02451693330563058</v>
+        <v>0.0242589978828511</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02863117746579205</v>
+        <v>0.02836429663608563</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04604000091552735</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01777882047427143</v>
+        <v>-0.01767570427944172</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-27 16:31:23</t>
+          <t>2026-07-28 16:27:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -20217,51 +20737,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>196.51</v>
+        <v>197.01</v>
       </c>
       <c r="F7" t="n">
-        <v>4759668391936</v>
+        <v>4771778920448</v>
       </c>
       <c r="G7" t="n">
-        <v>6.54</v>
+        <v>6.52</v>
       </c>
       <c r="H7" t="n">
         <v>12.86903</v>
       </c>
       <c r="I7" t="n">
-        <v>30.0474</v>
+        <v>30.216257</v>
       </c>
       <c r="J7" t="n">
-        <v>15.269993</v>
+        <v>15.3088455</v>
       </c>
       <c r="K7" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="L7" t="n">
-        <v>18.776478</v>
+        <v>18.824253</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03328074907129408</v>
+        <v>0.03309476676310847</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06548791410106357</v>
+        <v>0.06532170955789046</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04604000091552735</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01907791616100009</v>
+        <v>0.01928170864236312</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-27 16:31:23</t>
+          <t>2026-07-28 16:27:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -20275,49 +20795,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>494.95</v>
+        <v>454.62</v>
       </c>
       <c r="F8" t="n">
-        <v>807065747456</v>
+        <v>741303648256</v>
       </c>
       <c r="G8" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="H8" t="n">
-        <v>13.72374</v>
+        <v>13.77774</v>
       </c>
       <c r="I8" t="n">
-        <v>166.0906</v>
+        <v>150.53642</v>
       </c>
       <c r="J8" t="n">
-        <v>36.065243</v>
+        <v>32.996704</v>
       </c>
       <c r="K8" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0.006020810182846752</v>
+        <v>0.006642910562667722</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02772752803313466</v>
+        <v>0.03030605780651973</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04604000091552735</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01868246990692882</v>
+        <v>-0.01573394310900762</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-27 16:31:23</t>
+          <t>2026-07-28 16:27:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -20331,51 +20851,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>383.22</v>
+        <v>380.91</v>
       </c>
       <c r="F9" t="n">
-        <v>1823199985664</v>
+        <v>1812209860608</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>6.02</v>
       </c>
       <c r="H9" t="n">
         <v>19.51378</v>
       </c>
       <c r="I9" t="n">
-        <v>63.87</v>
+        <v>63.274086</v>
       </c>
       <c r="J9" t="n">
-        <v>19.63843</v>
+        <v>19.520052</v>
       </c>
       <c r="K9" t="n">
         <v>0.43</v>
       </c>
       <c r="L9" t="n">
-        <v>24.159544</v>
+        <v>24.013912</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01565680288085173</v>
+        <v>0.01580425822372739</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05092056782005114</v>
+        <v>0.05122937176760915</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04604000091552735</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004510569879987665</v>
+        <v>0.0051893708520818</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-27 16:31:23</t>
+          <t>2026-07-28 16:27:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -20389,10 +20909,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>70.40000000000001</v>
+        <v>72.39</v>
       </c>
       <c r="F10" t="n">
-        <v>293141348352</v>
+        <v>301427589120</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -20401,28 +20921,28 @@
         <v>3.81756</v>
       </c>
       <c r="I10" t="n">
-        <v>22.138365</v>
+        <v>22.76415</v>
       </c>
       <c r="J10" t="n">
-        <v>18.4411</v>
+        <v>18.962374</v>
       </c>
       <c r="K10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="L10" t="n">
-        <v>6.0603</v>
+        <v>6.2316065</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04517045454545454</v>
+        <v>0.04392871943638624</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05422670454545454</v>
+        <v>0.0527360132615002</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04604000091552735</v>
       </c>
       <c r="P10" t="n">
-        <v>0.007816706605391056</v>
+        <v>0.006696012345972856</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P343"/>
+  <dimension ref="A1:P352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19855,16 +19855,16 @@
         <v>11.064269</v>
       </c>
       <c r="M335" t="n">
-        <v>0.0242589978828511</v>
+        <v>0.024258997882851</v>
       </c>
       <c r="N335" t="n">
-        <v>0.02836429663608563</v>
+        <v>0.0283642966360856</v>
       </c>
       <c r="O335" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.0460400009155273</v>
       </c>
       <c r="P335" t="n">
-        <v>-0.01767570427944172</v>
+        <v>-0.0176757042794417</v>
       </c>
     </row>
     <row r="336">
@@ -19911,16 +19911,16 @@
       </c>
       <c r="L336" t="inlineStr"/>
       <c r="M336" t="n">
-        <v>0.006642910562667722</v>
+        <v>0.0066429105626677</v>
       </c>
       <c r="N336" t="n">
-        <v>0.03030605780651973</v>
+        <v>0.0303060578065197</v>
       </c>
       <c r="O336" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.0460400009155273</v>
       </c>
       <c r="P336" t="n">
-        <v>-0.01573394310900762</v>
+        <v>-0.0157339431090076</v>
       </c>
     </row>
     <row r="337">
@@ -19969,16 +19969,16 @@
         <v>3.3433852</v>
       </c>
       <c r="M337" t="n">
-        <v>0.03616910681798492</v>
+        <v>0.0361691068179849</v>
       </c>
       <c r="N337" t="n">
-        <v>0.04297331716191631</v>
+        <v>0.0429733171619163</v>
       </c>
       <c r="O337" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.0460400009155273</v>
       </c>
       <c r="P337" t="n">
-        <v>-0.003066683753611035</v>
+        <v>-0.003066683753611</v>
       </c>
     </row>
     <row r="338">
@@ -20027,13 +20027,13 @@
         <v>24.013912</v>
       </c>
       <c r="M338" t="n">
-        <v>0.01580425822372739</v>
+        <v>0.0158042582237273</v>
       </c>
       <c r="N338" t="n">
-        <v>0.05122937176760915</v>
+        <v>0.0512293717676091</v>
       </c>
       <c r="O338" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.0460400009155273</v>
       </c>
       <c r="P338" t="n">
         <v>0.0051893708520818</v>
@@ -20085,16 +20085,16 @@
         <v>9.123092</v>
       </c>
       <c r="M339" t="n">
-        <v>0.05989176187612748</v>
+        <v>0.0598917618761274</v>
       </c>
       <c r="N339" t="n">
-        <v>0.04425472038484666</v>
+        <v>0.0442547203848466</v>
       </c>
       <c r="O339" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.0460400009155273</v>
       </c>
       <c r="P339" t="n">
-        <v>-0.001785280530680687</v>
+        <v>-0.0017852805306806</v>
       </c>
     </row>
     <row r="340">
@@ -20143,16 +20143,16 @@
         <v>7.007372</v>
       </c>
       <c r="M340" t="n">
-        <v>0.04634232655331053</v>
+        <v>0.0463423265533105</v>
       </c>
       <c r="N340" t="n">
-        <v>0.06237168231071267</v>
+        <v>0.0623716823107126</v>
       </c>
       <c r="O340" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.0460400009155273</v>
       </c>
       <c r="P340" t="n">
-        <v>0.01633168139518532</v>
+        <v>0.0163316813951853</v>
       </c>
     </row>
     <row r="341">
@@ -20201,16 +20201,16 @@
         <v>9.180719</v>
       </c>
       <c r="M341" t="n">
-        <v>0.04273547731028346</v>
+        <v>0.0427354773102834</v>
       </c>
       <c r="N341" t="n">
-        <v>0.04926599720350832</v>
+        <v>0.0492659972035083</v>
       </c>
       <c r="O341" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.0460400009155273</v>
       </c>
       <c r="P341" t="n">
-        <v>0.003225996287980974</v>
+        <v>0.0032259962879809</v>
       </c>
     </row>
     <row r="342">
@@ -20259,16 +20259,16 @@
         <v>6.2316065</v>
       </c>
       <c r="M342" t="n">
-        <v>0.04392871943638624</v>
+        <v>0.0439287194363862</v>
       </c>
       <c r="N342" t="n">
         <v>0.0527360132615002</v>
       </c>
       <c r="O342" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.0460400009155273</v>
       </c>
       <c r="P342" t="n">
-        <v>0.006696012345972856</v>
+        <v>0.0066960123459728</v>
       </c>
     </row>
     <row r="343">
@@ -20317,16 +20317,534 @@
         <v>18.824253</v>
       </c>
       <c r="M343" t="n">
-        <v>0.03309476676310847</v>
+        <v>0.0330947667631084</v>
       </c>
       <c r="N343" t="n">
-        <v>0.06532170955789046</v>
+        <v>0.06532170955789041</v>
       </c>
       <c r="O343" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.0460400009155273</v>
       </c>
       <c r="P343" t="n">
-        <v>0.01928170864236312</v>
+        <v>0.0192817086423631</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>2026-07-29 16:28:02</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>338.19</v>
+      </c>
+      <c r="F344" t="n">
+        <v>4967117094912</v>
+      </c>
+      <c r="G344" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H344" t="n">
+        <v>9.65692</v>
+      </c>
+      <c r="I344" t="n">
+        <v>40.9431</v>
+      </c>
+      <c r="J344" t="n">
+        <v>35.02048</v>
+      </c>
+      <c r="K344" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L344" t="n">
+        <v>11.00278</v>
+      </c>
+      <c r="M344" t="n">
+        <v>0.02442414027617611</v>
+      </c>
+      <c r="N344" t="n">
+        <v>0.02855471776220468</v>
+      </c>
+      <c r="O344" t="n">
+        <v>0.04622000217437744</v>
+      </c>
+      <c r="P344" t="n">
+        <v>-0.01766528441217276</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2026-07-29 16:28:02</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>429.56</v>
+      </c>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="n">
+        <v>3</v>
+      </c>
+      <c r="H345" t="n">
+        <v>13.77774</v>
+      </c>
+      <c r="I345" t="n">
+        <v>143.18666</v>
+      </c>
+      <c r="J345" t="n">
+        <v>31.177828</v>
+      </c>
+      <c r="K345" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L345" t="inlineStr"/>
+      <c r="M345" t="n">
+        <v>0.006983890492597076</v>
+      </c>
+      <c r="N345" t="n">
+        <v>0.03207407579849148</v>
+      </c>
+      <c r="O345" t="n">
+        <v>0.04622000217437744</v>
+      </c>
+      <c r="P345" t="n">
+        <v>-0.01414592637588596</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2026-07-29 16:28:02</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>226.65</v>
+      </c>
+      <c r="F346" t="n">
+        <v>2438098845696</v>
+      </c>
+      <c r="G346" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="H346" t="n">
+        <v>9.920820000000001</v>
+      </c>
+      <c r="I346" t="n">
+        <v>27.111244</v>
+      </c>
+      <c r="J346" t="n">
+        <v>22.845892</v>
+      </c>
+      <c r="K346" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L346" t="n">
+        <v>3.2824147</v>
+      </c>
+      <c r="M346" t="n">
+        <v>0.03688506507831458</v>
+      </c>
+      <c r="N346" t="n">
+        <v>0.04377154202514891</v>
+      </c>
+      <c r="O346" t="n">
+        <v>0.04622000217437744</v>
+      </c>
+      <c r="P346" t="n">
+        <v>-0.002448460149228532</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>2026-07-29 16:28:02</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>370.32</v>
+      </c>
+      <c r="F347" t="n">
+        <v>1761827225600</v>
+      </c>
+      <c r="G347" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H347" t="n">
+        <v>19.51378</v>
+      </c>
+      <c r="I347" t="n">
+        <v>61.51495</v>
+      </c>
+      <c r="J347" t="n">
+        <v>18.977358</v>
+      </c>
+      <c r="K347" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L347" t="n">
+        <v>23.346283</v>
+      </c>
+      <c r="M347" t="n">
+        <v>0.01625621084467488</v>
+      </c>
+      <c r="N347" t="n">
+        <v>0.05269437243465112</v>
+      </c>
+      <c r="O347" t="n">
+        <v>0.04622000217437744</v>
+      </c>
+      <c r="P347" t="n">
+        <v>0.006474370260273678</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2026-07-29 16:28:02</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>335.76</v>
+      </c>
+      <c r="F348" t="n">
+        <v>4106323230720</v>
+      </c>
+      <c r="G348" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H348" t="n">
+        <v>14.72855</v>
+      </c>
+      <c r="I348" t="n">
+        <v>16.855423</v>
+      </c>
+      <c r="J348" t="n">
+        <v>22.796541</v>
+      </c>
+      <c r="K348" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L348" t="n">
+        <v>9.209770000000001</v>
+      </c>
+      <c r="M348" t="n">
+        <v>0.05932809149392424</v>
+      </c>
+      <c r="N348" t="n">
+        <v>0.04386630331188945</v>
+      </c>
+      <c r="O348" t="n">
+        <v>0.04622000217437744</v>
+      </c>
+      <c r="P348" t="n">
+        <v>-0.002353698862487992</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2026-07-29 16:28:02</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>585.61</v>
+      </c>
+      <c r="F349" t="n">
+        <v>1486526087168</v>
+      </c>
+      <c r="G349" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="H349" t="n">
+        <v>37.01198</v>
+      </c>
+      <c r="I349" t="n">
+        <v>21.318165</v>
+      </c>
+      <c r="J349" t="n">
+        <v>15.822175</v>
+      </c>
+      <c r="K349" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L349" t="n">
+        <v>6.915265</v>
+      </c>
+      <c r="M349" t="n">
+        <v>0.04690835197486382</v>
+      </c>
+      <c r="N349" t="n">
+        <v>0.0632024384829494</v>
+      </c>
+      <c r="O349" t="n">
+        <v>0.04622000217437744</v>
+      </c>
+      <c r="P349" t="n">
+        <v>0.01698243630857196</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>2026-07-29 16:28:02</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>390.54</v>
+      </c>
+      <c r="F350" t="n">
+        <v>2901100986368</v>
+      </c>
+      <c r="G350" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H350" t="n">
+        <v>19.37878</v>
+      </c>
+      <c r="I350" t="n">
+        <v>23.24643</v>
+      </c>
+      <c r="J350" t="n">
+        <v>20.152971</v>
+      </c>
+      <c r="K350" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L350" t="n">
+        <v>9.115133999999999</v>
+      </c>
+      <c r="M350" t="n">
+        <v>0.0430173605776617</v>
+      </c>
+      <c r="N350" t="n">
+        <v>0.04962047421518922</v>
+      </c>
+      <c r="O350" t="n">
+        <v>0.04622000217437744</v>
+      </c>
+      <c r="P350" t="n">
+        <v>0.003400472040811779</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>2026-07-29 16:28:02</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>73.63</v>
+      </c>
+      <c r="F351" t="n">
+        <v>306590875648</v>
+      </c>
+      <c r="G351" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H351" t="n">
+        <v>3.81756</v>
+      </c>
+      <c r="I351" t="n">
+        <v>23.154087</v>
+      </c>
+      <c r="J351" t="n">
+        <v>19.287188</v>
+      </c>
+      <c r="K351" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L351" t="n">
+        <v>6.338351</v>
+      </c>
+      <c r="M351" t="n">
+        <v>0.04318891756077686</v>
+      </c>
+      <c r="N351" t="n">
+        <v>0.05184788808909412</v>
+      </c>
+      <c r="O351" t="n">
+        <v>0.04622000217437744</v>
+      </c>
+      <c r="P351" t="n">
+        <v>0.005627885914716683</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>2026-07-29 16:28:02</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>190.01</v>
+      </c>
+      <c r="F352" t="n">
+        <v>4602232045568</v>
+      </c>
+      <c r="G352" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="H352" t="n">
+        <v>12.86903</v>
+      </c>
+      <c r="I352" t="n">
+        <v>29.142637</v>
+      </c>
+      <c r="J352" t="n">
+        <v>14.764904</v>
+      </c>
+      <c r="K352" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L352" t="n">
+        <v>18.155405</v>
+      </c>
+      <c r="M352" t="n">
+        <v>0.03431398347455397</v>
+      </c>
+      <c r="N352" t="n">
+        <v>0.06772817220146309</v>
+      </c>
+      <c r="O352" t="n">
+        <v>0.04622000217437744</v>
+      </c>
+      <c r="P352" t="n">
+        <v>0.02150817002708565</v>
       </c>
     </row>
   </sheetData>
@@ -20428,12 +20946,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-28 16:27:38</t>
+          <t>2026-07-29 16:28:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -20447,51 +20965,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>332.6</v>
+        <v>335.76</v>
       </c>
       <c r="F2" t="n">
-        <v>4067676389376</v>
+        <v>4106323230720</v>
       </c>
       <c r="G2" t="n">
         <v>19.92</v>
       </c>
       <c r="H2" t="n">
-        <v>14.71912</v>
+        <v>14.72855</v>
       </c>
       <c r="I2" t="n">
-        <v>16.696787</v>
+        <v>16.855423</v>
       </c>
       <c r="J2" t="n">
-        <v>22.59646</v>
+        <v>22.796541</v>
       </c>
       <c r="K2" t="n">
         <v>1.27</v>
       </c>
       <c r="L2" t="n">
-        <v>9.123092</v>
+        <v>9.209770000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05989176187612748</v>
+        <v>0.05932809149392424</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04425472038484666</v>
+        <v>0.04386630331188945</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.04622000217437744</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.001785280530680687</v>
+        <v>-0.002353698862487992</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-28 16:27:38</t>
+          <t>2026-07-29 16:28:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -20505,51 +21023,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>393.35</v>
+        <v>390.54</v>
       </c>
       <c r="F3" t="n">
-        <v>2921974988800</v>
+        <v>2901100986368</v>
       </c>
       <c r="G3" t="n">
-        <v>16.81</v>
+        <v>16.8</v>
       </c>
       <c r="H3" t="n">
         <v>19.37878</v>
       </c>
       <c r="I3" t="n">
-        <v>23.399763</v>
+        <v>23.24643</v>
       </c>
       <c r="J3" t="n">
-        <v>20.297976</v>
+        <v>20.152971</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="L3" t="n">
-        <v>9.180719</v>
+        <v>9.115133999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04273547731028346</v>
+        <v>0.0430173605776617</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04926599720350832</v>
+        <v>0.04962047421518922</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.04622000217437744</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003225996287980974</v>
+        <v>0.003400472040811779</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-28 16:27:38</t>
+          <t>2026-07-29 16:28:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -20563,51 +21081,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>593.41</v>
+        <v>585.61</v>
       </c>
       <c r="F4" t="n">
-        <v>1506325692416</v>
+        <v>1486526087168</v>
       </c>
       <c r="G4" t="n">
-        <v>27.5</v>
+        <v>27.47</v>
       </c>
       <c r="H4" t="n">
         <v>37.01198</v>
       </c>
       <c r="I4" t="n">
-        <v>21.578545</v>
+        <v>21.318165</v>
       </c>
       <c r="J4" t="n">
-        <v>16.032917</v>
+        <v>15.822175</v>
       </c>
       <c r="K4" t="n">
         <v>0.87</v>
       </c>
       <c r="L4" t="n">
-        <v>7.007372</v>
+        <v>6.915265</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04634232655331053</v>
+        <v>0.04690835197486382</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06237168231071267</v>
+        <v>0.0632024384829494</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.04622000217437744</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01633168139518532</v>
+        <v>0.01698243630857196</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-28 16:27:38</t>
+          <t>2026-07-29 16:28:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -20621,51 +21139,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230.86</v>
+        <v>226.65</v>
       </c>
       <c r="F5" t="n">
-        <v>2483386318848</v>
+        <v>2438098845696</v>
       </c>
       <c r="G5" t="n">
-        <v>8.35</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="H5" t="n">
         <v>9.920820000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>27.647903</v>
+        <v>27.111244</v>
       </c>
       <c r="J5" t="n">
-        <v>23.270254</v>
+        <v>22.845892</v>
       </c>
       <c r="K5" t="n">
         <v>1.24</v>
       </c>
       <c r="L5" t="n">
-        <v>3.3433852</v>
+        <v>3.2824147</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03616910681798492</v>
+        <v>0.03688506507831458</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04297331716191631</v>
+        <v>0.04377154202514891</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.04622000217437744</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.003066683753611035</v>
+        <v>-0.002448460149228532</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-28 16:27:38</t>
+          <t>2026-07-29 16:28:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -20679,51 +21197,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>340.08</v>
+        <v>338.19</v>
       </c>
       <c r="F6" t="n">
-        <v>4994876047360</v>
+        <v>4967117094912</v>
       </c>
       <c r="G6" t="n">
-        <v>8.25</v>
+        <v>8.26</v>
       </c>
       <c r="H6" t="n">
-        <v>9.646129999999999</v>
+        <v>9.65692</v>
       </c>
       <c r="I6" t="n">
-        <v>41.221817</v>
+        <v>40.9431</v>
       </c>
       <c r="J6" t="n">
-        <v>35.25559</v>
+        <v>35.02048</v>
       </c>
       <c r="K6" t="n">
         <v>2.71</v>
       </c>
       <c r="L6" t="n">
-        <v>11.064269</v>
+        <v>11.00278</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0242589978828511</v>
+        <v>0.02442414027617611</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02836429663608563</v>
+        <v>0.02855471776220468</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.04622000217437744</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01767570427944172</v>
+        <v>-0.01766528441217276</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-28 16:27:38</t>
+          <t>2026-07-29 16:28:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -20737,10 +21255,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>197.01</v>
+        <v>190.01</v>
       </c>
       <c r="F7" t="n">
-        <v>4771778920448</v>
+        <v>4602232045568</v>
       </c>
       <c r="G7" t="n">
         <v>6.52</v>
@@ -20749,39 +21267,39 @@
         <v>12.86903</v>
       </c>
       <c r="I7" t="n">
-        <v>30.216257</v>
+        <v>29.142637</v>
       </c>
       <c r="J7" t="n">
-        <v>15.3088455</v>
+        <v>14.764904</v>
       </c>
       <c r="K7" t="n">
         <v>0.54</v>
       </c>
       <c r="L7" t="n">
-        <v>18.824253</v>
+        <v>18.155405</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03309476676310847</v>
+        <v>0.03431398347455397</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06532170955789046</v>
+        <v>0.06772817220146309</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.04622000217437744</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01928170864236312</v>
+        <v>0.02150817002708565</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-28 16:27:38</t>
+          <t>2026-07-29 16:28:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -20795,49 +21313,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>454.62</v>
-      </c>
-      <c r="F8" t="n">
-        <v>741303648256</v>
-      </c>
+        <v>429.56</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>13.77774</v>
       </c>
       <c r="I8" t="n">
-        <v>150.53642</v>
+        <v>143.18666</v>
       </c>
       <c r="J8" t="n">
-        <v>32.996704</v>
+        <v>31.177828</v>
       </c>
       <c r="K8" t="n">
         <v>1.16</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0.006642910562667722</v>
+        <v>0.006983890492597076</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03030605780651973</v>
+        <v>0.03207407579849148</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.04622000217437744</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01573394310900762</v>
+        <v>-0.01414592637588596</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-28 16:27:38</t>
+          <t>2026-07-29 16:28:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -20851,10 +21367,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>380.91</v>
+        <v>370.32</v>
       </c>
       <c r="F9" t="n">
-        <v>1812209860608</v>
+        <v>1761827225600</v>
       </c>
       <c r="G9" t="n">
         <v>6.02</v>
@@ -20863,39 +21379,39 @@
         <v>19.51378</v>
       </c>
       <c r="I9" t="n">
-        <v>63.274086</v>
+        <v>61.51495</v>
       </c>
       <c r="J9" t="n">
-        <v>19.520052</v>
+        <v>18.977358</v>
       </c>
       <c r="K9" t="n">
         <v>0.43</v>
       </c>
       <c r="L9" t="n">
-        <v>24.013912</v>
+        <v>23.346283</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01580425822372739</v>
+        <v>0.01625621084467488</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05122937176760915</v>
+        <v>0.05269437243465112</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.04622000217437744</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0051893708520818</v>
+        <v>0.006474370260273678</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-28 16:27:38</t>
+          <t>2026-07-29 16:28:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -20909,10 +21425,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>72.39</v>
+        <v>73.63</v>
       </c>
       <c r="F10" t="n">
-        <v>301427589120</v>
+        <v>306590875648</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -20921,28 +21437,28 @@
         <v>3.81756</v>
       </c>
       <c r="I10" t="n">
-        <v>22.76415</v>
+        <v>23.154087</v>
       </c>
       <c r="J10" t="n">
-        <v>18.962374</v>
+        <v>19.287188</v>
       </c>
       <c r="K10" t="n">
         <v>1.58</v>
       </c>
       <c r="L10" t="n">
-        <v>6.2316065</v>
+        <v>6.338351</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04392871943638624</v>
+        <v>0.04318891756077686</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0527360132615002</v>
+        <v>0.05184788808909412</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.04622000217437744</v>
       </c>
       <c r="P10" t="n">
-        <v>0.006696012345972856</v>
+        <v>0.005627885914716683</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P352"/>
+  <dimension ref="A1:P361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20375,16 +20375,16 @@
         <v>11.00278</v>
       </c>
       <c r="M344" t="n">
-        <v>0.02442414027617611</v>
+        <v>0.0244241402761761</v>
       </c>
       <c r="N344" t="n">
-        <v>0.02855471776220468</v>
+        <v>0.0285547177622046</v>
       </c>
       <c r="O344" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.0462200021743774</v>
       </c>
       <c r="P344" t="n">
-        <v>-0.01766528441217276</v>
+        <v>-0.0176652844121727</v>
       </c>
     </row>
     <row r="345">
@@ -20429,16 +20429,16 @@
       </c>
       <c r="L345" t="inlineStr"/>
       <c r="M345" t="n">
-        <v>0.006983890492597076</v>
+        <v>0.006983890492597</v>
       </c>
       <c r="N345" t="n">
-        <v>0.03207407579849148</v>
+        <v>0.0320740757984914</v>
       </c>
       <c r="O345" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.0462200021743774</v>
       </c>
       <c r="P345" t="n">
-        <v>-0.01414592637588596</v>
+        <v>-0.0141459263758859</v>
       </c>
     </row>
     <row r="346">
@@ -20487,16 +20487,16 @@
         <v>3.2824147</v>
       </c>
       <c r="M346" t="n">
-        <v>0.03688506507831458</v>
+        <v>0.0368850650783145</v>
       </c>
       <c r="N346" t="n">
-        <v>0.04377154202514891</v>
+        <v>0.0437715420251489</v>
       </c>
       <c r="O346" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.0462200021743774</v>
       </c>
       <c r="P346" t="n">
-        <v>-0.002448460149228532</v>
+        <v>-0.0024484601492285</v>
       </c>
     </row>
     <row r="347">
@@ -20545,16 +20545,16 @@
         <v>23.346283</v>
       </c>
       <c r="M347" t="n">
-        <v>0.01625621084467488</v>
+        <v>0.0162562108446748</v>
       </c>
       <c r="N347" t="n">
-        <v>0.05269437243465112</v>
+        <v>0.0526943724346511</v>
       </c>
       <c r="O347" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.0462200021743774</v>
       </c>
       <c r="P347" t="n">
-        <v>0.006474370260273678</v>
+        <v>0.0064743702602736</v>
       </c>
     </row>
     <row r="348">
@@ -20603,16 +20603,16 @@
         <v>9.209770000000001</v>
       </c>
       <c r="M348" t="n">
-        <v>0.05932809149392424</v>
+        <v>0.0593280914939242</v>
       </c>
       <c r="N348" t="n">
-        <v>0.04386630331188945</v>
+        <v>0.0438663033118894</v>
       </c>
       <c r="O348" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.0462200021743774</v>
       </c>
       <c r="P348" t="n">
-        <v>-0.002353698862487992</v>
+        <v>-0.0023536988624879</v>
       </c>
     </row>
     <row r="349">
@@ -20661,16 +20661,16 @@
         <v>6.915265</v>
       </c>
       <c r="M349" t="n">
-        <v>0.04690835197486382</v>
+        <v>0.0469083519748638</v>
       </c>
       <c r="N349" t="n">
         <v>0.0632024384829494</v>
       </c>
       <c r="O349" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.0462200021743774</v>
       </c>
       <c r="P349" t="n">
-        <v>0.01698243630857196</v>
+        <v>0.0169824363085719</v>
       </c>
     </row>
     <row r="350">
@@ -20722,13 +20722,13 @@
         <v>0.0430173605776617</v>
       </c>
       <c r="N350" t="n">
-        <v>0.04962047421518922</v>
+        <v>0.0496204742151892</v>
       </c>
       <c r="O350" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.0462200021743774</v>
       </c>
       <c r="P350" t="n">
-        <v>0.003400472040811779</v>
+        <v>0.0034004720408117</v>
       </c>
     </row>
     <row r="351">
@@ -20777,16 +20777,16 @@
         <v>6.338351</v>
       </c>
       <c r="M351" t="n">
-        <v>0.04318891756077686</v>
+        <v>0.0431889175607768</v>
       </c>
       <c r="N351" t="n">
-        <v>0.05184788808909412</v>
+        <v>0.0518478880890941</v>
       </c>
       <c r="O351" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.0462200021743774</v>
       </c>
       <c r="P351" t="n">
-        <v>0.005627885914716683</v>
+        <v>0.0056278859147166</v>
       </c>
     </row>
     <row r="352">
@@ -20835,16 +20835,534 @@
         <v>18.155405</v>
       </c>
       <c r="M352" t="n">
-        <v>0.03431398347455397</v>
+        <v>0.0343139834745539</v>
       </c>
       <c r="N352" t="n">
-        <v>0.06772817220146309</v>
+        <v>0.067728172201463</v>
       </c>
       <c r="O352" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.0462200021743774</v>
       </c>
       <c r="P352" t="n">
-        <v>0.02150817002708565</v>
+        <v>0.0215081700270856</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:30:11</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>333.43</v>
+      </c>
+      <c r="F353" t="n">
+        <v>4897204862976</v>
+      </c>
+      <c r="G353" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H353" t="n">
+        <v>9.65692</v>
+      </c>
+      <c r="I353" t="n">
+        <v>40.415756</v>
+      </c>
+      <c r="J353" t="n">
+        <v>34.52757</v>
+      </c>
+      <c r="K353" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L353" t="n">
+        <v>10.847916</v>
+      </c>
+      <c r="M353" t="n">
+        <v>0.02474282458087155</v>
+      </c>
+      <c r="N353" t="n">
+        <v>0.02896236091533455</v>
+      </c>
+      <c r="O353" t="n">
+        <v>0.04663000106811523</v>
+      </c>
+      <c r="P353" t="n">
+        <v>-0.01766764015278068</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:30:11</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>485.39</v>
+      </c>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="H354" t="n">
+        <v>13.8213</v>
+      </c>
+      <c r="I354" t="n">
+        <v>161.25914</v>
+      </c>
+      <c r="J354" t="n">
+        <v>35.118984</v>
+      </c>
+      <c r="K354" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L354" t="inlineStr"/>
+      <c r="M354" t="n">
+        <v>0.006201199035826861</v>
+      </c>
+      <c r="N354" t="n">
+        <v>0.02847462864912751</v>
+      </c>
+      <c r="O354" t="n">
+        <v>0.04663000106811523</v>
+      </c>
+      <c r="P354" t="n">
+        <v>-0.01815537241898773</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:30:11</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="F355" t="n">
+        <v>2533299322880</v>
+      </c>
+      <c r="G355" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="H355" t="n">
+        <v>9.931369999999999</v>
+      </c>
+      <c r="I355" t="n">
+        <v>28.169857</v>
+      </c>
+      <c r="J355" t="n">
+        <v>23.712742</v>
+      </c>
+      <c r="K355" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L355" t="n">
+        <v>3.4105833</v>
+      </c>
+      <c r="M355" t="n">
+        <v>0.03549893842887474</v>
+      </c>
+      <c r="N355" t="n">
+        <v>0.04217142250530785</v>
+      </c>
+      <c r="O355" t="n">
+        <v>0.04663000106811523</v>
+      </c>
+      <c r="P355" t="n">
+        <v>-0.004458578562807382</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:30:11</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>387.84</v>
+      </c>
+      <c r="F356" t="n">
+        <v>1845179973632</v>
+      </c>
+      <c r="G356" t="n">
+        <v>6</v>
+      </c>
+      <c r="H356" t="n">
+        <v>19.49196</v>
+      </c>
+      <c r="I356" t="n">
+        <v>64.64</v>
+      </c>
+      <c r="J356" t="n">
+        <v>19.897434</v>
+      </c>
+      <c r="K356" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L356" t="n">
+        <v>24.450806</v>
+      </c>
+      <c r="M356" t="n">
+        <v>0.01547029702970297</v>
+      </c>
+      <c r="N356" t="n">
+        <v>0.05025773514851485</v>
+      </c>
+      <c r="O356" t="n">
+        <v>0.04663000106811523</v>
+      </c>
+      <c r="P356" t="n">
+        <v>0.003627734080399618</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:30:11</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>333.68</v>
+      </c>
+      <c r="F357" t="n">
+        <v>4080884776960</v>
+      </c>
+      <c r="G357" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="H357" t="n">
+        <v>14.73443</v>
+      </c>
+      <c r="I357" t="n">
+        <v>16.734201</v>
+      </c>
+      <c r="J357" t="n">
+        <v>22.646276</v>
+      </c>
+      <c r="K357" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L357" t="n">
+        <v>9.152716</v>
+      </c>
+      <c r="M357" t="n">
+        <v>0.05975785183409255</v>
+      </c>
+      <c r="N357" t="n">
+        <v>0.04415736633900743</v>
+      </c>
+      <c r="O357" t="n">
+        <v>0.04663000106811523</v>
+      </c>
+      <c r="P357" t="n">
+        <v>-0.002472634729107803</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:30:11</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>539.03</v>
+      </c>
+      <c r="F358" t="n">
+        <v>1368286429184</v>
+      </c>
+      <c r="G358" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="H358" t="n">
+        <v>36.58071</v>
+      </c>
+      <c r="I358" t="n">
+        <v>20.317755</v>
+      </c>
+      <c r="J358" t="n">
+        <v>14.735362</v>
+      </c>
+      <c r="K358" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L358" t="n">
+        <v>6.3652186</v>
+      </c>
+      <c r="M358" t="n">
+        <v>0.04921803981225535</v>
+      </c>
+      <c r="N358" t="n">
+        <v>0.06786395933435987</v>
+      </c>
+      <c r="O358" t="n">
+        <v>0.04663000106811523</v>
+      </c>
+      <c r="P358" t="n">
+        <v>0.02123395826624464</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:30:11</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>451.1</v>
+      </c>
+      <c r="F359" t="n">
+        <v>3350967091200</v>
+      </c>
+      <c r="G359" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="H359" t="n">
+        <v>23.08484</v>
+      </c>
+      <c r="I359" t="n">
+        <v>25.116928</v>
+      </c>
+      <c r="J359" t="n">
+        <v>19.540962</v>
+      </c>
+      <c r="K359" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L359" t="n">
+        <v>10.528594</v>
+      </c>
+      <c r="M359" t="n">
+        <v>0.03981378851695855</v>
+      </c>
+      <c r="N359" t="n">
+        <v>0.05117455109731767</v>
+      </c>
+      <c r="O359" t="n">
+        <v>0.04663000106811523</v>
+      </c>
+      <c r="P359" t="n">
+        <v>0.004544550029202434</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:30:11</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>73.17</v>
+      </c>
+      <c r="F360" t="n">
+        <v>304675454976</v>
+      </c>
+      <c r="G360" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H360" t="n">
+        <v>3.81756</v>
+      </c>
+      <c r="I360" t="n">
+        <v>23.009434</v>
+      </c>
+      <c r="J360" t="n">
+        <v>19.166693</v>
+      </c>
+      <c r="K360" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L360" t="n">
+        <v>6.298752</v>
+      </c>
+      <c r="M360" t="n">
+        <v>0.04346043460434604</v>
+      </c>
+      <c r="N360" t="n">
+        <v>0.05217384173841738</v>
+      </c>
+      <c r="O360" t="n">
+        <v>0.04663000106811523</v>
+      </c>
+      <c r="P360" t="n">
+        <v>0.005543840670302148</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:30:11</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>195.04</v>
+      </c>
+      <c r="F361" t="n">
+        <v>4724063469568</v>
+      </c>
+      <c r="G361" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="H361" t="n">
+        <v>12.86903</v>
+      </c>
+      <c r="I361" t="n">
+        <v>29.82263</v>
+      </c>
+      <c r="J361" t="n">
+        <v>15.155765</v>
+      </c>
+      <c r="K361" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L361" t="n">
+        <v>18.63602</v>
+      </c>
+      <c r="M361" t="n">
+        <v>0.03353158326497129</v>
+      </c>
+      <c r="N361" t="n">
+        <v>0.06598149097621002</v>
+      </c>
+      <c r="O361" t="n">
+        <v>0.04663000106811523</v>
+      </c>
+      <c r="P361" t="n">
+        <v>0.01935148990809479</v>
       </c>
     </row>
   </sheetData>
@@ -20946,12 +21464,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29 16:28:02</t>
+          <t>2026-07-30 16:30:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -20965,51 +21483,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>335.76</v>
+        <v>333.68</v>
       </c>
       <c r="F2" t="n">
-        <v>4106323230720</v>
+        <v>4080884776960</v>
       </c>
       <c r="G2" t="n">
-        <v>19.92</v>
+        <v>19.94</v>
       </c>
       <c r="H2" t="n">
-        <v>14.72855</v>
+        <v>14.73443</v>
       </c>
       <c r="I2" t="n">
-        <v>16.855423</v>
+        <v>16.734201</v>
       </c>
       <c r="J2" t="n">
-        <v>22.796541</v>
+        <v>22.646276</v>
       </c>
       <c r="K2" t="n">
-        <v>1.27</v>
+        <v>0.91</v>
       </c>
       <c r="L2" t="n">
-        <v>9.209770000000001</v>
+        <v>9.152716</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05932809149392424</v>
+        <v>0.05975785183409255</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04386630331188945</v>
+        <v>0.04415736633900743</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.04663000106811523</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.002353698862487992</v>
+        <v>-0.002472634729107803</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:28:02</t>
+          <t>2026-07-30 16:30:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -21023,51 +21541,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>390.54</v>
+        <v>451.1</v>
       </c>
       <c r="F3" t="n">
-        <v>2901100986368</v>
+        <v>3350967091200</v>
       </c>
       <c r="G3" t="n">
-        <v>16.8</v>
+        <v>17.96</v>
       </c>
       <c r="H3" t="n">
-        <v>19.37878</v>
+        <v>23.08484</v>
       </c>
       <c r="I3" t="n">
-        <v>23.24643</v>
+        <v>25.116928</v>
       </c>
       <c r="J3" t="n">
-        <v>20.152971</v>
+        <v>19.540962</v>
       </c>
       <c r="K3" t="n">
         <v>1.21</v>
       </c>
       <c r="L3" t="n">
-        <v>9.115133999999999</v>
+        <v>10.528594</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0430173605776617</v>
+        <v>0.03981378851695855</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04962047421518922</v>
+        <v>0.05117455109731767</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.04663000106811523</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003400472040811779</v>
+        <v>0.004544550029202434</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-29 16:28:02</t>
+          <t>2026-07-30 16:30:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -21081,51 +21599,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>585.61</v>
+        <v>539.03</v>
       </c>
       <c r="F4" t="n">
-        <v>1486526087168</v>
+        <v>1368286429184</v>
       </c>
       <c r="G4" t="n">
-        <v>27.47</v>
+        <v>26.53</v>
       </c>
       <c r="H4" t="n">
-        <v>37.01198</v>
+        <v>36.58071</v>
       </c>
       <c r="I4" t="n">
-        <v>21.318165</v>
+        <v>20.317755</v>
       </c>
       <c r="J4" t="n">
-        <v>15.822175</v>
+        <v>14.735362</v>
       </c>
       <c r="K4" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="L4" t="n">
-        <v>6.915265</v>
+        <v>6.3652186</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04690835197486382</v>
+        <v>0.04921803981225535</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0632024384829494</v>
+        <v>0.06786395933435987</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.04663000106811523</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01698243630857196</v>
+        <v>0.02123395826624464</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-29 16:28:02</t>
+          <t>2026-07-30 16:30:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -21139,51 +21657,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>226.65</v>
+        <v>235.5</v>
       </c>
       <c r="F5" t="n">
-        <v>2438098845696</v>
+        <v>2533299322880</v>
       </c>
       <c r="G5" t="n">
         <v>8.359999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>9.920820000000001</v>
+        <v>9.931369999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>27.111244</v>
+        <v>28.169857</v>
       </c>
       <c r="J5" t="n">
-        <v>22.845892</v>
+        <v>23.712742</v>
       </c>
       <c r="K5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="L5" t="n">
-        <v>3.2824147</v>
+        <v>3.4105833</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03688506507831458</v>
+        <v>0.03549893842887474</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04377154202514891</v>
+        <v>0.04217142250530785</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.04663000106811523</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.002448460149228532</v>
+        <v>-0.004458578562807382</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-29 16:28:02</t>
+          <t>2026-07-30 16:30:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -21197,51 +21715,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>338.19</v>
+        <v>333.43</v>
       </c>
       <c r="F6" t="n">
-        <v>4967117094912</v>
+        <v>4897204862976</v>
       </c>
       <c r="G6" t="n">
-        <v>8.26</v>
+        <v>8.25</v>
       </c>
       <c r="H6" t="n">
         <v>9.65692</v>
       </c>
       <c r="I6" t="n">
-        <v>40.9431</v>
+        <v>40.415756</v>
       </c>
       <c r="J6" t="n">
-        <v>35.02048</v>
+        <v>34.52757</v>
       </c>
       <c r="K6" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="L6" t="n">
-        <v>11.00278</v>
+        <v>10.847916</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02442414027617611</v>
+        <v>0.02474282458087155</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02855471776220468</v>
+        <v>0.02896236091533455</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.04663000106811523</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01766528441217276</v>
+        <v>-0.01766764015278068</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-29 16:28:02</t>
+          <t>2026-07-30 16:30:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -21255,51 +21773,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>190.01</v>
+        <v>195.04</v>
       </c>
       <c r="F7" t="n">
-        <v>4602232045568</v>
+        <v>4724063469568</v>
       </c>
       <c r="G7" t="n">
-        <v>6.52</v>
+        <v>6.54</v>
       </c>
       <c r="H7" t="n">
         <v>12.86903</v>
       </c>
       <c r="I7" t="n">
-        <v>29.142637</v>
+        <v>29.82263</v>
       </c>
       <c r="J7" t="n">
-        <v>14.764904</v>
+        <v>15.155765</v>
       </c>
       <c r="K7" t="n">
         <v>0.54</v>
       </c>
       <c r="L7" t="n">
-        <v>18.155405</v>
+        <v>18.63602</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03431398347455397</v>
+        <v>0.03353158326497129</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06772817220146309</v>
+        <v>0.06598149097621002</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.04663000106811523</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02150817002708565</v>
+        <v>0.01935148990809479</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-29 16:28:02</t>
+          <t>2026-07-30 16:30:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -21313,47 +21831,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>429.56</v>
+        <v>485.39</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="H8" t="n">
-        <v>13.77774</v>
+        <v>13.8213</v>
       </c>
       <c r="I8" t="n">
-        <v>143.18666</v>
+        <v>161.25914</v>
       </c>
       <c r="J8" t="n">
-        <v>31.177828</v>
+        <v>35.118984</v>
       </c>
       <c r="K8" t="n">
         <v>1.16</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0.006983890492597076</v>
+        <v>0.006201199035826861</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03207407579849148</v>
+        <v>0.02847462864912751</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.04663000106811523</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01414592637588596</v>
+        <v>-0.01815537241898773</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-29 16:28:02</t>
+          <t>2026-07-30 16:30:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -21367,51 +21885,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>370.32</v>
+        <v>387.84</v>
       </c>
       <c r="F9" t="n">
-        <v>1761827225600</v>
+        <v>1845179973632</v>
       </c>
       <c r="G9" t="n">
-        <v>6.02</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>19.51378</v>
+        <v>19.49196</v>
       </c>
       <c r="I9" t="n">
-        <v>61.51495</v>
+        <v>64.64</v>
       </c>
       <c r="J9" t="n">
-        <v>18.977358</v>
+        <v>19.897434</v>
       </c>
       <c r="K9" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="L9" t="n">
-        <v>23.346283</v>
+        <v>24.450806</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01625621084467488</v>
+        <v>0.01547029702970297</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05269437243465112</v>
+        <v>0.05025773514851485</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.04663000106811523</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006474370260273678</v>
+        <v>0.003627734080399618</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-29 16:28:02</t>
+          <t>2026-07-30 16:30:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -21425,10 +21943,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73.63</v>
+        <v>73.17</v>
       </c>
       <c r="F10" t="n">
-        <v>306590875648</v>
+        <v>304675454976</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -21437,28 +21955,28 @@
         <v>3.81756</v>
       </c>
       <c r="I10" t="n">
-        <v>23.154087</v>
+        <v>23.009434</v>
       </c>
       <c r="J10" t="n">
-        <v>19.287188</v>
+        <v>19.166693</v>
       </c>
       <c r="K10" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="L10" t="n">
-        <v>6.338351</v>
+        <v>6.298752</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04318891756077686</v>
+        <v>0.04346043460434604</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05184788808909412</v>
+        <v>0.05217384173841738</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04622000217437744</v>
+        <v>0.04663000106811523</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005627885914716683</v>
+        <v>0.005543840670302148</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P361"/>
+  <dimension ref="A1:P370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20893,16 +20893,16 @@
         <v>10.847916</v>
       </c>
       <c r="M353" t="n">
-        <v>0.02474282458087155</v>
+        <v>0.0247428245808715</v>
       </c>
       <c r="N353" t="n">
-        <v>0.02896236091533455</v>
+        <v>0.0289623609153345</v>
       </c>
       <c r="O353" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.0466300010681152</v>
       </c>
       <c r="P353" t="n">
-        <v>-0.01766764015278068</v>
+        <v>-0.0176676401527806</v>
       </c>
     </row>
     <row r="354">
@@ -20947,16 +20947,16 @@
       </c>
       <c r="L354" t="inlineStr"/>
       <c r="M354" t="n">
-        <v>0.006201199035826861</v>
+        <v>0.0062011990358268</v>
       </c>
       <c r="N354" t="n">
-        <v>0.02847462864912751</v>
+        <v>0.0284746286491275</v>
       </c>
       <c r="O354" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.0466300010681152</v>
       </c>
       <c r="P354" t="n">
-        <v>-0.01815537241898773</v>
+        <v>-0.0181553724189877</v>
       </c>
     </row>
     <row r="355">
@@ -21005,16 +21005,16 @@
         <v>3.4105833</v>
       </c>
       <c r="M355" t="n">
-        <v>0.03549893842887474</v>
+        <v>0.0354989384288747</v>
       </c>
       <c r="N355" t="n">
-        <v>0.04217142250530785</v>
+        <v>0.0421714225053078</v>
       </c>
       <c r="O355" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.0466300010681152</v>
       </c>
       <c r="P355" t="n">
-        <v>-0.004458578562807382</v>
+        <v>-0.0044585785628073</v>
       </c>
     </row>
     <row r="356">
@@ -21063,16 +21063,16 @@
         <v>24.450806</v>
       </c>
       <c r="M356" t="n">
-        <v>0.01547029702970297</v>
+        <v>0.0154702970297029</v>
       </c>
       <c r="N356" t="n">
-        <v>0.05025773514851485</v>
+        <v>0.0502577351485148</v>
       </c>
       <c r="O356" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.0466300010681152</v>
       </c>
       <c r="P356" t="n">
-        <v>0.003627734080399618</v>
+        <v>0.0036277340803996</v>
       </c>
     </row>
     <row r="357">
@@ -21121,16 +21121,16 @@
         <v>9.152716</v>
       </c>
       <c r="M357" t="n">
-        <v>0.05975785183409255</v>
+        <v>0.0597578518340925</v>
       </c>
       <c r="N357" t="n">
-        <v>0.04415736633900743</v>
+        <v>0.0441573663390074</v>
       </c>
       <c r="O357" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.0466300010681152</v>
       </c>
       <c r="P357" t="n">
-        <v>-0.002472634729107803</v>
+        <v>-0.0024726347291078</v>
       </c>
     </row>
     <row r="358">
@@ -21179,16 +21179,16 @@
         <v>6.3652186</v>
       </c>
       <c r="M358" t="n">
-        <v>0.04921803981225535</v>
+        <v>0.0492180398122553</v>
       </c>
       <c r="N358" t="n">
-        <v>0.06786395933435987</v>
+        <v>0.06786395933435981</v>
       </c>
       <c r="O358" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.0466300010681152</v>
       </c>
       <c r="P358" t="n">
-        <v>0.02123395826624464</v>
+        <v>0.0212339582662446</v>
       </c>
     </row>
     <row r="359">
@@ -21237,16 +21237,16 @@
         <v>10.528594</v>
       </c>
       <c r="M359" t="n">
-        <v>0.03981378851695855</v>
+        <v>0.0398137885169585</v>
       </c>
       <c r="N359" t="n">
-        <v>0.05117455109731767</v>
+        <v>0.0511745510973176</v>
       </c>
       <c r="O359" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.0466300010681152</v>
       </c>
       <c r="P359" t="n">
-        <v>0.004544550029202434</v>
+        <v>0.0045445500292024</v>
       </c>
     </row>
     <row r="360">
@@ -21295,16 +21295,16 @@
         <v>6.298752</v>
       </c>
       <c r="M360" t="n">
-        <v>0.04346043460434604</v>
+        <v>0.043460434604346</v>
       </c>
       <c r="N360" t="n">
-        <v>0.05217384173841738</v>
+        <v>0.0521738417384173</v>
       </c>
       <c r="O360" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.0466300010681152</v>
       </c>
       <c r="P360" t="n">
-        <v>0.005543840670302148</v>
+        <v>0.0055438406703021</v>
       </c>
     </row>
     <row r="361">
@@ -21353,16 +21353,538 @@
         <v>18.63602</v>
       </c>
       <c r="M361" t="n">
-        <v>0.03353158326497129</v>
+        <v>0.0335315832649712</v>
       </c>
       <c r="N361" t="n">
-        <v>0.06598149097621002</v>
+        <v>0.06598149097621001</v>
       </c>
       <c r="O361" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.0466300010681152</v>
       </c>
       <c r="P361" t="n">
-        <v>0.01935148990809479</v>
+        <v>0.0193514899080947</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:27:56</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>308.91</v>
+      </c>
+      <c r="F362" t="n">
+        <v>4537070911488</v>
+      </c>
+      <c r="G362" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="H362" t="n">
+        <v>9.57062</v>
+      </c>
+      <c r="I362" t="n">
+        <v>35.344395</v>
+      </c>
+      <c r="J362" t="n">
+        <v>32.27691</v>
+      </c>
+      <c r="K362" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L362" t="n">
+        <v>9.719039</v>
+      </c>
+      <c r="M362" t="n">
+        <v>0.02829303033245929</v>
+      </c>
+      <c r="N362" t="n">
+        <v>0.03098190411446699</v>
+      </c>
+      <c r="O362" t="n">
+        <v>0.04744999885559082</v>
+      </c>
+      <c r="P362" t="n">
+        <v>-0.01646809474112383</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:27:56</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>476.15</v>
+      </c>
+      <c r="F363" t="n">
+        <v>776410431488</v>
+      </c>
+      <c r="G363" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="H363" t="n">
+        <v>13.8213</v>
+      </c>
+      <c r="I363" t="n">
+        <v>158.18936</v>
+      </c>
+      <c r="J363" t="n">
+        <v>34.45045</v>
+      </c>
+      <c r="K363" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L363" t="n">
+        <v>20.729706</v>
+      </c>
+      <c r="M363" t="n">
+        <v>0.006321537330673107</v>
+      </c>
+      <c r="N363" t="n">
+        <v>0.0290271973117715</v>
+      </c>
+      <c r="O363" t="n">
+        <v>0.04744999885559082</v>
+      </c>
+      <c r="P363" t="n">
+        <v>-0.01842280154381932</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:27:56</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>271.58</v>
+      </c>
+      <c r="F364" t="n">
+        <v>2921415835648</v>
+      </c>
+      <c r="G364" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H364" t="n">
+        <v>10.15873</v>
+      </c>
+      <c r="I364" t="n">
+        <v>21.848751</v>
+      </c>
+      <c r="J364" t="n">
+        <v>26.733656</v>
+      </c>
+      <c r="K364" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L364" t="n">
+        <v>3.766264</v>
+      </c>
+      <c r="M364" t="n">
+        <v>0.04576920244495176</v>
+      </c>
+      <c r="N364" t="n">
+        <v>0.03740603137197143</v>
+      </c>
+      <c r="O364" t="n">
+        <v>0.04744999885559082</v>
+      </c>
+      <c r="P364" t="n">
+        <v>-0.01004396748361939</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:27:56</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>389.28</v>
+      </c>
+      <c r="F365" t="n">
+        <v>1852030844928</v>
+      </c>
+      <c r="G365" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H365" t="n">
+        <v>19.49196</v>
+      </c>
+      <c r="I365" t="n">
+        <v>64.77204</v>
+      </c>
+      <c r="J365" t="n">
+        <v>19.971312</v>
+      </c>
+      <c r="K365" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L365" t="n">
+        <v>24.541588</v>
+      </c>
+      <c r="M365" t="n">
+        <v>0.01543875873407316</v>
+      </c>
+      <c r="N365" t="n">
+        <v>0.05007182490752158</v>
+      </c>
+      <c r="O365" t="n">
+        <v>0.04744999885559082</v>
+      </c>
+      <c r="P365" t="n">
+        <v>0.002621826051930759</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:27:56</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>356.65</v>
+      </c>
+      <c r="F366" t="n">
+        <v>4361806151680</v>
+      </c>
+      <c r="G366" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H366" t="n">
+        <v>14.73443</v>
+      </c>
+      <c r="I366" t="n">
+        <v>17.904116</v>
+      </c>
+      <c r="J366" t="n">
+        <v>24.205212</v>
+      </c>
+      <c r="K366" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L366" t="n">
+        <v>9.782774</v>
+      </c>
+      <c r="M366" t="n">
+        <v>0.05585307724660032</v>
+      </c>
+      <c r="N366" t="n">
+        <v>0.04131341651479041</v>
+      </c>
+      <c r="O366" t="n">
+        <v>0.04744999885559082</v>
+      </c>
+      <c r="P366" t="n">
+        <v>-0.00613658234080041</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:27:56</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>556.71</v>
+      </c>
+      <c r="F367" t="n">
+        <v>1418222239744</v>
+      </c>
+      <c r="G367" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="H367" t="n">
+        <v>35.558</v>
+      </c>
+      <c r="I367" t="n">
+        <v>20.95258</v>
+      </c>
+      <c r="J367" t="n">
+        <v>15.656394</v>
+      </c>
+      <c r="K367" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L367" t="n">
+        <v>6.213542</v>
+      </c>
+      <c r="M367" t="n">
+        <v>0.04772682366043362</v>
+      </c>
+      <c r="N367" t="n">
+        <v>0.0638716746600564</v>
+      </c>
+      <c r="O367" t="n">
+        <v>0.04744999885559082</v>
+      </c>
+      <c r="P367" t="n">
+        <v>0.01642167580446558</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:27:56</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>464.72</v>
+      </c>
+      <c r="F368" t="n">
+        <v>3450799652864</v>
+      </c>
+      <c r="G368" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H368" t="n">
+        <v>23.27714</v>
+      </c>
+      <c r="I368" t="n">
+        <v>25.889692</v>
+      </c>
+      <c r="J368" t="n">
+        <v>19.964653</v>
+      </c>
+      <c r="K368" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L368" t="n">
+        <v>10.399017</v>
+      </c>
+      <c r="M368" t="n">
+        <v>0.03862540884833878</v>
+      </c>
+      <c r="N368" t="n">
+        <v>0.05008852642451368</v>
+      </c>
+      <c r="O368" t="n">
+        <v>0.04744999885559082</v>
+      </c>
+      <c r="P368" t="n">
+        <v>0.002638527568922862</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:27:56</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>71.70999999999999</v>
+      </c>
+      <c r="F369" t="n">
+        <v>298596106240</v>
+      </c>
+      <c r="G369" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H369" t="n">
+        <v>3.81756</v>
+      </c>
+      <c r="I369" t="n">
+        <v>22.550314</v>
+      </c>
+      <c r="J369" t="n">
+        <v>18.78425</v>
+      </c>
+      <c r="K369" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L369" t="n">
+        <v>6.1730695</v>
+      </c>
+      <c r="M369" t="n">
+        <v>0.04434527959838238</v>
+      </c>
+      <c r="N369" t="n">
+        <v>0.05323608980616372</v>
+      </c>
+      <c r="O369" t="n">
+        <v>0.04744999885559082</v>
+      </c>
+      <c r="P369" t="n">
+        <v>0.005786090950572899</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:27:56</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>200.75</v>
+      </c>
+      <c r="F370" t="n">
+        <v>4862365925376</v>
+      </c>
+      <c r="G370" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H370" t="n">
+        <v>12.86903</v>
+      </c>
+      <c r="I370" t="n">
+        <v>30.742725</v>
+      </c>
+      <c r="J370" t="n">
+        <v>15.599466</v>
+      </c>
+      <c r="K370" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L370" t="n">
+        <v>19.181612</v>
+      </c>
+      <c r="M370" t="n">
+        <v>0.0325280199252802</v>
+      </c>
+      <c r="N370" t="n">
+        <v>0.06410475716064758</v>
+      </c>
+      <c r="O370" t="n">
+        <v>0.04744999885559082</v>
+      </c>
+      <c r="P370" t="n">
+        <v>0.01665475830505676</v>
       </c>
     </row>
   </sheetData>
@@ -21464,12 +21986,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-30 16:30:11</t>
+          <t>2026-07-31 16:27:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -21483,51 +22005,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>333.68</v>
+        <v>356.65</v>
       </c>
       <c r="F2" t="n">
-        <v>4080884776960</v>
+        <v>4361806151680</v>
       </c>
       <c r="G2" t="n">
-        <v>19.94</v>
+        <v>19.92</v>
       </c>
       <c r="H2" t="n">
         <v>14.73443</v>
       </c>
       <c r="I2" t="n">
-        <v>16.734201</v>
+        <v>17.904116</v>
       </c>
       <c r="J2" t="n">
-        <v>22.646276</v>
+        <v>24.205212</v>
       </c>
       <c r="K2" t="n">
         <v>0.91</v>
       </c>
       <c r="L2" t="n">
-        <v>9.152716</v>
+        <v>9.782774</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05975785183409255</v>
+        <v>0.05585307724660032</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04415736633900743</v>
+        <v>0.04131341651479041</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.04744999885559082</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.002472634729107803</v>
+        <v>-0.00613658234080041</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-30 16:30:11</t>
+          <t>2026-07-31 16:27:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -21541,51 +22063,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>451.1</v>
+        <v>464.72</v>
       </c>
       <c r="F3" t="n">
-        <v>3350967091200</v>
+        <v>3450799652864</v>
       </c>
       <c r="G3" t="n">
-        <v>17.96</v>
+        <v>17.95</v>
       </c>
       <c r="H3" t="n">
-        <v>23.08484</v>
+        <v>23.27714</v>
       </c>
       <c r="I3" t="n">
-        <v>25.116928</v>
+        <v>25.889692</v>
       </c>
       <c r="J3" t="n">
-        <v>19.540962</v>
+        <v>19.964653</v>
       </c>
       <c r="K3" t="n">
         <v>1.21</v>
       </c>
       <c r="L3" t="n">
-        <v>10.528594</v>
+        <v>10.399017</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03981378851695855</v>
+        <v>0.03862540884833878</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05117455109731767</v>
+        <v>0.05008852642451368</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.04744999885559082</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004544550029202434</v>
+        <v>0.002638527568922862</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-30 16:30:11</t>
+          <t>2026-07-31 16:27:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -21599,51 +22121,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>539.03</v>
+        <v>556.71</v>
       </c>
       <c r="F4" t="n">
-        <v>1368286429184</v>
+        <v>1418222239744</v>
       </c>
       <c r="G4" t="n">
-        <v>26.53</v>
+        <v>26.57</v>
       </c>
       <c r="H4" t="n">
-        <v>36.58071</v>
+        <v>35.558</v>
       </c>
       <c r="I4" t="n">
-        <v>20.317755</v>
+        <v>20.95258</v>
       </c>
       <c r="J4" t="n">
-        <v>14.735362</v>
+        <v>15.656394</v>
       </c>
       <c r="K4" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="L4" t="n">
-        <v>6.3652186</v>
+        <v>6.213542</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04921803981225535</v>
+        <v>0.04772682366043362</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06786395933435987</v>
+        <v>0.0638716746600564</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.04744999885559082</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02123395826624464</v>
+        <v>0.01642167580446558</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-30 16:30:11</t>
+          <t>2026-07-31 16:27:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -21657,51 +22179,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>235.5</v>
+        <v>271.58</v>
       </c>
       <c r="F5" t="n">
-        <v>2533299322880</v>
+        <v>2921415835648</v>
       </c>
       <c r="G5" t="n">
-        <v>8.359999999999999</v>
+        <v>12.43</v>
       </c>
       <c r="H5" t="n">
-        <v>9.931369999999999</v>
+        <v>10.15873</v>
       </c>
       <c r="I5" t="n">
-        <v>28.169857</v>
+        <v>21.848751</v>
       </c>
       <c r="J5" t="n">
-        <v>23.712742</v>
+        <v>26.733656</v>
       </c>
       <c r="K5" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4105833</v>
+        <v>3.766264</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03549893842887474</v>
+        <v>0.04576920244495176</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04217142250530785</v>
+        <v>0.03740603137197143</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.04744999885559082</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.004458578562807382</v>
+        <v>-0.01004396748361939</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-30 16:30:11</t>
+          <t>2026-07-31 16:27:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -21715,51 +22237,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>333.43</v>
+        <v>308.91</v>
       </c>
       <c r="F6" t="n">
-        <v>4897204862976</v>
+        <v>4537070911488</v>
       </c>
       <c r="G6" t="n">
-        <v>8.25</v>
+        <v>8.74</v>
       </c>
       <c r="H6" t="n">
-        <v>9.65692</v>
+        <v>9.57062</v>
       </c>
       <c r="I6" t="n">
-        <v>40.415756</v>
+        <v>35.344395</v>
       </c>
       <c r="J6" t="n">
-        <v>34.52757</v>
+        <v>32.27691</v>
       </c>
       <c r="K6" t="n">
         <v>2.72</v>
       </c>
       <c r="L6" t="n">
-        <v>10.847916</v>
+        <v>9.719039</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02474282458087155</v>
+        <v>0.02829303033245929</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02896236091533455</v>
+        <v>0.03098190411446699</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.04744999885559082</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01766764015278068</v>
+        <v>-0.01646809474112383</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-30 16:30:11</t>
+          <t>2026-07-31 16:27:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -21773,51 +22295,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>195.04</v>
+        <v>200.75</v>
       </c>
       <c r="F7" t="n">
-        <v>4724063469568</v>
+        <v>4862365925376</v>
       </c>
       <c r="G7" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
       <c r="H7" t="n">
         <v>12.86903</v>
       </c>
       <c r="I7" t="n">
-        <v>29.82263</v>
+        <v>30.742725</v>
       </c>
       <c r="J7" t="n">
-        <v>15.155765</v>
+        <v>15.599466</v>
       </c>
       <c r="K7" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="L7" t="n">
-        <v>18.63602</v>
+        <v>19.181612</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03353158326497129</v>
+        <v>0.0325280199252802</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06598149097621002</v>
+        <v>0.06410475716064758</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.04744999885559082</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01935148990809479</v>
+        <v>0.01665475830505676</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-30 16:30:11</t>
+          <t>2026-07-31 16:27:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -21831,9 +22353,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>485.39</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>476.15</v>
+      </c>
+      <c r="F8" t="n">
+        <v>776410431488</v>
+      </c>
       <c r="G8" t="n">
         <v>3.01</v>
       </c>
@@ -21841,37 +22365,39 @@
         <v>13.8213</v>
       </c>
       <c r="I8" t="n">
-        <v>161.25914</v>
+        <v>158.18936</v>
       </c>
       <c r="J8" t="n">
-        <v>35.118984</v>
+        <v>34.45045</v>
       </c>
       <c r="K8" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>1.01</v>
+      </c>
+      <c r="L8" t="n">
+        <v>20.729706</v>
+      </c>
       <c r="M8" t="n">
-        <v>0.006201199035826861</v>
+        <v>0.006321537330673107</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02847462864912751</v>
+        <v>0.0290271973117715</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.04744999885559082</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01815537241898773</v>
+        <v>-0.01842280154381932</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-30 16:30:11</t>
+          <t>2026-07-31 16:27:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -21885,51 +22411,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>387.84</v>
+        <v>389.28</v>
       </c>
       <c r="F9" t="n">
-        <v>1845179973632</v>
+        <v>1852030844928</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>6.01</v>
       </c>
       <c r="H9" t="n">
         <v>19.49196</v>
       </c>
       <c r="I9" t="n">
-        <v>64.64</v>
+        <v>64.77204</v>
       </c>
       <c r="J9" t="n">
-        <v>19.897434</v>
+        <v>19.971312</v>
       </c>
       <c r="K9" t="n">
         <v>0.42</v>
       </c>
       <c r="L9" t="n">
-        <v>24.450806</v>
+        <v>24.541588</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01547029702970297</v>
+        <v>0.01543875873407316</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05025773514851485</v>
+        <v>0.05007182490752158</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.04744999885559082</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003627734080399618</v>
+        <v>0.002621826051930759</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-30 16:30:11</t>
+          <t>2026-07-31 16:27:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -21943,10 +22469,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73.17</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>304675454976</v>
+        <v>298596106240</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -21955,28 +22481,28 @@
         <v>3.81756</v>
       </c>
       <c r="I10" t="n">
-        <v>23.009434</v>
+        <v>22.550314</v>
       </c>
       <c r="J10" t="n">
-        <v>19.166693</v>
+        <v>18.78425</v>
       </c>
       <c r="K10" t="n">
         <v>1.65</v>
       </c>
       <c r="L10" t="n">
-        <v>6.298752</v>
+        <v>6.1730695</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04346043460434604</v>
+        <v>0.04434527959838238</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05217384173841738</v>
+        <v>0.05323608980616372</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04663000106811523</v>
+        <v>0.04744999885559082</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005543840670302148</v>
+        <v>0.005786090950572899</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P370"/>
+  <dimension ref="A1:P379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21411,16 +21411,16 @@
         <v>9.719039</v>
       </c>
       <c r="M362" t="n">
-        <v>0.02829303033245929</v>
+        <v>0.0282930303324592</v>
       </c>
       <c r="N362" t="n">
-        <v>0.03098190411446699</v>
+        <v>0.0309819041144669</v>
       </c>
       <c r="O362" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.0474499988555908</v>
       </c>
       <c r="P362" t="n">
-        <v>-0.01646809474112383</v>
+        <v>-0.0164680947411238</v>
       </c>
     </row>
     <row r="363">
@@ -21469,16 +21469,16 @@
         <v>20.729706</v>
       </c>
       <c r="M363" t="n">
-        <v>0.006321537330673107</v>
+        <v>0.0063215373306731</v>
       </c>
       <c r="N363" t="n">
         <v>0.0290271973117715</v>
       </c>
       <c r="O363" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.0474499988555908</v>
       </c>
       <c r="P363" t="n">
-        <v>-0.01842280154381932</v>
+        <v>-0.0184228015438193</v>
       </c>
     </row>
     <row r="364">
@@ -21527,16 +21527,16 @@
         <v>3.766264</v>
       </c>
       <c r="M364" t="n">
-        <v>0.04576920244495176</v>
+        <v>0.0457692024449517</v>
       </c>
       <c r="N364" t="n">
-        <v>0.03740603137197143</v>
+        <v>0.0374060313719714</v>
       </c>
       <c r="O364" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.0474499988555908</v>
       </c>
       <c r="P364" t="n">
-        <v>-0.01004396748361939</v>
+        <v>-0.0100439674836193</v>
       </c>
     </row>
     <row r="365">
@@ -21585,16 +21585,16 @@
         <v>24.541588</v>
       </c>
       <c r="M365" t="n">
-        <v>0.01543875873407316</v>
+        <v>0.0154387587340731</v>
       </c>
       <c r="N365" t="n">
-        <v>0.05007182490752158</v>
+        <v>0.0500718249075215</v>
       </c>
       <c r="O365" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.0474499988555908</v>
       </c>
       <c r="P365" t="n">
-        <v>0.002621826051930759</v>
+        <v>0.0026218260519307</v>
       </c>
     </row>
     <row r="366">
@@ -21643,16 +21643,16 @@
         <v>9.782774</v>
       </c>
       <c r="M366" t="n">
-        <v>0.05585307724660032</v>
+        <v>0.0558530772466003</v>
       </c>
       <c r="N366" t="n">
-        <v>0.04131341651479041</v>
+        <v>0.0413134165147904</v>
       </c>
       <c r="O366" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.0474499988555908</v>
       </c>
       <c r="P366" t="n">
-        <v>-0.00613658234080041</v>
+        <v>-0.0061365823408004</v>
       </c>
     </row>
     <row r="367">
@@ -21701,16 +21701,16 @@
         <v>6.213542</v>
       </c>
       <c r="M367" t="n">
-        <v>0.04772682366043362</v>
+        <v>0.0477268236604336</v>
       </c>
       <c r="N367" t="n">
         <v>0.0638716746600564</v>
       </c>
       <c r="O367" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.0474499988555908</v>
       </c>
       <c r="P367" t="n">
-        <v>0.01642167580446558</v>
+        <v>0.0164216758044655</v>
       </c>
     </row>
     <row r="368">
@@ -21759,16 +21759,16 @@
         <v>10.399017</v>
       </c>
       <c r="M368" t="n">
-        <v>0.03862540884833878</v>
+        <v>0.0386254088483387</v>
       </c>
       <c r="N368" t="n">
-        <v>0.05008852642451368</v>
+        <v>0.0500885264245136</v>
       </c>
       <c r="O368" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.0474499988555908</v>
       </c>
       <c r="P368" t="n">
-        <v>0.002638527568922862</v>
+        <v>0.0026385275689228</v>
       </c>
     </row>
     <row r="369">
@@ -21817,16 +21817,16 @@
         <v>6.1730695</v>
       </c>
       <c r="M369" t="n">
-        <v>0.04434527959838238</v>
+        <v>0.0443452795983823</v>
       </c>
       <c r="N369" t="n">
-        <v>0.05323608980616372</v>
+        <v>0.0532360898061637</v>
       </c>
       <c r="O369" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.0474499988555908</v>
       </c>
       <c r="P369" t="n">
-        <v>0.005786090950572899</v>
+        <v>0.0057860909505728</v>
       </c>
     </row>
     <row r="370">
@@ -21878,13 +21878,531 @@
         <v>0.0325280199252802</v>
       </c>
       <c r="N370" t="n">
-        <v>0.06410475716064758</v>
+        <v>0.06410475716064749</v>
       </c>
       <c r="O370" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.0474499988555908</v>
       </c>
       <c r="P370" t="n">
-        <v>0.01665475830505676</v>
+        <v>0.0166547583050567</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:32:28</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>303.42</v>
+      </c>
+      <c r="F371" t="n">
+        <v>4456437514240</v>
+      </c>
+      <c r="G371" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H371" t="n">
+        <v>9.513070000000001</v>
+      </c>
+      <c r="I371" t="n">
+        <v>34.835823</v>
+      </c>
+      <c r="J371" t="n">
+        <v>31.895067</v>
+      </c>
+      <c r="K371" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="L371" t="n">
+        <v>9.546310999999999</v>
+      </c>
+      <c r="M371" t="n">
+        <v>0.02870608397600686</v>
+      </c>
+      <c r="N371" t="n">
+        <v>0.03135281128468789</v>
+      </c>
+      <c r="O371" t="n">
+        <v>0.04685999870300293</v>
+      </c>
+      <c r="P371" t="n">
+        <v>-0.01550718741831503</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:32:28</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>484.64</v>
+      </c>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="n">
+        <v>3</v>
+      </c>
+      <c r="H372" t="n">
+        <v>13.91754</v>
+      </c>
+      <c r="I372" t="n">
+        <v>161.54668</v>
+      </c>
+      <c r="J372" t="n">
+        <v>34.822247</v>
+      </c>
+      <c r="K372" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L372" t="inlineStr"/>
+      <c r="M372" t="n">
+        <v>0.006190161769560911</v>
+      </c>
+      <c r="N372" t="n">
+        <v>0.02871727467811159</v>
+      </c>
+      <c r="O372" t="n">
+        <v>0.04685999870300293</v>
+      </c>
+      <c r="P372" t="n">
+        <v>-0.01814272402489134</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:32:28</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>284.02</v>
+      </c>
+      <c r="F373" t="n">
+        <v>3055234318336</v>
+      </c>
+      <c r="G373" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="H373" t="n">
+        <v>10.31743</v>
+      </c>
+      <c r="I373" t="n">
+        <v>22.83119</v>
+      </c>
+      <c r="J373" t="n">
+        <v>27.528173</v>
+      </c>
+      <c r="K373" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L373" t="n">
+        <v>3.9387817</v>
+      </c>
+      <c r="M373" t="n">
+        <v>0.04379973241321033</v>
+      </c>
+      <c r="N373" t="n">
+        <v>0.03632642067460038</v>
+      </c>
+      <c r="O373" t="n">
+        <v>0.04685999870300293</v>
+      </c>
+      <c r="P373" t="n">
+        <v>-0.01053357802840255</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:32:28</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>392.23</v>
+      </c>
+      <c r="F374" t="n">
+        <v>1866065772544</v>
+      </c>
+      <c r="G374" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="H374" t="n">
+        <v>19.49196</v>
+      </c>
+      <c r="I374" t="n">
+        <v>65.48080400000001</v>
+      </c>
+      <c r="J374" t="n">
+        <v>20.122656</v>
+      </c>
+      <c r="K374" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L374" t="n">
+        <v>24.727566</v>
+      </c>
+      <c r="M374" t="n">
+        <v>0.01527165183693241</v>
+      </c>
+      <c r="N374" t="n">
+        <v>0.0496952298396349</v>
+      </c>
+      <c r="O374" t="n">
+        <v>0.04685999870300293</v>
+      </c>
+      <c r="P374" t="n">
+        <v>0.002835231136631977</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:32:28</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>372.47</v>
+      </c>
+      <c r="F375" t="n">
+        <v>4555284152320</v>
+      </c>
+      <c r="G375" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="H375" t="n">
+        <v>14.73443</v>
+      </c>
+      <c r="I375" t="n">
+        <v>18.679539</v>
+      </c>
+      <c r="J375" t="n">
+        <v>25.278887</v>
+      </c>
+      <c r="K375" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L375" t="n">
+        <v>10.216712</v>
+      </c>
+      <c r="M375" t="n">
+        <v>0.05353451284667222</v>
+      </c>
+      <c r="N375" t="n">
+        <v>0.03955870271431256</v>
+      </c>
+      <c r="O375" t="n">
+        <v>0.04685999870300293</v>
+      </c>
+      <c r="P375" t="n">
+        <v>-0.007301295988690365</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:32:28</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>590.24</v>
+      </c>
+      <c r="F376" t="n">
+        <v>1503640027136</v>
+      </c>
+      <c r="G376" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="H376" t="n">
+        <v>34.89882</v>
+      </c>
+      <c r="I376" t="n">
+        <v>22.22289</v>
+      </c>
+      <c r="J376" t="n">
+        <v>16.912893</v>
+      </c>
+      <c r="K376" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L376" t="n">
+        <v>6.5877757</v>
+      </c>
+      <c r="M376" t="n">
+        <v>0.04499864461913797</v>
+      </c>
+      <c r="N376" t="n">
+        <v>0.05912649091894823</v>
+      </c>
+      <c r="O376" t="n">
+        <v>0.04685999870300293</v>
+      </c>
+      <c r="P376" t="n">
+        <v>0.0122664922159453</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:32:28</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>487.65</v>
+      </c>
+      <c r="F377" t="n">
+        <v>3621067423744</v>
+      </c>
+      <c r="G377" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H377" t="n">
+        <v>23.46875</v>
+      </c>
+      <c r="I377" t="n">
+        <v>27.182274</v>
+      </c>
+      <c r="J377" t="n">
+        <v>20.778694</v>
+      </c>
+      <c r="K377" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L377" t="n">
+        <v>10.912121</v>
+      </c>
+      <c r="M377" t="n">
+        <v>0.03678868040602892</v>
+      </c>
+      <c r="N377" t="n">
+        <v>0.04812621757407978</v>
+      </c>
+      <c r="O377" t="n">
+        <v>0.04685999870300293</v>
+      </c>
+      <c r="P377" t="n">
+        <v>0.001266218871076849</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:32:28</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="F378" t="n">
+        <v>305341693952</v>
+      </c>
+      <c r="G378" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H378" t="n">
+        <v>3.81756</v>
+      </c>
+      <c r="I378" t="n">
+        <v>23.059748</v>
+      </c>
+      <c r="J378" t="n">
+        <v>19.208605</v>
+      </c>
+      <c r="K378" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L378" t="n">
+        <v>6.3125257</v>
+      </c>
+      <c r="M378" t="n">
+        <v>0.0433656075276149</v>
+      </c>
+      <c r="N378" t="n">
+        <v>0.0520600027273967</v>
+      </c>
+      <c r="O378" t="n">
+        <v>0.04685999870300293</v>
+      </c>
+      <c r="P378" t="n">
+        <v>0.005200004024393773</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:32:28</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>206.64</v>
+      </c>
+      <c r="F379" t="n">
+        <v>5005027311616</v>
+      </c>
+      <c r="G379" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="H379" t="n">
+        <v>12.89043</v>
+      </c>
+      <c r="I379" t="n">
+        <v>31.69325</v>
+      </c>
+      <c r="J379" t="n">
+        <v>16.030497</v>
+      </c>
+      <c r="K379" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L379" t="n">
+        <v>19.744398</v>
+      </c>
+      <c r="M379" t="n">
+        <v>0.03155245838172668</v>
+      </c>
+      <c r="N379" t="n">
+        <v>0.06238109756097562</v>
+      </c>
+      <c r="O379" t="n">
+        <v>0.04685999870300293</v>
+      </c>
+      <c r="P379" t="n">
+        <v>0.01552109885797269</v>
       </c>
     </row>
   </sheetData>
@@ -21986,12 +22504,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 16:27:56</t>
+          <t>2026-08-03 16:32:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -22005,51 +22523,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>356.65</v>
+        <v>372.47</v>
       </c>
       <c r="F2" t="n">
-        <v>4361806151680</v>
+        <v>4555284152320</v>
       </c>
       <c r="G2" t="n">
-        <v>19.92</v>
+        <v>19.94</v>
       </c>
       <c r="H2" t="n">
         <v>14.73443</v>
       </c>
       <c r="I2" t="n">
-        <v>17.904116</v>
+        <v>18.679539</v>
       </c>
       <c r="J2" t="n">
-        <v>24.205212</v>
+        <v>25.278887</v>
       </c>
       <c r="K2" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="L2" t="n">
-        <v>9.782774</v>
+        <v>10.216712</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05585307724660032</v>
+        <v>0.05353451284667222</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04131341651479041</v>
+        <v>0.03955870271431256</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.04685999870300293</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.00613658234080041</v>
+        <v>-0.007301295988690365</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-31 16:27:56</t>
+          <t>2026-08-03 16:32:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -22063,51 +22581,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>464.72</v>
+        <v>487.65</v>
       </c>
       <c r="F3" t="n">
-        <v>3450799652864</v>
+        <v>3621067423744</v>
       </c>
       <c r="G3" t="n">
-        <v>17.95</v>
+        <v>17.94</v>
       </c>
       <c r="H3" t="n">
-        <v>23.27714</v>
+        <v>23.46875</v>
       </c>
       <c r="I3" t="n">
-        <v>25.889692</v>
+        <v>27.182274</v>
       </c>
       <c r="J3" t="n">
-        <v>19.964653</v>
+        <v>20.778694</v>
       </c>
       <c r="K3" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="L3" t="n">
-        <v>10.399017</v>
+        <v>10.912121</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03862540884833878</v>
+        <v>0.03678868040602892</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05008852642451368</v>
+        <v>0.04812621757407978</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.04685999870300293</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002638527568922862</v>
+        <v>0.001266218871076849</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-31 16:27:56</t>
+          <t>2026-08-03 16:32:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -22121,51 +22639,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>556.71</v>
+        <v>590.24</v>
       </c>
       <c r="F4" t="n">
-        <v>1418222239744</v>
+        <v>1503640027136</v>
       </c>
       <c r="G4" t="n">
-        <v>26.57</v>
+        <v>26.56</v>
       </c>
       <c r="H4" t="n">
-        <v>35.558</v>
+        <v>34.89882</v>
       </c>
       <c r="I4" t="n">
-        <v>20.95258</v>
+        <v>22.22289</v>
       </c>
       <c r="J4" t="n">
-        <v>15.656394</v>
+        <v>16.912893</v>
       </c>
       <c r="K4" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="L4" t="n">
-        <v>6.213542</v>
+        <v>6.5877757</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04772682366043362</v>
+        <v>0.04499864461913797</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0638716746600564</v>
+        <v>0.05912649091894823</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.04685999870300293</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01642167580446558</v>
+        <v>0.0122664922159453</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-31 16:27:56</t>
+          <t>2026-08-03 16:32:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -22179,51 +22697,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>271.58</v>
+        <v>284.02</v>
       </c>
       <c r="F5" t="n">
-        <v>2921415835648</v>
+        <v>3055234318336</v>
       </c>
       <c r="G5" t="n">
-        <v>12.43</v>
+        <v>12.44</v>
       </c>
       <c r="H5" t="n">
-        <v>10.15873</v>
+        <v>10.31743</v>
       </c>
       <c r="I5" t="n">
-        <v>21.848751</v>
+        <v>22.83119</v>
       </c>
       <c r="J5" t="n">
-        <v>26.733656</v>
+        <v>27.528173</v>
       </c>
       <c r="K5" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="L5" t="n">
-        <v>3.766264</v>
+        <v>3.9387817</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04576920244495176</v>
+        <v>0.04379973241321033</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03740603137197143</v>
+        <v>0.03632642067460038</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.04685999870300293</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01004396748361939</v>
+        <v>-0.01053357802840255</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-31 16:27:56</t>
+          <t>2026-08-03 16:32:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -22237,51 +22755,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308.91</v>
+        <v>303.42</v>
       </c>
       <c r="F6" t="n">
-        <v>4537070911488</v>
+        <v>4456437514240</v>
       </c>
       <c r="G6" t="n">
-        <v>8.74</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>9.57062</v>
+        <v>9.513070000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>35.344395</v>
+        <v>34.835823</v>
       </c>
       <c r="J6" t="n">
-        <v>32.27691</v>
+        <v>31.895067</v>
       </c>
       <c r="K6" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="L6" t="n">
-        <v>9.719039</v>
+        <v>9.546310999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02829303033245929</v>
+        <v>0.02870608397600686</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03098190411446699</v>
+        <v>0.03135281128468789</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.04685999870300293</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01646809474112383</v>
+        <v>-0.01550718741831503</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-31 16:27:56</t>
+          <t>2026-08-03 16:32:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -22295,51 +22813,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>200.75</v>
+        <v>206.64</v>
       </c>
       <c r="F7" t="n">
-        <v>4862365925376</v>
+        <v>5005027311616</v>
       </c>
       <c r="G7" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
       <c r="H7" t="n">
-        <v>12.86903</v>
+        <v>12.89043</v>
       </c>
       <c r="I7" t="n">
-        <v>30.742725</v>
+        <v>31.69325</v>
       </c>
       <c r="J7" t="n">
-        <v>15.599466</v>
+        <v>16.030497</v>
       </c>
       <c r="K7" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="L7" t="n">
-        <v>19.181612</v>
+        <v>19.744398</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0325280199252802</v>
+        <v>0.03155245838172668</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06410475716064758</v>
+        <v>0.06238109756097562</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.04685999870300293</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01665475830505676</v>
+        <v>0.01552109885797269</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-31 16:27:56</t>
+          <t>2026-08-03 16:32:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -22353,51 +22871,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>476.15</v>
-      </c>
-      <c r="F8" t="n">
-        <v>776410431488</v>
-      </c>
+        <v>484.64</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>13.8213</v>
+        <v>13.91754</v>
       </c>
       <c r="I8" t="n">
-        <v>158.18936</v>
+        <v>161.54668</v>
       </c>
       <c r="J8" t="n">
-        <v>34.45045</v>
+        <v>34.822247</v>
       </c>
       <c r="K8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="L8" t="n">
-        <v>20.729706</v>
-      </c>
+        <v>1.12</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0.006321537330673107</v>
+        <v>0.006190161769560911</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0290271973117715</v>
+        <v>0.02871727467811159</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.04685999870300293</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01842280154381932</v>
+        <v>-0.01814272402489134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-31 16:27:56</t>
+          <t>2026-08-03 16:32:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -22411,51 +22925,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>389.28</v>
+        <v>392.23</v>
       </c>
       <c r="F9" t="n">
-        <v>1852030844928</v>
+        <v>1866065772544</v>
       </c>
       <c r="G9" t="n">
-        <v>6.01</v>
+        <v>5.99</v>
       </c>
       <c r="H9" t="n">
         <v>19.49196</v>
       </c>
       <c r="I9" t="n">
-        <v>64.77204</v>
+        <v>65.48080400000001</v>
       </c>
       <c r="J9" t="n">
-        <v>19.971312</v>
+        <v>20.122656</v>
       </c>
       <c r="K9" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="L9" t="n">
-        <v>24.541588</v>
+        <v>24.727566</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01543875873407316</v>
+        <v>0.01527165183693241</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05007182490752158</v>
+        <v>0.0496952298396349</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.04685999870300293</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002621826051930759</v>
+        <v>0.002835231136631977</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-31 16:27:56</t>
+          <t>2026-08-03 16:32:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -22469,10 +22983,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71.70999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="F10" t="n">
-        <v>298596106240</v>
+        <v>305341693952</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -22481,28 +22995,28 @@
         <v>3.81756</v>
       </c>
       <c r="I10" t="n">
-        <v>22.550314</v>
+        <v>23.059748</v>
       </c>
       <c r="J10" t="n">
-        <v>18.78425</v>
+        <v>19.208605</v>
       </c>
       <c r="K10" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="L10" t="n">
-        <v>6.1730695</v>
+        <v>6.3125257</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04434527959838238</v>
+        <v>0.0433656075276149</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05323608980616372</v>
+        <v>0.0520600027273967</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.04685999870300293</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005786090950572899</v>
+        <v>0.005200004024393773</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P379"/>
+  <dimension ref="A1:P388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21933,16 +21933,16 @@
         <v>9.546310999999999</v>
       </c>
       <c r="M371" t="n">
-        <v>0.02870608397600686</v>
+        <v>0.0287060839760068</v>
       </c>
       <c r="N371" t="n">
-        <v>0.03135281128468789</v>
+        <v>0.0313528112846878</v>
       </c>
       <c r="O371" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.0468599987030029</v>
       </c>
       <c r="P371" t="n">
-        <v>-0.01550718741831503</v>
+        <v>-0.015507187418315</v>
       </c>
     </row>
     <row r="372">
@@ -21987,16 +21987,16 @@
       </c>
       <c r="L372" t="inlineStr"/>
       <c r="M372" t="n">
-        <v>0.006190161769560911</v>
+        <v>0.0061901617695609</v>
       </c>
       <c r="N372" t="n">
-        <v>0.02871727467811159</v>
+        <v>0.0287172746781115</v>
       </c>
       <c r="O372" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.0468599987030029</v>
       </c>
       <c r="P372" t="n">
-        <v>-0.01814272402489134</v>
+        <v>-0.0181427240248913</v>
       </c>
     </row>
     <row r="373">
@@ -22045,16 +22045,16 @@
         <v>3.9387817</v>
       </c>
       <c r="M373" t="n">
-        <v>0.04379973241321033</v>
+        <v>0.0437997324132103</v>
       </c>
       <c r="N373" t="n">
-        <v>0.03632642067460038</v>
+        <v>0.0363264206746003</v>
       </c>
       <c r="O373" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.0468599987030029</v>
       </c>
       <c r="P373" t="n">
-        <v>-0.01053357802840255</v>
+        <v>-0.0105335780284025</v>
       </c>
     </row>
     <row r="374">
@@ -22103,16 +22103,16 @@
         <v>24.727566</v>
       </c>
       <c r="M374" t="n">
-        <v>0.01527165183693241</v>
+        <v>0.0152716518369324</v>
       </c>
       <c r="N374" t="n">
         <v>0.0496952298396349</v>
       </c>
       <c r="O374" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.0468599987030029</v>
       </c>
       <c r="P374" t="n">
-        <v>0.002835231136631977</v>
+        <v>0.0028352311366319</v>
       </c>
     </row>
     <row r="375">
@@ -22161,16 +22161,16 @@
         <v>10.216712</v>
       </c>
       <c r="M375" t="n">
-        <v>0.05353451284667222</v>
+        <v>0.0535345128466722</v>
       </c>
       <c r="N375" t="n">
-        <v>0.03955870271431256</v>
+        <v>0.0395587027143125</v>
       </c>
       <c r="O375" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.0468599987030029</v>
       </c>
       <c r="P375" t="n">
-        <v>-0.007301295988690365</v>
+        <v>-0.0073012959886903</v>
       </c>
     </row>
     <row r="376">
@@ -22219,13 +22219,13 @@
         <v>6.5877757</v>
       </c>
       <c r="M376" t="n">
-        <v>0.04499864461913797</v>
+        <v>0.0449986446191379</v>
       </c>
       <c r="N376" t="n">
-        <v>0.05912649091894823</v>
+        <v>0.0591264909189482</v>
       </c>
       <c r="O376" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.0468599987030029</v>
       </c>
       <c r="P376" t="n">
         <v>0.0122664922159453</v>
@@ -22277,16 +22277,16 @@
         <v>10.912121</v>
       </c>
       <c r="M377" t="n">
-        <v>0.03678868040602892</v>
+        <v>0.0367886804060289</v>
       </c>
       <c r="N377" t="n">
-        <v>0.04812621757407978</v>
+        <v>0.0481262175740797</v>
       </c>
       <c r="O377" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.0468599987030029</v>
       </c>
       <c r="P377" t="n">
-        <v>0.001266218871076849</v>
+        <v>0.0012662188710768</v>
       </c>
     </row>
     <row r="378">
@@ -22341,10 +22341,10 @@
         <v>0.0520600027273967</v>
       </c>
       <c r="O378" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.0468599987030029</v>
       </c>
       <c r="P378" t="n">
-        <v>0.005200004024393773</v>
+        <v>0.0052000040243937</v>
       </c>
     </row>
     <row r="379">
@@ -22393,16 +22393,534 @@
         <v>19.744398</v>
       </c>
       <c r="M379" t="n">
-        <v>0.03155245838172668</v>
+        <v>0.0315524583817266</v>
       </c>
       <c r="N379" t="n">
-        <v>0.06238109756097562</v>
+        <v>0.0623810975609756</v>
       </c>
       <c r="O379" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.0468599987030029</v>
       </c>
       <c r="P379" t="n">
-        <v>0.01552109885797269</v>
+        <v>0.0155210988579726</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2026-08-04 16:29:27</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>309.38</v>
+      </c>
+      <c r="F380" t="n">
+        <v>4515147284480</v>
+      </c>
+      <c r="G380" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H380" t="n">
+        <v>9.513070000000001</v>
+      </c>
+      <c r="I380" t="n">
+        <v>35.520092</v>
+      </c>
+      <c r="J380" t="n">
+        <v>32.521572</v>
+      </c>
+      <c r="K380" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="L380" t="n">
+        <v>9.672075</v>
+      </c>
+      <c r="M380" t="n">
+        <v>0.02815308035425691</v>
+      </c>
+      <c r="N380" t="n">
+        <v>0.03074882022108734</v>
+      </c>
+      <c r="O380" t="n">
+        <v>0.04626999855041504</v>
+      </c>
+      <c r="P380" t="n">
+        <v>-0.0155211783293277</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>2026-08-04 16:29:27</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>518.58</v>
+      </c>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="n">
+        <v>3</v>
+      </c>
+      <c r="H381" t="n">
+        <v>13.91754</v>
+      </c>
+      <c r="I381" t="n">
+        <v>172.86</v>
+      </c>
+      <c r="J381" t="n">
+        <v>37.2609</v>
+      </c>
+      <c r="K381" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L381" t="inlineStr"/>
+      <c r="M381" t="n">
+        <v>0.005785028346638898</v>
+      </c>
+      <c r="N381" t="n">
+        <v>0.02683778780516025</v>
+      </c>
+      <c r="O381" t="n">
+        <v>0.04626999855041504</v>
+      </c>
+      <c r="P381" t="n">
+        <v>-0.01943221074525479</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>2026-08-04 16:29:27</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>277.42</v>
+      </c>
+      <c r="F382" t="n">
+        <v>2992339156992</v>
+      </c>
+      <c r="G382" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="H382" t="n">
+        <v>10.31743</v>
+      </c>
+      <c r="I382" t="n">
+        <v>22.300646</v>
+      </c>
+      <c r="J382" t="n">
+        <v>26.888481</v>
+      </c>
+      <c r="K382" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L382" t="n">
+        <v>3.8576977</v>
+      </c>
+      <c r="M382" t="n">
+        <v>0.04484175618196237</v>
+      </c>
+      <c r="N382" t="n">
+        <v>0.03719064955662894</v>
+      </c>
+      <c r="O382" t="n">
+        <v>0.04626999855041504</v>
+      </c>
+      <c r="P382" t="n">
+        <v>-0.009079348993786103</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>2026-08-04 16:29:27</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>418.16</v>
+      </c>
+      <c r="F383" t="n">
+        <v>1989429821440</v>
+      </c>
+      <c r="G383" t="n">
+        <v>6</v>
+      </c>
+      <c r="H383" t="n">
+        <v>19.49196</v>
+      </c>
+      <c r="I383" t="n">
+        <v>69.69334000000001</v>
+      </c>
+      <c r="J383" t="n">
+        <v>21.452948</v>
+      </c>
+      <c r="K383" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L383" t="n">
+        <v>26.362286</v>
+      </c>
+      <c r="M383" t="n">
+        <v>0.01434857470824565</v>
+      </c>
+      <c r="N383" t="n">
+        <v>0.0466136407116893</v>
+      </c>
+      <c r="O383" t="n">
+        <v>0.04626999855041504</v>
+      </c>
+      <c r="P383" t="n">
+        <v>0.0003436421612742629</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>2026-08-04 16:29:27</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>375.35</v>
+      </c>
+      <c r="F384" t="n">
+        <v>4590506344448</v>
+      </c>
+      <c r="G384" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H384" t="n">
+        <v>14.73443</v>
+      </c>
+      <c r="I384" t="n">
+        <v>18.833418</v>
+      </c>
+      <c r="J384" t="n">
+        <v>25.474348</v>
+      </c>
+      <c r="K384" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L384" t="n">
+        <v>10.295709</v>
+      </c>
+      <c r="M384" t="n">
+        <v>0.05309710936459304</v>
+      </c>
+      <c r="N384" t="n">
+        <v>0.03925517516984148</v>
+      </c>
+      <c r="O384" t="n">
+        <v>0.04626999855041504</v>
+      </c>
+      <c r="P384" t="n">
+        <v>-0.007014823380573562</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2026-08-04 16:29:27</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>587.9400000000001</v>
+      </c>
+      <c r="F385" t="n">
+        <v>1497780846592</v>
+      </c>
+      <c r="G385" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="H385" t="n">
+        <v>34.89882</v>
+      </c>
+      <c r="I385" t="n">
+        <v>22.136295</v>
+      </c>
+      <c r="J385" t="n">
+        <v>16.846989</v>
+      </c>
+      <c r="K385" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L385" t="n">
+        <v>6.5621057</v>
+      </c>
+      <c r="M385" t="n">
+        <v>0.04517467768819947</v>
+      </c>
+      <c r="N385" t="n">
+        <v>0.05935779161138891</v>
+      </c>
+      <c r="O385" t="n">
+        <v>0.04626999855041504</v>
+      </c>
+      <c r="P385" t="n">
+        <v>0.01308779306097387</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2026-08-04 16:29:27</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>492.81</v>
+      </c>
+      <c r="F386" t="n">
+        <v>3659383177216</v>
+      </c>
+      <c r="G386" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H386" t="n">
+        <v>23.46875</v>
+      </c>
+      <c r="I386" t="n">
+        <v>27.454596</v>
+      </c>
+      <c r="J386" t="n">
+        <v>20.998562</v>
+      </c>
+      <c r="K386" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L386" t="n">
+        <v>11.027586</v>
+      </c>
+      <c r="M386" t="n">
+        <v>0.03642377386822507</v>
+      </c>
+      <c r="N386" t="n">
+        <v>0.04762230880055194</v>
+      </c>
+      <c r="O386" t="n">
+        <v>0.04626999855041504</v>
+      </c>
+      <c r="P386" t="n">
+        <v>0.0013523102501369</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2026-08-04 16:29:27</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>73.56999999999999</v>
+      </c>
+      <c r="F387" t="n">
+        <v>306341019648</v>
+      </c>
+      <c r="G387" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H387" t="n">
+        <v>3.81756</v>
+      </c>
+      <c r="I387" t="n">
+        <v>23.13522</v>
+      </c>
+      <c r="J387" t="n">
+        <v>19.271471</v>
+      </c>
+      <c r="K387" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L387" t="n">
+        <v>6.333185</v>
+      </c>
+      <c r="M387" t="n">
+        <v>0.04322414027456845</v>
+      </c>
+      <c r="N387" t="n">
+        <v>0.05189017262471116</v>
+      </c>
+      <c r="O387" t="n">
+        <v>0.04626999855041504</v>
+      </c>
+      <c r="P387" t="n">
+        <v>0.005620174074296123</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>2026-08-04 16:29:27</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>211.94</v>
+      </c>
+      <c r="F388" t="n">
+        <v>5133398704128</v>
+      </c>
+      <c r="G388" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="H388" t="n">
+        <v>12.89043</v>
+      </c>
+      <c r="I388" t="n">
+        <v>32.506134</v>
+      </c>
+      <c r="J388" t="n">
+        <v>16.441654</v>
+      </c>
+      <c r="K388" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L388" t="n">
+        <v>20.250813</v>
+      </c>
+      <c r="M388" t="n">
+        <v>0.03076342361045579</v>
+      </c>
+      <c r="N388" t="n">
+        <v>0.06082112862130792</v>
+      </c>
+      <c r="O388" t="n">
+        <v>0.04626999855041504</v>
+      </c>
+      <c r="P388" t="n">
+        <v>0.01455113007089288</v>
       </c>
     </row>
   </sheetData>
@@ -22504,12 +23022,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-03 16:32:28</t>
+          <t>2026-08-04 16:29:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -22523,51 +23041,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>372.47</v>
+        <v>375.35</v>
       </c>
       <c r="F2" t="n">
-        <v>4555284152320</v>
+        <v>4590506344448</v>
       </c>
       <c r="G2" t="n">
-        <v>19.94</v>
+        <v>19.93</v>
       </c>
       <c r="H2" t="n">
         <v>14.73443</v>
       </c>
       <c r="I2" t="n">
-        <v>18.679539</v>
+        <v>18.833418</v>
       </c>
       <c r="J2" t="n">
-        <v>25.278887</v>
+        <v>25.474348</v>
       </c>
       <c r="K2" t="n">
         <v>0.97</v>
       </c>
       <c r="L2" t="n">
-        <v>10.216712</v>
+        <v>10.295709</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05353451284667222</v>
+        <v>0.05309710936459304</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03955870271431256</v>
+        <v>0.03925517516984148</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.04626999855041504</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.007301295988690365</v>
+        <v>-0.007014823380573562</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-03 16:32:28</t>
+          <t>2026-08-04 16:29:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -22581,51 +23099,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>487.65</v>
+        <v>492.81</v>
       </c>
       <c r="F3" t="n">
-        <v>3621067423744</v>
+        <v>3659383177216</v>
       </c>
       <c r="G3" t="n">
-        <v>17.94</v>
+        <v>17.95</v>
       </c>
       <c r="H3" t="n">
         <v>23.46875</v>
       </c>
       <c r="I3" t="n">
-        <v>27.182274</v>
+        <v>27.454596</v>
       </c>
       <c r="J3" t="n">
-        <v>20.778694</v>
+        <v>20.998562</v>
       </c>
       <c r="K3" t="n">
         <v>1.52</v>
       </c>
       <c r="L3" t="n">
-        <v>10.912121</v>
+        <v>11.027586</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03678868040602892</v>
+        <v>0.03642377386822507</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04812621757407978</v>
+        <v>0.04762230880055194</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.04626999855041504</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001266218871076849</v>
+        <v>0.0013523102501369</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-03 16:32:28</t>
+          <t>2026-08-04 16:29:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -22639,10 +23157,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>590.24</v>
+        <v>587.9400000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1503640027136</v>
+        <v>1497780846592</v>
       </c>
       <c r="G4" t="n">
         <v>26.56</v>
@@ -22651,39 +23169,39 @@
         <v>34.89882</v>
       </c>
       <c r="I4" t="n">
-        <v>22.22289</v>
+        <v>22.136295</v>
       </c>
       <c r="J4" t="n">
-        <v>16.912893</v>
+        <v>16.846989</v>
       </c>
       <c r="K4" t="n">
         <v>0.83</v>
       </c>
       <c r="L4" t="n">
-        <v>6.5877757</v>
+        <v>6.5621057</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04499864461913797</v>
+        <v>0.04517467768819947</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05912649091894823</v>
+        <v>0.05935779161138891</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.04626999855041504</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0122664922159453</v>
+        <v>0.01308779306097387</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-03 16:32:28</t>
+          <t>2026-08-04 16:29:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -22697,10 +23215,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>284.02</v>
+        <v>277.42</v>
       </c>
       <c r="F5" t="n">
-        <v>3055234318336</v>
+        <v>2992339156992</v>
       </c>
       <c r="G5" t="n">
         <v>12.44</v>
@@ -22709,39 +23227,39 @@
         <v>10.31743</v>
       </c>
       <c r="I5" t="n">
-        <v>22.83119</v>
+        <v>22.300646</v>
       </c>
       <c r="J5" t="n">
-        <v>27.528173</v>
+        <v>26.888481</v>
       </c>
       <c r="K5" t="n">
         <v>1.46</v>
       </c>
       <c r="L5" t="n">
-        <v>3.9387817</v>
+        <v>3.8576977</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04379973241321033</v>
+        <v>0.04484175618196237</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03632642067460038</v>
+        <v>0.03719064955662894</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.04626999855041504</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01053357802840255</v>
+        <v>-0.009079348993786103</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-03 16:32:28</t>
+          <t>2026-08-04 16:29:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -22755,10 +23273,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>303.42</v>
+        <v>309.38</v>
       </c>
       <c r="F6" t="n">
-        <v>4456437514240</v>
+        <v>4515147284480</v>
       </c>
       <c r="G6" t="n">
         <v>8.710000000000001</v>
@@ -22767,39 +23285,39 @@
         <v>9.513070000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>34.835823</v>
+        <v>35.520092</v>
       </c>
       <c r="J6" t="n">
-        <v>31.895067</v>
+        <v>32.521572</v>
       </c>
       <c r="K6" t="n">
         <v>2.46</v>
       </c>
       <c r="L6" t="n">
-        <v>9.546310999999999</v>
+        <v>9.672075</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02870608397600686</v>
+        <v>0.02815308035425691</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03135281128468789</v>
+        <v>0.03074882022108734</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.04626999855041504</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01550718741831503</v>
+        <v>-0.0155211783293277</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-03 16:32:28</t>
+          <t>2026-08-04 16:29:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -22813,10 +23331,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206.64</v>
+        <v>211.94</v>
       </c>
       <c r="F7" t="n">
-        <v>5005027311616</v>
+        <v>5133398704128</v>
       </c>
       <c r="G7" t="n">
         <v>6.52</v>
@@ -22825,39 +23343,39 @@
         <v>12.89043</v>
       </c>
       <c r="I7" t="n">
-        <v>31.69325</v>
+        <v>32.506134</v>
       </c>
       <c r="J7" t="n">
-        <v>16.030497</v>
+        <v>16.441654</v>
       </c>
       <c r="K7" t="n">
         <v>0.55</v>
       </c>
       <c r="L7" t="n">
-        <v>19.744398</v>
+        <v>20.250813</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03155245838172668</v>
+        <v>0.03076342361045579</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06238109756097562</v>
+        <v>0.06082112862130792</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.04626999855041504</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01552109885797269</v>
+        <v>0.01455113007089288</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-03 16:32:28</t>
+          <t>2026-08-04 16:29:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -22871,7 +23389,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>484.64</v>
+        <v>518.58</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
@@ -22881,37 +23399,37 @@
         <v>13.91754</v>
       </c>
       <c r="I8" t="n">
-        <v>161.54668</v>
+        <v>172.86</v>
       </c>
       <c r="J8" t="n">
-        <v>34.822247</v>
+        <v>37.2609</v>
       </c>
       <c r="K8" t="n">
         <v>1.12</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0.006190161769560911</v>
+        <v>0.005785028346638898</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02871727467811159</v>
+        <v>0.02683778780516025</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.04626999855041504</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01814272402489134</v>
+        <v>-0.01943221074525479</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-03 16:32:28</t>
+          <t>2026-08-04 16:29:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -22925,51 +23443,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392.23</v>
+        <v>418.16</v>
       </c>
       <c r="F9" t="n">
-        <v>1866065772544</v>
+        <v>1989429821440</v>
       </c>
       <c r="G9" t="n">
-        <v>5.99</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>19.49196</v>
       </c>
       <c r="I9" t="n">
-        <v>65.48080400000001</v>
+        <v>69.69334000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>20.122656</v>
+        <v>21.452948</v>
       </c>
       <c r="K9" t="n">
         <v>0.44</v>
       </c>
       <c r="L9" t="n">
-        <v>24.727566</v>
+        <v>26.362286</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01527165183693241</v>
+        <v>0.01434857470824565</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0496952298396349</v>
+        <v>0.0466136407116893</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.04626999855041504</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002835231136631977</v>
+        <v>0.0003436421612742629</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-03 16:32:28</t>
+          <t>2026-08-04 16:29:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -22983,10 +23501,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73.33</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>305341693952</v>
+        <v>306341019648</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -22995,28 +23513,28 @@
         <v>3.81756</v>
       </c>
       <c r="I10" t="n">
-        <v>23.059748</v>
+        <v>23.13522</v>
       </c>
       <c r="J10" t="n">
-        <v>19.208605</v>
+        <v>19.271471</v>
       </c>
       <c r="K10" t="n">
         <v>1.61</v>
       </c>
       <c r="L10" t="n">
-        <v>6.3125257</v>
+        <v>6.333185</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0433656075276149</v>
+        <v>0.04322414027456845</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0520600027273967</v>
+        <v>0.05189017262471116</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04685999870300293</v>
+        <v>0.04626999855041504</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005200004024393773</v>
+        <v>0.005620174074296123</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P388"/>
+  <dimension ref="A1:P397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22451,13 +22451,13 @@
         <v>9.672075</v>
       </c>
       <c r="M380" t="n">
-        <v>0.02815308035425691</v>
+        <v>0.0281530803542569</v>
       </c>
       <c r="N380" t="n">
-        <v>0.03074882022108734</v>
+        <v>0.0307488202210873</v>
       </c>
       <c r="O380" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.046269998550415</v>
       </c>
       <c r="P380" t="n">
         <v>-0.0155211783293277</v>
@@ -22505,16 +22505,16 @@
       </c>
       <c r="L381" t="inlineStr"/>
       <c r="M381" t="n">
-        <v>0.005785028346638898</v>
+        <v>0.0057850283466388</v>
       </c>
       <c r="N381" t="n">
-        <v>0.02683778780516025</v>
+        <v>0.0268377878051602</v>
       </c>
       <c r="O381" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.046269998550415</v>
       </c>
       <c r="P381" t="n">
-        <v>-0.01943221074525479</v>
+        <v>-0.0194322107452547</v>
       </c>
     </row>
     <row r="382">
@@ -22563,16 +22563,16 @@
         <v>3.8576977</v>
       </c>
       <c r="M382" t="n">
-        <v>0.04484175618196237</v>
+        <v>0.0448417561819623</v>
       </c>
       <c r="N382" t="n">
-        <v>0.03719064955662894</v>
+        <v>0.0371906495566289</v>
       </c>
       <c r="O382" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.046269998550415</v>
       </c>
       <c r="P382" t="n">
-        <v>-0.009079348993786103</v>
+        <v>-0.0090793489937861</v>
       </c>
     </row>
     <row r="383">
@@ -22621,16 +22621,16 @@
         <v>26.362286</v>
       </c>
       <c r="M383" t="n">
-        <v>0.01434857470824565</v>
+        <v>0.0143485747082456</v>
       </c>
       <c r="N383" t="n">
         <v>0.0466136407116893</v>
       </c>
       <c r="O383" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.046269998550415</v>
       </c>
       <c r="P383" t="n">
-        <v>0.0003436421612742629</v>
+        <v>0.0003436421612742</v>
       </c>
     </row>
     <row r="384">
@@ -22679,16 +22679,16 @@
         <v>10.295709</v>
       </c>
       <c r="M384" t="n">
-        <v>0.05309710936459304</v>
+        <v>0.053097109364593</v>
       </c>
       <c r="N384" t="n">
-        <v>0.03925517516984148</v>
+        <v>0.0392551751698414</v>
       </c>
       <c r="O384" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.046269998550415</v>
       </c>
       <c r="P384" t="n">
-        <v>-0.007014823380573562</v>
+        <v>-0.0070148233805735</v>
       </c>
     </row>
     <row r="385">
@@ -22737,16 +22737,16 @@
         <v>6.5621057</v>
       </c>
       <c r="M385" t="n">
-        <v>0.04517467768819947</v>
+        <v>0.0451746776881994</v>
       </c>
       <c r="N385" t="n">
-        <v>0.05935779161138891</v>
+        <v>0.0593577916113889</v>
       </c>
       <c r="O385" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.046269998550415</v>
       </c>
       <c r="P385" t="n">
-        <v>0.01308779306097387</v>
+        <v>0.0130877930609738</v>
       </c>
     </row>
     <row r="386">
@@ -22795,16 +22795,16 @@
         <v>11.027586</v>
       </c>
       <c r="M386" t="n">
-        <v>0.03642377386822507</v>
+        <v>0.036423773868225</v>
       </c>
       <c r="N386" t="n">
-        <v>0.04762230880055194</v>
+        <v>0.0476223088005519</v>
       </c>
       <c r="O386" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.046269998550415</v>
       </c>
       <c r="P386" t="n">
-        <v>0.0013523102501369</v>
+        <v>0.0013523102501368</v>
       </c>
     </row>
     <row r="387">
@@ -22853,16 +22853,16 @@
         <v>6.333185</v>
       </c>
       <c r="M387" t="n">
-        <v>0.04322414027456845</v>
+        <v>0.0432241402745684</v>
       </c>
       <c r="N387" t="n">
-        <v>0.05189017262471116</v>
+        <v>0.0518901726247111</v>
       </c>
       <c r="O387" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.046269998550415</v>
       </c>
       <c r="P387" t="n">
-        <v>0.005620174074296123</v>
+        <v>0.0056201740742961</v>
       </c>
     </row>
     <row r="388">
@@ -22911,16 +22911,538 @@
         <v>20.250813</v>
       </c>
       <c r="M388" t="n">
-        <v>0.03076342361045579</v>
+        <v>0.0307634236104557</v>
       </c>
       <c r="N388" t="n">
-        <v>0.06082112862130792</v>
+        <v>0.0608211286213079</v>
       </c>
       <c r="O388" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.046269998550415</v>
       </c>
       <c r="P388" t="n">
-        <v>0.01455113007089288</v>
+        <v>0.0145511300708928</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:27:56</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>311</v>
+      </c>
+      <c r="F389" t="n">
+        <v>4538790051840</v>
+      </c>
+      <c r="G389" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H389" t="n">
+        <v>9.513070000000001</v>
+      </c>
+      <c r="I389" t="n">
+        <v>35.66514</v>
+      </c>
+      <c r="J389" t="n">
+        <v>32.691864</v>
+      </c>
+      <c r="K389" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="L389" t="n">
+        <v>9.722721999999999</v>
+      </c>
+      <c r="M389" t="n">
+        <v>0.02803858520900322</v>
+      </c>
+      <c r="N389" t="n">
+        <v>0.03058864951768489</v>
+      </c>
+      <c r="O389" t="n">
+        <v>0.04616999626159668</v>
+      </c>
+      <c r="P389" t="n">
+        <v>-0.01558134674391179</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:27:56</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>482.05</v>
+      </c>
+      <c r="F390" t="n">
+        <v>786030985216</v>
+      </c>
+      <c r="G390" t="n">
+        <v>3</v>
+      </c>
+      <c r="H390" t="n">
+        <v>14.98479</v>
+      </c>
+      <c r="I390" t="n">
+        <v>160.68333</v>
+      </c>
+      <c r="J390" t="n">
+        <v>32.169285</v>
+      </c>
+      <c r="K390" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L390" t="n">
+        <v>20.98657</v>
+      </c>
+      <c r="M390" t="n">
+        <v>0.006223420806970231</v>
+      </c>
+      <c r="N390" t="n">
+        <v>0.03108555129135982</v>
+      </c>
+      <c r="O390" t="n">
+        <v>0.04616999626159668</v>
+      </c>
+      <c r="P390" t="n">
+        <v>-0.01508444497023686</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:27:56</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>272.65</v>
+      </c>
+      <c r="F391" t="n">
+        <v>2940888154112</v>
+      </c>
+      <c r="G391" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="H391" t="n">
+        <v>10.34953</v>
+      </c>
+      <c r="I391" t="n">
+        <v>21.917202</v>
+      </c>
+      <c r="J391" t="n">
+        <v>26.34419</v>
+      </c>
+      <c r="K391" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L391" t="n">
+        <v>3.7913675</v>
+      </c>
+      <c r="M391" t="n">
+        <v>0.04562626077388594</v>
+      </c>
+      <c r="N391" t="n">
+        <v>0.0379590317256556</v>
+      </c>
+      <c r="O391" t="n">
+        <v>0.04616999626159668</v>
+      </c>
+      <c r="P391" t="n">
+        <v>-0.008210964535941077</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:27:56</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>418.28</v>
+      </c>
+      <c r="F392" t="n">
+        <v>1990000640000</v>
+      </c>
+      <c r="G392" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H392" t="n">
+        <v>19.49196</v>
+      </c>
+      <c r="I392" t="n">
+        <v>69.48173</v>
+      </c>
+      <c r="J392" t="n">
+        <v>21.459103</v>
+      </c>
+      <c r="K392" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L392" t="n">
+        <v>26.369848</v>
+      </c>
+      <c r="M392" t="n">
+        <v>0.01439227311848523</v>
+      </c>
+      <c r="N392" t="n">
+        <v>0.04660026776322081</v>
+      </c>
+      <c r="O392" t="n">
+        <v>0.04616999626159668</v>
+      </c>
+      <c r="P392" t="n">
+        <v>0.0004302715016241271</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:27:56</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>360.13</v>
+      </c>
+      <c r="F393" t="n">
+        <v>4404366802944</v>
+      </c>
+      <c r="G393" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H393" t="n">
+        <v>14.73443</v>
+      </c>
+      <c r="I393" t="n">
+        <v>18.069744</v>
+      </c>
+      <c r="J393" t="n">
+        <v>24.441393</v>
+      </c>
+      <c r="K393" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L393" t="n">
+        <v>9.87823</v>
+      </c>
+      <c r="M393" t="n">
+        <v>0.05534112681531669</v>
+      </c>
+      <c r="N393" t="n">
+        <v>0.04091419765084831</v>
+      </c>
+      <c r="O393" t="n">
+        <v>0.04616999626159668</v>
+      </c>
+      <c r="P393" t="n">
+        <v>-0.005255798610748375</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:27:56</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>588.77</v>
+      </c>
+      <c r="F394" t="n">
+        <v>1499895300096</v>
+      </c>
+      <c r="G394" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="H394" t="n">
+        <v>35.13625</v>
+      </c>
+      <c r="I394" t="n">
+        <v>22.159203</v>
+      </c>
+      <c r="J394" t="n">
+        <v>16.75677</v>
+      </c>
+      <c r="K394" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L394" t="n">
+        <v>6.571369</v>
+      </c>
+      <c r="M394" t="n">
+        <v>0.04512797866739134</v>
+      </c>
+      <c r="N394" t="n">
+        <v>0.05967737826315878</v>
+      </c>
+      <c r="O394" t="n">
+        <v>0.04616999626159668</v>
+      </c>
+      <c r="P394" t="n">
+        <v>0.0135073820015621</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:27:56</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>487.46</v>
+      </c>
+      <c r="F395" t="n">
+        <v>3619656564736</v>
+      </c>
+      <c r="G395" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="H395" t="n">
+        <v>23.46875</v>
+      </c>
+      <c r="I395" t="n">
+        <v>25.901169</v>
+      </c>
+      <c r="J395" t="n">
+        <v>20.7706</v>
+      </c>
+      <c r="K395" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L395" t="n">
+        <v>10.907869</v>
+      </c>
+      <c r="M395" t="n">
+        <v>0.03860829606531818</v>
+      </c>
+      <c r="N395" t="n">
+        <v>0.04814497599803061</v>
+      </c>
+      <c r="O395" t="n">
+        <v>0.04616999626159668</v>
+      </c>
+      <c r="P395" t="n">
+        <v>0.001974979736433929</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:27:56</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="F396" t="n">
+        <v>308964294656</v>
+      </c>
+      <c r="G396" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H396" t="n">
+        <v>3.81756</v>
+      </c>
+      <c r="I396" t="n">
+        <v>23.333332</v>
+      </c>
+      <c r="J396" t="n">
+        <v>19.436499</v>
+      </c>
+      <c r="K396" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L396" t="n">
+        <v>6.387418</v>
+      </c>
+      <c r="M396" t="n">
+        <v>0.04285714285714286</v>
+      </c>
+      <c r="N396" t="n">
+        <v>0.05144959568733153</v>
+      </c>
+      <c r="O396" t="n">
+        <v>0.04616999626159668</v>
+      </c>
+      <c r="P396" t="n">
+        <v>0.005279599425734853</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:27:56</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>219.22</v>
+      </c>
+      <c r="F397" t="n">
+        <v>5309727768576</v>
+      </c>
+      <c r="G397" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H397" t="n">
+        <v>12.89043</v>
+      </c>
+      <c r="I397" t="n">
+        <v>33.57121</v>
+      </c>
+      <c r="J397" t="n">
+        <v>17.006414</v>
+      </c>
+      <c r="K397" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L397" t="n">
+        <v>20.946415</v>
+      </c>
+      <c r="M397" t="n">
+        <v>0.02978742815436548</v>
+      </c>
+      <c r="N397" t="n">
+        <v>0.05880134111851108</v>
+      </c>
+      <c r="O397" t="n">
+        <v>0.04616999626159668</v>
+      </c>
+      <c r="P397" t="n">
+        <v>0.0126313448569144</v>
       </c>
     </row>
   </sheetData>
@@ -23022,12 +23544,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-04 16:29:27</t>
+          <t>2026-08-05 16:27:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -23041,10 +23563,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>375.35</v>
+        <v>360.13</v>
       </c>
       <c r="F2" t="n">
-        <v>4590506344448</v>
+        <v>4404366802944</v>
       </c>
       <c r="G2" t="n">
         <v>19.93</v>
@@ -23053,39 +23575,39 @@
         <v>14.73443</v>
       </c>
       <c r="I2" t="n">
-        <v>18.833418</v>
+        <v>18.069744</v>
       </c>
       <c r="J2" t="n">
-        <v>25.474348</v>
+        <v>24.441393</v>
       </c>
       <c r="K2" t="n">
         <v>0.97</v>
       </c>
       <c r="L2" t="n">
-        <v>10.295709</v>
+        <v>9.87823</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05309710936459304</v>
+        <v>0.05534112681531669</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03925517516984148</v>
+        <v>0.04091419765084831</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.04616999626159668</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.007014823380573562</v>
+        <v>-0.005255798610748375</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-04 16:29:27</t>
+          <t>2026-08-05 16:27:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -23099,51 +23621,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>492.81</v>
+        <v>487.46</v>
       </c>
       <c r="F3" t="n">
-        <v>3659383177216</v>
+        <v>3619656564736</v>
       </c>
       <c r="G3" t="n">
-        <v>17.95</v>
+        <v>18.82</v>
       </c>
       <c r="H3" t="n">
         <v>23.46875</v>
       </c>
       <c r="I3" t="n">
-        <v>27.454596</v>
+        <v>25.901169</v>
       </c>
       <c r="J3" t="n">
-        <v>20.998562</v>
+        <v>20.7706</v>
       </c>
       <c r="K3" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="L3" t="n">
-        <v>11.027586</v>
+        <v>10.907869</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03642377386822507</v>
+        <v>0.03860829606531818</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04762230880055194</v>
+        <v>0.04814497599803061</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.04616999626159668</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0013523102501369</v>
+        <v>0.001974979736433929</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-04 16:29:27</t>
+          <t>2026-08-05 16:27:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -23157,51 +23679,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>587.9400000000001</v>
+        <v>588.77</v>
       </c>
       <c r="F4" t="n">
-        <v>1497780846592</v>
+        <v>1499895300096</v>
       </c>
       <c r="G4" t="n">
-        <v>26.56</v>
+        <v>26.57</v>
       </c>
       <c r="H4" t="n">
-        <v>34.89882</v>
+        <v>35.13625</v>
       </c>
       <c r="I4" t="n">
-        <v>22.136295</v>
+        <v>22.159203</v>
       </c>
       <c r="J4" t="n">
-        <v>16.846989</v>
+        <v>16.75677</v>
       </c>
       <c r="K4" t="n">
         <v>0.83</v>
       </c>
       <c r="L4" t="n">
-        <v>6.5621057</v>
+        <v>6.571369</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04517467768819947</v>
+        <v>0.04512797866739134</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05935779161138891</v>
+        <v>0.05967737826315878</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.04616999626159668</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01308779306097387</v>
+        <v>0.0135073820015621</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-04 16:29:27</t>
+          <t>2026-08-05 16:27:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -23215,51 +23737,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>277.42</v>
+        <v>272.65</v>
       </c>
       <c r="F5" t="n">
-        <v>2992339156992</v>
+        <v>2940888154112</v>
       </c>
       <c r="G5" t="n">
         <v>12.44</v>
       </c>
       <c r="H5" t="n">
-        <v>10.31743</v>
+        <v>10.34953</v>
       </c>
       <c r="I5" t="n">
-        <v>22.300646</v>
+        <v>21.917202</v>
       </c>
       <c r="J5" t="n">
-        <v>26.888481</v>
+        <v>26.34419</v>
       </c>
       <c r="K5" t="n">
         <v>1.46</v>
       </c>
       <c r="L5" t="n">
-        <v>3.8576977</v>
+        <v>3.7913675</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04484175618196237</v>
+        <v>0.04562626077388594</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03719064955662894</v>
+        <v>0.0379590317256556</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.04616999626159668</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.009079348993786103</v>
+        <v>-0.008210964535941077</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-04 16:29:27</t>
+          <t>2026-08-05 16:27:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -23273,51 +23795,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>309.38</v>
+        <v>311</v>
       </c>
       <c r="F6" t="n">
-        <v>4515147284480</v>
+        <v>4538790051840</v>
       </c>
       <c r="G6" t="n">
-        <v>8.710000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>9.513070000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>35.520092</v>
+        <v>35.66514</v>
       </c>
       <c r="J6" t="n">
-        <v>32.521572</v>
+        <v>32.691864</v>
       </c>
       <c r="K6" t="n">
         <v>2.46</v>
       </c>
       <c r="L6" t="n">
-        <v>9.672075</v>
+        <v>9.722721999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02815308035425691</v>
+        <v>0.02803858520900322</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03074882022108734</v>
+        <v>0.03058864951768489</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.04616999626159668</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0155211783293277</v>
+        <v>-0.01558134674391179</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-04 16:29:27</t>
+          <t>2026-08-05 16:27:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -23331,51 +23853,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>211.94</v>
+        <v>219.22</v>
       </c>
       <c r="F7" t="n">
-        <v>5133398704128</v>
+        <v>5309727768576</v>
       </c>
       <c r="G7" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="H7" t="n">
         <v>12.89043</v>
       </c>
       <c r="I7" t="n">
-        <v>32.506134</v>
+        <v>33.57121</v>
       </c>
       <c r="J7" t="n">
-        <v>16.441654</v>
+        <v>17.006414</v>
       </c>
       <c r="K7" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="L7" t="n">
-        <v>20.250813</v>
+        <v>20.946415</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03076342361045579</v>
+        <v>0.02978742815436548</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06082112862130792</v>
+        <v>0.05880134111851108</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.04616999626159668</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01455113007089288</v>
+        <v>0.0126313448569144</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-04 16:29:27</t>
+          <t>2026-08-05 16:27:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -23389,47 +23911,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>518.58</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>482.05</v>
+      </c>
+      <c r="F8" t="n">
+        <v>786030985216</v>
+      </c>
       <c r="G8" t="n">
         <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>13.91754</v>
+        <v>14.98479</v>
       </c>
       <c r="I8" t="n">
-        <v>172.86</v>
+        <v>160.68333</v>
       </c>
       <c r="J8" t="n">
-        <v>37.2609</v>
+        <v>32.169285</v>
       </c>
       <c r="K8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>1.14</v>
+      </c>
+      <c r="L8" t="n">
+        <v>20.98657</v>
+      </c>
       <c r="M8" t="n">
-        <v>0.005785028346638898</v>
+        <v>0.006223420806970231</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02683778780516025</v>
+        <v>0.03108555129135982</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.04616999626159668</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01943221074525479</v>
+        <v>-0.01508444497023686</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-04 16:29:27</t>
+          <t>2026-08-05 16:27:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -23443,51 +23969,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>418.16</v>
+        <v>418.28</v>
       </c>
       <c r="F9" t="n">
-        <v>1989429821440</v>
+        <v>1990000640000</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>6.02</v>
       </c>
       <c r="H9" t="n">
         <v>19.49196</v>
       </c>
       <c r="I9" t="n">
-        <v>69.69334000000001</v>
+        <v>69.48173</v>
       </c>
       <c r="J9" t="n">
-        <v>21.452948</v>
+        <v>21.459103</v>
       </c>
       <c r="K9" t="n">
         <v>0.44</v>
       </c>
       <c r="L9" t="n">
-        <v>26.362286</v>
+        <v>26.369848</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01434857470824565</v>
+        <v>0.01439227311848523</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0466136407116893</v>
+        <v>0.04660026776322081</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.04616999626159668</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0003436421612742629</v>
+        <v>0.0004302715016241271</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-04 16:29:27</t>
+          <t>2026-08-05 16:27:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -23501,10 +24027,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73.56999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="F10" t="n">
-        <v>306341019648</v>
+        <v>308964294656</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -23513,28 +24039,28 @@
         <v>3.81756</v>
       </c>
       <c r="I10" t="n">
-        <v>23.13522</v>
+        <v>23.333332</v>
       </c>
       <c r="J10" t="n">
-        <v>19.271471</v>
+        <v>19.436499</v>
       </c>
       <c r="K10" t="n">
         <v>1.61</v>
       </c>
       <c r="L10" t="n">
-        <v>6.333185</v>
+        <v>6.387418</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04322414027456845</v>
+        <v>0.04285714285714286</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05189017262471116</v>
+        <v>0.05144959568733153</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04626999855041504</v>
+        <v>0.04616999626159668</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005620174074296123</v>
+        <v>0.005279599425734853</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P397"/>
+  <dimension ref="A1:P406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22969,16 +22969,16 @@
         <v>9.722721999999999</v>
       </c>
       <c r="M389" t="n">
-        <v>0.02803858520900322</v>
+        <v>0.0280385852090032</v>
       </c>
       <c r="N389" t="n">
-        <v>0.03058864951768489</v>
+        <v>0.0305886495176848</v>
       </c>
       <c r="O389" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.0461699962615966</v>
       </c>
       <c r="P389" t="n">
-        <v>-0.01558134674391179</v>
+        <v>-0.0155813467439117</v>
       </c>
     </row>
     <row r="390">
@@ -23027,16 +23027,16 @@
         <v>20.98657</v>
       </c>
       <c r="M390" t="n">
-        <v>0.006223420806970231</v>
+        <v>0.0062234208069702</v>
       </c>
       <c r="N390" t="n">
-        <v>0.03108555129135982</v>
+        <v>0.0310855512913598</v>
       </c>
       <c r="O390" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.0461699962615966</v>
       </c>
       <c r="P390" t="n">
-        <v>-0.01508444497023686</v>
+        <v>-0.0150844449702368</v>
       </c>
     </row>
     <row r="391">
@@ -23085,16 +23085,16 @@
         <v>3.7913675</v>
       </c>
       <c r="M391" t="n">
-        <v>0.04562626077388594</v>
+        <v>0.0456262607738859</v>
       </c>
       <c r="N391" t="n">
         <v>0.0379590317256556</v>
       </c>
       <c r="O391" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.0461699962615966</v>
       </c>
       <c r="P391" t="n">
-        <v>-0.008210964535941077</v>
+        <v>-0.008210964535940999</v>
       </c>
     </row>
     <row r="392">
@@ -23143,16 +23143,16 @@
         <v>26.369848</v>
       </c>
       <c r="M392" t="n">
-        <v>0.01439227311848523</v>
+        <v>0.0143922731184852</v>
       </c>
       <c r="N392" t="n">
-        <v>0.04660026776322081</v>
+        <v>0.0466002677632208</v>
       </c>
       <c r="O392" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.0461699962615966</v>
       </c>
       <c r="P392" t="n">
-        <v>0.0004302715016241271</v>
+        <v>0.0004302715016241</v>
       </c>
     </row>
     <row r="393">
@@ -23201,16 +23201,16 @@
         <v>9.87823</v>
       </c>
       <c r="M393" t="n">
-        <v>0.05534112681531669</v>
+        <v>0.0553411268153166</v>
       </c>
       <c r="N393" t="n">
-        <v>0.04091419765084831</v>
+        <v>0.0409141976508483</v>
       </c>
       <c r="O393" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.0461699962615966</v>
       </c>
       <c r="P393" t="n">
-        <v>-0.005255798610748375</v>
+        <v>-0.0052557986107483</v>
       </c>
     </row>
     <row r="394">
@@ -23259,13 +23259,13 @@
         <v>6.571369</v>
       </c>
       <c r="M394" t="n">
-        <v>0.04512797866739134</v>
+        <v>0.0451279786673913</v>
       </c>
       <c r="N394" t="n">
-        <v>0.05967737826315878</v>
+        <v>0.0596773782631587</v>
       </c>
       <c r="O394" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.0461699962615966</v>
       </c>
       <c r="P394" t="n">
         <v>0.0135073820015621</v>
@@ -23317,16 +23317,16 @@
         <v>10.907869</v>
       </c>
       <c r="M395" t="n">
-        <v>0.03860829606531818</v>
+        <v>0.0386082960653181</v>
       </c>
       <c r="N395" t="n">
-        <v>0.04814497599803061</v>
+        <v>0.0481449759980306</v>
       </c>
       <c r="O395" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.0461699962615966</v>
       </c>
       <c r="P395" t="n">
-        <v>0.001974979736433929</v>
+        <v>0.0019749797364339</v>
       </c>
     </row>
     <row r="396">
@@ -23375,16 +23375,16 @@
         <v>6.387418</v>
       </c>
       <c r="M396" t="n">
-        <v>0.04285714285714286</v>
+        <v>0.0428571428571428</v>
       </c>
       <c r="N396" t="n">
-        <v>0.05144959568733153</v>
+        <v>0.0514495956873315</v>
       </c>
       <c r="O396" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.0461699962615966</v>
       </c>
       <c r="P396" t="n">
-        <v>0.005279599425734853</v>
+        <v>0.0052795994257348</v>
       </c>
     </row>
     <row r="397">
@@ -23433,16 +23433,534 @@
         <v>20.946415</v>
       </c>
       <c r="M397" t="n">
-        <v>0.02978742815436548</v>
+        <v>0.0297874281543654</v>
       </c>
       <c r="N397" t="n">
-        <v>0.05880134111851108</v>
+        <v>0.058801341118511</v>
       </c>
       <c r="O397" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.0461699962615966</v>
       </c>
       <c r="P397" t="n">
         <v>0.0126313448569144</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>2026-08-06 18:35:34</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>312.41</v>
+      </c>
+      <c r="F398" t="n">
+        <v>4559367831552</v>
+      </c>
+      <c r="G398" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H398" t="n">
+        <v>9.513070000000001</v>
+      </c>
+      <c r="I398" t="n">
+        <v>35.86797</v>
+      </c>
+      <c r="J398" t="n">
+        <v>32.84008</v>
+      </c>
+      <c r="K398" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="L398" t="n">
+        <v>9.766802</v>
+      </c>
+      <c r="M398" t="n">
+        <v>0.02788002944848116</v>
+      </c>
+      <c r="N398" t="n">
+        <v>0.03045059377100605</v>
+      </c>
+      <c r="O398" t="n">
+        <v>0.04670000076293945</v>
+      </c>
+      <c r="P398" t="n">
+        <v>-0.0162494069919334</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>2026-08-06 18:35:34</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>489.28</v>
+      </c>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H399" t="n">
+        <v>13.91754</v>
+      </c>
+      <c r="I399" t="n">
+        <v>125.456406</v>
+      </c>
+      <c r="J399" t="n">
+        <v>35.15564</v>
+      </c>
+      <c r="K399" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L399" t="inlineStr"/>
+      <c r="M399" t="n">
+        <v>0.007970896010464357</v>
+      </c>
+      <c r="N399" t="n">
+        <v>0.0284449395029431</v>
+      </c>
+      <c r="O399" t="n">
+        <v>0.04670000076293945</v>
+      </c>
+      <c r="P399" t="n">
+        <v>-0.01825506125999635</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2026-08-06 18:35:34</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>272.26</v>
+      </c>
+      <c r="F400" t="n">
+        <v>2936681791488</v>
+      </c>
+      <c r="G400" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H400" t="n">
+        <v>10.32895</v>
+      </c>
+      <c r="I400" t="n">
+        <v>21.90346</v>
+      </c>
+      <c r="J400" t="n">
+        <v>26.358925</v>
+      </c>
+      <c r="K400" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="L400" t="n">
+        <v>3.7859447</v>
+      </c>
+      <c r="M400" t="n">
+        <v>0.04565488870932197</v>
+      </c>
+      <c r="N400" t="n">
+        <v>0.03793781679277162</v>
+      </c>
+      <c r="O400" t="n">
+        <v>0.04670000076293945</v>
+      </c>
+      <c r="P400" t="n">
+        <v>-0.008762183970167835</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>2026-08-06 18:35:34</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>420.565</v>
+      </c>
+      <c r="F401" t="n">
+        <v>2000871751680</v>
+      </c>
+      <c r="G401" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H401" t="n">
+        <v>19.49196</v>
+      </c>
+      <c r="I401" t="n">
+        <v>69.8613</v>
+      </c>
+      <c r="J401" t="n">
+        <v>21.576332</v>
+      </c>
+      <c r="K401" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L401" t="n">
+        <v>26.513905</v>
+      </c>
+      <c r="M401" t="n">
+        <v>0.01431407749099426</v>
+      </c>
+      <c r="N401" t="n">
+        <v>0.04634708071285057</v>
+      </c>
+      <c r="O401" t="n">
+        <v>0.04670000076293945</v>
+      </c>
+      <c r="P401" t="n">
+        <v>-0.0003529200500888841</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>2026-08-06 18:35:34</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>356.62</v>
+      </c>
+      <c r="F402" t="n">
+        <v>4361439412224</v>
+      </c>
+      <c r="G402" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H402" t="n">
+        <v>14.73443</v>
+      </c>
+      <c r="I402" t="n">
+        <v>17.90261</v>
+      </c>
+      <c r="J402" t="n">
+        <v>24.203175</v>
+      </c>
+      <c r="K402" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L402" t="n">
+        <v>9.781952</v>
+      </c>
+      <c r="M402" t="n">
+        <v>0.05585777578374741</v>
+      </c>
+      <c r="N402" t="n">
+        <v>0.0413168919297852</v>
+      </c>
+      <c r="O402" t="n">
+        <v>0.04670000076293945</v>
+      </c>
+      <c r="P402" t="n">
+        <v>-0.005383108833154251</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>2026-08-06 18:35:34</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>589.9</v>
+      </c>
+      <c r="F403" t="n">
+        <v>1502773903360</v>
+      </c>
+      <c r="G403" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="H403" t="n">
+        <v>35.13625</v>
+      </c>
+      <c r="I403" t="n">
+        <v>22.218458</v>
+      </c>
+      <c r="J403" t="n">
+        <v>16.788929</v>
+      </c>
+      <c r="K403" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L403" t="n">
+        <v>6.583981</v>
+      </c>
+      <c r="M403" t="n">
+        <v>0.04500762841159519</v>
+      </c>
+      <c r="N403" t="n">
+        <v>0.05956306153585353</v>
+      </c>
+      <c r="O403" t="n">
+        <v>0.04670000076293945</v>
+      </c>
+      <c r="P403" t="n">
+        <v>0.01286306077291408</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>2026-08-06 18:35:34</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>499.86</v>
+      </c>
+      <c r="F404" t="n">
+        <v>3711733071872</v>
+      </c>
+      <c r="G404" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H404" t="n">
+        <v>23.46875</v>
+      </c>
+      <c r="I404" t="n">
+        <v>27.862875</v>
+      </c>
+      <c r="J404" t="n">
+        <v>21.298962</v>
+      </c>
+      <c r="K404" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L404" t="n">
+        <v>11.185343</v>
+      </c>
+      <c r="M404" t="n">
+        <v>0.03589004921377986</v>
+      </c>
+      <c r="N404" t="n">
+        <v>0.04695064618093066</v>
+      </c>
+      <c r="O404" t="n">
+        <v>0.04670000076293945</v>
+      </c>
+      <c r="P404" t="n">
+        <v>0.0002506454179912049</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>2026-08-06 18:35:34</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>73.69</v>
+      </c>
+      <c r="F405" t="n">
+        <v>306840731648</v>
+      </c>
+      <c r="G405" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H405" t="n">
+        <v>3.81756</v>
+      </c>
+      <c r="I405" t="n">
+        <v>23.172956</v>
+      </c>
+      <c r="J405" t="n">
+        <v>19.302906</v>
+      </c>
+      <c r="K405" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="L405" t="n">
+        <v>6.343516</v>
+      </c>
+      <c r="M405" t="n">
+        <v>0.04315375220518388</v>
+      </c>
+      <c r="N405" t="n">
+        <v>0.05180567241145338</v>
+      </c>
+      <c r="O405" t="n">
+        <v>0.04670000076293945</v>
+      </c>
+      <c r="P405" t="n">
+        <v>0.005105671648513929</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>2026-08-06 18:35:34</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>218.99</v>
+      </c>
+      <c r="F406" t="n">
+        <v>5304156684288</v>
+      </c>
+      <c r="G406" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H406" t="n">
+        <v>12.89043</v>
+      </c>
+      <c r="I406" t="n">
+        <v>33.535988</v>
+      </c>
+      <c r="J406" t="n">
+        <v>16.988571</v>
+      </c>
+      <c r="K406" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L406" t="n">
+        <v>20.924438</v>
+      </c>
+      <c r="M406" t="n">
+        <v>0.02981871318325038</v>
+      </c>
+      <c r="N406" t="n">
+        <v>0.05886309877163341</v>
+      </c>
+      <c r="O406" t="n">
+        <v>0.04670000076293945</v>
+      </c>
+      <c r="P406" t="n">
+        <v>0.01216309800869395</v>
       </c>
     </row>
   </sheetData>
@@ -23544,12 +24062,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-05 16:27:56</t>
+          <t>2026-08-06 18:35:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -23563,51 +24081,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>360.13</v>
+        <v>356.62</v>
       </c>
       <c r="F2" t="n">
-        <v>4404366802944</v>
+        <v>4361439412224</v>
       </c>
       <c r="G2" t="n">
-        <v>19.93</v>
+        <v>19.92</v>
       </c>
       <c r="H2" t="n">
         <v>14.73443</v>
       </c>
       <c r="I2" t="n">
-        <v>18.069744</v>
+        <v>17.90261</v>
       </c>
       <c r="J2" t="n">
-        <v>24.441393</v>
+        <v>24.203175</v>
       </c>
       <c r="K2" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="L2" t="n">
-        <v>9.87823</v>
+        <v>9.781952</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05534112681531669</v>
+        <v>0.05585777578374741</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04091419765084831</v>
+        <v>0.0413168919297852</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.04670000076293945</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005255798610748375</v>
+        <v>-0.005383108833154251</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-05 16:27:56</t>
+          <t>2026-08-06 18:35:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -23621,51 +24139,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>487.46</v>
+        <v>499.86</v>
       </c>
       <c r="F3" t="n">
-        <v>3619656564736</v>
+        <v>3711733071872</v>
       </c>
       <c r="G3" t="n">
-        <v>18.82</v>
+        <v>17.94</v>
       </c>
       <c r="H3" t="n">
         <v>23.46875</v>
       </c>
       <c r="I3" t="n">
-        <v>25.901169</v>
+        <v>27.862875</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7706</v>
+        <v>21.298962</v>
       </c>
       <c r="K3" t="n">
         <v>1.59</v>
       </c>
       <c r="L3" t="n">
-        <v>10.907869</v>
+        <v>11.185343</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03860829606531818</v>
+        <v>0.03589004921377986</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04814497599803061</v>
+        <v>0.04695064618093066</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.04670000076293945</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001974979736433929</v>
+        <v>0.0002506454179912049</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:27:56</t>
+          <t>2026-08-06 18:35:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -23679,51 +24197,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>588.77</v>
+        <v>589.9</v>
       </c>
       <c r="F4" t="n">
-        <v>1499895300096</v>
+        <v>1502773903360</v>
       </c>
       <c r="G4" t="n">
-        <v>26.57</v>
+        <v>26.55</v>
       </c>
       <c r="H4" t="n">
         <v>35.13625</v>
       </c>
       <c r="I4" t="n">
-        <v>22.159203</v>
+        <v>22.218458</v>
       </c>
       <c r="J4" t="n">
-        <v>16.75677</v>
+        <v>16.788929</v>
       </c>
       <c r="K4" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="L4" t="n">
-        <v>6.571369</v>
+        <v>6.583981</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04512797866739134</v>
+        <v>0.04500762841159519</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05967737826315878</v>
+        <v>0.05956306153585353</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.04670000076293945</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0135073820015621</v>
+        <v>0.01286306077291408</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-05 16:27:56</t>
+          <t>2026-08-06 18:35:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -23737,51 +24255,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>272.65</v>
+        <v>272.26</v>
       </c>
       <c r="F5" t="n">
-        <v>2940888154112</v>
+        <v>2936681791488</v>
       </c>
       <c r="G5" t="n">
-        <v>12.44</v>
+        <v>12.43</v>
       </c>
       <c r="H5" t="n">
-        <v>10.34953</v>
+        <v>10.32895</v>
       </c>
       <c r="I5" t="n">
-        <v>21.917202</v>
+        <v>21.90346</v>
       </c>
       <c r="J5" t="n">
-        <v>26.34419</v>
+        <v>26.358925</v>
       </c>
       <c r="K5" t="n">
-        <v>1.46</v>
+        <v>1.98</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7913675</v>
+        <v>3.7859447</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04562626077388594</v>
+        <v>0.04565488870932197</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0379590317256556</v>
+        <v>0.03793781679277162</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.04670000076293945</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.008210964535941077</v>
+        <v>-0.008762183970167835</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-05 16:27:56</t>
+          <t>2026-08-06 18:35:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -23795,51 +24313,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>311</v>
+        <v>312.41</v>
       </c>
       <c r="F6" t="n">
-        <v>4538790051840</v>
+        <v>4559367831552</v>
       </c>
       <c r="G6" t="n">
-        <v>8.720000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>9.513070000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>35.66514</v>
+        <v>35.86797</v>
       </c>
       <c r="J6" t="n">
-        <v>32.691864</v>
+        <v>32.84008</v>
       </c>
       <c r="K6" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="L6" t="n">
-        <v>9.722721999999999</v>
+        <v>9.766802</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02803858520900322</v>
+        <v>0.02788002944848116</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03058864951768489</v>
+        <v>0.03045059377100605</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.04670000076293945</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01558134674391179</v>
+        <v>-0.0162494069919334</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-05 16:27:56</t>
+          <t>2026-08-06 18:35:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -23853,10 +24371,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219.22</v>
+        <v>218.99</v>
       </c>
       <c r="F7" t="n">
-        <v>5309727768576</v>
+        <v>5304156684288</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
@@ -23865,39 +24383,39 @@
         <v>12.89043</v>
       </c>
       <c r="I7" t="n">
-        <v>33.57121</v>
+        <v>33.535988</v>
       </c>
       <c r="J7" t="n">
-        <v>17.006414</v>
+        <v>16.988571</v>
       </c>
       <c r="K7" t="n">
         <v>0.57</v>
       </c>
       <c r="L7" t="n">
-        <v>20.946415</v>
+        <v>20.924438</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02978742815436548</v>
+        <v>0.02981871318325038</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05880134111851108</v>
+        <v>0.05886309877163341</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.04670000076293945</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0126313448569144</v>
+        <v>0.01216309800869395</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-05 16:27:56</t>
+          <t>2026-08-06 18:35:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -23911,51 +24429,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>482.05</v>
-      </c>
-      <c r="F8" t="n">
-        <v>786030985216</v>
-      </c>
+        <v>489.28</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="H8" t="n">
-        <v>14.98479</v>
+        <v>13.91754</v>
       </c>
       <c r="I8" t="n">
-        <v>160.68333</v>
+        <v>125.456406</v>
       </c>
       <c r="J8" t="n">
-        <v>32.169285</v>
+        <v>35.15564</v>
       </c>
       <c r="K8" t="n">
         <v>1.14</v>
       </c>
-      <c r="L8" t="n">
-        <v>20.98657</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0.006223420806970231</v>
+        <v>0.007970896010464357</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03108555129135982</v>
+        <v>0.0284449395029431</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.04670000076293945</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01508444497023686</v>
+        <v>-0.01825506125999635</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-05 16:27:56</t>
+          <t>2026-08-06 18:35:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -23969,10 +24483,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>418.28</v>
+        <v>420.565</v>
       </c>
       <c r="F9" t="n">
-        <v>1990000640000</v>
+        <v>2000871751680</v>
       </c>
       <c r="G9" t="n">
         <v>6.02</v>
@@ -23981,39 +24495,39 @@
         <v>19.49196</v>
       </c>
       <c r="I9" t="n">
-        <v>69.48173</v>
+        <v>69.8613</v>
       </c>
       <c r="J9" t="n">
-        <v>21.459103</v>
+        <v>21.576332</v>
       </c>
       <c r="K9" t="n">
         <v>0.44</v>
       </c>
       <c r="L9" t="n">
-        <v>26.369848</v>
+        <v>26.513905</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01439227311848523</v>
+        <v>0.01431407749099426</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04660026776322081</v>
+        <v>0.04634708071285057</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.04670000076293945</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0004302715016241271</v>
+        <v>-0.0003529200500888841</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-05 16:27:56</t>
+          <t>2026-08-06 18:35:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -24027,10 +24541,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>74.2</v>
+        <v>73.69</v>
       </c>
       <c r="F10" t="n">
-        <v>308964294656</v>
+        <v>306840731648</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -24039,28 +24553,28 @@
         <v>3.81756</v>
       </c>
       <c r="I10" t="n">
-        <v>23.333332</v>
+        <v>23.172956</v>
       </c>
       <c r="J10" t="n">
-        <v>19.436499</v>
+        <v>19.302906</v>
       </c>
       <c r="K10" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="L10" t="n">
-        <v>6.387418</v>
+        <v>6.343516</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04285714285714286</v>
+        <v>0.04315375220518388</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05144959568733153</v>
+        <v>0.05180567241145338</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04616999626159668</v>
+        <v>0.04670000076293945</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005279599425734853</v>
+        <v>0.005105671648513929</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P406"/>
+  <dimension ref="A1:P415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23491,13 +23491,13 @@
         <v>9.766802</v>
       </c>
       <c r="M398" t="n">
-        <v>0.02788002944848116</v>
+        <v>0.0278800294484811</v>
       </c>
       <c r="N398" t="n">
-        <v>0.03045059377100605</v>
+        <v>0.030450593771006</v>
       </c>
       <c r="O398" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.0467000007629394</v>
       </c>
       <c r="P398" t="n">
         <v>-0.0162494069919334</v>
@@ -23545,16 +23545,16 @@
       </c>
       <c r="L399" t="inlineStr"/>
       <c r="M399" t="n">
-        <v>0.007970896010464357</v>
+        <v>0.007970896010464299</v>
       </c>
       <c r="N399" t="n">
         <v>0.0284449395029431</v>
       </c>
       <c r="O399" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.0467000007629394</v>
       </c>
       <c r="P399" t="n">
-        <v>-0.01825506125999635</v>
+        <v>-0.0182550612599963</v>
       </c>
     </row>
     <row r="400">
@@ -23603,16 +23603,16 @@
         <v>3.7859447</v>
       </c>
       <c r="M400" t="n">
-        <v>0.04565488870932197</v>
+        <v>0.0456548887093219</v>
       </c>
       <c r="N400" t="n">
-        <v>0.03793781679277162</v>
+        <v>0.0379378167927716</v>
       </c>
       <c r="O400" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.0467000007629394</v>
       </c>
       <c r="P400" t="n">
-        <v>-0.008762183970167835</v>
+        <v>-0.0087621839701678</v>
       </c>
     </row>
     <row r="401">
@@ -23661,16 +23661,16 @@
         <v>26.513905</v>
       </c>
       <c r="M401" t="n">
-        <v>0.01431407749099426</v>
+        <v>0.0143140774909942</v>
       </c>
       <c r="N401" t="n">
-        <v>0.04634708071285057</v>
+        <v>0.0463470807128505</v>
       </c>
       <c r="O401" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.0467000007629394</v>
       </c>
       <c r="P401" t="n">
-        <v>-0.0003529200500888841</v>
+        <v>-0.0003529200500888</v>
       </c>
     </row>
     <row r="402">
@@ -23719,16 +23719,16 @@
         <v>9.781952</v>
       </c>
       <c r="M402" t="n">
-        <v>0.05585777578374741</v>
+        <v>0.0558577757837474</v>
       </c>
       <c r="N402" t="n">
         <v>0.0413168919297852</v>
       </c>
       <c r="O402" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.0467000007629394</v>
       </c>
       <c r="P402" t="n">
-        <v>-0.005383108833154251</v>
+        <v>-0.0053831088331542</v>
       </c>
     </row>
     <row r="403">
@@ -23777,16 +23777,16 @@
         <v>6.583981</v>
       </c>
       <c r="M403" t="n">
-        <v>0.04500762841159519</v>
+        <v>0.0450076284115951</v>
       </c>
       <c r="N403" t="n">
-        <v>0.05956306153585353</v>
+        <v>0.0595630615358535</v>
       </c>
       <c r="O403" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.0467000007629394</v>
       </c>
       <c r="P403" t="n">
-        <v>0.01286306077291408</v>
+        <v>0.012863060772914</v>
       </c>
     </row>
     <row r="404">
@@ -23835,16 +23835,16 @@
         <v>11.185343</v>
       </c>
       <c r="M404" t="n">
-        <v>0.03589004921377986</v>
+        <v>0.0358900492137798</v>
       </c>
       <c r="N404" t="n">
-        <v>0.04695064618093066</v>
+        <v>0.0469506461809306</v>
       </c>
       <c r="O404" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.0467000007629394</v>
       </c>
       <c r="P404" t="n">
-        <v>0.0002506454179912049</v>
+        <v>0.0002506454179912</v>
       </c>
     </row>
     <row r="405">
@@ -23893,16 +23893,16 @@
         <v>6.343516</v>
       </c>
       <c r="M405" t="n">
-        <v>0.04315375220518388</v>
+        <v>0.0431537522051838</v>
       </c>
       <c r="N405" t="n">
-        <v>0.05180567241145338</v>
+        <v>0.0518056724114533</v>
       </c>
       <c r="O405" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.0467000007629394</v>
       </c>
       <c r="P405" t="n">
-        <v>0.005105671648513929</v>
+        <v>0.0051056716485139</v>
       </c>
     </row>
     <row r="406">
@@ -23951,16 +23951,538 @@
         <v>20.924438</v>
       </c>
       <c r="M406" t="n">
-        <v>0.02981871318325038</v>
+        <v>0.0298187131832503</v>
       </c>
       <c r="N406" t="n">
-        <v>0.05886309877163341</v>
+        <v>0.0588630987716334</v>
       </c>
       <c r="O406" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.0467000007629394</v>
       </c>
       <c r="P406" t="n">
-        <v>0.01216309800869395</v>
+        <v>0.0121630980086939</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:01:15</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>313.33</v>
+      </c>
+      <c r="F407" t="n">
+        <v>4572794322944</v>
+      </c>
+      <c r="G407" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H407" t="n">
+        <v>9.513070000000001</v>
+      </c>
+      <c r="I407" t="n">
+        <v>35.93234</v>
+      </c>
+      <c r="J407" t="n">
+        <v>32.93679</v>
+      </c>
+      <c r="K407" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L407" t="n">
+        <v>9.795564000000001</v>
+      </c>
+      <c r="M407" t="n">
+        <v>0.0278300832987585</v>
+      </c>
+      <c r="N407" t="n">
+        <v>0.03036118469345419</v>
+      </c>
+      <c r="O407" t="n">
+        <v>0.04659999847412109</v>
+      </c>
+      <c r="P407" t="n">
+        <v>-0.0162388137806669</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:01:15</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>483.36</v>
+      </c>
+      <c r="F408" t="n">
+        <v>789073100800</v>
+      </c>
+      <c r="G408" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H408" t="n">
+        <v>15.45987</v>
+      </c>
+      <c r="I408" t="n">
+        <v>123.621475</v>
+      </c>
+      <c r="J408" t="n">
+        <v>31.265461</v>
+      </c>
+      <c r="K408" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L408" t="n">
+        <v>19.103573</v>
+      </c>
+      <c r="M408" t="n">
+        <v>0.008089208871234691</v>
+      </c>
+      <c r="N408" t="n">
+        <v>0.03198417328699106</v>
+      </c>
+      <c r="O408" t="n">
+        <v>0.04659999847412109</v>
+      </c>
+      <c r="P408" t="n">
+        <v>-0.01461582518713003</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:01:15</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>274.48</v>
+      </c>
+      <c r="F409" t="n">
+        <v>2960627335168</v>
+      </c>
+      <c r="G409" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="H409" t="n">
+        <v>10.33054</v>
+      </c>
+      <c r="I409" t="n">
+        <v>22.06431</v>
+      </c>
+      <c r="J409" t="n">
+        <v>26.569765</v>
+      </c>
+      <c r="K409" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L409" t="n">
+        <v>3.8168151</v>
+      </c>
+      <c r="M409" t="n">
+        <v>0.04532206353832701</v>
+      </c>
+      <c r="N409" t="n">
+        <v>0.0376367677062081</v>
+      </c>
+      <c r="O409" t="n">
+        <v>0.04659999847412109</v>
+      </c>
+      <c r="P409" t="n">
+        <v>-0.008963230767912993</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:01:15</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>427.76</v>
+      </c>
+      <c r="F410" t="n">
+        <v>2035102646272</v>
+      </c>
+      <c r="G410" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H410" t="n">
+        <v>19.49196</v>
+      </c>
+      <c r="I410" t="n">
+        <v>71.174706</v>
+      </c>
+      <c r="J410" t="n">
+        <v>21.94546</v>
+      </c>
+      <c r="K410" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L410" t="n">
+        <v>26.967505</v>
+      </c>
+      <c r="M410" t="n">
+        <v>0.01404993454273424</v>
+      </c>
+      <c r="N410" t="n">
+        <v>0.04556751449410885</v>
+      </c>
+      <c r="O410" t="n">
+        <v>0.04659999847412109</v>
+      </c>
+      <c r="P410" t="n">
+        <v>-0.001032483980012246</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:01:15</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>353.47</v>
+      </c>
+      <c r="F411" t="n">
+        <v>4322915254272</v>
+      </c>
+      <c r="G411" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="H411" t="n">
+        <v>14.73443</v>
+      </c>
+      <c r="I411" t="n">
+        <v>17.726679</v>
+      </c>
+      <c r="J411" t="n">
+        <v>23.989391</v>
+      </c>
+      <c r="K411" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L411" t="n">
+        <v>9.695548</v>
+      </c>
+      <c r="M411" t="n">
+        <v>0.05641214247319433</v>
+      </c>
+      <c r="N411" t="n">
+        <v>0.04168509350157015</v>
+      </c>
+      <c r="O411" t="n">
+        <v>0.04659999847412109</v>
+      </c>
+      <c r="P411" t="n">
+        <v>-0.004914904972550947</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:01:15</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>592.1</v>
+      </c>
+      <c r="F412" t="n">
+        <v>1508378279936</v>
+      </c>
+      <c r="G412" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="H412" t="n">
+        <v>35.13625</v>
+      </c>
+      <c r="I412" t="n">
+        <v>22.301317</v>
+      </c>
+      <c r="J412" t="n">
+        <v>16.851542</v>
+      </c>
+      <c r="K412" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L412" t="n">
+        <v>6.6085353</v>
+      </c>
+      <c r="M412" t="n">
+        <v>0.04484039858132072</v>
+      </c>
+      <c r="N412" t="n">
+        <v>0.05934174970444181</v>
+      </c>
+      <c r="O412" t="n">
+        <v>0.04659999847412109</v>
+      </c>
+      <c r="P412" t="n">
+        <v>0.01274175123032072</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:01:15</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>499.99</v>
+      </c>
+      <c r="F413" t="n">
+        <v>3712698548224</v>
+      </c>
+      <c r="G413" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H413" t="n">
+        <v>23.4742</v>
+      </c>
+      <c r="I413" t="n">
+        <v>27.870121</v>
+      </c>
+      <c r="J413" t="n">
+        <v>21.299555</v>
+      </c>
+      <c r="K413" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L413" t="n">
+        <v>11.188252</v>
+      </c>
+      <c r="M413" t="n">
+        <v>0.03588071761435229</v>
+      </c>
+      <c r="N413" t="n">
+        <v>0.04694933898677973</v>
+      </c>
+      <c r="O413" t="n">
+        <v>0.04659999847412109</v>
+      </c>
+      <c r="P413" t="n">
+        <v>0.0003493405126586413</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:01:15</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E414" t="n">
+        <v>74.14</v>
+      </c>
+      <c r="F414" t="n">
+        <v>308714471424</v>
+      </c>
+      <c r="G414" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H414" t="n">
+        <v>3.81728</v>
+      </c>
+      <c r="I414" t="n">
+        <v>23.314465</v>
+      </c>
+      <c r="J414" t="n">
+        <v>19.422207</v>
+      </c>
+      <c r="K414" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L414" t="n">
+        <v>6.382253</v>
+      </c>
+      <c r="M414" t="n">
+        <v>0.0428918262746156</v>
+      </c>
+      <c r="N414" t="n">
+        <v>0.05148745616401403</v>
+      </c>
+      <c r="O414" t="n">
+        <v>0.04659999847412109</v>
+      </c>
+      <c r="P414" t="n">
+        <v>0.004887457689892932</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:01:15</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E415" t="n">
+        <v>223.96</v>
+      </c>
+      <c r="F415" t="n">
+        <v>5424535306240</v>
+      </c>
+      <c r="G415" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H415" t="n">
+        <v>12.89043</v>
+      </c>
+      <c r="I415" t="n">
+        <v>34.29709</v>
+      </c>
+      <c r="J415" t="n">
+        <v>17.37413</v>
+      </c>
+      <c r="K415" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L415" t="n">
+        <v>21.39932</v>
+      </c>
+      <c r="M415" t="n">
+        <v>0.02915699232005715</v>
+      </c>
+      <c r="N415" t="n">
+        <v>0.05755684050723343</v>
+      </c>
+      <c r="O415" t="n">
+        <v>0.04659999847412109</v>
+      </c>
+      <c r="P415" t="n">
+        <v>0.01095684203311234</v>
       </c>
     </row>
   </sheetData>
@@ -24062,12 +24584,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-06 18:35:34</t>
+          <t>2026-08-07 16:01:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -24081,51 +24603,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>356.62</v>
+        <v>353.47</v>
       </c>
       <c r="F2" t="n">
-        <v>4361439412224</v>
+        <v>4322915254272</v>
       </c>
       <c r="G2" t="n">
-        <v>19.92</v>
+        <v>19.94</v>
       </c>
       <c r="H2" t="n">
         <v>14.73443</v>
       </c>
       <c r="I2" t="n">
-        <v>17.90261</v>
+        <v>17.726679</v>
       </c>
       <c r="J2" t="n">
-        <v>24.203175</v>
+        <v>23.989391</v>
       </c>
       <c r="K2" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="L2" t="n">
-        <v>9.781952</v>
+        <v>9.695548</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05585777578374741</v>
+        <v>0.05641214247319433</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0413168919297852</v>
+        <v>0.04168509350157015</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.04659999847412109</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005383108833154251</v>
+        <v>-0.004914904972550947</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-06 18:35:34</t>
+          <t>2026-08-07 16:01:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -24139,51 +24661,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>499.86</v>
+        <v>499.99</v>
       </c>
       <c r="F3" t="n">
-        <v>3711733071872</v>
+        <v>3712698548224</v>
       </c>
       <c r="G3" t="n">
         <v>17.94</v>
       </c>
       <c r="H3" t="n">
-        <v>23.46875</v>
+        <v>23.4742</v>
       </c>
       <c r="I3" t="n">
-        <v>27.862875</v>
+        <v>27.870121</v>
       </c>
       <c r="J3" t="n">
-        <v>21.298962</v>
+        <v>21.299555</v>
       </c>
       <c r="K3" t="n">
         <v>1.59</v>
       </c>
       <c r="L3" t="n">
-        <v>11.185343</v>
+        <v>11.188252</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03589004921377986</v>
+        <v>0.03588071761435229</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04695064618093066</v>
+        <v>0.04694933898677973</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.04659999847412109</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0002506454179912049</v>
+        <v>0.0003493405126586413</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-06 18:35:34</t>
+          <t>2026-08-07 16:01:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -24197,10 +24719,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>589.9</v>
+        <v>592.1</v>
       </c>
       <c r="F4" t="n">
-        <v>1502773903360</v>
+        <v>1508378279936</v>
       </c>
       <c r="G4" t="n">
         <v>26.55</v>
@@ -24209,39 +24731,39 @@
         <v>35.13625</v>
       </c>
       <c r="I4" t="n">
-        <v>22.218458</v>
+        <v>22.301317</v>
       </c>
       <c r="J4" t="n">
-        <v>16.788929</v>
+        <v>16.851542</v>
       </c>
       <c r="K4" t="n">
         <v>0.88</v>
       </c>
       <c r="L4" t="n">
-        <v>6.583981</v>
+        <v>6.6085353</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04500762841159519</v>
+        <v>0.04484039858132072</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05956306153585353</v>
+        <v>0.05934174970444181</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.04659999847412109</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01286306077291408</v>
+        <v>0.01274175123032072</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-06 18:35:34</t>
+          <t>2026-08-07 16:01:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -24255,51 +24777,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>272.26</v>
+        <v>274.48</v>
       </c>
       <c r="F5" t="n">
-        <v>2936681791488</v>
+        <v>2960627335168</v>
       </c>
       <c r="G5" t="n">
-        <v>12.43</v>
+        <v>12.44</v>
       </c>
       <c r="H5" t="n">
-        <v>10.32895</v>
+        <v>10.33054</v>
       </c>
       <c r="I5" t="n">
-        <v>21.90346</v>
+        <v>22.06431</v>
       </c>
       <c r="J5" t="n">
-        <v>26.358925</v>
+        <v>26.569765</v>
       </c>
       <c r="K5" t="n">
-        <v>1.98</v>
+        <v>1.45</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7859447</v>
+        <v>3.8168151</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04565488870932197</v>
+        <v>0.04532206353832701</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03793781679277162</v>
+        <v>0.0376367677062081</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.04659999847412109</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.008762183970167835</v>
+        <v>-0.008963230767912993</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-06 18:35:34</t>
+          <t>2026-08-07 16:01:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -24313,51 +24835,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>312.41</v>
+        <v>313.33</v>
       </c>
       <c r="F6" t="n">
-        <v>4559367831552</v>
+        <v>4572794322944</v>
       </c>
       <c r="G6" t="n">
-        <v>8.710000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>9.513070000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>35.86797</v>
+        <v>35.93234</v>
       </c>
       <c r="J6" t="n">
-        <v>32.84008</v>
+        <v>32.93679</v>
       </c>
       <c r="K6" t="n">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="L6" t="n">
-        <v>9.766802</v>
+        <v>9.795564000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02788002944848116</v>
+        <v>0.0278300832987585</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03045059377100605</v>
+        <v>0.03036118469345419</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.04659999847412109</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0162494069919334</v>
+        <v>-0.0162388137806669</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-06 18:35:34</t>
+          <t>2026-08-07 16:01:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -24371,10 +24893,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>218.99</v>
+        <v>223.96</v>
       </c>
       <c r="F7" t="n">
-        <v>5304156684288</v>
+        <v>5424535306240</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
@@ -24383,39 +24905,39 @@
         <v>12.89043</v>
       </c>
       <c r="I7" t="n">
-        <v>33.535988</v>
+        <v>34.29709</v>
       </c>
       <c r="J7" t="n">
-        <v>16.988571</v>
+        <v>17.37413</v>
       </c>
       <c r="K7" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="L7" t="n">
-        <v>20.924438</v>
+        <v>21.39932</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02981871318325038</v>
+        <v>0.02915699232005715</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05886309877163341</v>
+        <v>0.05755684050723343</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.04659999847412109</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01216309800869395</v>
+        <v>0.01095684203311234</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-06 18:35:34</t>
+          <t>2026-08-07 16:01:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -24429,47 +24951,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>489.28</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>483.36</v>
+      </c>
+      <c r="F8" t="n">
+        <v>789073100800</v>
+      </c>
       <c r="G8" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="H8" t="n">
-        <v>13.91754</v>
+        <v>15.45987</v>
       </c>
       <c r="I8" t="n">
-        <v>125.456406</v>
+        <v>123.621475</v>
       </c>
       <c r="J8" t="n">
-        <v>35.15564</v>
+        <v>31.265461</v>
       </c>
       <c r="K8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>1.13</v>
+      </c>
+      <c r="L8" t="n">
+        <v>19.103573</v>
+      </c>
       <c r="M8" t="n">
-        <v>0.007970896010464357</v>
+        <v>0.008089208871234691</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0284449395029431</v>
+        <v>0.03198417328699106</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.04659999847412109</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01825506125999635</v>
+        <v>-0.01461582518713003</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-06 18:35:34</t>
+          <t>2026-08-07 16:01:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -24483,51 +25009,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>420.565</v>
+        <v>427.76</v>
       </c>
       <c r="F9" t="n">
-        <v>2000871751680</v>
+        <v>2035102646272</v>
       </c>
       <c r="G9" t="n">
-        <v>6.02</v>
+        <v>6.01</v>
       </c>
       <c r="H9" t="n">
         <v>19.49196</v>
       </c>
       <c r="I9" t="n">
-        <v>69.8613</v>
+        <v>71.174706</v>
       </c>
       <c r="J9" t="n">
-        <v>21.576332</v>
+        <v>21.94546</v>
       </c>
       <c r="K9" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="L9" t="n">
-        <v>26.513905</v>
+        <v>26.967505</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01431407749099426</v>
+        <v>0.01404993454273424</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04634708071285057</v>
+        <v>0.04556751449410885</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.04659999847412109</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0003529200500888841</v>
+        <v>-0.001032483980012246</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-06 18:35:34</t>
+          <t>2026-08-07 16:01:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -24541,40 +25067,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73.69</v>
+        <v>74.14</v>
       </c>
       <c r="F10" t="n">
-        <v>306840731648</v>
+        <v>308714471424</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.81756</v>
+        <v>3.81728</v>
       </c>
       <c r="I10" t="n">
-        <v>23.172956</v>
+        <v>23.314465</v>
       </c>
       <c r="J10" t="n">
-        <v>19.302906</v>
+        <v>19.422207</v>
       </c>
       <c r="K10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="L10" t="n">
-        <v>6.343516</v>
+        <v>6.382253</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04315375220518388</v>
+        <v>0.0428918262746156</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05180567241145338</v>
+        <v>0.05148745616401403</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04670000076293945</v>
+        <v>0.04659999847412109</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005105671648513929</v>
+        <v>0.004887457689892932</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P415"/>
+  <dimension ref="A1:P424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24012,10 +24012,10 @@
         <v>0.0278300832987585</v>
       </c>
       <c r="N407" t="n">
-        <v>0.03036118469345419</v>
+        <v>0.0303611846934541</v>
       </c>
       <c r="O407" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.046599998474121</v>
       </c>
       <c r="P407" t="n">
         <v>-0.0162388137806669</v>
@@ -24067,16 +24067,16 @@
         <v>19.103573</v>
       </c>
       <c r="M408" t="n">
-        <v>0.008089208871234691</v>
+        <v>0.008089208871234601</v>
       </c>
       <c r="N408" t="n">
-        <v>0.03198417328699106</v>
+        <v>0.031984173286991</v>
       </c>
       <c r="O408" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.046599998474121</v>
       </c>
       <c r="P408" t="n">
-        <v>-0.01461582518713003</v>
+        <v>-0.01461582518713</v>
       </c>
     </row>
     <row r="409">
@@ -24125,16 +24125,16 @@
         <v>3.8168151</v>
       </c>
       <c r="M409" t="n">
-        <v>0.04532206353832701</v>
+        <v>0.045322063538327</v>
       </c>
       <c r="N409" t="n">
         <v>0.0376367677062081</v>
       </c>
       <c r="O409" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.046599998474121</v>
       </c>
       <c r="P409" t="n">
-        <v>-0.008963230767912993</v>
+        <v>-0.008963230767912901</v>
       </c>
     </row>
     <row r="410">
@@ -24183,16 +24183,16 @@
         <v>26.967505</v>
       </c>
       <c r="M410" t="n">
-        <v>0.01404993454273424</v>
+        <v>0.0140499345427342</v>
       </c>
       <c r="N410" t="n">
-        <v>0.04556751449410885</v>
+        <v>0.0455675144941088</v>
       </c>
       <c r="O410" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.046599998474121</v>
       </c>
       <c r="P410" t="n">
-        <v>-0.001032483980012246</v>
+        <v>-0.0010324839800122</v>
       </c>
     </row>
     <row r="411">
@@ -24241,16 +24241,16 @@
         <v>9.695548</v>
       </c>
       <c r="M411" t="n">
-        <v>0.05641214247319433</v>
+        <v>0.0564121424731943</v>
       </c>
       <c r="N411" t="n">
-        <v>0.04168509350157015</v>
+        <v>0.0416850935015701</v>
       </c>
       <c r="O411" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.046599998474121</v>
       </c>
       <c r="P411" t="n">
-        <v>-0.004914904972550947</v>
+        <v>-0.0049149049725509</v>
       </c>
     </row>
     <row r="412">
@@ -24299,16 +24299,16 @@
         <v>6.6085353</v>
       </c>
       <c r="M412" t="n">
-        <v>0.04484039858132072</v>
+        <v>0.0448403985813207</v>
       </c>
       <c r="N412" t="n">
-        <v>0.05934174970444181</v>
+        <v>0.0593417497044418</v>
       </c>
       <c r="O412" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.046599998474121</v>
       </c>
       <c r="P412" t="n">
-        <v>0.01274175123032072</v>
+        <v>0.0127417512303207</v>
       </c>
     </row>
     <row r="413">
@@ -24357,16 +24357,16 @@
         <v>11.188252</v>
       </c>
       <c r="M413" t="n">
-        <v>0.03588071761435229</v>
+        <v>0.0358807176143522</v>
       </c>
       <c r="N413" t="n">
-        <v>0.04694933898677973</v>
+        <v>0.0469493389867797</v>
       </c>
       <c r="O413" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.046599998474121</v>
       </c>
       <c r="P413" t="n">
-        <v>0.0003493405126586413</v>
+        <v>0.0003493405126586</v>
       </c>
     </row>
     <row r="414">
@@ -24415,16 +24415,16 @@
         <v>6.382253</v>
       </c>
       <c r="M414" t="n">
-        <v>0.0428918262746156</v>
+        <v>0.0428918262746155</v>
       </c>
       <c r="N414" t="n">
-        <v>0.05148745616401403</v>
+        <v>0.051487456164014</v>
       </c>
       <c r="O414" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.046599998474121</v>
       </c>
       <c r="P414" t="n">
-        <v>0.004887457689892932</v>
+        <v>0.0048874576898929</v>
       </c>
     </row>
     <row r="415">
@@ -24473,16 +24473,538 @@
         <v>21.39932</v>
       </c>
       <c r="M415" t="n">
-        <v>0.02915699232005715</v>
+        <v>0.0291569923200571</v>
       </c>
       <c r="N415" t="n">
-        <v>0.05755684050723343</v>
+        <v>0.0575568405072334</v>
       </c>
       <c r="O415" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.046599998474121</v>
       </c>
       <c r="P415" t="n">
-        <v>0.01095684203311234</v>
+        <v>0.0109568420331123</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:02:37</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>308.26</v>
+      </c>
+      <c r="F416" t="n">
+        <v>4498802081792</v>
+      </c>
+      <c r="G416" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H416" t="n">
+        <v>9.510149999999999</v>
+      </c>
+      <c r="I416" t="n">
+        <v>35.391506</v>
+      </c>
+      <c r="J416" t="n">
+        <v>32.41379</v>
+      </c>
+      <c r="K416" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="L416" t="n">
+        <v>9.637062</v>
+      </c>
+      <c r="M416" t="n">
+        <v>0.02825536884448194</v>
+      </c>
+      <c r="N416" t="n">
+        <v>0.0308510672808668</v>
+      </c>
+      <c r="O416" t="n">
+        <v>0.04699000358581543</v>
+      </c>
+      <c r="P416" t="n">
+        <v>-0.01613893630494862</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:02:37</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>469.56</v>
+      </c>
+      <c r="F417" t="n">
+        <v>766544969728</v>
+      </c>
+      <c r="G417" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H417" t="n">
+        <v>15.45987</v>
+      </c>
+      <c r="I417" t="n">
+        <v>119.78571</v>
+      </c>
+      <c r="J417" t="n">
+        <v>30.37283</v>
+      </c>
+      <c r="K417" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L417" t="n">
+        <v>18.558163</v>
+      </c>
+      <c r="M417" t="n">
+        <v>0.008348240906380441</v>
+      </c>
+      <c r="N417" t="n">
+        <v>0.03292416304625607</v>
+      </c>
+      <c r="O417" t="n">
+        <v>0.04699000358581543</v>
+      </c>
+      <c r="P417" t="n">
+        <v>-0.01406584053955936</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:02:37</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>278.09</v>
+      </c>
+      <c r="F418" t="n">
+        <v>2999565680640</v>
+      </c>
+      <c r="G418" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H418" t="n">
+        <v>10.33054</v>
+      </c>
+      <c r="I418" t="n">
+        <v>22.372484</v>
+      </c>
+      <c r="J418" t="n">
+        <v>26.919212</v>
+      </c>
+      <c r="K418" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L418" t="n">
+        <v>3.8670142</v>
+      </c>
+      <c r="M418" t="n">
+        <v>0.04469775971807689</v>
+      </c>
+      <c r="N418" t="n">
+        <v>0.03714818943507497</v>
+      </c>
+      <c r="O418" t="n">
+        <v>0.04699000358581543</v>
+      </c>
+      <c r="P418" t="n">
+        <v>-0.009841814150740452</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:02:37</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>422.4</v>
+      </c>
+      <c r="F419" t="n">
+        <v>2009601933312</v>
+      </c>
+      <c r="G419" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="H419" t="n">
+        <v>19.53066</v>
+      </c>
+      <c r="I419" t="n">
+        <v>70.51752999999999</v>
+      </c>
+      <c r="J419" t="n">
+        <v>21.627533</v>
+      </c>
+      <c r="K419" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L419" t="n">
+        <v>26.62959</v>
+      </c>
+      <c r="M419" t="n">
+        <v>0.01418087121212121</v>
+      </c>
+      <c r="N419" t="n">
+        <v>0.04623735795454546</v>
+      </c>
+      <c r="O419" t="n">
+        <v>0.04699000358581543</v>
+      </c>
+      <c r="P419" t="n">
+        <v>-0.00075264563126997</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:02:37</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>355.84</v>
+      </c>
+      <c r="F420" t="n">
+        <v>4351899992064</v>
+      </c>
+      <c r="G420" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="H420" t="n">
+        <v>14.73443</v>
+      </c>
+      <c r="I420" t="n">
+        <v>17.845535</v>
+      </c>
+      <c r="J420" t="n">
+        <v>24.150238</v>
+      </c>
+      <c r="K420" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L420" t="n">
+        <v>9.760555999999999</v>
+      </c>
+      <c r="M420" t="n">
+        <v>0.05603642086330936</v>
+      </c>
+      <c r="N420" t="n">
+        <v>0.04140745840827338</v>
+      </c>
+      <c r="O420" t="n">
+        <v>0.04699000358581543</v>
+      </c>
+      <c r="P420" t="n">
+        <v>-0.005582545177542045</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:02:37</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>594.92</v>
+      </c>
+      <c r="F421" t="n">
+        <v>1515562336256</v>
+      </c>
+      <c r="G421" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="H421" t="n">
+        <v>35.13625</v>
+      </c>
+      <c r="I421" t="n">
+        <v>22.424423</v>
+      </c>
+      <c r="J421" t="n">
+        <v>16.9318</v>
+      </c>
+      <c r="K421" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L421" t="n">
+        <v>6.64001</v>
+      </c>
+      <c r="M421" t="n">
+        <v>0.04459423115713038</v>
+      </c>
+      <c r="N421" t="n">
+        <v>0.05906046191084516</v>
+      </c>
+      <c r="O421" t="n">
+        <v>0.04699000358581543</v>
+      </c>
+      <c r="P421" t="n">
+        <v>0.01207045832502973</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:02:37</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>506.06</v>
+      </c>
+      <c r="F422" t="n">
+        <v>3757771587584</v>
+      </c>
+      <c r="G422" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H422" t="n">
+        <v>23.4742</v>
+      </c>
+      <c r="I422" t="n">
+        <v>28.192757</v>
+      </c>
+      <c r="J422" t="n">
+        <v>21.558136</v>
+      </c>
+      <c r="K422" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L422" t="n">
+        <v>11.32408</v>
+      </c>
+      <c r="M422" t="n">
+        <v>0.03547010235940402</v>
+      </c>
+      <c r="N422" t="n">
+        <v>0.0463861992649093</v>
+      </c>
+      <c r="O422" t="n">
+        <v>0.04699000358581543</v>
+      </c>
+      <c r="P422" t="n">
+        <v>-0.0006038043209061275</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:02:37</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>76.29000000000001</v>
+      </c>
+      <c r="F423" t="n">
+        <v>317666951168</v>
+      </c>
+      <c r="G423" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H423" t="n">
+        <v>3.81668</v>
+      </c>
+      <c r="I423" t="n">
+        <v>23.990566</v>
+      </c>
+      <c r="J423" t="n">
+        <v>19.988577</v>
+      </c>
+      <c r="K423" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L423" t="n">
+        <v>6.5673337</v>
+      </c>
+      <c r="M423" t="n">
+        <v>0.04168305151395989</v>
+      </c>
+      <c r="N423" t="n">
+        <v>0.05002857517367938</v>
+      </c>
+      <c r="O423" t="n">
+        <v>0.04699000358581543</v>
+      </c>
+      <c r="P423" t="n">
+        <v>0.003038571587863949</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:02:37</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>217.55</v>
+      </c>
+      <c r="F424" t="n">
+        <v>5269278425088</v>
+      </c>
+      <c r="G424" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="H424" t="n">
+        <v>12.89043</v>
+      </c>
+      <c r="I424" t="n">
+        <v>33.264526</v>
+      </c>
+      <c r="J424" t="n">
+        <v>16.876862</v>
+      </c>
+      <c r="K424" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L424" t="n">
+        <v>20.786846</v>
+      </c>
+      <c r="M424" t="n">
+        <v>0.03006205470006895</v>
+      </c>
+      <c r="N424" t="n">
+        <v>0.05925272351183636</v>
+      </c>
+      <c r="O424" t="n">
+        <v>0.04699000358581543</v>
+      </c>
+      <c r="P424" t="n">
+        <v>0.01226271992602093</v>
       </c>
     </row>
   </sheetData>
@@ -24584,12 +25106,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:15</t>
+          <t>2026-08-10 16:02:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -24603,10 +25125,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353.47</v>
+        <v>355.84</v>
       </c>
       <c r="F2" t="n">
-        <v>4322915254272</v>
+        <v>4351899992064</v>
       </c>
       <c r="G2" t="n">
         <v>19.94</v>
@@ -24615,39 +25137,39 @@
         <v>14.73443</v>
       </c>
       <c r="I2" t="n">
-        <v>17.726679</v>
+        <v>17.845535</v>
       </c>
       <c r="J2" t="n">
-        <v>23.989391</v>
+        <v>24.150238</v>
       </c>
       <c r="K2" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="L2" t="n">
-        <v>9.695548</v>
+        <v>9.760555999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05641214247319433</v>
+        <v>0.05603642086330936</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04168509350157015</v>
+        <v>0.04140745840827338</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.04699000358581543</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.004914904972550947</v>
+        <v>-0.005582545177542045</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:15</t>
+          <t>2026-08-10 16:02:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -24661,51 +25183,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>499.99</v>
+        <v>506.06</v>
       </c>
       <c r="F3" t="n">
-        <v>3712698548224</v>
+        <v>3757771587584</v>
       </c>
       <c r="G3" t="n">
-        <v>17.94</v>
+        <v>17.95</v>
       </c>
       <c r="H3" t="n">
         <v>23.4742</v>
       </c>
       <c r="I3" t="n">
-        <v>27.870121</v>
+        <v>28.192757</v>
       </c>
       <c r="J3" t="n">
-        <v>21.299555</v>
+        <v>21.558136</v>
       </c>
       <c r="K3" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="L3" t="n">
-        <v>11.188252</v>
+        <v>11.32408</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03588071761435229</v>
+        <v>0.03547010235940402</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04694933898677973</v>
+        <v>0.0463861992649093</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.04699000358581543</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003493405126586413</v>
+        <v>-0.0006038043209061275</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:15</t>
+          <t>2026-08-10 16:02:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -24719,51 +25241,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>592.1</v>
+        <v>594.92</v>
       </c>
       <c r="F4" t="n">
-        <v>1508378279936</v>
+        <v>1515562336256</v>
       </c>
       <c r="G4" t="n">
-        <v>26.55</v>
+        <v>26.53</v>
       </c>
       <c r="H4" t="n">
         <v>35.13625</v>
       </c>
       <c r="I4" t="n">
-        <v>22.301317</v>
+        <v>22.424423</v>
       </c>
       <c r="J4" t="n">
-        <v>16.851542</v>
+        <v>16.9318</v>
       </c>
       <c r="K4" t="n">
         <v>0.88</v>
       </c>
       <c r="L4" t="n">
-        <v>6.6085353</v>
+        <v>6.64001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04484039858132072</v>
+        <v>0.04459423115713038</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05934174970444181</v>
+        <v>0.05906046191084516</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.04699000358581543</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01274175123032072</v>
+        <v>0.01207045832502973</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:15</t>
+          <t>2026-08-10 16:02:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -24777,51 +25299,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>274.48</v>
+        <v>278.09</v>
       </c>
       <c r="F5" t="n">
-        <v>2960627335168</v>
+        <v>2999565680640</v>
       </c>
       <c r="G5" t="n">
-        <v>12.44</v>
+        <v>12.43</v>
       </c>
       <c r="H5" t="n">
         <v>10.33054</v>
       </c>
       <c r="I5" t="n">
-        <v>22.06431</v>
+        <v>22.372484</v>
       </c>
       <c r="J5" t="n">
-        <v>26.569765</v>
+        <v>26.919212</v>
       </c>
       <c r="K5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="L5" t="n">
-        <v>3.8168151</v>
+        <v>3.8670142</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04532206353832701</v>
+        <v>0.04469775971807689</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0376367677062081</v>
+        <v>0.03714818943507497</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.04699000358581543</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.008963230767912993</v>
+        <v>-0.009841814150740452</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:15</t>
+          <t>2026-08-10 16:02:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -24835,51 +25357,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>313.33</v>
+        <v>308.26</v>
       </c>
       <c r="F6" t="n">
-        <v>4572794322944</v>
+        <v>4498802081792</v>
       </c>
       <c r="G6" t="n">
-        <v>8.720000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>9.513070000000001</v>
+        <v>9.510149999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>35.93234</v>
+        <v>35.391506</v>
       </c>
       <c r="J6" t="n">
-        <v>32.93679</v>
+        <v>32.41379</v>
       </c>
       <c r="K6" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="L6" t="n">
-        <v>9.795564000000001</v>
+        <v>9.637062</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0278300832987585</v>
+        <v>0.02825536884448194</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03036118469345419</v>
+        <v>0.0308510672808668</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.04699000358581543</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0162388137806669</v>
+        <v>-0.01613893630494862</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:15</t>
+          <t>2026-08-10 16:02:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -24893,51 +25415,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223.96</v>
+        <v>217.55</v>
       </c>
       <c r="F7" t="n">
-        <v>5424535306240</v>
+        <v>5269278425088</v>
       </c>
       <c r="G7" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
       <c r="H7" t="n">
         <v>12.89043</v>
       </c>
       <c r="I7" t="n">
-        <v>34.29709</v>
+        <v>33.264526</v>
       </c>
       <c r="J7" t="n">
-        <v>17.37413</v>
+        <v>16.876862</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="L7" t="n">
-        <v>21.39932</v>
+        <v>20.786846</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02915699232005715</v>
+        <v>0.03006205470006895</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05755684050723343</v>
+        <v>0.05925272351183636</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.04699000358581543</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01095684203311234</v>
+        <v>0.01226271992602093</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:15</t>
+          <t>2026-08-10 16:02:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -24951,51 +25473,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>483.36</v>
+        <v>469.56</v>
       </c>
       <c r="F8" t="n">
-        <v>789073100800</v>
+        <v>766544969728</v>
       </c>
       <c r="G8" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="H8" t="n">
         <v>15.45987</v>
       </c>
       <c r="I8" t="n">
-        <v>123.621475</v>
+        <v>119.78571</v>
       </c>
       <c r="J8" t="n">
-        <v>31.265461</v>
+        <v>30.37283</v>
       </c>
       <c r="K8" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="L8" t="n">
-        <v>19.103573</v>
+        <v>18.558163</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008089208871234691</v>
+        <v>0.008348240906380441</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03198417328699106</v>
+        <v>0.03292416304625607</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.04699000358581543</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01461582518713003</v>
+        <v>-0.01406584053955936</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:15</t>
+          <t>2026-08-10 16:02:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -25009,51 +25531,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>427.76</v>
+        <v>422.4</v>
       </c>
       <c r="F9" t="n">
-        <v>2035102646272</v>
+        <v>2009601933312</v>
       </c>
       <c r="G9" t="n">
-        <v>6.01</v>
+        <v>5.99</v>
       </c>
       <c r="H9" t="n">
-        <v>19.49196</v>
+        <v>19.53066</v>
       </c>
       <c r="I9" t="n">
-        <v>71.174706</v>
+        <v>70.51752999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>21.94546</v>
+        <v>21.627533</v>
       </c>
       <c r="K9" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="L9" t="n">
-        <v>26.967505</v>
+        <v>26.62959</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01404993454273424</v>
+        <v>0.01418087121212121</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04556751449410885</v>
+        <v>0.04623735795454546</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.04699000358581543</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.001032483980012246</v>
+        <v>-0.00075264563126997</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:15</t>
+          <t>2026-08-10 16:02:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -25067,40 +25589,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>74.14</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>308714471424</v>
+        <v>317666951168</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.81728</v>
+        <v>3.81668</v>
       </c>
       <c r="I10" t="n">
-        <v>23.314465</v>
+        <v>23.990566</v>
       </c>
       <c r="J10" t="n">
-        <v>19.422207</v>
+        <v>19.988577</v>
       </c>
       <c r="K10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="L10" t="n">
-        <v>6.382253</v>
+        <v>6.5673337</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0428918262746156</v>
+        <v>0.04168305151395989</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05148745616401403</v>
+        <v>0.05002857517367938</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.04699000358581543</v>
       </c>
       <c r="P10" t="n">
-        <v>0.004887457689892932</v>
+        <v>0.003038571587863949</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P424"/>
+  <dimension ref="A1:P433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24531,16 +24531,16 @@
         <v>9.637062</v>
       </c>
       <c r="M416" t="n">
-        <v>0.02825536884448194</v>
+        <v>0.0282553688444819</v>
       </c>
       <c r="N416" t="n">
         <v>0.0308510672808668</v>
       </c>
       <c r="O416" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.0469900035858154</v>
       </c>
       <c r="P416" t="n">
-        <v>-0.01613893630494862</v>
+        <v>-0.0161389363049486</v>
       </c>
     </row>
     <row r="417">
@@ -24589,16 +24589,16 @@
         <v>18.558163</v>
       </c>
       <c r="M417" t="n">
-        <v>0.008348240906380441</v>
+        <v>0.008348240906380399</v>
       </c>
       <c r="N417" t="n">
-        <v>0.03292416304625607</v>
+        <v>0.032924163046256</v>
       </c>
       <c r="O417" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.0469900035858154</v>
       </c>
       <c r="P417" t="n">
-        <v>-0.01406584053955936</v>
+        <v>-0.0140658405395593</v>
       </c>
     </row>
     <row r="418">
@@ -24647,16 +24647,16 @@
         <v>3.8670142</v>
       </c>
       <c r="M418" t="n">
-        <v>0.04469775971807689</v>
+        <v>0.0446977597180768</v>
       </c>
       <c r="N418" t="n">
-        <v>0.03714818943507497</v>
+        <v>0.0371481894350749</v>
       </c>
       <c r="O418" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.0469900035858154</v>
       </c>
       <c r="P418" t="n">
-        <v>-0.009841814150740452</v>
+        <v>-0.0098418141507404</v>
       </c>
     </row>
     <row r="419">
@@ -24705,16 +24705,16 @@
         <v>26.62959</v>
       </c>
       <c r="M419" t="n">
-        <v>0.01418087121212121</v>
+        <v>0.0141808712121212</v>
       </c>
       <c r="N419" t="n">
-        <v>0.04623735795454546</v>
+        <v>0.0462373579545454</v>
       </c>
       <c r="O419" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.0469900035858154</v>
       </c>
       <c r="P419" t="n">
-        <v>-0.00075264563126997</v>
+        <v>-0.0007526456312699</v>
       </c>
     </row>
     <row r="420">
@@ -24763,16 +24763,16 @@
         <v>9.760555999999999</v>
       </c>
       <c r="M420" t="n">
-        <v>0.05603642086330936</v>
+        <v>0.0560364208633093</v>
       </c>
       <c r="N420" t="n">
-        <v>0.04140745840827338</v>
+        <v>0.0414074584082733</v>
       </c>
       <c r="O420" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.0469900035858154</v>
       </c>
       <c r="P420" t="n">
-        <v>-0.005582545177542045</v>
+        <v>-0.005582545177542</v>
       </c>
     </row>
     <row r="421">
@@ -24821,16 +24821,16 @@
         <v>6.64001</v>
       </c>
       <c r="M421" t="n">
-        <v>0.04459423115713038</v>
+        <v>0.0445942311571303</v>
       </c>
       <c r="N421" t="n">
-        <v>0.05906046191084516</v>
+        <v>0.0590604619108451</v>
       </c>
       <c r="O421" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.0469900035858154</v>
       </c>
       <c r="P421" t="n">
-        <v>0.01207045832502973</v>
+        <v>0.0120704583250297</v>
       </c>
     </row>
     <row r="422">
@@ -24879,16 +24879,16 @@
         <v>11.32408</v>
       </c>
       <c r="M422" t="n">
-        <v>0.03547010235940402</v>
+        <v>0.035470102359404</v>
       </c>
       <c r="N422" t="n">
         <v>0.0463861992649093</v>
       </c>
       <c r="O422" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.0469900035858154</v>
       </c>
       <c r="P422" t="n">
-        <v>-0.0006038043209061275</v>
+        <v>-0.0006038043209061</v>
       </c>
     </row>
     <row r="423">
@@ -24937,16 +24937,16 @@
         <v>6.5673337</v>
       </c>
       <c r="M423" t="n">
-        <v>0.04168305151395989</v>
+        <v>0.0416830515139598</v>
       </c>
       <c r="N423" t="n">
-        <v>0.05002857517367938</v>
+        <v>0.0500285751736793</v>
       </c>
       <c r="O423" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.0469900035858154</v>
       </c>
       <c r="P423" t="n">
-        <v>0.003038571587863949</v>
+        <v>0.0030385715878639</v>
       </c>
     </row>
     <row r="424">
@@ -24995,16 +24995,538 @@
         <v>20.786846</v>
       </c>
       <c r="M424" t="n">
-        <v>0.03006205470006895</v>
+        <v>0.0300620547000689</v>
       </c>
       <c r="N424" t="n">
-        <v>0.05925272351183636</v>
+        <v>0.0592527235118363</v>
       </c>
       <c r="O424" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.0469900035858154</v>
       </c>
       <c r="P424" t="n">
-        <v>0.01226271992602093</v>
+        <v>0.0122627199260209</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2026-08-11 16:09:13</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>304.91</v>
+      </c>
+      <c r="F425" t="n">
+        <v>4449911701504</v>
+      </c>
+      <c r="G425" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H425" t="n">
+        <v>9.507709999999999</v>
+      </c>
+      <c r="I425" t="n">
+        <v>34.966743</v>
+      </c>
+      <c r="J425" t="n">
+        <v>32.06976</v>
+      </c>
+      <c r="K425" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L425" t="n">
+        <v>9.532332</v>
+      </c>
+      <c r="M425" t="n">
+        <v>0.0285986028664196</v>
+      </c>
+      <c r="N425" t="n">
+        <v>0.03118202092420714</v>
+      </c>
+      <c r="O425" t="n">
+        <v>0.04684000015258789</v>
+      </c>
+      <c r="P425" t="n">
+        <v>-0.01565797922838075</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2026-08-11 16:09:13</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>474.32</v>
+      </c>
+      <c r="F426" t="n">
+        <v>774315573248</v>
+      </c>
+      <c r="G426" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H426" t="n">
+        <v>15.45987</v>
+      </c>
+      <c r="I426" t="n">
+        <v>121.620514</v>
+      </c>
+      <c r="J426" t="n">
+        <v>30.680723</v>
+      </c>
+      <c r="K426" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L426" t="n">
+        <v>18.74629</v>
+      </c>
+      <c r="M426" t="n">
+        <v>0.008222297183336145</v>
+      </c>
+      <c r="N426" t="n">
+        <v>0.03259375527070332</v>
+      </c>
+      <c r="O426" t="n">
+        <v>0.04684000015258789</v>
+      </c>
+      <c r="P426" t="n">
+        <v>-0.01424624488188457</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>2026-08-11 16:09:13</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>272.27</v>
+      </c>
+      <c r="F427" t="n">
+        <v>2936789270528</v>
+      </c>
+      <c r="G427" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H427" t="n">
+        <v>10.33054</v>
+      </c>
+      <c r="I427" t="n">
+        <v>21.904263</v>
+      </c>
+      <c r="J427" t="n">
+        <v>26.355833</v>
+      </c>
+      <c r="K427" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L427" t="n">
+        <v>3.7860835</v>
+      </c>
+      <c r="M427" t="n">
+        <v>0.04565321188526095</v>
+      </c>
+      <c r="N427" t="n">
+        <v>0.03794226319462298</v>
+      </c>
+      <c r="O427" t="n">
+        <v>0.04684000015258789</v>
+      </c>
+      <c r="P427" t="n">
+        <v>-0.008897736957964912</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>2026-08-11 16:09:13</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>416.08</v>
+      </c>
+      <c r="F428" t="n">
+        <v>1979533885440</v>
+      </c>
+      <c r="G428" t="n">
+        <v>6</v>
+      </c>
+      <c r="H428" t="n">
+        <v>19.53066</v>
+      </c>
+      <c r="I428" t="n">
+        <v>69.346664</v>
+      </c>
+      <c r="J428" t="n">
+        <v>21.303938</v>
+      </c>
+      <c r="K428" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L428" t="n">
+        <v>26.231152</v>
+      </c>
+      <c r="M428" t="n">
+        <v>0.01442030378773313</v>
+      </c>
+      <c r="N428" t="n">
+        <v>0.04693967506248799</v>
+      </c>
+      <c r="O428" t="n">
+        <v>0.04684000015258789</v>
+      </c>
+      <c r="P428" t="n">
+        <v>9.967490990009376e-05</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2026-08-11 16:09:13</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E429" t="n">
+        <v>343</v>
+      </c>
+      <c r="F429" t="n">
+        <v>4194867609600</v>
+      </c>
+      <c r="G429" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H429" t="n">
+        <v>14.73894</v>
+      </c>
+      <c r="I429" t="n">
+        <v>17.210236</v>
+      </c>
+      <c r="J429" t="n">
+        <v>23.271687</v>
+      </c>
+      <c r="K429" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L429" t="n">
+        <v>9.40836</v>
+      </c>
+      <c r="M429" t="n">
+        <v>0.05810495626822158</v>
+      </c>
+      <c r="N429" t="n">
+        <v>0.04297067055393586</v>
+      </c>
+      <c r="O429" t="n">
+        <v>0.04684000015258789</v>
+      </c>
+      <c r="P429" t="n">
+        <v>-0.003869329598652035</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>2026-08-11 16:09:13</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E430" t="n">
+        <v>599.12</v>
+      </c>
+      <c r="F430" t="n">
+        <v>1526261874688</v>
+      </c>
+      <c r="G430" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="H430" t="n">
+        <v>34.885</v>
+      </c>
+      <c r="I430" t="n">
+        <v>22.582735</v>
+      </c>
+      <c r="J430" t="n">
+        <v>17.174145</v>
+      </c>
+      <c r="K430" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L430" t="n">
+        <v>6.6868873</v>
+      </c>
+      <c r="M430" t="n">
+        <v>0.04428161303244759</v>
+      </c>
+      <c r="N430" t="n">
+        <v>0.05822706636400053</v>
+      </c>
+      <c r="O430" t="n">
+        <v>0.04684000015258789</v>
+      </c>
+      <c r="P430" t="n">
+        <v>0.01138706621141264</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>2026-08-11 16:09:13</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>503.81</v>
+      </c>
+      <c r="F431" t="n">
+        <v>3741064101888</v>
+      </c>
+      <c r="G431" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="H431" t="n">
+        <v>23.55269</v>
+      </c>
+      <c r="I431" t="n">
+        <v>28.036173</v>
+      </c>
+      <c r="J431" t="n">
+        <v>21.390762</v>
+      </c>
+      <c r="K431" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L431" t="n">
+        <v>11.273732</v>
+      </c>
+      <c r="M431" t="n">
+        <v>0.03566820825311129</v>
+      </c>
+      <c r="N431" t="n">
+        <v>0.04674915146583037</v>
+      </c>
+      <c r="O431" t="n">
+        <v>0.04684000015258789</v>
+      </c>
+      <c r="P431" t="n">
+        <v>-9.084868675752339e-05</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2026-08-11 16:09:13</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>74.79000000000001</v>
+      </c>
+      <c r="F432" t="n">
+        <v>311421042688</v>
+      </c>
+      <c r="G432" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H432" t="n">
+        <v>3.81668</v>
+      </c>
+      <c r="I432" t="n">
+        <v>23.518867</v>
+      </c>
+      <c r="J432" t="n">
+        <v>19.595566</v>
+      </c>
+      <c r="K432" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="L432" t="n">
+        <v>6.4382076</v>
+      </c>
+      <c r="M432" t="n">
+        <v>0.04251905334937826</v>
+      </c>
+      <c r="N432" t="n">
+        <v>0.0510319561438695</v>
+      </c>
+      <c r="O432" t="n">
+        <v>0.04684000015258789</v>
+      </c>
+      <c r="P432" t="n">
+        <v>0.004191955991281603</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>2026-08-11 16:09:13</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="F433" t="n">
+        <v>5268067319808</v>
+      </c>
+      <c r="G433" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H433" t="n">
+        <v>12.89043</v>
+      </c>
+      <c r="I433" t="n">
+        <v>33.307808</v>
+      </c>
+      <c r="J433" t="n">
+        <v>16.872982</v>
+      </c>
+      <c r="K433" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L433" t="n">
+        <v>20.782068</v>
+      </c>
+      <c r="M433" t="n">
+        <v>0.03002298850574713</v>
+      </c>
+      <c r="N433" t="n">
+        <v>0.05926634482758621</v>
+      </c>
+      <c r="O433" t="n">
+        <v>0.04684000015258789</v>
+      </c>
+      <c r="P433" t="n">
+        <v>0.01242634467499831</v>
       </c>
     </row>
   </sheetData>
@@ -25106,12 +25628,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10 16:02:37</t>
+          <t>2026-08-11 16:09:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -25125,51 +25647,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>355.84</v>
+        <v>343</v>
       </c>
       <c r="F2" t="n">
-        <v>4351899992064</v>
+        <v>4194867609600</v>
       </c>
       <c r="G2" t="n">
-        <v>19.94</v>
+        <v>19.93</v>
       </c>
       <c r="H2" t="n">
-        <v>14.73443</v>
+        <v>14.73894</v>
       </c>
       <c r="I2" t="n">
-        <v>17.845535</v>
+        <v>17.210236</v>
       </c>
       <c r="J2" t="n">
-        <v>24.150238</v>
+        <v>23.271687</v>
       </c>
       <c r="K2" t="n">
         <v>0.96</v>
       </c>
       <c r="L2" t="n">
-        <v>9.760555999999999</v>
+        <v>9.40836</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05603642086330936</v>
+        <v>0.05810495626822158</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04140745840827338</v>
+        <v>0.04297067055393586</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.04684000015258789</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005582545177542045</v>
+        <v>-0.003869329598652035</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-10 16:02:37</t>
+          <t>2026-08-11 16:09:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -25183,51 +25705,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>506.06</v>
+        <v>503.81</v>
       </c>
       <c r="F3" t="n">
-        <v>3757771587584</v>
+        <v>3741064101888</v>
       </c>
       <c r="G3" t="n">
-        <v>17.95</v>
+        <v>17.97</v>
       </c>
       <c r="H3" t="n">
-        <v>23.4742</v>
+        <v>23.55269</v>
       </c>
       <c r="I3" t="n">
-        <v>28.192757</v>
+        <v>28.036173</v>
       </c>
       <c r="J3" t="n">
-        <v>21.558136</v>
+        <v>21.390762</v>
       </c>
       <c r="K3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="L3" t="n">
-        <v>11.32408</v>
+        <v>11.273732</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03547010235940402</v>
+        <v>0.03566820825311129</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0463861992649093</v>
+        <v>0.04674915146583037</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.04684000015258789</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0006038043209061275</v>
+        <v>-9.084868675752339e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-10 16:02:37</t>
+          <t>2026-08-11 16:09:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -25241,51 +25763,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>594.92</v>
+        <v>599.12</v>
       </c>
       <c r="F4" t="n">
-        <v>1515562336256</v>
+        <v>1526261874688</v>
       </c>
       <c r="G4" t="n">
         <v>26.53</v>
       </c>
       <c r="H4" t="n">
-        <v>35.13625</v>
+        <v>34.885</v>
       </c>
       <c r="I4" t="n">
-        <v>22.424423</v>
+        <v>22.582735</v>
       </c>
       <c r="J4" t="n">
-        <v>16.9318</v>
+        <v>17.174145</v>
       </c>
       <c r="K4" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="L4" t="n">
-        <v>6.64001</v>
+        <v>6.6868873</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04459423115713038</v>
+        <v>0.04428161303244759</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05906046191084516</v>
+        <v>0.05822706636400053</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.04684000015258789</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01207045832502973</v>
+        <v>0.01138706621141264</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-10 16:02:37</t>
+          <t>2026-08-11 16:09:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -25299,10 +25821,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>278.09</v>
+        <v>272.27</v>
       </c>
       <c r="F5" t="n">
-        <v>2999565680640</v>
+        <v>2936789270528</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
@@ -25311,39 +25833,39 @@
         <v>10.33054</v>
       </c>
       <c r="I5" t="n">
-        <v>22.372484</v>
+        <v>21.904263</v>
       </c>
       <c r="J5" t="n">
-        <v>26.919212</v>
+        <v>26.355833</v>
       </c>
       <c r="K5" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="L5" t="n">
-        <v>3.8670142</v>
+        <v>3.7860835</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04469775971807689</v>
+        <v>0.04565321188526095</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03714818943507497</v>
+        <v>0.03794226319462298</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.04684000015258789</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.009841814150740452</v>
+        <v>-0.008897736957964912</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-10 16:02:37</t>
+          <t>2026-08-11 16:09:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -25357,51 +25879,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308.26</v>
+        <v>304.91</v>
       </c>
       <c r="F6" t="n">
-        <v>4498802081792</v>
+        <v>4449911701504</v>
       </c>
       <c r="G6" t="n">
-        <v>8.710000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>9.510149999999999</v>
+        <v>9.507709999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>35.391506</v>
+        <v>34.966743</v>
       </c>
       <c r="J6" t="n">
-        <v>32.41379</v>
+        <v>32.06976</v>
       </c>
       <c r="K6" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="L6" t="n">
-        <v>9.637062</v>
+        <v>9.532332</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02825536884448194</v>
+        <v>0.0285986028664196</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0308510672808668</v>
+        <v>0.03118202092420714</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.04684000015258789</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01613893630494862</v>
+        <v>-0.01565797922838075</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-10 16:02:37</t>
+          <t>2026-08-11 16:09:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -25415,51 +25937,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>217.55</v>
+        <v>217.5</v>
       </c>
       <c r="F7" t="n">
-        <v>5269278425088</v>
+        <v>5268067319808</v>
       </c>
       <c r="G7" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
       <c r="H7" t="n">
         <v>12.89043</v>
       </c>
       <c r="I7" t="n">
-        <v>33.264526</v>
+        <v>33.307808</v>
       </c>
       <c r="J7" t="n">
-        <v>16.876862</v>
+        <v>16.872982</v>
       </c>
       <c r="K7" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L7" t="n">
-        <v>20.786846</v>
+        <v>20.782068</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03006205470006895</v>
+        <v>0.03002298850574713</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05925272351183636</v>
+        <v>0.05926634482758621</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.04684000015258789</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01226271992602093</v>
+        <v>0.01242634467499831</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-10 16:02:37</t>
+          <t>2026-08-11 16:09:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -25473,51 +25995,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>469.56</v>
+        <v>474.32</v>
       </c>
       <c r="F8" t="n">
-        <v>766544969728</v>
+        <v>774315573248</v>
       </c>
       <c r="G8" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="H8" t="n">
         <v>15.45987</v>
       </c>
       <c r="I8" t="n">
-        <v>119.78571</v>
+        <v>121.620514</v>
       </c>
       <c r="J8" t="n">
-        <v>30.37283</v>
+        <v>30.680723</v>
       </c>
       <c r="K8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="L8" t="n">
-        <v>18.558163</v>
+        <v>18.74629</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008348240906380441</v>
+        <v>0.008222297183336145</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03292416304625607</v>
+        <v>0.03259375527070332</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.04684000015258789</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01406584053955936</v>
+        <v>-0.01424624488188457</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-10 16:02:37</t>
+          <t>2026-08-11 16:09:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -25531,51 +26053,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>422.4</v>
+        <v>416.08</v>
       </c>
       <c r="F9" t="n">
-        <v>2009601933312</v>
+        <v>1979533885440</v>
       </c>
       <c r="G9" t="n">
-        <v>5.99</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>19.53066</v>
       </c>
       <c r="I9" t="n">
-        <v>70.51752999999999</v>
+        <v>69.346664</v>
       </c>
       <c r="J9" t="n">
-        <v>21.627533</v>
+        <v>21.303938</v>
       </c>
       <c r="K9" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="L9" t="n">
-        <v>26.62959</v>
+        <v>26.231152</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01418087121212121</v>
+        <v>0.01442030378773313</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04623735795454546</v>
+        <v>0.04693967506248799</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.04684000015258789</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.00075264563126997</v>
+        <v>9.967490990009376e-05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-10 16:02:37</t>
+          <t>2026-08-11 16:09:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -25589,10 +26111,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>76.29000000000001</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>317666951168</v>
+        <v>311421042688</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -25601,28 +26123,28 @@
         <v>3.81668</v>
       </c>
       <c r="I10" t="n">
-        <v>23.990566</v>
+        <v>23.518867</v>
       </c>
       <c r="J10" t="n">
-        <v>19.988577</v>
+        <v>19.595566</v>
       </c>
       <c r="K10" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="L10" t="n">
-        <v>6.5673337</v>
+        <v>6.4382076</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04168305151395989</v>
+        <v>0.04251905334937826</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05002857517367938</v>
+        <v>0.0510319561438695</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.04684000015258789</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003038571587863949</v>
+        <v>0.004191955991281603</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P433"/>
+  <dimension ref="A1:P442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25056,13 +25056,13 @@
         <v>0.0285986028664196</v>
       </c>
       <c r="N425" t="n">
-        <v>0.03118202092420714</v>
+        <v>0.0311820209242071</v>
       </c>
       <c r="O425" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.0468400001525878</v>
       </c>
       <c r="P425" t="n">
-        <v>-0.01565797922838075</v>
+        <v>-0.0156579792283807</v>
       </c>
     </row>
     <row r="426">
@@ -25111,16 +25111,16 @@
         <v>18.74629</v>
       </c>
       <c r="M426" t="n">
-        <v>0.008222297183336145</v>
+        <v>0.0082222971833361</v>
       </c>
       <c r="N426" t="n">
-        <v>0.03259375527070332</v>
+        <v>0.0325937552707033</v>
       </c>
       <c r="O426" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.0468400001525878</v>
       </c>
       <c r="P426" t="n">
-        <v>-0.01424624488188457</v>
+        <v>-0.0142462448818845</v>
       </c>
     </row>
     <row r="427">
@@ -25169,16 +25169,16 @@
         <v>3.7860835</v>
       </c>
       <c r="M427" t="n">
-        <v>0.04565321188526095</v>
+        <v>0.0456532118852609</v>
       </c>
       <c r="N427" t="n">
-        <v>0.03794226319462298</v>
+        <v>0.0379422631946229</v>
       </c>
       <c r="O427" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.0468400001525878</v>
       </c>
       <c r="P427" t="n">
-        <v>-0.008897736957964912</v>
+        <v>-0.0088977369579649</v>
       </c>
     </row>
     <row r="428">
@@ -25227,13 +25227,13 @@
         <v>26.231152</v>
       </c>
       <c r="M428" t="n">
-        <v>0.01442030378773313</v>
+        <v>0.0144203037877331</v>
       </c>
       <c r="N428" t="n">
-        <v>0.04693967506248799</v>
+        <v>0.0469396750624879</v>
       </c>
       <c r="O428" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.0468400001525878</v>
       </c>
       <c r="P428" t="n">
         <v>9.967490990009376e-05</v>
@@ -25285,16 +25285,16 @@
         <v>9.40836</v>
       </c>
       <c r="M429" t="n">
-        <v>0.05810495626822158</v>
+        <v>0.0581049562682215</v>
       </c>
       <c r="N429" t="n">
-        <v>0.04297067055393586</v>
+        <v>0.0429706705539358</v>
       </c>
       <c r="O429" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.0468400001525878</v>
       </c>
       <c r="P429" t="n">
-        <v>-0.003869329598652035</v>
+        <v>-0.003869329598652</v>
       </c>
     </row>
     <row r="430">
@@ -25343,16 +25343,16 @@
         <v>6.6868873</v>
       </c>
       <c r="M430" t="n">
-        <v>0.04428161303244759</v>
+        <v>0.0442816130324475</v>
       </c>
       <c r="N430" t="n">
-        <v>0.05822706636400053</v>
+        <v>0.0582270663640005</v>
       </c>
       <c r="O430" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.0468400001525878</v>
       </c>
       <c r="P430" t="n">
-        <v>0.01138706621141264</v>
+        <v>0.0113870662114126</v>
       </c>
     </row>
     <row r="431">
@@ -25401,16 +25401,16 @@
         <v>11.273732</v>
       </c>
       <c r="M431" t="n">
-        <v>0.03566820825311129</v>
+        <v>0.0356682082531112</v>
       </c>
       <c r="N431" t="n">
-        <v>0.04674915146583037</v>
+        <v>0.0467491514658303</v>
       </c>
       <c r="O431" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.0468400001525878</v>
       </c>
       <c r="P431" t="n">
-        <v>-9.084868675752339e-05</v>
+        <v>-9.08486867575234e-05</v>
       </c>
     </row>
     <row r="432">
@@ -25459,16 +25459,16 @@
         <v>6.4382076</v>
       </c>
       <c r="M432" t="n">
-        <v>0.04251905334937826</v>
+        <v>0.0425190533493782</v>
       </c>
       <c r="N432" t="n">
-        <v>0.0510319561438695</v>
+        <v>0.0510319561438694</v>
       </c>
       <c r="O432" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.0468400001525878</v>
       </c>
       <c r="P432" t="n">
-        <v>0.004191955991281603</v>
+        <v>0.0041919559912816</v>
       </c>
     </row>
     <row r="433">
@@ -25517,16 +25517,538 @@
         <v>20.782068</v>
       </c>
       <c r="M433" t="n">
-        <v>0.03002298850574713</v>
+        <v>0.0300229885057471</v>
       </c>
       <c r="N433" t="n">
-        <v>0.05926634482758621</v>
+        <v>0.0592663448275862</v>
       </c>
       <c r="O433" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.0468400001525878</v>
       </c>
       <c r="P433" t="n">
-        <v>0.01242634467499831</v>
+        <v>0.0124263446749983</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>2026-08-12 16:07:37</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>302.25</v>
+      </c>
+      <c r="F434" t="n">
+        <v>4411090796544</v>
+      </c>
+      <c r="G434" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H434" t="n">
+        <v>9.507709999999999</v>
+      </c>
+      <c r="I434" t="n">
+        <v>34.661697</v>
+      </c>
+      <c r="J434" t="n">
+        <v>31.789988</v>
+      </c>
+      <c r="K434" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L434" t="n">
+        <v>9.449172000000001</v>
+      </c>
+      <c r="M434" t="n">
+        <v>0.02885028949545079</v>
+      </c>
+      <c r="N434" t="n">
+        <v>0.03145644334160463</v>
+      </c>
+      <c r="O434" t="n">
+        <v>0.04682000160217285</v>
+      </c>
+      <c r="P434" t="n">
+        <v>-0.01536355826056823</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>2026-08-12 16:07:37</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>482.93</v>
+      </c>
+      <c r="F435" t="n">
+        <v>788371144704</v>
+      </c>
+      <c r="G435" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="H435" t="n">
+        <v>15.45987</v>
+      </c>
+      <c r="I435" t="n">
+        <v>122.57106</v>
+      </c>
+      <c r="J435" t="n">
+        <v>31.237648</v>
+      </c>
+      <c r="K435" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L435" t="n">
+        <v>19.086578</v>
+      </c>
+      <c r="M435" t="n">
+        <v>0.008158532292464746</v>
+      </c>
+      <c r="N435" t="n">
+        <v>0.03201265193713375</v>
+      </c>
+      <c r="O435" t="n">
+        <v>0.04682000160217285</v>
+      </c>
+      <c r="P435" t="n">
+        <v>-0.0148073496650391</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>2026-08-12 16:07:37</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>267.28</v>
+      </c>
+      <c r="F436" t="n">
+        <v>2882965864448</v>
+      </c>
+      <c r="G436" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="H436" t="n">
+        <v>10.33054</v>
+      </c>
+      <c r="I436" t="n">
+        <v>21.48553</v>
+      </c>
+      <c r="J436" t="n">
+        <v>25.8728</v>
+      </c>
+      <c r="K436" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L436" t="n">
+        <v>3.7166946</v>
+      </c>
+      <c r="M436" t="n">
+        <v>0.04654295121221191</v>
+      </c>
+      <c r="N436" t="n">
+        <v>0.03865062855432505</v>
+      </c>
+      <c r="O436" t="n">
+        <v>0.04682000160217285</v>
+      </c>
+      <c r="P436" t="n">
+        <v>-0.008169373047847803</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>2026-08-12 16:07:37</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>416.05</v>
+      </c>
+      <c r="F437" t="n">
+        <v>1979391279104</v>
+      </c>
+      <c r="G437" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="H437" t="n">
+        <v>19.53066</v>
+      </c>
+      <c r="I437" t="n">
+        <v>69.45743</v>
+      </c>
+      <c r="J437" t="n">
+        <v>21.302402</v>
+      </c>
+      <c r="K437" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L437" t="n">
+        <v>26.229263</v>
+      </c>
+      <c r="M437" t="n">
+        <v>0.01439730801586348</v>
+      </c>
+      <c r="N437" t="n">
+        <v>0.04694305972839803</v>
+      </c>
+      <c r="O437" t="n">
+        <v>0.04682000160217285</v>
+      </c>
+      <c r="P437" t="n">
+        <v>0.0001230581262251784</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>2026-08-12 16:07:37</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>342.37</v>
+      </c>
+      <c r="F438" t="n">
+        <v>4187162935296</v>
+      </c>
+      <c r="G438" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H438" t="n">
+        <v>14.73894</v>
+      </c>
+      <c r="I438" t="n">
+        <v>17.178625</v>
+      </c>
+      <c r="J438" t="n">
+        <v>23.228943</v>
+      </c>
+      <c r="K438" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L438" t="n">
+        <v>9.391080000000001</v>
+      </c>
+      <c r="M438" t="n">
+        <v>0.05821187604054093</v>
+      </c>
+      <c r="N438" t="n">
+        <v>0.04304974150772556</v>
+      </c>
+      <c r="O438" t="n">
+        <v>0.04682000160217285</v>
+      </c>
+      <c r="P438" t="n">
+        <v>-0.003770260094447295</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>2026-08-12 16:07:37</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>578.85</v>
+      </c>
+      <c r="F439" t="n">
+        <v>1474623832064</v>
+      </c>
+      <c r="G439" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H439" t="n">
+        <v>34.885</v>
+      </c>
+      <c r="I439" t="n">
+        <v>21.810472</v>
+      </c>
+      <c r="J439" t="n">
+        <v>16.593092</v>
+      </c>
+      <c r="K439" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L439" t="n">
+        <v>6.4606495</v>
+      </c>
+      <c r="M439" t="n">
+        <v>0.04584952923900838</v>
+      </c>
+      <c r="N439" t="n">
+        <v>0.06026604474388874</v>
+      </c>
+      <c r="O439" t="n">
+        <v>0.04682000160217285</v>
+      </c>
+      <c r="P439" t="n">
+        <v>0.01344604314171589</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>2026-08-12 16:07:37</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>492.43</v>
+      </c>
+      <c r="F440" t="n">
+        <v>3656561459200</v>
+      </c>
+      <c r="G440" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H440" t="n">
+        <v>23.55269</v>
+      </c>
+      <c r="I440" t="n">
+        <v>27.448717</v>
+      </c>
+      <c r="J440" t="n">
+        <v>20.907589</v>
+      </c>
+      <c r="K440" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L440" t="n">
+        <v>11.019082</v>
+      </c>
+      <c r="M440" t="n">
+        <v>0.03643157403082672</v>
+      </c>
+      <c r="N440" t="n">
+        <v>0.0478295189163942</v>
+      </c>
+      <c r="O440" t="n">
+        <v>0.04682000160217285</v>
+      </c>
+      <c r="P440" t="n">
+        <v>0.001009517314221352</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>2026-08-12 16:07:37</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>74.20999999999999</v>
+      </c>
+      <c r="F441" t="n">
+        <v>309005942784</v>
+      </c>
+      <c r="G441" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H441" t="n">
+        <v>3.81668</v>
+      </c>
+      <c r="I441" t="n">
+        <v>23.336477</v>
+      </c>
+      <c r="J441" t="n">
+        <v>19.4436</v>
+      </c>
+      <c r="K441" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="L441" t="n">
+        <v>6.388279</v>
+      </c>
+      <c r="M441" t="n">
+        <v>0.04285136774019675</v>
+      </c>
+      <c r="N441" t="n">
+        <v>0.05143080447379059</v>
+      </c>
+      <c r="O441" t="n">
+        <v>0.04682000160217285</v>
+      </c>
+      <c r="P441" t="n">
+        <v>0.00461080287161774</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>2026-08-12 16:07:37</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>224.09</v>
+      </c>
+      <c r="F442" t="n">
+        <v>5427683655680</v>
+      </c>
+      <c r="G442" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="H442" t="n">
+        <v>12.81649</v>
+      </c>
+      <c r="I442" t="n">
+        <v>34.369633</v>
+      </c>
+      <c r="J442" t="n">
+        <v>17.484507</v>
+      </c>
+      <c r="K442" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L442" t="n">
+        <v>21.411741</v>
+      </c>
+      <c r="M442" t="n">
+        <v>0.02909545271988933</v>
+      </c>
+      <c r="N442" t="n">
+        <v>0.05719349368557276</v>
+      </c>
+      <c r="O442" t="n">
+        <v>0.04682000160217285</v>
+      </c>
+      <c r="P442" t="n">
+        <v>0.01037349208339991</v>
       </c>
     </row>
   </sheetData>
@@ -25628,12 +26150,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-11 16:09:13</t>
+          <t>2026-08-12 16:07:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -25647,10 +26169,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>343</v>
+        <v>342.37</v>
       </c>
       <c r="F2" t="n">
-        <v>4194867609600</v>
+        <v>4187162935296</v>
       </c>
       <c r="G2" t="n">
         <v>19.93</v>
@@ -25659,39 +26181,39 @@
         <v>14.73894</v>
       </c>
       <c r="I2" t="n">
-        <v>17.210236</v>
+        <v>17.178625</v>
       </c>
       <c r="J2" t="n">
-        <v>23.271687</v>
+        <v>23.228943</v>
       </c>
       <c r="K2" t="n">
         <v>0.96</v>
       </c>
       <c r="L2" t="n">
-        <v>9.40836</v>
+        <v>9.391080000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05810495626822158</v>
+        <v>0.05821187604054093</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04297067055393586</v>
+        <v>0.04304974150772556</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.04682000160217285</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003869329598652035</v>
+        <v>-0.003770260094447295</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11 16:09:13</t>
+          <t>2026-08-12 16:07:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -25705,51 +26227,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>503.81</v>
+        <v>492.43</v>
       </c>
       <c r="F3" t="n">
-        <v>3741064101888</v>
+        <v>3656561459200</v>
       </c>
       <c r="G3" t="n">
-        <v>17.97</v>
+        <v>17.94</v>
       </c>
       <c r="H3" t="n">
         <v>23.55269</v>
       </c>
       <c r="I3" t="n">
-        <v>28.036173</v>
+        <v>27.448717</v>
       </c>
       <c r="J3" t="n">
-        <v>21.390762</v>
+        <v>20.907589</v>
       </c>
       <c r="K3" t="n">
         <v>1.65</v>
       </c>
       <c r="L3" t="n">
-        <v>11.273732</v>
+        <v>11.019082</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03566820825311129</v>
+        <v>0.03643157403082672</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04674915146583037</v>
+        <v>0.0478295189163942</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.04682000160217285</v>
       </c>
       <c r="P3" t="n">
-        <v>-9.084868675752339e-05</v>
+        <v>0.001009517314221352</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-11 16:09:13</t>
+          <t>2026-08-12 16:07:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -25763,51 +26285,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>599.12</v>
+        <v>578.85</v>
       </c>
       <c r="F4" t="n">
-        <v>1526261874688</v>
+        <v>1474623832064</v>
       </c>
       <c r="G4" t="n">
-        <v>26.53</v>
+        <v>26.54</v>
       </c>
       <c r="H4" t="n">
         <v>34.885</v>
       </c>
       <c r="I4" t="n">
-        <v>22.582735</v>
+        <v>21.810472</v>
       </c>
       <c r="J4" t="n">
-        <v>17.174145</v>
+        <v>16.593092</v>
       </c>
       <c r="K4" t="n">
         <v>0.89</v>
       </c>
       <c r="L4" t="n">
-        <v>6.6868873</v>
+        <v>6.4606495</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04428161303244759</v>
+        <v>0.04584952923900838</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05822706636400053</v>
+        <v>0.06026604474388874</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.04682000160217285</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01138706621141264</v>
+        <v>0.01344604314171589</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-11 16:09:13</t>
+          <t>2026-08-12 16:07:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -25821,51 +26343,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>272.27</v>
+        <v>267.28</v>
       </c>
       <c r="F5" t="n">
-        <v>2936789270528</v>
+        <v>2882965864448</v>
       </c>
       <c r="G5" t="n">
-        <v>12.43</v>
+        <v>12.44</v>
       </c>
       <c r="H5" t="n">
         <v>10.33054</v>
       </c>
       <c r="I5" t="n">
-        <v>21.904263</v>
+        <v>21.48553</v>
       </c>
       <c r="J5" t="n">
-        <v>26.355833</v>
+        <v>25.8728</v>
       </c>
       <c r="K5" t="n">
         <v>1.48</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7860835</v>
+        <v>3.7166946</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04565321188526095</v>
+        <v>0.04654295121221191</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03794226319462298</v>
+        <v>0.03865062855432505</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.04682000160217285</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.008897736957964912</v>
+        <v>-0.008169373047847803</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-11 16:09:13</t>
+          <t>2026-08-12 16:07:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -25879,10 +26401,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>304.91</v>
+        <v>302.25</v>
       </c>
       <c r="F6" t="n">
-        <v>4449911701504</v>
+        <v>4411090796544</v>
       </c>
       <c r="G6" t="n">
         <v>8.720000000000001</v>
@@ -25891,39 +26413,39 @@
         <v>9.507709999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>34.966743</v>
+        <v>34.661697</v>
       </c>
       <c r="J6" t="n">
-        <v>32.06976</v>
+        <v>31.789988</v>
       </c>
       <c r="K6" t="n">
         <v>2.49</v>
       </c>
       <c r="L6" t="n">
-        <v>9.532332</v>
+        <v>9.449172000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0285986028664196</v>
+        <v>0.02885028949545079</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03118202092420714</v>
+        <v>0.03145644334160463</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.04682000160217285</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01565797922838075</v>
+        <v>-0.01536355826056823</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-11 16:09:13</t>
+          <t>2026-08-12 16:07:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -25937,51 +26459,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>217.5</v>
+        <v>224.09</v>
       </c>
       <c r="F7" t="n">
-        <v>5268067319808</v>
+        <v>5427683655680</v>
       </c>
       <c r="G7" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
       <c r="H7" t="n">
-        <v>12.89043</v>
+        <v>12.81649</v>
       </c>
       <c r="I7" t="n">
-        <v>33.307808</v>
+        <v>34.369633</v>
       </c>
       <c r="J7" t="n">
-        <v>16.872982</v>
+        <v>17.484507</v>
       </c>
       <c r="K7" t="n">
         <v>0.6</v>
       </c>
       <c r="L7" t="n">
-        <v>20.782068</v>
+        <v>21.411741</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03002298850574713</v>
+        <v>0.02909545271988933</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05926634482758621</v>
+        <v>0.05719349368557276</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.04682000160217285</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01242634467499831</v>
+        <v>0.01037349208339991</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-11 16:09:13</t>
+          <t>2026-08-12 16:07:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -25995,51 +26517,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>474.32</v>
+        <v>482.93</v>
       </c>
       <c r="F8" t="n">
-        <v>774315573248</v>
+        <v>788371144704</v>
       </c>
       <c r="G8" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="H8" t="n">
         <v>15.45987</v>
       </c>
       <c r="I8" t="n">
-        <v>121.620514</v>
+        <v>122.57106</v>
       </c>
       <c r="J8" t="n">
-        <v>30.680723</v>
+        <v>31.237648</v>
       </c>
       <c r="K8" t="n">
         <v>1.01</v>
       </c>
       <c r="L8" t="n">
-        <v>18.74629</v>
+        <v>19.086578</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008222297183336145</v>
+        <v>0.008158532292464746</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03259375527070332</v>
+        <v>0.03201265193713375</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.04682000160217285</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01424624488188457</v>
+        <v>-0.0148073496650391</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-11 16:09:13</t>
+          <t>2026-08-12 16:07:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -26053,51 +26575,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>416.08</v>
+        <v>416.05</v>
       </c>
       <c r="F9" t="n">
-        <v>1979533885440</v>
+        <v>1979391279104</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>5.99</v>
       </c>
       <c r="H9" t="n">
         <v>19.53066</v>
       </c>
       <c r="I9" t="n">
-        <v>69.346664</v>
+        <v>69.45743</v>
       </c>
       <c r="J9" t="n">
-        <v>21.303938</v>
+        <v>21.302402</v>
       </c>
       <c r="K9" t="n">
         <v>0.47</v>
       </c>
       <c r="L9" t="n">
-        <v>26.231152</v>
+        <v>26.229263</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01442030378773313</v>
+        <v>0.01439730801586348</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04693967506248799</v>
+        <v>0.04694305972839803</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.04682000160217285</v>
       </c>
       <c r="P9" t="n">
-        <v>9.967490990009376e-05</v>
+        <v>0.0001230581262251784</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-11 16:09:13</t>
+          <t>2026-08-12 16:07:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -26111,10 +26633,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>74.79000000000001</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>311421042688</v>
+        <v>309005942784</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -26123,28 +26645,28 @@
         <v>3.81668</v>
       </c>
       <c r="I10" t="n">
-        <v>23.518867</v>
+        <v>23.336477</v>
       </c>
       <c r="J10" t="n">
-        <v>19.595566</v>
+        <v>19.4436</v>
       </c>
       <c r="K10" t="n">
         <v>1.71</v>
       </c>
       <c r="L10" t="n">
-        <v>6.4382076</v>
+        <v>6.388279</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04251905334937826</v>
+        <v>0.04285136774019675</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0510319561438695</v>
+        <v>0.05143080447379059</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.04682000160217285</v>
       </c>
       <c r="P10" t="n">
-        <v>0.004191955991281603</v>
+        <v>0.00461080287161774</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="History" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Latest" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Latest" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P442"/>
+  <dimension ref="A1:P451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25575,16 +25575,16 @@
         <v>9.449172000000001</v>
       </c>
       <c r="M434" t="n">
-        <v>0.02885028949545079</v>
+        <v>0.0288502894954507</v>
       </c>
       <c r="N434" t="n">
-        <v>0.03145644334160463</v>
+        <v>0.0314564433416046</v>
       </c>
       <c r="O434" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.0468200016021728</v>
       </c>
       <c r="P434" t="n">
-        <v>-0.01536355826056823</v>
+        <v>-0.0153635582605682</v>
       </c>
     </row>
     <row r="435">
@@ -25633,13 +25633,13 @@
         <v>19.086578</v>
       </c>
       <c r="M435" t="n">
-        <v>0.008158532292464746</v>
+        <v>0.0081585322924647</v>
       </c>
       <c r="N435" t="n">
-        <v>0.03201265193713375</v>
+        <v>0.0320126519371337</v>
       </c>
       <c r="O435" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.0468200016021728</v>
       </c>
       <c r="P435" t="n">
         <v>-0.0148073496650391</v>
@@ -25691,16 +25691,16 @@
         <v>3.7166946</v>
       </c>
       <c r="M436" t="n">
-        <v>0.04654295121221191</v>
+        <v>0.0465429512122119</v>
       </c>
       <c r="N436" t="n">
-        <v>0.03865062855432505</v>
+        <v>0.038650628554325</v>
       </c>
       <c r="O436" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.0468200016021728</v>
       </c>
       <c r="P436" t="n">
-        <v>-0.008169373047847803</v>
+        <v>-0.008169373047847799</v>
       </c>
     </row>
     <row r="437">
@@ -25749,16 +25749,16 @@
         <v>26.229263</v>
       </c>
       <c r="M437" t="n">
-        <v>0.01439730801586348</v>
+        <v>0.0143973080158634</v>
       </c>
       <c r="N437" t="n">
-        <v>0.04694305972839803</v>
+        <v>0.046943059728398</v>
       </c>
       <c r="O437" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.0468200016021728</v>
       </c>
       <c r="P437" t="n">
-        <v>0.0001230581262251784</v>
+        <v>0.0001230581262251</v>
       </c>
     </row>
     <row r="438">
@@ -25807,16 +25807,16 @@
         <v>9.391080000000001</v>
       </c>
       <c r="M438" t="n">
-        <v>0.05821187604054093</v>
+        <v>0.0582118760405409</v>
       </c>
       <c r="N438" t="n">
-        <v>0.04304974150772556</v>
+        <v>0.0430497415077255</v>
       </c>
       <c r="O438" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.0468200016021728</v>
       </c>
       <c r="P438" t="n">
-        <v>-0.003770260094447295</v>
+        <v>-0.0037702600944472</v>
       </c>
     </row>
     <row r="439">
@@ -25865,16 +25865,16 @@
         <v>6.4606495</v>
       </c>
       <c r="M439" t="n">
-        <v>0.04584952923900838</v>
+        <v>0.0458495292390083</v>
       </c>
       <c r="N439" t="n">
-        <v>0.06026604474388874</v>
+        <v>0.0602660447438887</v>
       </c>
       <c r="O439" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.0468200016021728</v>
       </c>
       <c r="P439" t="n">
-        <v>0.01344604314171589</v>
+        <v>0.0134460431417158</v>
       </c>
     </row>
     <row r="440">
@@ -25923,16 +25923,16 @@
         <v>11.019082</v>
       </c>
       <c r="M440" t="n">
-        <v>0.03643157403082672</v>
+        <v>0.0364315740308267</v>
       </c>
       <c r="N440" t="n">
         <v>0.0478295189163942</v>
       </c>
       <c r="O440" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.0468200016021728</v>
       </c>
       <c r="P440" t="n">
-        <v>0.001009517314221352</v>
+        <v>0.0010095173142213</v>
       </c>
     </row>
     <row r="441">
@@ -25981,16 +25981,16 @@
         <v>6.388279</v>
       </c>
       <c r="M441" t="n">
-        <v>0.04285136774019675</v>
+        <v>0.0428513677401967</v>
       </c>
       <c r="N441" t="n">
-        <v>0.05143080447379059</v>
+        <v>0.0514308044737905</v>
       </c>
       <c r="O441" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.0468200016021728</v>
       </c>
       <c r="P441" t="n">
-        <v>0.00461080287161774</v>
+        <v>0.0046108028716177</v>
       </c>
     </row>
     <row r="442">
@@ -26039,16 +26039,538 @@
         <v>21.411741</v>
       </c>
       <c r="M442" t="n">
-        <v>0.02909545271988933</v>
+        <v>0.0290954527198893</v>
       </c>
       <c r="N442" t="n">
-        <v>0.05719349368557276</v>
+        <v>0.0571934936855727</v>
       </c>
       <c r="O442" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.0468200016021728</v>
       </c>
       <c r="P442" t="n">
-        <v>0.01037349208339991</v>
+        <v>0.0103734920833999</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2026-08-13 16:09:08</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>305.26</v>
+      </c>
+      <c r="F443" t="n">
+        <v>4455019315200</v>
+      </c>
+      <c r="G443" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="H443" t="n">
+        <v>9.507709999999999</v>
+      </c>
+      <c r="I443" t="n">
+        <v>34.926777</v>
+      </c>
+      <c r="J443" t="n">
+        <v>32.106575</v>
+      </c>
+      <c r="K443" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="L443" t="n">
+        <v>9.543272999999999</v>
+      </c>
+      <c r="M443" t="n">
+        <v>0.02863133066893796</v>
+      </c>
+      <c r="N443" t="n">
+        <v>0.03114626875450436</v>
+      </c>
+      <c r="O443" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P443" t="n">
+        <v>-0.01526372918555912</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>2026-08-13 16:09:08</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>483.01</v>
+      </c>
+      <c r="F444" t="n">
+        <v>788501757952</v>
+      </c>
+      <c r="G444" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H444" t="n">
+        <v>15.45987</v>
+      </c>
+      <c r="I444" t="n">
+        <v>123.53197</v>
+      </c>
+      <c r="J444" t="n">
+        <v>31.242825</v>
+      </c>
+      <c r="K444" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L444" t="n">
+        <v>19.08974</v>
+      </c>
+      <c r="M444" t="n">
+        <v>0.008095070495434878</v>
+      </c>
+      <c r="N444" t="n">
+        <v>0.03200734974431171</v>
+      </c>
+      <c r="O444" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P444" t="n">
+        <v>-0.01440264819575177</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>2026-08-13 16:09:08</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>265.13</v>
+      </c>
+      <c r="F445" t="n">
+        <v>2859775295488</v>
+      </c>
+      <c r="G445" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H445" t="n">
+        <v>10.3815</v>
+      </c>
+      <c r="I445" t="n">
+        <v>21.329847</v>
+      </c>
+      <c r="J445" t="n">
+        <v>25.538698</v>
+      </c>
+      <c r="K445" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L445" t="n">
+        <v>3.6867976</v>
+      </c>
+      <c r="M445" t="n">
+        <v>0.0468826613359484</v>
+      </c>
+      <c r="N445" t="n">
+        <v>0.03915626296533777</v>
+      </c>
+      <c r="O445" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P445" t="n">
+        <v>-0.007253734974725715</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2026-08-13 16:09:08</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>417.82</v>
+      </c>
+      <c r="F446" t="n">
+        <v>1987812261888</v>
+      </c>
+      <c r="G446" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="H446" t="n">
+        <v>19.53066</v>
+      </c>
+      <c r="I446" t="n">
+        <v>69.75292</v>
+      </c>
+      <c r="J446" t="n">
+        <v>21.39303</v>
+      </c>
+      <c r="K446" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L446" t="n">
+        <v>26.34085</v>
+      </c>
+      <c r="M446" t="n">
+        <v>0.01433631707433823</v>
+      </c>
+      <c r="N446" t="n">
+        <v>0.04674419606529127</v>
+      </c>
+      <c r="O446" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P446" t="n">
+        <v>0.0003341981252277942</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>2026-08-13 16:09:08</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>343.94</v>
+      </c>
+      <c r="F447" t="n">
+        <v>4206363934720</v>
+      </c>
+      <c r="G447" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H447" t="n">
+        <v>14.73894</v>
+      </c>
+      <c r="I447" t="n">
+        <v>17.2574</v>
+      </c>
+      <c r="J447" t="n">
+        <v>23.335464</v>
+      </c>
+      <c r="K447" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L447" t="n">
+        <v>9.434144</v>
+      </c>
+      <c r="M447" t="n">
+        <v>0.05794615339884863</v>
+      </c>
+      <c r="N447" t="n">
+        <v>0.04285323021457231</v>
+      </c>
+      <c r="O447" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P447" t="n">
+        <v>-0.003556767725491169</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>2026-08-13 16:09:08</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>594.97</v>
+      </c>
+      <c r="F448" t="n">
+        <v>1515689738240</v>
+      </c>
+      <c r="G448" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="H448" t="n">
+        <v>34.885</v>
+      </c>
+      <c r="I448" t="n">
+        <v>22.392548</v>
+      </c>
+      <c r="J448" t="n">
+        <v>17.055182</v>
+      </c>
+      <c r="K448" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L448" t="n">
+        <v>6.6405683</v>
+      </c>
+      <c r="M448" t="n">
+        <v>0.04465771383431097</v>
+      </c>
+      <c r="N448" t="n">
+        <v>0.05863320839706203</v>
+      </c>
+      <c r="O448" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P448" t="n">
+        <v>0.01222321045699855</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2026-08-13 16:09:08</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>496.88</v>
+      </c>
+      <c r="F449" t="n">
+        <v>3689605234688</v>
+      </c>
+      <c r="G449" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="H449" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I449" t="n">
+        <v>27.65053</v>
+      </c>
+      <c r="J449" t="n">
+        <v>21.078102</v>
+      </c>
+      <c r="K449" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L449" t="n">
+        <v>11.11866</v>
+      </c>
+      <c r="M449" t="n">
+        <v>0.03616567380454033</v>
+      </c>
+      <c r="N449" t="n">
+        <v>0.04744260183545323</v>
+      </c>
+      <c r="O449" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P449" t="n">
+        <v>0.001032603895389748</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>2026-08-13 16:09:08</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>78.23999999999999</v>
+      </c>
+      <c r="F450" t="n">
+        <v>325786632192</v>
+      </c>
+      <c r="G450" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H450" t="n">
+        <v>3.81668</v>
+      </c>
+      <c r="I450" t="n">
+        <v>24.603773</v>
+      </c>
+      <c r="J450" t="n">
+        <v>20.49949</v>
+      </c>
+      <c r="K450" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L450" t="n">
+        <v>6.735197</v>
+      </c>
+      <c r="M450" t="n">
+        <v>0.04064417177914111</v>
+      </c>
+      <c r="N450" t="n">
+        <v>0.0487816973415133</v>
+      </c>
+      <c r="O450" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P450" t="n">
+        <v>0.002371699401449816</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>2026-08-13 16:09:08</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>225.3</v>
+      </c>
+      <c r="F451" t="n">
+        <v>5456991354880</v>
+      </c>
+      <c r="G451" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="H451" t="n">
+        <v>12.81649</v>
+      </c>
+      <c r="I451" t="n">
+        <v>34.555214</v>
+      </c>
+      <c r="J451" t="n">
+        <v>17.578917</v>
+      </c>
+      <c r="K451" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L451" t="n">
+        <v>21.527357</v>
+      </c>
+      <c r="M451" t="n">
+        <v>0.02893919218819352</v>
+      </c>
+      <c r="N451" t="n">
+        <v>0.05688632933865957</v>
+      </c>
+      <c r="O451" t="n">
+        <v>0.04640999794006348</v>
+      </c>
+      <c r="P451" t="n">
+        <v>0.01047633139859609</v>
       </c>
     </row>
   </sheetData>
@@ -26150,12 +26672,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-12 16:07:37</t>
+          <t>2026-08-13 16:09:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -26169,10 +26691,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>342.37</v>
+        <v>343.94</v>
       </c>
       <c r="F2" t="n">
-        <v>4187162935296</v>
+        <v>4206363934720</v>
       </c>
       <c r="G2" t="n">
         <v>19.93</v>
@@ -26181,39 +26703,39 @@
         <v>14.73894</v>
       </c>
       <c r="I2" t="n">
-        <v>17.178625</v>
+        <v>17.2574</v>
       </c>
       <c r="J2" t="n">
-        <v>23.228943</v>
+        <v>23.335464</v>
       </c>
       <c r="K2" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="L2" t="n">
-        <v>9.391080000000001</v>
+        <v>9.434144</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05821187604054093</v>
+        <v>0.05794615339884863</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04304974150772556</v>
+        <v>0.04285323021457231</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003770260094447295</v>
+        <v>-0.003556767725491169</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-12 16:07:37</t>
+          <t>2026-08-13 16:09:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -26227,51 +26749,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>492.43</v>
+        <v>496.88</v>
       </c>
       <c r="F3" t="n">
-        <v>3656561459200</v>
+        <v>3689605234688</v>
       </c>
       <c r="G3" t="n">
-        <v>17.94</v>
+        <v>17.97</v>
       </c>
       <c r="H3" t="n">
-        <v>23.55269</v>
+        <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>27.448717</v>
+        <v>27.65053</v>
       </c>
       <c r="J3" t="n">
-        <v>20.907589</v>
+        <v>21.078102</v>
       </c>
       <c r="K3" t="n">
         <v>1.65</v>
       </c>
       <c r="L3" t="n">
-        <v>11.019082</v>
+        <v>11.11866</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03643157403082672</v>
+        <v>0.03616567380454033</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0478295189163942</v>
+        <v>0.04744260183545323</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001009517314221352</v>
+        <v>0.001032603895389748</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-12 16:07:37</t>
+          <t>2026-08-13 16:09:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -26285,51 +26807,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>578.85</v>
+        <v>594.97</v>
       </c>
       <c r="F4" t="n">
-        <v>1474623832064</v>
+        <v>1515689738240</v>
       </c>
       <c r="G4" t="n">
-        <v>26.54</v>
+        <v>26.57</v>
       </c>
       <c r="H4" t="n">
         <v>34.885</v>
       </c>
       <c r="I4" t="n">
-        <v>21.810472</v>
+        <v>22.392548</v>
       </c>
       <c r="J4" t="n">
-        <v>16.593092</v>
+        <v>17.055182</v>
       </c>
       <c r="K4" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="L4" t="n">
-        <v>6.4606495</v>
+        <v>6.6405683</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04584952923900838</v>
+        <v>0.04465771383431097</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06026604474388874</v>
+        <v>0.05863320839706203</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01344604314171589</v>
+        <v>0.01222321045699855</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-12 16:07:37</t>
+          <t>2026-08-13 16:09:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -26343,51 +26865,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>267.28</v>
+        <v>265.13</v>
       </c>
       <c r="F5" t="n">
-        <v>2882965864448</v>
+        <v>2859775295488</v>
       </c>
       <c r="G5" t="n">
-        <v>12.44</v>
+        <v>12.43</v>
       </c>
       <c r="H5" t="n">
-        <v>10.33054</v>
+        <v>10.3815</v>
       </c>
       <c r="I5" t="n">
-        <v>21.48553</v>
+        <v>21.329847</v>
       </c>
       <c r="J5" t="n">
-        <v>25.8728</v>
+        <v>25.538698</v>
       </c>
       <c r="K5" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7166946</v>
+        <v>3.6867976</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04654295121221191</v>
+        <v>0.0468826613359484</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03865062855432505</v>
+        <v>0.03915626296533777</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.008169373047847803</v>
+        <v>-0.007253734974725715</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-12 16:07:37</t>
+          <t>2026-08-13 16:09:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -26401,51 +26923,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>302.25</v>
+        <v>305.26</v>
       </c>
       <c r="F6" t="n">
-        <v>4411090796544</v>
+        <v>4455019315200</v>
       </c>
       <c r="G6" t="n">
-        <v>8.720000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="H6" t="n">
         <v>9.507709999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>34.661697</v>
+        <v>34.926777</v>
       </c>
       <c r="J6" t="n">
-        <v>31.789988</v>
+        <v>32.106575</v>
       </c>
       <c r="K6" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="L6" t="n">
-        <v>9.449172000000001</v>
+        <v>9.543272999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02885028949545079</v>
+        <v>0.02863133066893796</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03145644334160463</v>
+        <v>0.03114626875450436</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01536355826056823</v>
+        <v>-0.01526372918555912</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-12 16:07:37</t>
+          <t>2026-08-13 16:09:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -26459,10 +26981,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224.09</v>
+        <v>225.3</v>
       </c>
       <c r="F7" t="n">
-        <v>5427683655680</v>
+        <v>5456991354880</v>
       </c>
       <c r="G7" t="n">
         <v>6.52</v>
@@ -26471,39 +26993,39 @@
         <v>12.81649</v>
       </c>
       <c r="I7" t="n">
-        <v>34.369633</v>
+        <v>34.555214</v>
       </c>
       <c r="J7" t="n">
-        <v>17.484507</v>
+        <v>17.578917</v>
       </c>
       <c r="K7" t="n">
         <v>0.6</v>
       </c>
       <c r="L7" t="n">
-        <v>21.411741</v>
+        <v>21.527357</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02909545271988933</v>
+        <v>0.02893919218819352</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05719349368557276</v>
+        <v>0.05688632933865957</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01037349208339991</v>
+        <v>0.01047633139859609</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-12 16:07:37</t>
+          <t>2026-08-13 16:09:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -26517,51 +27039,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>482.93</v>
+        <v>483.01</v>
       </c>
       <c r="F8" t="n">
-        <v>788371144704</v>
+        <v>788501757952</v>
       </c>
       <c r="G8" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="H8" t="n">
         <v>15.45987</v>
       </c>
       <c r="I8" t="n">
-        <v>122.57106</v>
+        <v>123.53197</v>
       </c>
       <c r="J8" t="n">
-        <v>31.237648</v>
+        <v>31.242825</v>
       </c>
       <c r="K8" t="n">
         <v>1.01</v>
       </c>
       <c r="L8" t="n">
-        <v>19.086578</v>
+        <v>19.08974</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008158532292464746</v>
+        <v>0.008095070495434878</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03201265193713375</v>
+        <v>0.03200734974431171</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0148073496650391</v>
+        <v>-0.01440264819575177</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-12 16:07:37</t>
+          <t>2026-08-13 16:09:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -26575,10 +27097,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>416.05</v>
+        <v>417.82</v>
       </c>
       <c r="F9" t="n">
-        <v>1979391279104</v>
+        <v>1987812261888</v>
       </c>
       <c r="G9" t="n">
         <v>5.99</v>
@@ -26587,39 +27109,39 @@
         <v>19.53066</v>
       </c>
       <c r="I9" t="n">
-        <v>69.45743</v>
+        <v>69.75292</v>
       </c>
       <c r="J9" t="n">
-        <v>21.302402</v>
+        <v>21.39303</v>
       </c>
       <c r="K9" t="n">
         <v>0.47</v>
       </c>
       <c r="L9" t="n">
-        <v>26.229263</v>
+        <v>26.34085</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01439730801586348</v>
+        <v>0.01433631707433823</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04694305972839803</v>
+        <v>0.04674419606529127</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0001230581262251784</v>
+        <v>0.0003341981252277942</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-12 16:07:37</t>
+          <t>2026-08-13 16:09:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -26633,10 +27155,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>74.20999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>309005942784</v>
+        <v>325786632192</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -26645,28 +27167,28 @@
         <v>3.81668</v>
       </c>
       <c r="I10" t="n">
-        <v>23.336477</v>
+        <v>24.603773</v>
       </c>
       <c r="J10" t="n">
-        <v>19.4436</v>
+        <v>20.49949</v>
       </c>
       <c r="K10" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="L10" t="n">
-        <v>6.388279</v>
+        <v>6.735197</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04285136774019675</v>
+        <v>0.04064417177914111</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05143080447379059</v>
+        <v>0.0487816973415133</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04682000160217285</v>
+        <v>0.04640999794006348</v>
       </c>
       <c r="P10" t="n">
-        <v>0.00461080287161774</v>
+        <v>0.002371699401449816</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P451"/>
+  <dimension ref="A1:P460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26097,16 +26097,16 @@
         <v>9.543272999999999</v>
       </c>
       <c r="M443" t="n">
-        <v>0.02863133066893796</v>
+        <v>0.0286313306689379</v>
       </c>
       <c r="N443" t="n">
-        <v>0.03114626875450436</v>
+        <v>0.0311462687545043</v>
       </c>
       <c r="O443" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P443" t="n">
-        <v>-0.01526372918555912</v>
+        <v>-0.0152637291855591</v>
       </c>
     </row>
     <row r="444">
@@ -26155,16 +26155,16 @@
         <v>19.08974</v>
       </c>
       <c r="M444" t="n">
-        <v>0.008095070495434878</v>
+        <v>0.0080950704954348</v>
       </c>
       <c r="N444" t="n">
-        <v>0.03200734974431171</v>
+        <v>0.0320073497443117</v>
       </c>
       <c r="O444" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P444" t="n">
-        <v>-0.01440264819575177</v>
+        <v>-0.0144026481957517</v>
       </c>
     </row>
     <row r="445">
@@ -26216,13 +26216,13 @@
         <v>0.0468826613359484</v>
       </c>
       <c r="N445" t="n">
-        <v>0.03915626296533777</v>
+        <v>0.0391562629653377</v>
       </c>
       <c r="O445" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P445" t="n">
-        <v>-0.007253734974725715</v>
+        <v>-0.0072537349747257</v>
       </c>
     </row>
     <row r="446">
@@ -26271,16 +26271,16 @@
         <v>26.34085</v>
       </c>
       <c r="M446" t="n">
-        <v>0.01433631707433823</v>
+        <v>0.0143363170743382</v>
       </c>
       <c r="N446" t="n">
-        <v>0.04674419606529127</v>
+        <v>0.0467441960652912</v>
       </c>
       <c r="O446" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P446" t="n">
-        <v>0.0003341981252277942</v>
+        <v>0.0003341981252277</v>
       </c>
     </row>
     <row r="447">
@@ -26329,16 +26329,16 @@
         <v>9.434144</v>
       </c>
       <c r="M447" t="n">
-        <v>0.05794615339884863</v>
+        <v>0.0579461533988486</v>
       </c>
       <c r="N447" t="n">
-        <v>0.04285323021457231</v>
+        <v>0.0428532302145723</v>
       </c>
       <c r="O447" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P447" t="n">
-        <v>-0.003556767725491169</v>
+        <v>-0.0035567677254911</v>
       </c>
     </row>
     <row r="448">
@@ -26387,16 +26387,16 @@
         <v>6.6405683</v>
       </c>
       <c r="M448" t="n">
-        <v>0.04465771383431097</v>
+        <v>0.0446577138343109</v>
       </c>
       <c r="N448" t="n">
-        <v>0.05863320839706203</v>
+        <v>0.058633208397062</v>
       </c>
       <c r="O448" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P448" t="n">
-        <v>0.01222321045699855</v>
+        <v>0.0122232104569985</v>
       </c>
     </row>
     <row r="449">
@@ -26445,16 +26445,16 @@
         <v>11.11866</v>
       </c>
       <c r="M449" t="n">
-        <v>0.03616567380454033</v>
+        <v>0.0361656738045403</v>
       </c>
       <c r="N449" t="n">
-        <v>0.04744260183545323</v>
+        <v>0.0474426018354532</v>
       </c>
       <c r="O449" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P449" t="n">
-        <v>0.001032603895389748</v>
+        <v>0.0010326038953897</v>
       </c>
     </row>
     <row r="450">
@@ -26503,16 +26503,16 @@
         <v>6.735197</v>
       </c>
       <c r="M450" t="n">
-        <v>0.04064417177914111</v>
+        <v>0.0406441717791411</v>
       </c>
       <c r="N450" t="n">
-        <v>0.0487816973415133</v>
+        <v>0.0487816973415132</v>
       </c>
       <c r="O450" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P450" t="n">
-        <v>0.002371699401449816</v>
+        <v>0.0023716994014498</v>
       </c>
     </row>
     <row r="451">
@@ -26561,16 +26561,538 @@
         <v>21.527357</v>
       </c>
       <c r="M451" t="n">
-        <v>0.02893919218819352</v>
+        <v>0.0289391921881935</v>
       </c>
       <c r="N451" t="n">
-        <v>0.05688632933865957</v>
+        <v>0.0568863293386595</v>
       </c>
       <c r="O451" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.0464099979400634</v>
       </c>
       <c r="P451" t="n">
-        <v>0.01047633139859609</v>
+        <v>0.010476331398596</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:45:34</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>305.93</v>
+      </c>
+      <c r="F452" t="n">
+        <v>4464797286400</v>
+      </c>
+      <c r="G452" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H452" t="n">
+        <v>9.507709999999999</v>
+      </c>
+      <c r="I452" t="n">
+        <v>35.04353</v>
+      </c>
+      <c r="J452" t="n">
+        <v>32.17704</v>
+      </c>
+      <c r="K452" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L452" t="n">
+        <v>9.564218500000001</v>
+      </c>
+      <c r="M452" t="n">
+        <v>0.02853593959402478</v>
+      </c>
+      <c r="N452" t="n">
+        <v>0.03107805707187919</v>
+      </c>
+      <c r="O452" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P452" t="n">
+        <v>-0.0158819439199421</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:45:34</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>514.39</v>
+      </c>
+      <c r="F453" t="n">
+        <v>839728824320</v>
+      </c>
+      <c r="G453" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H453" t="n">
+        <v>15.45987</v>
+      </c>
+      <c r="I453" t="n">
+        <v>131.55754</v>
+      </c>
+      <c r="J453" t="n">
+        <v>33.272594</v>
+      </c>
+      <c r="K453" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L453" t="n">
+        <v>20.329954</v>
+      </c>
+      <c r="M453" t="n">
+        <v>0.007601236415948989</v>
+      </c>
+      <c r="N453" t="n">
+        <v>0.03005476389509905</v>
+      </c>
+      <c r="O453" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P453" t="n">
+        <v>-0.01690523709672223</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:45:34</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>262.65</v>
+      </c>
+      <c r="F454" t="n">
+        <v>2833025073152</v>
+      </c>
+      <c r="G454" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H454" t="n">
+        <v>10.39346</v>
+      </c>
+      <c r="I454" t="n">
+        <v>21.13033</v>
+      </c>
+      <c r="J454" t="n">
+        <v>25.270699</v>
+      </c>
+      <c r="K454" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L454" t="n">
+        <v>3.6523116</v>
+      </c>
+      <c r="M454" t="n">
+        <v>0.04732533790215115</v>
+      </c>
+      <c r="N454" t="n">
+        <v>0.0395715210355987</v>
+      </c>
+      <c r="O454" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P454" t="n">
+        <v>-0.007388479956222584</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:45:34</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>392.99</v>
+      </c>
+      <c r="F455" t="n">
+        <v>1869681393664</v>
+      </c>
+      <c r="G455" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H455" t="n">
+        <v>19.53066</v>
+      </c>
+      <c r="I455" t="n">
+        <v>65.28073000000001</v>
+      </c>
+      <c r="J455" t="n">
+        <v>20.121695</v>
+      </c>
+      <c r="K455" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L455" t="n">
+        <v>24.775478</v>
+      </c>
+      <c r="M455" t="n">
+        <v>0.01531845594035471</v>
+      </c>
+      <c r="N455" t="n">
+        <v>0.04969760044784854</v>
+      </c>
+      <c r="O455" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P455" t="n">
+        <v>0.002737599456027258</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:45:34</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>343.54</v>
+      </c>
+      <c r="F456" t="n">
+        <v>4201472065536</v>
+      </c>
+      <c r="G456" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="H456" t="n">
+        <v>14.74619</v>
+      </c>
+      <c r="I456" t="n">
+        <v>17.254646</v>
+      </c>
+      <c r="J456" t="n">
+        <v>23.296865</v>
+      </c>
+      <c r="K456" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L456" t="n">
+        <v>9.423171999999999</v>
+      </c>
+      <c r="M456" t="n">
+        <v>0.05795540548407754</v>
+      </c>
+      <c r="N456" t="n">
+        <v>0.04292423007510043</v>
+      </c>
+      <c r="O456" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P456" t="n">
+        <v>-0.00403577091672086</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:45:34</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>589.85</v>
+      </c>
+      <c r="F457" t="n">
+        <v>1502646501376</v>
+      </c>
+      <c r="G457" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H457" t="n">
+        <v>34.885</v>
+      </c>
+      <c r="I457" t="n">
+        <v>22.224941</v>
+      </c>
+      <c r="J457" t="n">
+        <v>16.908413</v>
+      </c>
+      <c r="K457" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L457" t="n">
+        <v>6.583423</v>
+      </c>
+      <c r="M457" t="n">
+        <v>0.04499449012460795</v>
+      </c>
+      <c r="N457" t="n">
+        <v>0.05914215478511486</v>
+      </c>
+      <c r="O457" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P457" t="n">
+        <v>0.01218215379329357</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:45:34</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>495.4</v>
+      </c>
+      <c r="F458" t="n">
+        <v>3678615371776</v>
+      </c>
+      <c r="G458" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H458" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I458" t="n">
+        <v>27.61427</v>
+      </c>
+      <c r="J458" t="n">
+        <v>21.015318</v>
+      </c>
+      <c r="K458" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L458" t="n">
+        <v>11.085542</v>
+      </c>
+      <c r="M458" t="n">
+        <v>0.03621316108195398</v>
+      </c>
+      <c r="N458" t="n">
+        <v>0.04758433589018975</v>
+      </c>
+      <c r="O458" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P458" t="n">
+        <v>0.0006243348983684602</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:45:34</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>78.16</v>
+      </c>
+      <c r="F459" t="n">
+        <v>325453545472</v>
+      </c>
+      <c r="G459" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H459" t="n">
+        <v>3.81668</v>
+      </c>
+      <c r="I459" t="n">
+        <v>24.578617</v>
+      </c>
+      <c r="J459" t="n">
+        <v>20.478533</v>
+      </c>
+      <c r="K459" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="L459" t="n">
+        <v>6.7283106</v>
+      </c>
+      <c r="M459" t="n">
+        <v>0.04068577277379734</v>
+      </c>
+      <c r="N459" t="n">
+        <v>0.04883162743091096</v>
+      </c>
+      <c r="O459" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P459" t="n">
+        <v>0.001871626439089669</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:45:34</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>225.16</v>
+      </c>
+      <c r="F460" t="n">
+        <v>5453600260096</v>
+      </c>
+      <c r="G460" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H460" t="n">
+        <v>12.81649</v>
+      </c>
+      <c r="I460" t="n">
+        <v>34.480858</v>
+      </c>
+      <c r="J460" t="n">
+        <v>17.567993</v>
+      </c>
+      <c r="K460" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L460" t="n">
+        <v>21.513979</v>
+      </c>
+      <c r="M460" t="n">
+        <v>0.02900159886303073</v>
+      </c>
+      <c r="N460" t="n">
+        <v>0.05692170012435602</v>
+      </c>
+      <c r="O460" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P460" t="n">
+        <v>0.009961699132534731</v>
       </c>
     </row>
   </sheetData>
@@ -26672,12 +27194,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-13 16:09:08</t>
+          <t>2026-08-14 15:45:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -26691,51 +27213,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>343.94</v>
+        <v>343.54</v>
       </c>
       <c r="F2" t="n">
-        <v>4206363934720</v>
+        <v>4201472065536</v>
       </c>
       <c r="G2" t="n">
-        <v>19.93</v>
+        <v>19.91</v>
       </c>
       <c r="H2" t="n">
-        <v>14.73894</v>
+        <v>14.74619</v>
       </c>
       <c r="I2" t="n">
-        <v>17.2574</v>
+        <v>17.254646</v>
       </c>
       <c r="J2" t="n">
-        <v>23.335464</v>
+        <v>23.296865</v>
       </c>
       <c r="K2" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="L2" t="n">
-        <v>9.434144</v>
+        <v>9.423171999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05794615339884863</v>
+        <v>0.05795540548407754</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04285323021457231</v>
+        <v>0.04292423007510043</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003556767725491169</v>
+        <v>-0.00403577091672086</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-13 16:09:08</t>
+          <t>2026-08-14 15:45:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -26749,51 +27271,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>496.88</v>
+        <v>495.4</v>
       </c>
       <c r="F3" t="n">
-        <v>3689605234688</v>
+        <v>3678615371776</v>
       </c>
       <c r="G3" t="n">
-        <v>17.97</v>
+        <v>17.94</v>
       </c>
       <c r="H3" t="n">
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>27.65053</v>
+        <v>27.61427</v>
       </c>
       <c r="J3" t="n">
-        <v>21.078102</v>
+        <v>21.015318</v>
       </c>
       <c r="K3" t="n">
         <v>1.65</v>
       </c>
       <c r="L3" t="n">
-        <v>11.11866</v>
+        <v>11.085542</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03616567380454033</v>
+        <v>0.03621316108195398</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04744260183545323</v>
+        <v>0.04758433589018975</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001032603895389748</v>
+        <v>0.0006243348983684602</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-13 16:09:08</t>
+          <t>2026-08-14 15:45:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -26807,51 +27329,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>594.97</v>
+        <v>589.85</v>
       </c>
       <c r="F4" t="n">
-        <v>1515689738240</v>
+        <v>1502646501376</v>
       </c>
       <c r="G4" t="n">
-        <v>26.57</v>
+        <v>26.54</v>
       </c>
       <c r="H4" t="n">
         <v>34.885</v>
       </c>
       <c r="I4" t="n">
-        <v>22.392548</v>
+        <v>22.224941</v>
       </c>
       <c r="J4" t="n">
-        <v>17.055182</v>
+        <v>16.908413</v>
       </c>
       <c r="K4" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="L4" t="n">
-        <v>6.6405683</v>
+        <v>6.583423</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04465771383431097</v>
+        <v>0.04499449012460795</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05863320839706203</v>
+        <v>0.05914215478511486</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01222321045699855</v>
+        <v>0.01218215379329357</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-13 16:09:08</t>
+          <t>2026-08-14 15:45:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -26865,51 +27387,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>265.13</v>
+        <v>262.65</v>
       </c>
       <c r="F5" t="n">
-        <v>2859775295488</v>
+        <v>2833025073152</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
       </c>
       <c r="H5" t="n">
-        <v>10.3815</v>
+        <v>10.39346</v>
       </c>
       <c r="I5" t="n">
-        <v>21.329847</v>
+        <v>21.13033</v>
       </c>
       <c r="J5" t="n">
-        <v>25.538698</v>
+        <v>25.270699</v>
       </c>
       <c r="K5" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6867976</v>
+        <v>3.6523116</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0468826613359484</v>
+        <v>0.04732533790215115</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03915626296533777</v>
+        <v>0.0395715210355987</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007253734974725715</v>
+        <v>-0.007388479956222584</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-13 16:09:08</t>
+          <t>2026-08-14 15:45:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -26923,51 +27445,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>305.26</v>
+        <v>305.93</v>
       </c>
       <c r="F6" t="n">
-        <v>4455019315200</v>
+        <v>4464797286400</v>
       </c>
       <c r="G6" t="n">
-        <v>8.74</v>
+        <v>8.73</v>
       </c>
       <c r="H6" t="n">
         <v>9.507709999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>34.926777</v>
+        <v>35.04353</v>
       </c>
       <c r="J6" t="n">
-        <v>32.106575</v>
+        <v>32.17704</v>
       </c>
       <c r="K6" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="L6" t="n">
-        <v>9.543272999999999</v>
+        <v>9.564218500000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02863133066893796</v>
+        <v>0.02853593959402478</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03114626875450436</v>
+        <v>0.03107805707187919</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01526372918555912</v>
+        <v>-0.0158819439199421</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-13 16:09:08</t>
+          <t>2026-08-14 15:45:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -26981,51 +27503,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>225.3</v>
+        <v>225.16</v>
       </c>
       <c r="F7" t="n">
-        <v>5456991354880</v>
+        <v>5453600260096</v>
       </c>
       <c r="G7" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="H7" t="n">
         <v>12.81649</v>
       </c>
       <c r="I7" t="n">
-        <v>34.555214</v>
+        <v>34.480858</v>
       </c>
       <c r="J7" t="n">
-        <v>17.578917</v>
+        <v>17.567993</v>
       </c>
       <c r="K7" t="n">
         <v>0.6</v>
       </c>
       <c r="L7" t="n">
-        <v>21.527357</v>
+        <v>21.513979</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02893919218819352</v>
+        <v>0.02900159886303073</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05688632933865957</v>
+        <v>0.05692170012435602</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01047633139859609</v>
+        <v>0.009961699132534731</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-13 16:09:08</t>
+          <t>2026-08-14 15:45:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -27039,10 +27561,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>483.01</v>
+        <v>514.39</v>
       </c>
       <c r="F8" t="n">
-        <v>788501757952</v>
+        <v>839728824320</v>
       </c>
       <c r="G8" t="n">
         <v>3.91</v>
@@ -27051,39 +27573,39 @@
         <v>15.45987</v>
       </c>
       <c r="I8" t="n">
-        <v>123.53197</v>
+        <v>131.55754</v>
       </c>
       <c r="J8" t="n">
-        <v>31.242825</v>
+        <v>33.272594</v>
       </c>
       <c r="K8" t="n">
         <v>1.01</v>
       </c>
       <c r="L8" t="n">
-        <v>19.08974</v>
+        <v>20.329954</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008095070495434878</v>
+        <v>0.007601236415948989</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03200734974431171</v>
+        <v>0.03005476389509905</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01440264819575177</v>
+        <v>-0.01690523709672223</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-13 16:09:08</t>
+          <t>2026-08-14 15:45:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -27097,51 +27619,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>417.82</v>
+        <v>392.99</v>
       </c>
       <c r="F9" t="n">
-        <v>1987812261888</v>
+        <v>1869681393664</v>
       </c>
       <c r="G9" t="n">
-        <v>5.99</v>
+        <v>6.02</v>
       </c>
       <c r="H9" t="n">
         <v>19.53066</v>
       </c>
       <c r="I9" t="n">
-        <v>69.75292</v>
+        <v>65.28073000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>21.39303</v>
+        <v>20.121695</v>
       </c>
       <c r="K9" t="n">
         <v>0.47</v>
       </c>
       <c r="L9" t="n">
-        <v>26.34085</v>
+        <v>24.775478</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01433631707433823</v>
+        <v>0.01531845594035471</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04674419606529127</v>
+        <v>0.04969760044784854</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0003341981252277942</v>
+        <v>0.002737599456027258</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-13 16:09:08</t>
+          <t>2026-08-14 15:45:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -27155,10 +27677,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>78.23999999999999</v>
+        <v>78.16</v>
       </c>
       <c r="F10" t="n">
-        <v>325786632192</v>
+        <v>325453545472</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -27167,28 +27689,28 @@
         <v>3.81668</v>
       </c>
       <c r="I10" t="n">
-        <v>24.603773</v>
+        <v>24.578617</v>
       </c>
       <c r="J10" t="n">
-        <v>20.49949</v>
+        <v>20.478533</v>
       </c>
       <c r="K10" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="L10" t="n">
-        <v>6.735197</v>
+        <v>6.7283106</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04064417177914111</v>
+        <v>0.04068577277379734</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0487816973415133</v>
+        <v>0.04883162743091096</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04640999794006348</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002371699401449816</v>
+        <v>0.001871626439089669</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P460"/>
+  <dimension ref="A1:P469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26619,13 +26619,13 @@
         <v>9.564218500000001</v>
       </c>
       <c r="M452" t="n">
-        <v>0.02853593959402478</v>
+        <v>0.0285359395940247</v>
       </c>
       <c r="N452" t="n">
-        <v>0.03107805707187919</v>
+        <v>0.0310780570718791</v>
       </c>
       <c r="O452" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P452" t="n">
         <v>-0.0158819439199421</v>
@@ -26677,16 +26677,16 @@
         <v>20.329954</v>
       </c>
       <c r="M453" t="n">
-        <v>0.007601236415948989</v>
+        <v>0.0076012364159489</v>
       </c>
       <c r="N453" t="n">
-        <v>0.03005476389509905</v>
+        <v>0.030054763895099</v>
       </c>
       <c r="O453" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P453" t="n">
-        <v>-0.01690523709672223</v>
+        <v>-0.0169052370967222</v>
       </c>
     </row>
     <row r="454">
@@ -26735,16 +26735,16 @@
         <v>3.6523116</v>
       </c>
       <c r="M454" t="n">
-        <v>0.04732533790215115</v>
+        <v>0.0473253379021511</v>
       </c>
       <c r="N454" t="n">
         <v>0.0395715210355987</v>
       </c>
       <c r="O454" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P454" t="n">
-        <v>-0.007388479956222584</v>
+        <v>-0.0073884799562225</v>
       </c>
     </row>
     <row r="455">
@@ -26793,16 +26793,16 @@
         <v>24.775478</v>
       </c>
       <c r="M455" t="n">
-        <v>0.01531845594035471</v>
+        <v>0.0153184559403547</v>
       </c>
       <c r="N455" t="n">
-        <v>0.04969760044784854</v>
+        <v>0.0496976004478485</v>
       </c>
       <c r="O455" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P455" t="n">
-        <v>0.002737599456027258</v>
+        <v>0.0027375994560272</v>
       </c>
     </row>
     <row r="456">
@@ -26851,16 +26851,16 @@
         <v>9.423171999999999</v>
       </c>
       <c r="M456" t="n">
-        <v>0.05795540548407754</v>
+        <v>0.0579554054840775</v>
       </c>
       <c r="N456" t="n">
-        <v>0.04292423007510043</v>
+        <v>0.0429242300751004</v>
       </c>
       <c r="O456" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P456" t="n">
-        <v>-0.00403577091672086</v>
+        <v>-0.0040357709167208</v>
       </c>
     </row>
     <row r="457">
@@ -26909,16 +26909,16 @@
         <v>6.583423</v>
       </c>
       <c r="M457" t="n">
-        <v>0.04499449012460795</v>
+        <v>0.0449944901246079</v>
       </c>
       <c r="N457" t="n">
-        <v>0.05914215478511486</v>
+        <v>0.0591421547851148</v>
       </c>
       <c r="O457" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P457" t="n">
-        <v>0.01218215379329357</v>
+        <v>0.0121821537932935</v>
       </c>
     </row>
     <row r="458">
@@ -26967,16 +26967,16 @@
         <v>11.085542</v>
       </c>
       <c r="M458" t="n">
-        <v>0.03621316108195398</v>
+        <v>0.0362131610819539</v>
       </c>
       <c r="N458" t="n">
-        <v>0.04758433589018975</v>
+        <v>0.0475843358901897</v>
       </c>
       <c r="O458" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P458" t="n">
-        <v>0.0006243348983684602</v>
+        <v>0.0006243348983684</v>
       </c>
     </row>
     <row r="459">
@@ -27025,16 +27025,16 @@
         <v>6.7283106</v>
       </c>
       <c r="M459" t="n">
-        <v>0.04068577277379734</v>
+        <v>0.0406857727737973</v>
       </c>
       <c r="N459" t="n">
-        <v>0.04883162743091096</v>
+        <v>0.0488316274309109</v>
       </c>
       <c r="O459" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P459" t="n">
-        <v>0.001871626439089669</v>
+        <v>0.0018716264390896</v>
       </c>
     </row>
     <row r="460">
@@ -27083,16 +27083,538 @@
         <v>21.513979</v>
       </c>
       <c r="M460" t="n">
-        <v>0.02900159886303073</v>
+        <v>0.0290015988630307</v>
       </c>
       <c r="N460" t="n">
-        <v>0.05692170012435602</v>
+        <v>0.056921700124356</v>
       </c>
       <c r="O460" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P460" t="n">
-        <v>0.009961699132534731</v>
+        <v>0.009961699132534699</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>2026-08-17 15:46:11</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>305.59</v>
+      </c>
+      <c r="F461" t="n">
+        <v>4459835424768</v>
+      </c>
+      <c r="G461" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H461" t="n">
+        <v>9.507709999999999</v>
+      </c>
+      <c r="I461" t="n">
+        <v>35.044724</v>
+      </c>
+      <c r="J461" t="n">
+        <v>32.14128</v>
+      </c>
+      <c r="K461" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="L461" t="n">
+        <v>9.55359</v>
+      </c>
+      <c r="M461" t="n">
+        <v>0.02853496514938316</v>
+      </c>
+      <c r="N461" t="n">
+        <v>0.03111263457573873</v>
+      </c>
+      <c r="O461" t="n">
+        <v>0.04723999977111817</v>
+      </c>
+      <c r="P461" t="n">
+        <v>-0.01612736519537943</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>2026-08-17 15:46:11</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>506</v>
+      </c>
+      <c r="F462" t="n">
+        <v>826032324608</v>
+      </c>
+      <c r="G462" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H462" t="n">
+        <v>15.45987</v>
+      </c>
+      <c r="I462" t="n">
+        <v>129.41176</v>
+      </c>
+      <c r="J462" t="n">
+        <v>32.7299</v>
+      </c>
+      <c r="K462" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L462" t="n">
+        <v>19.99836</v>
+      </c>
+      <c r="M462" t="n">
+        <v>0.007727272727272728</v>
+      </c>
+      <c r="N462" t="n">
+        <v>0.03055310276679842</v>
+      </c>
+      <c r="O462" t="n">
+        <v>0.04723999977111817</v>
+      </c>
+      <c r="P462" t="n">
+        <v>-0.01668689700431975</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>2026-08-17 15:46:11</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>261.31</v>
+      </c>
+      <c r="F463" t="n">
+        <v>2818571501568</v>
+      </c>
+      <c r="G463" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="H463" t="n">
+        <v>10.40326</v>
+      </c>
+      <c r="I463" t="n">
+        <v>21.039452</v>
+      </c>
+      <c r="J463" t="n">
+        <v>25.118088</v>
+      </c>
+      <c r="K463" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L463" t="n">
+        <v>3.633678</v>
+      </c>
+      <c r="M463" t="n">
+        <v>0.04752975393211128</v>
+      </c>
+      <c r="N463" t="n">
+        <v>0.03981194749531208</v>
+      </c>
+      <c r="O463" t="n">
+        <v>0.04723999977111817</v>
+      </c>
+      <c r="P463" t="n">
+        <v>-0.007428052275806091</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>2026-08-17 15:46:11</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>392.43</v>
+      </c>
+      <c r="F464" t="n">
+        <v>1867017224192</v>
+      </c>
+      <c r="G464" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H464" t="n">
+        <v>19.53066</v>
+      </c>
+      <c r="I464" t="n">
+        <v>65.29617</v>
+      </c>
+      <c r="J464" t="n">
+        <v>20.093021</v>
+      </c>
+      <c r="K464" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L464" t="n">
+        <v>24.740173</v>
+      </c>
+      <c r="M464" t="n">
+        <v>0.0153148332186632</v>
+      </c>
+      <c r="N464" t="n">
+        <v>0.04976851922635885</v>
+      </c>
+      <c r="O464" t="n">
+        <v>0.04723999977111817</v>
+      </c>
+      <c r="P464" t="n">
+        <v>0.002528519455240678</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>2026-08-17 15:46:11</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>341.45</v>
+      </c>
+      <c r="F465" t="n">
+        <v>4175911452672</v>
+      </c>
+      <c r="G465" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H465" t="n">
+        <v>14.74619</v>
+      </c>
+      <c r="I465" t="n">
+        <v>17.132463</v>
+      </c>
+      <c r="J465" t="n">
+        <v>23.155134</v>
+      </c>
+      <c r="K465" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L465" t="n">
+        <v>9.365845</v>
+      </c>
+      <c r="M465" t="n">
+        <v>0.05836872162834968</v>
+      </c>
+      <c r="N465" t="n">
+        <v>0.0431869673451457</v>
+      </c>
+      <c r="O465" t="n">
+        <v>0.04723999977111817</v>
+      </c>
+      <c r="P465" t="n">
+        <v>-0.004053032425972464</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>2026-08-17 15:46:11</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>568.97</v>
+      </c>
+      <c r="F466" t="n">
+        <v>1449454469120</v>
+      </c>
+      <c r="G466" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H466" t="n">
+        <v>34.885</v>
+      </c>
+      <c r="I466" t="n">
+        <v>21.438204</v>
+      </c>
+      <c r="J466" t="n">
+        <v>16.309875</v>
+      </c>
+      <c r="K466" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L466" t="n">
+        <v>6.350377</v>
+      </c>
+      <c r="M466" t="n">
+        <v>0.04664569309453925</v>
+      </c>
+      <c r="N466" t="n">
+        <v>0.06131254723447633</v>
+      </c>
+      <c r="O466" t="n">
+        <v>0.04723999977111817</v>
+      </c>
+      <c r="P466" t="n">
+        <v>0.01407254746335816</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>2026-08-17 15:46:11</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>480.35</v>
+      </c>
+      <c r="F467" t="n">
+        <v>3566861025280</v>
+      </c>
+      <c r="G467" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="H467" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I467" t="n">
+        <v>26.790295</v>
+      </c>
+      <c r="J467" t="n">
+        <v>20.376884</v>
+      </c>
+      <c r="K467" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L467" t="n">
+        <v>10.74877</v>
+      </c>
+      <c r="M467" t="n">
+        <v>0.03732694909961486</v>
+      </c>
+      <c r="N467" t="n">
+        <v>0.04907521598834183</v>
+      </c>
+      <c r="O467" t="n">
+        <v>0.04723999977111817</v>
+      </c>
+      <c r="P467" t="n">
+        <v>0.001835216217223663</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>2026-08-17 15:46:11</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>76.02</v>
+      </c>
+      <c r="F468" t="n">
+        <v>316542681088</v>
+      </c>
+      <c r="G468" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H468" t="n">
+        <v>3.81668</v>
+      </c>
+      <c r="I468" t="n">
+        <v>23.905659</v>
+      </c>
+      <c r="J468" t="n">
+        <v>19.917833</v>
+      </c>
+      <c r="K468" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L468" t="n">
+        <v>6.5440907</v>
+      </c>
+      <c r="M468" t="n">
+        <v>0.04183109707971587</v>
+      </c>
+      <c r="N468" t="n">
+        <v>0.05020626151012891</v>
+      </c>
+      <c r="O468" t="n">
+        <v>0.04723999977111817</v>
+      </c>
+      <c r="P468" t="n">
+        <v>0.002966261739010746</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>2026-08-17 15:46:11</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>225.01</v>
+      </c>
+      <c r="F469" t="n">
+        <v>5449966944256</v>
+      </c>
+      <c r="G469" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H469" t="n">
+        <v>12.79836</v>
+      </c>
+      <c r="I469" t="n">
+        <v>34.457886</v>
+      </c>
+      <c r="J469" t="n">
+        <v>17.581158</v>
+      </c>
+      <c r="K469" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L469" t="n">
+        <v>21.499647</v>
+      </c>
+      <c r="M469" t="n">
+        <v>0.02902093240300431</v>
+      </c>
+      <c r="N469" t="n">
+        <v>0.05687907204124262</v>
+      </c>
+      <c r="O469" t="n">
+        <v>0.04723999977111817</v>
+      </c>
+      <c r="P469" t="n">
+        <v>0.009639072270124449</v>
       </c>
     </row>
   </sheetData>
@@ -27194,12 +27716,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-14 15:45:34</t>
+          <t>2026-08-17 15:46:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -27213,51 +27735,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>343.54</v>
+        <v>341.45</v>
       </c>
       <c r="F2" t="n">
-        <v>4201472065536</v>
+        <v>4175911452672</v>
       </c>
       <c r="G2" t="n">
-        <v>19.91</v>
+        <v>19.93</v>
       </c>
       <c r="H2" t="n">
         <v>14.74619</v>
       </c>
       <c r="I2" t="n">
-        <v>17.254646</v>
+        <v>17.132463</v>
       </c>
       <c r="J2" t="n">
-        <v>23.296865</v>
+        <v>23.155134</v>
       </c>
       <c r="K2" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="L2" t="n">
-        <v>9.423171999999999</v>
+        <v>9.365845</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05795540548407754</v>
+        <v>0.05836872162834968</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04292423007510043</v>
+        <v>0.0431869673451457</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.04723999977111817</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.00403577091672086</v>
+        <v>-0.004053032425972464</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-14 15:45:34</t>
+          <t>2026-08-17 15:46:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -27271,51 +27793,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>495.4</v>
+        <v>480.35</v>
       </c>
       <c r="F3" t="n">
-        <v>3678615371776</v>
+        <v>3566861025280</v>
       </c>
       <c r="G3" t="n">
-        <v>17.94</v>
+        <v>17.93</v>
       </c>
       <c r="H3" t="n">
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>27.61427</v>
+        <v>26.790295</v>
       </c>
       <c r="J3" t="n">
-        <v>21.015318</v>
+        <v>20.376884</v>
       </c>
       <c r="K3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="L3" t="n">
-        <v>11.085542</v>
+        <v>10.74877</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03621316108195398</v>
+        <v>0.03732694909961486</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04758433589018975</v>
+        <v>0.04907521598834183</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.04723999977111817</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0006243348983684602</v>
+        <v>0.001835216217223663</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-14 15:45:34</t>
+          <t>2026-08-17 15:46:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -27329,10 +27851,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>589.85</v>
+        <v>568.97</v>
       </c>
       <c r="F4" t="n">
-        <v>1502646501376</v>
+        <v>1449454469120</v>
       </c>
       <c r="G4" t="n">
         <v>26.54</v>
@@ -27341,39 +27863,39 @@
         <v>34.885</v>
       </c>
       <c r="I4" t="n">
-        <v>22.224941</v>
+        <v>21.438204</v>
       </c>
       <c r="J4" t="n">
-        <v>16.908413</v>
+        <v>16.309875</v>
       </c>
       <c r="K4" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="L4" t="n">
-        <v>6.583423</v>
+        <v>6.350377</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04499449012460795</v>
+        <v>0.04664569309453925</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05914215478511486</v>
+        <v>0.06131254723447633</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.04723999977111817</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01218215379329357</v>
+        <v>0.01407254746335816</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-14 15:45:34</t>
+          <t>2026-08-17 15:46:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -27387,51 +27909,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>262.65</v>
+        <v>261.31</v>
       </c>
       <c r="F5" t="n">
-        <v>2833025073152</v>
+        <v>2818571501568</v>
       </c>
       <c r="G5" t="n">
-        <v>12.43</v>
+        <v>12.42</v>
       </c>
       <c r="H5" t="n">
-        <v>10.39346</v>
+        <v>10.40326</v>
       </c>
       <c r="I5" t="n">
-        <v>21.13033</v>
+        <v>21.039452</v>
       </c>
       <c r="J5" t="n">
-        <v>25.270699</v>
+        <v>25.118088</v>
       </c>
       <c r="K5" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6523116</v>
+        <v>3.633678</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04732533790215115</v>
+        <v>0.04752975393211128</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0395715210355987</v>
+        <v>0.03981194749531208</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.04723999977111817</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007388479956222584</v>
+        <v>-0.007428052275806091</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-14 15:45:34</t>
+          <t>2026-08-17 15:46:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -27445,51 +27967,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>305.93</v>
+        <v>305.59</v>
       </c>
       <c r="F6" t="n">
-        <v>4464797286400</v>
+        <v>4459835424768</v>
       </c>
       <c r="G6" t="n">
-        <v>8.73</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>9.507709999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>35.04353</v>
+        <v>35.044724</v>
       </c>
       <c r="J6" t="n">
-        <v>32.17704</v>
+        <v>32.14128</v>
       </c>
       <c r="K6" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="L6" t="n">
-        <v>9.564218500000001</v>
+        <v>9.55359</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02853593959402478</v>
+        <v>0.02853496514938316</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03107805707187919</v>
+        <v>0.03111263457573873</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.04723999977111817</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0158819439199421</v>
+        <v>-0.01612736519537943</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-14 15:45:34</t>
+          <t>2026-08-17 15:46:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -27503,51 +28025,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>225.16</v>
+        <v>225.01</v>
       </c>
       <c r="F7" t="n">
-        <v>5453600260096</v>
+        <v>5449966944256</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
       </c>
       <c r="H7" t="n">
-        <v>12.81649</v>
+        <v>12.79836</v>
       </c>
       <c r="I7" t="n">
-        <v>34.480858</v>
+        <v>34.457886</v>
       </c>
       <c r="J7" t="n">
-        <v>17.567993</v>
+        <v>17.581158</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="L7" t="n">
-        <v>21.513979</v>
+        <v>21.499647</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02900159886303073</v>
+        <v>0.02902093240300431</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05692170012435602</v>
+        <v>0.05687907204124262</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.04723999977111817</v>
       </c>
       <c r="P7" t="n">
-        <v>0.009961699132534731</v>
+        <v>0.009639072270124449</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-14 15:45:34</t>
+          <t>2026-08-17 15:46:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -27561,10 +28083,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>514.39</v>
+        <v>506</v>
       </c>
       <c r="F8" t="n">
-        <v>839728824320</v>
+        <v>826032324608</v>
       </c>
       <c r="G8" t="n">
         <v>3.91</v>
@@ -27573,39 +28095,39 @@
         <v>15.45987</v>
       </c>
       <c r="I8" t="n">
-        <v>131.55754</v>
+        <v>129.41176</v>
       </c>
       <c r="J8" t="n">
-        <v>33.272594</v>
+        <v>32.7299</v>
       </c>
       <c r="K8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="L8" t="n">
-        <v>20.329954</v>
+        <v>19.99836</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007601236415948989</v>
+        <v>0.007727272727272728</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03005476389509905</v>
+        <v>0.03055310276679842</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.04723999977111817</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01690523709672223</v>
+        <v>-0.01668689700431975</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-14 15:45:34</t>
+          <t>2026-08-17 15:46:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -27619,51 +28141,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392.99</v>
+        <v>392.43</v>
       </c>
       <c r="F9" t="n">
-        <v>1869681393664</v>
+        <v>1867017224192</v>
       </c>
       <c r="G9" t="n">
-        <v>6.02</v>
+        <v>6.01</v>
       </c>
       <c r="H9" t="n">
         <v>19.53066</v>
       </c>
       <c r="I9" t="n">
-        <v>65.28073000000001</v>
+        <v>65.29617</v>
       </c>
       <c r="J9" t="n">
-        <v>20.121695</v>
+        <v>20.093021</v>
       </c>
       <c r="K9" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="L9" t="n">
-        <v>24.775478</v>
+        <v>24.740173</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01531845594035471</v>
+        <v>0.0153148332186632</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04969760044784854</v>
+        <v>0.04976851922635885</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.04723999977111817</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002737599456027258</v>
+        <v>0.002528519455240678</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-14 15:45:34</t>
+          <t>2026-08-17 15:46:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -27677,10 +28199,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>78.16</v>
+        <v>76.02</v>
       </c>
       <c r="F10" t="n">
-        <v>325453545472</v>
+        <v>316542681088</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -27689,28 +28211,28 @@
         <v>3.81668</v>
       </c>
       <c r="I10" t="n">
-        <v>24.578617</v>
+        <v>23.905659</v>
       </c>
       <c r="J10" t="n">
-        <v>20.478533</v>
+        <v>19.917833</v>
       </c>
       <c r="K10" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="L10" t="n">
-        <v>6.7283106</v>
+        <v>6.5440907</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04068577277379734</v>
+        <v>0.04183109707971587</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04883162743091096</v>
+        <v>0.05020626151012891</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.04723999977111817</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001871626439089669</v>
+        <v>0.002966261739010746</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P469"/>
+  <dimension ref="A1:P478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27141,16 +27141,16 @@
         <v>9.55359</v>
       </c>
       <c r="M461" t="n">
-        <v>0.02853496514938316</v>
+        <v>0.0285349651493831</v>
       </c>
       <c r="N461" t="n">
-        <v>0.03111263457573873</v>
+        <v>0.0311126345757387</v>
       </c>
       <c r="O461" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.0472399997711181</v>
       </c>
       <c r="P461" t="n">
-        <v>-0.01612736519537943</v>
+        <v>-0.0161273651953794</v>
       </c>
     </row>
     <row r="462">
@@ -27199,16 +27199,16 @@
         <v>19.99836</v>
       </c>
       <c r="M462" t="n">
-        <v>0.007727272727272728</v>
+        <v>0.0077272727272727</v>
       </c>
       <c r="N462" t="n">
-        <v>0.03055310276679842</v>
+        <v>0.0305531027667984</v>
       </c>
       <c r="O462" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.0472399997711181</v>
       </c>
       <c r="P462" t="n">
-        <v>-0.01668689700431975</v>
+        <v>-0.0166868970043197</v>
       </c>
     </row>
     <row r="463">
@@ -27257,16 +27257,16 @@
         <v>3.633678</v>
       </c>
       <c r="M463" t="n">
-        <v>0.04752975393211128</v>
+        <v>0.0475297539321112</v>
       </c>
       <c r="N463" t="n">
-        <v>0.03981194749531208</v>
+        <v>0.039811947495312</v>
       </c>
       <c r="O463" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.0472399997711181</v>
       </c>
       <c r="P463" t="n">
-        <v>-0.007428052275806091</v>
+        <v>-0.007428052275806</v>
       </c>
     </row>
     <row r="464">
@@ -27318,13 +27318,13 @@
         <v>0.0153148332186632</v>
       </c>
       <c r="N464" t="n">
-        <v>0.04976851922635885</v>
+        <v>0.0497685192263588</v>
       </c>
       <c r="O464" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.0472399997711181</v>
       </c>
       <c r="P464" t="n">
-        <v>0.002528519455240678</v>
+        <v>0.0025285194552406</v>
       </c>
     </row>
     <row r="465">
@@ -27373,16 +27373,16 @@
         <v>9.365845</v>
       </c>
       <c r="M465" t="n">
-        <v>0.05836872162834968</v>
+        <v>0.0583687216283496</v>
       </c>
       <c r="N465" t="n">
         <v>0.0431869673451457</v>
       </c>
       <c r="O465" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.0472399997711181</v>
       </c>
       <c r="P465" t="n">
-        <v>-0.004053032425972464</v>
+        <v>-0.0040530324259724</v>
       </c>
     </row>
     <row r="466">
@@ -27431,16 +27431,16 @@
         <v>6.350377</v>
       </c>
       <c r="M466" t="n">
-        <v>0.04664569309453925</v>
+        <v>0.0466456930945392</v>
       </c>
       <c r="N466" t="n">
-        <v>0.06131254723447633</v>
+        <v>0.0613125472344763</v>
       </c>
       <c r="O466" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.0472399997711181</v>
       </c>
       <c r="P466" t="n">
-        <v>0.01407254746335816</v>
+        <v>0.0140725474633581</v>
       </c>
     </row>
     <row r="467">
@@ -27489,16 +27489,16 @@
         <v>10.74877</v>
       </c>
       <c r="M467" t="n">
-        <v>0.03732694909961486</v>
+        <v>0.0373269490996148</v>
       </c>
       <c r="N467" t="n">
-        <v>0.04907521598834183</v>
+        <v>0.0490752159883418</v>
       </c>
       <c r="O467" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.0472399997711181</v>
       </c>
       <c r="P467" t="n">
-        <v>0.001835216217223663</v>
+        <v>0.0018352162172236</v>
       </c>
     </row>
     <row r="468">
@@ -27547,16 +27547,16 @@
         <v>6.5440907</v>
       </c>
       <c r="M468" t="n">
-        <v>0.04183109707971587</v>
+        <v>0.0418310970797158</v>
       </c>
       <c r="N468" t="n">
-        <v>0.05020626151012891</v>
+        <v>0.0502062615101289</v>
       </c>
       <c r="O468" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.0472399997711181</v>
       </c>
       <c r="P468" t="n">
-        <v>0.002966261739010746</v>
+        <v>0.0029662617390107</v>
       </c>
     </row>
     <row r="469">
@@ -27605,16 +27605,538 @@
         <v>21.499647</v>
       </c>
       <c r="M469" t="n">
-        <v>0.02902093240300431</v>
+        <v>0.0290209324030043</v>
       </c>
       <c r="N469" t="n">
-        <v>0.05687907204124262</v>
+        <v>0.0568790720412426</v>
       </c>
       <c r="O469" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.0472399997711181</v>
       </c>
       <c r="P469" t="n">
-        <v>0.009639072270124449</v>
+        <v>0.009639072270124401</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:10</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>310.03</v>
+      </c>
+      <c r="F470" t="n">
+        <v>4524633751552</v>
+      </c>
+      <c r="G470" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H470" t="n">
+        <v>9.507709999999999</v>
+      </c>
+      <c r="I470" t="n">
+        <v>35.59472</v>
+      </c>
+      <c r="J470" t="n">
+        <v>32.608273</v>
+      </c>
+      <c r="K470" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="L470" t="n">
+        <v>9.692397</v>
+      </c>
+      <c r="M470" t="n">
+        <v>0.0280940554139922</v>
+      </c>
+      <c r="N470" t="n">
+        <v>0.0306670644776312</v>
+      </c>
+      <c r="O470" t="n">
+        <v>0.04706000328063965</v>
+      </c>
+      <c r="P470" t="n">
+        <v>-0.01639293880300845</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:10</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>484.39</v>
+      </c>
+      <c r="F471" t="n">
+        <v>790754623488</v>
+      </c>
+      <c r="G471" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H471" t="n">
+        <v>15.46743</v>
+      </c>
+      <c r="I471" t="n">
+        <v>124.20257</v>
+      </c>
+      <c r="J471" t="n">
+        <v>31.316774</v>
+      </c>
+      <c r="K471" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L471" t="n">
+        <v>19.144283</v>
+      </c>
+      <c r="M471" t="n">
+        <v>0.008051363570676521</v>
+      </c>
+      <c r="N471" t="n">
+        <v>0.03193176985486901</v>
+      </c>
+      <c r="O471" t="n">
+        <v>0.04706000328063965</v>
+      </c>
+      <c r="P471" t="n">
+        <v>-0.01512823342577063</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:10</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>259.45</v>
+      </c>
+      <c r="F472" t="n">
+        <v>2798509096960</v>
+      </c>
+      <c r="G472" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="H472" t="n">
+        <v>10.40326</v>
+      </c>
+      <c r="I472" t="n">
+        <v>20.856112</v>
+      </c>
+      <c r="J472" t="n">
+        <v>24.939299</v>
+      </c>
+      <c r="K472" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L472" t="n">
+        <v>3.6078138</v>
+      </c>
+      <c r="M472" t="n">
+        <v>0.04794758142223935</v>
+      </c>
+      <c r="N472" t="n">
+        <v>0.04009735979957603</v>
+      </c>
+      <c r="O472" t="n">
+        <v>0.04706000328063965</v>
+      </c>
+      <c r="P472" t="n">
+        <v>-0.006962643481063617</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:10</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>380</v>
+      </c>
+      <c r="F473" t="n">
+        <v>1807880552448</v>
+      </c>
+      <c r="G473" t="n">
+        <v>6</v>
+      </c>
+      <c r="H473" t="n">
+        <v>19.53066</v>
+      </c>
+      <c r="I473" t="n">
+        <v>63.333332</v>
+      </c>
+      <c r="J473" t="n">
+        <v>19.456587</v>
+      </c>
+      <c r="K473" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L473" t="n">
+        <v>23.956543</v>
+      </c>
+      <c r="M473" t="n">
+        <v>0.01578947368421053</v>
+      </c>
+      <c r="N473" t="n">
+        <v>0.05139647368421053</v>
+      </c>
+      <c r="O473" t="n">
+        <v>0.04706000328063965</v>
+      </c>
+      <c r="P473" t="n">
+        <v>0.00433647040357088</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:10</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>341.28</v>
+      </c>
+      <c r="F474" t="n">
+        <v>4173832126464</v>
+      </c>
+      <c r="G474" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="H474" t="n">
+        <v>14.74619</v>
+      </c>
+      <c r="I474" t="n">
+        <v>17.115345</v>
+      </c>
+      <c r="J474" t="n">
+        <v>23.143604</v>
+      </c>
+      <c r="K474" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L474" t="n">
+        <v>9.361181</v>
+      </c>
+      <c r="M474" t="n">
+        <v>0.05842709798406002</v>
+      </c>
+      <c r="N474" t="n">
+        <v>0.0432084798406001</v>
+      </c>
+      <c r="O474" t="n">
+        <v>0.04706000328063965</v>
+      </c>
+      <c r="P474" t="n">
+        <v>-0.003851523440039549</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:10</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>543.67</v>
+      </c>
+      <c r="F475" t="n">
+        <v>1385002696704</v>
+      </c>
+      <c r="G475" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="H475" t="n">
+        <v>34.885</v>
+      </c>
+      <c r="I475" t="n">
+        <v>20.461798</v>
+      </c>
+      <c r="J475" t="n">
+        <v>15.584636</v>
+      </c>
+      <c r="K475" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L475" t="n">
+        <v>6.068</v>
+      </c>
+      <c r="M475" t="n">
+        <v>0.04887155811429728</v>
+      </c>
+      <c r="N475" t="n">
+        <v>0.06416576231905384</v>
+      </c>
+      <c r="O475" t="n">
+        <v>0.04706000328063965</v>
+      </c>
+      <c r="P475" t="n">
+        <v>0.01710575903841419</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:10</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>481.63</v>
+      </c>
+      <c r="F476" t="n">
+        <v>3576365580288</v>
+      </c>
+      <c r="G476" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="H476" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I476" t="n">
+        <v>26.801893</v>
+      </c>
+      <c r="J476" t="n">
+        <v>20.431183</v>
+      </c>
+      <c r="K476" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L476" t="n">
+        <v>10.777411</v>
+      </c>
+      <c r="M476" t="n">
+        <v>0.03731079874592529</v>
+      </c>
+      <c r="N476" t="n">
+        <v>0.04894479164503873</v>
+      </c>
+      <c r="O476" t="n">
+        <v>0.04706000328063965</v>
+      </c>
+      <c r="P476" t="n">
+        <v>0.001884788364399079</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:10</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>77.77</v>
+      </c>
+      <c r="F477" t="n">
+        <v>323829563392</v>
+      </c>
+      <c r="G477" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H477" t="n">
+        <v>3.82319</v>
+      </c>
+      <c r="I477" t="n">
+        <v>24.455973</v>
+      </c>
+      <c r="J477" t="n">
+        <v>20.341652</v>
+      </c>
+      <c r="K477" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L477" t="n">
+        <v>6.694737</v>
+      </c>
+      <c r="M477" t="n">
+        <v>0.04088980326604089</v>
+      </c>
+      <c r="N477" t="n">
+        <v>0.04916021602160216</v>
+      </c>
+      <c r="O477" t="n">
+        <v>0.04706000328063965</v>
+      </c>
+      <c r="P477" t="n">
+        <v>0.002100212740962518</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:46:10</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>219.74</v>
+      </c>
+      <c r="F478" t="n">
+        <v>5322322739200</v>
+      </c>
+      <c r="G478" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H478" t="n">
+        <v>12.83399</v>
+      </c>
+      <c r="I478" t="n">
+        <v>33.65084</v>
+      </c>
+      <c r="J478" t="n">
+        <v>17.121721</v>
+      </c>
+      <c r="K478" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L478" t="n">
+        <v>20.996101</v>
+      </c>
+      <c r="M478" t="n">
+        <v>0.02971693819969054</v>
+      </c>
+      <c r="N478" t="n">
+        <v>0.05840534267771002</v>
+      </c>
+      <c r="O478" t="n">
+        <v>0.04706000328063965</v>
+      </c>
+      <c r="P478" t="n">
+        <v>0.01134533939707037</v>
       </c>
     </row>
   </sheetData>
@@ -27716,12 +28238,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-17 15:46:11</t>
+          <t>2026-08-18 15:46:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -27735,51 +28257,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>341.45</v>
+        <v>341.28</v>
       </c>
       <c r="F2" t="n">
-        <v>4175911452672</v>
+        <v>4173832126464</v>
       </c>
       <c r="G2" t="n">
-        <v>19.93</v>
+        <v>19.94</v>
       </c>
       <c r="H2" t="n">
         <v>14.74619</v>
       </c>
       <c r="I2" t="n">
-        <v>17.132463</v>
+        <v>17.115345</v>
       </c>
       <c r="J2" t="n">
-        <v>23.155134</v>
+        <v>23.143604</v>
       </c>
       <c r="K2" t="n">
         <v>0.93</v>
       </c>
       <c r="L2" t="n">
-        <v>9.365845</v>
+        <v>9.361181</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05836872162834968</v>
+        <v>0.05842709798406002</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0431869673451457</v>
+        <v>0.0432084798406001</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.04706000328063965</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.004053032425972464</v>
+        <v>-0.003851523440039549</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-17 15:46:11</t>
+          <t>2026-08-18 15:46:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -27793,51 +28315,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>480.35</v>
+        <v>481.63</v>
       </c>
       <c r="F3" t="n">
-        <v>3566861025280</v>
+        <v>3576365580288</v>
       </c>
       <c r="G3" t="n">
-        <v>17.93</v>
+        <v>17.97</v>
       </c>
       <c r="H3" t="n">
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>26.790295</v>
+        <v>26.801893</v>
       </c>
       <c r="J3" t="n">
-        <v>20.376884</v>
+        <v>20.431183</v>
       </c>
       <c r="K3" t="n">
         <v>1.61</v>
       </c>
       <c r="L3" t="n">
-        <v>10.74877</v>
+        <v>10.777411</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03732694909961486</v>
+        <v>0.03731079874592529</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04907521598834183</v>
+        <v>0.04894479164503873</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.04706000328063965</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001835216217223663</v>
+        <v>0.001884788364399079</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17 15:46:11</t>
+          <t>2026-08-18 15:46:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -27851,51 +28373,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>568.97</v>
+        <v>543.67</v>
       </c>
       <c r="F4" t="n">
-        <v>1449454469120</v>
+        <v>1385002696704</v>
       </c>
       <c r="G4" t="n">
-        <v>26.54</v>
+        <v>26.57</v>
       </c>
       <c r="H4" t="n">
         <v>34.885</v>
       </c>
       <c r="I4" t="n">
-        <v>21.438204</v>
+        <v>20.461798</v>
       </c>
       <c r="J4" t="n">
-        <v>16.309875</v>
+        <v>15.584636</v>
       </c>
       <c r="K4" t="n">
         <v>0.88</v>
       </c>
       <c r="L4" t="n">
-        <v>6.350377</v>
+        <v>6.068</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04664569309453925</v>
+        <v>0.04887155811429728</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06131254723447633</v>
+        <v>0.06416576231905384</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.04706000328063965</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01407254746335816</v>
+        <v>0.01710575903841419</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-17 15:46:11</t>
+          <t>2026-08-18 15:46:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -27909,51 +28431,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>261.31</v>
+        <v>259.45</v>
       </c>
       <c r="F5" t="n">
-        <v>2818571501568</v>
+        <v>2798509096960</v>
       </c>
       <c r="G5" t="n">
-        <v>12.42</v>
+        <v>12.44</v>
       </c>
       <c r="H5" t="n">
         <v>10.40326</v>
       </c>
       <c r="I5" t="n">
-        <v>21.039452</v>
+        <v>20.856112</v>
       </c>
       <c r="J5" t="n">
-        <v>25.118088</v>
+        <v>24.939299</v>
       </c>
       <c r="K5" t="n">
         <v>1.4</v>
       </c>
       <c r="L5" t="n">
-        <v>3.633678</v>
+        <v>3.6078138</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04752975393211128</v>
+        <v>0.04794758142223935</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03981194749531208</v>
+        <v>0.04009735979957603</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.04706000328063965</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007428052275806091</v>
+        <v>-0.006962643481063617</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-17 15:46:11</t>
+          <t>2026-08-18 15:46:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -27967,51 +28489,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>305.59</v>
+        <v>310.03</v>
       </c>
       <c r="F6" t="n">
-        <v>4459835424768</v>
+        <v>4524633751552</v>
       </c>
       <c r="G6" t="n">
-        <v>8.720000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>9.507709999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>35.044724</v>
+        <v>35.59472</v>
       </c>
       <c r="J6" t="n">
-        <v>32.14128</v>
+        <v>32.608273</v>
       </c>
       <c r="K6" t="n">
         <v>2.47</v>
       </c>
       <c r="L6" t="n">
-        <v>9.55359</v>
+        <v>9.692397</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02853496514938316</v>
+        <v>0.0280940554139922</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03111263457573873</v>
+        <v>0.0306670644776312</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.04706000328063965</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01612736519537943</v>
+        <v>-0.01639293880300845</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-17 15:46:11</t>
+          <t>2026-08-18 15:46:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -28025,51 +28547,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>225.01</v>
+        <v>219.74</v>
       </c>
       <c r="F7" t="n">
-        <v>5449966944256</v>
+        <v>5322322739200</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
       </c>
       <c r="H7" t="n">
-        <v>12.79836</v>
+        <v>12.83399</v>
       </c>
       <c r="I7" t="n">
-        <v>34.457886</v>
+        <v>33.65084</v>
       </c>
       <c r="J7" t="n">
-        <v>17.581158</v>
+        <v>17.121721</v>
       </c>
       <c r="K7" t="n">
         <v>0.62</v>
       </c>
       <c r="L7" t="n">
-        <v>21.499647</v>
+        <v>20.996101</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02902093240300431</v>
+        <v>0.02971693819969054</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05687907204124262</v>
+        <v>0.05840534267771002</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.04706000328063965</v>
       </c>
       <c r="P7" t="n">
-        <v>0.009639072270124449</v>
+        <v>0.01134533939707037</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:46:11</t>
+          <t>2026-08-18 15:46:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -28083,51 +28605,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>506</v>
+        <v>484.39</v>
       </c>
       <c r="F8" t="n">
-        <v>826032324608</v>
+        <v>790754623488</v>
       </c>
       <c r="G8" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="H8" t="n">
-        <v>15.45987</v>
+        <v>15.46743</v>
       </c>
       <c r="I8" t="n">
-        <v>129.41176</v>
+        <v>124.20257</v>
       </c>
       <c r="J8" t="n">
-        <v>32.7299</v>
+        <v>31.316774</v>
       </c>
       <c r="K8" t="n">
         <v>1.1</v>
       </c>
       <c r="L8" t="n">
-        <v>19.99836</v>
+        <v>19.144283</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007727272727272728</v>
+        <v>0.008051363570676521</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03055310276679842</v>
+        <v>0.03193176985486901</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.04706000328063965</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01668689700431975</v>
+        <v>-0.01512823342577063</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-17 15:46:11</t>
+          <t>2026-08-18 15:46:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -28141,51 +28663,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392.43</v>
+        <v>380</v>
       </c>
       <c r="F9" t="n">
-        <v>1867017224192</v>
+        <v>1807880552448</v>
       </c>
       <c r="G9" t="n">
-        <v>6.01</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>19.53066</v>
       </c>
       <c r="I9" t="n">
-        <v>65.29617</v>
+        <v>63.333332</v>
       </c>
       <c r="J9" t="n">
-        <v>20.093021</v>
+        <v>19.456587</v>
       </c>
       <c r="K9" t="n">
         <v>0.44</v>
       </c>
       <c r="L9" t="n">
-        <v>24.740173</v>
+        <v>23.956543</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0153148332186632</v>
+        <v>0.01578947368421053</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04976851922635885</v>
+        <v>0.05139647368421053</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.04706000328063965</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002528519455240678</v>
+        <v>0.00433647040357088</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-17 15:46:11</t>
+          <t>2026-08-18 15:46:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -28199,40 +28721,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>76.02</v>
+        <v>77.77</v>
       </c>
       <c r="F10" t="n">
-        <v>316542681088</v>
+        <v>323829563392</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.81668</v>
+        <v>3.82319</v>
       </c>
       <c r="I10" t="n">
-        <v>23.905659</v>
+        <v>24.455973</v>
       </c>
       <c r="J10" t="n">
-        <v>19.917833</v>
+        <v>20.341652</v>
       </c>
       <c r="K10" t="n">
         <v>1.75</v>
       </c>
       <c r="L10" t="n">
-        <v>6.5440907</v>
+        <v>6.694737</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04183109707971587</v>
+        <v>0.04088980326604089</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05020626151012891</v>
+        <v>0.04916021602160216</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04723999977111817</v>
+        <v>0.04706000328063965</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002966261739010746</v>
+        <v>0.002100212740962518</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P478"/>
+  <dimension ref="A1:P487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27663,16 +27663,16 @@
         <v>9.692397</v>
       </c>
       <c r="M470" t="n">
-        <v>0.0280940554139922</v>
+        <v>0.0280940554139921</v>
       </c>
       <c r="N470" t="n">
         <v>0.0306670644776312</v>
       </c>
       <c r="O470" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.0470600032806396</v>
       </c>
       <c r="P470" t="n">
-        <v>-0.01639293880300845</v>
+        <v>-0.0163929388030084</v>
       </c>
     </row>
     <row r="471">
@@ -27721,16 +27721,16 @@
         <v>19.144283</v>
       </c>
       <c r="M471" t="n">
-        <v>0.008051363570676521</v>
+        <v>0.0080513635706765</v>
       </c>
       <c r="N471" t="n">
-        <v>0.03193176985486901</v>
+        <v>0.031931769854869</v>
       </c>
       <c r="O471" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.0470600032806396</v>
       </c>
       <c r="P471" t="n">
-        <v>-0.01512823342577063</v>
+        <v>-0.0151282334257706</v>
       </c>
     </row>
     <row r="472">
@@ -27779,16 +27779,16 @@
         <v>3.6078138</v>
       </c>
       <c r="M472" t="n">
-        <v>0.04794758142223935</v>
+        <v>0.0479475814222393</v>
       </c>
       <c r="N472" t="n">
-        <v>0.04009735979957603</v>
+        <v>0.040097359799576</v>
       </c>
       <c r="O472" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.0470600032806396</v>
       </c>
       <c r="P472" t="n">
-        <v>-0.006962643481063617</v>
+        <v>-0.0069626434810636</v>
       </c>
     </row>
     <row r="473">
@@ -27837,16 +27837,16 @@
         <v>23.956543</v>
       </c>
       <c r="M473" t="n">
-        <v>0.01578947368421053</v>
+        <v>0.0157894736842105</v>
       </c>
       <c r="N473" t="n">
-        <v>0.05139647368421053</v>
+        <v>0.0513964736842105</v>
       </c>
       <c r="O473" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.0470600032806396</v>
       </c>
       <c r="P473" t="n">
-        <v>0.00433647040357088</v>
+        <v>0.0043364704035708</v>
       </c>
     </row>
     <row r="474">
@@ -27895,16 +27895,16 @@
         <v>9.361181</v>
       </c>
       <c r="M474" t="n">
-        <v>0.05842709798406002</v>
+        <v>0.05842709798406</v>
       </c>
       <c r="N474" t="n">
         <v>0.0432084798406001</v>
       </c>
       <c r="O474" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.0470600032806396</v>
       </c>
       <c r="P474" t="n">
-        <v>-0.003851523440039549</v>
+        <v>-0.0038515234400395</v>
       </c>
     </row>
     <row r="475">
@@ -27953,16 +27953,16 @@
         <v>6.068</v>
       </c>
       <c r="M475" t="n">
-        <v>0.04887155811429728</v>
+        <v>0.0488715581142972</v>
       </c>
       <c r="N475" t="n">
-        <v>0.06416576231905384</v>
+        <v>0.0641657623190538</v>
       </c>
       <c r="O475" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.0470600032806396</v>
       </c>
       <c r="P475" t="n">
-        <v>0.01710575903841419</v>
+        <v>0.0171057590384141</v>
       </c>
     </row>
     <row r="476">
@@ -28011,16 +28011,16 @@
         <v>10.777411</v>
       </c>
       <c r="M476" t="n">
-        <v>0.03731079874592529</v>
+        <v>0.0373107987459252</v>
       </c>
       <c r="N476" t="n">
-        <v>0.04894479164503873</v>
+        <v>0.0489447916450387</v>
       </c>
       <c r="O476" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.0470600032806396</v>
       </c>
       <c r="P476" t="n">
-        <v>0.001884788364399079</v>
+        <v>0.001884788364399</v>
       </c>
     </row>
     <row r="477">
@@ -28069,16 +28069,16 @@
         <v>6.694737</v>
       </c>
       <c r="M477" t="n">
-        <v>0.04088980326604089</v>
+        <v>0.0408898032660408</v>
       </c>
       <c r="N477" t="n">
-        <v>0.04916021602160216</v>
+        <v>0.0491602160216021</v>
       </c>
       <c r="O477" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.0470600032806396</v>
       </c>
       <c r="P477" t="n">
-        <v>0.002100212740962518</v>
+        <v>0.0021002127409625</v>
       </c>
     </row>
     <row r="478">
@@ -28127,16 +28127,538 @@
         <v>20.996101</v>
       </c>
       <c r="M478" t="n">
-        <v>0.02971693819969054</v>
+        <v>0.0297169381996905</v>
       </c>
       <c r="N478" t="n">
-        <v>0.05840534267771002</v>
+        <v>0.05840534267771</v>
       </c>
       <c r="O478" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.0470600032806396</v>
       </c>
       <c r="P478" t="n">
-        <v>0.01134533939707037</v>
+        <v>0.0113453393970703</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2026-08-19 15:47:09</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>316.83</v>
+      </c>
+      <c r="F479" t="n">
+        <v>4623874129920</v>
+      </c>
+      <c r="G479" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H479" t="n">
+        <v>9.539300000000001</v>
+      </c>
+      <c r="I479" t="n">
+        <v>36.375427</v>
+      </c>
+      <c r="J479" t="n">
+        <v>33.213127</v>
+      </c>
+      <c r="K479" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="L479" t="n">
+        <v>9.9049835</v>
+      </c>
+      <c r="M479" t="n">
+        <v>0.02749108354638135</v>
+      </c>
+      <c r="N479" t="n">
+        <v>0.03010857557680776</v>
+      </c>
+      <c r="O479" t="n">
+        <v>0.04652999877929687</v>
+      </c>
+      <c r="P479" t="n">
+        <v>-0.01642142320248912</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>2026-08-19 15:47:09</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>466.42</v>
+      </c>
+      <c r="F480" t="n">
+        <v>761419005952</v>
+      </c>
+      <c r="G480" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H480" t="n">
+        <v>15.46743</v>
+      </c>
+      <c r="I480" t="n">
+        <v>118.984695</v>
+      </c>
+      <c r="J480" t="n">
+        <v>30.154978</v>
+      </c>
+      <c r="K480" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L480" t="n">
+        <v>18.434063</v>
+      </c>
+      <c r="M480" t="n">
+        <v>0.008404442348098281</v>
+      </c>
+      <c r="N480" t="n">
+        <v>0.03316202135414433</v>
+      </c>
+      <c r="O480" t="n">
+        <v>0.04652999877929687</v>
+      </c>
+      <c r="P480" t="n">
+        <v>-0.01336797742515254</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>2026-08-19 15:47:09</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>265.84</v>
+      </c>
+      <c r="F481" t="n">
+        <v>2867433570304</v>
+      </c>
+      <c r="G481" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H481" t="n">
+        <v>10.40326</v>
+      </c>
+      <c r="I481" t="n">
+        <v>21.386967</v>
+      </c>
+      <c r="J481" t="n">
+        <v>25.553528</v>
+      </c>
+      <c r="K481" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L481" t="n">
+        <v>3.6966705</v>
+      </c>
+      <c r="M481" t="n">
+        <v>0.04675744808907614</v>
+      </c>
+      <c r="N481" t="n">
+        <v>0.03913353897080951</v>
+      </c>
+      <c r="O481" t="n">
+        <v>0.04652999877929687</v>
+      </c>
+      <c r="P481" t="n">
+        <v>-0.007396459808487361</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>2026-08-19 15:47:09</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>362.48</v>
+      </c>
+      <c r="F482" t="n">
+        <v>1724527804416</v>
+      </c>
+      <c r="G482" t="n">
+        <v>6</v>
+      </c>
+      <c r="H482" t="n">
+        <v>19.53226</v>
+      </c>
+      <c r="I482" t="n">
+        <v>60.413334</v>
+      </c>
+      <c r="J482" t="n">
+        <v>18.558016</v>
+      </c>
+      <c r="K482" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L482" t="n">
+        <v>22.852022</v>
+      </c>
+      <c r="M482" t="n">
+        <v>0.01655263738689031</v>
+      </c>
+      <c r="N482" t="n">
+        <v>0.05388506952107702</v>
+      </c>
+      <c r="O482" t="n">
+        <v>0.04652999877929687</v>
+      </c>
+      <c r="P482" t="n">
+        <v>0.007355070741780149</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2026-08-19 15:47:09</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>341.7</v>
+      </c>
+      <c r="F483" t="n">
+        <v>4178969100288</v>
+      </c>
+      <c r="G483" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H483" t="n">
+        <v>14.74619</v>
+      </c>
+      <c r="I483" t="n">
+        <v>17.145008</v>
+      </c>
+      <c r="J483" t="n">
+        <v>23.172089</v>
+      </c>
+      <c r="K483" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L483" t="n">
+        <v>9.372703</v>
+      </c>
+      <c r="M483" t="n">
+        <v>0.05832601697395376</v>
+      </c>
+      <c r="N483" t="n">
+        <v>0.04315537020778461</v>
+      </c>
+      <c r="O483" t="n">
+        <v>0.04652999877929687</v>
+      </c>
+      <c r="P483" t="n">
+        <v>-0.003374628571512266</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2026-08-19 15:47:09</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>546.03</v>
+      </c>
+      <c r="F484" t="n">
+        <v>1391014838272</v>
+      </c>
+      <c r="G484" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="H484" t="n">
+        <v>34.70468</v>
+      </c>
+      <c r="I484" t="n">
+        <v>20.581606</v>
+      </c>
+      <c r="J484" t="n">
+        <v>15.733613</v>
+      </c>
+      <c r="K484" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L484" t="n">
+        <v>6.0943403</v>
+      </c>
+      <c r="M484" t="n">
+        <v>0.04858707397029468</v>
+      </c>
+      <c r="N484" t="n">
+        <v>0.06355819277329085</v>
+      </c>
+      <c r="O484" t="n">
+        <v>0.04652999877929687</v>
+      </c>
+      <c r="P484" t="n">
+        <v>0.01702819399399397</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>2026-08-19 15:47:09</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>484.31</v>
+      </c>
+      <c r="F485" t="n">
+        <v>3596265979904</v>
+      </c>
+      <c r="G485" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="H485" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I485" t="n">
+        <v>26.966038</v>
+      </c>
+      <c r="J485" t="n">
+        <v>20.54487</v>
+      </c>
+      <c r="K485" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L485" t="n">
+        <v>10.837381</v>
+      </c>
+      <c r="M485" t="n">
+        <v>0.03708368606884021</v>
+      </c>
+      <c r="N485" t="n">
+        <v>0.04867394850405732</v>
+      </c>
+      <c r="O485" t="n">
+        <v>0.04652999877929687</v>
+      </c>
+      <c r="P485" t="n">
+        <v>0.002143949724760445</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2026-08-19 15:47:09</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>80.22</v>
+      </c>
+      <c r="F486" t="n">
+        <v>334031224832</v>
+      </c>
+      <c r="G486" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H486" t="n">
+        <v>3.82319</v>
+      </c>
+      <c r="I486" t="n">
+        <v>25.226416</v>
+      </c>
+      <c r="J486" t="n">
+        <v>20.98248</v>
+      </c>
+      <c r="K486" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L486" t="n">
+        <v>6.9056425</v>
+      </c>
+      <c r="M486" t="n">
+        <v>0.03964098728496634</v>
+      </c>
+      <c r="N486" t="n">
+        <v>0.04765881326352531</v>
+      </c>
+      <c r="O486" t="n">
+        <v>0.04652999877929687</v>
+      </c>
+      <c r="P486" t="n">
+        <v>0.001128814484228434</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>2026-08-19 15:47:09</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>217.56</v>
+      </c>
+      <c r="F487" t="n">
+        <v>5269520646144</v>
+      </c>
+      <c r="G487" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H487" t="n">
+        <v>12.8386</v>
+      </c>
+      <c r="I487" t="n">
+        <v>33.316998</v>
+      </c>
+      <c r="J487" t="n">
+        <v>16.945772</v>
+      </c>
+      <c r="K487" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L487" t="n">
+        <v>20.787802</v>
+      </c>
+      <c r="M487" t="n">
+        <v>0.03001470858613716</v>
+      </c>
+      <c r="N487" t="n">
+        <v>0.05901176686890972</v>
+      </c>
+      <c r="O487" t="n">
+        <v>0.04652999877929687</v>
+      </c>
+      <c r="P487" t="n">
+        <v>0.01248176808961285</v>
       </c>
     </row>
   </sheetData>
@@ -28238,12 +28760,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:10</t>
+          <t>2026-08-19 15:47:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -28257,51 +28779,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>341.28</v>
+        <v>341.7</v>
       </c>
       <c r="F2" t="n">
-        <v>4173832126464</v>
+        <v>4178969100288</v>
       </c>
       <c r="G2" t="n">
-        <v>19.94</v>
+        <v>19.93</v>
       </c>
       <c r="H2" t="n">
         <v>14.74619</v>
       </c>
       <c r="I2" t="n">
-        <v>17.115345</v>
+        <v>17.145008</v>
       </c>
       <c r="J2" t="n">
-        <v>23.143604</v>
+        <v>23.172089</v>
       </c>
       <c r="K2" t="n">
         <v>0.93</v>
       </c>
       <c r="L2" t="n">
-        <v>9.361181</v>
+        <v>9.372703</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05842709798406002</v>
+        <v>0.05832601697395376</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0432084798406001</v>
+        <v>0.04315537020778461</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.04652999877929687</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003851523440039549</v>
+        <v>-0.003374628571512266</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:10</t>
+          <t>2026-08-19 15:47:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -28315,51 +28837,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>481.63</v>
+        <v>484.31</v>
       </c>
       <c r="F3" t="n">
-        <v>3576365580288</v>
+        <v>3596265979904</v>
       </c>
       <c r="G3" t="n">
-        <v>17.97</v>
+        <v>17.96</v>
       </c>
       <c r="H3" t="n">
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>26.801893</v>
+        <v>26.966038</v>
       </c>
       <c r="J3" t="n">
-        <v>20.431183</v>
+        <v>20.54487</v>
       </c>
       <c r="K3" t="n">
         <v>1.61</v>
       </c>
       <c r="L3" t="n">
-        <v>10.777411</v>
+        <v>10.837381</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03731079874592529</v>
+        <v>0.03708368606884021</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04894479164503873</v>
+        <v>0.04867394850405732</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.04652999877929687</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001884788364399079</v>
+        <v>0.002143949724760445</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:10</t>
+          <t>2026-08-19 15:47:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -28373,51 +28895,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>543.67</v>
+        <v>546.03</v>
       </c>
       <c r="F4" t="n">
-        <v>1385002696704</v>
+        <v>1391014838272</v>
       </c>
       <c r="G4" t="n">
-        <v>26.57</v>
+        <v>26.53</v>
       </c>
       <c r="H4" t="n">
-        <v>34.885</v>
+        <v>34.70468</v>
       </c>
       <c r="I4" t="n">
-        <v>20.461798</v>
+        <v>20.581606</v>
       </c>
       <c r="J4" t="n">
-        <v>15.584636</v>
+        <v>15.733613</v>
       </c>
       <c r="K4" t="n">
         <v>0.88</v>
       </c>
       <c r="L4" t="n">
-        <v>6.068</v>
+        <v>6.0943403</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04887155811429728</v>
+        <v>0.04858707397029468</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06416576231905384</v>
+        <v>0.06355819277329085</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.04652999877929687</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01710575903841419</v>
+        <v>0.01702819399399397</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:10</t>
+          <t>2026-08-19 15:47:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -28431,51 +28953,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>259.45</v>
+        <v>265.84</v>
       </c>
       <c r="F5" t="n">
-        <v>2798509096960</v>
+        <v>2867433570304</v>
       </c>
       <c r="G5" t="n">
-        <v>12.44</v>
+        <v>12.43</v>
       </c>
       <c r="H5" t="n">
         <v>10.40326</v>
       </c>
       <c r="I5" t="n">
-        <v>20.856112</v>
+        <v>21.386967</v>
       </c>
       <c r="J5" t="n">
-        <v>24.939299</v>
+        <v>25.553528</v>
       </c>
       <c r="K5" t="n">
         <v>1.4</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6078138</v>
+        <v>3.6966705</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04794758142223935</v>
+        <v>0.04675744808907614</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04009735979957603</v>
+        <v>0.03913353897080951</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.04652999877929687</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.006962643481063617</v>
+        <v>-0.007396459808487361</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:10</t>
+          <t>2026-08-19 15:47:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -28489,51 +29011,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>310.03</v>
+        <v>316.83</v>
       </c>
       <c r="F6" t="n">
-        <v>4524633751552</v>
+        <v>4623874129920</v>
       </c>
       <c r="G6" t="n">
         <v>8.710000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>9.507709999999999</v>
+        <v>9.539300000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>35.59472</v>
+        <v>36.375427</v>
       </c>
       <c r="J6" t="n">
-        <v>32.608273</v>
+        <v>33.213127</v>
       </c>
       <c r="K6" t="n">
         <v>2.47</v>
       </c>
       <c r="L6" t="n">
-        <v>9.692397</v>
+        <v>9.9049835</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0280940554139922</v>
+        <v>0.02749108354638135</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0306670644776312</v>
+        <v>0.03010857557680776</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.04652999877929687</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01639293880300845</v>
+        <v>-0.01642142320248912</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:10</t>
+          <t>2026-08-19 15:47:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -28547,51 +29069,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219.74</v>
+        <v>217.56</v>
       </c>
       <c r="F7" t="n">
-        <v>5322322739200</v>
+        <v>5269520646144</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
       </c>
       <c r="H7" t="n">
-        <v>12.83399</v>
+        <v>12.8386</v>
       </c>
       <c r="I7" t="n">
-        <v>33.65084</v>
+        <v>33.316998</v>
       </c>
       <c r="J7" t="n">
-        <v>17.121721</v>
+        <v>16.945772</v>
       </c>
       <c r="K7" t="n">
         <v>0.62</v>
       </c>
       <c r="L7" t="n">
-        <v>20.996101</v>
+        <v>20.787802</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02971693819969054</v>
+        <v>0.03001470858613716</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05840534267771002</v>
+        <v>0.05901176686890972</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.04652999877929687</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01134533939707037</v>
+        <v>0.01248176808961285</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:10</t>
+          <t>2026-08-19 15:47:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -28605,51 +29127,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>484.39</v>
+        <v>466.42</v>
       </c>
       <c r="F8" t="n">
-        <v>790754623488</v>
+        <v>761419005952</v>
       </c>
       <c r="G8" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="H8" t="n">
         <v>15.46743</v>
       </c>
       <c r="I8" t="n">
-        <v>124.20257</v>
+        <v>118.984695</v>
       </c>
       <c r="J8" t="n">
-        <v>31.316774</v>
+        <v>30.154978</v>
       </c>
       <c r="K8" t="n">
         <v>1.1</v>
       </c>
       <c r="L8" t="n">
-        <v>19.144283</v>
+        <v>18.434063</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008051363570676521</v>
+        <v>0.008404442348098281</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03193176985486901</v>
+        <v>0.03316202135414433</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.04652999877929687</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01512823342577063</v>
+        <v>-0.01336797742515254</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:10</t>
+          <t>2026-08-19 15:47:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -28663,51 +29185,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>380</v>
+        <v>362.48</v>
       </c>
       <c r="F9" t="n">
-        <v>1807880552448</v>
+        <v>1724527804416</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>19.53066</v>
+        <v>19.53226</v>
       </c>
       <c r="I9" t="n">
-        <v>63.333332</v>
+        <v>60.413334</v>
       </c>
       <c r="J9" t="n">
-        <v>19.456587</v>
+        <v>18.558016</v>
       </c>
       <c r="K9" t="n">
         <v>0.44</v>
       </c>
       <c r="L9" t="n">
-        <v>23.956543</v>
+        <v>22.852022</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01578947368421053</v>
+        <v>0.01655263738689031</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05139647368421053</v>
+        <v>0.05388506952107702</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.04652999877929687</v>
       </c>
       <c r="P9" t="n">
-        <v>0.00433647040357088</v>
+        <v>0.007355070741780149</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-18 15:46:10</t>
+          <t>2026-08-19 15:47:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -28721,10 +29243,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>77.77</v>
+        <v>80.22</v>
       </c>
       <c r="F10" t="n">
-        <v>323829563392</v>
+        <v>334031224832</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -28733,28 +29255,28 @@
         <v>3.82319</v>
       </c>
       <c r="I10" t="n">
-        <v>24.455973</v>
+        <v>25.226416</v>
       </c>
       <c r="J10" t="n">
-        <v>20.341652</v>
+        <v>20.98248</v>
       </c>
       <c r="K10" t="n">
         <v>1.75</v>
       </c>
       <c r="L10" t="n">
-        <v>6.694737</v>
+        <v>6.9056425</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04088980326604089</v>
+        <v>0.03964098728496634</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04916021602160216</v>
+        <v>0.04765881326352531</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04706000328063965</v>
+        <v>0.04652999877929687</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002100212740962518</v>
+        <v>0.001128814484228434</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P487"/>
+  <dimension ref="A1:P496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28185,16 +28185,16 @@
         <v>9.9049835</v>
       </c>
       <c r="M479" t="n">
-        <v>0.02749108354638135</v>
+        <v>0.0274910835463813</v>
       </c>
       <c r="N479" t="n">
-        <v>0.03010857557680776</v>
+        <v>0.0301085755768077</v>
       </c>
       <c r="O479" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.0465299987792968</v>
       </c>
       <c r="P479" t="n">
-        <v>-0.01642142320248912</v>
+        <v>-0.0164214232024891</v>
       </c>
     </row>
     <row r="480">
@@ -28243,16 +28243,16 @@
         <v>18.434063</v>
       </c>
       <c r="M480" t="n">
-        <v>0.008404442348098281</v>
+        <v>0.008404442348098199</v>
       </c>
       <c r="N480" t="n">
-        <v>0.03316202135414433</v>
+        <v>0.0331620213541443</v>
       </c>
       <c r="O480" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.0465299987792968</v>
       </c>
       <c r="P480" t="n">
-        <v>-0.01336797742515254</v>
+        <v>-0.0133679774251525</v>
       </c>
     </row>
     <row r="481">
@@ -28301,16 +28301,16 @@
         <v>3.6966705</v>
       </c>
       <c r="M481" t="n">
-        <v>0.04675744808907614</v>
+        <v>0.0467574480890761</v>
       </c>
       <c r="N481" t="n">
-        <v>0.03913353897080951</v>
+        <v>0.0391335389708095</v>
       </c>
       <c r="O481" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.0465299987792968</v>
       </c>
       <c r="P481" t="n">
-        <v>-0.007396459808487361</v>
+        <v>-0.0073964598084873</v>
       </c>
     </row>
     <row r="482">
@@ -28359,16 +28359,16 @@
         <v>22.852022</v>
       </c>
       <c r="M482" t="n">
-        <v>0.01655263738689031</v>
+        <v>0.0165526373868903</v>
       </c>
       <c r="N482" t="n">
-        <v>0.05388506952107702</v>
+        <v>0.053885069521077</v>
       </c>
       <c r="O482" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.0465299987792968</v>
       </c>
       <c r="P482" t="n">
-        <v>0.007355070741780149</v>
+        <v>0.0073550707417801</v>
       </c>
     </row>
     <row r="483">
@@ -28417,16 +28417,16 @@
         <v>9.372703</v>
       </c>
       <c r="M483" t="n">
-        <v>0.05832601697395376</v>
+        <v>0.0583260169739537</v>
       </c>
       <c r="N483" t="n">
-        <v>0.04315537020778461</v>
+        <v>0.0431553702077846</v>
       </c>
       <c r="O483" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.0465299987792968</v>
       </c>
       <c r="P483" t="n">
-        <v>-0.003374628571512266</v>
+        <v>-0.0033746285715122</v>
       </c>
     </row>
     <row r="484">
@@ -28475,16 +28475,16 @@
         <v>6.0943403</v>
       </c>
       <c r="M484" t="n">
-        <v>0.04858707397029468</v>
+        <v>0.0485870739702946</v>
       </c>
       <c r="N484" t="n">
-        <v>0.06355819277329085</v>
+        <v>0.06355819277329081</v>
       </c>
       <c r="O484" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.0465299987792968</v>
       </c>
       <c r="P484" t="n">
-        <v>0.01702819399399397</v>
+        <v>0.0170281939939939</v>
       </c>
     </row>
     <row r="485">
@@ -28533,16 +28533,16 @@
         <v>10.837381</v>
       </c>
       <c r="M485" t="n">
-        <v>0.03708368606884021</v>
+        <v>0.0370836860688402</v>
       </c>
       <c r="N485" t="n">
-        <v>0.04867394850405732</v>
+        <v>0.0486739485040573</v>
       </c>
       <c r="O485" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.0465299987792968</v>
       </c>
       <c r="P485" t="n">
-        <v>0.002143949724760445</v>
+        <v>0.0021439497247604</v>
       </c>
     </row>
     <row r="486">
@@ -28591,16 +28591,16 @@
         <v>6.9056425</v>
       </c>
       <c r="M486" t="n">
-        <v>0.03964098728496634</v>
+        <v>0.0396409872849663</v>
       </c>
       <c r="N486" t="n">
-        <v>0.04765881326352531</v>
+        <v>0.0476588132635253</v>
       </c>
       <c r="O486" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.0465299987792968</v>
       </c>
       <c r="P486" t="n">
-        <v>0.001128814484228434</v>
+        <v>0.0011288144842284</v>
       </c>
     </row>
     <row r="487">
@@ -28649,16 +28649,538 @@
         <v>20.787802</v>
       </c>
       <c r="M487" t="n">
-        <v>0.03001470858613716</v>
+        <v>0.0300147085861371</v>
       </c>
       <c r="N487" t="n">
-        <v>0.05901176686890972</v>
+        <v>0.0590117668689097</v>
       </c>
       <c r="O487" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.0465299987792968</v>
       </c>
       <c r="P487" t="n">
-        <v>0.01248176808961285</v>
+        <v>0.0124817680896128</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:50:35</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>311.3</v>
+      </c>
+      <c r="F488" t="n">
+        <v>4543167856640</v>
+      </c>
+      <c r="G488" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H488" t="n">
+        <v>9.539300000000001</v>
+      </c>
+      <c r="I488" t="n">
+        <v>35.74053</v>
+      </c>
+      <c r="J488" t="n">
+        <v>32.63342</v>
+      </c>
+      <c r="K488" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L488" t="n">
+        <v>9.732100000000001</v>
+      </c>
+      <c r="M488" t="n">
+        <v>0.027979441053646</v>
+      </c>
+      <c r="N488" t="n">
+        <v>0.03064343077417283</v>
+      </c>
+      <c r="O488" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P488" t="n">
+        <v>-0.01631657021764846</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:50:35</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>469.455</v>
+      </c>
+      <c r="F489" t="n">
+        <v>766373527552</v>
+      </c>
+      <c r="G489" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H489" t="n">
+        <v>15.4961</v>
+      </c>
+      <c r="I489" t="n">
+        <v>119.75893</v>
+      </c>
+      <c r="J489" t="n">
+        <v>30.29504</v>
+      </c>
+      <c r="K489" t="n">
+        <v>1</v>
+      </c>
+      <c r="L489" t="n">
+        <v>18.554012</v>
+      </c>
+      <c r="M489" t="n">
+        <v>0.008350108104078133</v>
+      </c>
+      <c r="N489" t="n">
+        <v>0.03300870157949112</v>
+      </c>
+      <c r="O489" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P489" t="n">
+        <v>-0.01395129941233017</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:50:35</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>260.11</v>
+      </c>
+      <c r="F490" t="n">
+        <v>2805627879424</v>
+      </c>
+      <c r="G490" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="H490" t="n">
+        <v>10.37777</v>
+      </c>
+      <c r="I490" t="n">
+        <v>20.909164</v>
+      </c>
+      <c r="J490" t="n">
+        <v>25.06415</v>
+      </c>
+      <c r="K490" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L490" t="n">
+        <v>3.6169913</v>
+      </c>
+      <c r="M490" t="n">
+        <v>0.0478259198031602</v>
+      </c>
+      <c r="N490" t="n">
+        <v>0.03989762023759179</v>
+      </c>
+      <c r="O490" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P490" t="n">
+        <v>-0.007062380754229498</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:50:35</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>364.03</v>
+      </c>
+      <c r="F491" t="n">
+        <v>1731901915136</v>
+      </c>
+      <c r="G491" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H491" t="n">
+        <v>19.53226</v>
+      </c>
+      <c r="I491" t="n">
+        <v>60.4701</v>
+      </c>
+      <c r="J491" t="n">
+        <v>18.637371</v>
+      </c>
+      <c r="K491" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L491" t="n">
+        <v>22.949738</v>
+      </c>
+      <c r="M491" t="n">
+        <v>0.01653709859077548</v>
+      </c>
+      <c r="N491" t="n">
+        <v>0.05365563277751834</v>
+      </c>
+      <c r="O491" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P491" t="n">
+        <v>0.006695631785697057</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:50:35</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>338.2</v>
+      </c>
+      <c r="F492" t="n">
+        <v>4136164130816</v>
+      </c>
+      <c r="G492" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H492" t="n">
+        <v>14.81022</v>
+      </c>
+      <c r="I492" t="n">
+        <v>16.977913</v>
+      </c>
+      <c r="J492" t="n">
+        <v>22.835583</v>
+      </c>
+      <c r="K492" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L492" t="n">
+        <v>9.276698</v>
+      </c>
+      <c r="M492" t="n">
+        <v>0.05890005913660556</v>
+      </c>
+      <c r="N492" t="n">
+        <v>0.04379130691898285</v>
+      </c>
+      <c r="O492" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P492" t="n">
+        <v>-0.003168694072838436</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:50:35</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>545.83</v>
+      </c>
+      <c r="F493" t="n">
+        <v>1390505361408</v>
+      </c>
+      <c r="G493" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H493" t="n">
+        <v>34.70468</v>
+      </c>
+      <c r="I493" t="n">
+        <v>20.566315</v>
+      </c>
+      <c r="J493" t="n">
+        <v>15.72785</v>
+      </c>
+      <c r="K493" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L493" t="n">
+        <v>6.0921082</v>
+      </c>
+      <c r="M493" t="n">
+        <v>0.04862319769891724</v>
+      </c>
+      <c r="N493" t="n">
+        <v>0.06358148141362696</v>
+      </c>
+      <c r="O493" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P493" t="n">
+        <v>0.01662148042180567</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:50:35</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>481.15</v>
+      </c>
+      <c r="F494" t="n">
+        <v>3572801208320</v>
+      </c>
+      <c r="G494" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="H494" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I494" t="n">
+        <v>26.77518</v>
+      </c>
+      <c r="J494" t="n">
+        <v>20.41082</v>
+      </c>
+      <c r="K494" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L494" t="n">
+        <v>10.76667</v>
+      </c>
+      <c r="M494" t="n">
+        <v>0.03734802036786865</v>
+      </c>
+      <c r="N494" t="n">
+        <v>0.04899361945339292</v>
+      </c>
+      <c r="O494" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P494" t="n">
+        <v>0.002033618461571629</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:50:35</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>80.14</v>
+      </c>
+      <c r="F495" t="n">
+        <v>333698105344</v>
+      </c>
+      <c r="G495" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H495" t="n">
+        <v>3.82319</v>
+      </c>
+      <c r="I495" t="n">
+        <v>25.201258</v>
+      </c>
+      <c r="J495" t="n">
+        <v>20.961554</v>
+      </c>
+      <c r="K495" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L495" t="n">
+        <v>6.898756</v>
+      </c>
+      <c r="M495" t="n">
+        <v>0.039680559021712</v>
+      </c>
+      <c r="N495" t="n">
+        <v>0.04770638881956576</v>
+      </c>
+      <c r="O495" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P495" t="n">
+        <v>0.0007463878277444713</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:50:35</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>216.85</v>
+      </c>
+      <c r="F496" t="n">
+        <v>5252323999744</v>
+      </c>
+      <c r="G496" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H496" t="n">
+        <v>12.99922</v>
+      </c>
+      <c r="I496" t="n">
+        <v>33.20827</v>
+      </c>
+      <c r="J496" t="n">
+        <v>16.68177</v>
+      </c>
+      <c r="K496" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L496" t="n">
+        <v>20.719963</v>
+      </c>
+      <c r="M496" t="n">
+        <v>0.03011298132349551</v>
+      </c>
+      <c r="N496" t="n">
+        <v>0.05994567673507032</v>
+      </c>
+      <c r="O496" t="n">
+        <v>0.04696000099182129</v>
+      </c>
+      <c r="P496" t="n">
+        <v>0.01298567574324903</v>
       </c>
     </row>
   </sheetData>
@@ -28760,12 +29282,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-19 15:47:09</t>
+          <t>2026-08-20 15:50:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -28779,51 +29301,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>341.7</v>
+        <v>338.2</v>
       </c>
       <c r="F2" t="n">
-        <v>4178969100288</v>
+        <v>4136164130816</v>
       </c>
       <c r="G2" t="n">
-        <v>19.93</v>
+        <v>19.92</v>
       </c>
       <c r="H2" t="n">
-        <v>14.74619</v>
+        <v>14.81022</v>
       </c>
       <c r="I2" t="n">
-        <v>17.145008</v>
+        <v>16.977913</v>
       </c>
       <c r="J2" t="n">
-        <v>23.172089</v>
+        <v>22.835583</v>
       </c>
       <c r="K2" t="n">
         <v>0.93</v>
       </c>
       <c r="L2" t="n">
-        <v>9.372703</v>
+        <v>9.276698</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05832601697395376</v>
+        <v>0.05890005913660556</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04315537020778461</v>
+        <v>0.04379130691898285</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003374628571512266</v>
+        <v>-0.003168694072838436</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-19 15:47:09</t>
+          <t>2026-08-20 15:50:35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -28837,51 +29359,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>484.31</v>
+        <v>481.15</v>
       </c>
       <c r="F3" t="n">
-        <v>3596265979904</v>
+        <v>3572801208320</v>
       </c>
       <c r="G3" t="n">
-        <v>17.96</v>
+        <v>17.97</v>
       </c>
       <c r="H3" t="n">
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>26.966038</v>
+        <v>26.77518</v>
       </c>
       <c r="J3" t="n">
-        <v>20.54487</v>
+        <v>20.41082</v>
       </c>
       <c r="K3" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="L3" t="n">
-        <v>10.837381</v>
+        <v>10.76667</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03708368606884021</v>
+        <v>0.03734802036786865</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04867394850405732</v>
+        <v>0.04899361945339292</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002143949724760445</v>
+        <v>0.002033618461571629</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-19 15:47:09</t>
+          <t>2026-08-20 15:50:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -28895,51 +29417,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>546.03</v>
+        <v>545.83</v>
       </c>
       <c r="F4" t="n">
-        <v>1391014838272</v>
+        <v>1390505361408</v>
       </c>
       <c r="G4" t="n">
-        <v>26.53</v>
+        <v>26.54</v>
       </c>
       <c r="H4" t="n">
         <v>34.70468</v>
       </c>
       <c r="I4" t="n">
-        <v>20.581606</v>
+        <v>20.566315</v>
       </c>
       <c r="J4" t="n">
-        <v>15.733613</v>
+        <v>15.72785</v>
       </c>
       <c r="K4" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="L4" t="n">
-        <v>6.0943403</v>
+        <v>6.0921082</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04858707397029468</v>
+        <v>0.04862319769891724</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06355819277329085</v>
+        <v>0.06358148141362696</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01702819399399397</v>
+        <v>0.01662148042180567</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-19 15:47:09</t>
+          <t>2026-08-20 15:50:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -28953,51 +29475,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>265.84</v>
+        <v>260.11</v>
       </c>
       <c r="F5" t="n">
-        <v>2867433570304</v>
+        <v>2805627879424</v>
       </c>
       <c r="G5" t="n">
-        <v>12.43</v>
+        <v>12.44</v>
       </c>
       <c r="H5" t="n">
-        <v>10.40326</v>
+        <v>10.37777</v>
       </c>
       <c r="I5" t="n">
-        <v>21.386967</v>
+        <v>20.909164</v>
       </c>
       <c r="J5" t="n">
-        <v>25.553528</v>
+        <v>25.06415</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6966705</v>
+        <v>3.6169913</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04675744808907614</v>
+        <v>0.0478259198031602</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03913353897080951</v>
+        <v>0.03989762023759179</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007396459808487361</v>
+        <v>-0.007062380754229498</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-19 15:47:09</t>
+          <t>2026-08-20 15:50:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -29011,10 +29533,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>316.83</v>
+        <v>311.3</v>
       </c>
       <c r="F6" t="n">
-        <v>4623874129920</v>
+        <v>4543167856640</v>
       </c>
       <c r="G6" t="n">
         <v>8.710000000000001</v>
@@ -29023,39 +29545,39 @@
         <v>9.539300000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>36.375427</v>
+        <v>35.74053</v>
       </c>
       <c r="J6" t="n">
-        <v>33.213127</v>
+        <v>32.63342</v>
       </c>
       <c r="K6" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="L6" t="n">
-        <v>9.9049835</v>
+        <v>9.732100000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02749108354638135</v>
+        <v>0.027979441053646</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03010857557680776</v>
+        <v>0.03064343077417283</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01642142320248912</v>
+        <v>-0.01631657021764846</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-19 15:47:09</t>
+          <t>2026-08-20 15:50:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -29069,51 +29591,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>217.56</v>
+        <v>216.85</v>
       </c>
       <c r="F7" t="n">
-        <v>5269520646144</v>
+        <v>5252323999744</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
       </c>
       <c r="H7" t="n">
-        <v>12.8386</v>
+        <v>12.99922</v>
       </c>
       <c r="I7" t="n">
-        <v>33.316998</v>
+        <v>33.20827</v>
       </c>
       <c r="J7" t="n">
-        <v>16.945772</v>
+        <v>16.68177</v>
       </c>
       <c r="K7" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L7" t="n">
-        <v>20.787802</v>
+        <v>20.719963</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03001470858613716</v>
+        <v>0.03011298132349551</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05901176686890972</v>
+        <v>0.05994567673507032</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01248176808961285</v>
+        <v>0.01298567574324903</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-19 15:47:09</t>
+          <t>2026-08-20 15:50:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -29127,51 +29649,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>466.42</v>
+        <v>469.455</v>
       </c>
       <c r="F8" t="n">
-        <v>761419005952</v>
+        <v>766373527552</v>
       </c>
       <c r="G8" t="n">
         <v>3.92</v>
       </c>
       <c r="H8" t="n">
-        <v>15.46743</v>
+        <v>15.4961</v>
       </c>
       <c r="I8" t="n">
-        <v>118.984695</v>
+        <v>119.75893</v>
       </c>
       <c r="J8" t="n">
-        <v>30.154978</v>
+        <v>30.29504</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>18.434063</v>
+        <v>18.554012</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008404442348098281</v>
+        <v>0.008350108104078133</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03316202135414433</v>
+        <v>0.03300870157949112</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01336797742515254</v>
+        <v>-0.01395129941233017</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-19 15:47:09</t>
+          <t>2026-08-20 15:50:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -29185,51 +29707,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>362.48</v>
+        <v>364.03</v>
       </c>
       <c r="F9" t="n">
-        <v>1724527804416</v>
+        <v>1731901915136</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>6.02</v>
       </c>
       <c r="H9" t="n">
         <v>19.53226</v>
       </c>
       <c r="I9" t="n">
-        <v>60.413334</v>
+        <v>60.4701</v>
       </c>
       <c r="J9" t="n">
-        <v>18.558016</v>
+        <v>18.637371</v>
       </c>
       <c r="K9" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="L9" t="n">
-        <v>22.852022</v>
+        <v>22.949738</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01655263738689031</v>
+        <v>0.01653709859077548</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05388506952107702</v>
+        <v>0.05365563277751834</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P9" t="n">
-        <v>0.007355070741780149</v>
+        <v>0.006695631785697057</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-19 15:47:09</t>
+          <t>2026-08-20 15:50:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -29243,10 +29765,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>80.22</v>
+        <v>80.14</v>
       </c>
       <c r="F10" t="n">
-        <v>334031224832</v>
+        <v>333698105344</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -29255,28 +29777,28 @@
         <v>3.82319</v>
       </c>
       <c r="I10" t="n">
-        <v>25.226416</v>
+        <v>25.201258</v>
       </c>
       <c r="J10" t="n">
-        <v>20.98248</v>
+        <v>20.961554</v>
       </c>
       <c r="K10" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="L10" t="n">
-        <v>6.9056425</v>
+        <v>6.898756</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03964098728496634</v>
+        <v>0.039680559021712</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04765881326352531</v>
+        <v>0.04770638881956576</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04652999877929687</v>
+        <v>0.04696000099182129</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001128814484228434</v>
+        <v>0.0007463878277444713</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P496"/>
+  <dimension ref="A1:P505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28710,13 +28710,13 @@
         <v>0.027979441053646</v>
       </c>
       <c r="N488" t="n">
-        <v>0.03064343077417283</v>
+        <v>0.0306434307741728</v>
       </c>
       <c r="O488" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P488" t="n">
-        <v>-0.01631657021764846</v>
+        <v>-0.0163165702176484</v>
       </c>
     </row>
     <row r="489">
@@ -28765,16 +28765,16 @@
         <v>18.554012</v>
       </c>
       <c r="M489" t="n">
-        <v>0.008350108104078133</v>
+        <v>0.0083501081040781</v>
       </c>
       <c r="N489" t="n">
-        <v>0.03300870157949112</v>
+        <v>0.0330087015794911</v>
       </c>
       <c r="O489" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P489" t="n">
-        <v>-0.01395129941233017</v>
+        <v>-0.0139512994123301</v>
       </c>
     </row>
     <row r="490">
@@ -28826,13 +28826,13 @@
         <v>0.0478259198031602</v>
       </c>
       <c r="N490" t="n">
-        <v>0.03989762023759179</v>
+        <v>0.0398976202375917</v>
       </c>
       <c r="O490" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P490" t="n">
-        <v>-0.007062380754229498</v>
+        <v>-0.0070623807542294</v>
       </c>
     </row>
     <row r="491">
@@ -28881,16 +28881,16 @@
         <v>22.949738</v>
       </c>
       <c r="M491" t="n">
-        <v>0.01653709859077548</v>
+        <v>0.0165370985907754</v>
       </c>
       <c r="N491" t="n">
-        <v>0.05365563277751834</v>
+        <v>0.0536556327775183</v>
       </c>
       <c r="O491" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P491" t="n">
-        <v>0.006695631785697057</v>
+        <v>0.006695631785697</v>
       </c>
     </row>
     <row r="492">
@@ -28939,16 +28939,16 @@
         <v>9.276698</v>
       </c>
       <c r="M492" t="n">
-        <v>0.05890005913660556</v>
+        <v>0.0589000591366055</v>
       </c>
       <c r="N492" t="n">
-        <v>0.04379130691898285</v>
+        <v>0.0437913069189828</v>
       </c>
       <c r="O492" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P492" t="n">
-        <v>-0.003168694072838436</v>
+        <v>-0.0031686940728384</v>
       </c>
     </row>
     <row r="493">
@@ -28997,16 +28997,16 @@
         <v>6.0921082</v>
       </c>
       <c r="M493" t="n">
-        <v>0.04862319769891724</v>
+        <v>0.0486231976989172</v>
       </c>
       <c r="N493" t="n">
-        <v>0.06358148141362696</v>
+        <v>0.06358148141362691</v>
       </c>
       <c r="O493" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P493" t="n">
-        <v>0.01662148042180567</v>
+        <v>0.0166214804218056</v>
       </c>
     </row>
     <row r="494">
@@ -29055,16 +29055,16 @@
         <v>10.76667</v>
       </c>
       <c r="M494" t="n">
-        <v>0.03734802036786865</v>
+        <v>0.0373480203678686</v>
       </c>
       <c r="N494" t="n">
-        <v>0.04899361945339292</v>
+        <v>0.0489936194533929</v>
       </c>
       <c r="O494" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P494" t="n">
-        <v>0.002033618461571629</v>
+        <v>0.0020336184615716</v>
       </c>
     </row>
     <row r="495">
@@ -29116,13 +29116,13 @@
         <v>0.039680559021712</v>
       </c>
       <c r="N495" t="n">
-        <v>0.04770638881956576</v>
+        <v>0.0477063888195657</v>
       </c>
       <c r="O495" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P495" t="n">
-        <v>0.0007463878277444713</v>
+        <v>0.0007463878277444</v>
       </c>
     </row>
     <row r="496">
@@ -29171,16 +29171,538 @@
         <v>20.719963</v>
       </c>
       <c r="M496" t="n">
-        <v>0.03011298132349551</v>
+        <v>0.0301129813234955</v>
       </c>
       <c r="N496" t="n">
-        <v>0.05994567673507032</v>
+        <v>0.0599456767350703</v>
       </c>
       <c r="O496" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0469600009918212</v>
       </c>
       <c r="P496" t="n">
-        <v>0.01298567574324903</v>
+        <v>0.012985675743249</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:46:52</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>309.35</v>
+      </c>
+      <c r="F497" t="n">
+        <v>4514709504000</v>
+      </c>
+      <c r="G497" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H497" t="n">
+        <v>9.53851</v>
+      </c>
+      <c r="I497" t="n">
+        <v>35.475918</v>
+      </c>
+      <c r="J497" t="n">
+        <v>32.43169</v>
+      </c>
+      <c r="K497" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L497" t="n">
+        <v>9.671137999999999</v>
+      </c>
+      <c r="M497" t="n">
+        <v>0.02818813641506384</v>
+      </c>
+      <c r="N497" t="n">
+        <v>0.03083403911427186</v>
+      </c>
+      <c r="O497" t="n">
+        <v>0.0473799991607666</v>
+      </c>
+      <c r="P497" t="n">
+        <v>-0.01654596004649474</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:46:52</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>473.25</v>
+      </c>
+      <c r="F498" t="n">
+        <v>772568776704</v>
+      </c>
+      <c r="G498" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="H498" t="n">
+        <v>15.48597</v>
+      </c>
+      <c r="I498" t="n">
+        <v>120.11421</v>
+      </c>
+      <c r="J498" t="n">
+        <v>30.559921</v>
+      </c>
+      <c r="K498" t="n">
+        <v>1</v>
+      </c>
+      <c r="L498" t="n">
+        <v>18.704</v>
+      </c>
+      <c r="M498" t="n">
+        <v>0.00832540940306392</v>
+      </c>
+      <c r="N498" t="n">
+        <v>0.03272259904912837</v>
+      </c>
+      <c r="O498" t="n">
+        <v>0.0473799991607666</v>
+      </c>
+      <c r="P498" t="n">
+        <v>-0.01465740011163823</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:46:52</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>258.63</v>
+      </c>
+      <c r="F499" t="n">
+        <v>2789664358400</v>
+      </c>
+      <c r="G499" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H499" t="n">
+        <v>10.39051</v>
+      </c>
+      <c r="I499" t="n">
+        <v>20.80692</v>
+      </c>
+      <c r="J499" t="n">
+        <v>24.890984</v>
+      </c>
+      <c r="K499" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L499" t="n">
+        <v>3.5964112</v>
+      </c>
+      <c r="M499" t="n">
+        <v>0.04806093647295364</v>
+      </c>
+      <c r="N499" t="n">
+        <v>0.04017519235974172</v>
+      </c>
+      <c r="O499" t="n">
+        <v>0.0473799991607666</v>
+      </c>
+      <c r="P499" t="n">
+        <v>-0.007204806801024879</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:46:52</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>368.45</v>
+      </c>
+      <c r="F500" t="n">
+        <v>1752930451456</v>
+      </c>
+      <c r="G500" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H500" t="n">
+        <v>19.50413</v>
+      </c>
+      <c r="I500" t="n">
+        <v>61.306156</v>
+      </c>
+      <c r="J500" t="n">
+        <v>18.890873</v>
+      </c>
+      <c r="K500" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L500" t="n">
+        <v>23.22839</v>
+      </c>
+      <c r="M500" t="n">
+        <v>0.01631157551906636</v>
+      </c>
+      <c r="N500" t="n">
+        <v>0.05293562220111277</v>
+      </c>
+      <c r="O500" t="n">
+        <v>0.0473799991607666</v>
+      </c>
+      <c r="P500" t="n">
+        <v>0.005555623040346173</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:46:52</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>341.75</v>
+      </c>
+      <c r="F501" t="n">
+        <v>4179580420096</v>
+      </c>
+      <c r="G501" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H501" t="n">
+        <v>14.81101</v>
+      </c>
+      <c r="I501" t="n">
+        <v>17.156124</v>
+      </c>
+      <c r="J501" t="n">
+        <v>23.07405</v>
+      </c>
+      <c r="K501" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L501" t="n">
+        <v>9.374072999999999</v>
+      </c>
+      <c r="M501" t="n">
+        <v>0.05828822238478421</v>
+      </c>
+      <c r="N501" t="n">
+        <v>0.04333872713972202</v>
+      </c>
+      <c r="O501" t="n">
+        <v>0.0473799991607666</v>
+      </c>
+      <c r="P501" t="n">
+        <v>-0.004041272021044581</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:46:52</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>549.9</v>
+      </c>
+      <c r="F502" t="n">
+        <v>1400873680896</v>
+      </c>
+      <c r="G502" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="H502" t="n">
+        <v>34.70468</v>
+      </c>
+      <c r="I502" t="n">
+        <v>20.727478</v>
+      </c>
+      <c r="J502" t="n">
+        <v>15.845125</v>
+      </c>
+      <c r="K502" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L502" t="n">
+        <v>6.137534</v>
+      </c>
+      <c r="M502" t="n">
+        <v>0.04824513547917804</v>
+      </c>
+      <c r="N502" t="n">
+        <v>0.0631108928896163</v>
+      </c>
+      <c r="O502" t="n">
+        <v>0.0473799991607666</v>
+      </c>
+      <c r="P502" t="n">
+        <v>0.0157308937288497</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:46:52</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>483.24</v>
+      </c>
+      <c r="F503" t="n">
+        <v>3588320657408</v>
+      </c>
+      <c r="G503" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H503" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I503" t="n">
+        <v>26.921446</v>
+      </c>
+      <c r="J503" t="n">
+        <v>20.49948</v>
+      </c>
+      <c r="K503" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L503" t="n">
+        <v>10.813438</v>
+      </c>
+      <c r="M503" t="n">
+        <v>0.03714510388212896</v>
+      </c>
+      <c r="N503" t="n">
+        <v>0.04878172336727092</v>
+      </c>
+      <c r="O503" t="n">
+        <v>0.0473799991607666</v>
+      </c>
+      <c r="P503" t="n">
+        <v>0.001401724206504321</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:46:52</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>79.59</v>
+      </c>
+      <c r="F504" t="n">
+        <v>331407949824</v>
+      </c>
+      <c r="G504" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H504" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I504" t="n">
+        <v>25.0283</v>
+      </c>
+      <c r="J504" t="n">
+        <v>20.830116</v>
+      </c>
+      <c r="K504" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L504" t="n">
+        <v>6.85141</v>
+      </c>
+      <c r="M504" t="n">
+        <v>0.03995476818695816</v>
+      </c>
+      <c r="N504" t="n">
+        <v>0.04800741299158186</v>
+      </c>
+      <c r="O504" t="n">
+        <v>0.0473799991607666</v>
+      </c>
+      <c r="P504" t="n">
+        <v>0.0006274138308152571</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:46:52</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>214.72</v>
+      </c>
+      <c r="F505" t="n">
+        <v>5200733011968</v>
+      </c>
+      <c r="G505" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H505" t="n">
+        <v>13.02727</v>
+      </c>
+      <c r="I505" t="n">
+        <v>32.88208</v>
+      </c>
+      <c r="J505" t="n">
+        <v>16.482347</v>
+      </c>
+      <c r="K505" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L505" t="n">
+        <v>20.51644</v>
+      </c>
+      <c r="M505" t="n">
+        <v>0.03041169895678093</v>
+      </c>
+      <c r="N505" t="n">
+        <v>0.06067096684053651</v>
+      </c>
+      <c r="O505" t="n">
+        <v>0.0473799991607666</v>
+      </c>
+      <c r="P505" t="n">
+        <v>0.01329096767976991</v>
       </c>
     </row>
   </sheetData>
@@ -29282,12 +29804,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-20 15:50:35</t>
+          <t>2026-08-21 15:46:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -29301,51 +29823,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>338.2</v>
+        <v>341.75</v>
       </c>
       <c r="F2" t="n">
-        <v>4136164130816</v>
+        <v>4179580420096</v>
       </c>
       <c r="G2" t="n">
         <v>19.92</v>
       </c>
       <c r="H2" t="n">
-        <v>14.81022</v>
+        <v>14.81101</v>
       </c>
       <c r="I2" t="n">
-        <v>16.977913</v>
+        <v>17.156124</v>
       </c>
       <c r="J2" t="n">
-        <v>22.835583</v>
+        <v>23.07405</v>
       </c>
       <c r="K2" t="n">
         <v>0.93</v>
       </c>
       <c r="L2" t="n">
-        <v>9.276698</v>
+        <v>9.374072999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05890005913660556</v>
+        <v>0.05828822238478421</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04379130691898285</v>
+        <v>0.04333872713972202</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0473799991607666</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003168694072838436</v>
+        <v>-0.004041272021044581</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-20 15:50:35</t>
+          <t>2026-08-21 15:46:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -29359,51 +29881,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>481.15</v>
+        <v>483.24</v>
       </c>
       <c r="F3" t="n">
-        <v>3572801208320</v>
+        <v>3588320657408</v>
       </c>
       <c r="G3" t="n">
-        <v>17.97</v>
+        <v>17.95</v>
       </c>
       <c r="H3" t="n">
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>26.77518</v>
+        <v>26.921446</v>
       </c>
       <c r="J3" t="n">
-        <v>20.41082</v>
+        <v>20.49948</v>
       </c>
       <c r="K3" t="n">
         <v>1.57</v>
       </c>
       <c r="L3" t="n">
-        <v>10.76667</v>
+        <v>10.813438</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03734802036786865</v>
+        <v>0.03714510388212896</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04899361945339292</v>
+        <v>0.04878172336727092</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0473799991607666</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002033618461571629</v>
+        <v>0.001401724206504321</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-20 15:50:35</t>
+          <t>2026-08-21 15:46:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -29417,51 +29939,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>545.83</v>
+        <v>549.9</v>
       </c>
       <c r="F4" t="n">
-        <v>1390505361408</v>
+        <v>1400873680896</v>
       </c>
       <c r="G4" t="n">
-        <v>26.54</v>
+        <v>26.53</v>
       </c>
       <c r="H4" t="n">
         <v>34.70468</v>
       </c>
       <c r="I4" t="n">
-        <v>20.566315</v>
+        <v>20.727478</v>
       </c>
       <c r="J4" t="n">
-        <v>15.72785</v>
+        <v>15.845125</v>
       </c>
       <c r="K4" t="n">
         <v>0.82</v>
       </c>
       <c r="L4" t="n">
-        <v>6.0921082</v>
+        <v>6.137534</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04862319769891724</v>
+        <v>0.04824513547917804</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06358148141362696</v>
+        <v>0.0631108928896163</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0473799991607666</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01662148042180567</v>
+        <v>0.0157308937288497</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-20 15:50:35</t>
+          <t>2026-08-21 15:46:52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -29475,51 +29997,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>260.11</v>
+        <v>258.63</v>
       </c>
       <c r="F5" t="n">
-        <v>2805627879424</v>
+        <v>2789664358400</v>
       </c>
       <c r="G5" t="n">
-        <v>12.44</v>
+        <v>12.43</v>
       </c>
       <c r="H5" t="n">
-        <v>10.37777</v>
+        <v>10.39051</v>
       </c>
       <c r="I5" t="n">
-        <v>20.909164</v>
+        <v>20.80692</v>
       </c>
       <c r="J5" t="n">
-        <v>25.06415</v>
+        <v>24.890984</v>
       </c>
       <c r="K5" t="n">
         <v>1.42</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6169913</v>
+        <v>3.5964112</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0478259198031602</v>
+        <v>0.04806093647295364</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03989762023759179</v>
+        <v>0.04017519235974172</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0473799991607666</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007062380754229498</v>
+        <v>-0.007204806801024879</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-20 15:50:35</t>
+          <t>2026-08-21 15:46:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -29533,51 +30055,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>311.3</v>
+        <v>309.35</v>
       </c>
       <c r="F6" t="n">
-        <v>4543167856640</v>
+        <v>4514709504000</v>
       </c>
       <c r="G6" t="n">
-        <v>8.710000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>9.539300000000001</v>
+        <v>9.53851</v>
       </c>
       <c r="I6" t="n">
-        <v>35.74053</v>
+        <v>35.475918</v>
       </c>
       <c r="J6" t="n">
-        <v>32.63342</v>
+        <v>32.43169</v>
       </c>
       <c r="K6" t="n">
         <v>2.55</v>
       </c>
       <c r="L6" t="n">
-        <v>9.732100000000001</v>
+        <v>9.671137999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.027979441053646</v>
+        <v>0.02818813641506384</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03064343077417283</v>
+        <v>0.03083403911427186</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0473799991607666</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01631657021764846</v>
+        <v>-0.01654596004649474</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-20 15:50:35</t>
+          <t>2026-08-21 15:46:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -29591,51 +30113,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>216.85</v>
+        <v>214.72</v>
       </c>
       <c r="F7" t="n">
-        <v>5252323999744</v>
+        <v>5200733011968</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
       </c>
       <c r="H7" t="n">
-        <v>12.99922</v>
+        <v>13.02727</v>
       </c>
       <c r="I7" t="n">
-        <v>33.20827</v>
+        <v>32.88208</v>
       </c>
       <c r="J7" t="n">
-        <v>16.68177</v>
+        <v>16.482347</v>
       </c>
       <c r="K7" t="n">
         <v>0.6</v>
       </c>
       <c r="L7" t="n">
-        <v>20.719963</v>
+        <v>20.51644</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03011298132349551</v>
+        <v>0.03041169895678093</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05994567673507032</v>
+        <v>0.06067096684053651</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0473799991607666</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01298567574324903</v>
+        <v>0.01329096767976991</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-20 15:50:35</t>
+          <t>2026-08-21 15:46:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -29649,51 +30171,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>469.455</v>
+        <v>473.25</v>
       </c>
       <c r="F8" t="n">
-        <v>766373527552</v>
+        <v>772568776704</v>
       </c>
       <c r="G8" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="H8" t="n">
-        <v>15.4961</v>
+        <v>15.48597</v>
       </c>
       <c r="I8" t="n">
-        <v>119.75893</v>
+        <v>120.11421</v>
       </c>
       <c r="J8" t="n">
-        <v>30.29504</v>
+        <v>30.559921</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>18.554012</v>
+        <v>18.704</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008350108104078133</v>
+        <v>0.00832540940306392</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03300870157949112</v>
+        <v>0.03272259904912837</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0473799991607666</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01395129941233017</v>
+        <v>-0.01465740011163823</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-20 15:50:35</t>
+          <t>2026-08-21 15:46:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -29707,51 +30229,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>364.03</v>
+        <v>368.45</v>
       </c>
       <c r="F9" t="n">
-        <v>1731901915136</v>
+        <v>1752930451456</v>
       </c>
       <c r="G9" t="n">
-        <v>6.02</v>
+        <v>6.01</v>
       </c>
       <c r="H9" t="n">
-        <v>19.53226</v>
+        <v>19.50413</v>
       </c>
       <c r="I9" t="n">
-        <v>60.4701</v>
+        <v>61.306156</v>
       </c>
       <c r="J9" t="n">
-        <v>18.637371</v>
+        <v>18.890873</v>
       </c>
       <c r="K9" t="n">
         <v>0.41</v>
       </c>
       <c r="L9" t="n">
-        <v>22.949738</v>
+        <v>23.22839</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01653709859077548</v>
+        <v>0.01631157551906636</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05365563277751834</v>
+        <v>0.05293562220111277</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0473799991607666</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006695631785697057</v>
+        <v>0.005555623040346173</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-20 15:50:35</t>
+          <t>2026-08-21 15:46:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -29765,40 +30287,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>80.14</v>
+        <v>79.59</v>
       </c>
       <c r="F10" t="n">
-        <v>333698105344</v>
+        <v>331407949824</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.82319</v>
+        <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>25.201258</v>
+        <v>25.0283</v>
       </c>
       <c r="J10" t="n">
-        <v>20.961554</v>
+        <v>20.830116</v>
       </c>
       <c r="K10" t="n">
         <v>1.8</v>
       </c>
       <c r="L10" t="n">
-        <v>6.898756</v>
+        <v>6.85141</v>
       </c>
       <c r="M10" t="n">
-        <v>0.039680559021712</v>
+        <v>0.03995476818695816</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04770638881956576</v>
+        <v>0.04800741299158186</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.0473799991607666</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0007463878277444713</v>
+        <v>0.0006274138308152571</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P505"/>
+  <dimension ref="A1:P514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29229,16 +29229,16 @@
         <v>9.671137999999999</v>
       </c>
       <c r="M497" t="n">
-        <v>0.02818813641506384</v>
+        <v>0.0281881364150638</v>
       </c>
       <c r="N497" t="n">
-        <v>0.03083403911427186</v>
+        <v>0.0308340391142718</v>
       </c>
       <c r="O497" t="n">
         <v>0.0473799991607666</v>
       </c>
       <c r="P497" t="n">
-        <v>-0.01654596004649474</v>
+        <v>-0.0165459600464947</v>
       </c>
     </row>
     <row r="498">
@@ -29287,16 +29287,16 @@
         <v>18.704</v>
       </c>
       <c r="M498" t="n">
-        <v>0.00832540940306392</v>
+        <v>0.008325409403063901</v>
       </c>
       <c r="N498" t="n">
-        <v>0.03272259904912837</v>
+        <v>0.0327225990491283</v>
       </c>
       <c r="O498" t="n">
         <v>0.0473799991607666</v>
       </c>
       <c r="P498" t="n">
-        <v>-0.01465740011163823</v>
+        <v>-0.0146574001116382</v>
       </c>
     </row>
     <row r="499">
@@ -29345,16 +29345,16 @@
         <v>3.5964112</v>
       </c>
       <c r="M499" t="n">
-        <v>0.04806093647295364</v>
+        <v>0.0480609364729536</v>
       </c>
       <c r="N499" t="n">
-        <v>0.04017519235974172</v>
+        <v>0.0401751923597417</v>
       </c>
       <c r="O499" t="n">
         <v>0.0473799991607666</v>
       </c>
       <c r="P499" t="n">
-        <v>-0.007204806801024879</v>
+        <v>-0.0072048068010248</v>
       </c>
     </row>
     <row r="500">
@@ -29403,16 +29403,16 @@
         <v>23.22839</v>
       </c>
       <c r="M500" t="n">
-        <v>0.01631157551906636</v>
+        <v>0.0163115755190663</v>
       </c>
       <c r="N500" t="n">
-        <v>0.05293562220111277</v>
+        <v>0.0529356222011127</v>
       </c>
       <c r="O500" t="n">
         <v>0.0473799991607666</v>
       </c>
       <c r="P500" t="n">
-        <v>0.005555623040346173</v>
+        <v>0.0055556230403461</v>
       </c>
     </row>
     <row r="501">
@@ -29461,16 +29461,16 @@
         <v>9.374072999999999</v>
       </c>
       <c r="M501" t="n">
-        <v>0.05828822238478421</v>
+        <v>0.0582882223847842</v>
       </c>
       <c r="N501" t="n">
-        <v>0.04333872713972202</v>
+        <v>0.043338727139722</v>
       </c>
       <c r="O501" t="n">
         <v>0.0473799991607666</v>
       </c>
       <c r="P501" t="n">
-        <v>-0.004041272021044581</v>
+        <v>-0.0040412720210445</v>
       </c>
     </row>
     <row r="502">
@@ -29519,7 +29519,7 @@
         <v>6.137534</v>
       </c>
       <c r="M502" t="n">
-        <v>0.04824513547917804</v>
+        <v>0.048245135479178</v>
       </c>
       <c r="N502" t="n">
         <v>0.0631108928896163</v>
@@ -29577,16 +29577,16 @@
         <v>10.813438</v>
       </c>
       <c r="M503" t="n">
-        <v>0.03714510388212896</v>
+        <v>0.0371451038821289</v>
       </c>
       <c r="N503" t="n">
-        <v>0.04878172336727092</v>
+        <v>0.0487817233672709</v>
       </c>
       <c r="O503" t="n">
         <v>0.0473799991607666</v>
       </c>
       <c r="P503" t="n">
-        <v>0.001401724206504321</v>
+        <v>0.0014017242065043</v>
       </c>
     </row>
     <row r="504">
@@ -29635,16 +29635,16 @@
         <v>6.85141</v>
       </c>
       <c r="M504" t="n">
-        <v>0.03995476818695816</v>
+        <v>0.0399547681869581</v>
       </c>
       <c r="N504" t="n">
-        <v>0.04800741299158186</v>
+        <v>0.0480074129915818</v>
       </c>
       <c r="O504" t="n">
         <v>0.0473799991607666</v>
       </c>
       <c r="P504" t="n">
-        <v>0.0006274138308152571</v>
+        <v>0.0006274138308152</v>
       </c>
     </row>
     <row r="505">
@@ -29693,16 +29693,538 @@
         <v>20.51644</v>
       </c>
       <c r="M505" t="n">
-        <v>0.03041169895678093</v>
+        <v>0.0304116989567809</v>
       </c>
       <c r="N505" t="n">
-        <v>0.06067096684053651</v>
+        <v>0.0606709668405365</v>
       </c>
       <c r="O505" t="n">
         <v>0.0473799991607666</v>
       </c>
       <c r="P505" t="n">
-        <v>0.01329096767976991</v>
+        <v>0.0132909676797699</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:49:29</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>310.34</v>
+      </c>
+      <c r="F506" t="n">
+        <v>4529157832704</v>
+      </c>
+      <c r="G506" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H506" t="n">
+        <v>9.53851</v>
+      </c>
+      <c r="I506" t="n">
+        <v>35.589447</v>
+      </c>
+      <c r="J506" t="n">
+        <v>32.535477</v>
+      </c>
+      <c r="K506" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L506" t="n">
+        <v>9.702088</v>
+      </c>
+      <c r="M506" t="n">
+        <v>0.02809821486112007</v>
+      </c>
+      <c r="N506" t="n">
+        <v>0.03073567699941999</v>
+      </c>
+      <c r="O506" t="n">
+        <v>0.04703999996185303</v>
+      </c>
+      <c r="P506" t="n">
+        <v>-0.01630432296243303</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:49:29</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>456.745</v>
+      </c>
+      <c r="F507" t="n">
+        <v>745624764416</v>
+      </c>
+      <c r="G507" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H507" t="n">
+        <v>15.48597</v>
+      </c>
+      <c r="I507" t="n">
+        <v>116.2201</v>
+      </c>
+      <c r="J507" t="n">
+        <v>29.494118</v>
+      </c>
+      <c r="K507" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L507" t="n">
+        <v>18.051682</v>
+      </c>
+      <c r="M507" t="n">
+        <v>0.008604363485095622</v>
+      </c>
+      <c r="N507" t="n">
+        <v>0.03390506737895325</v>
+      </c>
+      <c r="O507" t="n">
+        <v>0.04703999996185303</v>
+      </c>
+      <c r="P507" t="n">
+        <v>-0.01313493258289978</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:49:29</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>262.07</v>
+      </c>
+      <c r="F508" t="n">
+        <v>2826769268736</v>
+      </c>
+      <c r="G508" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="H508" t="n">
+        <v>10.39051</v>
+      </c>
+      <c r="I508" t="n">
+        <v>21.066721</v>
+      </c>
+      <c r="J508" t="n">
+        <v>25.222055</v>
+      </c>
+      <c r="K508" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L508" t="n">
+        <v>3.6442466</v>
+      </c>
+      <c r="M508" t="n">
+        <v>0.04746823367802495</v>
+      </c>
+      <c r="N508" t="n">
+        <v>0.03964784217957035</v>
+      </c>
+      <c r="O508" t="n">
+        <v>0.04703999996185303</v>
+      </c>
+      <c r="P508" t="n">
+        <v>-0.00739215778228268</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:49:29</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>358.76</v>
+      </c>
+      <c r="F509" t="n">
+        <v>1706829545472</v>
+      </c>
+      <c r="G509" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H509" t="n">
+        <v>19.50413</v>
+      </c>
+      <c r="I509" t="n">
+        <v>59.693844</v>
+      </c>
+      <c r="J509" t="n">
+        <v>18.394054</v>
+      </c>
+      <c r="K509" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L509" t="n">
+        <v>22.617498</v>
+      </c>
+      <c r="M509" t="n">
+        <v>0.01675214628163675</v>
+      </c>
+      <c r="N509" t="n">
+        <v>0.05436539748020961</v>
+      </c>
+      <c r="O509" t="n">
+        <v>0.04703999996185303</v>
+      </c>
+      <c r="P509" t="n">
+        <v>0.007325397518356584</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:49:29</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>344.59</v>
+      </c>
+      <c r="F510" t="n">
+        <v>4214313189376</v>
+      </c>
+      <c r="G510" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H510" t="n">
+        <v>14.81101</v>
+      </c>
+      <c r="I510" t="n">
+        <v>17.298695</v>
+      </c>
+      <c r="J510" t="n">
+        <v>23.265799</v>
+      </c>
+      <c r="K510" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L510" t="n">
+        <v>9.451973000000001</v>
+      </c>
+      <c r="M510" t="n">
+        <v>0.05780782959459068</v>
+      </c>
+      <c r="N510" t="n">
+        <v>0.04298154328332221</v>
+      </c>
+      <c r="O510" t="n">
+        <v>0.04703999996185303</v>
+      </c>
+      <c r="P510" t="n">
+        <v>-0.004058456678530817</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:49:29</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>559.02</v>
+      </c>
+      <c r="F511" t="n">
+        <v>1424106979328</v>
+      </c>
+      <c r="G511" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="H511" t="n">
+        <v>34.70468</v>
+      </c>
+      <c r="I511" t="n">
+        <v>21.047441</v>
+      </c>
+      <c r="J511" t="n">
+        <v>16.107914</v>
+      </c>
+      <c r="K511" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L511" t="n">
+        <v>6.239324</v>
+      </c>
+      <c r="M511" t="n">
+        <v>0.04751171693320454</v>
+      </c>
+      <c r="N511" t="n">
+        <v>0.0620812851060785</v>
+      </c>
+      <c r="O511" t="n">
+        <v>0.04703999996185303</v>
+      </c>
+      <c r="P511" t="n">
+        <v>0.01504128514422547</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:49:29</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>487.31</v>
+      </c>
+      <c r="F512" t="n">
+        <v>3618542714880</v>
+      </c>
+      <c r="G512" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="H512" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I512" t="n">
+        <v>27.17847</v>
+      </c>
+      <c r="J512" t="n">
+        <v>20.672134</v>
+      </c>
+      <c r="K512" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L512" t="n">
+        <v>10.904512</v>
+      </c>
+      <c r="M512" t="n">
+        <v>0.03679382733783423</v>
+      </c>
+      <c r="N512" t="n">
+        <v>0.04837429972707312</v>
+      </c>
+      <c r="O512" t="n">
+        <v>0.04703999996185303</v>
+      </c>
+      <c r="P512" t="n">
+        <v>0.001334299765220093</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:49:29</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>80.01000000000001</v>
+      </c>
+      <c r="F513" t="n">
+        <v>333156810752</v>
+      </c>
+      <c r="G513" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H513" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I513" t="n">
+        <v>25.160378</v>
+      </c>
+      <c r="J513" t="n">
+        <v>20.940039</v>
+      </c>
+      <c r="K513" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="L513" t="n">
+        <v>6.887565</v>
+      </c>
+      <c r="M513" t="n">
+        <v>0.03974503187101612</v>
+      </c>
+      <c r="N513" t="n">
+        <v>0.04775540557430321</v>
+      </c>
+      <c r="O513" t="n">
+        <v>0.04703999996185303</v>
+      </c>
+      <c r="P513" t="n">
+        <v>0.0007154056124501831</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:49:29</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>208.48</v>
+      </c>
+      <c r="F514" t="n">
+        <v>5049593888768</v>
+      </c>
+      <c r="G514" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H514" t="n">
+        <v>13.041</v>
+      </c>
+      <c r="I514" t="n">
+        <v>31.92649</v>
+      </c>
+      <c r="J514" t="n">
+        <v>15.986504</v>
+      </c>
+      <c r="K514" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L514" t="n">
+        <v>19.92021</v>
+      </c>
+      <c r="M514" t="n">
+        <v>0.03132194934765925</v>
+      </c>
+      <c r="N514" t="n">
+        <v>0.06255276285495012</v>
+      </c>
+      <c r="O514" t="n">
+        <v>0.04703999996185303</v>
+      </c>
+      <c r="P514" t="n">
+        <v>0.0155127628930971</v>
       </c>
     </row>
   </sheetData>
@@ -29804,12 +30326,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 15:46:52</t>
+          <t>2026-08-24 15:49:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -29823,10 +30345,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>341.75</v>
+        <v>344.59</v>
       </c>
       <c r="F2" t="n">
-        <v>4179580420096</v>
+        <v>4214313189376</v>
       </c>
       <c r="G2" t="n">
         <v>19.92</v>
@@ -29835,39 +30357,39 @@
         <v>14.81101</v>
       </c>
       <c r="I2" t="n">
-        <v>17.156124</v>
+        <v>17.298695</v>
       </c>
       <c r="J2" t="n">
-        <v>23.07405</v>
+        <v>23.265799</v>
       </c>
       <c r="K2" t="n">
         <v>0.93</v>
       </c>
       <c r="L2" t="n">
-        <v>9.374072999999999</v>
+        <v>9.451973000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05828822238478421</v>
+        <v>0.05780782959459068</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04333872713972202</v>
+        <v>0.04298154328332221</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0473799991607666</v>
+        <v>0.04703999996185303</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.004041272021044581</v>
+        <v>-0.004058456678530817</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 15:46:52</t>
+          <t>2026-08-24 15:49:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -29881,51 +30403,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>483.24</v>
+        <v>487.31</v>
       </c>
       <c r="F3" t="n">
-        <v>3588320657408</v>
+        <v>3618542714880</v>
       </c>
       <c r="G3" t="n">
-        <v>17.95</v>
+        <v>17.93</v>
       </c>
       <c r="H3" t="n">
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>26.921446</v>
+        <v>27.17847</v>
       </c>
       <c r="J3" t="n">
-        <v>20.49948</v>
+        <v>20.672134</v>
       </c>
       <c r="K3" t="n">
         <v>1.57</v>
       </c>
       <c r="L3" t="n">
-        <v>10.813438</v>
+        <v>10.904512</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03714510388212896</v>
+        <v>0.03679382733783423</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04878172336727092</v>
+        <v>0.04837429972707312</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0473799991607666</v>
+        <v>0.04703999996185303</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001401724206504321</v>
+        <v>0.001334299765220093</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:46:52</t>
+          <t>2026-08-24 15:49:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -29939,51 +30461,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>549.9</v>
+        <v>559.02</v>
       </c>
       <c r="F4" t="n">
-        <v>1400873680896</v>
+        <v>1424106979328</v>
       </c>
       <c r="G4" t="n">
-        <v>26.53</v>
+        <v>26.56</v>
       </c>
       <c r="H4" t="n">
         <v>34.70468</v>
       </c>
       <c r="I4" t="n">
-        <v>20.727478</v>
+        <v>21.047441</v>
       </c>
       <c r="J4" t="n">
-        <v>15.845125</v>
+        <v>16.107914</v>
       </c>
       <c r="K4" t="n">
         <v>0.82</v>
       </c>
       <c r="L4" t="n">
-        <v>6.137534</v>
+        <v>6.239324</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04824513547917804</v>
+        <v>0.04751171693320454</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0631108928896163</v>
+        <v>0.0620812851060785</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0473799991607666</v>
+        <v>0.04703999996185303</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0157308937288497</v>
+        <v>0.01504128514422547</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 15:46:52</t>
+          <t>2026-08-24 15:49:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -29997,51 +30519,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>258.63</v>
+        <v>262.07</v>
       </c>
       <c r="F5" t="n">
-        <v>2789664358400</v>
+        <v>2826769268736</v>
       </c>
       <c r="G5" t="n">
-        <v>12.43</v>
+        <v>12.44</v>
       </c>
       <c r="H5" t="n">
         <v>10.39051</v>
       </c>
       <c r="I5" t="n">
-        <v>20.80692</v>
+        <v>21.066721</v>
       </c>
       <c r="J5" t="n">
-        <v>24.890984</v>
+        <v>25.222055</v>
       </c>
       <c r="K5" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5964112</v>
+        <v>3.6442466</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04806093647295364</v>
+        <v>0.04746823367802495</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04017519235974172</v>
+        <v>0.03964784217957035</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0473799991607666</v>
+        <v>0.04703999996185303</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007204806801024879</v>
+        <v>-0.00739215778228268</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 15:46:52</t>
+          <t>2026-08-24 15:49:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -30055,10 +30577,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>309.35</v>
+        <v>310.34</v>
       </c>
       <c r="F6" t="n">
-        <v>4514709504000</v>
+        <v>4529157832704</v>
       </c>
       <c r="G6" t="n">
         <v>8.720000000000001</v>
@@ -30067,39 +30589,39 @@
         <v>9.53851</v>
       </c>
       <c r="I6" t="n">
-        <v>35.475918</v>
+        <v>35.589447</v>
       </c>
       <c r="J6" t="n">
-        <v>32.43169</v>
+        <v>32.535477</v>
       </c>
       <c r="K6" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="L6" t="n">
-        <v>9.671137999999999</v>
+        <v>9.702088</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02818813641506384</v>
+        <v>0.02809821486112007</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03083403911427186</v>
+        <v>0.03073567699941999</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0473799991607666</v>
+        <v>0.04703999996185303</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01654596004649474</v>
+        <v>-0.01630432296243303</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 15:46:52</t>
+          <t>2026-08-24 15:49:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -30113,51 +30635,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>214.72</v>
+        <v>208.48</v>
       </c>
       <c r="F7" t="n">
-        <v>5200733011968</v>
+        <v>5049593888768</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
       </c>
       <c r="H7" t="n">
-        <v>13.02727</v>
+        <v>13.041</v>
       </c>
       <c r="I7" t="n">
-        <v>32.88208</v>
+        <v>31.92649</v>
       </c>
       <c r="J7" t="n">
-        <v>16.482347</v>
+        <v>15.986504</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="L7" t="n">
-        <v>20.51644</v>
+        <v>19.92021</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03041169895678093</v>
+        <v>0.03132194934765925</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06067096684053651</v>
+        <v>0.06255276285495012</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0473799991607666</v>
+        <v>0.04703999996185303</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01329096767976991</v>
+        <v>0.0155127628930971</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 15:46:52</t>
+          <t>2026-08-24 15:49:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -30171,51 +30693,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>473.25</v>
+        <v>456.745</v>
       </c>
       <c r="F8" t="n">
-        <v>772568776704</v>
+        <v>745624764416</v>
       </c>
       <c r="G8" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="H8" t="n">
         <v>15.48597</v>
       </c>
       <c r="I8" t="n">
-        <v>120.11421</v>
+        <v>116.2201</v>
       </c>
       <c r="J8" t="n">
-        <v>30.559921</v>
+        <v>29.494118</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="L8" t="n">
-        <v>18.704</v>
+        <v>18.051682</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00832540940306392</v>
+        <v>0.008604363485095622</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03272259904912837</v>
+        <v>0.03390506737895325</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0473799991607666</v>
+        <v>0.04703999996185303</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01465740011163823</v>
+        <v>-0.01313493258289978</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 15:46:52</t>
+          <t>2026-08-24 15:49:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -30229,10 +30751,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>368.45</v>
+        <v>358.76</v>
       </c>
       <c r="F9" t="n">
-        <v>1752930451456</v>
+        <v>1706829545472</v>
       </c>
       <c r="G9" t="n">
         <v>6.01</v>
@@ -30241,39 +30763,39 @@
         <v>19.50413</v>
       </c>
       <c r="I9" t="n">
-        <v>61.306156</v>
+        <v>59.693844</v>
       </c>
       <c r="J9" t="n">
-        <v>18.890873</v>
+        <v>18.394054</v>
       </c>
       <c r="K9" t="n">
         <v>0.41</v>
       </c>
       <c r="L9" t="n">
-        <v>23.22839</v>
+        <v>22.617498</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01631157551906636</v>
+        <v>0.01675214628163675</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05293562220111277</v>
+        <v>0.05436539748020961</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0473799991607666</v>
+        <v>0.04703999996185303</v>
       </c>
       <c r="P9" t="n">
-        <v>0.005555623040346173</v>
+        <v>0.007325397518356584</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 15:46:52</t>
+          <t>2026-08-24 15:49:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -30287,10 +30809,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>79.59</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>331407949824</v>
+        <v>333156810752</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -30299,28 +30821,28 @@
         <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>25.0283</v>
+        <v>25.160378</v>
       </c>
       <c r="J10" t="n">
-        <v>20.830116</v>
+        <v>20.940039</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="L10" t="n">
-        <v>6.85141</v>
+        <v>6.887565</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03995476818695816</v>
+        <v>0.03974503187101612</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04800741299158186</v>
+        <v>0.04775540557430321</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0473799991607666</v>
+        <v>0.04703999996185303</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0006274138308152571</v>
+        <v>0.0007154056124501831</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P514"/>
+  <dimension ref="A1:P523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29751,16 +29751,16 @@
         <v>9.702088</v>
       </c>
       <c r="M506" t="n">
-        <v>0.02809821486112007</v>
+        <v>0.02809821486112</v>
       </c>
       <c r="N506" t="n">
-        <v>0.03073567699941999</v>
+        <v>0.0307356769994199</v>
       </c>
       <c r="O506" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.047039999961853</v>
       </c>
       <c r="P506" t="n">
-        <v>-0.01630432296243303</v>
+        <v>-0.016304322962433</v>
       </c>
     </row>
     <row r="507">
@@ -29809,16 +29809,16 @@
         <v>18.051682</v>
       </c>
       <c r="M507" t="n">
-        <v>0.008604363485095622</v>
+        <v>0.008604363485095599</v>
       </c>
       <c r="N507" t="n">
-        <v>0.03390506737895325</v>
+        <v>0.0339050673789532</v>
       </c>
       <c r="O507" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.047039999961853</v>
       </c>
       <c r="P507" t="n">
-        <v>-0.01313493258289978</v>
+        <v>-0.0131349325828997</v>
       </c>
     </row>
     <row r="508">
@@ -29867,16 +29867,16 @@
         <v>3.6442466</v>
       </c>
       <c r="M508" t="n">
-        <v>0.04746823367802495</v>
+        <v>0.0474682336780249</v>
       </c>
       <c r="N508" t="n">
-        <v>0.03964784217957035</v>
+        <v>0.0396478421795703</v>
       </c>
       <c r="O508" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.047039999961853</v>
       </c>
       <c r="P508" t="n">
-        <v>-0.00739215778228268</v>
+        <v>-0.0073921577822826</v>
       </c>
     </row>
     <row r="509">
@@ -29925,16 +29925,16 @@
         <v>22.617498</v>
       </c>
       <c r="M509" t="n">
-        <v>0.01675214628163675</v>
+        <v>0.0167521462816367</v>
       </c>
       <c r="N509" t="n">
-        <v>0.05436539748020961</v>
+        <v>0.0543653974802096</v>
       </c>
       <c r="O509" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.047039999961853</v>
       </c>
       <c r="P509" t="n">
-        <v>0.007325397518356584</v>
+        <v>0.0073253975183565</v>
       </c>
     </row>
     <row r="510">
@@ -29983,16 +29983,16 @@
         <v>9.451973000000001</v>
       </c>
       <c r="M510" t="n">
-        <v>0.05780782959459068</v>
+        <v>0.0578078295945906</v>
       </c>
       <c r="N510" t="n">
-        <v>0.04298154328332221</v>
+        <v>0.0429815432833222</v>
       </c>
       <c r="O510" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.047039999961853</v>
       </c>
       <c r="P510" t="n">
-        <v>-0.004058456678530817</v>
+        <v>-0.0040584566785308</v>
       </c>
     </row>
     <row r="511">
@@ -30041,16 +30041,16 @@
         <v>6.239324</v>
       </c>
       <c r="M511" t="n">
-        <v>0.04751171693320454</v>
+        <v>0.0475117169332045</v>
       </c>
       <c r="N511" t="n">
         <v>0.0620812851060785</v>
       </c>
       <c r="O511" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.047039999961853</v>
       </c>
       <c r="P511" t="n">
-        <v>0.01504128514422547</v>
+        <v>0.0150412851442254</v>
       </c>
     </row>
     <row r="512">
@@ -30099,16 +30099,16 @@
         <v>10.904512</v>
       </c>
       <c r="M512" t="n">
-        <v>0.03679382733783423</v>
+        <v>0.0367938273378342</v>
       </c>
       <c r="N512" t="n">
-        <v>0.04837429972707312</v>
+        <v>0.0483742997270731</v>
       </c>
       <c r="O512" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.047039999961853</v>
       </c>
       <c r="P512" t="n">
-        <v>0.001334299765220093</v>
+        <v>0.00133429976522</v>
       </c>
     </row>
     <row r="513">
@@ -30157,16 +30157,16 @@
         <v>6.887565</v>
       </c>
       <c r="M513" t="n">
-        <v>0.03974503187101612</v>
+        <v>0.0397450318710161</v>
       </c>
       <c r="N513" t="n">
-        <v>0.04775540557430321</v>
+        <v>0.0477554055743032</v>
       </c>
       <c r="O513" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.047039999961853</v>
       </c>
       <c r="P513" t="n">
-        <v>0.0007154056124501831</v>
+        <v>0.0007154056124501</v>
       </c>
     </row>
     <row r="514">
@@ -30215,16 +30215,538 @@
         <v>19.92021</v>
       </c>
       <c r="M514" t="n">
-        <v>0.03132194934765925</v>
+        <v>0.0313219493476592</v>
       </c>
       <c r="N514" t="n">
-        <v>0.06255276285495012</v>
+        <v>0.06255276285495009</v>
       </c>
       <c r="O514" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.047039999961853</v>
       </c>
       <c r="P514" t="n">
-        <v>0.0155127628930971</v>
+        <v>0.015512762893097</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:51:02</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>309.9</v>
+      </c>
+      <c r="F515" t="n">
+        <v>4522736353280</v>
+      </c>
+      <c r="G515" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H515" t="n">
+        <v>9.53851</v>
+      </c>
+      <c r="I515" t="n">
+        <v>35.53899</v>
+      </c>
+      <c r="J515" t="n">
+        <v>32.48935</v>
+      </c>
+      <c r="K515" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L515" t="n">
+        <v>9.688333</v>
+      </c>
+      <c r="M515" t="n">
+        <v>0.02813810906744111</v>
+      </c>
+      <c r="N515" t="n">
+        <v>0.03077931590835754</v>
+      </c>
+      <c r="O515" t="n">
+        <v>0.04638999938964844</v>
+      </c>
+      <c r="P515" t="n">
+        <v>-0.0156106834812909</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:51:02</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>479.18</v>
+      </c>
+      <c r="F516" t="n">
+        <v>782249361408</v>
+      </c>
+      <c r="G516" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H516" t="n">
+        <v>15.48597</v>
+      </c>
+      <c r="I516" t="n">
+        <v>121.92875</v>
+      </c>
+      <c r="J516" t="n">
+        <v>30.942848</v>
+      </c>
+      <c r="K516" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L516" t="n">
+        <v>18.93837</v>
+      </c>
+      <c r="M516" t="n">
+        <v>0.008201510914478901</v>
+      </c>
+      <c r="N516" t="n">
+        <v>0.03231764681330607</v>
+      </c>
+      <c r="O516" t="n">
+        <v>0.04638999938964844</v>
+      </c>
+      <c r="P516" t="n">
+        <v>-0.01407235257634237</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:51:02</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>261.06</v>
+      </c>
+      <c r="F517" t="n">
+        <v>2815874826240</v>
+      </c>
+      <c r="G517" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="H517" t="n">
+        <v>10.39051</v>
+      </c>
+      <c r="I517" t="n">
+        <v>21.019323</v>
+      </c>
+      <c r="J517" t="n">
+        <v>25.12485</v>
+      </c>
+      <c r="K517" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L517" t="n">
+        <v>3.6302016</v>
+      </c>
+      <c r="M517" t="n">
+        <v>0.04757527005286141</v>
+      </c>
+      <c r="N517" t="n">
+        <v>0.0398012334329273</v>
+      </c>
+      <c r="O517" t="n">
+        <v>0.04638999938964844</v>
+      </c>
+      <c r="P517" t="n">
+        <v>-0.006588765956721143</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:51:02</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>356.74</v>
+      </c>
+      <c r="F518" t="n">
+        <v>1697219084288</v>
+      </c>
+      <c r="G518" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="H518" t="n">
+        <v>19.49103</v>
+      </c>
+      <c r="I518" t="n">
+        <v>59.16086</v>
+      </c>
+      <c r="J518" t="n">
+        <v>18.302778</v>
+      </c>
+      <c r="K518" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L518" t="n">
+        <v>22.490149</v>
+      </c>
+      <c r="M518" t="n">
+        <v>0.01690306665919157</v>
+      </c>
+      <c r="N518" t="n">
+        <v>0.05463651398777821</v>
+      </c>
+      <c r="O518" t="n">
+        <v>0.04638999938964844</v>
+      </c>
+      <c r="P518" t="n">
+        <v>0.008246514598129771</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:51:02</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>343.34</v>
+      </c>
+      <c r="F519" t="n">
+        <v>4199025999872</v>
+      </c>
+      <c r="G519" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H519" t="n">
+        <v>14.81101</v>
+      </c>
+      <c r="I519" t="n">
+        <v>17.235943</v>
+      </c>
+      <c r="J519" t="n">
+        <v>23.181402</v>
+      </c>
+      <c r="K519" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L519" t="n">
+        <v>9.417686</v>
+      </c>
+      <c r="M519" t="n">
+        <v>0.05801829090697269</v>
+      </c>
+      <c r="N519" t="n">
+        <v>0.04313802644608843</v>
+      </c>
+      <c r="O519" t="n">
+        <v>0.04638999938964844</v>
+      </c>
+      <c r="P519" t="n">
+        <v>-0.003251972943560014</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:51:02</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>570.05</v>
+      </c>
+      <c r="F520" t="n">
+        <v>1452205801472</v>
+      </c>
+      <c r="G520" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="H520" t="n">
+        <v>34.70468</v>
+      </c>
+      <c r="I520" t="n">
+        <v>21.47081</v>
+      </c>
+      <c r="J520" t="n">
+        <v>16.425737</v>
+      </c>
+      <c r="K520" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L520" t="n">
+        <v>6.362431</v>
+      </c>
+      <c r="M520" t="n">
+        <v>0.04657486185422332</v>
+      </c>
+      <c r="N520" t="n">
+        <v>0.06088006315235506</v>
+      </c>
+      <c r="O520" t="n">
+        <v>0.04638999938964844</v>
+      </c>
+      <c r="P520" t="n">
+        <v>0.01449006376270662</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:51:02</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>491.71</v>
+      </c>
+      <c r="F521" t="n">
+        <v>3651215032320</v>
+      </c>
+      <c r="G521" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="H521" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I521" t="n">
+        <v>27.42387</v>
+      </c>
+      <c r="J521" t="n">
+        <v>20.858786</v>
+      </c>
+      <c r="K521" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L521" t="n">
+        <v>11.002971</v>
+      </c>
+      <c r="M521" t="n">
+        <v>0.03646458278253442</v>
+      </c>
+      <c r="N521" t="n">
+        <v>0.047941428891013</v>
+      </c>
+      <c r="O521" t="n">
+        <v>0.04638999938964844</v>
+      </c>
+      <c r="P521" t="n">
+        <v>0.001551429501364561</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:51:02</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="F522" t="n">
+        <v>342400761856</v>
+      </c>
+      <c r="G522" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H522" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I522" t="n">
+        <v>25.858492</v>
+      </c>
+      <c r="J522" t="n">
+        <v>21.521051</v>
+      </c>
+      <c r="K522" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="L522" t="n">
+        <v>7.0786715</v>
+      </c>
+      <c r="M522" t="n">
+        <v>0.03867201751185698</v>
+      </c>
+      <c r="N522" t="n">
+        <v>0.04646613158214763</v>
+      </c>
+      <c r="O522" t="n">
+        <v>0.04638999938964844</v>
+      </c>
+      <c r="P522" t="n">
+        <v>7.613219249918979e-05</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:51:02</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>213.05</v>
+      </c>
+      <c r="F523" t="n">
+        <v>5160284192768</v>
+      </c>
+      <c r="G523" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="H523" t="n">
+        <v>13.041</v>
+      </c>
+      <c r="I523" t="n">
+        <v>32.62634</v>
+      </c>
+      <c r="J523" t="n">
+        <v>16.336937</v>
+      </c>
+      <c r="K523" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L523" t="n">
+        <v>20.356873</v>
+      </c>
+      <c r="M523" t="n">
+        <v>0.03065008214034264</v>
+      </c>
+      <c r="N523" t="n">
+        <v>0.06121098333724478</v>
+      </c>
+      <c r="O523" t="n">
+        <v>0.04638999938964844</v>
+      </c>
+      <c r="P523" t="n">
+        <v>0.01482098394759634</v>
       </c>
     </row>
   </sheetData>
@@ -30326,12 +30848,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 15:49:29</t>
+          <t>2026-08-25 15:51:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -30345,10 +30867,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>344.59</v>
+        <v>343.34</v>
       </c>
       <c r="F2" t="n">
-        <v>4214313189376</v>
+        <v>4199025999872</v>
       </c>
       <c r="G2" t="n">
         <v>19.92</v>
@@ -30357,39 +30879,39 @@
         <v>14.81101</v>
       </c>
       <c r="I2" t="n">
-        <v>17.298695</v>
+        <v>17.235943</v>
       </c>
       <c r="J2" t="n">
-        <v>23.265799</v>
+        <v>23.181402</v>
       </c>
       <c r="K2" t="n">
         <v>0.93</v>
       </c>
       <c r="L2" t="n">
-        <v>9.451973000000001</v>
+        <v>9.417686</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05780782959459068</v>
+        <v>0.05801829090697269</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04298154328332221</v>
+        <v>0.04313802644608843</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.04638999938964844</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.004058456678530817</v>
+        <v>-0.003251972943560014</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 15:49:29</t>
+          <t>2026-08-25 15:51:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -30403,10 +30925,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>487.31</v>
+        <v>491.71</v>
       </c>
       <c r="F3" t="n">
-        <v>3618542714880</v>
+        <v>3651215032320</v>
       </c>
       <c r="G3" t="n">
         <v>17.93</v>
@@ -30415,39 +30937,39 @@
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>27.17847</v>
+        <v>27.42387</v>
       </c>
       <c r="J3" t="n">
-        <v>20.672134</v>
+        <v>20.858786</v>
       </c>
       <c r="K3" t="n">
         <v>1.57</v>
       </c>
       <c r="L3" t="n">
-        <v>10.904512</v>
+        <v>11.002971</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03679382733783423</v>
+        <v>0.03646458278253442</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04837429972707312</v>
+        <v>0.047941428891013</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.04638999938964844</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001334299765220093</v>
+        <v>0.001551429501364561</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 15:49:29</t>
+          <t>2026-08-25 15:51:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -30461,51 +30983,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>559.02</v>
+        <v>570.05</v>
       </c>
       <c r="F4" t="n">
-        <v>1424106979328</v>
+        <v>1452205801472</v>
       </c>
       <c r="G4" t="n">
-        <v>26.56</v>
+        <v>26.55</v>
       </c>
       <c r="H4" t="n">
         <v>34.70468</v>
       </c>
       <c r="I4" t="n">
-        <v>21.047441</v>
+        <v>21.47081</v>
       </c>
       <c r="J4" t="n">
-        <v>16.107914</v>
+        <v>16.425737</v>
       </c>
       <c r="K4" t="n">
         <v>0.82</v>
       </c>
       <c r="L4" t="n">
-        <v>6.239324</v>
+        <v>6.362431</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04751171693320454</v>
+        <v>0.04657486185422332</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0620812851060785</v>
+        <v>0.06088006315235506</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.04638999938964844</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01504128514422547</v>
+        <v>0.01449006376270662</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 15:49:29</t>
+          <t>2026-08-25 15:51:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -30519,51 +31041,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>262.07</v>
+        <v>261.06</v>
       </c>
       <c r="F5" t="n">
-        <v>2826769268736</v>
+        <v>2815874826240</v>
       </c>
       <c r="G5" t="n">
-        <v>12.44</v>
+        <v>12.42</v>
       </c>
       <c r="H5" t="n">
         <v>10.39051</v>
       </c>
       <c r="I5" t="n">
-        <v>21.066721</v>
+        <v>21.019323</v>
       </c>
       <c r="J5" t="n">
-        <v>25.222055</v>
+        <v>25.12485</v>
       </c>
       <c r="K5" t="n">
         <v>1.38</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6442466</v>
+        <v>3.6302016</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04746823367802495</v>
+        <v>0.04757527005286141</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03964784217957035</v>
+        <v>0.0398012334329273</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.04638999938964844</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.00739215778228268</v>
+        <v>-0.006588765956721143</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:49:29</t>
+          <t>2026-08-25 15:51:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -30577,10 +31099,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>310.34</v>
+        <v>309.9</v>
       </c>
       <c r="F6" t="n">
-        <v>4529157832704</v>
+        <v>4522736353280</v>
       </c>
       <c r="G6" t="n">
         <v>8.720000000000001</v>
@@ -30589,39 +31111,39 @@
         <v>9.53851</v>
       </c>
       <c r="I6" t="n">
-        <v>35.589447</v>
+        <v>35.53899</v>
       </c>
       <c r="J6" t="n">
-        <v>32.535477</v>
+        <v>32.48935</v>
       </c>
       <c r="K6" t="n">
         <v>2.49</v>
       </c>
       <c r="L6" t="n">
-        <v>9.702088</v>
+        <v>9.688333</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02809821486112007</v>
+        <v>0.02813810906744111</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03073567699941999</v>
+        <v>0.03077931590835754</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.04638999938964844</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01630432296243303</v>
+        <v>-0.0156106834812909</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 15:49:29</t>
+          <t>2026-08-25 15:51:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -30635,10 +31157,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208.48</v>
+        <v>213.05</v>
       </c>
       <c r="F7" t="n">
-        <v>5049593888768</v>
+        <v>5160284192768</v>
       </c>
       <c r="G7" t="n">
         <v>6.53</v>
@@ -30647,39 +31169,39 @@
         <v>13.041</v>
       </c>
       <c r="I7" t="n">
-        <v>31.92649</v>
+        <v>32.62634</v>
       </c>
       <c r="J7" t="n">
-        <v>15.986504</v>
+        <v>16.336937</v>
       </c>
       <c r="K7" t="n">
         <v>0.59</v>
       </c>
       <c r="L7" t="n">
-        <v>19.92021</v>
+        <v>20.356873</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03132194934765925</v>
+        <v>0.03065008214034264</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06255276285495012</v>
+        <v>0.06121098333724478</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.04638999938964844</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0155127628930971</v>
+        <v>0.01482098394759634</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 15:49:29</t>
+          <t>2026-08-25 15:51:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -30693,10 +31215,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>456.745</v>
+        <v>479.18</v>
       </c>
       <c r="F8" t="n">
-        <v>745624764416</v>
+        <v>782249361408</v>
       </c>
       <c r="G8" t="n">
         <v>3.93</v>
@@ -30705,39 +31227,39 @@
         <v>15.48597</v>
       </c>
       <c r="I8" t="n">
-        <v>116.2201</v>
+        <v>121.92875</v>
       </c>
       <c r="J8" t="n">
-        <v>29.494118</v>
+        <v>30.942848</v>
       </c>
       <c r="K8" t="n">
         <v>1.01</v>
       </c>
       <c r="L8" t="n">
-        <v>18.051682</v>
+        <v>18.93837</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008604363485095622</v>
+        <v>0.008201510914478901</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03390506737895325</v>
+        <v>0.03231764681330607</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.04638999938964844</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01313493258289978</v>
+        <v>-0.01407235257634237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 15:49:29</t>
+          <t>2026-08-25 15:51:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -30751,51 +31273,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>358.76</v>
+        <v>356.74</v>
       </c>
       <c r="F9" t="n">
-        <v>1706829545472</v>
+        <v>1697219084288</v>
       </c>
       <c r="G9" t="n">
-        <v>6.01</v>
+        <v>6.03</v>
       </c>
       <c r="H9" t="n">
-        <v>19.50413</v>
+        <v>19.49103</v>
       </c>
       <c r="I9" t="n">
-        <v>59.693844</v>
+        <v>59.16086</v>
       </c>
       <c r="J9" t="n">
-        <v>18.394054</v>
+        <v>18.302778</v>
       </c>
       <c r="K9" t="n">
         <v>0.41</v>
       </c>
       <c r="L9" t="n">
-        <v>22.617498</v>
+        <v>22.490149</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01675214628163675</v>
+        <v>0.01690306665919157</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05436539748020961</v>
+        <v>0.05463651398777821</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.04638999938964844</v>
       </c>
       <c r="P9" t="n">
-        <v>0.007325397518356584</v>
+        <v>0.008246514598129771</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 15:49:29</t>
+          <t>2026-08-25 15:51:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -30809,10 +31331,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>80.01000000000001</v>
+        <v>82.23</v>
       </c>
       <c r="F10" t="n">
-        <v>333156810752</v>
+        <v>342400761856</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -30821,28 +31343,28 @@
         <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>25.160378</v>
+        <v>25.858492</v>
       </c>
       <c r="J10" t="n">
-        <v>20.940039</v>
+        <v>21.521051</v>
       </c>
       <c r="K10" t="n">
         <v>1.78</v>
       </c>
       <c r="L10" t="n">
-        <v>6.887565</v>
+        <v>7.0786715</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03974503187101612</v>
+        <v>0.03867201751185698</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04775540557430321</v>
+        <v>0.04646613158214763</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04703999996185303</v>
+        <v>0.04638999938964844</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0007154056124501831</v>
+        <v>7.613219249918979e-05</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P523"/>
+  <dimension ref="A1:P532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30273,13 +30273,13 @@
         <v>9.688333</v>
       </c>
       <c r="M515" t="n">
-        <v>0.02813810906744111</v>
+        <v>0.0281381090674411</v>
       </c>
       <c r="N515" t="n">
-        <v>0.03077931590835754</v>
+        <v>0.0307793159083575</v>
       </c>
       <c r="O515" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.0463899993896484</v>
       </c>
       <c r="P515" t="n">
         <v>-0.0156106834812909</v>
@@ -30331,16 +30331,16 @@
         <v>18.93837</v>
       </c>
       <c r="M516" t="n">
-        <v>0.008201510914478901</v>
+        <v>0.008201510914478899</v>
       </c>
       <c r="N516" t="n">
-        <v>0.03231764681330607</v>
+        <v>0.032317646813306</v>
       </c>
       <c r="O516" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.0463899993896484</v>
       </c>
       <c r="P516" t="n">
-        <v>-0.01407235257634237</v>
+        <v>-0.0140723525763423</v>
       </c>
     </row>
     <row r="517">
@@ -30389,16 +30389,16 @@
         <v>3.6302016</v>
       </c>
       <c r="M517" t="n">
-        <v>0.04757527005286141</v>
+        <v>0.0475752700528614</v>
       </c>
       <c r="N517" t="n">
         <v>0.0398012334329273</v>
       </c>
       <c r="O517" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.0463899993896484</v>
       </c>
       <c r="P517" t="n">
-        <v>-0.006588765956721143</v>
+        <v>-0.0065887659567211</v>
       </c>
     </row>
     <row r="518">
@@ -30447,16 +30447,16 @@
         <v>22.490149</v>
       </c>
       <c r="M518" t="n">
-        <v>0.01690306665919157</v>
+        <v>0.0169030666591915</v>
       </c>
       <c r="N518" t="n">
-        <v>0.05463651398777821</v>
+        <v>0.0546365139877782</v>
       </c>
       <c r="O518" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.0463899993896484</v>
       </c>
       <c r="P518" t="n">
-        <v>0.008246514598129771</v>
+        <v>0.0082465145981297</v>
       </c>
     </row>
     <row r="519">
@@ -30505,16 +30505,16 @@
         <v>9.417686</v>
       </c>
       <c r="M519" t="n">
-        <v>0.05801829090697269</v>
+        <v>0.0580182909069726</v>
       </c>
       <c r="N519" t="n">
-        <v>0.04313802644608843</v>
+        <v>0.0431380264460884</v>
       </c>
       <c r="O519" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.0463899993896484</v>
       </c>
       <c r="P519" t="n">
-        <v>-0.003251972943560014</v>
+        <v>-0.00325197294356</v>
       </c>
     </row>
     <row r="520">
@@ -30563,16 +30563,16 @@
         <v>6.362431</v>
       </c>
       <c r="M520" t="n">
-        <v>0.04657486185422332</v>
+        <v>0.0465748618542233</v>
       </c>
       <c r="N520" t="n">
-        <v>0.06088006315235506</v>
+        <v>0.060880063152355</v>
       </c>
       <c r="O520" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.0463899993896484</v>
       </c>
       <c r="P520" t="n">
-        <v>0.01449006376270662</v>
+        <v>0.0144900637627066</v>
       </c>
     </row>
     <row r="521">
@@ -30621,16 +30621,16 @@
         <v>11.002971</v>
       </c>
       <c r="M521" t="n">
-        <v>0.03646458278253442</v>
+        <v>0.0364645827825344</v>
       </c>
       <c r="N521" t="n">
         <v>0.047941428891013</v>
       </c>
       <c r="O521" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.0463899993896484</v>
       </c>
       <c r="P521" t="n">
-        <v>0.001551429501364561</v>
+        <v>0.0015514295013645</v>
       </c>
     </row>
     <row r="522">
@@ -30679,13 +30679,13 @@
         <v>7.0786715</v>
       </c>
       <c r="M522" t="n">
-        <v>0.03867201751185698</v>
+        <v>0.0386720175118569</v>
       </c>
       <c r="N522" t="n">
-        <v>0.04646613158214763</v>
+        <v>0.0464661315821476</v>
       </c>
       <c r="O522" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.0463899993896484</v>
       </c>
       <c r="P522" t="n">
         <v>7.613219249918979e-05</v>
@@ -30737,16 +30737,538 @@
         <v>20.356873</v>
       </c>
       <c r="M523" t="n">
-        <v>0.03065008214034264</v>
+        <v>0.0306500821403426</v>
       </c>
       <c r="N523" t="n">
-        <v>0.06121098333724478</v>
+        <v>0.0612109833372447</v>
       </c>
       <c r="O523" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.0463899993896484</v>
       </c>
       <c r="P523" t="n">
-        <v>0.01482098394759634</v>
+        <v>0.0148209839475963</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>2026-08-26 20:24:14</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>313.45</v>
+      </c>
+      <c r="F524" t="n">
+        <v>4574545969152</v>
+      </c>
+      <c r="G524" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H524" t="n">
+        <v>9.53851</v>
+      </c>
+      <c r="I524" t="n">
+        <v>35.987373</v>
+      </c>
+      <c r="J524" t="n">
+        <v>32.861526</v>
+      </c>
+      <c r="K524" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L524" t="n">
+        <v>9.799315999999999</v>
+      </c>
+      <c r="M524" t="n">
+        <v>0.02778752592119956</v>
+      </c>
+      <c r="N524" t="n">
+        <v>0.03043072260328601</v>
+      </c>
+      <c r="O524" t="n">
+        <v>0.04664000034332275</v>
+      </c>
+      <c r="P524" t="n">
+        <v>-0.01620927774003674</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>2026-08-26 20:24:14</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>480.93</v>
+      </c>
+      <c r="F525" t="n">
+        <v>785106206720</v>
+      </c>
+      <c r="G525" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="H525" t="n">
+        <v>15.47797</v>
+      </c>
+      <c r="I525" t="n">
+        <v>122.063446</v>
+      </c>
+      <c r="J525" t="n">
+        <v>31.071903</v>
+      </c>
+      <c r="K525" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L525" t="n">
+        <v>19.007534</v>
+      </c>
+      <c r="M525" t="n">
+        <v>0.008192460441228453</v>
+      </c>
+      <c r="N525" t="n">
+        <v>0.03218341546586821</v>
+      </c>
+      <c r="O525" t="n">
+        <v>0.04664000034332275</v>
+      </c>
+      <c r="P525" t="n">
+        <v>-0.01445658487745454</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>2026-08-26 20:24:14</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>260.28</v>
+      </c>
+      <c r="F526" t="n">
+        <v>2807461576704</v>
+      </c>
+      <c r="G526" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H526" t="n">
+        <v>10.39051</v>
+      </c>
+      <c r="I526" t="n">
+        <v>20.939661</v>
+      </c>
+      <c r="J526" t="n">
+        <v>25.049782</v>
+      </c>
+      <c r="K526" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L526" t="n">
+        <v>3.6193552</v>
+      </c>
+      <c r="M526" t="n">
+        <v>0.04775626248655294</v>
+      </c>
+      <c r="N526" t="n">
+        <v>0.03992050868295682</v>
+      </c>
+      <c r="O526" t="n">
+        <v>0.04664000034332275</v>
+      </c>
+      <c r="P526" t="n">
+        <v>-0.00671949166036593</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>2026-08-26 20:24:14</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>355.59</v>
+      </c>
+      <c r="F527" t="n">
+        <v>1691748007936</v>
+      </c>
+      <c r="G527" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="H527" t="n">
+        <v>19.49103</v>
+      </c>
+      <c r="I527" t="n">
+        <v>59.562817</v>
+      </c>
+      <c r="J527" t="n">
+        <v>18.243776</v>
+      </c>
+      <c r="K527" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L527" t="n">
+        <v>22.41765</v>
+      </c>
+      <c r="M527" t="n">
+        <v>0.01678899856576394</v>
+      </c>
+      <c r="N527" t="n">
+        <v>0.0548132118451025</v>
+      </c>
+      <c r="O527" t="n">
+        <v>0.04664000034332275</v>
+      </c>
+      <c r="P527" t="n">
+        <v>0.008173211501779749</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>2026-08-26 20:24:14</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>339.1</v>
+      </c>
+      <c r="F528" t="n">
+        <v>4147171033088</v>
+      </c>
+      <c r="G528" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="H528" t="n">
+        <v>14.81101</v>
+      </c>
+      <c r="I528" t="n">
+        <v>17.23945</v>
+      </c>
+      <c r="J528" t="n">
+        <v>22.89513</v>
+      </c>
+      <c r="K528" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L528" t="n">
+        <v>9.301385</v>
+      </c>
+      <c r="M528" t="n">
+        <v>0.05800648776172221</v>
+      </c>
+      <c r="N528" t="n">
+        <v>0.04367741079327631</v>
+      </c>
+      <c r="O528" t="n">
+        <v>0.04664000034332275</v>
+      </c>
+      <c r="P528" t="n">
+        <v>-0.002962589550046441</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>2026-08-26 20:24:14</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>576.14</v>
+      </c>
+      <c r="F529" t="n">
+        <v>1467720269824</v>
+      </c>
+      <c r="G529" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="H529" t="n">
+        <v>34.83499</v>
+      </c>
+      <c r="I529" t="n">
+        <v>21.457727</v>
+      </c>
+      <c r="J529" t="n">
+        <v>16.539118</v>
+      </c>
+      <c r="K529" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L529" t="n">
+        <v>6.4304037</v>
+      </c>
+      <c r="M529" t="n">
+        <v>0.04660325615301836</v>
+      </c>
+      <c r="N529" t="n">
+        <v>0.06046271739507758</v>
+      </c>
+      <c r="O529" t="n">
+        <v>0.04664000034332275</v>
+      </c>
+      <c r="P529" t="n">
+        <v>0.01382271705175483</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>2026-08-26 20:24:14</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>496.37</v>
+      </c>
+      <c r="F530" t="n">
+        <v>3685818040320</v>
+      </c>
+      <c r="G530" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="H530" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I530" t="n">
+        <v>27.393486</v>
+      </c>
+      <c r="J530" t="n">
+        <v>21.056467</v>
+      </c>
+      <c r="K530" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L530" t="n">
+        <v>11.107247</v>
+      </c>
+      <c r="M530" t="n">
+        <v>0.03650502649233435</v>
+      </c>
+      <c r="N530" t="n">
+        <v>0.04749134718053066</v>
+      </c>
+      <c r="O530" t="n">
+        <v>0.04664000034332275</v>
+      </c>
+      <c r="P530" t="n">
+        <v>0.0008513468372079031</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>2026-08-26 20:24:14</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>81.45999999999999</v>
+      </c>
+      <c r="F531" t="n">
+        <v>339194511360</v>
+      </c>
+      <c r="G531" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H531" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I531" t="n">
+        <v>25.860317</v>
+      </c>
+      <c r="J531" t="n">
+        <v>21.319529</v>
+      </c>
+      <c r="K531" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="L531" t="n">
+        <v>7.012387</v>
+      </c>
+      <c r="M531" t="n">
+        <v>0.03866928553891481</v>
+      </c>
+      <c r="N531" t="n">
+        <v>0.04690535232015713</v>
+      </c>
+      <c r="O531" t="n">
+        <v>0.04664000034332275</v>
+      </c>
+      <c r="P531" t="n">
+        <v>0.0002653519768343812</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>2026-08-26 20:24:14</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>209.66</v>
+      </c>
+      <c r="F532" t="n">
+        <v>5078174924800</v>
+      </c>
+      <c r="G532" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="H532" t="n">
+        <v>13.12766</v>
+      </c>
+      <c r="I532" t="n">
+        <v>32.5559</v>
+      </c>
+      <c r="J532" t="n">
+        <v>15.970859</v>
+      </c>
+      <c r="K532" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L532" t="n">
+        <v>20.032959</v>
+      </c>
+      <c r="M532" t="n">
+        <v>0.03071639797767815</v>
+      </c>
+      <c r="N532" t="n">
+        <v>0.06261404178193265</v>
+      </c>
+      <c r="O532" t="n">
+        <v>0.04664000034332275</v>
+      </c>
+      <c r="P532" t="n">
+        <v>0.0159740414386099</v>
       </c>
     </row>
   </sheetData>
@@ -30848,12 +31370,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:02</t>
+          <t>2026-08-26 20:24:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -30867,51 +31389,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>343.34</v>
+        <v>339.1</v>
       </c>
       <c r="F2" t="n">
-        <v>4199025999872</v>
+        <v>4147171033088</v>
       </c>
       <c r="G2" t="n">
-        <v>19.92</v>
+        <v>19.67</v>
       </c>
       <c r="H2" t="n">
         <v>14.81101</v>
       </c>
       <c r="I2" t="n">
-        <v>17.235943</v>
+        <v>17.23945</v>
       </c>
       <c r="J2" t="n">
-        <v>23.181402</v>
+        <v>22.89513</v>
       </c>
       <c r="K2" t="n">
         <v>0.93</v>
       </c>
       <c r="L2" t="n">
-        <v>9.417686</v>
+        <v>9.301385</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05801829090697269</v>
+        <v>0.05800648776172221</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04313802644608843</v>
+        <v>0.04367741079327631</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.04664000034332275</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003251972943560014</v>
+        <v>-0.002962589550046441</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:02</t>
+          <t>2026-08-26 20:24:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -30925,51 +31447,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>491.71</v>
+        <v>496.37</v>
       </c>
       <c r="F3" t="n">
-        <v>3651215032320</v>
+        <v>3685818040320</v>
       </c>
       <c r="G3" t="n">
-        <v>17.93</v>
+        <v>18.12</v>
       </c>
       <c r="H3" t="n">
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>27.42387</v>
+        <v>27.393486</v>
       </c>
       <c r="J3" t="n">
-        <v>20.858786</v>
+        <v>21.056467</v>
       </c>
       <c r="K3" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="L3" t="n">
-        <v>11.002971</v>
+        <v>11.107247</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03646458278253442</v>
+        <v>0.03650502649233435</v>
       </c>
       <c r="N3" t="n">
-        <v>0.047941428891013</v>
+        <v>0.04749134718053066</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.04664000034332275</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001551429501364561</v>
+        <v>0.0008513468372079031</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:02</t>
+          <t>2026-08-26 20:24:14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -30983,51 +31505,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>570.05</v>
+        <v>576.14</v>
       </c>
       <c r="F4" t="n">
-        <v>1452205801472</v>
+        <v>1467720269824</v>
       </c>
       <c r="G4" t="n">
-        <v>26.55</v>
+        <v>26.85</v>
       </c>
       <c r="H4" t="n">
-        <v>34.70468</v>
+        <v>34.83499</v>
       </c>
       <c r="I4" t="n">
-        <v>21.47081</v>
+        <v>21.457727</v>
       </c>
       <c r="J4" t="n">
-        <v>16.425737</v>
+        <v>16.539118</v>
       </c>
       <c r="K4" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="L4" t="n">
-        <v>6.362431</v>
+        <v>6.4304037</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04657486185422332</v>
+        <v>0.04660325615301836</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06088006315235506</v>
+        <v>0.06046271739507758</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.04664000034332275</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01449006376270662</v>
+        <v>0.01382271705175483</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:02</t>
+          <t>2026-08-26 20:24:14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -31041,51 +31563,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>261.06</v>
+        <v>260.28</v>
       </c>
       <c r="F5" t="n">
-        <v>2815874826240</v>
+        <v>2807461576704</v>
       </c>
       <c r="G5" t="n">
-        <v>12.42</v>
+        <v>12.43</v>
       </c>
       <c r="H5" t="n">
         <v>10.39051</v>
       </c>
       <c r="I5" t="n">
-        <v>21.019323</v>
+        <v>20.939661</v>
       </c>
       <c r="J5" t="n">
-        <v>25.12485</v>
+        <v>25.049782</v>
       </c>
       <c r="K5" t="n">
         <v>1.38</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6302016</v>
+        <v>3.6193552</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04757527005286141</v>
+        <v>0.04775626248655294</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0398012334329273</v>
+        <v>0.03992050868295682</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.04664000034332275</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.006588765956721143</v>
+        <v>-0.00671949166036593</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:02</t>
+          <t>2026-08-26 20:24:14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -31099,51 +31621,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>309.9</v>
+        <v>313.45</v>
       </c>
       <c r="F6" t="n">
-        <v>4522736353280</v>
+        <v>4574545969152</v>
       </c>
       <c r="G6" t="n">
-        <v>8.720000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>9.53851</v>
       </c>
       <c r="I6" t="n">
-        <v>35.53899</v>
+        <v>35.987373</v>
       </c>
       <c r="J6" t="n">
-        <v>32.48935</v>
+        <v>32.861526</v>
       </c>
       <c r="K6" t="n">
         <v>2.49</v>
       </c>
       <c r="L6" t="n">
-        <v>9.688333</v>
+        <v>9.799315999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02813810906744111</v>
+        <v>0.02778752592119956</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03077931590835754</v>
+        <v>0.03043072260328601</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.04664000034332275</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0156106834812909</v>
+        <v>-0.01620927774003674</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:02</t>
+          <t>2026-08-26 20:24:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -31157,51 +31679,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>213.05</v>
+        <v>209.66</v>
       </c>
       <c r="F7" t="n">
-        <v>5160284192768</v>
+        <v>5078174924800</v>
       </c>
       <c r="G7" t="n">
-        <v>6.53</v>
+        <v>6.44</v>
       </c>
       <c r="H7" t="n">
-        <v>13.041</v>
+        <v>13.12766</v>
       </c>
       <c r="I7" t="n">
-        <v>32.62634</v>
+        <v>32.5559</v>
       </c>
       <c r="J7" t="n">
-        <v>16.336937</v>
+        <v>15.970859</v>
       </c>
       <c r="K7" t="n">
         <v>0.59</v>
       </c>
       <c r="L7" t="n">
-        <v>20.356873</v>
+        <v>20.032959</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03065008214034264</v>
+        <v>0.03071639797767815</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06121098333724478</v>
+        <v>0.06261404178193265</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.04664000034332275</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01482098394759634</v>
+        <v>0.0159740414386099</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:02</t>
+          <t>2026-08-26 20:24:14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -31215,51 +31737,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>479.18</v>
+        <v>480.93</v>
       </c>
       <c r="F8" t="n">
-        <v>782249361408</v>
+        <v>785106206720</v>
       </c>
       <c r="G8" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="H8" t="n">
-        <v>15.48597</v>
+        <v>15.47797</v>
       </c>
       <c r="I8" t="n">
-        <v>121.92875</v>
+        <v>122.063446</v>
       </c>
       <c r="J8" t="n">
-        <v>30.942848</v>
+        <v>31.071903</v>
       </c>
       <c r="K8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="L8" t="n">
-        <v>18.93837</v>
+        <v>19.007534</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008201510914478901</v>
+        <v>0.008192460441228453</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03231764681330607</v>
+        <v>0.03218341546586821</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.04664000034332275</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01407235257634237</v>
+        <v>-0.01445658487745454</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:02</t>
+          <t>2026-08-26 20:24:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -31273,51 +31795,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>356.74</v>
+        <v>355.59</v>
       </c>
       <c r="F9" t="n">
-        <v>1697219084288</v>
+        <v>1691748007936</v>
       </c>
       <c r="G9" t="n">
-        <v>6.03</v>
+        <v>5.97</v>
       </c>
       <c r="H9" t="n">
         <v>19.49103</v>
       </c>
       <c r="I9" t="n">
-        <v>59.16086</v>
+        <v>59.562817</v>
       </c>
       <c r="J9" t="n">
-        <v>18.302778</v>
+        <v>18.243776</v>
       </c>
       <c r="K9" t="n">
         <v>0.41</v>
       </c>
       <c r="L9" t="n">
-        <v>22.490149</v>
+        <v>22.41765</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01690306665919157</v>
+        <v>0.01678899856576394</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05463651398777821</v>
+        <v>0.0548132118451025</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.04664000034332275</v>
       </c>
       <c r="P9" t="n">
-        <v>0.008246514598129771</v>
+        <v>0.008173211501779749</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 15:51:02</t>
+          <t>2026-08-26 20:24:14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -31331,40 +31853,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>82.23</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>342400761856</v>
+        <v>339194511360</v>
       </c>
       <c r="G10" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="H10" t="n">
         <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>25.858492</v>
+        <v>25.860317</v>
       </c>
       <c r="J10" t="n">
-        <v>21.521051</v>
+        <v>21.319529</v>
       </c>
       <c r="K10" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="L10" t="n">
-        <v>7.0786715</v>
+        <v>7.012387</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03867201751185698</v>
+        <v>0.03866928553891481</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04646613158214763</v>
+        <v>0.04690535232015713</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04638999938964844</v>
+        <v>0.04664000034332275</v>
       </c>
       <c r="P10" t="n">
-        <v>7.613219249918979e-05</v>
+        <v>0.0002653519768343812</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P532"/>
+  <dimension ref="A1:P541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30795,16 +30795,16 @@
         <v>9.799315999999999</v>
       </c>
       <c r="M524" t="n">
-        <v>0.02778752592119956</v>
+        <v>0.0277875259211995</v>
       </c>
       <c r="N524" t="n">
-        <v>0.03043072260328601</v>
+        <v>0.030430722603286</v>
       </c>
       <c r="O524" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.0466400003433227</v>
       </c>
       <c r="P524" t="n">
-        <v>-0.01620927774003674</v>
+        <v>-0.0162092777400367</v>
       </c>
     </row>
     <row r="525">
@@ -30853,16 +30853,16 @@
         <v>19.007534</v>
       </c>
       <c r="M525" t="n">
-        <v>0.008192460441228453</v>
+        <v>0.0081924604412284</v>
       </c>
       <c r="N525" t="n">
-        <v>0.03218341546586821</v>
+        <v>0.0321834154658682</v>
       </c>
       <c r="O525" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.0466400003433227</v>
       </c>
       <c r="P525" t="n">
-        <v>-0.01445658487745454</v>
+        <v>-0.0144565848774545</v>
       </c>
     </row>
     <row r="526">
@@ -30911,16 +30911,16 @@
         <v>3.6193552</v>
       </c>
       <c r="M526" t="n">
-        <v>0.04775626248655294</v>
+        <v>0.0477562624865529</v>
       </c>
       <c r="N526" t="n">
-        <v>0.03992050868295682</v>
+        <v>0.0399205086829568</v>
       </c>
       <c r="O526" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.0466400003433227</v>
       </c>
       <c r="P526" t="n">
-        <v>-0.00671949166036593</v>
+        <v>-0.0067194916603659</v>
       </c>
     </row>
     <row r="527">
@@ -30969,16 +30969,16 @@
         <v>22.41765</v>
       </c>
       <c r="M527" t="n">
-        <v>0.01678899856576394</v>
+        <v>0.0167889985657639</v>
       </c>
       <c r="N527" t="n">
         <v>0.0548132118451025</v>
       </c>
       <c r="O527" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.0466400003433227</v>
       </c>
       <c r="P527" t="n">
-        <v>0.008173211501779749</v>
+        <v>0.008173211501779701</v>
       </c>
     </row>
     <row r="528">
@@ -31027,16 +31027,16 @@
         <v>9.301385</v>
       </c>
       <c r="M528" t="n">
-        <v>0.05800648776172221</v>
+        <v>0.0580064877617222</v>
       </c>
       <c r="N528" t="n">
-        <v>0.04367741079327631</v>
+        <v>0.0436774107932763</v>
       </c>
       <c r="O528" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.0466400003433227</v>
       </c>
       <c r="P528" t="n">
-        <v>-0.002962589550046441</v>
+        <v>-0.0029625895500464</v>
       </c>
     </row>
     <row r="529">
@@ -31085,16 +31085,16 @@
         <v>6.4304037</v>
       </c>
       <c r="M529" t="n">
-        <v>0.04660325615301836</v>
+        <v>0.0466032561530183</v>
       </c>
       <c r="N529" t="n">
-        <v>0.06046271739507758</v>
+        <v>0.0604627173950775</v>
       </c>
       <c r="O529" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.0466400003433227</v>
       </c>
       <c r="P529" t="n">
-        <v>0.01382271705175483</v>
+        <v>0.0138227170517548</v>
       </c>
     </row>
     <row r="530">
@@ -31143,16 +31143,16 @@
         <v>11.107247</v>
       </c>
       <c r="M530" t="n">
-        <v>0.03650502649233435</v>
+        <v>0.0365050264923343</v>
       </c>
       <c r="N530" t="n">
-        <v>0.04749134718053066</v>
+        <v>0.0474913471805306</v>
       </c>
       <c r="O530" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.0466400003433227</v>
       </c>
       <c r="P530" t="n">
-        <v>0.0008513468372079031</v>
+        <v>0.0008513468372079</v>
       </c>
     </row>
     <row r="531">
@@ -31201,16 +31201,16 @@
         <v>7.012387</v>
       </c>
       <c r="M531" t="n">
-        <v>0.03866928553891481</v>
+        <v>0.0386692855389148</v>
       </c>
       <c r="N531" t="n">
-        <v>0.04690535232015713</v>
+        <v>0.0469053523201571</v>
       </c>
       <c r="O531" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.0466400003433227</v>
       </c>
       <c r="P531" t="n">
-        <v>0.0002653519768343812</v>
+        <v>0.0002653519768343</v>
       </c>
     </row>
     <row r="532">
@@ -31259,16 +31259,538 @@
         <v>20.032959</v>
       </c>
       <c r="M532" t="n">
-        <v>0.03071639797767815</v>
+        <v>0.0307163979776781</v>
       </c>
       <c r="N532" t="n">
-        <v>0.06261404178193265</v>
+        <v>0.0626140417819326</v>
       </c>
       <c r="O532" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.0466400003433227</v>
       </c>
       <c r="P532" t="n">
         <v>0.0159740414386099</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>2026-08-27 23:11:54</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>314.58</v>
+      </c>
+      <c r="F533" t="n">
+        <v>4591036923904</v>
+      </c>
+      <c r="G533" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H533" t="n">
+        <v>9.53851</v>
+      </c>
+      <c r="I533" t="n">
+        <v>36.117104</v>
+      </c>
+      <c r="J533" t="n">
+        <v>32.979992</v>
+      </c>
+      <c r="K533" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L533" t="n">
+        <v>9.834641</v>
+      </c>
+      <c r="M533" t="n">
+        <v>0.027687710598258</v>
+      </c>
+      <c r="N533" t="n">
+        <v>0.03032141267722042</v>
+      </c>
+      <c r="O533" t="n">
+        <v>0.04671999931335449</v>
+      </c>
+      <c r="P533" t="n">
+        <v>-0.01639858663613407</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>2026-08-27 23:11:54</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>476.67</v>
+      </c>
+      <c r="F534" t="n">
+        <v>778151854080</v>
+      </c>
+      <c r="G534" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H534" t="n">
+        <v>15.45073</v>
+      </c>
+      <c r="I534" t="n">
+        <v>121.910484</v>
+      </c>
+      <c r="J534" t="n">
+        <v>30.85097</v>
+      </c>
+      <c r="K534" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L534" t="n">
+        <v>18.839167</v>
+      </c>
+      <c r="M534" t="n">
+        <v>0.008202739840980133</v>
+      </c>
+      <c r="N534" t="n">
+        <v>0.03241389221054398</v>
+      </c>
+      <c r="O534" t="n">
+        <v>0.04671999931335449</v>
+      </c>
+      <c r="P534" t="n">
+        <v>-0.01430610710281051</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>2026-08-27 23:11:54</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>256.26</v>
+      </c>
+      <c r="F535" t="n">
+        <v>2764100599808</v>
+      </c>
+      <c r="G535" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="H535" t="n">
+        <v>10.39051</v>
+      </c>
+      <c r="I535" t="n">
+        <v>20.919184</v>
+      </c>
+      <c r="J535" t="n">
+        <v>24.662891</v>
+      </c>
+      <c r="K535" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L535" t="n">
+        <v>3.5634546</v>
+      </c>
+      <c r="M535" t="n">
+        <v>0.0478030125653633</v>
+      </c>
+      <c r="N535" t="n">
+        <v>0.04054674939514556</v>
+      </c>
+      <c r="O535" t="n">
+        <v>0.04671999931335449</v>
+      </c>
+      <c r="P535" t="n">
+        <v>-0.006173249918208931</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>2026-08-27 23:11:54</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>371.54</v>
+      </c>
+      <c r="F536" t="n">
+        <v>1767631355904</v>
+      </c>
+      <c r="G536" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="H536" t="n">
+        <v>19.49997</v>
+      </c>
+      <c r="I536" t="n">
+        <v>59.16242</v>
+      </c>
+      <c r="J536" t="n">
+        <v>19.053364</v>
+      </c>
+      <c r="K536" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L536" t="n">
+        <v>23.423195</v>
+      </c>
+      <c r="M536" t="n">
+        <v>0.01690262152123594</v>
+      </c>
+      <c r="N536" t="n">
+        <v>0.05248417397857566</v>
+      </c>
+      <c r="O536" t="n">
+        <v>0.04671999931335449</v>
+      </c>
+      <c r="P536" t="n">
+        <v>0.005764174665221167</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>2026-08-27 23:11:54</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>337.71</v>
+      </c>
+      <c r="F537" t="n">
+        <v>4130171256832</v>
+      </c>
+      <c r="G537" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="H537" t="n">
+        <v>14.82767</v>
+      </c>
+      <c r="I537" t="n">
+        <v>17.00453</v>
+      </c>
+      <c r="J537" t="n">
+        <v>22.775661</v>
+      </c>
+      <c r="K537" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L537" t="n">
+        <v>9.263256999999999</v>
+      </c>
+      <c r="M537" t="n">
+        <v>0.05880785289153416</v>
+      </c>
+      <c r="N537" t="n">
+        <v>0.04390651742619407</v>
+      </c>
+      <c r="O537" t="n">
+        <v>0.04671999931335449</v>
+      </c>
+      <c r="P537" t="n">
+        <v>-0.002813481887160421</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>2026-08-27 23:11:54</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>571.1</v>
+      </c>
+      <c r="F538" t="n">
+        <v>1454880718848</v>
+      </c>
+      <c r="G538" t="n">
+        <v>26.33</v>
+      </c>
+      <c r="H538" t="n">
+        <v>34.83499</v>
+      </c>
+      <c r="I538" t="n">
+        <v>21.690086</v>
+      </c>
+      <c r="J538" t="n">
+        <v>16.394434</v>
+      </c>
+      <c r="K538" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L538" t="n">
+        <v>6.3741508</v>
+      </c>
+      <c r="M538" t="n">
+        <v>0.04610400980563824</v>
+      </c>
+      <c r="N538" t="n">
+        <v>0.06099630537559096</v>
+      </c>
+      <c r="O538" t="n">
+        <v>0.04671999931335449</v>
+      </c>
+      <c r="P538" t="n">
+        <v>0.01427630606223647</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>2026-08-27 23:11:54</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>505.06</v>
+      </c>
+      <c r="F539" t="n">
+        <v>3750346096640</v>
+      </c>
+      <c r="G539" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="H539" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I539" t="n">
+        <v>28.105732</v>
+      </c>
+      <c r="J539" t="n">
+        <v>21.425104</v>
+      </c>
+      <c r="K539" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L539" t="n">
+        <v>11.301703</v>
+      </c>
+      <c r="M539" t="n">
+        <v>0.03557993109729537</v>
+      </c>
+      <c r="N539" t="n">
+        <v>0.04667421692472182</v>
+      </c>
+      <c r="O539" t="n">
+        <v>0.04671999931335449</v>
+      </c>
+      <c r="P539" t="n">
+        <v>-4.578238863267581e-05</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2026-08-27 23:11:54</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>79.84</v>
+      </c>
+      <c r="F540" t="n">
+        <v>332448923648</v>
+      </c>
+      <c r="G540" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="H540" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I540" t="n">
+        <v>25.672026</v>
+      </c>
+      <c r="J540" t="n">
+        <v>20.895544</v>
+      </c>
+      <c r="K540" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="L540" t="n">
+        <v>6.8729305</v>
+      </c>
+      <c r="M540" t="n">
+        <v>0.03895290581162324</v>
+      </c>
+      <c r="N540" t="n">
+        <v>0.04785708917835671</v>
+      </c>
+      <c r="O540" t="n">
+        <v>0.04671999931335449</v>
+      </c>
+      <c r="P540" t="n">
+        <v>0.001137089865002217</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>2026-08-27 23:11:54</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>227.98</v>
+      </c>
+      <c r="F541" t="n">
+        <v>5505032912896</v>
+      </c>
+      <c r="G541" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="H541" t="n">
+        <v>14.52753</v>
+      </c>
+      <c r="I541" t="n">
+        <v>32.155148</v>
+      </c>
+      <c r="J541" t="n">
+        <v>15.692964</v>
+      </c>
+      <c r="K541" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L541" t="n">
+        <v>21.716877</v>
+      </c>
+      <c r="M541" t="n">
+        <v>0.031099219229757</v>
+      </c>
+      <c r="N541" t="n">
+        <v>0.06372282656373367</v>
+      </c>
+      <c r="O541" t="n">
+        <v>0.04671999931335449</v>
+      </c>
+      <c r="P541" t="n">
+        <v>0.01700282725037917</v>
       </c>
     </row>
   </sheetData>
@@ -31370,12 +31892,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 20:24:14</t>
+          <t>2026-08-27 23:11:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -31389,51 +31911,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>339.1</v>
+        <v>337.71</v>
       </c>
       <c r="F2" t="n">
-        <v>4147171033088</v>
+        <v>4130171256832</v>
       </c>
       <c r="G2" t="n">
-        <v>19.67</v>
+        <v>19.86</v>
       </c>
       <c r="H2" t="n">
-        <v>14.81101</v>
+        <v>14.82767</v>
       </c>
       <c r="I2" t="n">
-        <v>17.23945</v>
+        <v>17.00453</v>
       </c>
       <c r="J2" t="n">
-        <v>22.89513</v>
+        <v>22.775661</v>
       </c>
       <c r="K2" t="n">
         <v>0.93</v>
       </c>
       <c r="L2" t="n">
-        <v>9.301385</v>
+        <v>9.263256999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05800648776172221</v>
+        <v>0.05880785289153416</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04367741079327631</v>
+        <v>0.04390651742619407</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.04671999931335449</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.002962589550046441</v>
+        <v>-0.002813481887160421</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 20:24:14</t>
+          <t>2026-08-27 23:11:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -31447,51 +31969,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>496.37</v>
+        <v>505.06</v>
       </c>
       <c r="F3" t="n">
-        <v>3685818040320</v>
+        <v>3750346096640</v>
       </c>
       <c r="G3" t="n">
-        <v>18.12</v>
+        <v>17.97</v>
       </c>
       <c r="H3" t="n">
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>27.393486</v>
+        <v>28.105732</v>
       </c>
       <c r="J3" t="n">
-        <v>21.056467</v>
+        <v>21.425104</v>
       </c>
       <c r="K3" t="n">
         <v>1.6</v>
       </c>
       <c r="L3" t="n">
-        <v>11.107247</v>
+        <v>11.301703</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03650502649233435</v>
+        <v>0.03557993109729537</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04749134718053066</v>
+        <v>0.04667421692472182</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.04671999931335449</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008513468372079031</v>
+        <v>-4.578238863267581e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 20:24:14</t>
+          <t>2026-08-27 23:11:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -31505,51 +32027,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>576.14</v>
+        <v>571.1</v>
       </c>
       <c r="F4" t="n">
-        <v>1467720269824</v>
+        <v>1454880718848</v>
       </c>
       <c r="G4" t="n">
-        <v>26.85</v>
+        <v>26.33</v>
       </c>
       <c r="H4" t="n">
         <v>34.83499</v>
       </c>
       <c r="I4" t="n">
-        <v>21.457727</v>
+        <v>21.690086</v>
       </c>
       <c r="J4" t="n">
-        <v>16.539118</v>
+        <v>16.394434</v>
       </c>
       <c r="K4" t="n">
         <v>0.85</v>
       </c>
       <c r="L4" t="n">
-        <v>6.4304037</v>
+        <v>6.3741508</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04660325615301836</v>
+        <v>0.04610400980563824</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06046271739507758</v>
+        <v>0.06099630537559096</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.04671999931335449</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01382271705175483</v>
+        <v>0.01427630606223647</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 20:24:14</t>
+          <t>2026-08-27 23:11:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -31563,51 +32085,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>260.28</v>
+        <v>256.26</v>
       </c>
       <c r="F5" t="n">
-        <v>2807461576704</v>
+        <v>2764100599808</v>
       </c>
       <c r="G5" t="n">
-        <v>12.43</v>
+        <v>12.25</v>
       </c>
       <c r="H5" t="n">
         <v>10.39051</v>
       </c>
       <c r="I5" t="n">
-        <v>20.939661</v>
+        <v>20.919184</v>
       </c>
       <c r="J5" t="n">
-        <v>25.049782</v>
+        <v>24.662891</v>
       </c>
       <c r="K5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6193552</v>
+        <v>3.5634546</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04775626248655294</v>
+        <v>0.0478030125653633</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03992050868295682</v>
+        <v>0.04054674939514556</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.04671999931335449</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.00671949166036593</v>
+        <v>-0.006173249918208931</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 20:24:14</t>
+          <t>2026-08-27 23:11:54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -31621,10 +32143,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>313.45</v>
+        <v>314.58</v>
       </c>
       <c r="F6" t="n">
-        <v>4574545969152</v>
+        <v>4591036923904</v>
       </c>
       <c r="G6" t="n">
         <v>8.710000000000001</v>
@@ -31633,39 +32155,39 @@
         <v>9.53851</v>
       </c>
       <c r="I6" t="n">
-        <v>35.987373</v>
+        <v>36.117104</v>
       </c>
       <c r="J6" t="n">
-        <v>32.861526</v>
+        <v>32.979992</v>
       </c>
       <c r="K6" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="L6" t="n">
-        <v>9.799315999999999</v>
+        <v>9.834641</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02778752592119956</v>
+        <v>0.027687710598258</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03043072260328601</v>
+        <v>0.03032141267722042</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.04671999931335449</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01620927774003674</v>
+        <v>-0.01639858663613407</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 20:24:14</t>
+          <t>2026-08-27 23:11:54</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -31679,51 +32201,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>209.66</v>
+        <v>227.98</v>
       </c>
       <c r="F7" t="n">
-        <v>5078174924800</v>
+        <v>5505032912896</v>
       </c>
       <c r="G7" t="n">
-        <v>6.44</v>
+        <v>7.09</v>
       </c>
       <c r="H7" t="n">
-        <v>13.12766</v>
+        <v>14.52753</v>
       </c>
       <c r="I7" t="n">
-        <v>32.5559</v>
+        <v>32.155148</v>
       </c>
       <c r="J7" t="n">
-        <v>15.970859</v>
+        <v>15.692964</v>
       </c>
       <c r="K7" t="n">
         <v>0.59</v>
       </c>
       <c r="L7" t="n">
-        <v>20.032959</v>
+        <v>21.716877</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03071639797767815</v>
+        <v>0.031099219229757</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06261404178193265</v>
+        <v>0.06372282656373367</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.04671999931335449</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0159740414386099</v>
+        <v>0.01700282725037917</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 20:24:14</t>
+          <t>2026-08-27 23:11:54</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -31737,51 +32259,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>480.93</v>
+        <v>476.67</v>
       </c>
       <c r="F8" t="n">
-        <v>785106206720</v>
+        <v>778151854080</v>
       </c>
       <c r="G8" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="H8" t="n">
-        <v>15.47797</v>
+        <v>15.45073</v>
       </c>
       <c r="I8" t="n">
-        <v>122.063446</v>
+        <v>121.910484</v>
       </c>
       <c r="J8" t="n">
-        <v>31.071903</v>
+        <v>30.85097</v>
       </c>
       <c r="K8" t="n">
         <v>1.03</v>
       </c>
       <c r="L8" t="n">
-        <v>19.007534</v>
+        <v>18.839167</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008192460441228453</v>
+        <v>0.008202739840980133</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03218341546586821</v>
+        <v>0.03241389221054398</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.04671999931335449</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01445658487745454</v>
+        <v>-0.01430610710281051</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 20:24:14</t>
+          <t>2026-08-27 23:11:54</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -31795,51 +32317,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>355.59</v>
+        <v>371.54</v>
       </c>
       <c r="F9" t="n">
-        <v>1691748007936</v>
+        <v>1767631355904</v>
       </c>
       <c r="G9" t="n">
-        <v>5.97</v>
+        <v>6.28</v>
       </c>
       <c r="H9" t="n">
-        <v>19.49103</v>
+        <v>19.49997</v>
       </c>
       <c r="I9" t="n">
-        <v>59.562817</v>
+        <v>59.16242</v>
       </c>
       <c r="J9" t="n">
-        <v>18.243776</v>
+        <v>19.053364</v>
       </c>
       <c r="K9" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="L9" t="n">
-        <v>22.41765</v>
+        <v>23.423195</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01678899856576394</v>
+        <v>0.01690262152123594</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0548132118451025</v>
+        <v>0.05248417397857566</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.04671999931335449</v>
       </c>
       <c r="P9" t="n">
-        <v>0.008173211501779749</v>
+        <v>0.005764174665221167</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 20:24:14</t>
+          <t>2026-08-27 23:11:54</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -31853,40 +32375,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>81.45999999999999</v>
+        <v>79.84</v>
       </c>
       <c r="F10" t="n">
-        <v>339194511360</v>
+        <v>332448923648</v>
       </c>
       <c r="G10" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="H10" t="n">
         <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>25.860317</v>
+        <v>25.672026</v>
       </c>
       <c r="J10" t="n">
-        <v>21.319529</v>
+        <v>20.895544</v>
       </c>
       <c r="K10" t="n">
         <v>1.84</v>
       </c>
       <c r="L10" t="n">
-        <v>7.012387</v>
+        <v>6.8729305</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03866928553891481</v>
+        <v>0.03895290581162324</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04690535232015713</v>
+        <v>0.04785708917835671</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04664000034332275</v>
+        <v>0.04671999931335449</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0002653519768343812</v>
+        <v>0.001137089865002217</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P541"/>
+  <dimension ref="A1:P550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31320,13 +31320,13 @@
         <v>0.027687710598258</v>
       </c>
       <c r="N533" t="n">
-        <v>0.03032141267722042</v>
+        <v>0.0303214126772204</v>
       </c>
       <c r="O533" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.0467199993133544</v>
       </c>
       <c r="P533" t="n">
-        <v>-0.01639858663613407</v>
+        <v>-0.016398586636134</v>
       </c>
     </row>
     <row r="534">
@@ -31375,16 +31375,16 @@
         <v>18.839167</v>
       </c>
       <c r="M534" t="n">
-        <v>0.008202739840980133</v>
+        <v>0.0082027398409801</v>
       </c>
       <c r="N534" t="n">
-        <v>0.03241389221054398</v>
+        <v>0.0324138922105439</v>
       </c>
       <c r="O534" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.0467199993133544</v>
       </c>
       <c r="P534" t="n">
-        <v>-0.01430610710281051</v>
+        <v>-0.0143061071028105</v>
       </c>
     </row>
     <row r="535">
@@ -31436,13 +31436,13 @@
         <v>0.0478030125653633</v>
       </c>
       <c r="N535" t="n">
-        <v>0.04054674939514556</v>
+        <v>0.0405467493951455</v>
       </c>
       <c r="O535" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.0467199993133544</v>
       </c>
       <c r="P535" t="n">
-        <v>-0.006173249918208931</v>
+        <v>-0.0061732499182089</v>
       </c>
     </row>
     <row r="536">
@@ -31491,16 +31491,16 @@
         <v>23.423195</v>
       </c>
       <c r="M536" t="n">
-        <v>0.01690262152123594</v>
+        <v>0.0169026215212359</v>
       </c>
       <c r="N536" t="n">
-        <v>0.05248417397857566</v>
+        <v>0.0524841739785756</v>
       </c>
       <c r="O536" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.0467199993133544</v>
       </c>
       <c r="P536" t="n">
-        <v>0.005764174665221167</v>
+        <v>0.0057641746652211</v>
       </c>
     </row>
     <row r="537">
@@ -31549,16 +31549,16 @@
         <v>9.263256999999999</v>
       </c>
       <c r="M537" t="n">
-        <v>0.05880785289153416</v>
+        <v>0.0588078528915341</v>
       </c>
       <c r="N537" t="n">
-        <v>0.04390651742619407</v>
+        <v>0.043906517426194</v>
       </c>
       <c r="O537" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.0467199993133544</v>
       </c>
       <c r="P537" t="n">
-        <v>-0.002813481887160421</v>
+        <v>-0.0028134818871604</v>
       </c>
     </row>
     <row r="538">
@@ -31607,16 +31607,16 @@
         <v>6.3741508</v>
       </c>
       <c r="M538" t="n">
-        <v>0.04610400980563824</v>
+        <v>0.0461040098056382</v>
       </c>
       <c r="N538" t="n">
-        <v>0.06099630537559096</v>
+        <v>0.0609963053755909</v>
       </c>
       <c r="O538" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.0467199993133544</v>
       </c>
       <c r="P538" t="n">
-        <v>0.01427630606223647</v>
+        <v>0.0142763060622364</v>
       </c>
     </row>
     <row r="539">
@@ -31665,13 +31665,13 @@
         <v>11.301703</v>
       </c>
       <c r="M539" t="n">
-        <v>0.03557993109729537</v>
+        <v>0.0355799310972953</v>
       </c>
       <c r="N539" t="n">
-        <v>0.04667421692472182</v>
+        <v>0.0466742169247218</v>
       </c>
       <c r="O539" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.0467199993133544</v>
       </c>
       <c r="P539" t="n">
         <v>-4.578238863267581e-05</v>
@@ -31723,16 +31723,16 @@
         <v>6.8729305</v>
       </c>
       <c r="M540" t="n">
-        <v>0.03895290581162324</v>
+        <v>0.0389529058116232</v>
       </c>
       <c r="N540" t="n">
-        <v>0.04785708917835671</v>
+        <v>0.0478570891783567</v>
       </c>
       <c r="O540" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.0467199993133544</v>
       </c>
       <c r="P540" t="n">
-        <v>0.001137089865002217</v>
+        <v>0.0011370898650022</v>
       </c>
     </row>
     <row r="541">
@@ -31781,16 +31781,538 @@
         <v>21.716877</v>
       </c>
       <c r="M541" t="n">
-        <v>0.031099219229757</v>
+        <v>0.0310992192297569</v>
       </c>
       <c r="N541" t="n">
-        <v>0.06372282656373367</v>
+        <v>0.0637228265637336</v>
       </c>
       <c r="O541" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.0467199993133544</v>
       </c>
       <c r="P541" t="n">
-        <v>0.01700282725037917</v>
+        <v>0.0170028272503791</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:45:39</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>319.7</v>
+      </c>
+      <c r="F542" t="n">
+        <v>4665759498240</v>
+      </c>
+      <c r="G542" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H542" t="n">
+        <v>9.53851</v>
+      </c>
+      <c r="I542" t="n">
+        <v>36.704937</v>
+      </c>
+      <c r="J542" t="n">
+        <v>33.516766</v>
+      </c>
+      <c r="K542" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L542" t="n">
+        <v>9.994707999999999</v>
+      </c>
+      <c r="M542" t="n">
+        <v>0.0272442915233031</v>
+      </c>
+      <c r="N542" t="n">
+        <v>0.02983581482639975</v>
+      </c>
+      <c r="O542" t="n">
+        <v>0.04720000267028809</v>
+      </c>
+      <c r="P542" t="n">
+        <v>-0.01736418784388833</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:45:39</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>465.58</v>
+      </c>
+      <c r="F543" t="n">
+        <v>760047665152</v>
+      </c>
+      <c r="G543" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H543" t="n">
+        <v>15.45073</v>
+      </c>
+      <c r="I543" t="n">
+        <v>119.074165</v>
+      </c>
+      <c r="J543" t="n">
+        <v>30.133204</v>
+      </c>
+      <c r="K543" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L543" t="n">
+        <v>18.400862</v>
+      </c>
+      <c r="M543" t="n">
+        <v>0.008398127067313889</v>
+      </c>
+      <c r="N543" t="n">
+        <v>0.03318598307487435</v>
+      </c>
+      <c r="O543" t="n">
+        <v>0.04720000267028809</v>
+      </c>
+      <c r="P543" t="n">
+        <v>-0.01401401959541373</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:45:39</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>266.43</v>
+      </c>
+      <c r="F544" t="n">
+        <v>2873797378048</v>
+      </c>
+      <c r="G544" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H544" t="n">
+        <v>10.39051</v>
+      </c>
+      <c r="I544" t="n">
+        <v>21.434431</v>
+      </c>
+      <c r="J544" t="n">
+        <v>25.641668</v>
+      </c>
+      <c r="K544" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L544" t="n">
+        <v>3.7048748</v>
+      </c>
+      <c r="M544" t="n">
+        <v>0.04665390534099013</v>
+      </c>
+      <c r="N544" t="n">
+        <v>0.03899902413391886</v>
+      </c>
+      <c r="O544" t="n">
+        <v>0.04720000267028809</v>
+      </c>
+      <c r="P544" t="n">
+        <v>-0.008200978536369231</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:45:39</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>368.79</v>
+      </c>
+      <c r="F545" t="n">
+        <v>1754548011008</v>
+      </c>
+      <c r="G545" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H545" t="n">
+        <v>19.50742</v>
+      </c>
+      <c r="I545" t="n">
+        <v>61.2608</v>
+      </c>
+      <c r="J545" t="n">
+        <v>18.905115</v>
+      </c>
+      <c r="K545" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L545" t="n">
+        <v>23.249825</v>
+      </c>
+      <c r="M545" t="n">
+        <v>0.01632365302746821</v>
+      </c>
+      <c r="N545" t="n">
+        <v>0.05289574012310529</v>
+      </c>
+      <c r="O545" t="n">
+        <v>0.04720000267028809</v>
+      </c>
+      <c r="P545" t="n">
+        <v>0.0056957374528172</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:45:39</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>342.88</v>
+      </c>
+      <c r="F546" t="n">
+        <v>4193400127488</v>
+      </c>
+      <c r="G546" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H546" t="n">
+        <v>14.82767</v>
+      </c>
+      <c r="I546" t="n">
+        <v>17.212852</v>
+      </c>
+      <c r="J546" t="n">
+        <v>23.124334</v>
+      </c>
+      <c r="K546" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L546" t="n">
+        <v>9.405068</v>
+      </c>
+      <c r="M546" t="n">
+        <v>0.05809612692487168</v>
+      </c>
+      <c r="N546" t="n">
+        <v>0.0432444878674755</v>
+      </c>
+      <c r="O546" t="n">
+        <v>0.04720000267028809</v>
+      </c>
+      <c r="P546" t="n">
+        <v>-0.003955514802812587</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:45:39</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>578.02</v>
+      </c>
+      <c r="F547" t="n">
+        <v>1472509509632</v>
+      </c>
+      <c r="G547" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="H547" t="n">
+        <v>34.95966</v>
+      </c>
+      <c r="I547" t="n">
+        <v>21.762802</v>
+      </c>
+      <c r="J547" t="n">
+        <v>16.533915</v>
+      </c>
+      <c r="K547" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L547" t="n">
+        <v>6.451386</v>
+      </c>
+      <c r="M547" t="n">
+        <v>0.04594996712916508</v>
+      </c>
+      <c r="N547" t="n">
+        <v>0.06048174803640013</v>
+      </c>
+      <c r="O547" t="n">
+        <v>0.04720000267028809</v>
+      </c>
+      <c r="P547" t="n">
+        <v>0.01328174536611204</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:45:39</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>513.53</v>
+      </c>
+      <c r="F548" t="n">
+        <v>3813240733696</v>
+      </c>
+      <c r="G548" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="H548" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I548" t="n">
+        <v>28.640827</v>
+      </c>
+      <c r="J548" t="n">
+        <v>21.78441</v>
+      </c>
+      <c r="K548" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L548" t="n">
+        <v>11.491237</v>
+      </c>
+      <c r="M548" t="n">
+        <v>0.03491519482795553</v>
+      </c>
+      <c r="N548" t="n">
+        <v>0.04590438728019785</v>
+      </c>
+      <c r="O548" t="n">
+        <v>0.04720000267028809</v>
+      </c>
+      <c r="P548" t="n">
+        <v>-0.001295615390090238</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:45:39</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E549" t="n">
+        <v>81.72</v>
+      </c>
+      <c r="F549" t="n">
+        <v>340277133312</v>
+      </c>
+      <c r="G549" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H549" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I549" t="n">
+        <v>25.698112</v>
+      </c>
+      <c r="J549" t="n">
+        <v>21.387575</v>
+      </c>
+      <c r="K549" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="L549" t="n">
+        <v>7.0347686</v>
+      </c>
+      <c r="M549" t="n">
+        <v>0.03891336270190896</v>
+      </c>
+      <c r="N549" t="n">
+        <v>0.04675611845325502</v>
+      </c>
+      <c r="O549" t="n">
+        <v>0.04720000267028809</v>
+      </c>
+      <c r="P549" t="n">
+        <v>-0.0004438842170330706</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:45:39</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>217.55</v>
+      </c>
+      <c r="F550" t="n">
+        <v>5253179637760</v>
+      </c>
+      <c r="G550" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H550" t="n">
+        <v>15.1679</v>
+      </c>
+      <c r="I550" t="n">
+        <v>27.503162</v>
+      </c>
+      <c r="J550" t="n">
+        <v>14.34279</v>
+      </c>
+      <c r="K550" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L550" t="n">
+        <v>17.338943</v>
+      </c>
+      <c r="M550" t="n">
+        <v>0.03635945759595495</v>
+      </c>
+      <c r="N550" t="n">
+        <v>0.06972144334635716</v>
+      </c>
+      <c r="O550" t="n">
+        <v>0.04720000267028809</v>
+      </c>
+      <c r="P550" t="n">
+        <v>0.02252144067606907</v>
       </c>
     </row>
   </sheetData>
@@ -31892,12 +32414,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 23:11:54</t>
+          <t>2026-08-28 20:45:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -31911,51 +32433,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>337.71</v>
+        <v>342.88</v>
       </c>
       <c r="F2" t="n">
-        <v>4130171256832</v>
+        <v>4193400127488</v>
       </c>
       <c r="G2" t="n">
-        <v>19.86</v>
+        <v>19.92</v>
       </c>
       <c r="H2" t="n">
         <v>14.82767</v>
       </c>
       <c r="I2" t="n">
-        <v>17.00453</v>
+        <v>17.212852</v>
       </c>
       <c r="J2" t="n">
-        <v>22.775661</v>
+        <v>23.124334</v>
       </c>
       <c r="K2" t="n">
         <v>0.93</v>
       </c>
       <c r="L2" t="n">
-        <v>9.263256999999999</v>
+        <v>9.405068</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05880785289153416</v>
+        <v>0.05809612692487168</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04390651742619407</v>
+        <v>0.0432444878674755</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.04720000267028809</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.002813481887160421</v>
+        <v>-0.003955514802812587</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 23:11:54</t>
+          <t>2026-08-28 20:45:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -31969,51 +32491,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>505.06</v>
+        <v>513.53</v>
       </c>
       <c r="F3" t="n">
-        <v>3750346096640</v>
+        <v>3813240733696</v>
       </c>
       <c r="G3" t="n">
-        <v>17.97</v>
+        <v>17.93</v>
       </c>
       <c r="H3" t="n">
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>28.105732</v>
+        <v>28.640827</v>
       </c>
       <c r="J3" t="n">
-        <v>21.425104</v>
+        <v>21.78441</v>
       </c>
       <c r="K3" t="n">
         <v>1.6</v>
       </c>
       <c r="L3" t="n">
-        <v>11.301703</v>
+        <v>11.491237</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03557993109729537</v>
+        <v>0.03491519482795553</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04667421692472182</v>
+        <v>0.04590438728019785</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.04720000267028809</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.578238863267581e-05</v>
+        <v>-0.001295615390090238</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 23:11:54</t>
+          <t>2026-08-28 20:45:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -32027,51 +32549,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>571.1</v>
+        <v>578.02</v>
       </c>
       <c r="F4" t="n">
-        <v>1454880718848</v>
+        <v>1472509509632</v>
       </c>
       <c r="G4" t="n">
-        <v>26.33</v>
+        <v>26.56</v>
       </c>
       <c r="H4" t="n">
-        <v>34.83499</v>
+        <v>34.95966</v>
       </c>
       <c r="I4" t="n">
-        <v>21.690086</v>
+        <v>21.762802</v>
       </c>
       <c r="J4" t="n">
-        <v>16.394434</v>
+        <v>16.533915</v>
       </c>
       <c r="K4" t="n">
         <v>0.85</v>
       </c>
       <c r="L4" t="n">
-        <v>6.3741508</v>
+        <v>6.451386</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04610400980563824</v>
+        <v>0.04594996712916508</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06099630537559096</v>
+        <v>0.06048174803640013</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.04720000267028809</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01427630606223647</v>
+        <v>0.01328174536611204</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 23:11:54</t>
+          <t>2026-08-28 20:45:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -32085,51 +32607,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>256.26</v>
+        <v>266.43</v>
       </c>
       <c r="F5" t="n">
-        <v>2764100599808</v>
+        <v>2873797378048</v>
       </c>
       <c r="G5" t="n">
-        <v>12.25</v>
+        <v>12.43</v>
       </c>
       <c r="H5" t="n">
         <v>10.39051</v>
       </c>
       <c r="I5" t="n">
-        <v>20.919184</v>
+        <v>21.434431</v>
       </c>
       <c r="J5" t="n">
-        <v>24.662891</v>
+        <v>25.641668</v>
       </c>
       <c r="K5" t="n">
         <v>1.39</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5634546</v>
+        <v>3.7048748</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0478030125653633</v>
+        <v>0.04665390534099013</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04054674939514556</v>
+        <v>0.03899902413391886</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.04720000267028809</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.006173249918208931</v>
+        <v>-0.008200978536369231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 23:11:54</t>
+          <t>2026-08-28 20:45:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -32143,10 +32665,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>314.58</v>
+        <v>319.7</v>
       </c>
       <c r="F6" t="n">
-        <v>4591036923904</v>
+        <v>4665759498240</v>
       </c>
       <c r="G6" t="n">
         <v>8.710000000000001</v>
@@ -32155,39 +32677,39 @@
         <v>9.53851</v>
       </c>
       <c r="I6" t="n">
-        <v>36.117104</v>
+        <v>36.704937</v>
       </c>
       <c r="J6" t="n">
-        <v>32.979992</v>
+        <v>33.516766</v>
       </c>
       <c r="K6" t="n">
         <v>2.5</v>
       </c>
       <c r="L6" t="n">
-        <v>9.834641</v>
+        <v>9.994707999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.027687710598258</v>
+        <v>0.0272442915233031</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03032141267722042</v>
+        <v>0.02983581482639975</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.04720000267028809</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01639858663613407</v>
+        <v>-0.01736418784388833</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 23:11:54</t>
+          <t>2026-08-28 20:45:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -32201,51 +32723,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>227.98</v>
+        <v>217.55</v>
       </c>
       <c r="F7" t="n">
-        <v>5505032912896</v>
+        <v>5253179637760</v>
       </c>
       <c r="G7" t="n">
-        <v>7.09</v>
+        <v>7.91</v>
       </c>
       <c r="H7" t="n">
-        <v>14.52753</v>
+        <v>15.1679</v>
       </c>
       <c r="I7" t="n">
-        <v>32.155148</v>
+        <v>27.503162</v>
       </c>
       <c r="J7" t="n">
-        <v>15.692964</v>
+        <v>14.34279</v>
       </c>
       <c r="K7" t="n">
         <v>0.59</v>
       </c>
       <c r="L7" t="n">
-        <v>21.716877</v>
+        <v>17.338943</v>
       </c>
       <c r="M7" t="n">
-        <v>0.031099219229757</v>
+        <v>0.03635945759595495</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06372282656373367</v>
+        <v>0.06972144334635716</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.04720000267028809</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01700282725037917</v>
+        <v>0.02252144067606907</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 23:11:54</t>
+          <t>2026-08-28 20:45:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -32259,10 +32781,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>476.67</v>
+        <v>465.58</v>
       </c>
       <c r="F8" t="n">
-        <v>778151854080</v>
+        <v>760047665152</v>
       </c>
       <c r="G8" t="n">
         <v>3.91</v>
@@ -32271,39 +32793,39 @@
         <v>15.45073</v>
       </c>
       <c r="I8" t="n">
-        <v>121.910484</v>
+        <v>119.074165</v>
       </c>
       <c r="J8" t="n">
-        <v>30.85097</v>
+        <v>30.133204</v>
       </c>
       <c r="K8" t="n">
         <v>1.03</v>
       </c>
       <c r="L8" t="n">
-        <v>18.839167</v>
+        <v>18.400862</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008202739840980133</v>
+        <v>0.008398127067313889</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03241389221054398</v>
+        <v>0.03318598307487435</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.04720000267028809</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01430610710281051</v>
+        <v>-0.01401401959541373</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 23:11:54</t>
+          <t>2026-08-28 20:45:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -32317,51 +32839,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>371.54</v>
+        <v>368.79</v>
       </c>
       <c r="F9" t="n">
-        <v>1767631355904</v>
+        <v>1754548011008</v>
       </c>
       <c r="G9" t="n">
-        <v>6.28</v>
+        <v>6.02</v>
       </c>
       <c r="H9" t="n">
-        <v>19.49997</v>
+        <v>19.50742</v>
       </c>
       <c r="I9" t="n">
-        <v>59.16242</v>
+        <v>61.2608</v>
       </c>
       <c r="J9" t="n">
-        <v>19.053364</v>
+        <v>18.905115</v>
       </c>
       <c r="K9" t="n">
         <v>0.4</v>
       </c>
       <c r="L9" t="n">
-        <v>23.423195</v>
+        <v>23.249825</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01690262152123594</v>
+        <v>0.01632365302746821</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05248417397857566</v>
+        <v>0.05289574012310529</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.04720000267028809</v>
       </c>
       <c r="P9" t="n">
-        <v>0.005764174665221167</v>
+        <v>0.0056957374528172</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 23:11:54</t>
+          <t>2026-08-28 20:45:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -32375,40 +32897,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>79.84</v>
+        <v>81.72</v>
       </c>
       <c r="F10" t="n">
-        <v>332448923648</v>
+        <v>340277133312</v>
       </c>
       <c r="G10" t="n">
-        <v>3.11</v>
+        <v>3.18</v>
       </c>
       <c r="H10" t="n">
         <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>25.672026</v>
+        <v>25.698112</v>
       </c>
       <c r="J10" t="n">
-        <v>20.895544</v>
+        <v>21.387575</v>
       </c>
       <c r="K10" t="n">
         <v>1.84</v>
       </c>
       <c r="L10" t="n">
-        <v>6.8729305</v>
+        <v>7.0347686</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03895290581162324</v>
+        <v>0.03891336270190896</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04785708917835671</v>
+        <v>0.04675611845325502</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04671999931335449</v>
+        <v>0.04720000267028809</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001137089865002217</v>
+        <v>-0.0004438842170330706</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P550"/>
+  <dimension ref="A1:P559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31842,13 +31842,13 @@
         <v>0.0272442915233031</v>
       </c>
       <c r="N542" t="n">
-        <v>0.02983581482639975</v>
+        <v>0.0298358148263997</v>
       </c>
       <c r="O542" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.047200002670288</v>
       </c>
       <c r="P542" t="n">
-        <v>-0.01736418784388833</v>
+        <v>-0.0173641878438883</v>
       </c>
     </row>
     <row r="543">
@@ -31897,16 +31897,16 @@
         <v>18.400862</v>
       </c>
       <c r="M543" t="n">
-        <v>0.008398127067313889</v>
+        <v>0.0083981270673138</v>
       </c>
       <c r="N543" t="n">
-        <v>0.03318598307487435</v>
+        <v>0.0331859830748743</v>
       </c>
       <c r="O543" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.047200002670288</v>
       </c>
       <c r="P543" t="n">
-        <v>-0.01401401959541373</v>
+        <v>-0.0140140195954137</v>
       </c>
     </row>
     <row r="544">
@@ -31955,16 +31955,16 @@
         <v>3.7048748</v>
       </c>
       <c r="M544" t="n">
-        <v>0.04665390534099013</v>
+        <v>0.0466539053409901</v>
       </c>
       <c r="N544" t="n">
-        <v>0.03899902413391886</v>
+        <v>0.0389990241339188</v>
       </c>
       <c r="O544" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.047200002670288</v>
       </c>
       <c r="P544" t="n">
-        <v>-0.008200978536369231</v>
+        <v>-0.0082009785363692</v>
       </c>
     </row>
     <row r="545">
@@ -32013,13 +32013,13 @@
         <v>23.249825</v>
       </c>
       <c r="M545" t="n">
-        <v>0.01632365302746821</v>
+        <v>0.0163236530274682</v>
       </c>
       <c r="N545" t="n">
-        <v>0.05289574012310529</v>
+        <v>0.0528957401231052</v>
       </c>
       <c r="O545" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.047200002670288</v>
       </c>
       <c r="P545" t="n">
         <v>0.0056957374528172</v>
@@ -32071,16 +32071,16 @@
         <v>9.405068</v>
       </c>
       <c r="M546" t="n">
-        <v>0.05809612692487168</v>
+        <v>0.0580961269248716</v>
       </c>
       <c r="N546" t="n">
         <v>0.0432444878674755</v>
       </c>
       <c r="O546" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.047200002670288</v>
       </c>
       <c r="P546" t="n">
-        <v>-0.003955514802812587</v>
+        <v>-0.0039555148028125</v>
       </c>
     </row>
     <row r="547">
@@ -32129,16 +32129,16 @@
         <v>6.451386</v>
       </c>
       <c r="M547" t="n">
-        <v>0.04594996712916508</v>
+        <v>0.045949967129165</v>
       </c>
       <c r="N547" t="n">
-        <v>0.06048174803640013</v>
+        <v>0.0604817480364001</v>
       </c>
       <c r="O547" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.047200002670288</v>
       </c>
       <c r="P547" t="n">
-        <v>0.01328174536611204</v>
+        <v>0.013281745366112</v>
       </c>
     </row>
     <row r="548">
@@ -32187,16 +32187,16 @@
         <v>11.491237</v>
       </c>
       <c r="M548" t="n">
-        <v>0.03491519482795553</v>
+        <v>0.0349151948279555</v>
       </c>
       <c r="N548" t="n">
-        <v>0.04590438728019785</v>
+        <v>0.0459043872801978</v>
       </c>
       <c r="O548" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.047200002670288</v>
       </c>
       <c r="P548" t="n">
-        <v>-0.001295615390090238</v>
+        <v>-0.0012956153900902</v>
       </c>
     </row>
     <row r="549">
@@ -32245,16 +32245,16 @@
         <v>7.0347686</v>
       </c>
       <c r="M549" t="n">
-        <v>0.03891336270190896</v>
+        <v>0.0389133627019089</v>
       </c>
       <c r="N549" t="n">
-        <v>0.04675611845325502</v>
+        <v>0.046756118453255</v>
       </c>
       <c r="O549" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.047200002670288</v>
       </c>
       <c r="P549" t="n">
-        <v>-0.0004438842170330706</v>
+        <v>-0.000443884217033</v>
       </c>
     </row>
     <row r="550">
@@ -32303,16 +32303,538 @@
         <v>17.338943</v>
       </c>
       <c r="M550" t="n">
-        <v>0.03635945759595495</v>
+        <v>0.0363594575959549</v>
       </c>
       <c r="N550" t="n">
-        <v>0.06972144334635716</v>
+        <v>0.0697214433463571</v>
       </c>
       <c r="O550" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.047200002670288</v>
       </c>
       <c r="P550" t="n">
-        <v>0.02252144067606907</v>
+        <v>0.022521440676069</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>2026-08-31 18:19:46</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>316.85</v>
+      </c>
+      <c r="F551" t="n">
+        <v>4624166158336</v>
+      </c>
+      <c r="G551" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H551" t="n">
+        <v>9.53851</v>
+      </c>
+      <c r="I551" t="n">
+        <v>36.29439</v>
+      </c>
+      <c r="J551" t="n">
+        <v>33.217976</v>
+      </c>
+      <c r="K551" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="L551" t="n">
+        <v>9.905609</v>
+      </c>
+      <c r="M551" t="n">
+        <v>0.02755246962284993</v>
+      </c>
+      <c r="N551" t="n">
+        <v>0.03010418178949029</v>
+      </c>
+      <c r="O551" t="n">
+        <v>0.04758000373840332</v>
+      </c>
+      <c r="P551" t="n">
+        <v>-0.01747582194891303</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>2026-08-31 18:19:46</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>470.72</v>
+      </c>
+      <c r="F552" t="n">
+        <v>768438632448</v>
+      </c>
+      <c r="G552" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H552" t="n">
+        <v>15.45073</v>
+      </c>
+      <c r="I552" t="n">
+        <v>120.38875</v>
+      </c>
+      <c r="J552" t="n">
+        <v>30.465874</v>
+      </c>
+      <c r="K552" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L552" t="n">
+        <v>18.60401</v>
+      </c>
+      <c r="M552" t="n">
+        <v>0.008306424201223657</v>
+      </c>
+      <c r="N552" t="n">
+        <v>0.03282361063902108</v>
+      </c>
+      <c r="O552" t="n">
+        <v>0.04758000373840332</v>
+      </c>
+      <c r="P552" t="n">
+        <v>-0.01475639309938225</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>2026-08-31 18:19:46</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>259.77</v>
+      </c>
+      <c r="F553" t="n">
+        <v>2801960484864</v>
+      </c>
+      <c r="G553" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="H553" t="n">
+        <v>10.39051</v>
+      </c>
+      <c r="I553" t="n">
+        <v>20.881832</v>
+      </c>
+      <c r="J553" t="n">
+        <v>25.000698</v>
+      </c>
+      <c r="K553" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L553" t="n">
+        <v>3.6122632</v>
+      </c>
+      <c r="M553" t="n">
+        <v>0.04788851676483043</v>
+      </c>
+      <c r="N553" t="n">
+        <v>0.03999888362782462</v>
+      </c>
+      <c r="O553" t="n">
+        <v>0.04758000373840332</v>
+      </c>
+      <c r="P553" t="n">
+        <v>-0.007581120110578703</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>2026-08-31 18:19:46</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>370.34</v>
+      </c>
+      <c r="F554" t="n">
+        <v>1761922252800</v>
+      </c>
+      <c r="G554" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H554" t="n">
+        <v>19.50742</v>
+      </c>
+      <c r="I554" t="n">
+        <v>61.62063</v>
+      </c>
+      <c r="J554" t="n">
+        <v>18.984571</v>
+      </c>
+      <c r="K554" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L554" t="n">
+        <v>23.347542</v>
+      </c>
+      <c r="M554" t="n">
+        <v>0.0162283307231193</v>
+      </c>
+      <c r="N554" t="n">
+        <v>0.05267435329697035</v>
+      </c>
+      <c r="O554" t="n">
+        <v>0.04758000373840332</v>
+      </c>
+      <c r="P554" t="n">
+        <v>0.005094349558567031</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>2026-08-31 18:19:46</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>335.41</v>
+      </c>
+      <c r="F555" t="n">
+        <v>4102042681344</v>
+      </c>
+      <c r="G555" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H555" t="n">
+        <v>14.82767</v>
+      </c>
+      <c r="I555" t="n">
+        <v>16.837852</v>
+      </c>
+      <c r="J555" t="n">
+        <v>22.620546</v>
+      </c>
+      <c r="K555" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L555" t="n">
+        <v>9.20017</v>
+      </c>
+      <c r="M555" t="n">
+        <v>0.05939000029814257</v>
+      </c>
+      <c r="N555" t="n">
+        <v>0.0442075966727289</v>
+      </c>
+      <c r="O555" t="n">
+        <v>0.04758000373840332</v>
+      </c>
+      <c r="P555" t="n">
+        <v>-0.003372407065674425</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>2026-08-31 18:19:46</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>572.34</v>
+      </c>
+      <c r="F556" t="n">
+        <v>1458039816192</v>
+      </c>
+      <c r="G556" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="H556" t="n">
+        <v>34.95966</v>
+      </c>
+      <c r="I556" t="n">
+        <v>21.573313</v>
+      </c>
+      <c r="J556" t="n">
+        <v>16.37144</v>
+      </c>
+      <c r="K556" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L556" t="n">
+        <v>6.3879914</v>
+      </c>
+      <c r="M556" t="n">
+        <v>0.0463535660621309</v>
+      </c>
+      <c r="N556" t="n">
+        <v>0.06108197924310724</v>
+      </c>
+      <c r="O556" t="n">
+        <v>0.04758000373840332</v>
+      </c>
+      <c r="P556" t="n">
+        <v>0.01350197550470392</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>2026-08-31 18:19:46</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>507.29</v>
+      </c>
+      <c r="F557" t="n">
+        <v>3766905208832</v>
+      </c>
+      <c r="G557" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="H557" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I557" t="n">
+        <v>28.22983</v>
+      </c>
+      <c r="J557" t="n">
+        <v>21.519703</v>
+      </c>
+      <c r="K557" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="L557" t="n">
+        <v>11.351604</v>
+      </c>
+      <c r="M557" t="n">
+        <v>0.03542352500542096</v>
+      </c>
+      <c r="N557" t="n">
+        <v>0.04646904137672731</v>
+      </c>
+      <c r="O557" t="n">
+        <v>0.04758000373840332</v>
+      </c>
+      <c r="P557" t="n">
+        <v>-0.001110962361676009</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>2026-08-31 18:19:46</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>81.05</v>
+      </c>
+      <c r="F558" t="n">
+        <v>337487331328</v>
+      </c>
+      <c r="G558" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H558" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I558" t="n">
+        <v>25.487421</v>
+      </c>
+      <c r="J558" t="n">
+        <v>21.212225</v>
+      </c>
+      <c r="K558" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="L558" t="n">
+        <v>6.977093</v>
+      </c>
+      <c r="M558" t="n">
+        <v>0.03923504009870451</v>
+      </c>
+      <c r="N558" t="n">
+        <v>0.04714262800740284</v>
+      </c>
+      <c r="O558" t="n">
+        <v>0.04758000373840332</v>
+      </c>
+      <c r="P558" t="n">
+        <v>-0.0004373757310004792</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>2026-08-31 18:19:46</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E559" t="n">
+        <v>220.78</v>
+      </c>
+      <c r="F559" t="n">
+        <v>5331174293504</v>
+      </c>
+      <c r="G559" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="H559" t="n">
+        <v>15.30598</v>
+      </c>
+      <c r="I559" t="n">
+        <v>27.876263</v>
+      </c>
+      <c r="J559" t="n">
+        <v>14.424428</v>
+      </c>
+      <c r="K559" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L559" t="n">
+        <v>17.596376</v>
+      </c>
+      <c r="M559" t="n">
+        <v>0.03587281456653682</v>
+      </c>
+      <c r="N559" t="n">
+        <v>0.069326841199384</v>
+      </c>
+      <c r="O559" t="n">
+        <v>0.04758000373840332</v>
+      </c>
+      <c r="P559" t="n">
+        <v>0.02174683746098068</v>
       </c>
     </row>
   </sheetData>
@@ -32414,12 +32936,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 20:45:39</t>
+          <t>2026-08-31 18:19:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -32433,10 +32955,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>342.88</v>
+        <v>335.41</v>
       </c>
       <c r="F2" t="n">
-        <v>4193400127488</v>
+        <v>4102042681344</v>
       </c>
       <c r="G2" t="n">
         <v>19.92</v>
@@ -32445,39 +32967,39 @@
         <v>14.82767</v>
       </c>
       <c r="I2" t="n">
-        <v>17.212852</v>
+        <v>16.837852</v>
       </c>
       <c r="J2" t="n">
-        <v>23.124334</v>
+        <v>22.620546</v>
       </c>
       <c r="K2" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="L2" t="n">
-        <v>9.405068</v>
+        <v>9.20017</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05809612692487168</v>
+        <v>0.05939000029814257</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0432444878674755</v>
+        <v>0.0442075966727289</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.04758000373840332</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003955514802812587</v>
+        <v>-0.003372407065674425</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 20:45:39</t>
+          <t>2026-08-31 18:19:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -32491,51 +33013,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>513.53</v>
+        <v>507.29</v>
       </c>
       <c r="F3" t="n">
-        <v>3813240733696</v>
+        <v>3766905208832</v>
       </c>
       <c r="G3" t="n">
-        <v>17.93</v>
+        <v>17.97</v>
       </c>
       <c r="H3" t="n">
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>28.640827</v>
+        <v>28.22983</v>
       </c>
       <c r="J3" t="n">
-        <v>21.78441</v>
+        <v>21.519703</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="L3" t="n">
-        <v>11.491237</v>
+        <v>11.351604</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03491519482795553</v>
+        <v>0.03542352500542096</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04590438728019785</v>
+        <v>0.04646904137672731</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.04758000373840332</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.001295615390090238</v>
+        <v>-0.001110962361676009</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 20:45:39</t>
+          <t>2026-08-31 18:19:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -32549,51 +33071,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>578.02</v>
+        <v>572.34</v>
       </c>
       <c r="F4" t="n">
-        <v>1472509509632</v>
+        <v>1458039816192</v>
       </c>
       <c r="G4" t="n">
-        <v>26.56</v>
+        <v>26.53</v>
       </c>
       <c r="H4" t="n">
         <v>34.95966</v>
       </c>
       <c r="I4" t="n">
-        <v>21.762802</v>
+        <v>21.573313</v>
       </c>
       <c r="J4" t="n">
-        <v>16.533915</v>
+        <v>16.37144</v>
       </c>
       <c r="K4" t="n">
         <v>0.85</v>
       </c>
       <c r="L4" t="n">
-        <v>6.451386</v>
+        <v>6.3879914</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04594996712916508</v>
+        <v>0.0463535660621309</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06048174803640013</v>
+        <v>0.06108197924310724</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.04758000373840332</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01328174536611204</v>
+        <v>0.01350197550470392</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 20:45:39</t>
+          <t>2026-08-31 18:19:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -32607,51 +33129,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>266.43</v>
+        <v>259.77</v>
       </c>
       <c r="F5" t="n">
-        <v>2873797378048</v>
+        <v>2801960484864</v>
       </c>
       <c r="G5" t="n">
-        <v>12.43</v>
+        <v>12.44</v>
       </c>
       <c r="H5" t="n">
         <v>10.39051</v>
       </c>
       <c r="I5" t="n">
-        <v>21.434431</v>
+        <v>20.881832</v>
       </c>
       <c r="J5" t="n">
-        <v>25.641668</v>
+        <v>25.000698</v>
       </c>
       <c r="K5" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7048748</v>
+        <v>3.6122632</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04665390534099013</v>
+        <v>0.04788851676483043</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03899902413391886</v>
+        <v>0.03999888362782462</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.04758000373840332</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.008200978536369231</v>
+        <v>-0.007581120110578703</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:45:39</t>
+          <t>2026-08-31 18:19:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -32665,51 +33187,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>319.7</v>
+        <v>316.85</v>
       </c>
       <c r="F6" t="n">
-        <v>4665759498240</v>
+        <v>4624166158336</v>
       </c>
       <c r="G6" t="n">
-        <v>8.710000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="H6" t="n">
         <v>9.53851</v>
       </c>
       <c r="I6" t="n">
-        <v>36.704937</v>
+        <v>36.29439</v>
       </c>
       <c r="J6" t="n">
-        <v>33.516766</v>
+        <v>33.217976</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="L6" t="n">
-        <v>9.994707999999999</v>
+        <v>9.905609</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0272442915233031</v>
+        <v>0.02755246962284993</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02983581482639975</v>
+        <v>0.03010418178949029</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.04758000373840332</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01736418784388833</v>
+        <v>-0.01747582194891303</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 20:45:39</t>
+          <t>2026-08-31 18:19:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -32723,51 +33245,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>217.55</v>
+        <v>220.78</v>
       </c>
       <c r="F7" t="n">
-        <v>5253179637760</v>
+        <v>5331174293504</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91</v>
+        <v>7.92</v>
       </c>
       <c r="H7" t="n">
-        <v>15.1679</v>
+        <v>15.30598</v>
       </c>
       <c r="I7" t="n">
-        <v>27.503162</v>
+        <v>27.876263</v>
       </c>
       <c r="J7" t="n">
-        <v>14.34279</v>
+        <v>14.424428</v>
       </c>
       <c r="K7" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="L7" t="n">
-        <v>17.338943</v>
+        <v>17.596376</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03635945759595495</v>
+        <v>0.03587281456653682</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06972144334635716</v>
+        <v>0.069326841199384</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.04758000373840332</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02252144067606907</v>
+        <v>0.02174683746098068</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 20:45:39</t>
+          <t>2026-08-31 18:19:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -32781,10 +33303,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>465.58</v>
+        <v>470.72</v>
       </c>
       <c r="F8" t="n">
-        <v>760047665152</v>
+        <v>768438632448</v>
       </c>
       <c r="G8" t="n">
         <v>3.91</v>
@@ -32793,39 +33315,39 @@
         <v>15.45073</v>
       </c>
       <c r="I8" t="n">
-        <v>119.074165</v>
+        <v>120.38875</v>
       </c>
       <c r="J8" t="n">
-        <v>30.133204</v>
+        <v>30.465874</v>
       </c>
       <c r="K8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="L8" t="n">
-        <v>18.400862</v>
+        <v>18.60401</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008398127067313889</v>
+        <v>0.008306424201223657</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03318598307487435</v>
+        <v>0.03282361063902108</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.04758000373840332</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01401401959541373</v>
+        <v>-0.01475639309938225</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 20:45:39</t>
+          <t>2026-08-31 18:19:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -32839,51 +33361,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>368.79</v>
+        <v>370.34</v>
       </c>
       <c r="F9" t="n">
-        <v>1754548011008</v>
+        <v>1761922252800</v>
       </c>
       <c r="G9" t="n">
-        <v>6.02</v>
+        <v>6.01</v>
       </c>
       <c r="H9" t="n">
         <v>19.50742</v>
       </c>
       <c r="I9" t="n">
-        <v>61.2608</v>
+        <v>61.62063</v>
       </c>
       <c r="J9" t="n">
-        <v>18.905115</v>
+        <v>18.984571</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="L9" t="n">
-        <v>23.249825</v>
+        <v>23.347542</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01632365302746821</v>
+        <v>0.0162283307231193</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05289574012310529</v>
+        <v>0.05267435329697035</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.04758000373840332</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0056957374528172</v>
+        <v>0.005094349558567031</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 20:45:39</t>
+          <t>2026-08-31 18:19:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -32897,10 +33419,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>81.72</v>
+        <v>81.05</v>
       </c>
       <c r="F10" t="n">
-        <v>340277133312</v>
+        <v>337487331328</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -32909,28 +33431,28 @@
         <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>25.698112</v>
+        <v>25.487421</v>
       </c>
       <c r="J10" t="n">
-        <v>21.387575</v>
+        <v>21.212225</v>
       </c>
       <c r="K10" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="L10" t="n">
-        <v>7.0347686</v>
+        <v>6.977093</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03891336270190896</v>
+        <v>0.03923504009870451</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04675611845325502</v>
+        <v>0.04714262800740284</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04720000267028809</v>
+        <v>0.04758000373840332</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0004438842170330706</v>
+        <v>-0.0004373757310004792</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P559"/>
+  <dimension ref="A1:P568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32361,16 +32361,16 @@
         <v>9.905609</v>
       </c>
       <c r="M551" t="n">
-        <v>0.02755246962284993</v>
+        <v>0.0275524696228499</v>
       </c>
       <c r="N551" t="n">
-        <v>0.03010418178949029</v>
+        <v>0.0301041817894902</v>
       </c>
       <c r="O551" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.0475800037384033</v>
       </c>
       <c r="P551" t="n">
-        <v>-0.01747582194891303</v>
+        <v>-0.017475821948913</v>
       </c>
     </row>
     <row r="552">
@@ -32419,16 +32419,16 @@
         <v>18.60401</v>
       </c>
       <c r="M552" t="n">
-        <v>0.008306424201223657</v>
+        <v>0.0083064242012236</v>
       </c>
       <c r="N552" t="n">
-        <v>0.03282361063902108</v>
+        <v>0.032823610639021</v>
       </c>
       <c r="O552" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.0475800037384033</v>
       </c>
       <c r="P552" t="n">
-        <v>-0.01475639309938225</v>
+        <v>-0.0147563930993822</v>
       </c>
     </row>
     <row r="553">
@@ -32477,16 +32477,16 @@
         <v>3.6122632</v>
       </c>
       <c r="M553" t="n">
-        <v>0.04788851676483043</v>
+        <v>0.0478885167648304</v>
       </c>
       <c r="N553" t="n">
-        <v>0.03999888362782462</v>
+        <v>0.0399988836278246</v>
       </c>
       <c r="O553" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.0475800037384033</v>
       </c>
       <c r="P553" t="n">
-        <v>-0.007581120110578703</v>
+        <v>-0.0075811201105787</v>
       </c>
     </row>
     <row r="554">
@@ -32535,16 +32535,16 @@
         <v>23.347542</v>
       </c>
       <c r="M554" t="n">
-        <v>0.0162283307231193</v>
+        <v>0.0162283307231192</v>
       </c>
       <c r="N554" t="n">
-        <v>0.05267435329697035</v>
+        <v>0.0526743532969703</v>
       </c>
       <c r="O554" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.0475800037384033</v>
       </c>
       <c r="P554" t="n">
-        <v>0.005094349558567031</v>
+        <v>0.005094349558567</v>
       </c>
     </row>
     <row r="555">
@@ -32593,16 +32593,16 @@
         <v>9.20017</v>
       </c>
       <c r="M555" t="n">
-        <v>0.05939000029814257</v>
+        <v>0.0593900002981425</v>
       </c>
       <c r="N555" t="n">
-        <v>0.0442075966727289</v>
+        <v>0.0442075966727288</v>
       </c>
       <c r="O555" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.0475800037384033</v>
       </c>
       <c r="P555" t="n">
-        <v>-0.003372407065674425</v>
+        <v>-0.0033724070656744</v>
       </c>
     </row>
     <row r="556">
@@ -32654,13 +32654,13 @@
         <v>0.0463535660621309</v>
       </c>
       <c r="N556" t="n">
-        <v>0.06108197924310724</v>
+        <v>0.0610819792431072</v>
       </c>
       <c r="O556" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.0475800037384033</v>
       </c>
       <c r="P556" t="n">
-        <v>0.01350197550470392</v>
+        <v>0.0135019755047039</v>
       </c>
     </row>
     <row r="557">
@@ -32709,16 +32709,16 @@
         <v>11.351604</v>
       </c>
       <c r="M557" t="n">
-        <v>0.03542352500542096</v>
+        <v>0.0354235250054209</v>
       </c>
       <c r="N557" t="n">
-        <v>0.04646904137672731</v>
+        <v>0.0464690413767273</v>
       </c>
       <c r="O557" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.0475800037384033</v>
       </c>
       <c r="P557" t="n">
-        <v>-0.001110962361676009</v>
+        <v>-0.001110962361676</v>
       </c>
     </row>
     <row r="558">
@@ -32767,16 +32767,16 @@
         <v>6.977093</v>
       </c>
       <c r="M558" t="n">
-        <v>0.03923504009870451</v>
+        <v>0.0392350400987045</v>
       </c>
       <c r="N558" t="n">
-        <v>0.04714262800740284</v>
+        <v>0.0471426280074028</v>
       </c>
       <c r="O558" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.0475800037384033</v>
       </c>
       <c r="P558" t="n">
-        <v>-0.0004373757310004792</v>
+        <v>-0.0004373757310004</v>
       </c>
     </row>
     <row r="559">
@@ -32825,16 +32825,538 @@
         <v>17.596376</v>
       </c>
       <c r="M559" t="n">
-        <v>0.03587281456653682</v>
+        <v>0.0358728145665368</v>
       </c>
       <c r="N559" t="n">
         <v>0.069326841199384</v>
       </c>
       <c r="O559" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.0475800037384033</v>
       </c>
       <c r="P559" t="n">
-        <v>0.02174683746098068</v>
+        <v>0.0217468374609806</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:21:09</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E560" t="n">
+        <v>325.13</v>
+      </c>
+      <c r="F560" t="n">
+        <v>4745005629440</v>
+      </c>
+      <c r="G560" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H560" t="n">
+        <v>9.53782</v>
+      </c>
+      <c r="I560" t="n">
+        <v>37.328358</v>
+      </c>
+      <c r="J560" t="n">
+        <v>34.088505</v>
+      </c>
+      <c r="K560" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="L560" t="n">
+        <v>10.164464</v>
+      </c>
+      <c r="M560" t="n">
+        <v>0.02678928428628549</v>
+      </c>
+      <c r="N560" t="n">
+        <v>0.02933540429981853</v>
+      </c>
+      <c r="O560" t="n">
+        <v>0.04796000003814697</v>
+      </c>
+      <c r="P560" t="n">
+        <v>-0.01862459573832844</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:21:09</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E561" t="n">
+        <v>459.61</v>
+      </c>
+      <c r="F561" t="n">
+        <v>750301806592</v>
+      </c>
+      <c r="G561" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H561" t="n">
+        <v>15.45073</v>
+      </c>
+      <c r="I561" t="n">
+        <v>117.54731</v>
+      </c>
+      <c r="J561" t="n">
+        <v>29.746813</v>
+      </c>
+      <c r="K561" t="n">
+        <v>1</v>
+      </c>
+      <c r="L561" t="n">
+        <v>18.164913</v>
+      </c>
+      <c r="M561" t="n">
+        <v>0.008507212636800767</v>
+      </c>
+      <c r="N561" t="n">
+        <v>0.03361704488588151</v>
+      </c>
+      <c r="O561" t="n">
+        <v>0.04796000003814697</v>
+      </c>
+      <c r="P561" t="n">
+        <v>-0.01434295515226547</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:21:09</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E562" t="n">
+        <v>254.92</v>
+      </c>
+      <c r="F562" t="n">
+        <v>2749647028224</v>
+      </c>
+      <c r="G562" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="H562" t="n">
+        <v>10.39378</v>
+      </c>
+      <c r="I562" t="n">
+        <v>20.491962</v>
+      </c>
+      <c r="J562" t="n">
+        <v>24.526207</v>
+      </c>
+      <c r="K562" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L562" t="n">
+        <v>3.5448213</v>
+      </c>
+      <c r="M562" t="n">
+        <v>0.04879962341126628</v>
+      </c>
+      <c r="N562" t="n">
+        <v>0.04077271300800251</v>
+      </c>
+      <c r="O562" t="n">
+        <v>0.04796000003814697</v>
+      </c>
+      <c r="P562" t="n">
+        <v>-0.007187287030144464</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:21:09</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E563" t="n">
+        <v>369.68</v>
+      </c>
+      <c r="F563" t="n">
+        <v>1758782291968</v>
+      </c>
+      <c r="G563" t="n">
+        <v>6</v>
+      </c>
+      <c r="H563" t="n">
+        <v>19.5728</v>
+      </c>
+      <c r="I563" t="n">
+        <v>61.61333</v>
+      </c>
+      <c r="J563" t="n">
+        <v>18.887436</v>
+      </c>
+      <c r="K563" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L563" t="n">
+        <v>23.305935</v>
+      </c>
+      <c r="M563" t="n">
+        <v>0.01623025319194979</v>
+      </c>
+      <c r="N563" t="n">
+        <v>0.05294524994589916</v>
+      </c>
+      <c r="O563" t="n">
+        <v>0.04796000003814697</v>
+      </c>
+      <c r="P563" t="n">
+        <v>0.004985249907752183</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:21:09</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E564" t="n">
+        <v>332.03</v>
+      </c>
+      <c r="F564" t="n">
+        <v>4060705456128</v>
+      </c>
+      <c r="G564" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H564" t="n">
+        <v>14.82767</v>
+      </c>
+      <c r="I564" t="n">
+        <v>16.668173</v>
+      </c>
+      <c r="J564" t="n">
+        <v>22.392593</v>
+      </c>
+      <c r="K564" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L564" t="n">
+        <v>9.107457</v>
+      </c>
+      <c r="M564" t="n">
+        <v>0.05999457880312021</v>
+      </c>
+      <c r="N564" t="n">
+        <v>0.04465762129928019</v>
+      </c>
+      <c r="O564" t="n">
+        <v>0.04796000003814697</v>
+      </c>
+      <c r="P564" t="n">
+        <v>-0.003302378738866789</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:21:09</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E565" t="n">
+        <v>578.54</v>
+      </c>
+      <c r="F565" t="n">
+        <v>1473834123264</v>
+      </c>
+      <c r="G565" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="H565" t="n">
+        <v>34.95966</v>
+      </c>
+      <c r="I565" t="n">
+        <v>21.78238</v>
+      </c>
+      <c r="J565" t="n">
+        <v>16.548788</v>
+      </c>
+      <c r="K565" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L565" t="n">
+        <v>6.4571896</v>
+      </c>
+      <c r="M565" t="n">
+        <v>0.04590866664362015</v>
+      </c>
+      <c r="N565" t="n">
+        <v>0.06042738617900232</v>
+      </c>
+      <c r="O565" t="n">
+        <v>0.04796000003814697</v>
+      </c>
+      <c r="P565" t="n">
+        <v>0.01246738614085535</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:21:09</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E566" t="n">
+        <v>501.02</v>
+      </c>
+      <c r="F566" t="n">
+        <v>3720346861568</v>
+      </c>
+      <c r="G566" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="H566" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I566" t="n">
+        <v>27.896437</v>
+      </c>
+      <c r="J566" t="n">
+        <v>21.253723</v>
+      </c>
+      <c r="K566" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L566" t="n">
+        <v>11.211301</v>
+      </c>
+      <c r="M566" t="n">
+        <v>0.0358468723803441</v>
+      </c>
+      <c r="N566" t="n">
+        <v>0.04705057682328051</v>
+      </c>
+      <c r="O566" t="n">
+        <v>0.04796000003814697</v>
+      </c>
+      <c r="P566" t="n">
+        <v>-0.0009094232148664644</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:21:09</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E567" t="n">
+        <v>80.81</v>
+      </c>
+      <c r="F567" t="n">
+        <v>336487940096</v>
+      </c>
+      <c r="G567" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H567" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I567" t="n">
+        <v>25.41195</v>
+      </c>
+      <c r="J567" t="n">
+        <v>21.149412</v>
+      </c>
+      <c r="K567" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L567" t="n">
+        <v>6.956432</v>
+      </c>
+      <c r="M567" t="n">
+        <v>0.03935156540032175</v>
+      </c>
+      <c r="N567" t="n">
+        <v>0.04728263828734067</v>
+      </c>
+      <c r="O567" t="n">
+        <v>0.04796000003814697</v>
+      </c>
+      <c r="P567" t="n">
+        <v>-0.0006773617508063004</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:21:09</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E568" t="n">
+        <v>217.44</v>
+      </c>
+      <c r="F568" t="n">
+        <v>5250523594752</v>
+      </c>
+      <c r="G568" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="H568" t="n">
+        <v>15.30598</v>
+      </c>
+      <c r="I568" t="n">
+        <v>27.454546</v>
+      </c>
+      <c r="J568" t="n">
+        <v>14.206213</v>
+      </c>
+      <c r="K568" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L568" t="n">
+        <v>17.330175</v>
+      </c>
+      <c r="M568" t="n">
+        <v>0.03642384105960265</v>
+      </c>
+      <c r="N568" t="n">
+        <v>0.07039174025018397</v>
+      </c>
+      <c r="O568" t="n">
+        <v>0.04796000003814697</v>
+      </c>
+      <c r="P568" t="n">
+        <v>0.02243174021203699</v>
       </c>
     </row>
   </sheetData>
@@ -32936,12 +33458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 18:19:46</t>
+          <t>2026-09-01 17:21:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -32955,10 +33477,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>335.41</v>
+        <v>332.03</v>
       </c>
       <c r="F2" t="n">
-        <v>4102042681344</v>
+        <v>4060705456128</v>
       </c>
       <c r="G2" t="n">
         <v>19.92</v>
@@ -32967,39 +33489,39 @@
         <v>14.82767</v>
       </c>
       <c r="I2" t="n">
-        <v>16.837852</v>
+        <v>16.668173</v>
       </c>
       <c r="J2" t="n">
-        <v>22.620546</v>
+        <v>22.392593</v>
       </c>
       <c r="K2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="L2" t="n">
-        <v>9.20017</v>
+        <v>9.107457</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05939000029814257</v>
+        <v>0.05999457880312021</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0442075966727289</v>
+        <v>0.04465762129928019</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.04796000003814697</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003372407065674425</v>
+        <v>-0.003302378738866789</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 18:19:46</t>
+          <t>2026-09-01 17:21:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -33013,51 +33535,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>507.29</v>
+        <v>501.02</v>
       </c>
       <c r="F3" t="n">
-        <v>3766905208832</v>
+        <v>3720346861568</v>
       </c>
       <c r="G3" t="n">
-        <v>17.97</v>
+        <v>17.96</v>
       </c>
       <c r="H3" t="n">
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>28.22983</v>
+        <v>27.896437</v>
       </c>
       <c r="J3" t="n">
-        <v>21.519703</v>
+        <v>21.253723</v>
       </c>
       <c r="K3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="L3" t="n">
-        <v>11.351604</v>
+        <v>11.211301</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03542352500542096</v>
+        <v>0.0358468723803441</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04646904137672731</v>
+        <v>0.04705057682328051</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.04796000003814697</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.001110962361676009</v>
+        <v>-0.0009094232148664644</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 18:19:46</t>
+          <t>2026-09-01 17:21:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -33071,51 +33593,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>572.34</v>
+        <v>578.54</v>
       </c>
       <c r="F4" t="n">
-        <v>1458039816192</v>
+        <v>1473834123264</v>
       </c>
       <c r="G4" t="n">
-        <v>26.53</v>
+        <v>26.56</v>
       </c>
       <c r="H4" t="n">
         <v>34.95966</v>
       </c>
       <c r="I4" t="n">
-        <v>21.573313</v>
+        <v>21.78238</v>
       </c>
       <c r="J4" t="n">
-        <v>16.37144</v>
+        <v>16.548788</v>
       </c>
       <c r="K4" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="L4" t="n">
-        <v>6.3879914</v>
+        <v>6.4571896</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0463535660621309</v>
+        <v>0.04590866664362015</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06108197924310724</v>
+        <v>0.06042738617900232</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.04796000003814697</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01350197550470392</v>
+        <v>0.01246738614085535</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 18:19:46</t>
+          <t>2026-09-01 17:21:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -33129,51 +33651,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>259.77</v>
+        <v>254.92</v>
       </c>
       <c r="F5" t="n">
-        <v>2801960484864</v>
+        <v>2749647028224</v>
       </c>
       <c r="G5" t="n">
         <v>12.44</v>
       </c>
       <c r="H5" t="n">
-        <v>10.39051</v>
+        <v>10.39378</v>
       </c>
       <c r="I5" t="n">
-        <v>20.881832</v>
+        <v>20.491962</v>
       </c>
       <c r="J5" t="n">
-        <v>25.000698</v>
+        <v>24.526207</v>
       </c>
       <c r="K5" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6122632</v>
+        <v>3.5448213</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04788851676483043</v>
+        <v>0.04879962341126628</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03999888362782462</v>
+        <v>0.04077271300800251</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.04796000003814697</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007581120110578703</v>
+        <v>-0.007187287030144464</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 18:19:46</t>
+          <t>2026-09-01 17:21:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -33187,51 +33709,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>316.85</v>
+        <v>325.13</v>
       </c>
       <c r="F6" t="n">
-        <v>4624166158336</v>
+        <v>4745005629440</v>
       </c>
       <c r="G6" t="n">
-        <v>8.73</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>9.53851</v>
+        <v>9.53782</v>
       </c>
       <c r="I6" t="n">
-        <v>36.29439</v>
+        <v>37.328358</v>
       </c>
       <c r="J6" t="n">
-        <v>33.217976</v>
+        <v>34.088505</v>
       </c>
       <c r="K6" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="L6" t="n">
-        <v>9.905609</v>
+        <v>10.164464</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02755246962284993</v>
+        <v>0.02678928428628549</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03010418178949029</v>
+        <v>0.02933540429981853</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.04796000003814697</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01747582194891303</v>
+        <v>-0.01862459573832844</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 18:19:46</t>
+          <t>2026-09-01 17:21:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -33245,10 +33767,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220.78</v>
+        <v>217.44</v>
       </c>
       <c r="F7" t="n">
-        <v>5331174293504</v>
+        <v>5250523594752</v>
       </c>
       <c r="G7" t="n">
         <v>7.92</v>
@@ -33257,39 +33779,39 @@
         <v>15.30598</v>
       </c>
       <c r="I7" t="n">
-        <v>27.876263</v>
+        <v>27.454546</v>
       </c>
       <c r="J7" t="n">
-        <v>14.424428</v>
+        <v>14.206213</v>
       </c>
       <c r="K7" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>17.596376</v>
+        <v>17.330175</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03587281456653682</v>
+        <v>0.03642384105960265</v>
       </c>
       <c r="N7" t="n">
-        <v>0.069326841199384</v>
+        <v>0.07039174025018397</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.04796000003814697</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02174683746098068</v>
+        <v>0.02243174021203699</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 18:19:46</t>
+          <t>2026-09-01 17:21:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -33303,10 +33825,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>470.72</v>
+        <v>459.61</v>
       </c>
       <c r="F8" t="n">
-        <v>768438632448</v>
+        <v>750301806592</v>
       </c>
       <c r="G8" t="n">
         <v>3.91</v>
@@ -33315,39 +33837,39 @@
         <v>15.45073</v>
       </c>
       <c r="I8" t="n">
-        <v>120.38875</v>
+        <v>117.54731</v>
       </c>
       <c r="J8" t="n">
-        <v>30.465874</v>
+        <v>29.746813</v>
       </c>
       <c r="K8" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>18.60401</v>
+        <v>18.164913</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008306424201223657</v>
+        <v>0.008507212636800767</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03282361063902108</v>
+        <v>0.03361704488588151</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.04796000003814697</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01475639309938225</v>
+        <v>-0.01434295515226547</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 18:19:46</t>
+          <t>2026-09-01 17:21:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -33361,51 +33883,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>370.34</v>
+        <v>369.68</v>
       </c>
       <c r="F9" t="n">
-        <v>1761922252800</v>
+        <v>1758782291968</v>
       </c>
       <c r="G9" t="n">
-        <v>6.01</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>19.50742</v>
+        <v>19.5728</v>
       </c>
       <c r="I9" t="n">
-        <v>61.62063</v>
+        <v>61.61333</v>
       </c>
       <c r="J9" t="n">
-        <v>18.984571</v>
+        <v>18.887436</v>
       </c>
       <c r="K9" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="L9" t="n">
-        <v>23.347542</v>
+        <v>23.305935</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0162283307231193</v>
+        <v>0.01623025319194979</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05267435329697035</v>
+        <v>0.05294524994589916</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.04796000003814697</v>
       </c>
       <c r="P9" t="n">
-        <v>0.005094349558567031</v>
+        <v>0.004985249907752183</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 18:19:46</t>
+          <t>2026-09-01 17:21:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -33419,10 +33941,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>81.05</v>
+        <v>80.81</v>
       </c>
       <c r="F10" t="n">
-        <v>337487331328</v>
+        <v>336487940096</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -33431,28 +33953,28 @@
         <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>25.487421</v>
+        <v>25.41195</v>
       </c>
       <c r="J10" t="n">
-        <v>21.212225</v>
+        <v>21.149412</v>
       </c>
       <c r="K10" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="L10" t="n">
-        <v>6.977093</v>
+        <v>6.956432</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03923504009870451</v>
+        <v>0.03935156540032175</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04714262800740284</v>
+        <v>0.04728263828734067</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04758000373840332</v>
+        <v>0.04796000003814697</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0004373757310004792</v>
+        <v>-0.0006773617508063004</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P568"/>
+  <dimension ref="A1:P577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32883,16 +32883,16 @@
         <v>10.164464</v>
       </c>
       <c r="M560" t="n">
-        <v>0.02678928428628549</v>
+        <v>0.0267892842862854</v>
       </c>
       <c r="N560" t="n">
-        <v>0.02933540429981853</v>
+        <v>0.0293354042998185</v>
       </c>
       <c r="O560" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0479600000381469</v>
       </c>
       <c r="P560" t="n">
-        <v>-0.01862459573832844</v>
+        <v>-0.0186245957383284</v>
       </c>
     </row>
     <row r="561">
@@ -32941,16 +32941,16 @@
         <v>18.164913</v>
       </c>
       <c r="M561" t="n">
-        <v>0.008507212636800767</v>
+        <v>0.008507212636800701</v>
       </c>
       <c r="N561" t="n">
-        <v>0.03361704488588151</v>
+        <v>0.0336170448858815</v>
       </c>
       <c r="O561" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0479600000381469</v>
       </c>
       <c r="P561" t="n">
-        <v>-0.01434295515226547</v>
+        <v>-0.0143429551522654</v>
       </c>
     </row>
     <row r="562">
@@ -32999,16 +32999,16 @@
         <v>3.5448213</v>
       </c>
       <c r="M562" t="n">
-        <v>0.04879962341126628</v>
+        <v>0.0487996234112662</v>
       </c>
       <c r="N562" t="n">
-        <v>0.04077271300800251</v>
+        <v>0.0407727130080025</v>
       </c>
       <c r="O562" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0479600000381469</v>
       </c>
       <c r="P562" t="n">
-        <v>-0.007187287030144464</v>
+        <v>-0.0071872870301444</v>
       </c>
     </row>
     <row r="563">
@@ -33057,16 +33057,16 @@
         <v>23.305935</v>
       </c>
       <c r="M563" t="n">
-        <v>0.01623025319194979</v>
+        <v>0.0162302531919497</v>
       </c>
       <c r="N563" t="n">
-        <v>0.05294524994589916</v>
+        <v>0.0529452499458991</v>
       </c>
       <c r="O563" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0479600000381469</v>
       </c>
       <c r="P563" t="n">
-        <v>0.004985249907752183</v>
+        <v>0.0049852499077521</v>
       </c>
     </row>
     <row r="564">
@@ -33115,16 +33115,16 @@
         <v>9.107457</v>
       </c>
       <c r="M564" t="n">
-        <v>0.05999457880312021</v>
+        <v>0.0599945788031202</v>
       </c>
       <c r="N564" t="n">
-        <v>0.04465762129928019</v>
+        <v>0.0446576212992801</v>
       </c>
       <c r="O564" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0479600000381469</v>
       </c>
       <c r="P564" t="n">
-        <v>-0.003302378738866789</v>
+        <v>-0.0033023787388667</v>
       </c>
     </row>
     <row r="565">
@@ -33173,16 +33173,16 @@
         <v>6.4571896</v>
       </c>
       <c r="M565" t="n">
-        <v>0.04590866664362015</v>
+        <v>0.0459086666436201</v>
       </c>
       <c r="N565" t="n">
-        <v>0.06042738617900232</v>
+        <v>0.0604273861790023</v>
       </c>
       <c r="O565" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0479600000381469</v>
       </c>
       <c r="P565" t="n">
-        <v>0.01246738614085535</v>
+        <v>0.0124673861408553</v>
       </c>
     </row>
     <row r="566">
@@ -33234,13 +33234,13 @@
         <v>0.0358468723803441</v>
       </c>
       <c r="N566" t="n">
-        <v>0.04705057682328051</v>
+        <v>0.0470505768232805</v>
       </c>
       <c r="O566" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0479600000381469</v>
       </c>
       <c r="P566" t="n">
-        <v>-0.0009094232148664644</v>
+        <v>-0.0009094232148664</v>
       </c>
     </row>
     <row r="567">
@@ -33289,16 +33289,16 @@
         <v>6.956432</v>
       </c>
       <c r="M567" t="n">
-        <v>0.03935156540032175</v>
+        <v>0.0393515654003217</v>
       </c>
       <c r="N567" t="n">
-        <v>0.04728263828734067</v>
+        <v>0.0472826382873406</v>
       </c>
       <c r="O567" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0479600000381469</v>
       </c>
       <c r="P567" t="n">
-        <v>-0.0006773617508063004</v>
+        <v>-0.0006773617508063</v>
       </c>
     </row>
     <row r="568">
@@ -33347,16 +33347,538 @@
         <v>17.330175</v>
       </c>
       <c r="M568" t="n">
-        <v>0.03642384105960265</v>
+        <v>0.0364238410596026</v>
       </c>
       <c r="N568" t="n">
-        <v>0.07039174025018397</v>
+        <v>0.0703917402501839</v>
       </c>
       <c r="O568" t="n">
+        <v>0.0479600000381469</v>
+      </c>
+      <c r="P568" t="n">
+        <v>0.0224317402120369</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:23:40</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E569" t="n">
+        <v>324.96</v>
+      </c>
+      <c r="F569" t="n">
+        <v>4742524698624</v>
+      </c>
+      <c r="G569" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H569" t="n">
+        <v>9.54013</v>
+      </c>
+      <c r="I569" t="n">
+        <v>37.308838</v>
+      </c>
+      <c r="J569" t="n">
+        <v>34.062428</v>
+      </c>
+      <c r="K569" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L569" t="n">
+        <v>10.15915</v>
+      </c>
+      <c r="M569" t="n">
+        <v>0.02680329886755294</v>
+      </c>
+      <c r="N569" t="n">
+        <v>0.02935785942885278</v>
+      </c>
+      <c r="O569" t="n">
         <v>0.04796000003814697</v>
       </c>
-      <c r="P568" t="n">
-        <v>0.02243174021203699</v>
+      <c r="P569" t="n">
+        <v>-0.01860214060929419</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:23:40</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E570" t="n">
+        <v>457.06</v>
+      </c>
+      <c r="F570" t="n">
+        <v>746139025408</v>
+      </c>
+      <c r="G570" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H570" t="n">
+        <v>15.45073</v>
+      </c>
+      <c r="I570" t="n">
+        <v>116.895134</v>
+      </c>
+      <c r="J570" t="n">
+        <v>29.581774</v>
+      </c>
+      <c r="K570" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L570" t="n">
+        <v>18.064133</v>
+      </c>
+      <c r="M570" t="n">
+        <v>0.008554675534940707</v>
+      </c>
+      <c r="N570" t="n">
+        <v>0.03380459895856124</v>
+      </c>
+      <c r="O570" t="n">
+        <v>0.04796000003814697</v>
+      </c>
+      <c r="P570" t="n">
+        <v>-0.01415540107958573</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:23:40</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E571" t="n">
+        <v>254.98</v>
+      </c>
+      <c r="F571" t="n">
+        <v>2750293999616</v>
+      </c>
+      <c r="G571" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="H571" t="n">
+        <v>10.39378</v>
+      </c>
+      <c r="I571" t="n">
+        <v>20.496784</v>
+      </c>
+      <c r="J571" t="n">
+        <v>24.53198</v>
+      </c>
+      <c r="K571" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L571" t="n">
+        <v>3.5456553</v>
+      </c>
+      <c r="M571" t="n">
+        <v>0.04878814024629383</v>
+      </c>
+      <c r="N571" t="n">
+        <v>0.04076311867597458</v>
+      </c>
+      <c r="O571" t="n">
+        <v>0.04796000003814697</v>
+      </c>
+      <c r="P571" t="n">
+        <v>-0.007196881362172391</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:23:40</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E572" t="n">
+        <v>367.24</v>
+      </c>
+      <c r="F572" t="n">
+        <v>1747173769216</v>
+      </c>
+      <c r="G572" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="H572" t="n">
+        <v>19.5728</v>
+      </c>
+      <c r="I572" t="n">
+        <v>60.902153</v>
+      </c>
+      <c r="J572" t="n">
+        <v>18.762774</v>
+      </c>
+      <c r="K572" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L572" t="n">
+        <v>23.152107</v>
+      </c>
+      <c r="M572" t="n">
+        <v>0.01641977998039429</v>
+      </c>
+      <c r="N572" t="n">
+        <v>0.05329702646770505</v>
+      </c>
+      <c r="O572" t="n">
+        <v>0.04796000003814697</v>
+      </c>
+      <c r="P572" t="n">
+        <v>0.005337026429558071</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:23:40</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E573" t="n">
+        <v>333.78</v>
+      </c>
+      <c r="F573" t="n">
+        <v>4082107678720</v>
+      </c>
+      <c r="G573" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H573" t="n">
+        <v>14.82767</v>
+      </c>
+      <c r="I573" t="n">
+        <v>16.756023</v>
+      </c>
+      <c r="J573" t="n">
+        <v>22.510616</v>
+      </c>
+      <c r="K573" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L573" t="n">
+        <v>9.155457999999999</v>
+      </c>
+      <c r="M573" t="n">
+        <v>0.05968002876145966</v>
+      </c>
+      <c r="N573" t="n">
+        <v>0.04442348253340524</v>
+      </c>
+      <c r="O573" t="n">
+        <v>0.04796000003814697</v>
+      </c>
+      <c r="P573" t="n">
+        <v>-0.003536517504741737</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:23:40</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E574" t="n">
+        <v>592.85</v>
+      </c>
+      <c r="F574" t="n">
+        <v>1510288916480</v>
+      </c>
+      <c r="G574" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="H574" t="n">
+        <v>34.95966</v>
+      </c>
+      <c r="I574" t="n">
+        <v>22.329567</v>
+      </c>
+      <c r="J574" t="n">
+        <v>16.958117</v>
+      </c>
+      <c r="K574" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L574" t="n">
+        <v>6.616906</v>
+      </c>
+      <c r="M574" t="n">
+        <v>0.04478367209243485</v>
+      </c>
+      <c r="N574" t="n">
+        <v>0.05896881167242979</v>
+      </c>
+      <c r="O574" t="n">
+        <v>0.04796000003814697</v>
+      </c>
+      <c r="P574" t="n">
+        <v>0.01100881163428281</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:23:40</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E575" t="n">
+        <v>496.82</v>
+      </c>
+      <c r="F575" t="n">
+        <v>3689159589888</v>
+      </c>
+      <c r="G575" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H575" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I575" t="n">
+        <v>27.693422</v>
+      </c>
+      <c r="J575" t="n">
+        <v>21.075556</v>
+      </c>
+      <c r="K575" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L575" t="n">
+        <v>11.117317</v>
+      </c>
+      <c r="M575" t="n">
+        <v>0.03610965742119883</v>
+      </c>
+      <c r="N575" t="n">
+        <v>0.0474483313876253</v>
+      </c>
+      <c r="O575" t="n">
+        <v>0.04796000003814697</v>
+      </c>
+      <c r="P575" t="n">
+        <v>-0.000511668650521678</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:23:40</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E576" t="n">
+        <v>82.73</v>
+      </c>
+      <c r="F576" t="n">
+        <v>344482742272</v>
+      </c>
+      <c r="G576" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H576" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I576" t="n">
+        <v>26.015724</v>
+      </c>
+      <c r="J576" t="n">
+        <v>21.65191</v>
+      </c>
+      <c r="K576" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L576" t="n">
+        <v>7.1217136</v>
+      </c>
+      <c r="M576" t="n">
+        <v>0.0384382932430799</v>
+      </c>
+      <c r="N576" t="n">
+        <v>0.04618530158346428</v>
+      </c>
+      <c r="O576" t="n">
+        <v>0.04796000003814697</v>
+      </c>
+      <c r="P576" t="n">
+        <v>-0.001774698454682692</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:23:40</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E577" t="n">
+        <v>224.41</v>
+      </c>
+      <c r="F577" t="n">
+        <v>5418828431360</v>
+      </c>
+      <c r="G577" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H577" t="n">
+        <v>15.40425</v>
+      </c>
+      <c r="I577" t="n">
+        <v>28.370419</v>
+      </c>
+      <c r="J577" t="n">
+        <v>14.568058</v>
+      </c>
+      <c r="K577" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L577" t="n">
+        <v>17.885693</v>
+      </c>
+      <c r="M577" t="n">
+        <v>0.03524798360144379</v>
+      </c>
+      <c r="N577" t="n">
+        <v>0.06864333140234392</v>
+      </c>
+      <c r="O577" t="n">
+        <v>0.04796000003814697</v>
+      </c>
+      <c r="P577" t="n">
+        <v>0.02068333136419695</v>
       </c>
     </row>
   </sheetData>
@@ -33458,12 +33980,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 17:21:09</t>
+          <t>2026-09-02 17:23:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -33477,10 +33999,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>332.03</v>
+        <v>333.78</v>
       </c>
       <c r="F2" t="n">
-        <v>4060705456128</v>
+        <v>4082107678720</v>
       </c>
       <c r="G2" t="n">
         <v>19.92</v>
@@ -33489,39 +34011,39 @@
         <v>14.82767</v>
       </c>
       <c r="I2" t="n">
-        <v>16.668173</v>
+        <v>16.756023</v>
       </c>
       <c r="J2" t="n">
-        <v>22.392593</v>
+        <v>22.510616</v>
       </c>
       <c r="K2" t="n">
-        <v>0.93</v>
+        <v>1.23</v>
       </c>
       <c r="L2" t="n">
-        <v>9.107457</v>
+        <v>9.155457999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05999457880312021</v>
+        <v>0.05968002876145966</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04465762129928019</v>
+        <v>0.04442348253340524</v>
       </c>
       <c r="O2" t="n">
         <v>0.04796000003814697</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003302378738866789</v>
+        <v>-0.003536517504741737</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 17:21:09</t>
+          <t>2026-09-02 17:23:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -33535,51 +34057,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>501.02</v>
+        <v>496.82</v>
       </c>
       <c r="F3" t="n">
-        <v>3720346861568</v>
+        <v>3689159589888</v>
       </c>
       <c r="G3" t="n">
-        <v>17.96</v>
+        <v>17.94</v>
       </c>
       <c r="H3" t="n">
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>27.896437</v>
+        <v>27.693422</v>
       </c>
       <c r="J3" t="n">
-        <v>21.253723</v>
+        <v>21.075556</v>
       </c>
       <c r="K3" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="L3" t="n">
-        <v>11.211301</v>
+        <v>11.117317</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0358468723803441</v>
+        <v>0.03610965742119883</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04705057682328051</v>
+        <v>0.0474483313876253</v>
       </c>
       <c r="O3" t="n">
         <v>0.04796000003814697</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0009094232148664644</v>
+        <v>-0.000511668650521678</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 17:21:09</t>
+          <t>2026-09-02 17:23:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -33593,51 +34115,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>578.54</v>
+        <v>592.85</v>
       </c>
       <c r="F4" t="n">
-        <v>1473834123264</v>
+        <v>1510288916480</v>
       </c>
       <c r="G4" t="n">
-        <v>26.56</v>
+        <v>26.55</v>
       </c>
       <c r="H4" t="n">
         <v>34.95966</v>
       </c>
       <c r="I4" t="n">
-        <v>21.78238</v>
+        <v>22.329567</v>
       </c>
       <c r="J4" t="n">
-        <v>16.548788</v>
+        <v>16.958117</v>
       </c>
       <c r="K4" t="n">
-        <v>0.87</v>
+        <v>0.77</v>
       </c>
       <c r="L4" t="n">
-        <v>6.4571896</v>
+        <v>6.616906</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04590866664362015</v>
+        <v>0.04478367209243485</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06042738617900232</v>
+        <v>0.05896881167242979</v>
       </c>
       <c r="O4" t="n">
         <v>0.04796000003814697</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01246738614085535</v>
+        <v>0.01100881163428281</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 17:21:09</t>
+          <t>2026-09-02 17:23:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -33651,10 +34173,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>254.92</v>
+        <v>254.98</v>
       </c>
       <c r="F5" t="n">
-        <v>2749647028224</v>
+        <v>2750293999616</v>
       </c>
       <c r="G5" t="n">
         <v>12.44</v>
@@ -33663,39 +34185,39 @@
         <v>10.39378</v>
       </c>
       <c r="I5" t="n">
-        <v>20.491962</v>
+        <v>20.496784</v>
       </c>
       <c r="J5" t="n">
-        <v>24.526207</v>
+        <v>24.53198</v>
       </c>
       <c r="K5" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5448213</v>
+        <v>3.5456553</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04879962341126628</v>
+        <v>0.04878814024629383</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04077271300800251</v>
+        <v>0.04076311867597458</v>
       </c>
       <c r="O5" t="n">
         <v>0.04796000003814697</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007187287030144464</v>
+        <v>-0.007196881362172391</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 17:21:09</t>
+          <t>2026-09-02 17:23:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -33709,51 +34231,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>325.13</v>
+        <v>324.96</v>
       </c>
       <c r="F6" t="n">
-        <v>4745005629440</v>
+        <v>4742524698624</v>
       </c>
       <c r="G6" t="n">
         <v>8.710000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>9.53782</v>
+        <v>9.54013</v>
       </c>
       <c r="I6" t="n">
-        <v>37.328358</v>
+        <v>37.308838</v>
       </c>
       <c r="J6" t="n">
-        <v>34.088505</v>
+        <v>34.062428</v>
       </c>
       <c r="K6" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="L6" t="n">
-        <v>10.164464</v>
+        <v>10.15915</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02678928428628549</v>
+        <v>0.02680329886755294</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02933540429981853</v>
+        <v>0.02935785942885278</v>
       </c>
       <c r="O6" t="n">
         <v>0.04796000003814697</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01862459573832844</v>
+        <v>-0.01860214060929419</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 17:21:09</t>
+          <t>2026-09-02 17:23:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -33767,51 +34289,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>217.44</v>
+        <v>224.41</v>
       </c>
       <c r="F7" t="n">
-        <v>5250523594752</v>
+        <v>5418828431360</v>
       </c>
       <c r="G7" t="n">
-        <v>7.92</v>
+        <v>7.91</v>
       </c>
       <c r="H7" t="n">
-        <v>15.30598</v>
+        <v>15.40425</v>
       </c>
       <c r="I7" t="n">
-        <v>27.454546</v>
+        <v>28.370419</v>
       </c>
       <c r="J7" t="n">
-        <v>14.206213</v>
+        <v>14.568058</v>
       </c>
       <c r="K7" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>17.330175</v>
+        <v>17.885693</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03642384105960265</v>
+        <v>0.03524798360144379</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07039174025018397</v>
+        <v>0.06864333140234392</v>
       </c>
       <c r="O7" t="n">
         <v>0.04796000003814697</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02243174021203699</v>
+        <v>0.02068333136419695</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 17:21:09</t>
+          <t>2026-09-02 17:23:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -33825,10 +34347,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>459.61</v>
+        <v>457.06</v>
       </c>
       <c r="F8" t="n">
-        <v>750301806592</v>
+        <v>746139025408</v>
       </c>
       <c r="G8" t="n">
         <v>3.91</v>
@@ -33837,39 +34359,39 @@
         <v>15.45073</v>
       </c>
       <c r="I8" t="n">
-        <v>117.54731</v>
+        <v>116.895134</v>
       </c>
       <c r="J8" t="n">
-        <v>29.746813</v>
+        <v>29.581774</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="L8" t="n">
-        <v>18.164913</v>
+        <v>18.064133</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008507212636800767</v>
+        <v>0.008554675534940707</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03361704488588151</v>
+        <v>0.03380459895856124</v>
       </c>
       <c r="O8" t="n">
         <v>0.04796000003814697</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01434295515226547</v>
+        <v>-0.01415540107958573</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 17:21:09</t>
+          <t>2026-09-02 17:23:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -33883,51 +34405,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>369.68</v>
+        <v>367.24</v>
       </c>
       <c r="F9" t="n">
-        <v>1758782291968</v>
+        <v>1747173769216</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>6.03</v>
       </c>
       <c r="H9" t="n">
         <v>19.5728</v>
       </c>
       <c r="I9" t="n">
-        <v>61.61333</v>
+        <v>60.902153</v>
       </c>
       <c r="J9" t="n">
-        <v>18.887436</v>
+        <v>18.762774</v>
       </c>
       <c r="K9" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="L9" t="n">
-        <v>23.305935</v>
+        <v>23.152107</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01623025319194979</v>
+        <v>0.01641977998039429</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05294524994589916</v>
+        <v>0.05329702646770505</v>
       </c>
       <c r="O9" t="n">
         <v>0.04796000003814697</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004985249907752183</v>
+        <v>0.005337026429558071</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 17:21:09</t>
+          <t>2026-09-02 17:23:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -33941,10 +34463,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>80.81</v>
+        <v>82.73</v>
       </c>
       <c r="F10" t="n">
-        <v>336487940096</v>
+        <v>344482742272</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -33953,28 +34475,28 @@
         <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>25.41195</v>
+        <v>26.015724</v>
       </c>
       <c r="J10" t="n">
-        <v>21.149412</v>
+        <v>21.65191</v>
       </c>
       <c r="K10" t="n">
-        <v>1.83</v>
+        <v>1.49</v>
       </c>
       <c r="L10" t="n">
-        <v>6.956432</v>
+        <v>7.1217136</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03935156540032175</v>
+        <v>0.0384382932430799</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04728263828734067</v>
+        <v>0.04618530158346428</v>
       </c>
       <c r="O10" t="n">
         <v>0.04796000003814697</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0006773617508063004</v>
+        <v>-0.001774698454682692</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P577"/>
+  <dimension ref="A1:P586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33405,16 +33405,16 @@
         <v>10.15915</v>
       </c>
       <c r="M569" t="n">
-        <v>0.02680329886755294</v>
+        <v>0.0268032988675529</v>
       </c>
       <c r="N569" t="n">
-        <v>0.02935785942885278</v>
+        <v>0.0293578594288527</v>
       </c>
       <c r="O569" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0479600000381469</v>
       </c>
       <c r="P569" t="n">
-        <v>-0.01860214060929419</v>
+        <v>-0.0186021406092941</v>
       </c>
     </row>
     <row r="570">
@@ -33463,16 +33463,16 @@
         <v>18.064133</v>
       </c>
       <c r="M570" t="n">
-        <v>0.008554675534940707</v>
+        <v>0.008554675534940701</v>
       </c>
       <c r="N570" t="n">
-        <v>0.03380459895856124</v>
+        <v>0.0338045989585612</v>
       </c>
       <c r="O570" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0479600000381469</v>
       </c>
       <c r="P570" t="n">
-        <v>-0.01415540107958573</v>
+        <v>-0.0141554010795857</v>
       </c>
     </row>
     <row r="571">
@@ -33521,16 +33521,16 @@
         <v>3.5456553</v>
       </c>
       <c r="M571" t="n">
-        <v>0.04878814024629383</v>
+        <v>0.0487881402462938</v>
       </c>
       <c r="N571" t="n">
-        <v>0.04076311867597458</v>
+        <v>0.0407631186759745</v>
       </c>
       <c r="O571" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0479600000381469</v>
       </c>
       <c r="P571" t="n">
-        <v>-0.007196881362172391</v>
+        <v>-0.0071968813621723</v>
       </c>
     </row>
     <row r="572">
@@ -33579,16 +33579,16 @@
         <v>23.152107</v>
       </c>
       <c r="M572" t="n">
-        <v>0.01641977998039429</v>
+        <v>0.0164197799803942</v>
       </c>
       <c r="N572" t="n">
-        <v>0.05329702646770505</v>
+        <v>0.053297026467705</v>
       </c>
       <c r="O572" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0479600000381469</v>
       </c>
       <c r="P572" t="n">
-        <v>0.005337026429558071</v>
+        <v>0.005337026429558</v>
       </c>
     </row>
     <row r="573">
@@ -33637,16 +33637,16 @@
         <v>9.155457999999999</v>
       </c>
       <c r="M573" t="n">
-        <v>0.05968002876145966</v>
+        <v>0.0596800287614596</v>
       </c>
       <c r="N573" t="n">
-        <v>0.04442348253340524</v>
+        <v>0.0444234825334052</v>
       </c>
       <c r="O573" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0479600000381469</v>
       </c>
       <c r="P573" t="n">
-        <v>-0.003536517504741737</v>
+        <v>-0.0035365175047417</v>
       </c>
     </row>
     <row r="574">
@@ -33695,16 +33695,16 @@
         <v>6.616906</v>
       </c>
       <c r="M574" t="n">
-        <v>0.04478367209243485</v>
+        <v>0.0447836720924348</v>
       </c>
       <c r="N574" t="n">
-        <v>0.05896881167242979</v>
+        <v>0.0589688116724297</v>
       </c>
       <c r="O574" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0479600000381469</v>
       </c>
       <c r="P574" t="n">
-        <v>0.01100881163428281</v>
+        <v>0.0110088116342828</v>
       </c>
     </row>
     <row r="575">
@@ -33753,16 +33753,16 @@
         <v>11.117317</v>
       </c>
       <c r="M575" t="n">
-        <v>0.03610965742119883</v>
+        <v>0.0361096574211988</v>
       </c>
       <c r="N575" t="n">
-        <v>0.0474483313876253</v>
+        <v>0.0474483313876252</v>
       </c>
       <c r="O575" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0479600000381469</v>
       </c>
       <c r="P575" t="n">
-        <v>-0.000511668650521678</v>
+        <v>-0.0005116686505216</v>
       </c>
     </row>
     <row r="576">
@@ -33814,13 +33814,13 @@
         <v>0.0384382932430799</v>
       </c>
       <c r="N576" t="n">
-        <v>0.04618530158346428</v>
+        <v>0.0461853015834642</v>
       </c>
       <c r="O576" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0479600000381469</v>
       </c>
       <c r="P576" t="n">
-        <v>-0.001774698454682692</v>
+        <v>-0.0017746984546826</v>
       </c>
     </row>
     <row r="577">
@@ -33869,16 +33869,538 @@
         <v>17.885693</v>
       </c>
       <c r="M577" t="n">
-        <v>0.03524798360144379</v>
+        <v>0.0352479836014437</v>
       </c>
       <c r="N577" t="n">
-        <v>0.06864333140234392</v>
+        <v>0.0686433314023439</v>
       </c>
       <c r="O577" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0479600000381469</v>
       </c>
       <c r="P577" t="n">
-        <v>0.02068333136419695</v>
+        <v>0.0206833313641969</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:11:50</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E578" t="n">
+        <v>328.21</v>
+      </c>
+      <c r="F578" t="n">
+        <v>4789955985408</v>
+      </c>
+      <c r="G578" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H578" t="n">
+        <v>9.54013</v>
+      </c>
+      <c r="I578" t="n">
+        <v>37.681973</v>
+      </c>
+      <c r="J578" t="n">
+        <v>34.403095</v>
+      </c>
+      <c r="K578" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L578" t="n">
+        <v>10.260755</v>
+      </c>
+      <c r="M578" t="n">
+        <v>0.02653788732823498</v>
+      </c>
+      <c r="N578" t="n">
+        <v>0.0290671521282106</v>
+      </c>
+      <c r="O578" t="n">
+        <v>0.0476200008392334</v>
+      </c>
+      <c r="P578" t="n">
+        <v>-0.0185528487110228</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:11:50</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E579" t="n">
+        <v>456.16</v>
+      </c>
+      <c r="F579" t="n">
+        <v>744669773824</v>
+      </c>
+      <c r="G579" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H579" t="n">
+        <v>15.45073</v>
+      </c>
+      <c r="I579" t="n">
+        <v>116.07124</v>
+      </c>
+      <c r="J579" t="n">
+        <v>29.523523</v>
+      </c>
+      <c r="K579" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L579" t="n">
+        <v>18.028563</v>
+      </c>
+      <c r="M579" t="n">
+        <v>0.008615398105927744</v>
+      </c>
+      <c r="N579" t="n">
+        <v>0.03387129515959313</v>
+      </c>
+      <c r="O579" t="n">
+        <v>0.0476200008392334</v>
+      </c>
+      <c r="P579" t="n">
+        <v>-0.01374870567964027</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:11:50</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>258.9</v>
+      </c>
+      <c r="F580" t="n">
+        <v>2792576516096</v>
+      </c>
+      <c r="G580" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="H580" t="n">
+        <v>10.40032</v>
+      </c>
+      <c r="I580" t="n">
+        <v>20.84541</v>
+      </c>
+      <c r="J580" t="n">
+        <v>24.893465</v>
+      </c>
+      <c r="K580" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L580" t="n">
+        <v>3.6001656</v>
+      </c>
+      <c r="M580" t="n">
+        <v>0.04797219003476246</v>
+      </c>
+      <c r="N580" t="n">
+        <v>0.04017118578601778</v>
+      </c>
+      <c r="O580" t="n">
+        <v>0.0476200008392334</v>
+      </c>
+      <c r="P580" t="n">
+        <v>-0.007448815053215624</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:11:50</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E581" t="n">
+        <v>357.16</v>
+      </c>
+      <c r="F581" t="n">
+        <v>1699217408000</v>
+      </c>
+      <c r="G581" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="H581" t="n">
+        <v>19.31391</v>
+      </c>
+      <c r="I581" t="n">
+        <v>45.672634</v>
+      </c>
+      <c r="J581" t="n">
+        <v>18.492373</v>
+      </c>
+      <c r="K581" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L581" t="n">
+        <v>22.51663</v>
+      </c>
+      <c r="M581" t="n">
+        <v>0.02189494904244596</v>
+      </c>
+      <c r="N581" t="n">
+        <v>0.05407635233508791</v>
+      </c>
+      <c r="O581" t="n">
+        <v>0.0476200008392334</v>
+      </c>
+      <c r="P581" t="n">
+        <v>0.006456351495854509</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:11:50</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>339.08</v>
+      </c>
+      <c r="F582" t="n">
+        <v>4146926190592</v>
+      </c>
+      <c r="G582" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H582" t="n">
+        <v>14.82767</v>
+      </c>
+      <c r="I582" t="n">
+        <v>17.013546</v>
+      </c>
+      <c r="J582" t="n">
+        <v>22.868055</v>
+      </c>
+      <c r="K582" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L582" t="n">
+        <v>9.300836</v>
+      </c>
+      <c r="M582" t="n">
+        <v>0.05877668986669812</v>
+      </c>
+      <c r="N582" t="n">
+        <v>0.04372911997168809</v>
+      </c>
+      <c r="O582" t="n">
+        <v>0.0476200008392334</v>
+      </c>
+      <c r="P582" t="n">
+        <v>-0.003890880867545306</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:11:50</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E583" t="n">
+        <v>610.6799999999999</v>
+      </c>
+      <c r="F583" t="n">
+        <v>1555711000576</v>
+      </c>
+      <c r="G583" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="H583" t="n">
+        <v>34.95966</v>
+      </c>
+      <c r="I583" t="n">
+        <v>22.99247</v>
+      </c>
+      <c r="J583" t="n">
+        <v>17.468134</v>
+      </c>
+      <c r="K583" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L583" t="n">
+        <v>6.8159103</v>
+      </c>
+      <c r="M583" t="n">
+        <v>0.04349250016375188</v>
+      </c>
+      <c r="N583" t="n">
+        <v>0.05724710159166831</v>
+      </c>
+      <c r="O583" t="n">
+        <v>0.0476200008392334</v>
+      </c>
+      <c r="P583" t="n">
+        <v>0.009627100752434906</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:11:50</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E584" t="n">
+        <v>510.12</v>
+      </c>
+      <c r="F584" t="n">
+        <v>3787919458304</v>
+      </c>
+      <c r="G584" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H584" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I584" t="n">
+        <v>28.434782</v>
+      </c>
+      <c r="J584" t="n">
+        <v>21.639755</v>
+      </c>
+      <c r="K584" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L584" t="n">
+        <v>11.414931</v>
+      </c>
+      <c r="M584" t="n">
+        <v>0.03516819571865443</v>
+      </c>
+      <c r="N584" t="n">
+        <v>0.04621124441307928</v>
+      </c>
+      <c r="O584" t="n">
+        <v>0.0476200008392334</v>
+      </c>
+      <c r="P584" t="n">
+        <v>-0.001408756426154123</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:11:50</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E585" t="n">
+        <v>82.67</v>
+      </c>
+      <c r="F585" t="n">
+        <v>344232886272</v>
+      </c>
+      <c r="G585" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H585" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I585" t="n">
+        <v>25.996855</v>
+      </c>
+      <c r="J585" t="n">
+        <v>21.636208</v>
+      </c>
+      <c r="K585" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L585" t="n">
+        <v>7.116548</v>
+      </c>
+      <c r="M585" t="n">
+        <v>0.03846619087940002</v>
+      </c>
+      <c r="N585" t="n">
+        <v>0.04621882182170074</v>
+      </c>
+      <c r="O585" t="n">
+        <v>0.0476200008392334</v>
+      </c>
+      <c r="P585" t="n">
+        <v>-0.001401179017532665</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:11:50</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>228.45</v>
+      </c>
+      <c r="F586" t="n">
+        <v>5516382175232</v>
+      </c>
+      <c r="G586" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H586" t="n">
+        <v>15.40425</v>
+      </c>
+      <c r="I586" t="n">
+        <v>28.91772</v>
+      </c>
+      <c r="J586" t="n">
+        <v>14.830322</v>
+      </c>
+      <c r="K586" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L586" t="n">
+        <v>18.207684</v>
+      </c>
+      <c r="M586" t="n">
+        <v>0.03458087108776538</v>
+      </c>
+      <c r="N586" t="n">
+        <v>0.06742941562705188</v>
+      </c>
+      <c r="O586" t="n">
+        <v>0.0476200008392334</v>
+      </c>
+      <c r="P586" t="n">
+        <v>0.01980941478781847</v>
       </c>
     </row>
   </sheetData>
@@ -33980,12 +34502,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 17:23:40</t>
+          <t>2026-09-03 17:11:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -33999,51 +34521,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>333.78</v>
+        <v>339.08</v>
       </c>
       <c r="F2" t="n">
-        <v>4082107678720</v>
+        <v>4146926190592</v>
       </c>
       <c r="G2" t="n">
-        <v>19.92</v>
+        <v>19.93</v>
       </c>
       <c r="H2" t="n">
         <v>14.82767</v>
       </c>
       <c r="I2" t="n">
-        <v>16.756023</v>
+        <v>17.013546</v>
       </c>
       <c r="J2" t="n">
-        <v>22.510616</v>
+        <v>22.868055</v>
       </c>
       <c r="K2" t="n">
         <v>1.23</v>
       </c>
       <c r="L2" t="n">
-        <v>9.155457999999999</v>
+        <v>9.300836</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05968002876145966</v>
+        <v>0.05877668986669812</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04442348253340524</v>
+        <v>0.04372911997168809</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0476200008392334</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003536517504741737</v>
+        <v>-0.003890880867545306</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 17:23:40</t>
+          <t>2026-09-03 17:11:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -34057,10 +34579,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>496.82</v>
+        <v>510.12</v>
       </c>
       <c r="F3" t="n">
-        <v>3689159589888</v>
+        <v>3787919458304</v>
       </c>
       <c r="G3" t="n">
         <v>17.94</v>
@@ -34069,39 +34591,39 @@
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>27.693422</v>
+        <v>28.434782</v>
       </c>
       <c r="J3" t="n">
-        <v>21.075556</v>
+        <v>21.639755</v>
       </c>
       <c r="K3" t="n">
         <v>1.63</v>
       </c>
       <c r="L3" t="n">
-        <v>11.117317</v>
+        <v>11.414931</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03610965742119883</v>
+        <v>0.03516819571865443</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0474483313876253</v>
+        <v>0.04621124441307928</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0476200008392334</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.000511668650521678</v>
+        <v>-0.001408756426154123</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 17:23:40</t>
+          <t>2026-09-03 17:11:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -34115,51 +34637,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>592.85</v>
+        <v>610.6799999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1510288916480</v>
+        <v>1555711000576</v>
       </c>
       <c r="G4" t="n">
-        <v>26.55</v>
+        <v>26.56</v>
       </c>
       <c r="H4" t="n">
         <v>34.95966</v>
       </c>
       <c r="I4" t="n">
-        <v>22.329567</v>
+        <v>22.99247</v>
       </c>
       <c r="J4" t="n">
-        <v>16.958117</v>
+        <v>17.468134</v>
       </c>
       <c r="K4" t="n">
         <v>0.77</v>
       </c>
       <c r="L4" t="n">
-        <v>6.616906</v>
+        <v>6.8159103</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04478367209243485</v>
+        <v>0.04349250016375188</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05896881167242979</v>
+        <v>0.05724710159166831</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0476200008392334</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01100881163428281</v>
+        <v>0.009627100752434906</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 17:23:40</t>
+          <t>2026-09-03 17:11:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -34173,51 +34695,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>254.98</v>
+        <v>258.9</v>
       </c>
       <c r="F5" t="n">
-        <v>2750293999616</v>
+        <v>2792576516096</v>
       </c>
       <c r="G5" t="n">
-        <v>12.44</v>
+        <v>12.42</v>
       </c>
       <c r="H5" t="n">
-        <v>10.39378</v>
+        <v>10.40032</v>
       </c>
       <c r="I5" t="n">
-        <v>20.496784</v>
+        <v>20.84541</v>
       </c>
       <c r="J5" t="n">
-        <v>24.53198</v>
+        <v>24.893465</v>
       </c>
       <c r="K5" t="n">
         <v>1.49</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5456553</v>
+        <v>3.6001656</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04878814024629383</v>
+        <v>0.04797219003476246</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04076311867597458</v>
+        <v>0.04017118578601778</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0476200008392334</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007196881362172391</v>
+        <v>-0.007448815053215624</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 17:23:40</t>
+          <t>2026-09-03 17:11:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -34231,10 +34753,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>324.96</v>
+        <v>328.21</v>
       </c>
       <c r="F6" t="n">
-        <v>4742524698624</v>
+        <v>4789955985408</v>
       </c>
       <c r="G6" t="n">
         <v>8.710000000000001</v>
@@ -34243,39 +34765,39 @@
         <v>9.54013</v>
       </c>
       <c r="I6" t="n">
-        <v>37.308838</v>
+        <v>37.681973</v>
       </c>
       <c r="J6" t="n">
-        <v>34.062428</v>
+        <v>34.403095</v>
       </c>
       <c r="K6" t="n">
         <v>2.56</v>
       </c>
       <c r="L6" t="n">
-        <v>10.15915</v>
+        <v>10.260755</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02680329886755294</v>
+        <v>0.02653788732823498</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02935785942885278</v>
+        <v>0.0290671521282106</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0476200008392334</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01860214060929419</v>
+        <v>-0.0185528487110228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 17:23:40</t>
+          <t>2026-09-03 17:11:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -34289,51 +34811,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224.41</v>
+        <v>228.45</v>
       </c>
       <c r="F7" t="n">
-        <v>5418828431360</v>
+        <v>5516382175232</v>
       </c>
       <c r="G7" t="n">
-        <v>7.91</v>
+        <v>7.9</v>
       </c>
       <c r="H7" t="n">
         <v>15.40425</v>
       </c>
       <c r="I7" t="n">
-        <v>28.370419</v>
+        <v>28.91772</v>
       </c>
       <c r="J7" t="n">
-        <v>14.568058</v>
+        <v>14.830322</v>
       </c>
       <c r="K7" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>17.885693</v>
+        <v>18.207684</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03524798360144379</v>
+        <v>0.03458087108776538</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06864333140234392</v>
+        <v>0.06742941562705188</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0476200008392334</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02068333136419695</v>
+        <v>0.01980941478781847</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 17:23:40</t>
+          <t>2026-09-03 17:11:50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -34347,51 +34869,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>457.06</v>
+        <v>456.16</v>
       </c>
       <c r="F8" t="n">
-        <v>746139025408</v>
+        <v>744669773824</v>
       </c>
       <c r="G8" t="n">
-        <v>3.91</v>
+        <v>3.93</v>
       </c>
       <c r="H8" t="n">
         <v>15.45073</v>
       </c>
       <c r="I8" t="n">
-        <v>116.895134</v>
+        <v>116.07124</v>
       </c>
       <c r="J8" t="n">
-        <v>29.581774</v>
+        <v>29.523523</v>
       </c>
       <c r="K8" t="n">
         <v>0.48</v>
       </c>
       <c r="L8" t="n">
-        <v>18.064133</v>
+        <v>18.028563</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008554675534940707</v>
+        <v>0.008615398105927744</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03380459895856124</v>
+        <v>0.03387129515959313</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0476200008392334</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01415540107958573</v>
+        <v>-0.01374870567964027</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 17:23:40</t>
+          <t>2026-09-03 17:11:50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -34405,51 +34927,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>367.24</v>
+        <v>357.16</v>
       </c>
       <c r="F9" t="n">
-        <v>1747173769216</v>
+        <v>1699217408000</v>
       </c>
       <c r="G9" t="n">
-        <v>6.03</v>
+        <v>7.82</v>
       </c>
       <c r="H9" t="n">
-        <v>19.5728</v>
+        <v>19.31391</v>
       </c>
       <c r="I9" t="n">
-        <v>60.902153</v>
+        <v>45.672634</v>
       </c>
       <c r="J9" t="n">
-        <v>18.762774</v>
+        <v>18.492373</v>
       </c>
       <c r="K9" t="n">
         <v>0.42</v>
       </c>
       <c r="L9" t="n">
-        <v>23.152107</v>
+        <v>22.51663</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01641977998039429</v>
+        <v>0.02189494904244596</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05329702646770505</v>
+        <v>0.05407635233508791</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0476200008392334</v>
       </c>
       <c r="P9" t="n">
-        <v>0.005337026429558071</v>
+        <v>0.006456351495854509</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 17:23:40</t>
+          <t>2026-09-03 17:11:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -34463,10 +34985,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>82.73</v>
+        <v>82.67</v>
       </c>
       <c r="F10" t="n">
-        <v>344482742272</v>
+        <v>344232886272</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -34475,28 +34997,28 @@
         <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>26.015724</v>
+        <v>25.996855</v>
       </c>
       <c r="J10" t="n">
-        <v>21.65191</v>
+        <v>21.636208</v>
       </c>
       <c r="K10" t="n">
         <v>1.49</v>
       </c>
       <c r="L10" t="n">
-        <v>7.1217136</v>
+        <v>7.116548</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0384382932430799</v>
+        <v>0.03846619087940002</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04618530158346428</v>
+        <v>0.04621882182170074</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04796000003814697</v>
+        <v>0.0476200008392334</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.001774698454682692</v>
+        <v>-0.001401179017532665</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P586"/>
+  <dimension ref="A1:P595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33927,10 +33927,10 @@
         <v>10.260755</v>
       </c>
       <c r="M578" t="n">
-        <v>0.02653788732823498</v>
+        <v>0.0265378873282349</v>
       </c>
       <c r="N578" t="n">
-        <v>0.0290671521282106</v>
+        <v>0.0290671521282105</v>
       </c>
       <c r="O578" t="n">
         <v>0.0476200008392334</v>
@@ -33985,16 +33985,16 @@
         <v>18.028563</v>
       </c>
       <c r="M579" t="n">
-        <v>0.008615398105927744</v>
+        <v>0.0086153981059277</v>
       </c>
       <c r="N579" t="n">
-        <v>0.03387129515959313</v>
+        <v>0.0338712951595931</v>
       </c>
       <c r="O579" t="n">
         <v>0.0476200008392334</v>
       </c>
       <c r="P579" t="n">
-        <v>-0.01374870567964027</v>
+        <v>-0.0137487056796402</v>
       </c>
     </row>
     <row r="580">
@@ -34043,16 +34043,16 @@
         <v>3.6001656</v>
       </c>
       <c r="M580" t="n">
-        <v>0.04797219003476246</v>
+        <v>0.0479721900347624</v>
       </c>
       <c r="N580" t="n">
-        <v>0.04017118578601778</v>
+        <v>0.0401711857860177</v>
       </c>
       <c r="O580" t="n">
         <v>0.0476200008392334</v>
       </c>
       <c r="P580" t="n">
-        <v>-0.007448815053215624</v>
+        <v>-0.0074488150532156</v>
       </c>
     </row>
     <row r="581">
@@ -34101,16 +34101,16 @@
         <v>22.51663</v>
       </c>
       <c r="M581" t="n">
-        <v>0.02189494904244596</v>
+        <v>0.0218949490424459</v>
       </c>
       <c r="N581" t="n">
-        <v>0.05407635233508791</v>
+        <v>0.0540763523350879</v>
       </c>
       <c r="O581" t="n">
         <v>0.0476200008392334</v>
       </c>
       <c r="P581" t="n">
-        <v>0.006456351495854509</v>
+        <v>0.0064563514958545</v>
       </c>
     </row>
     <row r="582">
@@ -34159,16 +34159,16 @@
         <v>9.300836</v>
       </c>
       <c r="M582" t="n">
-        <v>0.05877668986669812</v>
+        <v>0.0587766898666981</v>
       </c>
       <c r="N582" t="n">
-        <v>0.04372911997168809</v>
+        <v>0.043729119971688</v>
       </c>
       <c r="O582" t="n">
         <v>0.0476200008392334</v>
       </c>
       <c r="P582" t="n">
-        <v>-0.003890880867545306</v>
+        <v>-0.0038908808675453</v>
       </c>
     </row>
     <row r="583">
@@ -34217,16 +34217,16 @@
         <v>6.8159103</v>
       </c>
       <c r="M583" t="n">
-        <v>0.04349250016375188</v>
+        <v>0.0434925001637518</v>
       </c>
       <c r="N583" t="n">
-        <v>0.05724710159166831</v>
+        <v>0.0572471015916683</v>
       </c>
       <c r="O583" t="n">
         <v>0.0476200008392334</v>
       </c>
       <c r="P583" t="n">
-        <v>0.009627100752434906</v>
+        <v>0.0096271007524349</v>
       </c>
     </row>
     <row r="584">
@@ -34275,16 +34275,16 @@
         <v>11.414931</v>
       </c>
       <c r="M584" t="n">
-        <v>0.03516819571865443</v>
+        <v>0.0351681957186544</v>
       </c>
       <c r="N584" t="n">
-        <v>0.04621124441307928</v>
+        <v>0.0462112444130792</v>
       </c>
       <c r="O584" t="n">
         <v>0.0476200008392334</v>
       </c>
       <c r="P584" t="n">
-        <v>-0.001408756426154123</v>
+        <v>-0.0014087564261541</v>
       </c>
     </row>
     <row r="585">
@@ -34333,16 +34333,16 @@
         <v>7.116548</v>
       </c>
       <c r="M585" t="n">
-        <v>0.03846619087940002</v>
+        <v>0.0384661908794</v>
       </c>
       <c r="N585" t="n">
-        <v>0.04621882182170074</v>
+        <v>0.0462188218217007</v>
       </c>
       <c r="O585" t="n">
         <v>0.0476200008392334</v>
       </c>
       <c r="P585" t="n">
-        <v>-0.001401179017532665</v>
+        <v>-0.0014011790175326</v>
       </c>
     </row>
     <row r="586">
@@ -34391,16 +34391,538 @@
         <v>18.207684</v>
       </c>
       <c r="M586" t="n">
-        <v>0.03458087108776538</v>
+        <v>0.0345808710877653</v>
       </c>
       <c r="N586" t="n">
-        <v>0.06742941562705188</v>
+        <v>0.06742941562705181</v>
       </c>
       <c r="O586" t="n">
         <v>0.0476200008392334</v>
       </c>
       <c r="P586" t="n">
-        <v>0.01980941478781847</v>
+        <v>0.0198094147878184</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>2026-09-04 17:12:50</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>319.97</v>
+      </c>
+      <c r="F587" t="n">
+        <v>4669700046848</v>
+      </c>
+      <c r="G587" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H587" t="n">
+        <v>9.574350000000001</v>
+      </c>
+      <c r="I587" t="n">
+        <v>36.65178</v>
+      </c>
+      <c r="J587" t="n">
+        <v>33.4195</v>
+      </c>
+      <c r="K587" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="L587" t="n">
+        <v>10.003149</v>
+      </c>
+      <c r="M587" t="n">
+        <v>0.02728380785698659</v>
+      </c>
+      <c r="N587" t="n">
+        <v>0.02992264899834359</v>
+      </c>
+      <c r="O587" t="n">
+        <v>0.04783999919891357</v>
+      </c>
+      <c r="P587" t="n">
+        <v>-0.01791735020056998</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>2026-09-04 17:12:50</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>477.57</v>
+      </c>
+      <c r="F588" t="n">
+        <v>779621105664</v>
+      </c>
+      <c r="G588" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H588" t="n">
+        <v>15.45073</v>
+      </c>
+      <c r="I588" t="n">
+        <v>121.82908</v>
+      </c>
+      <c r="J588" t="n">
+        <v>30.90922</v>
+      </c>
+      <c r="K588" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L588" t="n">
+        <v>18.874739</v>
+      </c>
+      <c r="M588" t="n">
+        <v>0.008208220784387628</v>
+      </c>
+      <c r="N588" t="n">
+        <v>0.03235280691835752</v>
+      </c>
+      <c r="O588" t="n">
+        <v>0.04783999919891357</v>
+      </c>
+      <c r="P588" t="n">
+        <v>-0.01548719228055605</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>2026-09-04 17:12:50</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E589" t="n">
+        <v>258.51</v>
+      </c>
+      <c r="F589" t="n">
+        <v>2788369891328</v>
+      </c>
+      <c r="G589" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H589" t="n">
+        <v>10.40032</v>
+      </c>
+      <c r="I589" t="n">
+        <v>20.797264</v>
+      </c>
+      <c r="J589" t="n">
+        <v>24.855967</v>
+      </c>
+      <c r="K589" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L589" t="n">
+        <v>3.5947423</v>
+      </c>
+      <c r="M589" t="n">
+        <v>0.04808324629608139</v>
+      </c>
+      <c r="N589" t="n">
+        <v>0.0402317898727322</v>
+      </c>
+      <c r="O589" t="n">
+        <v>0.04783999919891357</v>
+      </c>
+      <c r="P589" t="n">
+        <v>-0.007608209326181371</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>2026-09-04 17:12:50</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E590" t="n">
+        <v>357.895</v>
+      </c>
+      <c r="F590" t="n">
+        <v>1702714146816</v>
+      </c>
+      <c r="G590" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="H590" t="n">
+        <v>19.37208</v>
+      </c>
+      <c r="I590" t="n">
+        <v>45.533714</v>
+      </c>
+      <c r="J590" t="n">
+        <v>18.474785</v>
+      </c>
+      <c r="K590" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L590" t="n">
+        <v>19.10929</v>
+      </c>
+      <c r="M590" t="n">
+        <v>0.02196174855753783</v>
+      </c>
+      <c r="N590" t="n">
+        <v>0.05412783078835972</v>
+      </c>
+      <c r="O590" t="n">
+        <v>0.04783999919891357</v>
+      </c>
+      <c r="P590" t="n">
+        <v>0.006287831589446145</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>2026-09-04 17:12:50</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E591" t="n">
+        <v>335.31</v>
+      </c>
+      <c r="F591" t="n">
+        <v>4100819517440</v>
+      </c>
+      <c r="G591" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="H591" t="n">
+        <v>14.85423</v>
+      </c>
+      <c r="I591" t="n">
+        <v>16.815947</v>
+      </c>
+      <c r="J591" t="n">
+        <v>22.573368</v>
+      </c>
+      <c r="K591" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L591" t="n">
+        <v>9.197426</v>
+      </c>
+      <c r="M591" t="n">
+        <v>0.05946735856371716</v>
+      </c>
+      <c r="N591" t="n">
+        <v>0.04429999105305538</v>
+      </c>
+      <c r="O591" t="n">
+        <v>0.04783999919891357</v>
+      </c>
+      <c r="P591" t="n">
+        <v>-0.003540008145858198</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>2026-09-04 17:12:50</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E592" t="n">
+        <v>616.77</v>
+      </c>
+      <c r="F592" t="n">
+        <v>1571225468928</v>
+      </c>
+      <c r="G592" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="H592" t="n">
+        <v>34.95966</v>
+      </c>
+      <c r="I592" t="n">
+        <v>23.221764</v>
+      </c>
+      <c r="J592" t="n">
+        <v>17.642334</v>
+      </c>
+      <c r="K592" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L592" t="n">
+        <v>6.8838825</v>
+      </c>
+      <c r="M592" t="n">
+        <v>0.04306305429900936</v>
+      </c>
+      <c r="N592" t="n">
+        <v>0.05668184250206722</v>
+      </c>
+      <c r="O592" t="n">
+        <v>0.04783999919891357</v>
+      </c>
+      <c r="P592" t="n">
+        <v>0.00884184330315365</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>2026-09-04 17:12:50</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E593" t="n">
+        <v>499.7</v>
+      </c>
+      <c r="F593" t="n">
+        <v>3710545297408</v>
+      </c>
+      <c r="G593" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="H593" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I593" t="n">
+        <v>27.822943</v>
+      </c>
+      <c r="J593" t="n">
+        <v>21.19773</v>
+      </c>
+      <c r="K593" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L593" t="n">
+        <v>11.181764</v>
+      </c>
+      <c r="M593" t="n">
+        <v>0.03594156493896338</v>
+      </c>
+      <c r="N593" t="n">
+        <v>0.04717486491895137</v>
+      </c>
+      <c r="O593" t="n">
+        <v>0.04783999919891357</v>
+      </c>
+      <c r="P593" t="n">
+        <v>-0.000665134279962204</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>2026-09-04 17:12:50</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E594" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="F594" t="n">
+        <v>325828280320</v>
+      </c>
+      <c r="G594" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H594" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I594" t="n">
+        <v>24.606918</v>
+      </c>
+      <c r="J594" t="n">
+        <v>20.479414</v>
+      </c>
+      <c r="K594" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L594" t="n">
+        <v>6.7360578</v>
+      </c>
+      <c r="M594" t="n">
+        <v>0.04063897763578275</v>
+      </c>
+      <c r="N594" t="n">
+        <v>0.04882952076677316</v>
+      </c>
+      <c r="O594" t="n">
+        <v>0.04783999919891357</v>
+      </c>
+      <c r="P594" t="n">
+        <v>0.0009895215678595859</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>2026-09-04 17:12:50</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E595" t="n">
+        <v>230.36</v>
+      </c>
+      <c r="F595" t="n">
+        <v>5562502742016</v>
+      </c>
+      <c r="G595" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H595" t="n">
+        <v>15.4581</v>
+      </c>
+      <c r="I595" t="n">
+        <v>29.159492</v>
+      </c>
+      <c r="J595" t="n">
+        <v>14.902219</v>
+      </c>
+      <c r="K595" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L595" t="n">
+        <v>18.359913</v>
+      </c>
+      <c r="M595" t="n">
+        <v>0.03429414828963362</v>
+      </c>
+      <c r="N595" t="n">
+        <v>0.06710409793366903</v>
+      </c>
+      <c r="O595" t="n">
+        <v>0.04783999919891357</v>
+      </c>
+      <c r="P595" t="n">
+        <v>0.01926409873475546</v>
       </c>
     </row>
   </sheetData>
@@ -34502,12 +35024,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 17:11:50</t>
+          <t>2026-09-04 17:12:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -34521,51 +35043,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>339.08</v>
+        <v>335.31</v>
       </c>
       <c r="F2" t="n">
-        <v>4146926190592</v>
+        <v>4100819517440</v>
       </c>
       <c r="G2" t="n">
-        <v>19.93</v>
+        <v>19.94</v>
       </c>
       <c r="H2" t="n">
-        <v>14.82767</v>
+        <v>14.85423</v>
       </c>
       <c r="I2" t="n">
-        <v>17.013546</v>
+        <v>16.815947</v>
       </c>
       <c r="J2" t="n">
-        <v>22.868055</v>
+        <v>22.573368</v>
       </c>
       <c r="K2" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="L2" t="n">
-        <v>9.300836</v>
+        <v>9.197426</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05877668986669812</v>
+        <v>0.05946735856371716</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04372911997168809</v>
+        <v>0.04429999105305538</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0476200008392334</v>
+        <v>0.04783999919891357</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003890880867545306</v>
+        <v>-0.003540008145858198</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 17:11:50</t>
+          <t>2026-09-04 17:12:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -34579,51 +35101,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510.12</v>
+        <v>499.7</v>
       </c>
       <c r="F3" t="n">
-        <v>3787919458304</v>
+        <v>3710545297408</v>
       </c>
       <c r="G3" t="n">
-        <v>17.94</v>
+        <v>17.96</v>
       </c>
       <c r="H3" t="n">
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>28.434782</v>
+        <v>27.822943</v>
       </c>
       <c r="J3" t="n">
-        <v>21.639755</v>
+        <v>21.19773</v>
       </c>
       <c r="K3" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="L3" t="n">
-        <v>11.414931</v>
+        <v>11.181764</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03516819571865443</v>
+        <v>0.03594156493896338</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04621124441307928</v>
+        <v>0.04717486491895137</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0476200008392334</v>
+        <v>0.04783999919891357</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.001408756426154123</v>
+        <v>-0.000665134279962204</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 17:11:50</t>
+          <t>2026-09-04 17:12:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -34637,10 +35159,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>610.6799999999999</v>
+        <v>616.77</v>
       </c>
       <c r="F4" t="n">
-        <v>1555711000576</v>
+        <v>1571225468928</v>
       </c>
       <c r="G4" t="n">
         <v>26.56</v>
@@ -34649,39 +35171,39 @@
         <v>34.95966</v>
       </c>
       <c r="I4" t="n">
-        <v>22.99247</v>
+        <v>23.221764</v>
       </c>
       <c r="J4" t="n">
-        <v>17.468134</v>
+        <v>17.642334</v>
       </c>
       <c r="K4" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>6.8159103</v>
+        <v>6.8838825</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04349250016375188</v>
+        <v>0.04306305429900936</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05724710159166831</v>
+        <v>0.05668184250206722</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0476200008392334</v>
+        <v>0.04783999919891357</v>
       </c>
       <c r="P4" t="n">
-        <v>0.009627100752434906</v>
+        <v>0.00884184330315365</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 17:11:50</t>
+          <t>2026-09-04 17:12:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -34695,51 +35217,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>258.9</v>
+        <v>258.51</v>
       </c>
       <c r="F5" t="n">
-        <v>2792576516096</v>
+        <v>2788369891328</v>
       </c>
       <c r="G5" t="n">
-        <v>12.42</v>
+        <v>12.43</v>
       </c>
       <c r="H5" t="n">
         <v>10.40032</v>
       </c>
       <c r="I5" t="n">
-        <v>20.84541</v>
+        <v>20.797264</v>
       </c>
       <c r="J5" t="n">
-        <v>24.893465</v>
+        <v>24.855967</v>
       </c>
       <c r="K5" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6001656</v>
+        <v>3.5947423</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04797219003476246</v>
+        <v>0.04808324629608139</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04017118578601778</v>
+        <v>0.0402317898727322</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0476200008392334</v>
+        <v>0.04783999919891357</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007448815053215624</v>
+        <v>-0.007608209326181371</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 17:11:50</t>
+          <t>2026-09-04 17:12:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -34753,51 +35275,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>328.21</v>
+        <v>319.97</v>
       </c>
       <c r="F6" t="n">
-        <v>4789955985408</v>
+        <v>4669700046848</v>
       </c>
       <c r="G6" t="n">
-        <v>8.710000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="H6" t="n">
-        <v>9.54013</v>
+        <v>9.574350000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>37.681973</v>
+        <v>36.65178</v>
       </c>
       <c r="J6" t="n">
-        <v>34.403095</v>
+        <v>33.4195</v>
       </c>
       <c r="K6" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="L6" t="n">
-        <v>10.260755</v>
+        <v>10.003149</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02653788732823498</v>
+        <v>0.02728380785698659</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0290671521282106</v>
+        <v>0.02992264899834359</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0476200008392334</v>
+        <v>0.04783999919891357</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0185528487110228</v>
+        <v>-0.01791735020056998</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 17:11:50</t>
+          <t>2026-09-04 17:12:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -34811,51 +35333,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228.45</v>
+        <v>230.36</v>
       </c>
       <c r="F7" t="n">
-        <v>5516382175232</v>
+        <v>5562502742016</v>
       </c>
       <c r="G7" t="n">
         <v>7.9</v>
       </c>
       <c r="H7" t="n">
-        <v>15.40425</v>
+        <v>15.4581</v>
       </c>
       <c r="I7" t="n">
-        <v>28.91772</v>
+        <v>29.159492</v>
       </c>
       <c r="J7" t="n">
-        <v>14.830322</v>
+        <v>14.902219</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="L7" t="n">
-        <v>18.207684</v>
+        <v>18.359913</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03458087108776538</v>
+        <v>0.03429414828963362</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06742941562705188</v>
+        <v>0.06710409793366903</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0476200008392334</v>
+        <v>0.04783999919891357</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01980941478781847</v>
+        <v>0.01926409873475546</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 17:11:50</t>
+          <t>2026-09-04 17:12:50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -34869,51 +35391,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>456.16</v>
+        <v>477.57</v>
       </c>
       <c r="F8" t="n">
-        <v>744669773824</v>
+        <v>779621105664</v>
       </c>
       <c r="G8" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="H8" t="n">
         <v>15.45073</v>
       </c>
       <c r="I8" t="n">
-        <v>116.07124</v>
+        <v>121.82908</v>
       </c>
       <c r="J8" t="n">
-        <v>29.523523</v>
+        <v>30.90922</v>
       </c>
       <c r="K8" t="n">
         <v>0.48</v>
       </c>
       <c r="L8" t="n">
-        <v>18.028563</v>
+        <v>18.874739</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008615398105927744</v>
+        <v>0.008208220784387628</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03387129515959313</v>
+        <v>0.03235280691835752</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0476200008392334</v>
+        <v>0.04783999919891357</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01374870567964027</v>
+        <v>-0.01548719228055605</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 17:11:50</t>
+          <t>2026-09-04 17:12:50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -34927,51 +35449,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>357.16</v>
+        <v>357.895</v>
       </c>
       <c r="F9" t="n">
-        <v>1699217408000</v>
+        <v>1702714146816</v>
       </c>
       <c r="G9" t="n">
-        <v>7.82</v>
+        <v>7.86</v>
       </c>
       <c r="H9" t="n">
-        <v>19.31391</v>
+        <v>19.37208</v>
       </c>
       <c r="I9" t="n">
-        <v>45.672634</v>
+        <v>45.533714</v>
       </c>
       <c r="J9" t="n">
-        <v>18.492373</v>
+        <v>18.474785</v>
       </c>
       <c r="K9" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="L9" t="n">
-        <v>22.51663</v>
+        <v>19.10929</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02189494904244596</v>
+        <v>0.02196174855753783</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05407635233508791</v>
+        <v>0.05412783078835972</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0476200008392334</v>
+        <v>0.04783999919891357</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006456351495854509</v>
+        <v>0.006287831589446145</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 17:11:50</t>
+          <t>2026-09-04 17:12:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -34985,10 +35507,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>82.67</v>
+        <v>78.25</v>
       </c>
       <c r="F10" t="n">
-        <v>344232886272</v>
+        <v>325828280320</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -34997,28 +35519,28 @@
         <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>25.996855</v>
+        <v>24.606918</v>
       </c>
       <c r="J10" t="n">
-        <v>21.636208</v>
+        <v>20.479414</v>
       </c>
       <c r="K10" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="L10" t="n">
-        <v>7.116548</v>
+        <v>6.7360578</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03846619087940002</v>
+        <v>0.04063897763578275</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04621882182170074</v>
+        <v>0.04882952076677316</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0476200008392334</v>
+        <v>0.04783999919891357</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.001401179017532665</v>
+        <v>0.0009895215678595859</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P595"/>
+  <dimension ref="A1:P604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34449,16 +34449,16 @@
         <v>10.003149</v>
       </c>
       <c r="M587" t="n">
-        <v>0.02728380785698659</v>
+        <v>0.0272838078569865</v>
       </c>
       <c r="N587" t="n">
-        <v>0.02992264899834359</v>
+        <v>0.0299226489983435</v>
       </c>
       <c r="O587" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.0478399991989135</v>
       </c>
       <c r="P587" t="n">
-        <v>-0.01791735020056998</v>
+        <v>-0.0179173502005699</v>
       </c>
     </row>
     <row r="588">
@@ -34507,16 +34507,16 @@
         <v>18.874739</v>
       </c>
       <c r="M588" t="n">
-        <v>0.008208220784387628</v>
+        <v>0.0082082207843876</v>
       </c>
       <c r="N588" t="n">
-        <v>0.03235280691835752</v>
+        <v>0.0323528069183575</v>
       </c>
       <c r="O588" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.0478399991989135</v>
       </c>
       <c r="P588" t="n">
-        <v>-0.01548719228055605</v>
+        <v>-0.015487192280556</v>
       </c>
     </row>
     <row r="589">
@@ -34565,16 +34565,16 @@
         <v>3.5947423</v>
       </c>
       <c r="M589" t="n">
-        <v>0.04808324629608139</v>
+        <v>0.0480832462960813</v>
       </c>
       <c r="N589" t="n">
         <v>0.0402317898727322</v>
       </c>
       <c r="O589" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.0478399991989135</v>
       </c>
       <c r="P589" t="n">
-        <v>-0.007608209326181371</v>
+        <v>-0.0076082093261813</v>
       </c>
     </row>
     <row r="590">
@@ -34623,16 +34623,16 @@
         <v>19.10929</v>
       </c>
       <c r="M590" t="n">
-        <v>0.02196174855753783</v>
+        <v>0.0219617485575378</v>
       </c>
       <c r="N590" t="n">
-        <v>0.05412783078835972</v>
+        <v>0.0541278307883597</v>
       </c>
       <c r="O590" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.0478399991989135</v>
       </c>
       <c r="P590" t="n">
-        <v>0.006287831589446145</v>
+        <v>0.0062878315894461</v>
       </c>
     </row>
     <row r="591">
@@ -34681,16 +34681,16 @@
         <v>9.197426</v>
       </c>
       <c r="M591" t="n">
-        <v>0.05946735856371716</v>
+        <v>0.0594673585637171</v>
       </c>
       <c r="N591" t="n">
-        <v>0.04429999105305538</v>
+        <v>0.0442999910530553</v>
       </c>
       <c r="O591" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.0478399991989135</v>
       </c>
       <c r="P591" t="n">
-        <v>-0.003540008145858198</v>
+        <v>-0.0035400081458581</v>
       </c>
     </row>
     <row r="592">
@@ -34739,16 +34739,16 @@
         <v>6.8838825</v>
       </c>
       <c r="M592" t="n">
-        <v>0.04306305429900936</v>
+        <v>0.0430630542990093</v>
       </c>
       <c r="N592" t="n">
-        <v>0.05668184250206722</v>
+        <v>0.0566818425020672</v>
       </c>
       <c r="O592" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.0478399991989135</v>
       </c>
       <c r="P592" t="n">
-        <v>0.00884184330315365</v>
+        <v>0.0088418433031536</v>
       </c>
     </row>
     <row r="593">
@@ -34797,16 +34797,16 @@
         <v>11.181764</v>
       </c>
       <c r="M593" t="n">
-        <v>0.03594156493896338</v>
+        <v>0.0359415649389633</v>
       </c>
       <c r="N593" t="n">
-        <v>0.04717486491895137</v>
+        <v>0.0471748649189513</v>
       </c>
       <c r="O593" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.0478399991989135</v>
       </c>
       <c r="P593" t="n">
-        <v>-0.000665134279962204</v>
+        <v>-0.0006651342799622</v>
       </c>
     </row>
     <row r="594">
@@ -34855,16 +34855,16 @@
         <v>6.7360578</v>
       </c>
       <c r="M594" t="n">
-        <v>0.04063897763578275</v>
+        <v>0.0406389776357827</v>
       </c>
       <c r="N594" t="n">
-        <v>0.04882952076677316</v>
+        <v>0.0488295207667731</v>
       </c>
       <c r="O594" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.0478399991989135</v>
       </c>
       <c r="P594" t="n">
-        <v>0.0009895215678595859</v>
+        <v>0.0009895215678595</v>
       </c>
     </row>
     <row r="595">
@@ -34913,16 +34913,538 @@
         <v>18.359913</v>
       </c>
       <c r="M595" t="n">
+        <v>0.0342941482896336</v>
+      </c>
+      <c r="N595" t="n">
+        <v>0.067104097933669</v>
+      </c>
+      <c r="O595" t="n">
+        <v>0.0478399991989135</v>
+      </c>
+      <c r="P595" t="n">
+        <v>0.0192640987347554</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:32:54</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E596" t="n">
+        <v>319.97</v>
+      </c>
+      <c r="F596" t="n">
+        <v>4669700046848</v>
+      </c>
+      <c r="G596" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="H596" t="n">
+        <v>9.574350000000001</v>
+      </c>
+      <c r="I596" t="n">
+        <v>36.60984</v>
+      </c>
+      <c r="J596" t="n">
+        <v>33.4195</v>
+      </c>
+      <c r="K596" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L596" t="n">
+        <v>10.003149</v>
+      </c>
+      <c r="M596" t="n">
+        <v>0.02731506078694878</v>
+      </c>
+      <c r="N596" t="n">
+        <v>0.02992264899834359</v>
+      </c>
+      <c r="O596" t="n">
+        <v>0.04783999919891357</v>
+      </c>
+      <c r="P596" t="n">
+        <v>-0.01791735020056998</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:32:54</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E597" t="n">
+        <v>477.57</v>
+      </c>
+      <c r="F597" t="n">
+        <v>779621105664</v>
+      </c>
+      <c r="G597" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H597" t="n">
+        <v>15.51307</v>
+      </c>
+      <c r="I597" t="n">
+        <v>121.82908</v>
+      </c>
+      <c r="J597" t="n">
+        <v>30.78501</v>
+      </c>
+      <c r="K597" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L597" t="n">
+        <v>18.874739</v>
+      </c>
+      <c r="M597" t="n">
+        <v>0.008208220784387628</v>
+      </c>
+      <c r="N597" t="n">
+        <v>0.03248334275603577</v>
+      </c>
+      <c r="O597" t="n">
+        <v>0.04783999919891357</v>
+      </c>
+      <c r="P597" t="n">
+        <v>-0.01535665644287781</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:32:54</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E598" t="n">
+        <v>258.51</v>
+      </c>
+      <c r="F598" t="n">
+        <v>2788369891328</v>
+      </c>
+      <c r="G598" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H598" t="n">
+        <v>10.40032</v>
+      </c>
+      <c r="I598" t="n">
+        <v>20.797264</v>
+      </c>
+      <c r="J598" t="n">
+        <v>24.855967</v>
+      </c>
+      <c r="K598" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L598" t="n">
+        <v>3.5947423</v>
+      </c>
+      <c r="M598" t="n">
+        <v>0.04808324629608139</v>
+      </c>
+      <c r="N598" t="n">
+        <v>0.0402317898727322</v>
+      </c>
+      <c r="O598" t="n">
+        <v>0.04783999919891357</v>
+      </c>
+      <c r="P598" t="n">
+        <v>-0.007608209326181371</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:32:54</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E599" t="n">
+        <v>357.895</v>
+      </c>
+      <c r="F599" t="n">
+        <v>1702714146816</v>
+      </c>
+      <c r="G599" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="H599" t="n">
+        <v>19.37208</v>
+      </c>
+      <c r="I599" t="n">
+        <v>45.64987</v>
+      </c>
+      <c r="J599" t="n">
+        <v>18.474785</v>
+      </c>
+      <c r="K599" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L599" t="n">
+        <v>19.10929</v>
+      </c>
+      <c r="M599" t="n">
+        <v>0.02190586624568659</v>
+      </c>
+      <c r="N599" t="n">
+        <v>0.05412783078835972</v>
+      </c>
+      <c r="O599" t="n">
+        <v>0.04783999919891357</v>
+      </c>
+      <c r="P599" t="n">
+        <v>0.006287831589446145</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:32:54</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E600" t="n">
+        <v>335.31</v>
+      </c>
+      <c r="F600" t="n">
+        <v>4100819517440</v>
+      </c>
+      <c r="G600" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H600" t="n">
+        <v>14.85423</v>
+      </c>
+      <c r="I600" t="n">
+        <v>16.83283</v>
+      </c>
+      <c r="J600" t="n">
+        <v>22.573368</v>
+      </c>
+      <c r="K600" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L600" t="n">
+        <v>9.197426</v>
+      </c>
+      <c r="M600" t="n">
+        <v>0.05940771226626108</v>
+      </c>
+      <c r="N600" t="n">
+        <v>0.04429999105305538</v>
+      </c>
+      <c r="O600" t="n">
+        <v>0.04783999919891357</v>
+      </c>
+      <c r="P600" t="n">
+        <v>-0.003540008145858198</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:32:54</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E601" t="n">
+        <v>616.77</v>
+      </c>
+      <c r="F601" t="n">
+        <v>1571225468928</v>
+      </c>
+      <c r="G601" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="H601" t="n">
+        <v>34.95966</v>
+      </c>
+      <c r="I601" t="n">
+        <v>23.256788</v>
+      </c>
+      <c r="J601" t="n">
+        <v>17.642334</v>
+      </c>
+      <c r="K601" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L601" t="n">
+        <v>6.8838825</v>
+      </c>
+      <c r="M601" t="n">
+        <v>0.04299820030157109</v>
+      </c>
+      <c r="N601" t="n">
+        <v>0.05668184250206722</v>
+      </c>
+      <c r="O601" t="n">
+        <v>0.04783999919891357</v>
+      </c>
+      <c r="P601" t="n">
+        <v>0.00884184330315365</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:32:54</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E602" t="n">
+        <v>499.7</v>
+      </c>
+      <c r="F602" t="n">
+        <v>3710545297408</v>
+      </c>
+      <c r="G602" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H602" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I602" t="n">
+        <v>27.853958</v>
+      </c>
+      <c r="J602" t="n">
+        <v>21.19773</v>
+      </c>
+      <c r="K602" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L602" t="n">
+        <v>11.181764</v>
+      </c>
+      <c r="M602" t="n">
+        <v>0.03590154092455473</v>
+      </c>
+      <c r="N602" t="n">
+        <v>0.04717486491895137</v>
+      </c>
+      <c r="O602" t="n">
+        <v>0.04783999919891357</v>
+      </c>
+      <c r="P602" t="n">
+        <v>-0.000665134279962204</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:32:54</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E603" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="F603" t="n">
+        <v>325828280320</v>
+      </c>
+      <c r="G603" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H603" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I603" t="n">
+        <v>24.606918</v>
+      </c>
+      <c r="J603" t="n">
+        <v>20.479414</v>
+      </c>
+      <c r="K603" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L603" t="n">
+        <v>6.7360578</v>
+      </c>
+      <c r="M603" t="n">
+        <v>0.04063897763578275</v>
+      </c>
+      <c r="N603" t="n">
+        <v>0.04882952076677316</v>
+      </c>
+      <c r="O603" t="n">
+        <v>0.04783999919891357</v>
+      </c>
+      <c r="P603" t="n">
+        <v>0.0009895215678595859</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:32:54</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E604" t="n">
+        <v>230.36</v>
+      </c>
+      <c r="F604" t="n">
+        <v>5562502742016</v>
+      </c>
+      <c r="G604" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H604" t="n">
+        <v>15.51906</v>
+      </c>
+      <c r="I604" t="n">
+        <v>29.159492</v>
+      </c>
+      <c r="J604" t="n">
+        <v>14.843682</v>
+      </c>
+      <c r="K604" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L604" t="n">
+        <v>18.359913</v>
+      </c>
+      <c r="M604" t="n">
         <v>0.03429414828963362</v>
       </c>
-      <c r="N595" t="n">
-        <v>0.06710409793366903</v>
-      </c>
-      <c r="O595" t="n">
+      <c r="N604" t="n">
+        <v>0.06736872720958499</v>
+      </c>
+      <c r="O604" t="n">
         <v>0.04783999919891357</v>
       </c>
-      <c r="P595" t="n">
-        <v>0.01926409873475546</v>
+      <c r="P604" t="n">
+        <v>0.01952872801067142</v>
       </c>
     </row>
   </sheetData>
@@ -35024,12 +35546,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-04 17:12:50</t>
+          <t>2026-09-07 17:32:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -35049,25 +35571,25 @@
         <v>4100819517440</v>
       </c>
       <c r="G2" t="n">
-        <v>19.94</v>
+        <v>19.92</v>
       </c>
       <c r="H2" t="n">
         <v>14.85423</v>
       </c>
       <c r="I2" t="n">
-        <v>16.815947</v>
+        <v>16.83283</v>
       </c>
       <c r="J2" t="n">
         <v>22.573368</v>
       </c>
       <c r="K2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="L2" t="n">
         <v>9.197426</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05946735856371716</v>
+        <v>0.05940771226626108</v>
       </c>
       <c r="N2" t="n">
         <v>0.04429999105305538</v>
@@ -35082,12 +35604,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-04 17:12:50</t>
+          <t>2026-09-07 17:32:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -35107,25 +35629,25 @@
         <v>3710545297408</v>
       </c>
       <c r="G3" t="n">
-        <v>17.96</v>
+        <v>17.94</v>
       </c>
       <c r="H3" t="n">
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>27.822943</v>
+        <v>27.853958</v>
       </c>
       <c r="J3" t="n">
         <v>21.19773</v>
       </c>
       <c r="K3" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="L3" t="n">
         <v>11.181764</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03594156493896338</v>
+        <v>0.03590154092455473</v>
       </c>
       <c r="N3" t="n">
         <v>0.04717486491895137</v>
@@ -35140,12 +35662,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-04 17:12:50</t>
+          <t>2026-09-07 17:32:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -35165,25 +35687,25 @@
         <v>1571225468928</v>
       </c>
       <c r="G4" t="n">
-        <v>26.56</v>
+        <v>26.52</v>
       </c>
       <c r="H4" t="n">
         <v>34.95966</v>
       </c>
       <c r="I4" t="n">
-        <v>23.221764</v>
+        <v>23.256788</v>
       </c>
       <c r="J4" t="n">
         <v>17.642334</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="L4" t="n">
         <v>6.8838825</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04306305429900936</v>
+        <v>0.04299820030157109</v>
       </c>
       <c r="N4" t="n">
         <v>0.05668184250206722</v>
@@ -35198,12 +35720,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-04 17:12:50</t>
+          <t>2026-09-07 17:32:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -35235,7 +35757,7 @@
         <v>24.855967</v>
       </c>
       <c r="K5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="L5" t="n">
         <v>3.5947423</v>
@@ -35256,12 +35778,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-04 17:12:50</t>
+          <t>2026-09-07 17:32:54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -35281,25 +35803,25 @@
         <v>4669700046848</v>
       </c>
       <c r="G6" t="n">
-        <v>8.73</v>
+        <v>8.74</v>
       </c>
       <c r="H6" t="n">
         <v>9.574350000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>36.65178</v>
+        <v>36.60984</v>
       </c>
       <c r="J6" t="n">
         <v>33.4195</v>
       </c>
       <c r="K6" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="L6" t="n">
         <v>10.003149</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02728380785698659</v>
+        <v>0.02731506078694878</v>
       </c>
       <c r="N6" t="n">
         <v>0.02992264899834359</v>
@@ -35314,12 +35836,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-04 17:12:50</t>
+          <t>2026-09-07 17:32:54</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -35342,16 +35864,16 @@
         <v>7.9</v>
       </c>
       <c r="H7" t="n">
-        <v>15.4581</v>
+        <v>15.51906</v>
       </c>
       <c r="I7" t="n">
         <v>29.159492</v>
       </c>
       <c r="J7" t="n">
-        <v>14.902219</v>
+        <v>14.843682</v>
       </c>
       <c r="K7" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="L7" t="n">
         <v>18.359913</v>
@@ -35360,24 +35882,24 @@
         <v>0.03429414828963362</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06710409793366903</v>
+        <v>0.06736872720958499</v>
       </c>
       <c r="O7" t="n">
         <v>0.04783999919891357</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01926409873475546</v>
+        <v>0.01952872801067142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-04 17:12:50</t>
+          <t>2026-09-07 17:32:54</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -35400,16 +35922,16 @@
         <v>3.92</v>
       </c>
       <c r="H8" t="n">
-        <v>15.45073</v>
+        <v>15.51307</v>
       </c>
       <c r="I8" t="n">
         <v>121.82908</v>
       </c>
       <c r="J8" t="n">
-        <v>30.90922</v>
+        <v>30.78501</v>
       </c>
       <c r="K8" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="L8" t="n">
         <v>18.874739</v>
@@ -35418,24 +35940,24 @@
         <v>0.008208220784387628</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03235280691835752</v>
+        <v>0.03248334275603577</v>
       </c>
       <c r="O8" t="n">
         <v>0.04783999919891357</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01548719228055605</v>
+        <v>-0.01535665644287781</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-04 17:12:50</t>
+          <t>2026-09-07 17:32:54</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -35455,25 +35977,25 @@
         <v>1702714146816</v>
       </c>
       <c r="G9" t="n">
-        <v>7.86</v>
+        <v>7.84</v>
       </c>
       <c r="H9" t="n">
         <v>19.37208</v>
       </c>
       <c r="I9" t="n">
-        <v>45.533714</v>
+        <v>45.64987</v>
       </c>
       <c r="J9" t="n">
         <v>18.474785</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="L9" t="n">
         <v>19.10929</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02196174855753783</v>
+        <v>0.02190586624568659</v>
       </c>
       <c r="N9" t="n">
         <v>0.05412783078835972</v>
@@ -35488,12 +36010,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-04 17:12:50</t>
+          <t>2026-09-07 17:32:54</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -35525,7 +36047,7 @@
         <v>20.479414</v>
       </c>
       <c r="K10" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="L10" t="n">
         <v>6.7360578</v>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P604"/>
+  <dimension ref="A1:P613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34971,16 +34971,16 @@
         <v>10.003149</v>
       </c>
       <c r="M596" t="n">
-        <v>0.02731506078694878</v>
+        <v>0.0273150607869487</v>
       </c>
       <c r="N596" t="n">
-        <v>0.02992264899834359</v>
+        <v>0.0299226489983435</v>
       </c>
       <c r="O596" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.0478399991989135</v>
       </c>
       <c r="P596" t="n">
-        <v>-0.01791735020056998</v>
+        <v>-0.0179173502005699</v>
       </c>
     </row>
     <row r="597">
@@ -35029,16 +35029,16 @@
         <v>18.874739</v>
       </c>
       <c r="M597" t="n">
-        <v>0.008208220784387628</v>
+        <v>0.0082082207843876</v>
       </c>
       <c r="N597" t="n">
-        <v>0.03248334275603577</v>
+        <v>0.0324833427560357</v>
       </c>
       <c r="O597" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.0478399991989135</v>
       </c>
       <c r="P597" t="n">
-        <v>-0.01535665644287781</v>
+        <v>-0.0153566564428778</v>
       </c>
     </row>
     <row r="598">
@@ -35087,16 +35087,16 @@
         <v>3.5947423</v>
       </c>
       <c r="M598" t="n">
-        <v>0.04808324629608139</v>
+        <v>0.0480832462960813</v>
       </c>
       <c r="N598" t="n">
         <v>0.0402317898727322</v>
       </c>
       <c r="O598" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.0478399991989135</v>
       </c>
       <c r="P598" t="n">
-        <v>-0.007608209326181371</v>
+        <v>-0.0076082093261813</v>
       </c>
     </row>
     <row r="599">
@@ -35145,16 +35145,16 @@
         <v>19.10929</v>
       </c>
       <c r="M599" t="n">
-        <v>0.02190586624568659</v>
+        <v>0.0219058662456865</v>
       </c>
       <c r="N599" t="n">
-        <v>0.05412783078835972</v>
+        <v>0.0541278307883597</v>
       </c>
       <c r="O599" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.0478399991989135</v>
       </c>
       <c r="P599" t="n">
-        <v>0.006287831589446145</v>
+        <v>0.0062878315894461</v>
       </c>
     </row>
     <row r="600">
@@ -35203,16 +35203,16 @@
         <v>9.197426</v>
       </c>
       <c r="M600" t="n">
-        <v>0.05940771226626108</v>
+        <v>0.059407712266261</v>
       </c>
       <c r="N600" t="n">
-        <v>0.04429999105305538</v>
+        <v>0.0442999910530553</v>
       </c>
       <c r="O600" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.0478399991989135</v>
       </c>
       <c r="P600" t="n">
-        <v>-0.003540008145858198</v>
+        <v>-0.0035400081458581</v>
       </c>
     </row>
     <row r="601">
@@ -35261,16 +35261,16 @@
         <v>6.8838825</v>
       </c>
       <c r="M601" t="n">
-        <v>0.04299820030157109</v>
+        <v>0.042998200301571</v>
       </c>
       <c r="N601" t="n">
-        <v>0.05668184250206722</v>
+        <v>0.0566818425020672</v>
       </c>
       <c r="O601" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.0478399991989135</v>
       </c>
       <c r="P601" t="n">
-        <v>0.00884184330315365</v>
+        <v>0.0088418433031536</v>
       </c>
     </row>
     <row r="602">
@@ -35319,16 +35319,16 @@
         <v>11.181764</v>
       </c>
       <c r="M602" t="n">
-        <v>0.03590154092455473</v>
+        <v>0.0359015409245547</v>
       </c>
       <c r="N602" t="n">
-        <v>0.04717486491895137</v>
+        <v>0.0471748649189513</v>
       </c>
       <c r="O602" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.0478399991989135</v>
       </c>
       <c r="P602" t="n">
-        <v>-0.000665134279962204</v>
+        <v>-0.0006651342799622</v>
       </c>
     </row>
     <row r="603">
@@ -35377,16 +35377,16 @@
         <v>6.7360578</v>
       </c>
       <c r="M603" t="n">
-        <v>0.04063897763578275</v>
+        <v>0.0406389776357827</v>
       </c>
       <c r="N603" t="n">
-        <v>0.04882952076677316</v>
+        <v>0.0488295207667731</v>
       </c>
       <c r="O603" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.0478399991989135</v>
       </c>
       <c r="P603" t="n">
-        <v>0.0009895215678595859</v>
+        <v>0.0009895215678595</v>
       </c>
     </row>
     <row r="604">
@@ -35435,16 +35435,538 @@
         <v>18.359913</v>
       </c>
       <c r="M604" t="n">
-        <v>0.03429414828963362</v>
+        <v>0.0342941482896336</v>
       </c>
       <c r="N604" t="n">
-        <v>0.06736872720958499</v>
+        <v>0.06736872720958489</v>
       </c>
       <c r="O604" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.0478399991989135</v>
       </c>
       <c r="P604" t="n">
-        <v>0.01952872801067142</v>
+        <v>0.0195287280106714</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>2026-09-08 17:23:08</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E605" t="n">
+        <v>316.22</v>
+      </c>
+      <c r="F605" t="n">
+        <v>4614971719680</v>
+      </c>
+      <c r="G605" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="H605" t="n">
+        <v>9.574350000000001</v>
+      </c>
+      <c r="I605" t="n">
+        <v>36.18078</v>
+      </c>
+      <c r="J605" t="n">
+        <v>33.02783</v>
+      </c>
+      <c r="K605" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L605" t="n">
+        <v>9.885914</v>
+      </c>
+      <c r="M605" t="n">
+        <v>0.02763898551641262</v>
+      </c>
+      <c r="N605" t="n">
+        <v>0.03027749667952691</v>
+      </c>
+      <c r="O605" t="n">
+        <v>0.04806000232696533</v>
+      </c>
+      <c r="P605" t="n">
+        <v>-0.01778250564743842</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>2026-09-08 17:23:08</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E606" t="n">
+        <v>505.74</v>
+      </c>
+      <c r="F606" t="n">
+        <v>825607913472</v>
+      </c>
+      <c r="G606" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H606" t="n">
+        <v>15.51307</v>
+      </c>
+      <c r="I606" t="n">
+        <v>129.0153</v>
+      </c>
+      <c r="J606" t="n">
+        <v>32.600895</v>
+      </c>
+      <c r="K606" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L606" t="n">
+        <v>19.988085</v>
+      </c>
+      <c r="M606" t="n">
+        <v>0.007751018309803456</v>
+      </c>
+      <c r="N606" t="n">
+        <v>0.03067400245185273</v>
+      </c>
+      <c r="O606" t="n">
+        <v>0.04806000232696533</v>
+      </c>
+      <c r="P606" t="n">
+        <v>-0.0173859998751126</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>2026-09-08 17:23:08</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E607" t="n">
+        <v>256.97</v>
+      </c>
+      <c r="F607" t="n">
+        <v>2771758874624</v>
+      </c>
+      <c r="G607" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="H607" t="n">
+        <v>10.40032</v>
+      </c>
+      <c r="I607" t="n">
+        <v>20.67337</v>
+      </c>
+      <c r="J607" t="n">
+        <v>24.707893</v>
+      </c>
+      <c r="K607" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L607" t="n">
+        <v>3.5733275</v>
+      </c>
+      <c r="M607" t="n">
+        <v>0.04837140522239949</v>
+      </c>
+      <c r="N607" t="n">
+        <v>0.04047289566875511</v>
+      </c>
+      <c r="O607" t="n">
+        <v>0.04806000232696533</v>
+      </c>
+      <c r="P607" t="n">
+        <v>-0.007587106658210226</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>2026-09-08 17:23:08</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E608" t="n">
+        <v>368.56</v>
+      </c>
+      <c r="F608" t="n">
+        <v>1753453821952</v>
+      </c>
+      <c r="G608" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="H608" t="n">
+        <v>19.3879</v>
+      </c>
+      <c r="I608" t="n">
+        <v>47.010204</v>
+      </c>
+      <c r="J608" t="n">
+        <v>19.009796</v>
+      </c>
+      <c r="K608" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L608" t="n">
+        <v>19.678734</v>
+      </c>
+      <c r="M608" t="n">
+        <v>0.02127197742565661</v>
+      </c>
+      <c r="N608" t="n">
+        <v>0.05260446060342956</v>
+      </c>
+      <c r="O608" t="n">
+        <v>0.04806000232696533</v>
+      </c>
+      <c r="P608" t="n">
+        <v>0.004544458276464228</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>2026-09-08 17:23:08</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E609" t="n">
+        <v>335.38</v>
+      </c>
+      <c r="F609" t="n">
+        <v>4101675679744</v>
+      </c>
+      <c r="G609" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H609" t="n">
+        <v>14.85403</v>
+      </c>
+      <c r="I609" t="n">
+        <v>16.836346</v>
+      </c>
+      <c r="J609" t="n">
+        <v>22.578384</v>
+      </c>
+      <c r="K609" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L609" t="n">
+        <v>9.199346999999999</v>
+      </c>
+      <c r="M609" t="n">
+        <v>0.05939531277953367</v>
+      </c>
+      <c r="N609" t="n">
+        <v>0.04429014848828195</v>
+      </c>
+      <c r="O609" t="n">
+        <v>0.04806000232696533</v>
+      </c>
+      <c r="P609" t="n">
+        <v>-0.003769853838683383</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>2026-09-08 17:23:08</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E610" t="n">
+        <v>613.48</v>
+      </c>
+      <c r="F610" t="n">
+        <v>1562844069888</v>
+      </c>
+      <c r="G610" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="H610" t="n">
+        <v>34.95966</v>
+      </c>
+      <c r="I610" t="n">
+        <v>23.132729</v>
+      </c>
+      <c r="J610" t="n">
+        <v>17.548225</v>
+      </c>
+      <c r="K610" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L610" t="n">
+        <v>6.847162</v>
+      </c>
+      <c r="M610" t="n">
+        <v>0.04322879311468996</v>
+      </c>
+      <c r="N610" t="n">
+        <v>0.05698581860859359</v>
+      </c>
+      <c r="O610" t="n">
+        <v>0.04806000232696533</v>
+      </c>
+      <c r="P610" t="n">
+        <v>0.008925816281628259</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>2026-09-08 17:23:08</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E611" t="n">
+        <v>493.95</v>
+      </c>
+      <c r="F611" t="n">
+        <v>3667848331264</v>
+      </c>
+      <c r="G611" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H611" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I611" t="n">
+        <v>27.533445</v>
+      </c>
+      <c r="J611" t="n">
+        <v>20.95381</v>
+      </c>
+      <c r="K611" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L611" t="n">
+        <v>11.053096</v>
+      </c>
+      <c r="M611" t="n">
+        <v>0.03631946553294868</v>
+      </c>
+      <c r="N611" t="n">
+        <v>0.04772402064986335</v>
+      </c>
+      <c r="O611" t="n">
+        <v>0.04806000232696533</v>
+      </c>
+      <c r="P611" t="n">
+        <v>-0.0003359816771019847</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>2026-09-08 17:23:08</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E612" t="n">
+        <v>76.77</v>
+      </c>
+      <c r="F612" t="n">
+        <v>319665635328</v>
+      </c>
+      <c r="G612" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H612" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I612" t="n">
+        <v>24.141508</v>
+      </c>
+      <c r="J612" t="n">
+        <v>20.092072</v>
+      </c>
+      <c r="K612" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L612" t="n">
+        <v>6.6086535</v>
+      </c>
+      <c r="M612" t="n">
+        <v>0.04142243063696757</v>
+      </c>
+      <c r="N612" t="n">
+        <v>0.04977087403933829</v>
+      </c>
+      <c r="O612" t="n">
+        <v>0.04806000232696533</v>
+      </c>
+      <c r="P612" t="n">
+        <v>0.001710871712372955</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>2026-09-08 17:23:08</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E613" t="n">
+        <v>225.73</v>
+      </c>
+      <c r="F613" t="n">
+        <v>5450701996032</v>
+      </c>
+      <c r="G613" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H613" t="n">
+        <v>15.51906</v>
+      </c>
+      <c r="I613" t="n">
+        <v>28.573418</v>
+      </c>
+      <c r="J613" t="n">
+        <v>14.54534</v>
+      </c>
+      <c r="K613" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L613" t="n">
+        <v>17.990896</v>
+      </c>
+      <c r="M613" t="n">
+        <v>0.03499756346077172</v>
+      </c>
+      <c r="N613" t="n">
+        <v>0.0687505426837372</v>
+      </c>
+      <c r="O613" t="n">
+        <v>0.04806000232696533</v>
+      </c>
+      <c r="P613" t="n">
+        <v>0.02069054035677187</v>
       </c>
     </row>
   </sheetData>
@@ -35546,12 +36068,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07 17:32:54</t>
+          <t>2026-09-08 17:23:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -35565,51 +36087,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>335.31</v>
+        <v>335.38</v>
       </c>
       <c r="F2" t="n">
-        <v>4100819517440</v>
+        <v>4101675679744</v>
       </c>
       <c r="G2" t="n">
         <v>19.92</v>
       </c>
       <c r="H2" t="n">
-        <v>14.85423</v>
+        <v>14.85403</v>
       </c>
       <c r="I2" t="n">
-        <v>16.83283</v>
+        <v>16.836346</v>
       </c>
       <c r="J2" t="n">
-        <v>22.573368</v>
+        <v>22.578384</v>
       </c>
       <c r="K2" t="n">
         <v>1.24</v>
       </c>
       <c r="L2" t="n">
-        <v>9.197426</v>
+        <v>9.199346999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05940771226626108</v>
+        <v>0.05939531277953367</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04429999105305538</v>
+        <v>0.04429014848828195</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.04806000232696533</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003540008145858198</v>
+        <v>-0.003769853838683383</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07 17:32:54</t>
+          <t>2026-09-08 17:23:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -35623,10 +36145,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>499.7</v>
+        <v>493.95</v>
       </c>
       <c r="F3" t="n">
-        <v>3710545297408</v>
+        <v>3667848331264</v>
       </c>
       <c r="G3" t="n">
         <v>17.94</v>
@@ -35635,39 +36157,39 @@
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>27.853958</v>
+        <v>27.533445</v>
       </c>
       <c r="J3" t="n">
-        <v>21.19773</v>
+        <v>20.95381</v>
       </c>
       <c r="K3" t="n">
         <v>1.62</v>
       </c>
       <c r="L3" t="n">
-        <v>11.181764</v>
+        <v>11.053096</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03590154092455473</v>
+        <v>0.03631946553294868</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04717486491895137</v>
+        <v>0.04772402064986335</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.04806000232696533</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.000665134279962204</v>
+        <v>-0.0003359816771019847</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07 17:32:54</t>
+          <t>2026-09-08 17:23:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -35681,10 +36203,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>616.77</v>
+        <v>613.48</v>
       </c>
       <c r="F4" t="n">
-        <v>1571225468928</v>
+        <v>1562844069888</v>
       </c>
       <c r="G4" t="n">
         <v>26.52</v>
@@ -35693,39 +36215,39 @@
         <v>34.95966</v>
       </c>
       <c r="I4" t="n">
-        <v>23.256788</v>
+        <v>23.132729</v>
       </c>
       <c r="J4" t="n">
-        <v>17.642334</v>
+        <v>17.548225</v>
       </c>
       <c r="K4" t="n">
         <v>0.82</v>
       </c>
       <c r="L4" t="n">
-        <v>6.8838825</v>
+        <v>6.847162</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04299820030157109</v>
+        <v>0.04322879311468996</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05668184250206722</v>
+        <v>0.05698581860859359</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.04806000232696533</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00884184330315365</v>
+        <v>0.008925816281628259</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-07 17:32:54</t>
+          <t>2026-09-08 17:23:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -35739,10 +36261,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>258.51</v>
+        <v>256.97</v>
       </c>
       <c r="F5" t="n">
-        <v>2788369891328</v>
+        <v>2771758874624</v>
       </c>
       <c r="G5" t="n">
         <v>12.43</v>
@@ -35751,39 +36273,39 @@
         <v>10.40032</v>
       </c>
       <c r="I5" t="n">
-        <v>20.797264</v>
+        <v>20.67337</v>
       </c>
       <c r="J5" t="n">
-        <v>24.855967</v>
+        <v>24.707893</v>
       </c>
       <c r="K5" t="n">
         <v>1.51</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5947423</v>
+        <v>3.5733275</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04808324629608139</v>
+        <v>0.04837140522239949</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0402317898727322</v>
+        <v>0.04047289566875511</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.04806000232696533</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007608209326181371</v>
+        <v>-0.007587106658210226</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-07 17:32:54</t>
+          <t>2026-09-08 17:23:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -35797,10 +36319,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>319.97</v>
+        <v>316.22</v>
       </c>
       <c r="F6" t="n">
-        <v>4669700046848</v>
+        <v>4614971719680</v>
       </c>
       <c r="G6" t="n">
         <v>8.74</v>
@@ -35809,39 +36331,39 @@
         <v>9.574350000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>36.60984</v>
+        <v>36.18078</v>
       </c>
       <c r="J6" t="n">
-        <v>33.4195</v>
+        <v>33.02783</v>
       </c>
       <c r="K6" t="n">
         <v>2.52</v>
       </c>
       <c r="L6" t="n">
-        <v>10.003149</v>
+        <v>9.885914</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02731506078694878</v>
+        <v>0.02763898551641262</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02992264899834359</v>
+        <v>0.03027749667952691</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.04806000232696533</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01791735020056998</v>
+        <v>-0.01778250564743842</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-07 17:32:54</t>
+          <t>2026-09-08 17:23:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -35855,10 +36377,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230.36</v>
+        <v>225.73</v>
       </c>
       <c r="F7" t="n">
-        <v>5562502742016</v>
+        <v>5450701996032</v>
       </c>
       <c r="G7" t="n">
         <v>7.9</v>
@@ -35867,39 +36389,39 @@
         <v>15.51906</v>
       </c>
       <c r="I7" t="n">
-        <v>29.159492</v>
+        <v>28.573418</v>
       </c>
       <c r="J7" t="n">
-        <v>14.843682</v>
+        <v>14.54534</v>
       </c>
       <c r="K7" t="n">
         <v>0.59</v>
       </c>
       <c r="L7" t="n">
-        <v>18.359913</v>
+        <v>17.990896</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03429414828963362</v>
+        <v>0.03499756346077172</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06736872720958499</v>
+        <v>0.0687505426837372</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.04806000232696533</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01952872801067142</v>
+        <v>0.02069054035677187</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-07 17:32:54</t>
+          <t>2026-09-08 17:23:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -35913,10 +36435,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>477.57</v>
+        <v>505.74</v>
       </c>
       <c r="F8" t="n">
-        <v>779621105664</v>
+        <v>825607913472</v>
       </c>
       <c r="G8" t="n">
         <v>3.92</v>
@@ -35925,39 +36447,39 @@
         <v>15.51307</v>
       </c>
       <c r="I8" t="n">
-        <v>121.82908</v>
+        <v>129.0153</v>
       </c>
       <c r="J8" t="n">
-        <v>30.78501</v>
+        <v>32.600895</v>
       </c>
       <c r="K8" t="n">
         <v>0.49</v>
       </c>
       <c r="L8" t="n">
-        <v>18.874739</v>
+        <v>19.988085</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008208220784387628</v>
+        <v>0.007751018309803456</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03248334275603577</v>
+        <v>0.03067400245185273</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.04806000232696533</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.01535665644287781</v>
+        <v>-0.0173859998751126</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-07 17:32:54</t>
+          <t>2026-09-08 17:23:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -35971,51 +36493,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>357.895</v>
+        <v>368.56</v>
       </c>
       <c r="F9" t="n">
-        <v>1702714146816</v>
+        <v>1753453821952</v>
       </c>
       <c r="G9" t="n">
         <v>7.84</v>
       </c>
       <c r="H9" t="n">
-        <v>19.37208</v>
+        <v>19.3879</v>
       </c>
       <c r="I9" t="n">
-        <v>45.64987</v>
+        <v>47.010204</v>
       </c>
       <c r="J9" t="n">
-        <v>18.474785</v>
+        <v>19.009796</v>
       </c>
       <c r="K9" t="n">
         <v>0.35</v>
       </c>
       <c r="L9" t="n">
-        <v>19.10929</v>
+        <v>19.678734</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02190586624568659</v>
+        <v>0.02127197742565661</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05412783078835972</v>
+        <v>0.05260446060342956</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.04806000232696533</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006287831589446145</v>
+        <v>0.004544458276464228</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-07 17:32:54</t>
+          <t>2026-09-08 17:23:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -36029,10 +36551,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>78.25</v>
+        <v>76.77</v>
       </c>
       <c r="F10" t="n">
-        <v>325828280320</v>
+        <v>319665635328</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -36041,28 +36563,28 @@
         <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>24.606918</v>
+        <v>24.141508</v>
       </c>
       <c r="J10" t="n">
-        <v>20.479414</v>
+        <v>20.092072</v>
       </c>
       <c r="K10" t="n">
         <v>1.45</v>
       </c>
       <c r="L10" t="n">
-        <v>6.7360578</v>
+        <v>6.6086535</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04063897763578275</v>
+        <v>0.04142243063696757</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04882952076677316</v>
+        <v>0.04977087403933829</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.04806000232696533</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0009895215678595859</v>
+        <v>0.001710871712372955</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P613"/>
+  <dimension ref="A1:P622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35493,16 +35493,16 @@
         <v>9.885914</v>
       </c>
       <c r="M605" t="n">
-        <v>0.02763898551641262</v>
+        <v>0.0276389855164126</v>
       </c>
       <c r="N605" t="n">
-        <v>0.03027749667952691</v>
+        <v>0.0302774966795269</v>
       </c>
       <c r="O605" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.0480600023269653</v>
       </c>
       <c r="P605" t="n">
-        <v>-0.01778250564743842</v>
+        <v>-0.0177825056474384</v>
       </c>
     </row>
     <row r="606">
@@ -35551,13 +35551,13 @@
         <v>19.988085</v>
       </c>
       <c r="M606" t="n">
-        <v>0.007751018309803456</v>
+        <v>0.0077510183098034</v>
       </c>
       <c r="N606" t="n">
-        <v>0.03067400245185273</v>
+        <v>0.0306740024518527</v>
       </c>
       <c r="O606" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.0480600023269653</v>
       </c>
       <c r="P606" t="n">
         <v>-0.0173859998751126</v>
@@ -35609,16 +35609,16 @@
         <v>3.5733275</v>
       </c>
       <c r="M607" t="n">
-        <v>0.04837140522239949</v>
+        <v>0.0483714052223994</v>
       </c>
       <c r="N607" t="n">
-        <v>0.04047289566875511</v>
+        <v>0.0404728956687551</v>
       </c>
       <c r="O607" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.0480600023269653</v>
       </c>
       <c r="P607" t="n">
-        <v>-0.007587106658210226</v>
+        <v>-0.0075871066582102</v>
       </c>
     </row>
     <row r="608">
@@ -35667,16 +35667,16 @@
         <v>19.678734</v>
       </c>
       <c r="M608" t="n">
-        <v>0.02127197742565661</v>
+        <v>0.0212719774256566</v>
       </c>
       <c r="N608" t="n">
-        <v>0.05260446060342956</v>
+        <v>0.0526044606034295</v>
       </c>
       <c r="O608" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.0480600023269653</v>
       </c>
       <c r="P608" t="n">
-        <v>0.004544458276464228</v>
+        <v>0.0045444582764642</v>
       </c>
     </row>
     <row r="609">
@@ -35725,16 +35725,16 @@
         <v>9.199346999999999</v>
       </c>
       <c r="M609" t="n">
-        <v>0.05939531277953367</v>
+        <v>0.0593953127795336</v>
       </c>
       <c r="N609" t="n">
-        <v>0.04429014848828195</v>
+        <v>0.0442901484882819</v>
       </c>
       <c r="O609" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.0480600023269653</v>
       </c>
       <c r="P609" t="n">
-        <v>-0.003769853838683383</v>
+        <v>-0.0037698538386833</v>
       </c>
     </row>
     <row r="610">
@@ -35783,16 +35783,16 @@
         <v>6.847162</v>
       </c>
       <c r="M610" t="n">
-        <v>0.04322879311468996</v>
+        <v>0.0432287931146899</v>
       </c>
       <c r="N610" t="n">
-        <v>0.05698581860859359</v>
+        <v>0.0569858186085935</v>
       </c>
       <c r="O610" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.0480600023269653</v>
       </c>
       <c r="P610" t="n">
-        <v>0.008925816281628259</v>
+        <v>0.0089258162816282</v>
       </c>
     </row>
     <row r="611">
@@ -35841,16 +35841,16 @@
         <v>11.053096</v>
       </c>
       <c r="M611" t="n">
-        <v>0.03631946553294868</v>
+        <v>0.0363194655329486</v>
       </c>
       <c r="N611" t="n">
-        <v>0.04772402064986335</v>
+        <v>0.0477240206498633</v>
       </c>
       <c r="O611" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.0480600023269653</v>
       </c>
       <c r="P611" t="n">
-        <v>-0.0003359816771019847</v>
+        <v>-0.0003359816771019</v>
       </c>
     </row>
     <row r="612">
@@ -35899,16 +35899,16 @@
         <v>6.6086535</v>
       </c>
       <c r="M612" t="n">
-        <v>0.04142243063696757</v>
+        <v>0.0414224306369675</v>
       </c>
       <c r="N612" t="n">
-        <v>0.04977087403933829</v>
+        <v>0.0497708740393382</v>
       </c>
       <c r="O612" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.0480600023269653</v>
       </c>
       <c r="P612" t="n">
-        <v>0.001710871712372955</v>
+        <v>0.0017108717123729</v>
       </c>
     </row>
     <row r="613">
@@ -35957,16 +35957,538 @@
         <v>17.990896</v>
       </c>
       <c r="M613" t="n">
-        <v>0.03499756346077172</v>
+        <v>0.0349975634607717</v>
       </c>
       <c r="N613" t="n">
         <v>0.0687505426837372</v>
       </c>
       <c r="O613" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.0480600023269653</v>
       </c>
       <c r="P613" t="n">
-        <v>0.02069054035677187</v>
+        <v>0.0206905403567718</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:21:24</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E614" t="n">
+        <v>315.34</v>
+      </c>
+      <c r="F614" t="n">
+        <v>4602128760832</v>
+      </c>
+      <c r="G614" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H614" t="n">
+        <v>9.57757</v>
+      </c>
+      <c r="I614" t="n">
+        <v>36.12142</v>
+      </c>
+      <c r="J614" t="n">
+        <v>32.924843</v>
+      </c>
+      <c r="K614" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L614" t="n">
+        <v>9.858402</v>
+      </c>
+      <c r="M614" t="n">
+        <v>0.02768440413521913</v>
+      </c>
+      <c r="N614" t="n">
+        <v>0.0303722014333735</v>
+      </c>
+      <c r="O614" t="n">
+        <v>0.04836999893188477</v>
+      </c>
+      <c r="P614" t="n">
+        <v>-0.01799779749851127</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:21:24</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E615" t="n">
+        <v>521.095</v>
+      </c>
+      <c r="F615" t="n">
+        <v>850674515968</v>
+      </c>
+      <c r="G615" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="H615" t="n">
+        <v>15.51307</v>
+      </c>
+      <c r="I615" t="n">
+        <v>132.2576</v>
+      </c>
+      <c r="J615" t="n">
+        <v>33.590706</v>
+      </c>
+      <c r="K615" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L615" t="n">
+        <v>20.594952</v>
+      </c>
+      <c r="M615" t="n">
+        <v>0.007561001352920292</v>
+      </c>
+      <c r="N615" t="n">
+        <v>0.02977013788272772</v>
+      </c>
+      <c r="O615" t="n">
+        <v>0.04836999893188477</v>
+      </c>
+      <c r="P615" t="n">
+        <v>-0.01859986104915705</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:21:24</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E616" t="n">
+        <v>252.4</v>
+      </c>
+      <c r="F616" t="n">
+        <v>2722465316864</v>
+      </c>
+      <c r="G616" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="H616" t="n">
+        <v>10.40032</v>
+      </c>
+      <c r="I616" t="n">
+        <v>20.289389</v>
+      </c>
+      <c r="J616" t="n">
+        <v>24.268484</v>
+      </c>
+      <c r="K616" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L616" t="n">
+        <v>3.5097787</v>
+      </c>
+      <c r="M616" t="n">
+        <v>0.04928684627575277</v>
+      </c>
+      <c r="N616" t="n">
+        <v>0.04120570522979398</v>
+      </c>
+      <c r="O616" t="n">
+        <v>0.04836999893188477</v>
+      </c>
+      <c r="P616" t="n">
+        <v>-0.00716429370209079</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:21:24</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E617" t="n">
+        <v>364.38</v>
+      </c>
+      <c r="F617" t="n">
+        <v>1733567184896</v>
+      </c>
+      <c r="G617" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="H617" t="n">
+        <v>19.38391</v>
+      </c>
+      <c r="I617" t="n">
+        <v>46.417835</v>
+      </c>
+      <c r="J617" t="n">
+        <v>18.798065</v>
+      </c>
+      <c r="K617" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L617" t="n">
+        <v>19.45555</v>
+      </c>
+      <c r="M617" t="n">
+        <v>0.02154344365771996</v>
+      </c>
+      <c r="N617" t="n">
+        <v>0.05319696470717383</v>
+      </c>
+      <c r="O617" t="n">
+        <v>0.04836999893188477</v>
+      </c>
+      <c r="P617" t="n">
+        <v>0.004826965775289065</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:21:24</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E618" t="n">
+        <v>328.38</v>
+      </c>
+      <c r="F618" t="n">
+        <v>4016066265088</v>
+      </c>
+      <c r="G618" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="H618" t="n">
+        <v>14.85403</v>
+      </c>
+      <c r="I618" t="n">
+        <v>16.48494</v>
+      </c>
+      <c r="J618" t="n">
+        <v>22.107132</v>
+      </c>
+      <c r="K618" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L618" t="n">
+        <v>9.0073395</v>
+      </c>
+      <c r="M618" t="n">
+        <v>0.06066142883245022</v>
+      </c>
+      <c r="N618" t="n">
+        <v>0.04523427127108837</v>
+      </c>
+      <c r="O618" t="n">
+        <v>0.04836999893188477</v>
+      </c>
+      <c r="P618" t="n">
+        <v>-0.003135727660796395</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:21:24</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E619" t="n">
+        <v>653.6900000000001</v>
+      </c>
+      <c r="F619" t="n">
+        <v>1665279328256</v>
+      </c>
+      <c r="G619" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="H619" t="n">
+        <v>34.95966</v>
+      </c>
+      <c r="I619" t="n">
+        <v>24.611822</v>
+      </c>
+      <c r="J619" t="n">
+        <v>18.698408</v>
+      </c>
+      <c r="K619" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L619" t="n">
+        <v>7.295953</v>
+      </c>
+      <c r="M619" t="n">
+        <v>0.04063088008077222</v>
+      </c>
+      <c r="N619" t="n">
+        <v>0.05348048769294313</v>
+      </c>
+      <c r="O619" t="n">
+        <v>0.04836999893188477</v>
+      </c>
+      <c r="P619" t="n">
+        <v>0.005110488761058365</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:21:24</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E620" t="n">
+        <v>491.65</v>
+      </c>
+      <c r="F620" t="n">
+        <v>3650769387520</v>
+      </c>
+      <c r="G620" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="H620" t="n">
+        <v>23.57328</v>
+      </c>
+      <c r="I620" t="n">
+        <v>27.420523</v>
+      </c>
+      <c r="J620" t="n">
+        <v>20.85624</v>
+      </c>
+      <c r="K620" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L620" t="n">
+        <v>11.001628</v>
+      </c>
+      <c r="M620" t="n">
+        <v>0.03646903284857114</v>
+      </c>
+      <c r="N620" t="n">
+        <v>0.04794727956879895</v>
+      </c>
+      <c r="O620" t="n">
+        <v>0.04836999893188477</v>
+      </c>
+      <c r="P620" t="n">
+        <v>-0.0004227193630858203</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:21:24</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E621" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="F621" t="n">
+        <v>316584329216</v>
+      </c>
+      <c r="G621" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H621" t="n">
+        <v>3.82091</v>
+      </c>
+      <c r="I621" t="n">
+        <v>23.908804</v>
+      </c>
+      <c r="J621" t="n">
+        <v>19.898401</v>
+      </c>
+      <c r="K621" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L621" t="n">
+        <v>6.544952</v>
+      </c>
+      <c r="M621" t="n">
+        <v>0.04182559515980534</v>
+      </c>
+      <c r="N621" t="n">
+        <v>0.05025529396290938</v>
+      </c>
+      <c r="O621" t="n">
+        <v>0.04836999893188477</v>
+      </c>
+      <c r="P621" t="n">
+        <v>0.001885295031024609</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:21:24</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E622" t="n">
+        <v>223.67</v>
+      </c>
+      <c r="F622" t="n">
+        <v>5400959123456</v>
+      </c>
+      <c r="G622" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H622" t="n">
+        <v>15.51906</v>
+      </c>
+      <c r="I622" t="n">
+        <v>28.312658</v>
+      </c>
+      <c r="J622" t="n">
+        <v>14.4126</v>
+      </c>
+      <c r="K622" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L622" t="n">
+        <v>17.826712</v>
+      </c>
+      <c r="M622" t="n">
+        <v>0.03531989091071668</v>
+      </c>
+      <c r="N622" t="n">
+        <v>0.06938373496669201</v>
+      </c>
+      <c r="O622" t="n">
+        <v>0.04836999893188477</v>
+      </c>
+      <c r="P622" t="n">
+        <v>0.02101373603480724</v>
       </c>
     </row>
   </sheetData>
@@ -36068,12 +36590,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08 17:23:08</t>
+          <t>2026-09-09 17:21:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -36087,10 +36609,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>335.38</v>
+        <v>328.38</v>
       </c>
       <c r="F2" t="n">
-        <v>4101675679744</v>
+        <v>4016066265088</v>
       </c>
       <c r="G2" t="n">
         <v>19.92</v>
@@ -36099,39 +36621,39 @@
         <v>14.85403</v>
       </c>
       <c r="I2" t="n">
-        <v>16.836346</v>
+        <v>16.48494</v>
       </c>
       <c r="J2" t="n">
-        <v>22.578384</v>
+        <v>22.107132</v>
       </c>
       <c r="K2" t="n">
         <v>1.24</v>
       </c>
       <c r="L2" t="n">
-        <v>9.199346999999999</v>
+        <v>9.0073395</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05939531277953367</v>
+        <v>0.06066142883245022</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04429014848828195</v>
+        <v>0.04523427127108837</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.04836999893188477</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.003769853838683383</v>
+        <v>-0.003135727660796395</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-08 17:23:08</t>
+          <t>2026-09-09 17:21:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -36145,51 +36667,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>493.95</v>
+        <v>491.65</v>
       </c>
       <c r="F3" t="n">
-        <v>3667848331264</v>
+        <v>3650769387520</v>
       </c>
       <c r="G3" t="n">
-        <v>17.94</v>
+        <v>17.93</v>
       </c>
       <c r="H3" t="n">
         <v>23.57328</v>
       </c>
       <c r="I3" t="n">
-        <v>27.533445</v>
+        <v>27.420523</v>
       </c>
       <c r="J3" t="n">
-        <v>20.95381</v>
+        <v>20.85624</v>
       </c>
       <c r="K3" t="n">
         <v>1.62</v>
       </c>
       <c r="L3" t="n">
-        <v>11.053096</v>
+        <v>11.001628</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03631946553294868</v>
+        <v>0.03646903284857114</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04772402064986335</v>
+        <v>0.04794727956879895</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.04836999893188477</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0003359816771019847</v>
+        <v>-0.0004227193630858203</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-08 17:23:08</t>
+          <t>2026-09-09 17:21:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -36203,51 +36725,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>613.48</v>
+        <v>653.6900000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1562844069888</v>
+        <v>1665279328256</v>
       </c>
       <c r="G4" t="n">
-        <v>26.52</v>
+        <v>26.56</v>
       </c>
       <c r="H4" t="n">
         <v>34.95966</v>
       </c>
       <c r="I4" t="n">
-        <v>23.132729</v>
+        <v>24.611822</v>
       </c>
       <c r="J4" t="n">
-        <v>17.548225</v>
+        <v>18.698408</v>
       </c>
       <c r="K4" t="n">
         <v>0.82</v>
       </c>
       <c r="L4" t="n">
-        <v>6.847162</v>
+        <v>7.295953</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04322879311468996</v>
+        <v>0.04063088008077222</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05698581860859359</v>
+        <v>0.05348048769294313</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.04836999893188477</v>
       </c>
       <c r="P4" t="n">
-        <v>0.008925816281628259</v>
+        <v>0.005110488761058365</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-08 17:23:08</t>
+          <t>2026-09-09 17:21:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -36261,51 +36783,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>256.97</v>
+        <v>252.4</v>
       </c>
       <c r="F5" t="n">
-        <v>2771758874624</v>
+        <v>2722465316864</v>
       </c>
       <c r="G5" t="n">
-        <v>12.43</v>
+        <v>12.44</v>
       </c>
       <c r="H5" t="n">
         <v>10.40032</v>
       </c>
       <c r="I5" t="n">
-        <v>20.67337</v>
+        <v>20.289389</v>
       </c>
       <c r="J5" t="n">
-        <v>24.707893</v>
+        <v>24.268484</v>
       </c>
       <c r="K5" t="n">
         <v>1.51</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5733275</v>
+        <v>3.5097787</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04837140522239949</v>
+        <v>0.04928684627575277</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04047289566875511</v>
+        <v>0.04120570522979398</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.04836999893188477</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007587106658210226</v>
+        <v>-0.00716429370209079</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-08 17:23:08</t>
+          <t>2026-09-09 17:21:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -36319,51 +36841,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>316.22</v>
+        <v>315.34</v>
       </c>
       <c r="F6" t="n">
-        <v>4614971719680</v>
+        <v>4602128760832</v>
       </c>
       <c r="G6" t="n">
-        <v>8.74</v>
+        <v>8.73</v>
       </c>
       <c r="H6" t="n">
-        <v>9.574350000000001</v>
+        <v>9.57757</v>
       </c>
       <c r="I6" t="n">
-        <v>36.18078</v>
+        <v>36.12142</v>
       </c>
       <c r="J6" t="n">
-        <v>33.02783</v>
+        <v>32.924843</v>
       </c>
       <c r="K6" t="n">
         <v>2.52</v>
       </c>
       <c r="L6" t="n">
-        <v>9.885914</v>
+        <v>9.858402</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02763898551641262</v>
+        <v>0.02768440413521913</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03027749667952691</v>
+        <v>0.0303722014333735</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.04836999893188477</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01778250564743842</v>
+        <v>-0.01799779749851127</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-08 17:23:08</t>
+          <t>2026-09-09 17:21:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -36377,10 +36899,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>225.73</v>
+        <v>223.67</v>
       </c>
       <c r="F7" t="n">
-        <v>5450701996032</v>
+        <v>5400959123456</v>
       </c>
       <c r="G7" t="n">
         <v>7.9</v>
@@ -36389,39 +36911,39 @@
         <v>15.51906</v>
       </c>
       <c r="I7" t="n">
-        <v>28.573418</v>
+        <v>28.312658</v>
       </c>
       <c r="J7" t="n">
-        <v>14.54534</v>
+        <v>14.4126</v>
       </c>
       <c r="K7" t="n">
         <v>0.59</v>
       </c>
       <c r="L7" t="n">
-        <v>17.990896</v>
+        <v>17.826712</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03499756346077172</v>
+        <v>0.03531989091071668</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0687505426837372</v>
+        <v>0.06938373496669201</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.04836999893188477</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02069054035677187</v>
+        <v>0.02101373603480724</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-08 17:23:08</t>
+          <t>2026-09-09 17:21:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -36435,51 +36957,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>505.74</v>
+        <v>521.095</v>
       </c>
       <c r="F8" t="n">
-        <v>825607913472</v>
+        <v>850674515968</v>
       </c>
       <c r="G8" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="H8" t="n">
         <v>15.51307</v>
       </c>
       <c r="I8" t="n">
-        <v>129.0153</v>
+        <v>132.2576</v>
       </c>
       <c r="J8" t="n">
-        <v>32.600895</v>
+        <v>33.590706</v>
       </c>
       <c r="K8" t="n">
         <v>0.49</v>
       </c>
       <c r="L8" t="n">
-        <v>19.988085</v>
+        <v>20.594952</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007751018309803456</v>
+        <v>0.007561001352920292</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03067400245185273</v>
+        <v>0.02977013788272772</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.04836999893188477</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0173859998751126</v>
+        <v>-0.01859986104915705</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-08 17:23:08</t>
+          <t>2026-09-09 17:21:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -36493,51 +37015,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>368.56</v>
+        <v>364.38</v>
       </c>
       <c r="F9" t="n">
-        <v>1753453821952</v>
+        <v>1733567184896</v>
       </c>
       <c r="G9" t="n">
-        <v>7.84</v>
+        <v>7.85</v>
       </c>
       <c r="H9" t="n">
-        <v>19.3879</v>
+        <v>19.38391</v>
       </c>
       <c r="I9" t="n">
-        <v>47.010204</v>
+        <v>46.417835</v>
       </c>
       <c r="J9" t="n">
-        <v>19.009796</v>
+        <v>18.798065</v>
       </c>
       <c r="K9" t="n">
         <v>0.35</v>
       </c>
       <c r="L9" t="n">
-        <v>19.678734</v>
+        <v>19.45555</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02127197742565661</v>
+        <v>0.02154344365771996</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05260446060342956</v>
+        <v>0.05319696470717383</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.04836999893188477</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004544458276464228</v>
+        <v>0.004826965775289065</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-08 17:23:08</t>
+          <t>2026-09-09 17:21:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -36551,10 +37073,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>76.77</v>
+        <v>76.03</v>
       </c>
       <c r="F10" t="n">
-        <v>319665635328</v>
+        <v>316584329216</v>
       </c>
       <c r="G10" t="n">
         <v>3.18</v>
@@ -36563,28 +37085,28 @@
         <v>3.82091</v>
       </c>
       <c r="I10" t="n">
-        <v>24.141508</v>
+        <v>23.908804</v>
       </c>
       <c r="J10" t="n">
-        <v>20.092072</v>
+        <v>19.898401</v>
       </c>
       <c r="K10" t="n">
         <v>1.45</v>
       </c>
       <c r="L10" t="n">
-        <v>6.6086535</v>
+        <v>6.544952</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04142243063696757</v>
+        <v>0.04182559515980534</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04977087403933829</v>
+        <v>0.05025529396290938</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04806000232696533</v>
+        <v>0.04836999893188477</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001710871712372955</v>
+        <v>0.001885295031024609</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuation_history.xlsx
+++ b/data/valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P622"/>
+  <dimension ref="A1:P631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36015,16 +36015,16 @@
         <v>9.858402</v>
       </c>
       <c r="M614" t="n">
-        <v>0.02768440413521913</v>
+        <v>0.0276844041352191</v>
       </c>
       <c r="N614" t="n">
         <v>0.0303722014333735</v>
       </c>
       <c r="O614" t="n">
-        <v>0.04836999893188477</v>
+        <v>0.0483699989318847</v>
       </c>
       <c r="P614" t="n">
-        <v>-0.01799779749851127</v>
+        <v>-0.0179977974985112</v>
       </c>
     </row>
     <row r="615">
@@ -36073,16 +36073,16 @@
         <v>20.594952</v>
       </c>
       <c r="M615" t="n">
-        <v>0.007561001352920292</v>
+        <v>0.0075610013529202</v>
       </c>
       <c r="N615" t="n">
-        <v>0.02977013788272772</v>
+        <v>0.0297701378827277</v>
       </c>
       <c r="O615" t="n">
-        <v>0.04836999893188477</v>
+        <v>0.0483699989318847</v>
       </c>
       <c r="P615" t="n">
-        <v>-0.01859986104915705</v>
+        <v>-0.018599861049157</v>
       </c>
     </row>
     <row r="616">
@@ -36131,16 +36131,16 @@
         <v>3.5097787</v>
       </c>
       <c r="M616" t="n">
-        <v>0.04928684627575277</v>
+        <v>0.0492868462757527</v>
       </c>
       <c r="N616" t="n">
-        <v>0.04120570522979398</v>
+        <v>0.0412057052297939</v>
       </c>
       <c r="O616" t="n">
-        <v>0.04836999893188477</v>
+        <v>0.0483699989318847</v>
       </c>
       <c r="P616" t="n">
-        <v>-0.00716429370209079</v>
+        <v>-0.0071642937020907</v>
       </c>
     </row>
     <row r="617">
@@ -36189,16 +36189,16 @@
         <v>19.45555</v>
       </c>
       <c r="M617" t="n">
-        <v>0.02154344365771996</v>
+        <v>0.0215434436577199</v>
       </c>
       <c r="N617" t="n">
-        <v>0.05319696470717383</v>
+        <v>0.0531969647071738</v>
       </c>
       <c r="O617" t="n">
-        <v>0.04836999893188477</v>
+        <v>0.0483699989318847</v>
       </c>
       <c r="P617" t="n">
-        <v>0.004826965775289065</v>
+        <v>0.004826965775289</v>
       </c>
     </row>
     <row r="618">
@@ -36247,16 +36247,16 @@
         <v>9.0073395</v>
       </c>
       <c r="M618" t="n">
-        <v>0.06066142883245022</v>
+        <v>0.0606614288324502</v>
       </c>
       <c r="N618" t="n">
-        <v>0.04523427127108837</v>
+        <v>0.0452342712710883</v>
       </c>
       <c r="O618" t="n">
-        <v>0.04836999893188477</v>
+        <v>0.0483699989318847</v>
       </c>
       <c r="P618" t="n">
-        <v>-0.003135727660796395</v>
+        <v>-0.0031357276607963</v>
       </c>
     </row>
     <row r="619">
@@ -36305,16 +36305,16 @@
         <v>7.295953</v>
       </c>
       <c r="M619" t="n">
-        <v>0.04063088008077222</v>
+        <v>0.0406308800807722</v>
       </c>
       <c r="N619" t="n">
-        <v>0.05348048769294313</v>
+        <v>0.0534804876929431</v>
       </c>
       <c r="O619" t="n">
-        <v>0.04836999893188477</v>
+        <v>0.0483699989318847</v>
       </c>
       <c r="P619" t="n">
-        <v>0.005110488761058365</v>
+        <v>0.0051104887610583</v>
       </c>
     </row>
     <row r="620">
@@ -36363,16 +36363,16 @@
         <v>11.001628</v>
       </c>
       <c r="M620" t="n">
-        <v>0.03646903284857114</v>
+        <v>0.0364690328485711</v>
       </c>
       <c r="N620" t="n">
-        <v>0.04794727956879895</v>
+        <v>0.0479472795687989</v>
       </c>
       <c r="O620" t="n">
-        <v>0.04836999893188477</v>
+        <v>0.0483699989318847</v>
       </c>
       <c r="P620" t="n">
-        <v>-0.0004227193630858203</v>
+        <v>-0.0004227193630858</v>
       </c>
     </row>
     <row r="621">
@@ -36421,16 +36421,16 @@
         <v>6.544952</v>
       </c>
       <c r="M621" t="n">
-        <v>0.04182559515980534</v>
+        <v>0.0418255951598053</v>
       </c>
       <c r="N621" t="n">
-        <v>0.05025529396290938</v>
+        <v>0.0502552939629093</v>
       </c>
       <c r="O621" t="n">
-        <v>0.04836999893188477</v>
+        <v>0.0483699989318847</v>
       </c>
       <c r="P621" t="n">
-        <v>0.001885295031024609</v>
+        <v>0.0018852950310246</v>
       </c>
     </row>
     <row r="622">
@@ -36479,16 +36479,538 @@
         <v>17.826712</v>
       </c>
       <c r="M622" t="n">
-        <v>0.03531989091071668</v>
+        <v>0.0353198909107166</v>
       </c>
       <c r="N622" t="n">
         <v>0.06938373496669201</v>
       </c>
       <c r="O622" t="n">
-        <v>0.04836999893188477</v>
+        <v>0.0483699989318847</v>
       </c>
       <c r="P622" t="n">
-        <v>0.02101373603480724</v>
+        <v>0.0210137360348072</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:17:28</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E623" t="n">
+        <v>326.57</v>
+      </c>
+      <c r="F623" t="n">
+        <v>4766021713920</v>
+      </c>
+      <c r="G623" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H623" t="n">
+        <v>9.57757</v>
+      </c>
+      <c r="I623" t="n">
+        <v>37.40779</v>
+      </c>
+      <c r="J623" t="n">
+        <v>34.097378</v>
+      </c>
+      <c r="K623" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="L623" t="n">
+        <v>10.209484</v>
+      </c>
+      <c r="M623" t="n">
+        <v>0.02673240040420125</v>
+      </c>
+      <c r="N623" t="n">
+        <v>0.02932777046268794</v>
+      </c>
+      <c r="O623" t="n">
+        <v>0.04943999767303467</v>
+      </c>
+      <c r="P623" t="n">
+        <v>-0.02011222721034673</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:17:28</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E624" t="n">
+        <v>503.6</v>
+      </c>
+      <c r="F624" t="n">
+        <v>822114451456</v>
+      </c>
+      <c r="G624" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H624" t="n">
+        <v>15.63111</v>
+      </c>
+      <c r="I624" t="n">
+        <v>128.79796</v>
+      </c>
+      <c r="J624" t="n">
+        <v>32.2178</v>
+      </c>
+      <c r="K624" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L624" t="n">
+        <v>19.90351</v>
+      </c>
+      <c r="M624" t="n">
+        <v>0.007764098490865766</v>
+      </c>
+      <c r="N624" t="n">
+        <v>0.03103874106433677</v>
+      </c>
+      <c r="O624" t="n">
+        <v>0.04943999767303467</v>
+      </c>
+      <c r="P624" t="n">
+        <v>-0.0184012566086979</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:17:28</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E625" t="n">
+        <v>251.89</v>
+      </c>
+      <c r="F625" t="n">
+        <v>2716964487168</v>
+      </c>
+      <c r="G625" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="H625" t="n">
+        <v>10.40032</v>
+      </c>
+      <c r="I625" t="n">
+        <v>20.280998</v>
+      </c>
+      <c r="J625" t="n">
+        <v>24.219446</v>
+      </c>
+      <c r="K625" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L625" t="n">
+        <v>3.5026872</v>
+      </c>
+      <c r="M625" t="n">
+        <v>0.04930723728611696</v>
+      </c>
+      <c r="N625" t="n">
+        <v>0.04128913414585732</v>
+      </c>
+      <c r="O625" t="n">
+        <v>0.04943999767303467</v>
+      </c>
+      <c r="P625" t="n">
+        <v>-0.008150863527177345</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:17:28</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E626" t="n">
+        <v>360.83</v>
+      </c>
+      <c r="F626" t="n">
+        <v>1716677640192</v>
+      </c>
+      <c r="G626" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H626" t="n">
+        <v>19.38391</v>
+      </c>
+      <c r="I626" t="n">
+        <v>46.08301</v>
+      </c>
+      <c r="J626" t="n">
+        <v>18.614923</v>
+      </c>
+      <c r="K626" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L626" t="n">
+        <v>19.266</v>
+      </c>
+      <c r="M626" t="n">
+        <v>0.02169996951472993</v>
+      </c>
+      <c r="N626" t="n">
+        <v>0.05372033921791425</v>
+      </c>
+      <c r="O626" t="n">
+        <v>0.04943999767303467</v>
+      </c>
+      <c r="P626" t="n">
+        <v>0.004280341544879586</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:17:28</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E627" t="n">
+        <v>330.39</v>
+      </c>
+      <c r="F627" t="n">
+        <v>4040648556544</v>
+      </c>
+      <c r="G627" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H627" t="n">
+        <v>14.87383</v>
+      </c>
+      <c r="I627" t="n">
+        <v>16.577522</v>
+      </c>
+      <c r="J627" t="n">
+        <v>22.212841</v>
+      </c>
+      <c r="K627" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L627" t="n">
+        <v>9.062473000000001</v>
+      </c>
+      <c r="M627" t="n">
+        <v>0.06032264899058688</v>
+      </c>
+      <c r="N627" t="n">
+        <v>0.04501900783922032</v>
+      </c>
+      <c r="O627" t="n">
+        <v>0.04943999767303467</v>
+      </c>
+      <c r="P627" t="n">
+        <v>-0.004420989833814351</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:17:28</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E628" t="n">
+        <v>644.38</v>
+      </c>
+      <c r="F628" t="n">
+        <v>1641561980928</v>
+      </c>
+      <c r="G628" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H628" t="n">
+        <v>34.95966</v>
+      </c>
+      <c r="I628" t="n">
+        <v>24.279577</v>
+      </c>
+      <c r="J628" t="n">
+        <v>18.432102</v>
+      </c>
+      <c r="K628" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L628" t="n">
+        <v>7.192042</v>
+      </c>
+      <c r="M628" t="n">
+        <v>0.04118687730842049</v>
+      </c>
+      <c r="N628" t="n">
+        <v>0.05425317359322139</v>
+      </c>
+      <c r="O628" t="n">
+        <v>0.04943999767303467</v>
+      </c>
+      <c r="P628" t="n">
+        <v>0.004813175920186721</v>
+      </c>
+    </row>
+    <row r=